--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,72 +22,72 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>112</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>07 - Health</t>
   </si>
   <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -139,69 +139,69 @@
     <t>11330</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>114</t>
   </si>
   <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,27 +286,27 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,60 +340,60 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,21 +496,21 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>02 - Defence</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,42 +655,42 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,42 +811,42 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1219,12 +1219,12 @@
     <t>33110</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,13 +1863,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1909,13 +1909,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -1932,13 +1932,13 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -1978,13 +1978,13 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
@@ -2001,13 +2001,13 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
@@ -2024,13 +2024,13 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>24</v>
@@ -2047,19 +2047,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2070,13 +2070,13 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>24</v>
@@ -2093,13 +2093,13 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -2116,13 +2116,13 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
         <v>39</v>
@@ -2139,13 +2139,13 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>46</v>
@@ -2162,13 +2162,13 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
         <v>46</v>
@@ -2191,13 +2191,13 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
         <v>53</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>54</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2214,13 +2214,13 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" t="s">
         <v>53</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>54</v>
-      </c>
-      <c r="G18" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" t="s">
         <v>54</v>
-      </c>
-      <c r="G19" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2254,19 +2254,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
         <v>54</v>
-      </c>
-      <c r="G20" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2283,13 +2283,13 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" t="s">
         <v>53</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>54</v>
-      </c>
-      <c r="G21" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2300,19 +2300,19 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
         <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
         <v>64</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2346,19 +2346,19 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
         <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2369,19 +2369,19 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
         <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2392,19 +2392,19 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
         <v>64</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2415,19 +2415,19 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
         <v>64</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2438,19 +2438,19 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
         <v>64</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2461,19 +2461,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
         <v>64</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2490,13 +2490,13 @@
         <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s">
         <v>64</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2507,19 +2507,19 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
         <v>76</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2530,19 +2530,19 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
         <v>76</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2553,19 +2553,19 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s">
         <v>76</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2576,19 +2576,19 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
         <v>76</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2599,19 +2599,19 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
         <v>76</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E36" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
         <v>76</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2645,16 +2645,16 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" t="s">
         <v>83</v>
-      </c>
-      <c r="D37" t="s">
-        <v>31</v>
-      </c>
-      <c r="E37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2665,16 +2665,16 @@
         <v>8</v>
       </c>
       <c r="C38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
         <v>83</v>
-      </c>
-      <c r="D38" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2685,16 +2685,16 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
         <v>83</v>
-      </c>
-      <c r="D39" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2705,16 +2705,16 @@
         <v>8</v>
       </c>
       <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
         <v>83</v>
-      </c>
-      <c r="D40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2725,16 +2725,16 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="D41" t="s">
         <v>52</v>
       </c>
       <c r="E41" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G41" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2745,16 +2745,16 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
         <v>83</v>
-      </c>
-      <c r="D42" t="s">
-        <v>57</v>
-      </c>
-      <c r="E42" t="s">
-        <v>58</v>
-      </c>
-      <c r="G42" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2785,16 +2785,16 @@
         <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G44" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2845,16 +2845,16 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E47" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G47" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2905,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E50" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G50" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E52" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G52" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2965,7 +2965,7 @@
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2974,7 +2974,7 @@
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3008,13 +3008,13 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F55" t="s">
         <v>115</v>
@@ -3031,13 +3031,13 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E56" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F56" t="s">
         <v>115</v>
@@ -3054,19 +3054,19 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F57" t="s">
         <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3077,13 +3077,13 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
         <v>115</v>
@@ -3100,13 +3100,13 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E59" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
         <v>115</v>
@@ -3123,13 +3123,13 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E60" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F60" t="s">
         <v>115</v>
@@ -3146,13 +3146,13 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E61" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
@@ -3169,13 +3169,13 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E62" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
@@ -3192,13 +3192,13 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
         <v>133</v>
       </c>
       <c r="E63" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
@@ -3215,13 +3215,13 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D64" t="s">
         <v>133</v>
       </c>
       <c r="E64" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
@@ -3238,13 +3238,13 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F65" t="s">
         <v>115</v>
@@ -3284,13 +3284,13 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E67" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
@@ -3353,13 +3353,13 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E70" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F70" t="s">
         <v>115</v>
@@ -3376,13 +3376,13 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E71" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F71" t="s">
         <v>115</v>
@@ -3422,19 +3422,19 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E73" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="F73" t="s">
         <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3445,19 +3445,19 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E74" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="F74" t="s">
         <v>115</v>
       </c>
       <c r="G74" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3468,19 +3468,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E75" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="F75" t="s">
         <v>115</v>
       </c>
       <c r="G75" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3491,19 +3491,19 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E76" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="F76" t="s">
         <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3514,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E77" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="F77" t="s">
         <v>115</v>
       </c>
       <c r="G77" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3537,19 +3537,19 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E78" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="F78" t="s">
         <v>115</v>
       </c>
       <c r="G78" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3560,19 +3560,19 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E79" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="F79" t="s">
         <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3583,19 +3583,19 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F80" t="s">
         <v>115</v>
       </c>
       <c r="G80" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3606,19 +3606,19 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F81" t="s">
         <v>115</v>
       </c>
       <c r="G81" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3629,19 +3629,19 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E82" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F82" t="s">
         <v>115</v>
       </c>
       <c r="G82" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3675,13 +3675,13 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E84" t="s">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="F84" t="s">
         <v>115</v>
@@ -3698,13 +3698,13 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D85" t="s">
         <v>173</v>
       </c>
       <c r="E85" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F85" t="s">
         <v>115</v>
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E86" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F86" t="s">
         <v>115</v>
       </c>
       <c r="G86" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,13 +3744,13 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D87" t="s">
         <v>173</v>
       </c>
       <c r="E87" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F87" t="s">
         <v>115</v>
@@ -3767,13 +3767,13 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E88" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F88" t="s">
         <v>115</v>
@@ -3790,13 +3790,13 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D89" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E89" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F89" t="s">
         <v>115</v>
@@ -3813,19 +3813,19 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E90" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F90" t="s">
         <v>115</v>
       </c>
       <c r="G90" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3836,19 +3836,19 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F91" t="s">
         <v>115</v>
       </c>
       <c r="G91" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3859,19 +3859,19 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F92" t="s">
         <v>115</v>
       </c>
       <c r="G92" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3882,13 +3882,13 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E93" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F93" t="s">
         <v>115</v>
@@ -3905,19 +3905,19 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E94" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F94" t="s">
         <v>115</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3928,13 +3928,13 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E95" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="F95" t="s">
         <v>115</v>
@@ -3951,19 +3951,19 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D96" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E96" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F96" t="s">
         <v>192</v>
       </c>
       <c r="G96" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3974,19 +3974,19 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D97" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E97" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F97" t="s">
         <v>192</v>
       </c>
       <c r="G97" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3997,19 +3997,19 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>112</v>
+        <v>195</v>
       </c>
       <c r="D98" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E98" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F98" t="s">
         <v>192</v>
       </c>
       <c r="G98" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4020,19 +4020,19 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D99" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E99" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F99" t="s">
         <v>192</v>
       </c>
       <c r="G99" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="D100" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E100" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="F100" t="s">
         <v>192</v>
       </c>
       <c r="G100" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4066,19 +4066,19 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E101" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F101" t="s">
         <v>192</v>
       </c>
       <c r="G101" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4095,10 +4095,10 @@
         <v>203</v>
       </c>
       <c r="E102" t="s">
+        <v>184</v>
+      </c>
+      <c r="G102" t="s">
         <v>204</v>
-      </c>
-      <c r="G102" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4115,10 +4115,10 @@
         <v>203</v>
       </c>
       <c r="E103" t="s">
+        <v>184</v>
+      </c>
+      <c r="G103" t="s">
         <v>204</v>
-      </c>
-      <c r="G103" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4135,10 +4135,10 @@
         <v>203</v>
       </c>
       <c r="E104" t="s">
+        <v>184</v>
+      </c>
+      <c r="G104" t="s">
         <v>204</v>
-      </c>
-      <c r="G104" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4149,16 +4149,16 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D105" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E105" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="G105" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4175,10 +4175,10 @@
         <v>203</v>
       </c>
       <c r="E106" t="s">
+        <v>184</v>
+      </c>
+      <c r="G106" t="s">
         <v>204</v>
-      </c>
-      <c r="G106" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4189,16 +4189,16 @@
         <v>8</v>
       </c>
       <c r="C107" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D107" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E107" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G107" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4209,16 +4209,16 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D108" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E108" t="s">
-        <v>214</v>
+        <v>184</v>
       </c>
       <c r="G108" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4229,16 +4229,16 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="D109" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E109" t="s">
-        <v>217</v>
+        <v>92</v>
       </c>
       <c r="G109" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4249,16 +4249,16 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="D110" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E110" t="s">
-        <v>220</v>
+        <v>92</v>
       </c>
       <c r="G110" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4275,10 +4275,10 @@
         <v>203</v>
       </c>
       <c r="E111" t="s">
+        <v>184</v>
+      </c>
+      <c r="G111" t="s">
         <v>204</v>
-      </c>
-      <c r="G111" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4289,16 +4289,16 @@
         <v>8</v>
       </c>
       <c r="C112" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="D112" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G112" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4309,7 +4309,7 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="D113" t="s">
         <v>143</v>
@@ -4318,7 +4318,7 @@
         <v>114</v>
       </c>
       <c r="G113" t="s">
-        <v>116</v>
+        <v>204</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4329,16 +4329,16 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="D114" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E114" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="G114" t="s">
-        <v>126</v>
+        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4349,16 +4349,16 @@
         <v>8</v>
       </c>
       <c r="C115" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D115" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E115" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G115" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4369,16 +4369,16 @@
         <v>8</v>
       </c>
       <c r="C116" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="D116" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E116" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G116" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4389,16 +4389,16 @@
         <v>8</v>
       </c>
       <c r="C117" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="D117" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G117" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4409,16 +4409,16 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="D118" t="s">
         <v>234</v>
       </c>
       <c r="E118" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G118" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4429,16 +4429,16 @@
         <v>8</v>
       </c>
       <c r="C119" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D119" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E119" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G119" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4449,16 +4449,16 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
+        <v>170</v>
+      </c>
+      <c r="D120" t="s">
+        <v>171</v>
+      </c>
+      <c r="E120" t="s">
+        <v>114</v>
+      </c>
+      <c r="G120" t="s">
         <v>237</v>
-      </c>
-      <c r="D120" t="s">
-        <v>170</v>
-      </c>
-      <c r="E120" t="s">
-        <v>171</v>
-      </c>
-      <c r="G120" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4469,7 +4469,7 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>237</v>
+        <v>112</v>
       </c>
       <c r="D121" t="s">
         <v>143</v>
@@ -4478,7 +4478,7 @@
         <v>114</v>
       </c>
       <c r="G121" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>8</v>
       </c>
       <c r="C122" t="s">
+        <v>170</v>
+      </c>
+      <c r="D122" t="s">
+        <v>171</v>
+      </c>
+      <c r="E122" t="s">
+        <v>114</v>
+      </c>
+      <c r="G122" t="s">
         <v>237</v>
-      </c>
-      <c r="D122" t="s">
-        <v>170</v>
-      </c>
-      <c r="E122" t="s">
-        <v>171</v>
-      </c>
-      <c r="G122" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
+        <v>170</v>
+      </c>
+      <c r="D123" t="s">
+        <v>171</v>
+      </c>
+      <c r="E123" t="s">
+        <v>114</v>
+      </c>
+      <c r="G123" t="s">
         <v>237</v>
-      </c>
-      <c r="D123" t="s">
-        <v>170</v>
-      </c>
-      <c r="E123" t="s">
-        <v>171</v>
-      </c>
-      <c r="G123" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4529,16 +4529,16 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
+        <v>242</v>
+      </c>
+      <c r="D124" t="s">
+        <v>243</v>
+      </c>
+      <c r="E124" t="s">
+        <v>165</v>
+      </c>
+      <c r="G124" t="s">
         <v>237</v>
-      </c>
-      <c r="D124" t="s">
-        <v>242</v>
-      </c>
-      <c r="E124" t="s">
-        <v>243</v>
-      </c>
-      <c r="G124" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4549,16 +4549,16 @@
         <v>8</v>
       </c>
       <c r="C125" t="s">
+        <v>242</v>
+      </c>
+      <c r="D125" t="s">
+        <v>243</v>
+      </c>
+      <c r="E125" t="s">
+        <v>165</v>
+      </c>
+      <c r="G125" t="s">
         <v>237</v>
-      </c>
-      <c r="D125" t="s">
-        <v>242</v>
-      </c>
-      <c r="E125" t="s">
-        <v>243</v>
-      </c>
-      <c r="G125" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4569,16 +4569,16 @@
         <v>8</v>
       </c>
       <c r="C126" t="s">
+        <v>242</v>
+      </c>
+      <c r="D126" t="s">
+        <v>243</v>
+      </c>
+      <c r="E126" t="s">
+        <v>165</v>
+      </c>
+      <c r="G126" t="s">
         <v>237</v>
-      </c>
-      <c r="D126" t="s">
-        <v>242</v>
-      </c>
-      <c r="E126" t="s">
-        <v>243</v>
-      </c>
-      <c r="G126" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4589,16 +4589,16 @@
         <v>8</v>
       </c>
       <c r="C127" t="s">
+        <v>242</v>
+      </c>
+      <c r="D127" t="s">
+        <v>243</v>
+      </c>
+      <c r="E127" t="s">
+        <v>165</v>
+      </c>
+      <c r="G127" t="s">
         <v>237</v>
-      </c>
-      <c r="D127" t="s">
-        <v>242</v>
-      </c>
-      <c r="E127" t="s">
-        <v>243</v>
-      </c>
-      <c r="G127" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4609,16 +4609,16 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
+        <v>242</v>
+      </c>
+      <c r="D128" t="s">
+        <v>243</v>
+      </c>
+      <c r="E128" t="s">
+        <v>165</v>
+      </c>
+      <c r="G128" t="s">
         <v>237</v>
-      </c>
-      <c r="D128" t="s">
-        <v>242</v>
-      </c>
-      <c r="E128" t="s">
-        <v>243</v>
-      </c>
-      <c r="G128" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D129" t="s">
         <v>249</v>
       </c>
       <c r="E129" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
       <c r="G129" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D130" t="s">
         <v>251</v>
       </c>
       <c r="E130" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
       <c r="G130" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D131" t="s">
         <v>253</v>
       </c>
       <c r="E131" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
       <c r="G131" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,16 +4689,16 @@
         <v>8</v>
       </c>
       <c r="C132" t="s">
+        <v>255</v>
+      </c>
+      <c r="D132" t="s">
+        <v>256</v>
+      </c>
+      <c r="E132" t="s">
+        <v>165</v>
+      </c>
+      <c r="G132" t="s">
         <v>237</v>
-      </c>
-      <c r="D132" t="s">
-        <v>255</v>
-      </c>
-      <c r="E132" t="s">
-        <v>256</v>
-      </c>
-      <c r="G132" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4709,16 +4709,16 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
+        <v>189</v>
+      </c>
+      <c r="D133" t="s">
+        <v>190</v>
+      </c>
+      <c r="E133" t="s">
+        <v>114</v>
+      </c>
+      <c r="G133" t="s">
         <v>237</v>
-      </c>
-      <c r="D133" t="s">
-        <v>189</v>
-      </c>
-      <c r="E133" t="s">
-        <v>190</v>
-      </c>
-      <c r="G133" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4729,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="C134" t="s">
+        <v>175</v>
+      </c>
+      <c r="D134" t="s">
+        <v>176</v>
+      </c>
+      <c r="E134" t="s">
+        <v>165</v>
+      </c>
+      <c r="G134" t="s">
         <v>259</v>
-      </c>
-      <c r="D134" t="s">
-        <v>175</v>
-      </c>
-      <c r="E134" t="s">
-        <v>176</v>
-      </c>
-      <c r="G134" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4749,16 +4749,16 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
+        <v>175</v>
+      </c>
+      <c r="D135" t="s">
+        <v>176</v>
+      </c>
+      <c r="E135" t="s">
+        <v>165</v>
+      </c>
+      <c r="G135" t="s">
         <v>259</v>
-      </c>
-      <c r="D135" t="s">
-        <v>175</v>
-      </c>
-      <c r="E135" t="s">
-        <v>176</v>
-      </c>
-      <c r="G135" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4769,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="C136" t="s">
+        <v>175</v>
+      </c>
+      <c r="D136" t="s">
+        <v>176</v>
+      </c>
+      <c r="E136" t="s">
+        <v>165</v>
+      </c>
+      <c r="G136" t="s">
         <v>259</v>
-      </c>
-      <c r="D136" t="s">
-        <v>175</v>
-      </c>
-      <c r="E136" t="s">
-        <v>176</v>
-      </c>
-      <c r="G136" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4789,16 +4789,16 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
+        <v>175</v>
+      </c>
+      <c r="D137" t="s">
+        <v>176</v>
+      </c>
+      <c r="E137" t="s">
+        <v>165</v>
+      </c>
+      <c r="G137" t="s">
         <v>259</v>
-      </c>
-      <c r="D137" t="s">
-        <v>175</v>
-      </c>
-      <c r="E137" t="s">
-        <v>176</v>
-      </c>
-      <c r="G137" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4809,16 +4809,16 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
+        <v>175</v>
+      </c>
+      <c r="D138" t="s">
+        <v>176</v>
+      </c>
+      <c r="E138" t="s">
+        <v>165</v>
+      </c>
+      <c r="G138" t="s">
         <v>259</v>
-      </c>
-      <c r="D138" t="s">
-        <v>175</v>
-      </c>
-      <c r="E138" t="s">
-        <v>176</v>
-      </c>
-      <c r="G138" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4829,16 +4829,16 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
+        <v>265</v>
+      </c>
+      <c r="D139" t="s">
+        <v>266</v>
+      </c>
+      <c r="E139" t="s">
+        <v>225</v>
+      </c>
+      <c r="G139" t="s">
         <v>259</v>
-      </c>
-      <c r="D139" t="s">
-        <v>265</v>
-      </c>
-      <c r="E139" t="s">
-        <v>266</v>
-      </c>
-      <c r="G139" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
+        <v>175</v>
+      </c>
+      <c r="D140" t="s">
+        <v>176</v>
+      </c>
+      <c r="E140" t="s">
+        <v>165</v>
+      </c>
+      <c r="G140" t="s">
         <v>259</v>
-      </c>
-      <c r="D140" t="s">
-        <v>175</v>
-      </c>
-      <c r="E140" t="s">
-        <v>176</v>
-      </c>
-      <c r="G140" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4875,13 +4875,13 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
+        <v>165</v>
+      </c>
+      <c r="F141" t="s">
         <v>271</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>272</v>
-      </c>
-      <c r="G141" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4898,13 +4898,13 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
+        <v>165</v>
+      </c>
+      <c r="F142" t="s">
         <v>271</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>272</v>
-      </c>
-      <c r="G142" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4915,19 +4915,19 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E143" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F143" t="s">
+        <v>271</v>
+      </c>
+      <c r="G143" t="s">
         <v>272</v>
-      </c>
-      <c r="G143" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4938,19 +4938,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E144" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F144" t="s">
+        <v>271</v>
+      </c>
+      <c r="G144" t="s">
         <v>272</v>
-      </c>
-      <c r="G144" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4961,19 +4961,19 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E145" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F145" t="s">
+        <v>271</v>
+      </c>
+      <c r="G145" t="s">
         <v>272</v>
-      </c>
-      <c r="G145" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4990,13 +4990,13 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
+        <v>165</v>
+      </c>
+      <c r="F146" t="s">
         <v>271</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>272</v>
-      </c>
-      <c r="G146" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5013,13 +5013,13 @@
         <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F147" t="s">
         <v>281</v>
       </c>
       <c r="G147" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5036,13 +5036,13 @@
         <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F148" t="s">
         <v>281</v>
       </c>
       <c r="G148" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5059,13 +5059,13 @@
         <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F149" t="s">
         <v>281</v>
       </c>
       <c r="G149" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5082,13 +5082,13 @@
         <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F150" t="s">
         <v>281</v>
       </c>
       <c r="G150" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5105,13 +5105,13 @@
         <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F151" t="s">
         <v>281</v>
       </c>
       <c r="G151" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5128,13 +5128,13 @@
         <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F152" t="s">
         <v>281</v>
       </c>
       <c r="G152" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5151,13 +5151,13 @@
         <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F153" t="s">
         <v>281</v>
       </c>
       <c r="G153" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5174,13 +5174,13 @@
         <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F154" t="s">
         <v>281</v>
       </c>
       <c r="G154" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5197,13 +5197,13 @@
         <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F155" t="s">
         <v>281</v>
       </c>
       <c r="G155" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5220,13 +5220,13 @@
         <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F156" t="s">
         <v>291</v>
       </c>
       <c r="G156" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5243,13 +5243,13 @@
         <v>293</v>
       </c>
       <c r="E157" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F157" t="s">
         <v>291</v>
       </c>
       <c r="G157" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5266,13 +5266,13 @@
         <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F158" t="s">
         <v>291</v>
       </c>
       <c r="G158" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5289,13 +5289,13 @@
         <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F159" t="s">
         <v>291</v>
       </c>
       <c r="G159" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5312,13 +5312,13 @@
         <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F160" t="s">
         <v>291</v>
       </c>
       <c r="G160" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5335,13 +5335,13 @@
         <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F161" t="s">
         <v>291</v>
       </c>
       <c r="G161" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5358,13 +5358,13 @@
         <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F162" t="s">
         <v>299</v>
       </c>
       <c r="G162" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5381,13 +5381,13 @@
         <v>301</v>
       </c>
       <c r="E163" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F163" t="s">
         <v>302</v>
       </c>
       <c r="G163" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5404,13 +5404,13 @@
         <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F164" t="s">
         <v>304</v>
       </c>
       <c r="G164" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5427,13 +5427,13 @@
         <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F165" t="s">
         <v>304</v>
       </c>
       <c r="G165" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5450,13 +5450,13 @@
         <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F166" t="s">
         <v>304</v>
       </c>
       <c r="G166" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5473,13 +5473,13 @@
         <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F167" t="s">
         <v>304</v>
       </c>
       <c r="G167" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5496,13 +5496,13 @@
         <v>309</v>
       </c>
       <c r="E168" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F168" t="s">
         <v>304</v>
       </c>
       <c r="G168" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5519,13 +5519,13 @@
         <v>309</v>
       </c>
       <c r="E169" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F169" t="s">
         <v>304</v>
       </c>
       <c r="G169" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5542,13 +5542,13 @@
         <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F170" t="s">
         <v>304</v>
       </c>
       <c r="G170" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5559,16 +5559,16 @@
         <v>8</v>
       </c>
       <c r="C171" t="s">
+        <v>163</v>
+      </c>
+      <c r="D171" t="s">
+        <v>164</v>
+      </c>
+      <c r="E171" t="s">
+        <v>165</v>
+      </c>
+      <c r="G171" t="s">
         <v>313</v>
-      </c>
-      <c r="D171" t="s">
-        <v>163</v>
-      </c>
-      <c r="E171" t="s">
-        <v>164</v>
-      </c>
-      <c r="G171" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5579,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
+        <v>118</v>
+      </c>
+      <c r="D172" t="s">
+        <v>119</v>
+      </c>
+      <c r="E172" t="s">
+        <v>114</v>
+      </c>
+      <c r="G172" t="s">
         <v>313</v>
-      </c>
-      <c r="D172" t="s">
-        <v>118</v>
-      </c>
-      <c r="E172" t="s">
-        <v>119</v>
-      </c>
-      <c r="G172" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5599,16 +5599,16 @@
         <v>8</v>
       </c>
       <c r="C173" t="s">
+        <v>163</v>
+      </c>
+      <c r="D173" t="s">
+        <v>164</v>
+      </c>
+      <c r="E173" t="s">
+        <v>165</v>
+      </c>
+      <c r="G173" t="s">
         <v>313</v>
-      </c>
-      <c r="D173" t="s">
-        <v>163</v>
-      </c>
-      <c r="E173" t="s">
-        <v>164</v>
-      </c>
-      <c r="G173" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5619,16 +5619,16 @@
         <v>8</v>
       </c>
       <c r="C174" t="s">
+        <v>163</v>
+      </c>
+      <c r="D174" t="s">
+        <v>164</v>
+      </c>
+      <c r="E174" t="s">
+        <v>165</v>
+      </c>
+      <c r="G174" t="s">
         <v>313</v>
-      </c>
-      <c r="D174" t="s">
-        <v>163</v>
-      </c>
-      <c r="E174" t="s">
-        <v>164</v>
-      </c>
-      <c r="G174" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>8</v>
       </c>
       <c r="C175" t="s">
+        <v>163</v>
+      </c>
+      <c r="D175" t="s">
+        <v>164</v>
+      </c>
+      <c r="E175" t="s">
+        <v>165</v>
+      </c>
+      <c r="G175" t="s">
         <v>313</v>
-      </c>
-      <c r="D175" t="s">
-        <v>163</v>
-      </c>
-      <c r="E175" t="s">
-        <v>164</v>
-      </c>
-      <c r="G175" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>8</v>
       </c>
       <c r="C176" t="s">
+        <v>163</v>
+      </c>
+      <c r="D176" t="s">
+        <v>164</v>
+      </c>
+      <c r="E176" t="s">
+        <v>165</v>
+      </c>
+      <c r="G176" t="s">
         <v>313</v>
-      </c>
-      <c r="D176" t="s">
-        <v>163</v>
-      </c>
-      <c r="E176" t="s">
-        <v>164</v>
-      </c>
-      <c r="G176" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5679,16 +5679,16 @@
         <v>8</v>
       </c>
       <c r="C177" t="s">
+        <v>163</v>
+      </c>
+      <c r="D177" t="s">
+        <v>164</v>
+      </c>
+      <c r="E177" t="s">
+        <v>165</v>
+      </c>
+      <c r="G177" t="s">
         <v>320</v>
-      </c>
-      <c r="D177" t="s">
-        <v>163</v>
-      </c>
-      <c r="E177" t="s">
-        <v>164</v>
-      </c>
-      <c r="G177" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5699,16 +5699,16 @@
         <v>8</v>
       </c>
       <c r="C178" t="s">
+        <v>163</v>
+      </c>
+      <c r="D178" t="s">
+        <v>164</v>
+      </c>
+      <c r="E178" t="s">
+        <v>165</v>
+      </c>
+      <c r="G178" t="s">
         <v>320</v>
-      </c>
-      <c r="D178" t="s">
-        <v>163</v>
-      </c>
-      <c r="E178" t="s">
-        <v>164</v>
-      </c>
-      <c r="G178" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5719,16 +5719,16 @@
         <v>8</v>
       </c>
       <c r="C179" t="s">
+        <v>163</v>
+      </c>
+      <c r="D179" t="s">
+        <v>164</v>
+      </c>
+      <c r="E179" t="s">
+        <v>165</v>
+      </c>
+      <c r="G179" t="s">
         <v>320</v>
-      </c>
-      <c r="D179" t="s">
-        <v>163</v>
-      </c>
-      <c r="E179" t="s">
-        <v>164</v>
-      </c>
-      <c r="G179" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5739,16 +5739,16 @@
         <v>8</v>
       </c>
       <c r="C180" t="s">
+        <v>163</v>
+      </c>
+      <c r="D180" t="s">
+        <v>164</v>
+      </c>
+      <c r="E180" t="s">
+        <v>165</v>
+      </c>
+      <c r="G180" t="s">
         <v>320</v>
-      </c>
-      <c r="D180" t="s">
-        <v>163</v>
-      </c>
-      <c r="E180" t="s">
-        <v>164</v>
-      </c>
-      <c r="G180" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5765,13 +5765,13 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
+        <v>165</v>
+      </c>
+      <c r="F181" t="s">
         <v>327</v>
       </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
         <v>328</v>
-      </c>
-      <c r="G181" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5788,13 +5788,13 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
+        <v>165</v>
+      </c>
+      <c r="F182" t="s">
         <v>327</v>
       </c>
-      <c r="F182" t="s">
+      <c r="G182" t="s">
         <v>328</v>
-      </c>
-      <c r="G182" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5811,13 +5811,13 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
+        <v>165</v>
+      </c>
+      <c r="F183" t="s">
         <v>327</v>
       </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
         <v>328</v>
-      </c>
-      <c r="G183" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5834,13 +5834,13 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
+        <v>165</v>
+      </c>
+      <c r="F184" t="s">
         <v>327</v>
       </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
         <v>328</v>
-      </c>
-      <c r="G184" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5857,13 +5857,13 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
+        <v>165</v>
+      </c>
+      <c r="F185" t="s">
         <v>327</v>
       </c>
-      <c r="F185" t="s">
+      <c r="G185" t="s">
         <v>328</v>
-      </c>
-      <c r="G185" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5880,13 +5880,13 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
+        <v>165</v>
+      </c>
+      <c r="F186" t="s">
         <v>327</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>328</v>
-      </c>
-      <c r="G186" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5903,13 +5903,13 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
+        <v>165</v>
+      </c>
+      <c r="F187" t="s">
         <v>327</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>328</v>
-      </c>
-      <c r="G187" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5926,13 +5926,13 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
+        <v>165</v>
+      </c>
+      <c r="F188" t="s">
         <v>327</v>
       </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>328</v>
-      </c>
-      <c r="G188" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5949,13 +5949,13 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
+        <v>165</v>
+      </c>
+      <c r="F189" t="s">
         <v>327</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>328</v>
-      </c>
-      <c r="G189" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5972,13 +5972,13 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
+        <v>165</v>
+      </c>
+      <c r="F190" t="s">
         <v>327</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>328</v>
-      </c>
-      <c r="G190" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5995,13 +5995,13 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
+        <v>165</v>
+      </c>
+      <c r="F191" t="s">
         <v>327</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>328</v>
-      </c>
-      <c r="G191" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6018,13 +6018,13 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
+        <v>165</v>
+      </c>
+      <c r="F192" t="s">
         <v>327</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>328</v>
-      </c>
-      <c r="G192" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="D193" t="s">
         <v>341</v>
       </c>
       <c r="E193" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F193" t="s">
+        <v>327</v>
+      </c>
+      <c r="G193" t="s">
         <v>328</v>
-      </c>
-      <c r="G193" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6064,13 +6064,13 @@
         <v>326</v>
       </c>
       <c r="E194" t="s">
+        <v>165</v>
+      </c>
+      <c r="F194" t="s">
         <v>327</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>328</v>
-      </c>
-      <c r="G194" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6087,13 +6087,13 @@
         <v>326</v>
       </c>
       <c r="E195" t="s">
+        <v>165</v>
+      </c>
+      <c r="F195" t="s">
         <v>327</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>328</v>
-      </c>
-      <c r="G195" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6110,13 +6110,13 @@
         <v>326</v>
       </c>
       <c r="E196" t="s">
+        <v>165</v>
+      </c>
+      <c r="F196" t="s">
         <v>327</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>328</v>
-      </c>
-      <c r="G196" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6133,13 +6133,13 @@
         <v>326</v>
       </c>
       <c r="E197" t="s">
+        <v>165</v>
+      </c>
+      <c r="F197" t="s">
         <v>327</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
         <v>328</v>
-      </c>
-      <c r="G197" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6156,13 +6156,13 @@
         <v>326</v>
       </c>
       <c r="E198" t="s">
+        <v>165</v>
+      </c>
+      <c r="F198" t="s">
         <v>327</v>
       </c>
-      <c r="F198" t="s">
+      <c r="G198" t="s">
         <v>328</v>
-      </c>
-      <c r="G198" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6179,13 +6179,13 @@
         <v>348</v>
       </c>
       <c r="E199" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F199" t="s">
         <v>349</v>
       </c>
       <c r="G199" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6202,13 +6202,13 @@
         <v>348</v>
       </c>
       <c r="E200" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F200" t="s">
         <v>349</v>
       </c>
       <c r="G200" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6225,13 +6225,13 @@
         <v>348</v>
       </c>
       <c r="E201" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F201" t="s">
         <v>349</v>
       </c>
       <c r="G201" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6248,13 +6248,13 @@
         <v>348</v>
       </c>
       <c r="E202" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F202" t="s">
         <v>349</v>
       </c>
       <c r="G202" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="D203" t="s">
         <v>341</v>
       </c>
       <c r="E203" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F203" t="s">
         <v>349</v>
       </c>
       <c r="G203" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6294,13 +6294,13 @@
         <v>348</v>
       </c>
       <c r="E204" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F204" t="s">
         <v>349</v>
       </c>
       <c r="G204" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6317,13 +6317,13 @@
         <v>356</v>
       </c>
       <c r="E205" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F205" t="s">
         <v>357</v>
       </c>
       <c r="G205" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6340,13 +6340,13 @@
         <v>356</v>
       </c>
       <c r="E206" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F206" t="s">
         <v>357</v>
       </c>
       <c r="G206" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6363,13 +6363,13 @@
         <v>356</v>
       </c>
       <c r="E207" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F207" t="s">
         <v>357</v>
       </c>
       <c r="G207" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="D208" t="s">
         <v>341</v>
       </c>
       <c r="E208" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F208" t="s">
         <v>357</v>
       </c>
       <c r="G208" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6409,13 +6409,13 @@
         <v>356</v>
       </c>
       <c r="E209" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F209" t="s">
         <v>357</v>
       </c>
       <c r="G209" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6432,13 +6432,13 @@
         <v>364</v>
       </c>
       <c r="E210" t="s">
+        <v>165</v>
+      </c>
+      <c r="F210" t="s">
         <v>365</v>
       </c>
-      <c r="F210" t="s">
+      <c r="G210" t="s">
         <v>366</v>
-      </c>
-      <c r="G210" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6455,13 +6455,13 @@
         <v>364</v>
       </c>
       <c r="E211" t="s">
+        <v>165</v>
+      </c>
+      <c r="F211" t="s">
         <v>365</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>366</v>
-      </c>
-      <c r="G211" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6478,13 +6478,13 @@
         <v>364</v>
       </c>
       <c r="E212" t="s">
+        <v>165</v>
+      </c>
+      <c r="F212" t="s">
         <v>365</v>
       </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>366</v>
-      </c>
-      <c r="G212" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6501,13 +6501,13 @@
         <v>364</v>
       </c>
       <c r="E213" t="s">
+        <v>165</v>
+      </c>
+      <c r="F213" t="s">
         <v>365</v>
       </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>366</v>
-      </c>
-      <c r="G213" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6524,13 +6524,13 @@
         <v>364</v>
       </c>
       <c r="E214" t="s">
+        <v>165</v>
+      </c>
+      <c r="F214" t="s">
         <v>365</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>366</v>
-      </c>
-      <c r="G214" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>363</v>
+        <v>325</v>
       </c>
       <c r="D215" t="s">
         <v>348</v>
       </c>
       <c r="E215" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F215" t="s">
+        <v>365</v>
+      </c>
+      <c r="G215" t="s">
         <v>366</v>
-      </c>
-      <c r="G215" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6570,13 +6570,13 @@
         <v>364</v>
       </c>
       <c r="E216" t="s">
+        <v>165</v>
+      </c>
+      <c r="F216" t="s">
         <v>365</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>366</v>
-      </c>
-      <c r="G216" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6593,13 +6593,13 @@
         <v>364</v>
       </c>
       <c r="E217" t="s">
+        <v>165</v>
+      </c>
+      <c r="F217" t="s">
         <v>365</v>
       </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
         <v>366</v>
-      </c>
-      <c r="G217" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6616,13 +6616,13 @@
         <v>364</v>
       </c>
       <c r="E218" t="s">
+        <v>165</v>
+      </c>
+      <c r="F218" t="s">
         <v>365</v>
       </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>366</v>
-      </c>
-      <c r="G218" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6639,13 +6639,13 @@
         <v>364</v>
       </c>
       <c r="E219" t="s">
+        <v>165</v>
+      </c>
+      <c r="F219" t="s">
         <v>365</v>
       </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>366</v>
-      </c>
-      <c r="G219" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>363</v>
+        <v>269</v>
       </c>
       <c r="D220" t="s">
         <v>309</v>
       </c>
       <c r="E220" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F220" t="s">
+        <v>365</v>
+      </c>
+      <c r="G220" t="s">
         <v>366</v>
-      </c>
-      <c r="G220" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6685,13 +6685,13 @@
         <v>364</v>
       </c>
       <c r="E221" t="s">
+        <v>165</v>
+      </c>
+      <c r="F221" t="s">
         <v>365</v>
       </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>366</v>
-      </c>
-      <c r="G221" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6708,13 +6708,13 @@
         <v>364</v>
       </c>
       <c r="E222" t="s">
+        <v>165</v>
+      </c>
+      <c r="F222" t="s">
         <v>365</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>366</v>
-      </c>
-      <c r="G222" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6731,13 +6731,13 @@
         <v>364</v>
       </c>
       <c r="E223" t="s">
+        <v>165</v>
+      </c>
+      <c r="F223" t="s">
         <v>365</v>
       </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>366</v>
-      </c>
-      <c r="G223" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6754,13 +6754,13 @@
         <v>364</v>
       </c>
       <c r="E224" t="s">
+        <v>165</v>
+      </c>
+      <c r="F224" t="s">
         <v>365</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>366</v>
-      </c>
-      <c r="G224" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6777,13 +6777,13 @@
         <v>364</v>
       </c>
       <c r="E225" t="s">
+        <v>165</v>
+      </c>
+      <c r="F225" t="s">
         <v>365</v>
       </c>
-      <c r="F225" t="s">
+      <c r="G225" t="s">
         <v>366</v>
-      </c>
-      <c r="G225" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6794,19 +6794,19 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E226" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F226" t="s">
+        <v>365</v>
+      </c>
+      <c r="G226" t="s">
         <v>366</v>
-      </c>
-      <c r="G226" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6823,13 +6823,13 @@
         <v>364</v>
       </c>
       <c r="E227" t="s">
+        <v>165</v>
+      </c>
+      <c r="F227" t="s">
         <v>365</v>
       </c>
-      <c r="F227" t="s">
+      <c r="G227" t="s">
         <v>366</v>
-      </c>
-      <c r="G227" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6840,19 +6840,19 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E228" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F228" t="s">
+        <v>365</v>
+      </c>
+      <c r="G228" t="s">
         <v>366</v>
-      </c>
-      <c r="G228" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6869,13 +6869,13 @@
         <v>386</v>
       </c>
       <c r="E229" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F229" t="s">
         <v>387</v>
       </c>
       <c r="G229" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6892,13 +6892,13 @@
         <v>386</v>
       </c>
       <c r="E230" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F230" t="s">
         <v>387</v>
       </c>
       <c r="G230" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>363</v>
+        <v>269</v>
       </c>
       <c r="D231" t="s">
         <v>293</v>
       </c>
       <c r="E231" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F231" t="s">
         <v>387</v>
       </c>
       <c r="G231" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>363</v>
+        <v>269</v>
       </c>
       <c r="D232" t="s">
         <v>309</v>
       </c>
       <c r="E232" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F232" t="s">
         <v>387</v>
       </c>
       <c r="G232" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6961,13 +6961,13 @@
         <v>386</v>
       </c>
       <c r="E233" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F233" t="s">
         <v>387</v>
       </c>
       <c r="G233" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6984,13 +6984,13 @@
         <v>386</v>
       </c>
       <c r="E234" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F234" t="s">
         <v>387</v>
       </c>
       <c r="G234" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7007,13 +7007,13 @@
         <v>386</v>
       </c>
       <c r="E235" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F235" t="s">
         <v>387</v>
       </c>
       <c r="G235" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7030,13 +7030,13 @@
         <v>386</v>
       </c>
       <c r="E236" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F236" t="s">
         <v>387</v>
       </c>
       <c r="G236" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7053,13 +7053,13 @@
         <v>386</v>
       </c>
       <c r="E237" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F237" t="s">
         <v>387</v>
       </c>
       <c r="G237" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7076,13 +7076,13 @@
         <v>386</v>
       </c>
       <c r="E238" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F238" t="s">
         <v>387</v>
       </c>
       <c r="G238" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7099,13 +7099,13 @@
         <v>398</v>
       </c>
       <c r="E239" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F239" t="s">
         <v>399</v>
       </c>
       <c r="G239" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7116,19 +7116,19 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>163</v>
+      </c>
+      <c r="D240" t="s">
+        <v>164</v>
+      </c>
+      <c r="E240" t="s">
+        <v>165</v>
+      </c>
+      <c r="F240" t="s">
         <v>401</v>
       </c>
-      <c r="D240" t="s">
-        <v>163</v>
-      </c>
-      <c r="E240" t="s">
-        <v>164</v>
-      </c>
-      <c r="F240" t="s">
+      <c r="G240" t="s">
         <v>402</v>
-      </c>
-      <c r="G240" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7139,19 +7139,19 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>163</v>
+      </c>
+      <c r="D241" t="s">
+        <v>164</v>
+      </c>
+      <c r="E241" t="s">
+        <v>165</v>
+      </c>
+      <c r="F241" t="s">
         <v>401</v>
       </c>
-      <c r="D241" t="s">
-        <v>163</v>
-      </c>
-      <c r="E241" t="s">
-        <v>164</v>
-      </c>
-      <c r="F241" t="s">
+      <c r="G241" t="s">
         <v>402</v>
-      </c>
-      <c r="G241" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7162,19 +7162,19 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>163</v>
+      </c>
+      <c r="D242" t="s">
+        <v>164</v>
+      </c>
+      <c r="E242" t="s">
+        <v>165</v>
+      </c>
+      <c r="F242" t="s">
         <v>401</v>
       </c>
-      <c r="D242" t="s">
-        <v>163</v>
-      </c>
-      <c r="E242" t="s">
-        <v>164</v>
-      </c>
-      <c r="F242" t="s">
+      <c r="G242" t="s">
         <v>402</v>
-      </c>
-      <c r="G242" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7185,19 +7185,19 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>163</v>
+      </c>
+      <c r="D243" t="s">
+        <v>164</v>
+      </c>
+      <c r="E243" t="s">
+        <v>165</v>
+      </c>
+      <c r="F243" t="s">
         <v>401</v>
       </c>
-      <c r="D243" t="s">
-        <v>163</v>
-      </c>
-      <c r="E243" t="s">
-        <v>164</v>
-      </c>
-      <c r="F243" t="s">
+      <c r="G243" t="s">
         <v>402</v>
-      </c>
-      <c r="G243" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7208,19 +7208,19 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>163</v>
+      </c>
+      <c r="D244" t="s">
+        <v>164</v>
+      </c>
+      <c r="E244" t="s">
+        <v>165</v>
+      </c>
+      <c r="F244" t="s">
         <v>401</v>
       </c>
-      <c r="D244" t="s">
-        <v>163</v>
-      </c>
-      <c r="E244" t="s">
-        <v>164</v>
-      </c>
-      <c r="F244" t="s">
+      <c r="G244" t="s">
         <v>402</v>
-      </c>
-      <c r="G244" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7231,19 +7231,19 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>163</v>
+      </c>
+      <c r="D245" t="s">
+        <v>164</v>
+      </c>
+      <c r="E245" t="s">
+        <v>165</v>
+      </c>
+      <c r="F245" t="s">
         <v>401</v>
       </c>
-      <c r="D245" t="s">
-        <v>163</v>
-      </c>
-      <c r="E245" t="s">
-        <v>164</v>
-      </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
         <v>402</v>
-      </c>
-      <c r="G245" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>401</v>
+        <v>255</v>
       </c>
       <c r="D246" t="s">
         <v>409</v>
       </c>
       <c r="E246" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
       <c r="F246" t="s">
         <v>410</v>
       </c>
       <c r="G246" t="s">
-        <v>165</v>
+        <v>402</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7277,16 +7277,16 @@
         <v>8</v>
       </c>
       <c r="C247" t="s">
+        <v>95</v>
+      </c>
+      <c r="D247" t="s">
+        <v>96</v>
+      </c>
+      <c r="E247" t="s">
+        <v>97</v>
+      </c>
+      <c r="G247" t="s">
         <v>412</v>
-      </c>
-      <c r="D247" t="s">
-        <v>95</v>
-      </c>
-      <c r="E247" t="s">
-        <v>96</v>
-      </c>
-      <c r="G247" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7297,16 +7297,16 @@
         <v>8</v>
       </c>
       <c r="C248" t="s">
+        <v>95</v>
+      </c>
+      <c r="D248" t="s">
+        <v>96</v>
+      </c>
+      <c r="E248" t="s">
+        <v>97</v>
+      </c>
+      <c r="G248" t="s">
         <v>412</v>
-      </c>
-      <c r="D248" t="s">
-        <v>95</v>
-      </c>
-      <c r="E248" t="s">
-        <v>96</v>
-      </c>
-      <c r="G248" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7317,16 +7317,16 @@
         <v>8</v>
       </c>
       <c r="C249" t="s">
+        <v>415</v>
+      </c>
+      <c r="D249" t="s">
+        <v>416</v>
+      </c>
+      <c r="E249" t="s">
+        <v>97</v>
+      </c>
+      <c r="G249" t="s">
         <v>412</v>
-      </c>
-      <c r="D249" t="s">
-        <v>415</v>
-      </c>
-      <c r="E249" t="s">
-        <v>416</v>
-      </c>
-      <c r="G249" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7337,16 +7337,16 @@
         <v>8</v>
       </c>
       <c r="C250" t="s">
+        <v>95</v>
+      </c>
+      <c r="D250" t="s">
+        <v>96</v>
+      </c>
+      <c r="E250" t="s">
+        <v>97</v>
+      </c>
+      <c r="G250" t="s">
         <v>412</v>
-      </c>
-      <c r="D250" t="s">
-        <v>95</v>
-      </c>
-      <c r="E250" t="s">
-        <v>96</v>
-      </c>
-      <c r="G250" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7357,16 +7357,16 @@
         <v>8</v>
       </c>
       <c r="C251" t="s">
+        <v>95</v>
+      </c>
+      <c r="D251" t="s">
+        <v>96</v>
+      </c>
+      <c r="E251" t="s">
+        <v>97</v>
+      </c>
+      <c r="G251" t="s">
         <v>412</v>
-      </c>
-      <c r="D251" t="s">
-        <v>95</v>
-      </c>
-      <c r="E251" t="s">
-        <v>96</v>
-      </c>
-      <c r="G251" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7377,16 +7377,16 @@
         <v>8</v>
       </c>
       <c r="C252" t="s">
+        <v>95</v>
+      </c>
+      <c r="D252" t="s">
+        <v>96</v>
+      </c>
+      <c r="E252" t="s">
+        <v>97</v>
+      </c>
+      <c r="G252" t="s">
         <v>412</v>
-      </c>
-      <c r="D252" t="s">
-        <v>95</v>
-      </c>
-      <c r="E252" t="s">
-        <v>96</v>
-      </c>
-      <c r="G252" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7403,10 +7403,10 @@
         <v>422</v>
       </c>
       <c r="E253" t="s">
+        <v>165</v>
+      </c>
+      <c r="G253" t="s">
         <v>423</v>
-      </c>
-      <c r="G253" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7417,16 +7417,16 @@
         <v>8</v>
       </c>
       <c r="C254" t="s">
-        <v>421</v>
+        <v>219</v>
       </c>
       <c r="D254" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E254" t="s">
-        <v>220</v>
+        <v>92</v>
       </c>
       <c r="G254" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7437,16 +7437,16 @@
         <v>8</v>
       </c>
       <c r="C255" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D255" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E255" t="s">
-        <v>427</v>
+        <v>92</v>
       </c>
       <c r="G255" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7457,16 +7457,16 @@
         <v>8</v>
       </c>
       <c r="C256" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D256" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E256" t="s">
-        <v>427</v>
+        <v>92</v>
       </c>
       <c r="G256" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7477,16 +7477,16 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D257" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E257" t="s">
-        <v>427</v>
+        <v>92</v>
       </c>
       <c r="G257" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7497,16 +7497,16 @@
         <v>8</v>
       </c>
       <c r="C258" t="s">
-        <v>421</v>
+        <v>325</v>
       </c>
       <c r="D258" t="s">
         <v>326</v>
       </c>
       <c r="E258" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G258" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7517,16 +7517,16 @@
         <v>8</v>
       </c>
       <c r="C259" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D259" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E259" t="s">
-        <v>427</v>
+        <v>92</v>
       </c>
       <c r="G259" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7537,16 +7537,16 @@
         <v>8</v>
       </c>
       <c r="C260" t="s">
-        <v>421</v>
+        <v>163</v>
       </c>
       <c r="D260" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E260" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G260" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7557,16 +7557,16 @@
         <v>8</v>
       </c>
       <c r="C261" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="D261" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E261" t="s">
-        <v>435</v>
+        <v>197</v>
       </c>
       <c r="G261" t="s">
-        <v>197</v>
+        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7577,16 +7577,16 @@
         <v>8</v>
       </c>
       <c r="C262" t="s">
-        <v>421</v>
+        <v>163</v>
       </c>
       <c r="D262" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E262" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G262" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7597,16 +7597,16 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="D263" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E263" t="s">
-        <v>439</v>
+        <v>184</v>
       </c>
       <c r="G263" t="s">
-        <v>184</v>
+        <v>423</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7617,16 +7617,16 @@
         <v>8</v>
       </c>
       <c r="C264" t="s">
-        <v>421</v>
+        <v>31</v>
       </c>
       <c r="D264" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E264" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G264" t="s">
-        <v>33</v>
+        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7637,7 +7637,7 @@
         <v>8</v>
       </c>
       <c r="C265" t="s">
-        <v>421</v>
+        <v>9</v>
       </c>
       <c r="D265" t="s">
         <v>10</v>
@@ -7646,7 +7646,7 @@
         <v>11</v>
       </c>
       <c r="G265" t="s">
-        <v>13</v>
+        <v>423</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7657,16 +7657,16 @@
         <v>8</v>
       </c>
       <c r="C266" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="D266" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E266" t="s">
-        <v>444</v>
+        <v>114</v>
       </c>
       <c r="G266" t="s">
-        <v>116</v>
+        <v>423</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7677,16 +7677,16 @@
         <v>8</v>
       </c>
       <c r="C267" t="s">
+        <v>118</v>
+      </c>
+      <c r="D267" t="s">
+        <v>119</v>
+      </c>
+      <c r="E267" t="s">
+        <v>114</v>
+      </c>
+      <c r="G267" t="s">
         <v>446</v>
-      </c>
-      <c r="D267" t="s">
-        <v>118</v>
-      </c>
-      <c r="E267" t="s">
-        <v>119</v>
-      </c>
-      <c r="G267" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7697,16 +7697,16 @@
         <v>8</v>
       </c>
       <c r="C268" t="s">
-        <v>448</v>
+        <v>202</v>
       </c>
       <c r="D268" t="s">
         <v>203</v>
       </c>
       <c r="E268" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="G268" t="s">
-        <v>184</v>
+        <v>448</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7717,16 +7717,16 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
+        <v>118</v>
+      </c>
+      <c r="D269" t="s">
+        <v>119</v>
+      </c>
+      <c r="E269" t="s">
+        <v>114</v>
+      </c>
+      <c r="G269" t="s">
         <v>450</v>
-      </c>
-      <c r="D269" t="s">
-        <v>118</v>
-      </c>
-      <c r="E269" t="s">
-        <v>119</v>
-      </c>
-      <c r="G269" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7737,16 +7737,16 @@
         <v>8</v>
       </c>
       <c r="C270" t="s">
+        <v>118</v>
+      </c>
+      <c r="D270" t="s">
+        <v>119</v>
+      </c>
+      <c r="E270" t="s">
+        <v>114</v>
+      </c>
+      <c r="G270" t="s">
         <v>450</v>
-      </c>
-      <c r="D270" t="s">
-        <v>118</v>
-      </c>
-      <c r="E270" t="s">
-        <v>119</v>
-      </c>
-      <c r="G270" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7763,10 +7763,10 @@
         <v>454</v>
       </c>
       <c r="E271" t="s">
+        <v>114</v>
+      </c>
+      <c r="G271" t="s">
         <v>455</v>
-      </c>
-      <c r="G271" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7783,10 +7783,10 @@
         <v>454</v>
       </c>
       <c r="E272" t="s">
+        <v>114</v>
+      </c>
+      <c r="G272" t="s">
         <v>455</v>
-      </c>
-      <c r="G272" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7803,10 +7803,10 @@
         <v>454</v>
       </c>
       <c r="E273" t="s">
+        <v>114</v>
+      </c>
+      <c r="G273" t="s">
         <v>455</v>
-      </c>
-      <c r="G273" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7823,10 +7823,10 @@
         <v>454</v>
       </c>
       <c r="E274" t="s">
+        <v>114</v>
+      </c>
+      <c r="G274" t="s">
         <v>455</v>
-      </c>
-      <c r="G274" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7843,10 +7843,10 @@
         <v>454</v>
       </c>
       <c r="E275" t="s">
+        <v>114</v>
+      </c>
+      <c r="G275" t="s">
         <v>455</v>
-      </c>
-      <c r="G275" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7863,10 +7863,10 @@
         <v>454</v>
       </c>
       <c r="E276" t="s">
+        <v>114</v>
+      </c>
+      <c r="G276" t="s">
         <v>455</v>
-      </c>
-      <c r="G276" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7883,10 +7883,10 @@
         <v>454</v>
       </c>
       <c r="E277" t="s">
+        <v>114</v>
+      </c>
+      <c r="G277" t="s">
         <v>455</v>
-      </c>
-      <c r="G277" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7897,16 +7897,16 @@
         <v>8</v>
       </c>
       <c r="C278" t="s">
-        <v>463</v>
+        <v>202</v>
       </c>
       <c r="D278" t="s">
         <v>203</v>
       </c>
       <c r="E278" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="G278" t="s">
-        <v>184</v>
+        <v>463</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7917,16 +7917,16 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
-        <v>463</v>
+        <v>51</v>
       </c>
       <c r="D279" t="s">
         <v>52</v>
       </c>
       <c r="E279" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G279" t="s">
-        <v>33</v>
+        <v>463</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7937,7 +7937,7 @@
         <v>8</v>
       </c>
       <c r="C280" t="s">
-        <v>463</v>
+        <v>9</v>
       </c>
       <c r="D280" t="s">
         <v>10</v>
@@ -7946,7 +7946,7 @@
         <v>11</v>
       </c>
       <c r="G280" t="s">
-        <v>13</v>
+        <v>463</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7957,16 +7957,16 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
+        <v>170</v>
+      </c>
+      <c r="D281" t="s">
+        <v>171</v>
+      </c>
+      <c r="E281" t="s">
+        <v>114</v>
+      </c>
+      <c r="G281" t="s">
         <v>463</v>
-      </c>
-      <c r="D281" t="s">
-        <v>170</v>
-      </c>
-      <c r="E281" t="s">
-        <v>171</v>
-      </c>
-      <c r="G281" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7977,16 +7977,16 @@
         <v>8</v>
       </c>
       <c r="C282" t="s">
+        <v>124</v>
+      </c>
+      <c r="D282" t="s">
+        <v>125</v>
+      </c>
+      <c r="E282" t="s">
+        <v>126</v>
+      </c>
+      <c r="G282" t="s">
         <v>463</v>
-      </c>
-      <c r="D282" t="s">
-        <v>124</v>
-      </c>
-      <c r="E282" t="s">
-        <v>125</v>
-      </c>
-      <c r="G282" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7997,16 +7997,16 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>469</v>
+        <v>363</v>
       </c>
       <c r="D283" t="s">
         <v>398</v>
       </c>
       <c r="E283" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G283" t="s">
-        <v>165</v>
+        <v>469</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8017,16 +8017,16 @@
         <v>8</v>
       </c>
       <c r="C284" t="s">
+        <v>124</v>
+      </c>
+      <c r="D284" t="s">
+        <v>125</v>
+      </c>
+      <c r="E284" t="s">
+        <v>126</v>
+      </c>
+      <c r="G284" t="s">
         <v>471</v>
-      </c>
-      <c r="D284" t="s">
-        <v>124</v>
-      </c>
-      <c r="E284" t="s">
-        <v>125</v>
-      </c>
-      <c r="G284" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8037,16 +8037,16 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
+        <v>170</v>
+      </c>
+      <c r="D285" t="s">
+        <v>171</v>
+      </c>
+      <c r="E285" t="s">
+        <v>114</v>
+      </c>
+      <c r="G285" t="s">
         <v>473</v>
-      </c>
-      <c r="D285" t="s">
-        <v>170</v>
-      </c>
-      <c r="E285" t="s">
-        <v>171</v>
-      </c>
-      <c r="G285" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8057,16 +8057,16 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
+        <v>438</v>
+      </c>
+      <c r="D286" t="s">
+        <v>439</v>
+      </c>
+      <c r="E286" t="s">
+        <v>184</v>
+      </c>
+      <c r="G286" t="s">
         <v>475</v>
-      </c>
-      <c r="D286" t="s">
-        <v>438</v>
-      </c>
-      <c r="E286" t="s">
-        <v>439</v>
-      </c>
-      <c r="G286" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8077,16 +8077,16 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
+        <v>438</v>
+      </c>
+      <c r="D287" t="s">
+        <v>439</v>
+      </c>
+      <c r="E287" t="s">
+        <v>184</v>
+      </c>
+      <c r="G287" t="s">
         <v>475</v>
-      </c>
-      <c r="D287" t="s">
-        <v>438</v>
-      </c>
-      <c r="E287" t="s">
-        <v>439</v>
-      </c>
-      <c r="G287" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8097,16 +8097,16 @@
         <v>8</v>
       </c>
       <c r="C288" t="s">
+        <v>41</v>
+      </c>
+      <c r="D288" t="s">
+        <v>42</v>
+      </c>
+      <c r="E288" t="s">
+        <v>11</v>
+      </c>
+      <c r="G288" t="s">
         <v>475</v>
-      </c>
-      <c r="D288" t="s">
-        <v>41</v>
-      </c>
-      <c r="E288" t="s">
-        <v>42</v>
-      </c>
-      <c r="G288" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8117,16 +8117,16 @@
         <v>8</v>
       </c>
       <c r="C289" t="s">
+        <v>31</v>
+      </c>
+      <c r="D289" t="s">
+        <v>32</v>
+      </c>
+      <c r="E289" t="s">
+        <v>33</v>
+      </c>
+      <c r="G289" t="s">
         <v>475</v>
-      </c>
-      <c r="D289" t="s">
-        <v>31</v>
-      </c>
-      <c r="E289" t="s">
-        <v>32</v>
-      </c>
-      <c r="G289" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8137,16 +8137,16 @@
         <v>8</v>
       </c>
       <c r="C290" t="s">
+        <v>31</v>
+      </c>
+      <c r="D290" t="s">
+        <v>32</v>
+      </c>
+      <c r="E290" t="s">
+        <v>33</v>
+      </c>
+      <c r="G290" t="s">
         <v>475</v>
-      </c>
-      <c r="D290" t="s">
-        <v>31</v>
-      </c>
-      <c r="E290" t="s">
-        <v>32</v>
-      </c>
-      <c r="G290" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8157,16 +8157,16 @@
         <v>8</v>
       </c>
       <c r="C291" t="s">
+        <v>170</v>
+      </c>
+      <c r="D291" t="s">
+        <v>171</v>
+      </c>
+      <c r="E291" t="s">
+        <v>114</v>
+      </c>
+      <c r="G291" t="s">
         <v>475</v>
-      </c>
-      <c r="D291" t="s">
-        <v>170</v>
-      </c>
-      <c r="E291" t="s">
-        <v>171</v>
-      </c>
-      <c r="G291" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8177,16 +8177,16 @@
         <v>8</v>
       </c>
       <c r="C292" t="s">
+        <v>170</v>
+      </c>
+      <c r="D292" t="s">
+        <v>171</v>
+      </c>
+      <c r="E292" t="s">
+        <v>114</v>
+      </c>
+      <c r="G292" t="s">
         <v>475</v>
-      </c>
-      <c r="D292" t="s">
-        <v>170</v>
-      </c>
-      <c r="E292" t="s">
-        <v>171</v>
-      </c>
-      <c r="G292" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8197,16 +8197,16 @@
         <v>8</v>
       </c>
       <c r="C293" t="s">
+        <v>170</v>
+      </c>
+      <c r="D293" t="s">
+        <v>171</v>
+      </c>
+      <c r="E293" t="s">
+        <v>114</v>
+      </c>
+      <c r="G293" t="s">
         <v>475</v>
-      </c>
-      <c r="D293" t="s">
-        <v>170</v>
-      </c>
-      <c r="E293" t="s">
-        <v>171</v>
-      </c>
-      <c r="G293" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8217,16 +8217,16 @@
         <v>8</v>
       </c>
       <c r="C294" t="s">
+        <v>170</v>
+      </c>
+      <c r="D294" t="s">
+        <v>171</v>
+      </c>
+      <c r="E294" t="s">
+        <v>114</v>
+      </c>
+      <c r="G294" t="s">
         <v>475</v>
-      </c>
-      <c r="D294" t="s">
-        <v>170</v>
-      </c>
-      <c r="E294" t="s">
-        <v>171</v>
-      </c>
-      <c r="G294" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8237,16 +8237,16 @@
         <v>8</v>
       </c>
       <c r="C295" t="s">
+        <v>170</v>
+      </c>
+      <c r="D295" t="s">
+        <v>171</v>
+      </c>
+      <c r="E295" t="s">
+        <v>114</v>
+      </c>
+      <c r="G295" t="s">
         <v>485</v>
-      </c>
-      <c r="D295" t="s">
-        <v>170</v>
-      </c>
-      <c r="E295" t="s">
-        <v>171</v>
-      </c>
-      <c r="G295" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8257,16 +8257,16 @@
         <v>8</v>
       </c>
       <c r="C296" t="s">
+        <v>170</v>
+      </c>
+      <c r="D296" t="s">
+        <v>171</v>
+      </c>
+      <c r="E296" t="s">
+        <v>114</v>
+      </c>
+      <c r="G296" t="s">
         <v>485</v>
-      </c>
-      <c r="D296" t="s">
-        <v>170</v>
-      </c>
-      <c r="E296" t="s">
-        <v>171</v>
-      </c>
-      <c r="G296" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,42 +22,42 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -85,12 +85,12 @@
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>11320</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>09.2.2 - Upper‐secondary education (IS)</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -151,12 +151,12 @@
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -169,18 +169,18 @@
     <t>12110</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -286,6 +286,9 @@
     <t>14010</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
@@ -295,9 +298,6 @@
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -352,21 +352,21 @@
     <t>15110</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -823,18 +823,18 @@
     <t>23110</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>04.3.3 - Nuclear fuel (CS)</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>04.2.2 - Forestry (CS)</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>04.2.3 - Fishing and hunting (CS)</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,21 +1210,21 @@
     <t>32310</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>04.4.3 - Construction (CS)</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1279,15 +1279,15 @@
     <t>43010</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>600</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,16 +1863,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -1909,16 +1909,16 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -1932,13 +1932,13 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -1961,10 +1961,10 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -1978,13 +1978,13 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
@@ -2001,13 +2001,13 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
@@ -2024,16 +2024,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
         <v>29</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2047,19 +2047,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2070,16 +2070,16 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
         <v>35</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
         <v>36</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2093,13 +2093,13 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -2116,16 +2116,16 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
         <v>42</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>39</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -2139,13 +2139,13 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
         <v>44</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>46</v>
@@ -2162,16 +2162,16 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
         <v>48</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
         <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>46</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -2191,13 +2191,13 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" t="s">
         <v>33</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2214,13 +2214,13 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" t="s">
         <v>33</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
         <v>57</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" t="s">
         <v>58</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>33</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2254,19 +2254,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
         <v>60</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" t="s">
         <v>61</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>33</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2283,13 +2283,13 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" t="s">
         <v>33</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2300,19 +2300,19 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
         <v>31</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" t="s">
         <v>32</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>33</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
         <v>66</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" t="s">
         <v>67</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>33</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2346,19 +2346,19 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" t="s">
         <v>31</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>33</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2369,19 +2369,19 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" t="s">
         <v>31</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>33</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2392,19 +2392,19 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" t="s">
         <v>31</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" t="s">
         <v>32</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>33</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2415,19 +2415,19 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" t="s">
         <v>31</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
         <v>33</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-      <c r="G27" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2438,19 +2438,19 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" t="s">
         <v>31</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" t="s">
         <v>32</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>33</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-      <c r="G28" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2461,19 +2461,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" t="s">
         <v>31</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" t="s">
         <v>32</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>33</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-      <c r="G29" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2490,13 +2490,13 @@
         <v>52</v>
       </c>
       <c r="E30" t="s">
+        <v>64</v>
+      </c>
+      <c r="F30" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" t="s">
         <v>33</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-      <c r="G30" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2507,19 +2507,19 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" t="s">
         <v>31</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" t="s">
         <v>32</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>33</v>
-      </c>
-      <c r="F31" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2530,19 +2530,19 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" t="s">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" t="s">
         <v>32</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>33</v>
-      </c>
-      <c r="F32" t="s">
-        <v>76</v>
-      </c>
-      <c r="G32" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2553,19 +2553,19 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" t="s">
         <v>31</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" t="s">
         <v>32</v>
       </c>
-      <c r="E33" t="s">
+      <c r="G33" t="s">
         <v>33</v>
-      </c>
-      <c r="F33" t="s">
-        <v>76</v>
-      </c>
-      <c r="G33" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2576,19 +2576,19 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" t="s">
         <v>31</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" t="s">
         <v>32</v>
       </c>
-      <c r="E34" t="s">
+      <c r="G34" t="s">
         <v>33</v>
-      </c>
-      <c r="F34" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2599,19 +2599,19 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" t="s">
         <v>31</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" t="s">
         <v>32</v>
       </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>33</v>
-      </c>
-      <c r="F35" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" t="s">
         <v>57</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" t="s">
         <v>58</v>
       </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>33</v>
-      </c>
-      <c r="F36" t="s">
-        <v>76</v>
-      </c>
-      <c r="G36" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2645,16 +2645,16 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" t="s">
         <v>31</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>32</v>
       </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>33</v>
-      </c>
-      <c r="G37" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2665,16 +2665,16 @@
         <v>8</v>
       </c>
       <c r="C38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" t="s">
         <v>31</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>32</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>33</v>
-      </c>
-      <c r="G38" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2685,16 +2685,16 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" t="s">
         <v>31</v>
       </c>
-      <c r="D39" t="s">
+      <c r="F39" t="s">
         <v>32</v>
       </c>
-      <c r="E39" t="s">
+      <c r="G39" t="s">
         <v>33</v>
-      </c>
-      <c r="G39" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2705,16 +2705,16 @@
         <v>8</v>
       </c>
       <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s">
         <v>31</v>
       </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>32</v>
       </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
         <v>33</v>
-      </c>
-      <c r="G40" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2725,16 +2725,16 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="D41" t="s">
         <v>52</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
+        <v>54</v>
+      </c>
+      <c r="G41" t="s">
         <v>33</v>
-      </c>
-      <c r="G41" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2745,16 +2745,16 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" t="s">
         <v>57</v>
       </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
         <v>58</v>
       </c>
-      <c r="E42" t="s">
+      <c r="G42" t="s">
         <v>33</v>
-      </c>
-      <c r="G42" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2770,7 +2770,7 @@
       <c r="D43" t="s">
         <v>91</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>92</v>
       </c>
       <c r="G43" t="s">
@@ -2785,16 +2785,16 @@
         <v>8</v>
       </c>
       <c r="C44" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" t="s">
         <v>95</v>
       </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
         <v>96</v>
       </c>
-      <c r="E44" t="s">
+      <c r="G44" t="s">
         <v>97</v>
-      </c>
-      <c r="G44" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2810,7 +2810,7 @@
       <c r="D45" t="s">
         <v>91</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>92</v>
       </c>
       <c r="G45" t="s">
@@ -2830,7 +2830,7 @@
       <c r="D46" t="s">
         <v>91</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>92</v>
       </c>
       <c r="G46" t="s">
@@ -2845,16 +2845,16 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" t="s">
         <v>101</v>
       </c>
-      <c r="D47" t="s">
+      <c r="F47" t="s">
         <v>102</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>97</v>
-      </c>
-      <c r="G47" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2870,7 +2870,7 @@
       <c r="D48" t="s">
         <v>91</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>92</v>
       </c>
       <c r="G48" t="s">
@@ -2890,7 +2890,7 @@
       <c r="D49" t="s">
         <v>91</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>92</v>
       </c>
       <c r="G49" t="s">
@@ -2905,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" t="s">
         <v>101</v>
       </c>
-      <c r="D50" t="s">
+      <c r="F50" t="s">
         <v>102</v>
       </c>
-      <c r="E50" t="s">
+      <c r="G50" t="s">
         <v>97</v>
-      </c>
-      <c r="G50" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2930,7 +2930,7 @@
       <c r="D51" t="s">
         <v>91</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>92</v>
       </c>
       <c r="G51" t="s">
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" t="s">
         <v>108</v>
       </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
         <v>109</v>
       </c>
-      <c r="E52" t="s">
+      <c r="G52" t="s">
         <v>97</v>
-      </c>
-      <c r="G52" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2965,16 +2965,16 @@
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
       </c>
-      <c r="E53" t="s">
-        <v>11</v>
+      <c r="F53" t="s">
+        <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3008,16 +3008,16 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
         <v>118</v>
-      </c>
-      <c r="D55" t="s">
-        <v>119</v>
       </c>
       <c r="E55" t="s">
         <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G55" t="s">
         <v>116</v>
@@ -3031,16 +3031,16 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="s">
         <v>121</v>
-      </c>
-      <c r="D56" t="s">
-        <v>122</v>
       </c>
       <c r="E56" t="s">
         <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G56" t="s">
         <v>116</v>
@@ -3054,19 +3054,19 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
         <v>124</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" t="s">
         <v>125</v>
       </c>
-      <c r="E57" t="s">
+      <c r="G57" t="s">
         <v>126</v>
-      </c>
-      <c r="F57" t="s">
-        <v>115</v>
-      </c>
-      <c r="G57" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3077,16 +3077,16 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" t="s">
         <v>118</v>
-      </c>
-      <c r="D58" t="s">
-        <v>119</v>
       </c>
       <c r="E58" t="s">
         <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G58" t="s">
         <v>116</v>
@@ -3100,16 +3100,16 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
+        <v>112</v>
+      </c>
+      <c r="D59" t="s">
         <v>118</v>
-      </c>
-      <c r="D59" t="s">
-        <v>119</v>
       </c>
       <c r="E59" t="s">
         <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G59" t="s">
         <v>116</v>
@@ -3123,16 +3123,16 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" t="s">
         <v>118</v>
-      </c>
-      <c r="D60" t="s">
-        <v>119</v>
       </c>
       <c r="E60" t="s">
         <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G60" t="s">
         <v>116</v>
@@ -3146,16 +3146,16 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
+        <v>112</v>
+      </c>
+      <c r="D61" t="s">
         <v>118</v>
-      </c>
-      <c r="D61" t="s">
-        <v>119</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G61" t="s">
         <v>116</v>
@@ -3169,16 +3169,16 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" t="s">
         <v>118</v>
-      </c>
-      <c r="D62" t="s">
-        <v>119</v>
       </c>
       <c r="E62" t="s">
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G62" t="s">
         <v>116</v>
@@ -3192,16 +3192,16 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
+        <v>112</v>
+      </c>
+      <c r="D63" t="s">
         <v>118</v>
-      </c>
-      <c r="D63" t="s">
-        <v>133</v>
       </c>
       <c r="E63" t="s">
         <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G63" t="s">
         <v>116</v>
@@ -3215,16 +3215,16 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
+        <v>112</v>
+      </c>
+      <c r="D64" t="s">
         <v>118</v>
-      </c>
-      <c r="D64" t="s">
-        <v>133</v>
       </c>
       <c r="E64" t="s">
         <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G64" t="s">
         <v>116</v>
@@ -3238,16 +3238,16 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" t="s">
         <v>136</v>
-      </c>
-      <c r="D65" t="s">
-        <v>137</v>
       </c>
       <c r="E65" t="s">
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="G65" t="s">
         <v>116</v>
@@ -3284,16 +3284,16 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" t="s">
         <v>118</v>
-      </c>
-      <c r="D67" t="s">
-        <v>119</v>
       </c>
       <c r="E67" t="s">
         <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G67" t="s">
         <v>116</v>
@@ -3310,13 +3310,13 @@
         <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="G68" t="s">
         <v>116</v>
@@ -3333,13 +3333,13 @@
         <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G69" t="s">
         <v>116</v>
@@ -3353,16 +3353,16 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" t="s">
         <v>121</v>
-      </c>
-      <c r="D70" t="s">
-        <v>122</v>
       </c>
       <c r="E70" t="s">
         <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G70" t="s">
         <v>116</v>
@@ -3376,16 +3376,16 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" t="s">
         <v>121</v>
-      </c>
-      <c r="D71" t="s">
-        <v>122</v>
       </c>
       <c r="E71" t="s">
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G71" t="s">
         <v>116</v>
@@ -3422,19 +3422,19 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" t="s">
         <v>148</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
+        <v>114</v>
+      </c>
+      <c r="F73" t="s">
         <v>149</v>
       </c>
-      <c r="E73" t="s">
+      <c r="G73" t="s">
         <v>126</v>
-      </c>
-      <c r="F73" t="s">
-        <v>115</v>
-      </c>
-      <c r="G73" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3445,19 +3445,19 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" t="s">
         <v>151</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
+        <v>114</v>
+      </c>
+      <c r="F74" t="s">
         <v>152</v>
       </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
         <v>126</v>
-      </c>
-      <c r="F74" t="s">
-        <v>115</v>
-      </c>
-      <c r="G74" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3468,19 +3468,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" t="s">
         <v>154</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
+        <v>114</v>
+      </c>
+      <c r="F75" t="s">
         <v>155</v>
       </c>
-      <c r="E75" t="s">
+      <c r="G75" t="s">
         <v>126</v>
-      </c>
-      <c r="F75" t="s">
-        <v>115</v>
-      </c>
-      <c r="G75" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3491,19 +3491,19 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" t="s">
         <v>148</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
+        <v>114</v>
+      </c>
+      <c r="F76" t="s">
         <v>149</v>
       </c>
-      <c r="E76" t="s">
+      <c r="G76" t="s">
         <v>126</v>
-      </c>
-      <c r="F76" t="s">
-        <v>115</v>
-      </c>
-      <c r="G76" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3514,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" t="s">
         <v>148</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
+        <v>114</v>
+      </c>
+      <c r="F77" t="s">
         <v>149</v>
       </c>
-      <c r="E77" t="s">
+      <c r="G77" t="s">
         <v>126</v>
-      </c>
-      <c r="F77" t="s">
-        <v>115</v>
-      </c>
-      <c r="G77" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3537,19 +3537,19 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" t="s">
         <v>151</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
+        <v>114</v>
+      </c>
+      <c r="F78" t="s">
         <v>152</v>
       </c>
-      <c r="E78" t="s">
+      <c r="G78" t="s">
         <v>126</v>
-      </c>
-      <c r="F78" t="s">
-        <v>115</v>
-      </c>
-      <c r="G78" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3560,19 +3560,19 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" t="s">
         <v>160</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
+        <v>114</v>
+      </c>
+      <c r="F79" t="s">
         <v>161</v>
       </c>
-      <c r="E79" t="s">
+      <c r="G79" t="s">
         <v>126</v>
-      </c>
-      <c r="F79" t="s">
-        <v>115</v>
-      </c>
-      <c r="G79" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3583,19 +3583,19 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
+        <v>112</v>
+      </c>
+      <c r="D80" t="s">
         <v>163</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
+        <v>114</v>
+      </c>
+      <c r="F80" t="s">
         <v>164</v>
       </c>
-      <c r="E80" t="s">
-        <v>165</v>
-      </c>
-      <c r="F80" t="s">
-        <v>115</v>
-      </c>
       <c r="G80" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3606,19 +3606,19 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
+        <v>112</v>
+      </c>
+      <c r="D81" t="s">
         <v>163</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
+        <v>114</v>
+      </c>
+      <c r="F81" t="s">
         <v>164</v>
       </c>
-      <c r="E81" t="s">
-        <v>165</v>
-      </c>
-      <c r="F81" t="s">
-        <v>115</v>
-      </c>
       <c r="G81" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3629,19 +3629,19 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
+        <v>112</v>
+      </c>
+      <c r="D82" t="s">
         <v>163</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
+        <v>114</v>
+      </c>
+      <c r="F82" t="s">
         <v>164</v>
       </c>
-      <c r="E82" t="s">
-        <v>165</v>
-      </c>
-      <c r="F82" t="s">
-        <v>115</v>
-      </c>
       <c r="G82" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3655,13 +3655,13 @@
         <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
       </c>
       <c r="F83" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G83" t="s">
         <v>116</v>
@@ -3675,16 +3675,16 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
+        <v>112</v>
+      </c>
+      <c r="D84" t="s">
         <v>170</v>
-      </c>
-      <c r="D84" t="s">
-        <v>171</v>
       </c>
       <c r="E84" t="s">
         <v>114</v>
       </c>
       <c r="F84" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G84" t="s">
         <v>116</v>
@@ -3698,16 +3698,16 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
+        <v>112</v>
+      </c>
+      <c r="D85" t="s">
         <v>118</v>
-      </c>
-      <c r="D85" t="s">
-        <v>173</v>
       </c>
       <c r="E85" t="s">
         <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="G85" t="s">
         <v>116</v>
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
+        <v>112</v>
+      </c>
+      <c r="D86" t="s">
         <v>175</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
+        <v>114</v>
+      </c>
+      <c r="F86" t="s">
         <v>176</v>
       </c>
-      <c r="E86" t="s">
-        <v>165</v>
-      </c>
-      <c r="F86" t="s">
-        <v>115</v>
-      </c>
       <c r="G86" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,16 +3744,16 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
+        <v>112</v>
+      </c>
+      <c r="D87" t="s">
         <v>118</v>
-      </c>
-      <c r="D87" t="s">
-        <v>173</v>
       </c>
       <c r="E87" t="s">
         <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="G87" t="s">
         <v>116</v>
@@ -3767,16 +3767,16 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
+        <v>112</v>
+      </c>
+      <c r="D88" t="s">
         <v>118</v>
-      </c>
-      <c r="D88" t="s">
-        <v>119</v>
       </c>
       <c r="E88" t="s">
         <v>114</v>
       </c>
       <c r="F88" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G88" t="s">
         <v>116</v>
@@ -3790,16 +3790,16 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
+        <v>112</v>
+      </c>
+      <c r="D89" t="s">
         <v>118</v>
-      </c>
-      <c r="D89" t="s">
-        <v>119</v>
       </c>
       <c r="E89" t="s">
         <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G89" t="s">
         <v>116</v>
@@ -3813,19 +3813,19 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
+        <v>112</v>
+      </c>
+      <c r="D90" t="s">
         <v>124</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
+        <v>114</v>
+      </c>
+      <c r="F90" t="s">
         <v>125</v>
       </c>
-      <c r="E90" t="s">
+      <c r="G90" t="s">
         <v>126</v>
-      </c>
-      <c r="F90" t="s">
-        <v>115</v>
-      </c>
-      <c r="G90" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3836,19 +3836,19 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
+        <v>112</v>
+      </c>
+      <c r="D91" t="s">
         <v>182</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
+        <v>114</v>
+      </c>
+      <c r="F91" t="s">
         <v>183</v>
       </c>
-      <c r="E91" t="s">
+      <c r="G91" t="s">
         <v>184</v>
-      </c>
-      <c r="F91" t="s">
-        <v>115</v>
-      </c>
-      <c r="G91" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3859,19 +3859,19 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" t="s">
         <v>124</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
+        <v>114</v>
+      </c>
+      <c r="F92" t="s">
         <v>125</v>
       </c>
-      <c r="E92" t="s">
+      <c r="G92" t="s">
         <v>126</v>
-      </c>
-      <c r="F92" t="s">
-        <v>115</v>
-      </c>
-      <c r="G92" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3882,16 +3882,16 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" t="s">
         <v>121</v>
-      </c>
-      <c r="D93" t="s">
-        <v>122</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G93" t="s">
         <v>116</v>
@@ -3905,19 +3905,19 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
         <v>124</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
+        <v>114</v>
+      </c>
+      <c r="F94" t="s">
         <v>125</v>
       </c>
-      <c r="E94" t="s">
+      <c r="G94" t="s">
         <v>126</v>
-      </c>
-      <c r="F94" t="s">
-        <v>115</v>
-      </c>
-      <c r="G94" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3928,16 +3928,16 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
+        <v>112</v>
+      </c>
+      <c r="D95" t="s">
         <v>189</v>
-      </c>
-      <c r="D95" t="s">
-        <v>190</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="G95" t="s">
         <v>116</v>
@@ -3951,19 +3951,19 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>112</v>
+      </c>
+      <c r="D96" t="s">
         <v>124</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>192</v>
+      </c>
+      <c r="F96" t="s">
         <v>125</v>
       </c>
-      <c r="E96" t="s">
+      <c r="G96" t="s">
         <v>126</v>
-      </c>
-      <c r="F96" t="s">
-        <v>192</v>
-      </c>
-      <c r="G96" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3974,19 +3974,19 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>112</v>
+      </c>
+      <c r="D97" t="s">
         <v>124</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
+        <v>192</v>
+      </c>
+      <c r="F97" t="s">
         <v>125</v>
       </c>
-      <c r="E97" t="s">
+      <c r="G97" t="s">
         <v>126</v>
-      </c>
-      <c r="F97" t="s">
-        <v>192</v>
-      </c>
-      <c r="G97" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3997,19 +3997,19 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>112</v>
+      </c>
+      <c r="D98" t="s">
         <v>195</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
+        <v>192</v>
+      </c>
+      <c r="F98" t="s">
         <v>196</v>
       </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
         <v>197</v>
-      </c>
-      <c r="F98" t="s">
-        <v>192</v>
-      </c>
-      <c r="G98" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4020,19 +4020,19 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>112</v>
+      </c>
+      <c r="D99" t="s">
         <v>124</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
+        <v>192</v>
+      </c>
+      <c r="F99" t="s">
         <v>125</v>
       </c>
-      <c r="E99" t="s">
+      <c r="G99" t="s">
         <v>126</v>
-      </c>
-      <c r="F99" t="s">
-        <v>192</v>
-      </c>
-      <c r="G99" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" t="s">
         <v>154</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
+        <v>192</v>
+      </c>
+      <c r="F100" t="s">
         <v>155</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>126</v>
-      </c>
-      <c r="F100" t="s">
-        <v>192</v>
-      </c>
-      <c r="G100" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4066,19 +4066,19 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>112</v>
+      </c>
+      <c r="D101" t="s">
         <v>124</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
+        <v>192</v>
+      </c>
+      <c r="F101" t="s">
         <v>125</v>
       </c>
-      <c r="E101" t="s">
+      <c r="G101" t="s">
         <v>126</v>
-      </c>
-      <c r="F101" t="s">
-        <v>192</v>
-      </c>
-      <c r="G101" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4094,11 +4094,11 @@
       <c r="D102" t="s">
         <v>203</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
+        <v>204</v>
+      </c>
+      <c r="G102" t="s">
         <v>184</v>
-      </c>
-      <c r="G102" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4114,11 +4114,11 @@
       <c r="D103" t="s">
         <v>203</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
+        <v>204</v>
+      </c>
+      <c r="G103" t="s">
         <v>184</v>
-      </c>
-      <c r="G103" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4134,11 +4134,11 @@
       <c r="D104" t="s">
         <v>203</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
+        <v>204</v>
+      </c>
+      <c r="G104" t="s">
         <v>184</v>
-      </c>
-      <c r="G104" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4149,16 +4149,16 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
+        <v>202</v>
+      </c>
+      <c r="D105" t="s">
         <v>208</v>
       </c>
-      <c r="D105" t="s">
+      <c r="F105" t="s">
         <v>209</v>
       </c>
-      <c r="E105" t="s">
+      <c r="G105" t="s">
         <v>184</v>
-      </c>
-      <c r="G105" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4174,11 +4174,11 @@
       <c r="D106" t="s">
         <v>203</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
+        <v>204</v>
+      </c>
+      <c r="G106" t="s">
         <v>184</v>
-      </c>
-      <c r="G106" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4189,16 +4189,16 @@
         <v>8</v>
       </c>
       <c r="C107" t="s">
+        <v>202</v>
+      </c>
+      <c r="D107" t="s">
         <v>182</v>
       </c>
-      <c r="D107" t="s">
+      <c r="F107" t="s">
         <v>183</v>
       </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>184</v>
-      </c>
-      <c r="G107" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4209,16 +4209,16 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
+        <v>202</v>
+      </c>
+      <c r="D108" t="s">
         <v>213</v>
       </c>
-      <c r="D108" t="s">
+      <c r="F108" t="s">
         <v>214</v>
       </c>
-      <c r="E108" t="s">
+      <c r="G108" t="s">
         <v>184</v>
-      </c>
-      <c r="G108" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4229,16 +4229,16 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
+        <v>202</v>
+      </c>
+      <c r="D109" t="s">
         <v>216</v>
       </c>
-      <c r="D109" t="s">
+      <c r="F109" t="s">
         <v>217</v>
       </c>
-      <c r="E109" t="s">
-        <v>92</v>
-      </c>
       <c r="G109" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4249,16 +4249,16 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
+        <v>202</v>
+      </c>
+      <c r="D110" t="s">
         <v>219</v>
       </c>
-      <c r="D110" t="s">
+      <c r="F110" t="s">
         <v>220</v>
       </c>
-      <c r="E110" t="s">
-        <v>92</v>
-      </c>
       <c r="G110" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4274,11 +4274,11 @@
       <c r="D111" t="s">
         <v>203</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
+        <v>204</v>
+      </c>
+      <c r="G111" t="s">
         <v>184</v>
-      </c>
-      <c r="G111" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4289,16 +4289,16 @@
         <v>8</v>
       </c>
       <c r="C112" t="s">
+        <v>202</v>
+      </c>
+      <c r="D112" t="s">
         <v>223</v>
       </c>
-      <c r="D112" t="s">
+      <c r="F112" t="s">
         <v>224</v>
       </c>
-      <c r="E112" t="s">
+      <c r="G112" t="s">
         <v>225</v>
-      </c>
-      <c r="G112" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4309,16 +4309,16 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="D113" t="s">
+        <v>113</v>
+      </c>
+      <c r="F113" t="s">
         <v>143</v>
       </c>
-      <c r="E113" t="s">
-        <v>114</v>
-      </c>
       <c r="G113" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4329,16 +4329,16 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
+        <v>202</v>
+      </c>
+      <c r="D114" t="s">
         <v>151</v>
       </c>
-      <c r="D114" t="s">
+      <c r="F114" t="s">
         <v>152</v>
       </c>
-      <c r="E114" t="s">
+      <c r="G114" t="s">
         <v>126</v>
-      </c>
-      <c r="G114" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4349,16 +4349,16 @@
         <v>8</v>
       </c>
       <c r="C115" t="s">
+        <v>202</v>
+      </c>
+      <c r="D115" t="s">
         <v>182</v>
       </c>
-      <c r="D115" t="s">
+      <c r="F115" t="s">
         <v>183</v>
       </c>
-      <c r="E115" t="s">
+      <c r="G115" t="s">
         <v>184</v>
-      </c>
-      <c r="G115" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4369,16 +4369,16 @@
         <v>8</v>
       </c>
       <c r="C116" t="s">
+        <v>202</v>
+      </c>
+      <c r="D116" t="s">
         <v>230</v>
       </c>
-      <c r="D116" t="s">
+      <c r="F116" t="s">
         <v>231</v>
       </c>
-      <c r="E116" t="s">
+      <c r="G116" t="s">
         <v>225</v>
-      </c>
-      <c r="G116" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4389,16 +4389,16 @@
         <v>8</v>
       </c>
       <c r="C117" t="s">
+        <v>202</v>
+      </c>
+      <c r="D117" t="s">
         <v>223</v>
       </c>
-      <c r="D117" t="s">
+      <c r="F117" t="s">
         <v>224</v>
       </c>
-      <c r="E117" t="s">
+      <c r="G117" t="s">
         <v>225</v>
-      </c>
-      <c r="G117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4409,16 +4409,16 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
+        <v>202</v>
+      </c>
+      <c r="D118" t="s">
         <v>163</v>
       </c>
-      <c r="D118" t="s">
+      <c r="F118" t="s">
         <v>234</v>
       </c>
-      <c r="E118" t="s">
-        <v>165</v>
-      </c>
       <c r="G118" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4429,16 +4429,16 @@
         <v>8</v>
       </c>
       <c r="C119" t="s">
+        <v>202</v>
+      </c>
+      <c r="D119" t="s">
         <v>182</v>
       </c>
-      <c r="D119" t="s">
+      <c r="F119" t="s">
         <v>183</v>
       </c>
-      <c r="E119" t="s">
+      <c r="G119" t="s">
         <v>184</v>
-      </c>
-      <c r="G119" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4449,16 +4449,16 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
+        <v>237</v>
+      </c>
+      <c r="D120" t="s">
         <v>170</v>
       </c>
-      <c r="D120" t="s">
+      <c r="F120" t="s">
         <v>171</v>
       </c>
-      <c r="E120" t="s">
-        <v>114</v>
-      </c>
       <c r="G120" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4469,16 +4469,16 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>237</v>
       </c>
       <c r="D121" t="s">
+        <v>113</v>
+      </c>
+      <c r="F121" t="s">
         <v>143</v>
       </c>
-      <c r="E121" t="s">
-        <v>114</v>
-      </c>
       <c r="G121" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>8</v>
       </c>
       <c r="C122" t="s">
+        <v>237</v>
+      </c>
+      <c r="D122" t="s">
         <v>170</v>
       </c>
-      <c r="D122" t="s">
+      <c r="F122" t="s">
         <v>171</v>
       </c>
-      <c r="E122" t="s">
-        <v>114</v>
-      </c>
       <c r="G122" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
+        <v>237</v>
+      </c>
+      <c r="D123" t="s">
         <v>170</v>
       </c>
-      <c r="D123" t="s">
+      <c r="F123" t="s">
         <v>171</v>
       </c>
-      <c r="E123" t="s">
-        <v>114</v>
-      </c>
       <c r="G123" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4529,16 +4529,16 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
+        <v>237</v>
+      </c>
+      <c r="D124" t="s">
         <v>242</v>
       </c>
-      <c r="D124" t="s">
+      <c r="F124" t="s">
         <v>243</v>
       </c>
-      <c r="E124" t="s">
-        <v>165</v>
-      </c>
       <c r="G124" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4549,16 +4549,16 @@
         <v>8</v>
       </c>
       <c r="C125" t="s">
+        <v>237</v>
+      </c>
+      <c r="D125" t="s">
         <v>242</v>
       </c>
-      <c r="D125" t="s">
+      <c r="F125" t="s">
         <v>243</v>
       </c>
-      <c r="E125" t="s">
-        <v>165</v>
-      </c>
       <c r="G125" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4569,16 +4569,16 @@
         <v>8</v>
       </c>
       <c r="C126" t="s">
+        <v>237</v>
+      </c>
+      <c r="D126" t="s">
         <v>242</v>
       </c>
-      <c r="D126" t="s">
+      <c r="F126" t="s">
         <v>243</v>
       </c>
-      <c r="E126" t="s">
-        <v>165</v>
-      </c>
       <c r="G126" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4589,16 +4589,16 @@
         <v>8</v>
       </c>
       <c r="C127" t="s">
+        <v>237</v>
+      </c>
+      <c r="D127" t="s">
         <v>242</v>
       </c>
-      <c r="D127" t="s">
+      <c r="F127" t="s">
         <v>243</v>
       </c>
-      <c r="E127" t="s">
-        <v>165</v>
-      </c>
       <c r="G127" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4609,16 +4609,16 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
+        <v>237</v>
+      </c>
+      <c r="D128" t="s">
         <v>242</v>
       </c>
-      <c r="D128" t="s">
+      <c r="F128" t="s">
         <v>243</v>
       </c>
-      <c r="E128" t="s">
-        <v>165</v>
-      </c>
       <c r="G128" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>237</v>
+      </c>
+      <c r="D129" t="s">
         <v>242</v>
       </c>
-      <c r="D129" t="s">
+      <c r="F129" t="s">
         <v>249</v>
       </c>
-      <c r="E129" t="s">
-        <v>165</v>
-      </c>
       <c r="G129" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
+        <v>237</v>
+      </c>
+      <c r="D130" t="s">
         <v>242</v>
       </c>
-      <c r="D130" t="s">
+      <c r="F130" t="s">
         <v>251</v>
       </c>
-      <c r="E130" t="s">
-        <v>165</v>
-      </c>
       <c r="G130" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
+        <v>237</v>
+      </c>
+      <c r="D131" t="s">
         <v>242</v>
       </c>
-      <c r="D131" t="s">
+      <c r="F131" t="s">
         <v>253</v>
       </c>
-      <c r="E131" t="s">
-        <v>165</v>
-      </c>
       <c r="G131" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,16 +4689,16 @@
         <v>8</v>
       </c>
       <c r="C132" t="s">
+        <v>237</v>
+      </c>
+      <c r="D132" t="s">
         <v>255</v>
       </c>
-      <c r="D132" t="s">
+      <c r="F132" t="s">
         <v>256</v>
       </c>
-      <c r="E132" t="s">
-        <v>165</v>
-      </c>
       <c r="G132" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4709,16 +4709,16 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
+        <v>237</v>
+      </c>
+      <c r="D133" t="s">
         <v>189</v>
       </c>
-      <c r="D133" t="s">
+      <c r="F133" t="s">
         <v>190</v>
       </c>
-      <c r="E133" t="s">
-        <v>114</v>
-      </c>
       <c r="G133" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4729,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="C134" t="s">
+        <v>259</v>
+      </c>
+      <c r="D134" t="s">
         <v>175</v>
       </c>
-      <c r="D134" t="s">
+      <c r="F134" t="s">
         <v>176</v>
       </c>
-      <c r="E134" t="s">
-        <v>165</v>
-      </c>
       <c r="G134" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4749,16 +4749,16 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
+        <v>259</v>
+      </c>
+      <c r="D135" t="s">
         <v>175</v>
       </c>
-      <c r="D135" t="s">
+      <c r="F135" t="s">
         <v>176</v>
       </c>
-      <c r="E135" t="s">
-        <v>165</v>
-      </c>
       <c r="G135" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4769,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="C136" t="s">
+        <v>259</v>
+      </c>
+      <c r="D136" t="s">
         <v>175</v>
       </c>
-      <c r="D136" t="s">
+      <c r="F136" t="s">
         <v>176</v>
       </c>
-      <c r="E136" t="s">
-        <v>165</v>
-      </c>
       <c r="G136" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4789,16 +4789,16 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
+        <v>259</v>
+      </c>
+      <c r="D137" t="s">
         <v>175</v>
       </c>
-      <c r="D137" t="s">
+      <c r="F137" t="s">
         <v>176</v>
       </c>
-      <c r="E137" t="s">
-        <v>165</v>
-      </c>
       <c r="G137" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4809,16 +4809,16 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
+        <v>259</v>
+      </c>
+      <c r="D138" t="s">
         <v>175</v>
       </c>
-      <c r="D138" t="s">
+      <c r="F138" t="s">
         <v>176</v>
       </c>
-      <c r="E138" t="s">
-        <v>165</v>
-      </c>
       <c r="G138" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4829,16 +4829,16 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
+        <v>259</v>
+      </c>
+      <c r="D139" t="s">
         <v>265</v>
       </c>
-      <c r="D139" t="s">
+      <c r="F139" t="s">
         <v>266</v>
       </c>
-      <c r="E139" t="s">
+      <c r="G139" t="s">
         <v>225</v>
-      </c>
-      <c r="G139" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
+        <v>259</v>
+      </c>
+      <c r="D140" t="s">
         <v>175</v>
       </c>
-      <c r="D140" t="s">
+      <c r="F140" t="s">
         <v>176</v>
       </c>
-      <c r="E140" t="s">
-        <v>165</v>
-      </c>
       <c r="G140" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4875,13 +4875,13 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G141" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4898,13 +4898,13 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G142" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4915,19 +4915,19 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
+        <v>269</v>
+      </c>
+      <c r="D143" t="s">
         <v>275</v>
       </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
+        <v>271</v>
+      </c>
+      <c r="F143" t="s">
         <v>276</v>
       </c>
-      <c r="E143" t="s">
-        <v>165</v>
-      </c>
-      <c r="F143" t="s">
-        <v>271</v>
-      </c>
       <c r="G143" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4938,19 +4938,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
+        <v>269</v>
+      </c>
+      <c r="D144" t="s">
         <v>275</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
+        <v>271</v>
+      </c>
+      <c r="F144" t="s">
         <v>276</v>
       </c>
-      <c r="E144" t="s">
-        <v>165</v>
-      </c>
-      <c r="F144" t="s">
-        <v>271</v>
-      </c>
       <c r="G144" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4961,19 +4961,19 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
+        <v>269</v>
+      </c>
+      <c r="D145" t="s">
         <v>275</v>
       </c>
-      <c r="D145" t="s">
+      <c r="E145" t="s">
+        <v>271</v>
+      </c>
+      <c r="F145" t="s">
         <v>276</v>
       </c>
-      <c r="E145" t="s">
-        <v>165</v>
-      </c>
-      <c r="F145" t="s">
-        <v>271</v>
-      </c>
       <c r="G145" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4990,13 +4990,13 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G146" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5013,13 +5013,13 @@
         <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F147" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G147" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5036,13 +5036,13 @@
         <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F148" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G148" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5059,13 +5059,13 @@
         <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F149" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G149" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5082,13 +5082,13 @@
         <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F150" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G150" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5105,13 +5105,13 @@
         <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F151" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G151" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5128,13 +5128,13 @@
         <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F152" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G152" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5151,13 +5151,13 @@
         <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F153" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G153" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5174,13 +5174,13 @@
         <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F154" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G154" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5197,13 +5197,13 @@
         <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F155" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G155" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5220,13 +5220,13 @@
         <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="F156" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="G156" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5240,16 +5240,16 @@
         <v>269</v>
       </c>
       <c r="D157" t="s">
+        <v>270</v>
+      </c>
+      <c r="E157" t="s">
+        <v>291</v>
+      </c>
+      <c r="F157" t="s">
         <v>293</v>
       </c>
-      <c r="E157" t="s">
-        <v>165</v>
-      </c>
-      <c r="F157" t="s">
-        <v>291</v>
-      </c>
       <c r="G157" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5266,13 +5266,13 @@
         <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="F158" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="G158" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5289,13 +5289,13 @@
         <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="F159" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="G159" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5312,13 +5312,13 @@
         <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="F160" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="G160" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5335,13 +5335,13 @@
         <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="F161" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="G161" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5358,13 +5358,13 @@
         <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F162" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="G162" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5378,16 +5378,16 @@
         <v>269</v>
       </c>
       <c r="D163" t="s">
+        <v>270</v>
+      </c>
+      <c r="E163" t="s">
         <v>301</v>
-      </c>
-      <c r="E163" t="s">
-        <v>165</v>
       </c>
       <c r="F163" t="s">
         <v>302</v>
       </c>
       <c r="G163" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5404,13 +5404,13 @@
         <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F164" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G164" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5427,13 +5427,13 @@
         <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F165" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G165" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5450,13 +5450,13 @@
         <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F166" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G166" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5473,13 +5473,13 @@
         <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F167" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G167" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5493,16 +5493,16 @@
         <v>269</v>
       </c>
       <c r="D168" t="s">
+        <v>270</v>
+      </c>
+      <c r="E168" t="s">
+        <v>304</v>
+      </c>
+      <c r="F168" t="s">
         <v>309</v>
       </c>
-      <c r="E168" t="s">
-        <v>165</v>
-      </c>
-      <c r="F168" t="s">
-        <v>304</v>
-      </c>
       <c r="G168" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5516,16 +5516,16 @@
         <v>269</v>
       </c>
       <c r="D169" t="s">
+        <v>270</v>
+      </c>
+      <c r="E169" t="s">
+        <v>304</v>
+      </c>
+      <c r="F169" t="s">
         <v>309</v>
       </c>
-      <c r="E169" t="s">
-        <v>165</v>
-      </c>
-      <c r="F169" t="s">
-        <v>304</v>
-      </c>
       <c r="G169" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5542,13 +5542,13 @@
         <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F170" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G170" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5559,16 +5559,16 @@
         <v>8</v>
       </c>
       <c r="C171" t="s">
+        <v>313</v>
+      </c>
+      <c r="D171" t="s">
         <v>163</v>
       </c>
-      <c r="D171" t="s">
+      <c r="F171" t="s">
         <v>164</v>
       </c>
-      <c r="E171" t="s">
-        <v>165</v>
-      </c>
       <c r="G171" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5579,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
+        <v>313</v>
+      </c>
+      <c r="D172" t="s">
         <v>118</v>
       </c>
-      <c r="D172" t="s">
+      <c r="F172" t="s">
         <v>119</v>
       </c>
-      <c r="E172" t="s">
-        <v>114</v>
-      </c>
       <c r="G172" t="s">
-        <v>313</v>
+        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5599,16 +5599,16 @@
         <v>8</v>
       </c>
       <c r="C173" t="s">
+        <v>313</v>
+      </c>
+      <c r="D173" t="s">
         <v>163</v>
       </c>
-      <c r="D173" t="s">
+      <c r="F173" t="s">
         <v>164</v>
       </c>
-      <c r="E173" t="s">
-        <v>165</v>
-      </c>
       <c r="G173" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5619,16 +5619,16 @@
         <v>8</v>
       </c>
       <c r="C174" t="s">
+        <v>313</v>
+      </c>
+      <c r="D174" t="s">
         <v>163</v>
       </c>
-      <c r="D174" t="s">
+      <c r="F174" t="s">
         <v>164</v>
       </c>
-      <c r="E174" t="s">
-        <v>165</v>
-      </c>
       <c r="G174" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>8</v>
       </c>
       <c r="C175" t="s">
+        <v>313</v>
+      </c>
+      <c r="D175" t="s">
         <v>163</v>
       </c>
-      <c r="D175" t="s">
+      <c r="F175" t="s">
         <v>164</v>
       </c>
-      <c r="E175" t="s">
-        <v>165</v>
-      </c>
       <c r="G175" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>8</v>
       </c>
       <c r="C176" t="s">
+        <v>313</v>
+      </c>
+      <c r="D176" t="s">
         <v>163</v>
       </c>
-      <c r="D176" t="s">
+      <c r="F176" t="s">
         <v>164</v>
       </c>
-      <c r="E176" t="s">
-        <v>165</v>
-      </c>
       <c r="G176" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5679,16 +5679,16 @@
         <v>8</v>
       </c>
       <c r="C177" t="s">
+        <v>320</v>
+      </c>
+      <c r="D177" t="s">
         <v>163</v>
       </c>
-      <c r="D177" t="s">
+      <c r="F177" t="s">
         <v>164</v>
       </c>
-      <c r="E177" t="s">
-        <v>165</v>
-      </c>
       <c r="G177" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5699,16 +5699,16 @@
         <v>8</v>
       </c>
       <c r="C178" t="s">
+        <v>320</v>
+      </c>
+      <c r="D178" t="s">
         <v>163</v>
       </c>
-      <c r="D178" t="s">
+      <c r="F178" t="s">
         <v>164</v>
       </c>
-      <c r="E178" t="s">
-        <v>165</v>
-      </c>
       <c r="G178" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5719,16 +5719,16 @@
         <v>8</v>
       </c>
       <c r="C179" t="s">
+        <v>320</v>
+      </c>
+      <c r="D179" t="s">
         <v>163</v>
       </c>
-      <c r="D179" t="s">
+      <c r="F179" t="s">
         <v>164</v>
       </c>
-      <c r="E179" t="s">
-        <v>165</v>
-      </c>
       <c r="G179" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5739,16 +5739,16 @@
         <v>8</v>
       </c>
       <c r="C180" t="s">
+        <v>320</v>
+      </c>
+      <c r="D180" t="s">
         <v>163</v>
       </c>
-      <c r="D180" t="s">
+      <c r="F180" t="s">
         <v>164</v>
       </c>
-      <c r="E180" t="s">
-        <v>165</v>
-      </c>
       <c r="G180" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5765,13 +5765,13 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G181" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5788,13 +5788,13 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G182" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5811,13 +5811,13 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G183" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5834,13 +5834,13 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G184" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5857,13 +5857,13 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G185" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5880,13 +5880,13 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G186" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5903,13 +5903,13 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G187" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5926,13 +5926,13 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G188" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5949,13 +5949,13 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G189" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5972,13 +5972,13 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G190" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5995,13 +5995,13 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G191" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6018,13 +6018,13 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G192" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
+        <v>325</v>
+      </c>
+      <c r="D193" t="s">
         <v>275</v>
       </c>
-      <c r="D193" t="s">
+      <c r="E193" t="s">
+        <v>327</v>
+      </c>
+      <c r="F193" t="s">
         <v>341</v>
       </c>
-      <c r="E193" t="s">
-        <v>165</v>
-      </c>
-      <c r="F193" t="s">
-        <v>327</v>
-      </c>
       <c r="G193" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6064,13 +6064,13 @@
         <v>326</v>
       </c>
       <c r="E194" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G194" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6087,13 +6087,13 @@
         <v>326</v>
       </c>
       <c r="E195" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G195" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6110,13 +6110,13 @@
         <v>326</v>
       </c>
       <c r="E196" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G196" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6133,13 +6133,13 @@
         <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G197" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6156,13 +6156,13 @@
         <v>326</v>
       </c>
       <c r="E198" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G198" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6176,16 +6176,16 @@
         <v>325</v>
       </c>
       <c r="D199" t="s">
+        <v>326</v>
+      </c>
+      <c r="E199" t="s">
         <v>348</v>
-      </c>
-      <c r="E199" t="s">
-        <v>165</v>
       </c>
       <c r="F199" t="s">
         <v>349</v>
       </c>
       <c r="G199" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6199,16 +6199,16 @@
         <v>325</v>
       </c>
       <c r="D200" t="s">
+        <v>326</v>
+      </c>
+      <c r="E200" t="s">
         <v>348</v>
-      </c>
-      <c r="E200" t="s">
-        <v>165</v>
       </c>
       <c r="F200" t="s">
         <v>349</v>
       </c>
       <c r="G200" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6222,16 +6222,16 @@
         <v>325</v>
       </c>
       <c r="D201" t="s">
+        <v>326</v>
+      </c>
+      <c r="E201" t="s">
         <v>348</v>
-      </c>
-      <c r="E201" t="s">
-        <v>165</v>
       </c>
       <c r="F201" t="s">
         <v>349</v>
       </c>
       <c r="G201" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6245,16 +6245,16 @@
         <v>325</v>
       </c>
       <c r="D202" t="s">
+        <v>326</v>
+      </c>
+      <c r="E202" t="s">
         <v>348</v>
-      </c>
-      <c r="E202" t="s">
-        <v>165</v>
       </c>
       <c r="F202" t="s">
         <v>349</v>
       </c>
       <c r="G202" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>325</v>
+      </c>
+      <c r="D203" t="s">
         <v>275</v>
       </c>
-      <c r="D203" t="s">
+      <c r="E203" t="s">
+        <v>348</v>
+      </c>
+      <c r="F203" t="s">
         <v>341</v>
       </c>
-      <c r="E203" t="s">
-        <v>165</v>
-      </c>
-      <c r="F203" t="s">
-        <v>349</v>
-      </c>
       <c r="G203" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6291,16 +6291,16 @@
         <v>325</v>
       </c>
       <c r="D204" t="s">
+        <v>326</v>
+      </c>
+      <c r="E204" t="s">
         <v>348</v>
-      </c>
-      <c r="E204" t="s">
-        <v>165</v>
       </c>
       <c r="F204" t="s">
         <v>349</v>
       </c>
       <c r="G204" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6314,16 +6314,16 @@
         <v>325</v>
       </c>
       <c r="D205" t="s">
+        <v>326</v>
+      </c>
+      <c r="E205" t="s">
         <v>356</v>
-      </c>
-      <c r="E205" t="s">
-        <v>165</v>
       </c>
       <c r="F205" t="s">
         <v>357</v>
       </c>
       <c r="G205" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6337,16 +6337,16 @@
         <v>325</v>
       </c>
       <c r="D206" t="s">
+        <v>326</v>
+      </c>
+      <c r="E206" t="s">
         <v>356</v>
-      </c>
-      <c r="E206" t="s">
-        <v>165</v>
       </c>
       <c r="F206" t="s">
         <v>357</v>
       </c>
       <c r="G206" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6360,16 +6360,16 @@
         <v>325</v>
       </c>
       <c r="D207" t="s">
+        <v>326</v>
+      </c>
+      <c r="E207" t="s">
         <v>356</v>
-      </c>
-      <c r="E207" t="s">
-        <v>165</v>
       </c>
       <c r="F207" t="s">
         <v>357</v>
       </c>
       <c r="G207" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>325</v>
+      </c>
+      <c r="D208" t="s">
         <v>275</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
+        <v>356</v>
+      </c>
+      <c r="F208" t="s">
         <v>341</v>
       </c>
-      <c r="E208" t="s">
-        <v>165</v>
-      </c>
-      <c r="F208" t="s">
-        <v>357</v>
-      </c>
       <c r="G208" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6406,16 +6406,16 @@
         <v>325</v>
       </c>
       <c r="D209" t="s">
+        <v>326</v>
+      </c>
+      <c r="E209" t="s">
         <v>356</v>
-      </c>
-      <c r="E209" t="s">
-        <v>165</v>
       </c>
       <c r="F209" t="s">
         <v>357</v>
       </c>
       <c r="G209" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6432,13 +6432,13 @@
         <v>364</v>
       </c>
       <c r="E210" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G210" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6455,13 +6455,13 @@
         <v>364</v>
       </c>
       <c r="E211" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G211" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6478,13 +6478,13 @@
         <v>364</v>
       </c>
       <c r="E212" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G212" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6501,13 +6501,13 @@
         <v>364</v>
       </c>
       <c r="E213" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G213" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6524,13 +6524,13 @@
         <v>364</v>
       </c>
       <c r="E214" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G214" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="D215" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E215" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F215" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="G215" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6570,13 +6570,13 @@
         <v>364</v>
       </c>
       <c r="E216" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G216" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6593,13 +6593,13 @@
         <v>364</v>
       </c>
       <c r="E217" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G217" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6616,13 +6616,13 @@
         <v>364</v>
       </c>
       <c r="E218" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G218" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6639,13 +6639,13 @@
         <v>364</v>
       </c>
       <c r="E219" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G219" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="D220" t="s">
+        <v>270</v>
+      </c>
+      <c r="E220" t="s">
+        <v>365</v>
+      </c>
+      <c r="F220" t="s">
         <v>309</v>
       </c>
-      <c r="E220" t="s">
-        <v>165</v>
-      </c>
-      <c r="F220" t="s">
-        <v>365</v>
-      </c>
       <c r="G220" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6685,13 +6685,13 @@
         <v>364</v>
       </c>
       <c r="E221" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G221" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6708,13 +6708,13 @@
         <v>364</v>
       </c>
       <c r="E222" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G222" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6731,13 +6731,13 @@
         <v>364</v>
       </c>
       <c r="E223" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G223" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6754,13 +6754,13 @@
         <v>364</v>
       </c>
       <c r="E224" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G224" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6777,13 +6777,13 @@
         <v>364</v>
       </c>
       <c r="E225" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G225" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6794,19 +6794,19 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
+        <v>363</v>
+      </c>
+      <c r="D226" t="s">
         <v>275</v>
       </c>
-      <c r="D226" t="s">
+      <c r="E226" t="s">
+        <v>365</v>
+      </c>
+      <c r="F226" t="s">
         <v>276</v>
       </c>
-      <c r="E226" t="s">
-        <v>165</v>
-      </c>
-      <c r="F226" t="s">
-        <v>365</v>
-      </c>
       <c r="G226" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6823,13 +6823,13 @@
         <v>364</v>
       </c>
       <c r="E227" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G227" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6840,19 +6840,19 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
+        <v>363</v>
+      </c>
+      <c r="D228" t="s">
         <v>163</v>
       </c>
-      <c r="D228" t="s">
+      <c r="E228" t="s">
+        <v>365</v>
+      </c>
+      <c r="F228" t="s">
         <v>164</v>
       </c>
-      <c r="E228" t="s">
-        <v>165</v>
-      </c>
-      <c r="F228" t="s">
-        <v>365</v>
-      </c>
       <c r="G228" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6866,16 +6866,16 @@
         <v>363</v>
       </c>
       <c r="D229" t="s">
+        <v>364</v>
+      </c>
+      <c r="E229" t="s">
         <v>386</v>
-      </c>
-      <c r="E229" t="s">
-        <v>165</v>
       </c>
       <c r="F229" t="s">
         <v>387</v>
       </c>
       <c r="G229" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6889,16 +6889,16 @@
         <v>363</v>
       </c>
       <c r="D230" t="s">
+        <v>364</v>
+      </c>
+      <c r="E230" t="s">
         <v>386</v>
-      </c>
-      <c r="E230" t="s">
-        <v>165</v>
       </c>
       <c r="F230" t="s">
         <v>387</v>
       </c>
       <c r="G230" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="D231" t="s">
+        <v>270</v>
+      </c>
+      <c r="E231" t="s">
+        <v>386</v>
+      </c>
+      <c r="F231" t="s">
         <v>293</v>
       </c>
-      <c r="E231" t="s">
-        <v>165</v>
-      </c>
-      <c r="F231" t="s">
-        <v>387</v>
-      </c>
       <c r="G231" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="D232" t="s">
+        <v>270</v>
+      </c>
+      <c r="E232" t="s">
+        <v>386</v>
+      </c>
+      <c r="F232" t="s">
         <v>309</v>
       </c>
-      <c r="E232" t="s">
-        <v>165</v>
-      </c>
-      <c r="F232" t="s">
-        <v>387</v>
-      </c>
       <c r="G232" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6958,16 +6958,16 @@
         <v>363</v>
       </c>
       <c r="D233" t="s">
+        <v>364</v>
+      </c>
+      <c r="E233" t="s">
         <v>386</v>
-      </c>
-      <c r="E233" t="s">
-        <v>165</v>
       </c>
       <c r="F233" t="s">
         <v>387</v>
       </c>
       <c r="G233" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6981,16 +6981,16 @@
         <v>363</v>
       </c>
       <c r="D234" t="s">
+        <v>364</v>
+      </c>
+      <c r="E234" t="s">
         <v>386</v>
-      </c>
-      <c r="E234" t="s">
-        <v>165</v>
       </c>
       <c r="F234" t="s">
         <v>387</v>
       </c>
       <c r="G234" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7004,16 +7004,16 @@
         <v>363</v>
       </c>
       <c r="D235" t="s">
+        <v>364</v>
+      </c>
+      <c r="E235" t="s">
         <v>386</v>
-      </c>
-      <c r="E235" t="s">
-        <v>165</v>
       </c>
       <c r="F235" t="s">
         <v>387</v>
       </c>
       <c r="G235" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7027,16 +7027,16 @@
         <v>363</v>
       </c>
       <c r="D236" t="s">
+        <v>364</v>
+      </c>
+      <c r="E236" t="s">
         <v>386</v>
-      </c>
-      <c r="E236" t="s">
-        <v>165</v>
       </c>
       <c r="F236" t="s">
         <v>387</v>
       </c>
       <c r="G236" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7050,16 +7050,16 @@
         <v>363</v>
       </c>
       <c r="D237" t="s">
+        <v>364</v>
+      </c>
+      <c r="E237" t="s">
         <v>386</v>
-      </c>
-      <c r="E237" t="s">
-        <v>165</v>
       </c>
       <c r="F237" t="s">
         <v>387</v>
       </c>
       <c r="G237" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7073,16 +7073,16 @@
         <v>363</v>
       </c>
       <c r="D238" t="s">
+        <v>364</v>
+      </c>
+      <c r="E238" t="s">
         <v>386</v>
-      </c>
-      <c r="E238" t="s">
-        <v>165</v>
       </c>
       <c r="F238" t="s">
         <v>387</v>
       </c>
       <c r="G238" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7096,16 +7096,16 @@
         <v>363</v>
       </c>
       <c r="D239" t="s">
+        <v>364</v>
+      </c>
+      <c r="E239" t="s">
         <v>398</v>
-      </c>
-      <c r="E239" t="s">
-        <v>165</v>
       </c>
       <c r="F239" t="s">
         <v>399</v>
       </c>
       <c r="G239" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7116,19 +7116,19 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>401</v>
+      </c>
+      <c r="D240" t="s">
         <v>163</v>
       </c>
-      <c r="D240" t="s">
+      <c r="E240" t="s">
+        <v>402</v>
+      </c>
+      <c r="F240" t="s">
         <v>164</v>
       </c>
-      <c r="E240" t="s">
-        <v>165</v>
-      </c>
-      <c r="F240" t="s">
-        <v>401</v>
-      </c>
       <c r="G240" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7139,19 +7139,19 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>401</v>
+      </c>
+      <c r="D241" t="s">
         <v>163</v>
       </c>
-      <c r="D241" t="s">
+      <c r="E241" t="s">
+        <v>402</v>
+      </c>
+      <c r="F241" t="s">
         <v>164</v>
       </c>
-      <c r="E241" t="s">
-        <v>165</v>
-      </c>
-      <c r="F241" t="s">
-        <v>401</v>
-      </c>
       <c r="G241" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7162,19 +7162,19 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>401</v>
+      </c>
+      <c r="D242" t="s">
         <v>163</v>
       </c>
-      <c r="D242" t="s">
+      <c r="E242" t="s">
+        <v>402</v>
+      </c>
+      <c r="F242" t="s">
         <v>164</v>
       </c>
-      <c r="E242" t="s">
-        <v>165</v>
-      </c>
-      <c r="F242" t="s">
-        <v>401</v>
-      </c>
       <c r="G242" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7185,19 +7185,19 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>401</v>
+      </c>
+      <c r="D243" t="s">
         <v>163</v>
       </c>
-      <c r="D243" t="s">
+      <c r="E243" t="s">
+        <v>402</v>
+      </c>
+      <c r="F243" t="s">
         <v>164</v>
       </c>
-      <c r="E243" t="s">
-        <v>165</v>
-      </c>
-      <c r="F243" t="s">
-        <v>401</v>
-      </c>
       <c r="G243" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7208,19 +7208,19 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>401</v>
+      </c>
+      <c r="D244" t="s">
         <v>163</v>
       </c>
-      <c r="D244" t="s">
+      <c r="E244" t="s">
+        <v>402</v>
+      </c>
+      <c r="F244" t="s">
         <v>164</v>
       </c>
-      <c r="E244" t="s">
-        <v>165</v>
-      </c>
-      <c r="F244" t="s">
-        <v>401</v>
-      </c>
       <c r="G244" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7231,19 +7231,19 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>401</v>
+      </c>
+      <c r="D245" t="s">
         <v>163</v>
       </c>
-      <c r="D245" t="s">
+      <c r="E245" t="s">
+        <v>402</v>
+      </c>
+      <c r="F245" t="s">
         <v>164</v>
       </c>
-      <c r="E245" t="s">
-        <v>165</v>
-      </c>
-      <c r="F245" t="s">
-        <v>401</v>
-      </c>
       <c r="G245" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>401</v>
+      </c>
+      <c r="D246" t="s">
         <v>255</v>
       </c>
-      <c r="D246" t="s">
+      <c r="E246" t="s">
         <v>409</v>
-      </c>
-      <c r="E246" t="s">
-        <v>165</v>
       </c>
       <c r="F246" t="s">
         <v>410</v>
       </c>
       <c r="G246" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7277,16 +7277,16 @@
         <v>8</v>
       </c>
       <c r="C247" t="s">
+        <v>412</v>
+      </c>
+      <c r="D247" t="s">
         <v>95</v>
       </c>
-      <c r="D247" t="s">
+      <c r="F247" t="s">
         <v>96</v>
       </c>
-      <c r="E247" t="s">
+      <c r="G247" t="s">
         <v>97</v>
-      </c>
-      <c r="G247" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7297,16 +7297,16 @@
         <v>8</v>
       </c>
       <c r="C248" t="s">
+        <v>412</v>
+      </c>
+      <c r="D248" t="s">
         <v>95</v>
       </c>
-      <c r="D248" t="s">
+      <c r="F248" t="s">
         <v>96</v>
       </c>
-      <c r="E248" t="s">
+      <c r="G248" t="s">
         <v>97</v>
-      </c>
-      <c r="G248" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7317,16 +7317,16 @@
         <v>8</v>
       </c>
       <c r="C249" t="s">
+        <v>412</v>
+      </c>
+      <c r="D249" t="s">
         <v>415</v>
       </c>
-      <c r="D249" t="s">
+      <c r="F249" t="s">
         <v>416</v>
       </c>
-      <c r="E249" t="s">
+      <c r="G249" t="s">
         <v>97</v>
-      </c>
-      <c r="G249" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7337,16 +7337,16 @@
         <v>8</v>
       </c>
       <c r="C250" t="s">
+        <v>412</v>
+      </c>
+      <c r="D250" t="s">
         <v>95</v>
       </c>
-      <c r="D250" t="s">
+      <c r="F250" t="s">
         <v>96</v>
       </c>
-      <c r="E250" t="s">
+      <c r="G250" t="s">
         <v>97</v>
-      </c>
-      <c r="G250" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7357,16 +7357,16 @@
         <v>8</v>
       </c>
       <c r="C251" t="s">
+        <v>412</v>
+      </c>
+      <c r="D251" t="s">
         <v>95</v>
       </c>
-      <c r="D251" t="s">
+      <c r="F251" t="s">
         <v>96</v>
       </c>
-      <c r="E251" t="s">
+      <c r="G251" t="s">
         <v>97</v>
-      </c>
-      <c r="G251" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7377,16 +7377,16 @@
         <v>8</v>
       </c>
       <c r="C252" t="s">
+        <v>412</v>
+      </c>
+      <c r="D252" t="s">
         <v>95</v>
       </c>
-      <c r="D252" t="s">
+      <c r="F252" t="s">
         <v>96</v>
       </c>
-      <c r="E252" t="s">
+      <c r="G252" t="s">
         <v>97</v>
-      </c>
-      <c r="G252" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7402,11 +7402,11 @@
       <c r="D253" t="s">
         <v>422</v>
       </c>
-      <c r="E253" t="s">
-        <v>165</v>
+      <c r="F253" t="s">
+        <v>423</v>
       </c>
       <c r="G253" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7417,16 +7417,16 @@
         <v>8</v>
       </c>
       <c r="C254" t="s">
+        <v>421</v>
+      </c>
+      <c r="D254" t="s">
         <v>219</v>
       </c>
-      <c r="D254" t="s">
+      <c r="F254" t="s">
         <v>220</v>
       </c>
-      <c r="E254" t="s">
-        <v>92</v>
-      </c>
       <c r="G254" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7437,16 +7437,16 @@
         <v>8</v>
       </c>
       <c r="C255" t="s">
+        <v>421</v>
+      </c>
+      <c r="D255" t="s">
         <v>426</v>
       </c>
-      <c r="D255" t="s">
+      <c r="F255" t="s">
         <v>427</v>
       </c>
-      <c r="E255" t="s">
-        <v>92</v>
-      </c>
       <c r="G255" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7457,16 +7457,16 @@
         <v>8</v>
       </c>
       <c r="C256" t="s">
+        <v>421</v>
+      </c>
+      <c r="D256" t="s">
         <v>426</v>
       </c>
-      <c r="D256" t="s">
+      <c r="F256" t="s">
         <v>427</v>
       </c>
-      <c r="E256" t="s">
-        <v>92</v>
-      </c>
       <c r="G256" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7477,16 +7477,16 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
+        <v>421</v>
+      </c>
+      <c r="D257" t="s">
         <v>426</v>
       </c>
-      <c r="D257" t="s">
+      <c r="F257" t="s">
         <v>427</v>
       </c>
-      <c r="E257" t="s">
-        <v>92</v>
-      </c>
       <c r="G257" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7497,16 +7497,16 @@
         <v>8</v>
       </c>
       <c r="C258" t="s">
-        <v>325</v>
+        <v>421</v>
       </c>
       <c r="D258" t="s">
         <v>326</v>
       </c>
-      <c r="E258" t="s">
-        <v>165</v>
+      <c r="F258" t="s">
+        <v>328</v>
       </c>
       <c r="G258" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7517,16 +7517,16 @@
         <v>8</v>
       </c>
       <c r="C259" t="s">
+        <v>421</v>
+      </c>
+      <c r="D259" t="s">
         <v>426</v>
       </c>
-      <c r="D259" t="s">
+      <c r="F259" t="s">
         <v>427</v>
       </c>
-      <c r="E259" t="s">
-        <v>92</v>
-      </c>
       <c r="G259" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7537,16 +7537,16 @@
         <v>8</v>
       </c>
       <c r="C260" t="s">
+        <v>421</v>
+      </c>
+      <c r="D260" t="s">
         <v>163</v>
       </c>
-      <c r="D260" t="s">
+      <c r="F260" t="s">
         <v>164</v>
       </c>
-      <c r="E260" t="s">
-        <v>165</v>
-      </c>
       <c r="G260" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7557,16 +7557,16 @@
         <v>8</v>
       </c>
       <c r="C261" t="s">
+        <v>421</v>
+      </c>
+      <c r="D261" t="s">
         <v>434</v>
       </c>
-      <c r="D261" t="s">
+      <c r="F261" t="s">
         <v>435</v>
       </c>
-      <c r="E261" t="s">
+      <c r="G261" t="s">
         <v>197</v>
-      </c>
-      <c r="G261" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7577,16 +7577,16 @@
         <v>8</v>
       </c>
       <c r="C262" t="s">
+        <v>421</v>
+      </c>
+      <c r="D262" t="s">
         <v>163</v>
       </c>
-      <c r="D262" t="s">
+      <c r="F262" t="s">
         <v>164</v>
       </c>
-      <c r="E262" t="s">
-        <v>165</v>
-      </c>
       <c r="G262" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7597,16 +7597,16 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
+        <v>421</v>
+      </c>
+      <c r="D263" t="s">
         <v>438</v>
       </c>
-      <c r="D263" t="s">
+      <c r="F263" t="s">
         <v>439</v>
       </c>
-      <c r="E263" t="s">
+      <c r="G263" t="s">
         <v>184</v>
-      </c>
-      <c r="G263" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7617,16 +7617,16 @@
         <v>8</v>
       </c>
       <c r="C264" t="s">
+        <v>421</v>
+      </c>
+      <c r="D264" t="s">
         <v>31</v>
       </c>
-      <c r="D264" t="s">
+      <c r="F264" t="s">
         <v>32</v>
       </c>
-      <c r="E264" t="s">
+      <c r="G264" t="s">
         <v>33</v>
-      </c>
-      <c r="G264" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7637,16 +7637,16 @@
         <v>8</v>
       </c>
       <c r="C265" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="D265" t="s">
         <v>10</v>
       </c>
-      <c r="E265" t="s">
-        <v>11</v>
+      <c r="F265" t="s">
+        <v>12</v>
       </c>
       <c r="G265" t="s">
-        <v>423</v>
+        <v>13</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7657,16 +7657,16 @@
         <v>8</v>
       </c>
       <c r="C266" t="s">
+        <v>421</v>
+      </c>
+      <c r="D266" t="s">
         <v>443</v>
       </c>
-      <c r="D266" t="s">
+      <c r="F266" t="s">
         <v>444</v>
       </c>
-      <c r="E266" t="s">
-        <v>114</v>
-      </c>
       <c r="G266" t="s">
-        <v>423</v>
+        <v>116</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7677,16 +7677,16 @@
         <v>8</v>
       </c>
       <c r="C267" t="s">
+        <v>446</v>
+      </c>
+      <c r="D267" t="s">
         <v>118</v>
       </c>
-      <c r="D267" t="s">
+      <c r="F267" t="s">
         <v>119</v>
       </c>
-      <c r="E267" t="s">
-        <v>114</v>
-      </c>
       <c r="G267" t="s">
-        <v>446</v>
+        <v>116</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7697,16 +7697,16 @@
         <v>8</v>
       </c>
       <c r="C268" t="s">
-        <v>202</v>
+        <v>448</v>
       </c>
       <c r="D268" t="s">
         <v>203</v>
       </c>
-      <c r="E268" t="s">
+      <c r="F268" t="s">
+        <v>204</v>
+      </c>
+      <c r="G268" t="s">
         <v>184</v>
-      </c>
-      <c r="G268" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7717,16 +7717,16 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
+        <v>450</v>
+      </c>
+      <c r="D269" t="s">
         <v>118</v>
       </c>
-      <c r="D269" t="s">
+      <c r="F269" t="s">
         <v>119</v>
       </c>
-      <c r="E269" t="s">
-        <v>114</v>
-      </c>
       <c r="G269" t="s">
-        <v>450</v>
+        <v>116</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7737,16 +7737,16 @@
         <v>8</v>
       </c>
       <c r="C270" t="s">
+        <v>450</v>
+      </c>
+      <c r="D270" t="s">
         <v>118</v>
       </c>
-      <c r="D270" t="s">
+      <c r="F270" t="s">
         <v>119</v>
       </c>
-      <c r="E270" t="s">
-        <v>114</v>
-      </c>
       <c r="G270" t="s">
-        <v>450</v>
+        <v>116</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7762,11 +7762,11 @@
       <c r="D271" t="s">
         <v>454</v>
       </c>
-      <c r="E271" t="s">
-        <v>114</v>
+      <c r="F271" t="s">
+        <v>455</v>
       </c>
       <c r="G271" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7782,11 +7782,11 @@
       <c r="D272" t="s">
         <v>454</v>
       </c>
-      <c r="E272" t="s">
-        <v>114</v>
+      <c r="F272" t="s">
+        <v>455</v>
       </c>
       <c r="G272" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7802,11 +7802,11 @@
       <c r="D273" t="s">
         <v>454</v>
       </c>
-      <c r="E273" t="s">
-        <v>114</v>
+      <c r="F273" t="s">
+        <v>455</v>
       </c>
       <c r="G273" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7822,11 +7822,11 @@
       <c r="D274" t="s">
         <v>454</v>
       </c>
-      <c r="E274" t="s">
-        <v>114</v>
+      <c r="F274" t="s">
+        <v>455</v>
       </c>
       <c r="G274" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7842,11 +7842,11 @@
       <c r="D275" t="s">
         <v>454</v>
       </c>
-      <c r="E275" t="s">
-        <v>114</v>
+      <c r="F275" t="s">
+        <v>455</v>
       </c>
       <c r="G275" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7862,11 +7862,11 @@
       <c r="D276" t="s">
         <v>454</v>
       </c>
-      <c r="E276" t="s">
-        <v>114</v>
+      <c r="F276" t="s">
+        <v>455</v>
       </c>
       <c r="G276" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7882,11 +7882,11 @@
       <c r="D277" t="s">
         <v>454</v>
       </c>
-      <c r="E277" t="s">
-        <v>114</v>
+      <c r="F277" t="s">
+        <v>455</v>
       </c>
       <c r="G277" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7897,16 +7897,16 @@
         <v>8</v>
       </c>
       <c r="C278" t="s">
-        <v>202</v>
+        <v>463</v>
       </c>
       <c r="D278" t="s">
         <v>203</v>
       </c>
-      <c r="E278" t="s">
+      <c r="F278" t="s">
+        <v>204</v>
+      </c>
+      <c r="G278" t="s">
         <v>184</v>
-      </c>
-      <c r="G278" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7917,16 +7917,16 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
-        <v>51</v>
+        <v>463</v>
       </c>
       <c r="D279" t="s">
         <v>52</v>
       </c>
-      <c r="E279" t="s">
+      <c r="F279" t="s">
+        <v>54</v>
+      </c>
+      <c r="G279" t="s">
         <v>33</v>
-      </c>
-      <c r="G279" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7937,16 +7937,16 @@
         <v>8</v>
       </c>
       <c r="C280" t="s">
-        <v>9</v>
+        <v>463</v>
       </c>
       <c r="D280" t="s">
         <v>10</v>
       </c>
-      <c r="E280" t="s">
-        <v>11</v>
+      <c r="F280" t="s">
+        <v>12</v>
       </c>
       <c r="G280" t="s">
-        <v>463</v>
+        <v>13</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7957,16 +7957,16 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
+        <v>463</v>
+      </c>
+      <c r="D281" t="s">
         <v>170</v>
       </c>
-      <c r="D281" t="s">
+      <c r="F281" t="s">
         <v>171</v>
       </c>
-      <c r="E281" t="s">
-        <v>114</v>
-      </c>
       <c r="G281" t="s">
-        <v>463</v>
+        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7977,16 +7977,16 @@
         <v>8</v>
       </c>
       <c r="C282" t="s">
+        <v>463</v>
+      </c>
+      <c r="D282" t="s">
         <v>124</v>
       </c>
-      <c r="D282" t="s">
+      <c r="F282" t="s">
         <v>125</v>
       </c>
-      <c r="E282" t="s">
+      <c r="G282" t="s">
         <v>126</v>
-      </c>
-      <c r="G282" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7997,16 +7997,16 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>363</v>
+        <v>469</v>
       </c>
       <c r="D283" t="s">
-        <v>398</v>
-      </c>
-      <c r="E283" t="s">
-        <v>165</v>
+        <v>364</v>
+      </c>
+      <c r="F283" t="s">
+        <v>399</v>
       </c>
       <c r="G283" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8017,16 +8017,16 @@
         <v>8</v>
       </c>
       <c r="C284" t="s">
+        <v>471</v>
+      </c>
+      <c r="D284" t="s">
         <v>124</v>
       </c>
-      <c r="D284" t="s">
+      <c r="F284" t="s">
         <v>125</v>
       </c>
-      <c r="E284" t="s">
+      <c r="G284" t="s">
         <v>126</v>
-      </c>
-      <c r="G284" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8037,16 +8037,16 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
+        <v>473</v>
+      </c>
+      <c r="D285" t="s">
         <v>170</v>
       </c>
-      <c r="D285" t="s">
+      <c r="F285" t="s">
         <v>171</v>
       </c>
-      <c r="E285" t="s">
-        <v>114</v>
-      </c>
       <c r="G285" t="s">
-        <v>473</v>
+        <v>116</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8057,16 +8057,16 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
+        <v>475</v>
+      </c>
+      <c r="D286" t="s">
         <v>438</v>
       </c>
-      <c r="D286" t="s">
+      <c r="F286" t="s">
         <v>439</v>
       </c>
-      <c r="E286" t="s">
+      <c r="G286" t="s">
         <v>184</v>
-      </c>
-      <c r="G286" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8077,16 +8077,16 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
+        <v>475</v>
+      </c>
+      <c r="D287" t="s">
         <v>438</v>
       </c>
-      <c r="D287" t="s">
+      <c r="F287" t="s">
         <v>439</v>
       </c>
-      <c r="E287" t="s">
+      <c r="G287" t="s">
         <v>184</v>
-      </c>
-      <c r="G287" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8097,16 +8097,16 @@
         <v>8</v>
       </c>
       <c r="C288" t="s">
+        <v>475</v>
+      </c>
+      <c r="D288" t="s">
         <v>41</v>
       </c>
-      <c r="D288" t="s">
+      <c r="F288" t="s">
         <v>42</v>
       </c>
-      <c r="E288" t="s">
-        <v>11</v>
-      </c>
       <c r="G288" t="s">
-        <v>475</v>
+        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8117,16 +8117,16 @@
         <v>8</v>
       </c>
       <c r="C289" t="s">
+        <v>475</v>
+      </c>
+      <c r="D289" t="s">
         <v>31</v>
       </c>
-      <c r="D289" t="s">
+      <c r="F289" t="s">
         <v>32</v>
       </c>
-      <c r="E289" t="s">
+      <c r="G289" t="s">
         <v>33</v>
-      </c>
-      <c r="G289" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8137,16 +8137,16 @@
         <v>8</v>
       </c>
       <c r="C290" t="s">
+        <v>475</v>
+      </c>
+      <c r="D290" t="s">
         <v>31</v>
       </c>
-      <c r="D290" t="s">
+      <c r="F290" t="s">
         <v>32</v>
       </c>
-      <c r="E290" t="s">
+      <c r="G290" t="s">
         <v>33</v>
-      </c>
-      <c r="G290" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8157,16 +8157,16 @@
         <v>8</v>
       </c>
       <c r="C291" t="s">
+        <v>475</v>
+      </c>
+      <c r="D291" t="s">
         <v>170</v>
       </c>
-      <c r="D291" t="s">
+      <c r="F291" t="s">
         <v>171</v>
       </c>
-      <c r="E291" t="s">
-        <v>114</v>
-      </c>
       <c r="G291" t="s">
-        <v>475</v>
+        <v>116</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8177,16 +8177,16 @@
         <v>8</v>
       </c>
       <c r="C292" t="s">
+        <v>475</v>
+      </c>
+      <c r="D292" t="s">
         <v>170</v>
       </c>
-      <c r="D292" t="s">
+      <c r="F292" t="s">
         <v>171</v>
       </c>
-      <c r="E292" t="s">
-        <v>114</v>
-      </c>
       <c r="G292" t="s">
-        <v>475</v>
+        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8197,16 +8197,16 @@
         <v>8</v>
       </c>
       <c r="C293" t="s">
+        <v>475</v>
+      </c>
+      <c r="D293" t="s">
         <v>170</v>
       </c>
-      <c r="D293" t="s">
+      <c r="F293" t="s">
         <v>171</v>
       </c>
-      <c r="E293" t="s">
-        <v>114</v>
-      </c>
       <c r="G293" t="s">
-        <v>475</v>
+        <v>116</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8217,16 +8217,16 @@
         <v>8</v>
       </c>
       <c r="C294" t="s">
+        <v>475</v>
+      </c>
+      <c r="D294" t="s">
         <v>170</v>
       </c>
-      <c r="D294" t="s">
+      <c r="F294" t="s">
         <v>171</v>
       </c>
-      <c r="E294" t="s">
-        <v>114</v>
-      </c>
       <c r="G294" t="s">
-        <v>475</v>
+        <v>116</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8237,16 +8237,16 @@
         <v>8</v>
       </c>
       <c r="C295" t="s">
+        <v>485</v>
+      </c>
+      <c r="D295" t="s">
         <v>170</v>
       </c>
-      <c r="D295" t="s">
+      <c r="F295" t="s">
         <v>171</v>
       </c>
-      <c r="E295" t="s">
-        <v>114</v>
-      </c>
       <c r="G295" t="s">
-        <v>485</v>
+        <v>116</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8257,16 +8257,16 @@
         <v>8</v>
       </c>
       <c r="C296" t="s">
+        <v>485</v>
+      </c>
+      <c r="D296" t="s">
         <v>170</v>
       </c>
-      <c r="D296" t="s">
+      <c r="F296" t="s">
         <v>171</v>
       </c>
-      <c r="E296" t="s">
-        <v>114</v>
-      </c>
       <c r="G296" t="s">
-        <v>485</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -25,15 +25,15 @@
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
@@ -46,51 +46,51 @@
     <t>110</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>09 - Education</t>
   </si>
   <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,99 +109,99 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>07 - Health</t>
   </si>
   <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -289,24 +289,24 @@
     <t>140</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,12 +340,12 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -355,45 +355,45 @@
     <t>150</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>01 - General public services</t>
   </si>
   <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,21 +496,21 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>02 - Defence</t>
   </si>
   <si>
@@ -625,12 +625,12 @@
     <t>160</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,42 +655,42 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,12 +811,12 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -826,27 +826,27 @@
     <t>230</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -994,15 +994,15 @@
     <t>310</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1108,15 +1108,15 @@
     <t>320</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,12 +1210,12 @@
     <t>32310</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>04.7.3 - Tourism (CS)</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1282,24 +1282,24 @@
     <t>430</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1378,10 +1378,10 @@
     <t>600</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>60020</t>
@@ -2027,13 +2027,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2096,13 +2096,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2122,7 +2122,7 @@
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
         <v>42</v>
@@ -3195,13 +3195,13 @@
         <v>112</v>
       </c>
       <c r="D63" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="E63" t="s">
         <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="G63" t="s">
         <v>116</v>
@@ -3218,13 +3218,13 @@
         <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="E64" t="s">
         <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="G64" t="s">
         <v>116</v>
@@ -3310,13 +3310,13 @@
         <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="G68" t="s">
         <v>116</v>
@@ -3333,13 +3333,13 @@
         <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G69" t="s">
         <v>116</v>
@@ -3655,13 +3655,13 @@
         <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
       </c>
       <c r="F83" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G83" t="s">
         <v>116</v>
@@ -3701,13 +3701,13 @@
         <v>112</v>
       </c>
       <c r="D85" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="E85" t="s">
         <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="G85" t="s">
         <v>116</v>
@@ -3747,13 +3747,13 @@
         <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="E87" t="s">
         <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="G87" t="s">
         <v>116</v>
@@ -4312,10 +4312,10 @@
         <v>202</v>
       </c>
       <c r="D113" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="F113" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G113" t="s">
         <v>116</v>
@@ -4412,10 +4412,10 @@
         <v>202</v>
       </c>
       <c r="D118" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
       <c r="F118" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="G118" t="s">
         <v>165</v>
@@ -4472,10 +4472,10 @@
         <v>237</v>
       </c>
       <c r="D121" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="F121" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G121" t="s">
         <v>116</v>
@@ -4632,10 +4632,10 @@
         <v>237</v>
       </c>
       <c r="D129" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F129" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G129" t="s">
         <v>165</v>
@@ -4652,10 +4652,10 @@
         <v>237</v>
       </c>
       <c r="D130" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F130" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G130" t="s">
         <v>165</v>
@@ -4672,10 +4672,10 @@
         <v>237</v>
       </c>
       <c r="D131" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="F131" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="G131" t="s">
         <v>165</v>
@@ -5240,13 +5240,13 @@
         <v>269</v>
       </c>
       <c r="D157" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="E157" t="s">
         <v>291</v>
       </c>
       <c r="F157" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="G157" t="s">
         <v>165</v>
@@ -5378,13 +5378,13 @@
         <v>269</v>
       </c>
       <c r="D163" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="E163" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F163" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="G163" t="s">
         <v>165</v>
@@ -5493,13 +5493,13 @@
         <v>269</v>
       </c>
       <c r="D168" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="E168" t="s">
         <v>304</v>
       </c>
       <c r="F168" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="G168" t="s">
         <v>165</v>
@@ -5516,13 +5516,13 @@
         <v>269</v>
       </c>
       <c r="D169" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="E169" t="s">
         <v>304</v>
       </c>
       <c r="F169" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="G169" t="s">
         <v>165</v>
@@ -6038,13 +6038,13 @@
         <v>325</v>
       </c>
       <c r="D193" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="E193" t="s">
         <v>327</v>
       </c>
       <c r="F193" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="G193" t="s">
         <v>165</v>
@@ -6176,13 +6176,13 @@
         <v>325</v>
       </c>
       <c r="D199" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="E199" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F199" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G199" t="s">
         <v>165</v>
@@ -6199,13 +6199,13 @@
         <v>325</v>
       </c>
       <c r="D200" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="E200" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F200" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G200" t="s">
         <v>165</v>
@@ -6222,13 +6222,13 @@
         <v>325</v>
       </c>
       <c r="D201" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="E201" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F201" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G201" t="s">
         <v>165</v>
@@ -6245,13 +6245,13 @@
         <v>325</v>
       </c>
       <c r="D202" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="E202" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F202" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G202" t="s">
         <v>165</v>
@@ -6268,13 +6268,13 @@
         <v>325</v>
       </c>
       <c r="D203" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="E203" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F203" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="G203" t="s">
         <v>165</v>
@@ -6291,13 +6291,13 @@
         <v>325</v>
       </c>
       <c r="D204" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="E204" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F204" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G204" t="s">
         <v>165</v>
@@ -6314,13 +6314,13 @@
         <v>325</v>
       </c>
       <c r="D205" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="E205" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F205" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="G205" t="s">
         <v>165</v>
@@ -6337,13 +6337,13 @@
         <v>325</v>
       </c>
       <c r="D206" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="E206" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F206" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="G206" t="s">
         <v>165</v>
@@ -6360,13 +6360,13 @@
         <v>325</v>
       </c>
       <c r="D207" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="E207" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F207" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="G207" t="s">
         <v>165</v>
@@ -6383,13 +6383,13 @@
         <v>325</v>
       </c>
       <c r="D208" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="E208" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F208" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="G208" t="s">
         <v>165</v>
@@ -6406,13 +6406,13 @@
         <v>325</v>
       </c>
       <c r="D209" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="E209" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F209" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="G209" t="s">
         <v>165</v>
@@ -6544,13 +6544,13 @@
         <v>363</v>
       </c>
       <c r="D215" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="E215" t="s">
         <v>365</v>
       </c>
       <c r="F215" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G215" t="s">
         <v>165</v>
@@ -6659,13 +6659,13 @@
         <v>363</v>
       </c>
       <c r="D220" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="E220" t="s">
         <v>365</v>
       </c>
       <c r="F220" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="G220" t="s">
         <v>165</v>
@@ -6866,13 +6866,13 @@
         <v>363</v>
       </c>
       <c r="D229" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="E229" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F229" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G229" t="s">
         <v>165</v>
@@ -6889,13 +6889,13 @@
         <v>363</v>
       </c>
       <c r="D230" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="E230" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F230" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G230" t="s">
         <v>165</v>
@@ -6912,13 +6912,13 @@
         <v>363</v>
       </c>
       <c r="D231" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="E231" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F231" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="G231" t="s">
         <v>165</v>
@@ -6935,13 +6935,13 @@
         <v>363</v>
       </c>
       <c r="D232" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="E232" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F232" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="G232" t="s">
         <v>165</v>
@@ -6958,13 +6958,13 @@
         <v>363</v>
       </c>
       <c r="D233" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="E233" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F233" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G233" t="s">
         <v>165</v>
@@ -6981,13 +6981,13 @@
         <v>363</v>
       </c>
       <c r="D234" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="E234" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F234" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G234" t="s">
         <v>165</v>
@@ -7004,13 +7004,13 @@
         <v>363</v>
       </c>
       <c r="D235" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="E235" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F235" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G235" t="s">
         <v>165</v>
@@ -7027,13 +7027,13 @@
         <v>363</v>
       </c>
       <c r="D236" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="E236" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F236" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G236" t="s">
         <v>165</v>
@@ -7050,13 +7050,13 @@
         <v>363</v>
       </c>
       <c r="D237" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="E237" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F237" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G237" t="s">
         <v>165</v>
@@ -7073,13 +7073,13 @@
         <v>363</v>
       </c>
       <c r="D238" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="E238" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F238" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G238" t="s">
         <v>165</v>
@@ -7096,13 +7096,13 @@
         <v>363</v>
       </c>
       <c r="D239" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="E239" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F239" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
       <c r="G239" t="s">
         <v>165</v>
@@ -7257,13 +7257,13 @@
         <v>401</v>
       </c>
       <c r="D246" t="s">
-        <v>255</v>
+        <v>409</v>
       </c>
       <c r="E246" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F246" t="s">
-        <v>410</v>
+        <v>256</v>
       </c>
       <c r="G246" t="s">
         <v>165</v>
@@ -8000,10 +8000,10 @@
         <v>469</v>
       </c>
       <c r="D283" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="F283" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
       <c r="G283" t="s">
         <v>165</v>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,42 +22,42 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -85,12 +85,12 @@
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -151,12 +151,12 @@
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -169,18 +169,18 @@
     <t>12110</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -286,18 +286,18 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -352,21 +352,21 @@
     <t>15110</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -823,18 +823,18 @@
     <t>23110</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1279,15 +1279,15 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,16 +1863,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -1909,16 +1909,16 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -1932,19 +1932,19 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1961,13 +1961,13 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1978,19 +1978,19 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2001,19 +2001,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2024,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2047,19 +2047,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2070,19 +2070,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2116,19 +2116,19 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
         <v>39</v>
-      </c>
-      <c r="F14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2139,19 +2139,19 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
         <v>46</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2162,19 +2162,19 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2191,13 +2191,13 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
         <v>53</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>54</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2214,13 +2214,13 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" t="s">
         <v>53</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>54</v>
-      </c>
-      <c r="G18" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" t="s">
         <v>53</v>
       </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2254,19 +2254,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" t="s">
         <v>53</v>
       </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2283,13 +2283,13 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" t="s">
         <v>53</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>54</v>
-      </c>
-      <c r="G21" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2300,19 +2300,19 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" t="s">
         <v>64</v>
-      </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" t="s">
         <v>64</v>
-      </c>
-      <c r="F23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2346,19 +2346,19 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" t="s">
         <v>64</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2369,19 +2369,19 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" t="s">
         <v>64</v>
-      </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2392,19 +2392,19 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" t="s">
         <v>64</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2415,19 +2415,19 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" t="s">
         <v>64</v>
-      </c>
-      <c r="F27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2438,19 +2438,19 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" t="s">
         <v>64</v>
-      </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2461,19 +2461,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" t="s">
         <v>64</v>
-      </c>
-      <c r="F29" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2490,13 +2490,13 @@
         <v>52</v>
       </c>
       <c r="E30" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" t="s">
         <v>64</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2507,19 +2507,19 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" t="s">
         <v>76</v>
-      </c>
-      <c r="F31" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2530,19 +2530,19 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" t="s">
         <v>76</v>
-      </c>
-      <c r="F32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G32" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2553,19 +2553,19 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" t="s">
         <v>76</v>
-      </c>
-      <c r="F33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G33" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2576,19 +2576,19 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" t="s">
         <v>76</v>
-      </c>
-      <c r="F34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2599,19 +2599,19 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E35" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" t="s">
         <v>76</v>
-      </c>
-      <c r="F35" t="s">
-        <v>32</v>
-      </c>
-      <c r="G35" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E36" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" t="s">
         <v>76</v>
-      </c>
-      <c r="F36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G36" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2645,16 +2645,16 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" t="s">
         <v>83</v>
-      </c>
-      <c r="D37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2665,16 +2665,16 @@
         <v>8</v>
       </c>
       <c r="C38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" t="s">
+        <v>33</v>
+      </c>
+      <c r="F38" t="s">
         <v>83</v>
-      </c>
-      <c r="D38" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2685,16 +2685,16 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" t="s">
         <v>83</v>
-      </c>
-      <c r="D39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2705,16 +2705,16 @@
         <v>8</v>
       </c>
       <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" t="s">
         <v>83</v>
-      </c>
-      <c r="D40" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2725,16 +2725,16 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="D41" t="s">
         <v>52</v>
       </c>
+      <c r="E41" t="s">
+        <v>33</v>
+      </c>
       <c r="F41" t="s">
-        <v>54</v>
-      </c>
-      <c r="G41" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2745,16 +2745,16 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" t="s">
         <v>83</v>
-      </c>
-      <c r="D42" t="s">
-        <v>57</v>
-      </c>
-      <c r="F42" t="s">
-        <v>58</v>
-      </c>
-      <c r="G42" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2770,10 +2770,10 @@
       <c r="D43" t="s">
         <v>91</v>
       </c>
+      <c r="E43" t="s">
+        <v>92</v>
+      </c>
       <c r="F43" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2785,16 +2785,16 @@
         <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="E44" t="s">
+        <v>97</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
-      </c>
-      <c r="G44" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2810,10 +2810,10 @@
       <c r="D45" t="s">
         <v>91</v>
       </c>
+      <c r="E45" t="s">
+        <v>92</v>
+      </c>
       <c r="F45" t="s">
-        <v>92</v>
-      </c>
-      <c r="G45" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2830,10 +2830,10 @@
       <c r="D46" t="s">
         <v>91</v>
       </c>
+      <c r="E46" t="s">
+        <v>92</v>
+      </c>
       <c r="F46" t="s">
-        <v>92</v>
-      </c>
-      <c r="G46" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2845,16 +2845,16 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="E47" t="s">
+        <v>97</v>
       </c>
       <c r="F47" t="s">
-        <v>102</v>
-      </c>
-      <c r="G47" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2870,10 +2870,10 @@
       <c r="D48" t="s">
         <v>91</v>
       </c>
+      <c r="E48" t="s">
+        <v>92</v>
+      </c>
       <c r="F48" t="s">
-        <v>92</v>
-      </c>
-      <c r="G48" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2890,10 +2890,10 @@
       <c r="D49" t="s">
         <v>91</v>
       </c>
+      <c r="E49" t="s">
+        <v>92</v>
+      </c>
       <c r="F49" t="s">
-        <v>92</v>
-      </c>
-      <c r="G49" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2905,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="E50" t="s">
+        <v>97</v>
       </c>
       <c r="F50" t="s">
-        <v>102</v>
-      </c>
-      <c r="G50" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2930,10 +2930,10 @@
       <c r="D51" t="s">
         <v>91</v>
       </c>
+      <c r="E51" t="s">
+        <v>92</v>
+      </c>
       <c r="F51" t="s">
-        <v>92</v>
-      </c>
-      <c r="G51" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="E52" t="s">
+        <v>97</v>
       </c>
       <c r="F52" t="s">
-        <v>109</v>
-      </c>
-      <c r="G52" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2965,16 +2965,16 @@
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
       </c>
+      <c r="E53" t="s">
+        <v>11</v>
+      </c>
       <c r="F53" t="s">
-        <v>12</v>
-      </c>
-      <c r="G53" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3008,16 +3008,16 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
         <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G55" t="s">
         <v>116</v>
@@ -3031,16 +3031,16 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E56" t="s">
         <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G56" t="s">
         <v>116</v>
@@ -3054,19 +3054,19 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F57" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3077,16 +3077,16 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s">
         <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G58" t="s">
         <v>116</v>
@@ -3100,16 +3100,16 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E59" t="s">
         <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G59" t="s">
         <v>116</v>
@@ -3123,16 +3123,16 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E60" t="s">
         <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G60" t="s">
         <v>116</v>
@@ -3146,16 +3146,16 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
         <v>116</v>
@@ -3169,16 +3169,16 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E62" t="s">
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G62" t="s">
         <v>116</v>
@@ -3192,16 +3192,16 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D63" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E63" t="s">
         <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G63" t="s">
         <v>116</v>
@@ -3215,16 +3215,16 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D64" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E64" t="s">
         <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G64" t="s">
         <v>116</v>
@@ -3238,16 +3238,16 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="G65" t="s">
         <v>116</v>
@@ -3284,16 +3284,16 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E67" t="s">
         <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>116</v>
@@ -3307,10 +3307,10 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="D68" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
@@ -3330,10 +3330,10 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D69" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
@@ -3353,16 +3353,16 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E70" t="s">
         <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G70" t="s">
         <v>116</v>
@@ -3376,16 +3376,16 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E71" t="s">
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G71" t="s">
         <v>116</v>
@@ -3422,19 +3422,19 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F73" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3445,19 +3445,19 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F74" t="s">
-        <v>152</v>
+        <v>115</v>
       </c>
       <c r="G74" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3468,19 +3468,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F75" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="G75" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3491,19 +3491,19 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E76" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F76" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3514,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E77" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F77" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="G77" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3537,19 +3537,19 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E78" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F78" t="s">
-        <v>152</v>
+        <v>115</v>
       </c>
       <c r="G78" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3560,19 +3560,19 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E79" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F79" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3583,19 +3583,19 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="F80" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G80" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3606,19 +3606,19 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E81" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="F81" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G81" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3629,19 +3629,19 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E82" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="F82" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G82" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3652,10 +3652,10 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
@@ -3675,16 +3675,16 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E84" t="s">
         <v>114</v>
       </c>
       <c r="F84" t="s">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="G84" t="s">
         <v>116</v>
@@ -3698,16 +3698,16 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="E85" t="s">
         <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G85" t="s">
         <v>116</v>
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E86" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="F86" t="s">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="G86" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,16 +3744,16 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="D87" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="E87" t="s">
         <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G87" t="s">
         <v>116</v>
@@ -3767,16 +3767,16 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E88" t="s">
         <v>114</v>
       </c>
       <c r="F88" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G88" t="s">
         <v>116</v>
@@ -3790,16 +3790,16 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D89" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E89" t="s">
         <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G89" t="s">
         <v>116</v>
@@ -3813,19 +3813,19 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E90" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F90" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G90" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3836,19 +3836,19 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="F91" t="s">
-        <v>183</v>
+        <v>115</v>
       </c>
       <c r="G91" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3859,19 +3859,19 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F92" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G92" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3882,16 +3882,16 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G93" t="s">
         <v>116</v>
@@ -3905,19 +3905,19 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E94" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F94" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3928,16 +3928,16 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="G95" t="s">
         <v>116</v>
@@ -3951,19 +3951,19 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D96" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E96" t="s">
+        <v>126</v>
+      </c>
+      <c r="F96" t="s">
+        <v>115</v>
+      </c>
+      <c r="G96" t="s">
         <v>192</v>
-      </c>
-      <c r="F96" t="s">
-        <v>125</v>
-      </c>
-      <c r="G96" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3974,19 +3974,19 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D97" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E97" t="s">
+        <v>126</v>
+      </c>
+      <c r="F97" t="s">
+        <v>115</v>
+      </c>
+      <c r="G97" t="s">
         <v>192</v>
-      </c>
-      <c r="F97" t="s">
-        <v>125</v>
-      </c>
-      <c r="G97" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3997,19 +3997,19 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>112</v>
+        <v>195</v>
       </c>
       <c r="D98" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E98" t="s">
+        <v>197</v>
+      </c>
+      <c r="F98" t="s">
+        <v>115</v>
+      </c>
+      <c r="G98" t="s">
         <v>192</v>
-      </c>
-      <c r="F98" t="s">
-        <v>196</v>
-      </c>
-      <c r="G98" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4020,19 +4020,19 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D99" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E99" t="s">
+        <v>126</v>
+      </c>
+      <c r="F99" t="s">
+        <v>115</v>
+      </c>
+      <c r="G99" t="s">
         <v>192</v>
-      </c>
-      <c r="F99" t="s">
-        <v>125</v>
-      </c>
-      <c r="G99" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="D100" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E100" t="s">
+        <v>126</v>
+      </c>
+      <c r="F100" t="s">
+        <v>115</v>
+      </c>
+      <c r="G100" t="s">
         <v>192</v>
-      </c>
-      <c r="F100" t="s">
-        <v>155</v>
-      </c>
-      <c r="G100" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4066,19 +4066,19 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E101" t="s">
+        <v>126</v>
+      </c>
+      <c r="F101" t="s">
+        <v>115</v>
+      </c>
+      <c r="G101" t="s">
         <v>192</v>
-      </c>
-      <c r="F101" t="s">
-        <v>125</v>
-      </c>
-      <c r="G101" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4094,11 +4094,11 @@
       <c r="D102" t="s">
         <v>203</v>
       </c>
+      <c r="E102" t="s">
+        <v>184</v>
+      </c>
       <c r="F102" t="s">
         <v>204</v>
-      </c>
-      <c r="G102" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4114,11 +4114,11 @@
       <c r="D103" t="s">
         <v>203</v>
       </c>
+      <c r="E103" t="s">
+        <v>184</v>
+      </c>
       <c r="F103" t="s">
         <v>204</v>
-      </c>
-      <c r="G103" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4134,11 +4134,11 @@
       <c r="D104" t="s">
         <v>203</v>
       </c>
+      <c r="E104" t="s">
+        <v>184</v>
+      </c>
       <c r="F104" t="s">
         <v>204</v>
-      </c>
-      <c r="G104" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4149,16 +4149,16 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D105" t="s">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="E105" t="s">
+        <v>184</v>
       </c>
       <c r="F105" t="s">
-        <v>209</v>
-      </c>
-      <c r="G105" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4174,11 +4174,11 @@
       <c r="D106" t="s">
         <v>203</v>
       </c>
+      <c r="E106" t="s">
+        <v>184</v>
+      </c>
       <c r="F106" t="s">
         <v>204</v>
-      </c>
-      <c r="G106" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4189,16 +4189,16 @@
         <v>8</v>
       </c>
       <c r="C107" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D107" t="s">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="E107" t="s">
+        <v>184</v>
       </c>
       <c r="F107" t="s">
-        <v>183</v>
-      </c>
-      <c r="G107" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4209,16 +4209,16 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D108" t="s">
-        <v>213</v>
+        <v>214</v>
+      </c>
+      <c r="E108" t="s">
+        <v>184</v>
       </c>
       <c r="F108" t="s">
-        <v>214</v>
-      </c>
-      <c r="G108" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4229,16 +4229,16 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="D109" t="s">
-        <v>216</v>
+        <v>217</v>
+      </c>
+      <c r="E109" t="s">
+        <v>92</v>
       </c>
       <c r="F109" t="s">
-        <v>217</v>
-      </c>
-      <c r="G109" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4249,16 +4249,16 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="D110" t="s">
-        <v>219</v>
+        <v>220</v>
+      </c>
+      <c r="E110" t="s">
+        <v>92</v>
       </c>
       <c r="F110" t="s">
-        <v>220</v>
-      </c>
-      <c r="G110" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4274,11 +4274,11 @@
       <c r="D111" t="s">
         <v>203</v>
       </c>
+      <c r="E111" t="s">
+        <v>184</v>
+      </c>
       <c r="F111" t="s">
         <v>204</v>
-      </c>
-      <c r="G111" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4289,19 +4289,19 @@
         <v>8</v>
       </c>
       <c r="C112" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="D112" t="s">
-        <v>223</v>
+        <v>224</v>
+      </c>
+      <c r="E112" t="s">
+        <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>224</v>
-      </c>
-      <c r="G112" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>226</v>
       </c>
@@ -4309,19 +4309,19 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="D113" t="s">
-        <v>143</v>
+        <v>113</v>
+      </c>
+      <c r="E113" t="s">
+        <v>114</v>
       </c>
       <c r="F113" t="s">
-        <v>115</v>
-      </c>
-      <c r="G113" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -4329,19 +4329,19 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="D114" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="E114" t="s">
+        <v>126</v>
       </c>
       <c r="F114" t="s">
-        <v>152</v>
-      </c>
-      <c r="G114" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>228</v>
       </c>
@@ -4349,19 +4349,19 @@
         <v>8</v>
       </c>
       <c r="C115" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D115" t="s">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="E115" t="s">
+        <v>184</v>
       </c>
       <c r="F115" t="s">
-        <v>183</v>
-      </c>
-      <c r="G115" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>229</v>
       </c>
@@ -4369,19 +4369,19 @@
         <v>8</v>
       </c>
       <c r="C116" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="D116" t="s">
-        <v>230</v>
+        <v>231</v>
+      </c>
+      <c r="E116" t="s">
+        <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>231</v>
-      </c>
-      <c r="G116" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>232</v>
       </c>
@@ -4389,19 +4389,19 @@
         <v>8</v>
       </c>
       <c r="C117" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="D117" t="s">
-        <v>223</v>
+        <v>224</v>
+      </c>
+      <c r="E117" t="s">
+        <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>224</v>
-      </c>
-      <c r="G117" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>233</v>
       </c>
@@ -4409,19 +4409,19 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="D118" t="s">
-        <v>234</v>
+        <v>164</v>
+      </c>
+      <c r="E118" t="s">
+        <v>165</v>
       </c>
       <c r="F118" t="s">
-        <v>164</v>
-      </c>
-      <c r="G118" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>235</v>
       </c>
@@ -4429,19 +4429,19 @@
         <v>8</v>
       </c>
       <c r="C119" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D119" t="s">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="E119" t="s">
+        <v>184</v>
       </c>
       <c r="F119" t="s">
-        <v>183</v>
-      </c>
-      <c r="G119" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>236</v>
       </c>
@@ -4449,19 +4449,19 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
+        <v>170</v>
+      </c>
+      <c r="D120" t="s">
+        <v>171</v>
+      </c>
+      <c r="E120" t="s">
+        <v>114</v>
+      </c>
+      <c r="F120" t="s">
         <v>237</v>
       </c>
-      <c r="D120" t="s">
-        <v>170</v>
-      </c>
-      <c r="F120" t="s">
-        <v>171</v>
-      </c>
-      <c r="G120" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>238</v>
       </c>
@@ -4469,19 +4469,19 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
+        <v>143</v>
+      </c>
+      <c r="D121" t="s">
+        <v>113</v>
+      </c>
+      <c r="E121" t="s">
+        <v>114</v>
+      </c>
+      <c r="F121" t="s">
         <v>237</v>
       </c>
-      <c r="D121" t="s">
-        <v>143</v>
-      </c>
-      <c r="F121" t="s">
-        <v>115</v>
-      </c>
-      <c r="G121" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>239</v>
       </c>
@@ -4489,19 +4489,19 @@
         <v>8</v>
       </c>
       <c r="C122" t="s">
+        <v>170</v>
+      </c>
+      <c r="D122" t="s">
+        <v>171</v>
+      </c>
+      <c r="E122" t="s">
+        <v>114</v>
+      </c>
+      <c r="F122" t="s">
         <v>237</v>
       </c>
-      <c r="D122" t="s">
-        <v>170</v>
-      </c>
-      <c r="F122" t="s">
-        <v>171</v>
-      </c>
-      <c r="G122" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>240</v>
       </c>
@@ -4509,19 +4509,19 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
+        <v>170</v>
+      </c>
+      <c r="D123" t="s">
+        <v>171</v>
+      </c>
+      <c r="E123" t="s">
+        <v>114</v>
+      </c>
+      <c r="F123" t="s">
         <v>237</v>
       </c>
-      <c r="D123" t="s">
-        <v>170</v>
-      </c>
-      <c r="F123" t="s">
-        <v>171</v>
-      </c>
-      <c r="G123" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>241</v>
       </c>
@@ -4529,19 +4529,19 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
+        <v>242</v>
+      </c>
+      <c r="D124" t="s">
+        <v>243</v>
+      </c>
+      <c r="E124" t="s">
+        <v>165</v>
+      </c>
+      <c r="F124" t="s">
         <v>237</v>
       </c>
-      <c r="D124" t="s">
-        <v>242</v>
-      </c>
-      <c r="F124" t="s">
-        <v>243</v>
-      </c>
-      <c r="G124" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -4549,19 +4549,19 @@
         <v>8</v>
       </c>
       <c r="C125" t="s">
+        <v>242</v>
+      </c>
+      <c r="D125" t="s">
+        <v>243</v>
+      </c>
+      <c r="E125" t="s">
+        <v>165</v>
+      </c>
+      <c r="F125" t="s">
         <v>237</v>
       </c>
-      <c r="D125" t="s">
-        <v>242</v>
-      </c>
-      <c r="F125" t="s">
-        <v>243</v>
-      </c>
-      <c r="G125" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -4569,19 +4569,19 @@
         <v>8</v>
       </c>
       <c r="C126" t="s">
+        <v>242</v>
+      </c>
+      <c r="D126" t="s">
+        <v>243</v>
+      </c>
+      <c r="E126" t="s">
+        <v>165</v>
+      </c>
+      <c r="F126" t="s">
         <v>237</v>
       </c>
-      <c r="D126" t="s">
-        <v>242</v>
-      </c>
-      <c r="F126" t="s">
-        <v>243</v>
-      </c>
-      <c r="G126" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>246</v>
       </c>
@@ -4589,19 +4589,19 @@
         <v>8</v>
       </c>
       <c r="C127" t="s">
+        <v>242</v>
+      </c>
+      <c r="D127" t="s">
+        <v>243</v>
+      </c>
+      <c r="E127" t="s">
+        <v>165</v>
+      </c>
+      <c r="F127" t="s">
         <v>237</v>
       </c>
-      <c r="D127" t="s">
-        <v>242</v>
-      </c>
-      <c r="F127" t="s">
-        <v>243</v>
-      </c>
-      <c r="G127" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -4609,16 +4609,16 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
+        <v>242</v>
+      </c>
+      <c r="D128" t="s">
+        <v>243</v>
+      </c>
+      <c r="E128" t="s">
+        <v>165</v>
+      </c>
+      <c r="F128" t="s">
         <v>237</v>
-      </c>
-      <c r="D128" t="s">
-        <v>242</v>
-      </c>
-      <c r="F128" t="s">
-        <v>243</v>
-      </c>
-      <c r="G128" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>249</v>
+      </c>
+      <c r="D129" t="s">
+        <v>243</v>
+      </c>
+      <c r="E129" t="s">
+        <v>165</v>
+      </c>
+      <c r="F129" t="s">
         <v>237</v>
-      </c>
-      <c r="D129" t="s">
-        <v>249</v>
-      </c>
-      <c r="F129" t="s">
-        <v>243</v>
-      </c>
-      <c r="G129" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
+        <v>251</v>
+      </c>
+      <c r="D130" t="s">
+        <v>243</v>
+      </c>
+      <c r="E130" t="s">
+        <v>165</v>
+      </c>
+      <c r="F130" t="s">
         <v>237</v>
-      </c>
-      <c r="D130" t="s">
-        <v>251</v>
-      </c>
-      <c r="F130" t="s">
-        <v>243</v>
-      </c>
-      <c r="G130" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
+        <v>253</v>
+      </c>
+      <c r="D131" t="s">
+        <v>243</v>
+      </c>
+      <c r="E131" t="s">
+        <v>165</v>
+      </c>
+      <c r="F131" t="s">
         <v>237</v>
-      </c>
-      <c r="D131" t="s">
-        <v>253</v>
-      </c>
-      <c r="F131" t="s">
-        <v>243</v>
-      </c>
-      <c r="G131" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,16 +4689,16 @@
         <v>8</v>
       </c>
       <c r="C132" t="s">
+        <v>255</v>
+      </c>
+      <c r="D132" t="s">
+        <v>256</v>
+      </c>
+      <c r="E132" t="s">
+        <v>165</v>
+      </c>
+      <c r="F132" t="s">
         <v>237</v>
-      </c>
-      <c r="D132" t="s">
-        <v>255</v>
-      </c>
-      <c r="F132" t="s">
-        <v>256</v>
-      </c>
-      <c r="G132" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4709,16 +4709,16 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
+        <v>189</v>
+      </c>
+      <c r="D133" t="s">
+        <v>190</v>
+      </c>
+      <c r="E133" t="s">
+        <v>114</v>
+      </c>
+      <c r="F133" t="s">
         <v>237</v>
-      </c>
-      <c r="D133" t="s">
-        <v>189</v>
-      </c>
-      <c r="F133" t="s">
-        <v>190</v>
-      </c>
-      <c r="G133" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4729,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="C134" t="s">
+        <v>175</v>
+      </c>
+      <c r="D134" t="s">
+        <v>176</v>
+      </c>
+      <c r="E134" t="s">
+        <v>165</v>
+      </c>
+      <c r="F134" t="s">
         <v>259</v>
-      </c>
-      <c r="D134" t="s">
-        <v>175</v>
-      </c>
-      <c r="F134" t="s">
-        <v>176</v>
-      </c>
-      <c r="G134" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4749,16 +4749,16 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
+        <v>175</v>
+      </c>
+      <c r="D135" t="s">
+        <v>176</v>
+      </c>
+      <c r="E135" t="s">
+        <v>165</v>
+      </c>
+      <c r="F135" t="s">
         <v>259</v>
-      </c>
-      <c r="D135" t="s">
-        <v>175</v>
-      </c>
-      <c r="F135" t="s">
-        <v>176</v>
-      </c>
-      <c r="G135" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4769,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="C136" t="s">
+        <v>175</v>
+      </c>
+      <c r="D136" t="s">
+        <v>176</v>
+      </c>
+      <c r="E136" t="s">
+        <v>165</v>
+      </c>
+      <c r="F136" t="s">
         <v>259</v>
-      </c>
-      <c r="D136" t="s">
-        <v>175</v>
-      </c>
-      <c r="F136" t="s">
-        <v>176</v>
-      </c>
-      <c r="G136" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4789,16 +4789,16 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
+        <v>175</v>
+      </c>
+      <c r="D137" t="s">
+        <v>176</v>
+      </c>
+      <c r="E137" t="s">
+        <v>165</v>
+      </c>
+      <c r="F137" t="s">
         <v>259</v>
-      </c>
-      <c r="D137" t="s">
-        <v>175</v>
-      </c>
-      <c r="F137" t="s">
-        <v>176</v>
-      </c>
-      <c r="G137" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4809,16 +4809,16 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
+        <v>175</v>
+      </c>
+      <c r="D138" t="s">
+        <v>176</v>
+      </c>
+      <c r="E138" t="s">
+        <v>165</v>
+      </c>
+      <c r="F138" t="s">
         <v>259</v>
-      </c>
-      <c r="D138" t="s">
-        <v>175</v>
-      </c>
-      <c r="F138" t="s">
-        <v>176</v>
-      </c>
-      <c r="G138" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4829,16 +4829,16 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
+        <v>265</v>
+      </c>
+      <c r="D139" t="s">
+        <v>266</v>
+      </c>
+      <c r="E139" t="s">
+        <v>225</v>
+      </c>
+      <c r="F139" t="s">
         <v>259</v>
-      </c>
-      <c r="D139" t="s">
-        <v>265</v>
-      </c>
-      <c r="F139" t="s">
-        <v>266</v>
-      </c>
-      <c r="G139" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
+        <v>175</v>
+      </c>
+      <c r="D140" t="s">
+        <v>176</v>
+      </c>
+      <c r="E140" t="s">
+        <v>165</v>
+      </c>
+      <c r="F140" t="s">
         <v>259</v>
-      </c>
-      <c r="D140" t="s">
-        <v>175</v>
-      </c>
-      <c r="F140" t="s">
-        <v>176</v>
-      </c>
-      <c r="G140" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4875,13 +4875,13 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
+        <v>165</v>
+      </c>
+      <c r="F141" t="s">
         <v>271</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>272</v>
-      </c>
-      <c r="G141" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4898,13 +4898,13 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
+        <v>165</v>
+      </c>
+      <c r="F142" t="s">
         <v>271</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>272</v>
-      </c>
-      <c r="G142" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4915,19 +4915,19 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E143" t="s">
+        <v>165</v>
+      </c>
+      <c r="F143" t="s">
         <v>271</v>
       </c>
-      <c r="F143" t="s">
-        <v>276</v>
-      </c>
       <c r="G143" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4938,19 +4938,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E144" t="s">
+        <v>165</v>
+      </c>
+      <c r="F144" t="s">
         <v>271</v>
       </c>
-      <c r="F144" t="s">
-        <v>276</v>
-      </c>
       <c r="G144" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4961,19 +4961,19 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E145" t="s">
+        <v>165</v>
+      </c>
+      <c r="F145" t="s">
         <v>271</v>
       </c>
-      <c r="F145" t="s">
-        <v>276</v>
-      </c>
       <c r="G145" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4990,13 +4990,13 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
+        <v>165</v>
+      </c>
+      <c r="F146" t="s">
         <v>271</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>272</v>
-      </c>
-      <c r="G146" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5013,13 +5013,13 @@
         <v>270</v>
       </c>
       <c r="E147" t="s">
+        <v>165</v>
+      </c>
+      <c r="F147" t="s">
+        <v>271</v>
+      </c>
+      <c r="G147" t="s">
         <v>281</v>
-      </c>
-      <c r="F147" t="s">
-        <v>272</v>
-      </c>
-      <c r="G147" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5036,13 +5036,13 @@
         <v>270</v>
       </c>
       <c r="E148" t="s">
+        <v>165</v>
+      </c>
+      <c r="F148" t="s">
+        <v>271</v>
+      </c>
+      <c r="G148" t="s">
         <v>281</v>
-      </c>
-      <c r="F148" t="s">
-        <v>272</v>
-      </c>
-      <c r="G148" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5059,13 +5059,13 @@
         <v>270</v>
       </c>
       <c r="E149" t="s">
+        <v>165</v>
+      </c>
+      <c r="F149" t="s">
+        <v>271</v>
+      </c>
+      <c r="G149" t="s">
         <v>281</v>
-      </c>
-      <c r="F149" t="s">
-        <v>272</v>
-      </c>
-      <c r="G149" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5082,13 +5082,13 @@
         <v>270</v>
       </c>
       <c r="E150" t="s">
+        <v>165</v>
+      </c>
+      <c r="F150" t="s">
+        <v>271</v>
+      </c>
+      <c r="G150" t="s">
         <v>281</v>
-      </c>
-      <c r="F150" t="s">
-        <v>272</v>
-      </c>
-      <c r="G150" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5105,13 +5105,13 @@
         <v>270</v>
       </c>
       <c r="E151" t="s">
+        <v>165</v>
+      </c>
+      <c r="F151" t="s">
+        <v>271</v>
+      </c>
+      <c r="G151" t="s">
         <v>281</v>
-      </c>
-      <c r="F151" t="s">
-        <v>272</v>
-      </c>
-      <c r="G151" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5128,13 +5128,13 @@
         <v>270</v>
       </c>
       <c r="E152" t="s">
+        <v>165</v>
+      </c>
+      <c r="F152" t="s">
+        <v>271</v>
+      </c>
+      <c r="G152" t="s">
         <v>281</v>
-      </c>
-      <c r="F152" t="s">
-        <v>272</v>
-      </c>
-      <c r="G152" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5151,13 +5151,13 @@
         <v>270</v>
       </c>
       <c r="E153" t="s">
+        <v>165</v>
+      </c>
+      <c r="F153" t="s">
+        <v>271</v>
+      </c>
+      <c r="G153" t="s">
         <v>281</v>
-      </c>
-      <c r="F153" t="s">
-        <v>272</v>
-      </c>
-      <c r="G153" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5174,13 +5174,13 @@
         <v>270</v>
       </c>
       <c r="E154" t="s">
+        <v>165</v>
+      </c>
+      <c r="F154" t="s">
+        <v>271</v>
+      </c>
+      <c r="G154" t="s">
         <v>281</v>
-      </c>
-      <c r="F154" t="s">
-        <v>272</v>
-      </c>
-      <c r="G154" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5197,13 +5197,13 @@
         <v>270</v>
       </c>
       <c r="E155" t="s">
+        <v>165</v>
+      </c>
+      <c r="F155" t="s">
+        <v>271</v>
+      </c>
+      <c r="G155" t="s">
         <v>281</v>
-      </c>
-      <c r="F155" t="s">
-        <v>272</v>
-      </c>
-      <c r="G155" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5220,13 +5220,13 @@
         <v>270</v>
       </c>
       <c r="E156" t="s">
+        <v>165</v>
+      </c>
+      <c r="F156" t="s">
+        <v>271</v>
+      </c>
+      <c r="G156" t="s">
         <v>291</v>
-      </c>
-      <c r="F156" t="s">
-        <v>272</v>
-      </c>
-      <c r="G156" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D157" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="E157" t="s">
+        <v>165</v>
+      </c>
+      <c r="F157" t="s">
+        <v>271</v>
+      </c>
+      <c r="G157" t="s">
         <v>291</v>
-      </c>
-      <c r="F157" t="s">
-        <v>272</v>
-      </c>
-      <c r="G157" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5266,13 +5266,13 @@
         <v>270</v>
       </c>
       <c r="E158" t="s">
+        <v>165</v>
+      </c>
+      <c r="F158" t="s">
+        <v>271</v>
+      </c>
+      <c r="G158" t="s">
         <v>291</v>
-      </c>
-      <c r="F158" t="s">
-        <v>272</v>
-      </c>
-      <c r="G158" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5289,13 +5289,13 @@
         <v>270</v>
       </c>
       <c r="E159" t="s">
+        <v>165</v>
+      </c>
+      <c r="F159" t="s">
+        <v>271</v>
+      </c>
+      <c r="G159" t="s">
         <v>291</v>
-      </c>
-      <c r="F159" t="s">
-        <v>272</v>
-      </c>
-      <c r="G159" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5312,13 +5312,13 @@
         <v>270</v>
       </c>
       <c r="E160" t="s">
+        <v>165</v>
+      </c>
+      <c r="F160" t="s">
+        <v>271</v>
+      </c>
+      <c r="G160" t="s">
         <v>291</v>
-      </c>
-      <c r="F160" t="s">
-        <v>272</v>
-      </c>
-      <c r="G160" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5335,13 +5335,13 @@
         <v>270</v>
       </c>
       <c r="E161" t="s">
+        <v>165</v>
+      </c>
+      <c r="F161" t="s">
+        <v>271</v>
+      </c>
+      <c r="G161" t="s">
         <v>291</v>
-      </c>
-      <c r="F161" t="s">
-        <v>272</v>
-      </c>
-      <c r="G161" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5358,13 +5358,13 @@
         <v>270</v>
       </c>
       <c r="E162" t="s">
+        <v>165</v>
+      </c>
+      <c r="F162" t="s">
+        <v>271</v>
+      </c>
+      <c r="G162" t="s">
         <v>299</v>
-      </c>
-      <c r="F162" t="s">
-        <v>272</v>
-      </c>
-      <c r="G162" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="E163" t="s">
+        <v>165</v>
+      </c>
+      <c r="F163" t="s">
+        <v>271</v>
+      </c>
+      <c r="G163" t="s">
         <v>302</v>
-      </c>
-      <c r="F163" t="s">
-        <v>272</v>
-      </c>
-      <c r="G163" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5404,13 +5404,13 @@
         <v>270</v>
       </c>
       <c r="E164" t="s">
+        <v>165</v>
+      </c>
+      <c r="F164" t="s">
+        <v>271</v>
+      </c>
+      <c r="G164" t="s">
         <v>304</v>
-      </c>
-      <c r="F164" t="s">
-        <v>272</v>
-      </c>
-      <c r="G164" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5427,13 +5427,13 @@
         <v>270</v>
       </c>
       <c r="E165" t="s">
+        <v>165</v>
+      </c>
+      <c r="F165" t="s">
+        <v>271</v>
+      </c>
+      <c r="G165" t="s">
         <v>304</v>
-      </c>
-      <c r="F165" t="s">
-        <v>272</v>
-      </c>
-      <c r="G165" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5450,13 +5450,13 @@
         <v>270</v>
       </c>
       <c r="E166" t="s">
+        <v>165</v>
+      </c>
+      <c r="F166" t="s">
+        <v>271</v>
+      </c>
+      <c r="G166" t="s">
         <v>304</v>
-      </c>
-      <c r="F166" t="s">
-        <v>272</v>
-      </c>
-      <c r="G166" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5473,13 +5473,13 @@
         <v>270</v>
       </c>
       <c r="E167" t="s">
+        <v>165</v>
+      </c>
+      <c r="F167" t="s">
+        <v>271</v>
+      </c>
+      <c r="G167" t="s">
         <v>304</v>
-      </c>
-      <c r="F167" t="s">
-        <v>272</v>
-      </c>
-      <c r="G167" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D168" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="E168" t="s">
+        <v>165</v>
+      </c>
+      <c r="F168" t="s">
+        <v>271</v>
+      </c>
+      <c r="G168" t="s">
         <v>304</v>
-      </c>
-      <c r="F168" t="s">
-        <v>272</v>
-      </c>
-      <c r="G168" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D169" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="E169" t="s">
+        <v>165</v>
+      </c>
+      <c r="F169" t="s">
+        <v>271</v>
+      </c>
+      <c r="G169" t="s">
         <v>304</v>
-      </c>
-      <c r="F169" t="s">
-        <v>272</v>
-      </c>
-      <c r="G169" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5542,13 +5542,13 @@
         <v>270</v>
       </c>
       <c r="E170" t="s">
+        <v>165</v>
+      </c>
+      <c r="F170" t="s">
+        <v>271</v>
+      </c>
+      <c r="G170" t="s">
         <v>304</v>
-      </c>
-      <c r="F170" t="s">
-        <v>272</v>
-      </c>
-      <c r="G170" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5559,16 +5559,16 @@
         <v>8</v>
       </c>
       <c r="C171" t="s">
+        <v>163</v>
+      </c>
+      <c r="D171" t="s">
+        <v>164</v>
+      </c>
+      <c r="E171" t="s">
+        <v>165</v>
+      </c>
+      <c r="F171" t="s">
         <v>313</v>
-      </c>
-      <c r="D171" t="s">
-        <v>163</v>
-      </c>
-      <c r="F171" t="s">
-        <v>164</v>
-      </c>
-      <c r="G171" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5579,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
+        <v>118</v>
+      </c>
+      <c r="D172" t="s">
+        <v>119</v>
+      </c>
+      <c r="E172" t="s">
+        <v>114</v>
+      </c>
+      <c r="F172" t="s">
         <v>313</v>
-      </c>
-      <c r="D172" t="s">
-        <v>118</v>
-      </c>
-      <c r="F172" t="s">
-        <v>119</v>
-      </c>
-      <c r="G172" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5599,16 +5599,16 @@
         <v>8</v>
       </c>
       <c r="C173" t="s">
+        <v>163</v>
+      </c>
+      <c r="D173" t="s">
+        <v>164</v>
+      </c>
+      <c r="E173" t="s">
+        <v>165</v>
+      </c>
+      <c r="F173" t="s">
         <v>313</v>
-      </c>
-      <c r="D173" t="s">
-        <v>163</v>
-      </c>
-      <c r="F173" t="s">
-        <v>164</v>
-      </c>
-      <c r="G173" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5619,16 +5619,16 @@
         <v>8</v>
       </c>
       <c r="C174" t="s">
+        <v>163</v>
+      </c>
+      <c r="D174" t="s">
+        <v>164</v>
+      </c>
+      <c r="E174" t="s">
+        <v>165</v>
+      </c>
+      <c r="F174" t="s">
         <v>313</v>
-      </c>
-      <c r="D174" t="s">
-        <v>163</v>
-      </c>
-      <c r="F174" t="s">
-        <v>164</v>
-      </c>
-      <c r="G174" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>8</v>
       </c>
       <c r="C175" t="s">
+        <v>163</v>
+      </c>
+      <c r="D175" t="s">
+        <v>164</v>
+      </c>
+      <c r="E175" t="s">
+        <v>165</v>
+      </c>
+      <c r="F175" t="s">
         <v>313</v>
-      </c>
-      <c r="D175" t="s">
-        <v>163</v>
-      </c>
-      <c r="F175" t="s">
-        <v>164</v>
-      </c>
-      <c r="G175" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>8</v>
       </c>
       <c r="C176" t="s">
+        <v>163</v>
+      </c>
+      <c r="D176" t="s">
+        <v>164</v>
+      </c>
+      <c r="E176" t="s">
+        <v>165</v>
+      </c>
+      <c r="F176" t="s">
         <v>313</v>
-      </c>
-      <c r="D176" t="s">
-        <v>163</v>
-      </c>
-      <c r="F176" t="s">
-        <v>164</v>
-      </c>
-      <c r="G176" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5679,16 +5679,16 @@
         <v>8</v>
       </c>
       <c r="C177" t="s">
+        <v>163</v>
+      </c>
+      <c r="D177" t="s">
+        <v>164</v>
+      </c>
+      <c r="E177" t="s">
+        <v>165</v>
+      </c>
+      <c r="F177" t="s">
         <v>320</v>
-      </c>
-      <c r="D177" t="s">
-        <v>163</v>
-      </c>
-      <c r="F177" t="s">
-        <v>164</v>
-      </c>
-      <c r="G177" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5699,16 +5699,16 @@
         <v>8</v>
       </c>
       <c r="C178" t="s">
+        <v>163</v>
+      </c>
+      <c r="D178" t="s">
+        <v>164</v>
+      </c>
+      <c r="E178" t="s">
+        <v>165</v>
+      </c>
+      <c r="F178" t="s">
         <v>320</v>
-      </c>
-      <c r="D178" t="s">
-        <v>163</v>
-      </c>
-      <c r="F178" t="s">
-        <v>164</v>
-      </c>
-      <c r="G178" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5719,16 +5719,16 @@
         <v>8</v>
       </c>
       <c r="C179" t="s">
+        <v>163</v>
+      </c>
+      <c r="D179" t="s">
+        <v>164</v>
+      </c>
+      <c r="E179" t="s">
+        <v>165</v>
+      </c>
+      <c r="F179" t="s">
         <v>320</v>
-      </c>
-      <c r="D179" t="s">
-        <v>163</v>
-      </c>
-      <c r="F179" t="s">
-        <v>164</v>
-      </c>
-      <c r="G179" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5739,16 +5739,16 @@
         <v>8</v>
       </c>
       <c r="C180" t="s">
+        <v>163</v>
+      </c>
+      <c r="D180" t="s">
+        <v>164</v>
+      </c>
+      <c r="E180" t="s">
+        <v>165</v>
+      </c>
+      <c r="F180" t="s">
         <v>320</v>
-      </c>
-      <c r="D180" t="s">
-        <v>163</v>
-      </c>
-      <c r="F180" t="s">
-        <v>164</v>
-      </c>
-      <c r="G180" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5765,13 +5765,13 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
+        <v>165</v>
+      </c>
+      <c r="F181" t="s">
         <v>327</v>
       </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
         <v>328</v>
-      </c>
-      <c r="G181" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5788,13 +5788,13 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
+        <v>165</v>
+      </c>
+      <c r="F182" t="s">
         <v>327</v>
       </c>
-      <c r="F182" t="s">
+      <c r="G182" t="s">
         <v>328</v>
-      </c>
-      <c r="G182" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5811,13 +5811,13 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
+        <v>165</v>
+      </c>
+      <c r="F183" t="s">
         <v>327</v>
       </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
         <v>328</v>
-      </c>
-      <c r="G183" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5834,13 +5834,13 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
+        <v>165</v>
+      </c>
+      <c r="F184" t="s">
         <v>327</v>
       </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
         <v>328</v>
-      </c>
-      <c r="G184" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5857,13 +5857,13 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
+        <v>165</v>
+      </c>
+      <c r="F185" t="s">
         <v>327</v>
       </c>
-      <c r="F185" t="s">
+      <c r="G185" t="s">
         <v>328</v>
-      </c>
-      <c r="G185" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5880,13 +5880,13 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
+        <v>165</v>
+      </c>
+      <c r="F186" t="s">
         <v>327</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>328</v>
-      </c>
-      <c r="G186" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5903,13 +5903,13 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
+        <v>165</v>
+      </c>
+      <c r="F187" t="s">
         <v>327</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>328</v>
-      </c>
-      <c r="G187" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5926,13 +5926,13 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
+        <v>165</v>
+      </c>
+      <c r="F188" t="s">
         <v>327</v>
       </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>328</v>
-      </c>
-      <c r="G188" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5949,13 +5949,13 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
+        <v>165</v>
+      </c>
+      <c r="F189" t="s">
         <v>327</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>328</v>
-      </c>
-      <c r="G189" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5972,13 +5972,13 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
+        <v>165</v>
+      </c>
+      <c r="F190" t="s">
         <v>327</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>328</v>
-      </c>
-      <c r="G190" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5995,13 +5995,13 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
+        <v>165</v>
+      </c>
+      <c r="F191" t="s">
         <v>327</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>328</v>
-      </c>
-      <c r="G191" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6018,13 +6018,13 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
+        <v>165</v>
+      </c>
+      <c r="F192" t="s">
         <v>327</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>328</v>
-      </c>
-      <c r="G192" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="D193" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="E193" t="s">
+        <v>165</v>
+      </c>
+      <c r="F193" t="s">
         <v>327</v>
       </c>
-      <c r="F193" t="s">
-        <v>276</v>
-      </c>
       <c r="G193" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6064,13 +6064,13 @@
         <v>326</v>
       </c>
       <c r="E194" t="s">
+        <v>165</v>
+      </c>
+      <c r="F194" t="s">
         <v>327</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>328</v>
-      </c>
-      <c r="G194" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6087,13 +6087,13 @@
         <v>326</v>
       </c>
       <c r="E195" t="s">
+        <v>165</v>
+      </c>
+      <c r="F195" t="s">
         <v>327</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>328</v>
-      </c>
-      <c r="G195" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6110,13 +6110,13 @@
         <v>326</v>
       </c>
       <c r="E196" t="s">
+        <v>165</v>
+      </c>
+      <c r="F196" t="s">
         <v>327</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>328</v>
-      </c>
-      <c r="G196" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6133,13 +6133,13 @@
         <v>326</v>
       </c>
       <c r="E197" t="s">
+        <v>165</v>
+      </c>
+      <c r="F197" t="s">
         <v>327</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
         <v>328</v>
-      </c>
-      <c r="G197" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6156,13 +6156,13 @@
         <v>326</v>
       </c>
       <c r="E198" t="s">
+        <v>165</v>
+      </c>
+      <c r="F198" t="s">
         <v>327</v>
       </c>
-      <c r="F198" t="s">
+      <c r="G198" t="s">
         <v>328</v>
-      </c>
-      <c r="G198" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E199" t="s">
+        <v>165</v>
+      </c>
+      <c r="F199" t="s">
+        <v>327</v>
+      </c>
+      <c r="G199" t="s">
         <v>349</v>
-      </c>
-      <c r="F199" t="s">
-        <v>328</v>
-      </c>
-      <c r="G199" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E200" t="s">
+        <v>165</v>
+      </c>
+      <c r="F200" t="s">
+        <v>327</v>
+      </c>
+      <c r="G200" t="s">
         <v>349</v>
-      </c>
-      <c r="F200" t="s">
-        <v>328</v>
-      </c>
-      <c r="G200" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E201" t="s">
+        <v>165</v>
+      </c>
+      <c r="F201" t="s">
+        <v>327</v>
+      </c>
+      <c r="G201" t="s">
         <v>349</v>
-      </c>
-      <c r="F201" t="s">
-        <v>328</v>
-      </c>
-      <c r="G201" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E202" t="s">
+        <v>165</v>
+      </c>
+      <c r="F202" t="s">
+        <v>327</v>
+      </c>
+      <c r="G202" t="s">
         <v>349</v>
-      </c>
-      <c r="F202" t="s">
-        <v>328</v>
-      </c>
-      <c r="G202" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="D203" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="E203" t="s">
+        <v>165</v>
+      </c>
+      <c r="F203" t="s">
+        <v>327</v>
+      </c>
+      <c r="G203" t="s">
         <v>349</v>
-      </c>
-      <c r="F203" t="s">
-        <v>276</v>
-      </c>
-      <c r="G203" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E204" t="s">
+        <v>165</v>
+      </c>
+      <c r="F204" t="s">
+        <v>327</v>
+      </c>
+      <c r="G204" t="s">
         <v>349</v>
-      </c>
-      <c r="F204" t="s">
-        <v>328</v>
-      </c>
-      <c r="G204" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E205" t="s">
+        <v>165</v>
+      </c>
+      <c r="F205" t="s">
+        <v>327</v>
+      </c>
+      <c r="G205" t="s">
         <v>357</v>
-      </c>
-      <c r="F205" t="s">
-        <v>328</v>
-      </c>
-      <c r="G205" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E206" t="s">
+        <v>165</v>
+      </c>
+      <c r="F206" t="s">
+        <v>327</v>
+      </c>
+      <c r="G206" t="s">
         <v>357</v>
-      </c>
-      <c r="F206" t="s">
-        <v>328</v>
-      </c>
-      <c r="G206" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E207" t="s">
+        <v>165</v>
+      </c>
+      <c r="F207" t="s">
+        <v>327</v>
+      </c>
+      <c r="G207" t="s">
         <v>357</v>
-      </c>
-      <c r="F207" t="s">
-        <v>328</v>
-      </c>
-      <c r="G207" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="D208" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="E208" t="s">
+        <v>165</v>
+      </c>
+      <c r="F208" t="s">
+        <v>327</v>
+      </c>
+      <c r="G208" t="s">
         <v>357</v>
-      </c>
-      <c r="F208" t="s">
-        <v>276</v>
-      </c>
-      <c r="G208" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E209" t="s">
+        <v>165</v>
+      </c>
+      <c r="F209" t="s">
+        <v>327</v>
+      </c>
+      <c r="G209" t="s">
         <v>357</v>
-      </c>
-      <c r="F209" t="s">
-        <v>328</v>
-      </c>
-      <c r="G209" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6432,13 +6432,13 @@
         <v>364</v>
       </c>
       <c r="E210" t="s">
+        <v>165</v>
+      </c>
+      <c r="F210" t="s">
         <v>365</v>
       </c>
-      <c r="F210" t="s">
+      <c r="G210" t="s">
         <v>366</v>
-      </c>
-      <c r="G210" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6455,13 +6455,13 @@
         <v>364</v>
       </c>
       <c r="E211" t="s">
+        <v>165</v>
+      </c>
+      <c r="F211" t="s">
         <v>365</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>366</v>
-      </c>
-      <c r="G211" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6478,13 +6478,13 @@
         <v>364</v>
       </c>
       <c r="E212" t="s">
+        <v>165</v>
+      </c>
+      <c r="F212" t="s">
         <v>365</v>
       </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>366</v>
-      </c>
-      <c r="G212" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6501,13 +6501,13 @@
         <v>364</v>
       </c>
       <c r="E213" t="s">
+        <v>165</v>
+      </c>
+      <c r="F213" t="s">
         <v>365</v>
       </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>366</v>
-      </c>
-      <c r="G213" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6524,13 +6524,13 @@
         <v>364</v>
       </c>
       <c r="E214" t="s">
+        <v>165</v>
+      </c>
+      <c r="F214" t="s">
         <v>365</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>366</v>
-      </c>
-      <c r="G214" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D215" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E215" t="s">
+        <v>165</v>
+      </c>
+      <c r="F215" t="s">
         <v>365</v>
       </c>
-      <c r="F215" t="s">
-        <v>328</v>
-      </c>
       <c r="G215" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6570,13 +6570,13 @@
         <v>364</v>
       </c>
       <c r="E216" t="s">
+        <v>165</v>
+      </c>
+      <c r="F216" t="s">
         <v>365</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>366</v>
-      </c>
-      <c r="G216" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6593,13 +6593,13 @@
         <v>364</v>
       </c>
       <c r="E217" t="s">
+        <v>165</v>
+      </c>
+      <c r="F217" t="s">
         <v>365</v>
       </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
         <v>366</v>
-      </c>
-      <c r="G217" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6616,13 +6616,13 @@
         <v>364</v>
       </c>
       <c r="E218" t="s">
+        <v>165</v>
+      </c>
+      <c r="F218" t="s">
         <v>365</v>
       </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>366</v>
-      </c>
-      <c r="G218" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6639,13 +6639,13 @@
         <v>364</v>
       </c>
       <c r="E219" t="s">
+        <v>165</v>
+      </c>
+      <c r="F219" t="s">
         <v>365</v>
       </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>366</v>
-      </c>
-      <c r="G219" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="D220" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="E220" t="s">
+        <v>165</v>
+      </c>
+      <c r="F220" t="s">
         <v>365</v>
       </c>
-      <c r="F220" t="s">
-        <v>272</v>
-      </c>
       <c r="G220" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6685,13 +6685,13 @@
         <v>364</v>
       </c>
       <c r="E221" t="s">
+        <v>165</v>
+      </c>
+      <c r="F221" t="s">
         <v>365</v>
       </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>366</v>
-      </c>
-      <c r="G221" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6708,13 +6708,13 @@
         <v>364</v>
       </c>
       <c r="E222" t="s">
+        <v>165</v>
+      </c>
+      <c r="F222" t="s">
         <v>365</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>366</v>
-      </c>
-      <c r="G222" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6731,13 +6731,13 @@
         <v>364</v>
       </c>
       <c r="E223" t="s">
+        <v>165</v>
+      </c>
+      <c r="F223" t="s">
         <v>365</v>
       </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>366</v>
-      </c>
-      <c r="G223" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6754,13 +6754,13 @@
         <v>364</v>
       </c>
       <c r="E224" t="s">
+        <v>165</v>
+      </c>
+      <c r="F224" t="s">
         <v>365</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>366</v>
-      </c>
-      <c r="G224" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6777,13 +6777,13 @@
         <v>364</v>
       </c>
       <c r="E225" t="s">
+        <v>165</v>
+      </c>
+      <c r="F225" t="s">
         <v>365</v>
       </c>
-      <c r="F225" t="s">
+      <c r="G225" t="s">
         <v>366</v>
-      </c>
-      <c r="G225" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6794,19 +6794,19 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E226" t="s">
+        <v>165</v>
+      </c>
+      <c r="F226" t="s">
         <v>365</v>
       </c>
-      <c r="F226" t="s">
-        <v>276</v>
-      </c>
       <c r="G226" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6823,13 +6823,13 @@
         <v>364</v>
       </c>
       <c r="E227" t="s">
+        <v>165</v>
+      </c>
+      <c r="F227" t="s">
         <v>365</v>
       </c>
-      <c r="F227" t="s">
+      <c r="G227" t="s">
         <v>366</v>
-      </c>
-      <c r="G227" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6840,19 +6840,19 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E228" t="s">
+        <v>165</v>
+      </c>
+      <c r="F228" t="s">
         <v>365</v>
       </c>
-      <c r="F228" t="s">
-        <v>164</v>
-      </c>
       <c r="G228" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E229" t="s">
+        <v>165</v>
+      </c>
+      <c r="F229" t="s">
+        <v>365</v>
+      </c>
+      <c r="G229" t="s">
         <v>387</v>
-      </c>
-      <c r="F229" t="s">
-        <v>366</v>
-      </c>
-      <c r="G229" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E230" t="s">
+        <v>165</v>
+      </c>
+      <c r="F230" t="s">
+        <v>365</v>
+      </c>
+      <c r="G230" t="s">
         <v>387</v>
-      </c>
-      <c r="F230" t="s">
-        <v>366</v>
-      </c>
-      <c r="G230" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>363</v>
+        <v>293</v>
       </c>
       <c r="D231" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="E231" t="s">
+        <v>165</v>
+      </c>
+      <c r="F231" t="s">
+        <v>365</v>
+      </c>
+      <c r="G231" t="s">
         <v>387</v>
-      </c>
-      <c r="F231" t="s">
-        <v>272</v>
-      </c>
-      <c r="G231" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="D232" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="E232" t="s">
+        <v>165</v>
+      </c>
+      <c r="F232" t="s">
+        <v>365</v>
+      </c>
+      <c r="G232" t="s">
         <v>387</v>
-      </c>
-      <c r="F232" t="s">
-        <v>272</v>
-      </c>
-      <c r="G232" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E233" t="s">
+        <v>165</v>
+      </c>
+      <c r="F233" t="s">
+        <v>365</v>
+      </c>
+      <c r="G233" t="s">
         <v>387</v>
-      </c>
-      <c r="F233" t="s">
-        <v>366</v>
-      </c>
-      <c r="G233" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E234" t="s">
+        <v>165</v>
+      </c>
+      <c r="F234" t="s">
+        <v>365</v>
+      </c>
+      <c r="G234" t="s">
         <v>387</v>
-      </c>
-      <c r="F234" t="s">
-        <v>366</v>
-      </c>
-      <c r="G234" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E235" t="s">
+        <v>165</v>
+      </c>
+      <c r="F235" t="s">
+        <v>365</v>
+      </c>
+      <c r="G235" t="s">
         <v>387</v>
-      </c>
-      <c r="F235" t="s">
-        <v>366</v>
-      </c>
-      <c r="G235" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E236" t="s">
+        <v>165</v>
+      </c>
+      <c r="F236" t="s">
+        <v>365</v>
+      </c>
+      <c r="G236" t="s">
         <v>387</v>
-      </c>
-      <c r="F236" t="s">
-        <v>366</v>
-      </c>
-      <c r="G236" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E237" t="s">
+        <v>165</v>
+      </c>
+      <c r="F237" t="s">
+        <v>365</v>
+      </c>
+      <c r="G237" t="s">
         <v>387</v>
-      </c>
-      <c r="F237" t="s">
-        <v>366</v>
-      </c>
-      <c r="G237" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E238" t="s">
+        <v>165</v>
+      </c>
+      <c r="F238" t="s">
+        <v>365</v>
+      </c>
+      <c r="G238" t="s">
         <v>387</v>
-      </c>
-      <c r="F238" t="s">
-        <v>366</v>
-      </c>
-      <c r="G238" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="E239" t="s">
+        <v>165</v>
+      </c>
+      <c r="F239" t="s">
+        <v>365</v>
+      </c>
+      <c r="G239" t="s">
         <v>399</v>
-      </c>
-      <c r="F239" t="s">
-        <v>366</v>
-      </c>
-      <c r="G239" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7116,19 +7116,19 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>163</v>
+      </c>
+      <c r="D240" t="s">
+        <v>164</v>
+      </c>
+      <c r="E240" t="s">
+        <v>165</v>
+      </c>
+      <c r="F240" t="s">
         <v>401</v>
       </c>
-      <c r="D240" t="s">
-        <v>163</v>
-      </c>
-      <c r="E240" t="s">
+      <c r="G240" t="s">
         <v>402</v>
-      </c>
-      <c r="F240" t="s">
-        <v>164</v>
-      </c>
-      <c r="G240" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7139,19 +7139,19 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>163</v>
+      </c>
+      <c r="D241" t="s">
+        <v>164</v>
+      </c>
+      <c r="E241" t="s">
+        <v>165</v>
+      </c>
+      <c r="F241" t="s">
         <v>401</v>
       </c>
-      <c r="D241" t="s">
-        <v>163</v>
-      </c>
-      <c r="E241" t="s">
+      <c r="G241" t="s">
         <v>402</v>
-      </c>
-      <c r="F241" t="s">
-        <v>164</v>
-      </c>
-      <c r="G241" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7162,19 +7162,19 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>163</v>
+      </c>
+      <c r="D242" t="s">
+        <v>164</v>
+      </c>
+      <c r="E242" t="s">
+        <v>165</v>
+      </c>
+      <c r="F242" t="s">
         <v>401</v>
       </c>
-      <c r="D242" t="s">
-        <v>163</v>
-      </c>
-      <c r="E242" t="s">
+      <c r="G242" t="s">
         <v>402</v>
-      </c>
-      <c r="F242" t="s">
-        <v>164</v>
-      </c>
-      <c r="G242" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7185,19 +7185,19 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>163</v>
+      </c>
+      <c r="D243" t="s">
+        <v>164</v>
+      </c>
+      <c r="E243" t="s">
+        <v>165</v>
+      </c>
+      <c r="F243" t="s">
         <v>401</v>
       </c>
-      <c r="D243" t="s">
-        <v>163</v>
-      </c>
-      <c r="E243" t="s">
+      <c r="G243" t="s">
         <v>402</v>
-      </c>
-      <c r="F243" t="s">
-        <v>164</v>
-      </c>
-      <c r="G243" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7208,19 +7208,19 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>163</v>
+      </c>
+      <c r="D244" t="s">
+        <v>164</v>
+      </c>
+      <c r="E244" t="s">
+        <v>165</v>
+      </c>
+      <c r="F244" t="s">
         <v>401</v>
       </c>
-      <c r="D244" t="s">
-        <v>163</v>
-      </c>
-      <c r="E244" t="s">
+      <c r="G244" t="s">
         <v>402</v>
-      </c>
-      <c r="F244" t="s">
-        <v>164</v>
-      </c>
-      <c r="G244" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7231,19 +7231,19 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>163</v>
+      </c>
+      <c r="D245" t="s">
+        <v>164</v>
+      </c>
+      <c r="E245" t="s">
+        <v>165</v>
+      </c>
+      <c r="F245" t="s">
         <v>401</v>
       </c>
-      <c r="D245" t="s">
-        <v>163</v>
-      </c>
-      <c r="E245" t="s">
+      <c r="G245" t="s">
         <v>402</v>
-      </c>
-      <c r="F245" t="s">
-        <v>164</v>
-      </c>
-      <c r="G245" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>409</v>
+      </c>
+      <c r="D246" t="s">
+        <v>256</v>
+      </c>
+      <c r="E246" t="s">
+        <v>165</v>
+      </c>
+      <c r="F246" t="s">
         <v>401</v>
       </c>
-      <c r="D246" t="s">
-        <v>409</v>
-      </c>
-      <c r="E246" t="s">
+      <c r="G246" t="s">
         <v>410</v>
-      </c>
-      <c r="F246" t="s">
-        <v>256</v>
-      </c>
-      <c r="G246" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7277,16 +7277,16 @@
         <v>8</v>
       </c>
       <c r="C247" t="s">
+        <v>95</v>
+      </c>
+      <c r="D247" t="s">
+        <v>96</v>
+      </c>
+      <c r="E247" t="s">
+        <v>97</v>
+      </c>
+      <c r="F247" t="s">
         <v>412</v>
-      </c>
-      <c r="D247" t="s">
-        <v>95</v>
-      </c>
-      <c r="F247" t="s">
-        <v>96</v>
-      </c>
-      <c r="G247" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7297,16 +7297,16 @@
         <v>8</v>
       </c>
       <c r="C248" t="s">
+        <v>95</v>
+      </c>
+      <c r="D248" t="s">
+        <v>96</v>
+      </c>
+      <c r="E248" t="s">
+        <v>97</v>
+      </c>
+      <c r="F248" t="s">
         <v>412</v>
-      </c>
-      <c r="D248" t="s">
-        <v>95</v>
-      </c>
-      <c r="F248" t="s">
-        <v>96</v>
-      </c>
-      <c r="G248" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7317,16 +7317,16 @@
         <v>8</v>
       </c>
       <c r="C249" t="s">
+        <v>415</v>
+      </c>
+      <c r="D249" t="s">
+        <v>416</v>
+      </c>
+      <c r="E249" t="s">
+        <v>97</v>
+      </c>
+      <c r="F249" t="s">
         <v>412</v>
-      </c>
-      <c r="D249" t="s">
-        <v>415</v>
-      </c>
-      <c r="F249" t="s">
-        <v>416</v>
-      </c>
-      <c r="G249" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7337,16 +7337,16 @@
         <v>8</v>
       </c>
       <c r="C250" t="s">
+        <v>95</v>
+      </c>
+      <c r="D250" t="s">
+        <v>96</v>
+      </c>
+      <c r="E250" t="s">
+        <v>97</v>
+      </c>
+      <c r="F250" t="s">
         <v>412</v>
-      </c>
-      <c r="D250" t="s">
-        <v>95</v>
-      </c>
-      <c r="F250" t="s">
-        <v>96</v>
-      </c>
-      <c r="G250" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7357,16 +7357,16 @@
         <v>8</v>
       </c>
       <c r="C251" t="s">
+        <v>95</v>
+      </c>
+      <c r="D251" t="s">
+        <v>96</v>
+      </c>
+      <c r="E251" t="s">
+        <v>97</v>
+      </c>
+      <c r="F251" t="s">
         <v>412</v>
-      </c>
-      <c r="D251" t="s">
-        <v>95</v>
-      </c>
-      <c r="F251" t="s">
-        <v>96</v>
-      </c>
-      <c r="G251" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7377,16 +7377,16 @@
         <v>8</v>
       </c>
       <c r="C252" t="s">
+        <v>95</v>
+      </c>
+      <c r="D252" t="s">
+        <v>96</v>
+      </c>
+      <c r="E252" t="s">
+        <v>97</v>
+      </c>
+      <c r="F252" t="s">
         <v>412</v>
-      </c>
-      <c r="D252" t="s">
-        <v>95</v>
-      </c>
-      <c r="F252" t="s">
-        <v>96</v>
-      </c>
-      <c r="G252" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7402,11 +7402,11 @@
       <c r="D253" t="s">
         <v>422</v>
       </c>
+      <c r="E253" t="s">
+        <v>165</v>
+      </c>
       <c r="F253" t="s">
         <v>423</v>
-      </c>
-      <c r="G253" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7417,16 +7417,16 @@
         <v>8</v>
       </c>
       <c r="C254" t="s">
-        <v>421</v>
+        <v>219</v>
       </c>
       <c r="D254" t="s">
-        <v>219</v>
+        <v>220</v>
+      </c>
+      <c r="E254" t="s">
+        <v>92</v>
       </c>
       <c r="F254" t="s">
-        <v>220</v>
-      </c>
-      <c r="G254" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7437,16 +7437,16 @@
         <v>8</v>
       </c>
       <c r="C255" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D255" t="s">
-        <v>426</v>
+        <v>427</v>
+      </c>
+      <c r="E255" t="s">
+        <v>92</v>
       </c>
       <c r="F255" t="s">
-        <v>427</v>
-      </c>
-      <c r="G255" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7457,19 +7457,19 @@
         <v>8</v>
       </c>
       <c r="C256" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D256" t="s">
-        <v>426</v>
+        <v>427</v>
+      </c>
+      <c r="E256" t="s">
+        <v>92</v>
       </c>
       <c r="F256" t="s">
-        <v>427</v>
-      </c>
-      <c r="G256" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>429</v>
       </c>
@@ -7477,19 +7477,19 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D257" t="s">
-        <v>426</v>
+        <v>427</v>
+      </c>
+      <c r="E257" t="s">
+        <v>92</v>
       </c>
       <c r="F257" t="s">
-        <v>427</v>
-      </c>
-      <c r="G257" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>430</v>
       </c>
@@ -7497,19 +7497,19 @@
         <v>8</v>
       </c>
       <c r="C258" t="s">
-        <v>421</v>
+        <v>325</v>
       </c>
       <c r="D258" t="s">
         <v>326</v>
       </c>
+      <c r="E258" t="s">
+        <v>165</v>
+      </c>
       <c r="F258" t="s">
-        <v>328</v>
-      </c>
-      <c r="G258" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>431</v>
       </c>
@@ -7517,19 +7517,19 @@
         <v>8</v>
       </c>
       <c r="C259" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D259" t="s">
-        <v>426</v>
+        <v>427</v>
+      </c>
+      <c r="E259" t="s">
+        <v>92</v>
       </c>
       <c r="F259" t="s">
-        <v>427</v>
-      </c>
-      <c r="G259" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>432</v>
       </c>
@@ -7537,19 +7537,19 @@
         <v>8</v>
       </c>
       <c r="C260" t="s">
-        <v>421</v>
+        <v>163</v>
       </c>
       <c r="D260" t="s">
-        <v>163</v>
+        <v>164</v>
+      </c>
+      <c r="E260" t="s">
+        <v>165</v>
       </c>
       <c r="F260" t="s">
-        <v>164</v>
-      </c>
-      <c r="G260" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>433</v>
       </c>
@@ -7557,19 +7557,19 @@
         <v>8</v>
       </c>
       <c r="C261" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="D261" t="s">
-        <v>434</v>
+        <v>435</v>
+      </c>
+      <c r="E261" t="s">
+        <v>197</v>
       </c>
       <c r="F261" t="s">
-        <v>435</v>
-      </c>
-      <c r="G261" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>436</v>
       </c>
@@ -7577,19 +7577,19 @@
         <v>8</v>
       </c>
       <c r="C262" t="s">
-        <v>421</v>
+        <v>163</v>
       </c>
       <c r="D262" t="s">
-        <v>163</v>
+        <v>164</v>
+      </c>
+      <c r="E262" t="s">
+        <v>165</v>
       </c>
       <c r="F262" t="s">
-        <v>164</v>
-      </c>
-      <c r="G262" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>437</v>
       </c>
@@ -7597,19 +7597,19 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="D263" t="s">
-        <v>438</v>
+        <v>439</v>
+      </c>
+      <c r="E263" t="s">
+        <v>184</v>
       </c>
       <c r="F263" t="s">
-        <v>439</v>
-      </c>
-      <c r="G263" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>440</v>
       </c>
@@ -7617,19 +7617,19 @@
         <v>8</v>
       </c>
       <c r="C264" t="s">
-        <v>421</v>
+        <v>31</v>
       </c>
       <c r="D264" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="E264" t="s">
+        <v>33</v>
       </c>
       <c r="F264" t="s">
-        <v>32</v>
-      </c>
-      <c r="G264" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>441</v>
       </c>
@@ -7637,19 +7637,19 @@
         <v>8</v>
       </c>
       <c r="C265" t="s">
-        <v>421</v>
+        <v>9</v>
       </c>
       <c r="D265" t="s">
         <v>10</v>
       </c>
+      <c r="E265" t="s">
+        <v>11</v>
+      </c>
       <c r="F265" t="s">
-        <v>12</v>
-      </c>
-      <c r="G265" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>442</v>
       </c>
@@ -7657,19 +7657,19 @@
         <v>8</v>
       </c>
       <c r="C266" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="D266" t="s">
-        <v>443</v>
+        <v>444</v>
+      </c>
+      <c r="E266" t="s">
+        <v>114</v>
       </c>
       <c r="F266" t="s">
-        <v>444</v>
-      </c>
-      <c r="G266" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>445</v>
       </c>
@@ -7677,19 +7677,19 @@
         <v>8</v>
       </c>
       <c r="C267" t="s">
+        <v>118</v>
+      </c>
+      <c r="D267" t="s">
+        <v>119</v>
+      </c>
+      <c r="E267" t="s">
+        <v>114</v>
+      </c>
+      <c r="F267" t="s">
         <v>446</v>
       </c>
-      <c r="D267" t="s">
-        <v>118</v>
-      </c>
-      <c r="F267" t="s">
-        <v>119</v>
-      </c>
-      <c r="G267" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7">
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>447</v>
       </c>
@@ -7697,19 +7697,19 @@
         <v>8</v>
       </c>
       <c r="C268" t="s">
-        <v>448</v>
+        <v>202</v>
       </c>
       <c r="D268" t="s">
         <v>203</v>
       </c>
+      <c r="E268" t="s">
+        <v>184</v>
+      </c>
       <c r="F268" t="s">
-        <v>204</v>
-      </c>
-      <c r="G268" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>449</v>
       </c>
@@ -7717,19 +7717,19 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
+        <v>118</v>
+      </c>
+      <c r="D269" t="s">
+        <v>119</v>
+      </c>
+      <c r="E269" t="s">
+        <v>114</v>
+      </c>
+      <c r="F269" t="s">
         <v>450</v>
       </c>
-      <c r="D269" t="s">
-        <v>118</v>
-      </c>
-      <c r="F269" t="s">
-        <v>119</v>
-      </c>
-      <c r="G269" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7">
+    </row>
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>451</v>
       </c>
@@ -7737,19 +7737,19 @@
         <v>8</v>
       </c>
       <c r="C270" t="s">
+        <v>118</v>
+      </c>
+      <c r="D270" t="s">
+        <v>119</v>
+      </c>
+      <c r="E270" t="s">
+        <v>114</v>
+      </c>
+      <c r="F270" t="s">
         <v>450</v>
       </c>
-      <c r="D270" t="s">
-        <v>118</v>
-      </c>
-      <c r="F270" t="s">
-        <v>119</v>
-      </c>
-      <c r="G270" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7">
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>452</v>
       </c>
@@ -7762,14 +7762,14 @@
       <c r="D271" t="s">
         <v>454</v>
       </c>
+      <c r="E271" t="s">
+        <v>114</v>
+      </c>
       <c r="F271" t="s">
         <v>455</v>
       </c>
-      <c r="G271" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7">
+    </row>
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>456</v>
       </c>
@@ -7782,14 +7782,14 @@
       <c r="D272" t="s">
         <v>454</v>
       </c>
+      <c r="E272" t="s">
+        <v>114</v>
+      </c>
       <c r="F272" t="s">
         <v>455</v>
       </c>
-      <c r="G272" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7">
+    </row>
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>457</v>
       </c>
@@ -7802,14 +7802,14 @@
       <c r="D273" t="s">
         <v>454</v>
       </c>
+      <c r="E273" t="s">
+        <v>114</v>
+      </c>
       <c r="F273" t="s">
         <v>455</v>
       </c>
-      <c r="G273" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7">
+    </row>
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>458</v>
       </c>
@@ -7822,14 +7822,14 @@
       <c r="D274" t="s">
         <v>454</v>
       </c>
+      <c r="E274" t="s">
+        <v>114</v>
+      </c>
       <c r="F274" t="s">
         <v>455</v>
       </c>
-      <c r="G274" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7">
+    </row>
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>459</v>
       </c>
@@ -7842,14 +7842,14 @@
       <c r="D275" t="s">
         <v>454</v>
       </c>
+      <c r="E275" t="s">
+        <v>114</v>
+      </c>
       <c r="F275" t="s">
         <v>455</v>
       </c>
-      <c r="G275" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7">
+    </row>
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>460</v>
       </c>
@@ -7862,14 +7862,14 @@
       <c r="D276" t="s">
         <v>454</v>
       </c>
+      <c r="E276" t="s">
+        <v>114</v>
+      </c>
       <c r="F276" t="s">
         <v>455</v>
       </c>
-      <c r="G276" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7">
+    </row>
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>461</v>
       </c>
@@ -7882,14 +7882,14 @@
       <c r="D277" t="s">
         <v>454</v>
       </c>
+      <c r="E277" t="s">
+        <v>114</v>
+      </c>
       <c r="F277" t="s">
         <v>455</v>
       </c>
-      <c r="G277" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7">
+    </row>
+    <row r="278" spans="1:6">
       <c r="A278" t="s">
         <v>462</v>
       </c>
@@ -7897,19 +7897,19 @@
         <v>8</v>
       </c>
       <c r="C278" t="s">
-        <v>463</v>
+        <v>202</v>
       </c>
       <c r="D278" t="s">
         <v>203</v>
       </c>
+      <c r="E278" t="s">
+        <v>184</v>
+      </c>
       <c r="F278" t="s">
-        <v>204</v>
-      </c>
-      <c r="G278" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>464</v>
       </c>
@@ -7917,19 +7917,19 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
-        <v>463</v>
+        <v>51</v>
       </c>
       <c r="D279" t="s">
         <v>52</v>
       </c>
+      <c r="E279" t="s">
+        <v>33</v>
+      </c>
       <c r="F279" t="s">
-        <v>54</v>
-      </c>
-      <c r="G279" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280" t="s">
         <v>465</v>
       </c>
@@ -7937,19 +7937,19 @@
         <v>8</v>
       </c>
       <c r="C280" t="s">
-        <v>463</v>
+        <v>9</v>
       </c>
       <c r="D280" t="s">
         <v>10</v>
       </c>
+      <c r="E280" t="s">
+        <v>11</v>
+      </c>
       <c r="F280" t="s">
-        <v>12</v>
-      </c>
-      <c r="G280" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281" t="s">
         <v>466</v>
       </c>
@@ -7957,19 +7957,19 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
+        <v>170</v>
+      </c>
+      <c r="D281" t="s">
+        <v>171</v>
+      </c>
+      <c r="E281" t="s">
+        <v>114</v>
+      </c>
+      <c r="F281" t="s">
         <v>463</v>
       </c>
-      <c r="D281" t="s">
-        <v>170</v>
-      </c>
-      <c r="F281" t="s">
-        <v>171</v>
-      </c>
-      <c r="G281" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7">
+    </row>
+    <row r="282" spans="1:6">
       <c r="A282" t="s">
         <v>467</v>
       </c>
@@ -7977,19 +7977,19 @@
         <v>8</v>
       </c>
       <c r="C282" t="s">
+        <v>124</v>
+      </c>
+      <c r="D282" t="s">
+        <v>125</v>
+      </c>
+      <c r="E282" t="s">
+        <v>126</v>
+      </c>
+      <c r="F282" t="s">
         <v>463</v>
       </c>
-      <c r="D282" t="s">
-        <v>124</v>
-      </c>
-      <c r="F282" t="s">
-        <v>125</v>
-      </c>
-      <c r="G282" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7">
+    </row>
+    <row r="283" spans="1:6">
       <c r="A283" t="s">
         <v>468</v>
       </c>
@@ -7997,19 +7997,19 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
+        <v>398</v>
+      </c>
+      <c r="D283" t="s">
+        <v>364</v>
+      </c>
+      <c r="E283" t="s">
+        <v>165</v>
+      </c>
+      <c r="F283" t="s">
         <v>469</v>
       </c>
-      <c r="D283" t="s">
-        <v>398</v>
-      </c>
-      <c r="F283" t="s">
-        <v>366</v>
-      </c>
-      <c r="G283" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
+    </row>
+    <row r="284" spans="1:6">
       <c r="A284" t="s">
         <v>470</v>
       </c>
@@ -8017,19 +8017,19 @@
         <v>8</v>
       </c>
       <c r="C284" t="s">
+        <v>124</v>
+      </c>
+      <c r="D284" t="s">
+        <v>125</v>
+      </c>
+      <c r="E284" t="s">
+        <v>126</v>
+      </c>
+      <c r="F284" t="s">
         <v>471</v>
       </c>
-      <c r="D284" t="s">
-        <v>124</v>
-      </c>
-      <c r="F284" t="s">
-        <v>125</v>
-      </c>
-      <c r="G284" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7">
+    </row>
+    <row r="285" spans="1:6">
       <c r="A285" t="s">
         <v>472</v>
       </c>
@@ -8037,19 +8037,19 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
+        <v>170</v>
+      </c>
+      <c r="D285" t="s">
+        <v>171</v>
+      </c>
+      <c r="E285" t="s">
+        <v>114</v>
+      </c>
+      <c r="F285" t="s">
         <v>473</v>
       </c>
-      <c r="D285" t="s">
-        <v>170</v>
-      </c>
-      <c r="F285" t="s">
-        <v>171</v>
-      </c>
-      <c r="G285" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
+    </row>
+    <row r="286" spans="1:6">
       <c r="A286" t="s">
         <v>474</v>
       </c>
@@ -8057,19 +8057,19 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
+        <v>438</v>
+      </c>
+      <c r="D286" t="s">
+        <v>439</v>
+      </c>
+      <c r="E286" t="s">
+        <v>184</v>
+      </c>
+      <c r="F286" t="s">
         <v>475</v>
       </c>
-      <c r="D286" t="s">
-        <v>438</v>
-      </c>
-      <c r="F286" t="s">
-        <v>439</v>
-      </c>
-      <c r="G286" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
+    </row>
+    <row r="287" spans="1:6">
       <c r="A287" t="s">
         <v>476</v>
       </c>
@@ -8077,19 +8077,19 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
+        <v>438</v>
+      </c>
+      <c r="D287" t="s">
+        <v>439</v>
+      </c>
+      <c r="E287" t="s">
+        <v>184</v>
+      </c>
+      <c r="F287" t="s">
         <v>475</v>
       </c>
-      <c r="D287" t="s">
-        <v>438</v>
-      </c>
-      <c r="F287" t="s">
-        <v>439</v>
-      </c>
-      <c r="G287" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7">
+    </row>
+    <row r="288" spans="1:6">
       <c r="A288" t="s">
         <v>477</v>
       </c>
@@ -8097,19 +8097,19 @@
         <v>8</v>
       </c>
       <c r="C288" t="s">
+        <v>41</v>
+      </c>
+      <c r="D288" t="s">
+        <v>42</v>
+      </c>
+      <c r="E288" t="s">
+        <v>11</v>
+      </c>
+      <c r="F288" t="s">
         <v>475</v>
       </c>
-      <c r="D288" t="s">
-        <v>41</v>
-      </c>
-      <c r="F288" t="s">
-        <v>42</v>
-      </c>
-      <c r="G288" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7">
+    </row>
+    <row r="289" spans="1:6">
       <c r="A289" t="s">
         <v>478</v>
       </c>
@@ -8117,19 +8117,19 @@
         <v>8</v>
       </c>
       <c r="C289" t="s">
+        <v>31</v>
+      </c>
+      <c r="D289" t="s">
+        <v>32</v>
+      </c>
+      <c r="E289" t="s">
+        <v>33</v>
+      </c>
+      <c r="F289" t="s">
         <v>475</v>
       </c>
-      <c r="D289" t="s">
-        <v>31</v>
-      </c>
-      <c r="F289" t="s">
-        <v>32</v>
-      </c>
-      <c r="G289" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7">
+    </row>
+    <row r="290" spans="1:6">
       <c r="A290" t="s">
         <v>479</v>
       </c>
@@ -8137,19 +8137,19 @@
         <v>8</v>
       </c>
       <c r="C290" t="s">
+        <v>31</v>
+      </c>
+      <c r="D290" t="s">
+        <v>32</v>
+      </c>
+      <c r="E290" t="s">
+        <v>33</v>
+      </c>
+      <c r="F290" t="s">
         <v>475</v>
       </c>
-      <c r="D290" t="s">
-        <v>31</v>
-      </c>
-      <c r="F290" t="s">
-        <v>32</v>
-      </c>
-      <c r="G290" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7">
+    </row>
+    <row r="291" spans="1:6">
       <c r="A291" t="s">
         <v>480</v>
       </c>
@@ -8157,19 +8157,19 @@
         <v>8</v>
       </c>
       <c r="C291" t="s">
+        <v>170</v>
+      </c>
+      <c r="D291" t="s">
+        <v>171</v>
+      </c>
+      <c r="E291" t="s">
+        <v>114</v>
+      </c>
+      <c r="F291" t="s">
         <v>475</v>
       </c>
-      <c r="D291" t="s">
-        <v>170</v>
-      </c>
-      <c r="F291" t="s">
-        <v>171</v>
-      </c>
-      <c r="G291" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7">
+    </row>
+    <row r="292" spans="1:6">
       <c r="A292" t="s">
         <v>481</v>
       </c>
@@ -8177,19 +8177,19 @@
         <v>8</v>
       </c>
       <c r="C292" t="s">
+        <v>170</v>
+      </c>
+      <c r="D292" t="s">
+        <v>171</v>
+      </c>
+      <c r="E292" t="s">
+        <v>114</v>
+      </c>
+      <c r="F292" t="s">
         <v>475</v>
       </c>
-      <c r="D292" t="s">
-        <v>170</v>
-      </c>
-      <c r="F292" t="s">
-        <v>171</v>
-      </c>
-      <c r="G292" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7">
+    </row>
+    <row r="293" spans="1:6">
       <c r="A293" t="s">
         <v>482</v>
       </c>
@@ -8197,19 +8197,19 @@
         <v>8</v>
       </c>
       <c r="C293" t="s">
+        <v>170</v>
+      </c>
+      <c r="D293" t="s">
+        <v>171</v>
+      </c>
+      <c r="E293" t="s">
+        <v>114</v>
+      </c>
+      <c r="F293" t="s">
         <v>475</v>
       </c>
-      <c r="D293" t="s">
-        <v>170</v>
-      </c>
-      <c r="F293" t="s">
-        <v>171</v>
-      </c>
-      <c r="G293" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7">
+    </row>
+    <row r="294" spans="1:6">
       <c r="A294" t="s">
         <v>483</v>
       </c>
@@ -8217,19 +8217,19 @@
         <v>8</v>
       </c>
       <c r="C294" t="s">
+        <v>170</v>
+      </c>
+      <c r="D294" t="s">
+        <v>171</v>
+      </c>
+      <c r="E294" t="s">
+        <v>114</v>
+      </c>
+      <c r="F294" t="s">
         <v>475</v>
       </c>
-      <c r="D294" t="s">
-        <v>170</v>
-      </c>
-      <c r="F294" t="s">
-        <v>171</v>
-      </c>
-      <c r="G294" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7">
+    </row>
+    <row r="295" spans="1:6">
       <c r="A295" t="s">
         <v>484</v>
       </c>
@@ -8237,19 +8237,19 @@
         <v>8</v>
       </c>
       <c r="C295" t="s">
+        <v>170</v>
+      </c>
+      <c r="D295" t="s">
+        <v>171</v>
+      </c>
+      <c r="E295" t="s">
+        <v>114</v>
+      </c>
+      <c r="F295" t="s">
         <v>485</v>
       </c>
-      <c r="D295" t="s">
-        <v>170</v>
-      </c>
-      <c r="F295" t="s">
-        <v>171</v>
-      </c>
-      <c r="G295" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7">
+    </row>
+    <row r="296" spans="1:6">
       <c r="A296" t="s">
         <v>486</v>
       </c>
@@ -8257,16 +8257,16 @@
         <v>8</v>
       </c>
       <c r="C296" t="s">
+        <v>170</v>
+      </c>
+      <c r="D296" t="s">
+        <v>171</v>
+      </c>
+      <c r="E296" t="s">
+        <v>114</v>
+      </c>
+      <c r="F296" t="s">
         <v>485</v>
-      </c>
-      <c r="D296" t="s">
-        <v>170</v>
-      </c>
-      <c r="F296" t="s">
-        <v>171</v>
-      </c>
-      <c r="G296" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,75 +22,75 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,99 +109,99 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>09.2.2 - Upper‐secondary education (IS)</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,42 +811,42 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>04.3.3 - Nuclear fuel (CS)</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>04.2.2 - Forestry (CS)</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>04.2.3 - Fishing and hunting (CS)</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,12 +1210,12 @@
     <t>32310</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>04.4.3 - Construction (CS)</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,19 +1863,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1909,19 +1909,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1932,16 +1932,16 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1961,13 +1961,13 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1978,16 +1978,16 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -2001,16 +2001,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -2024,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
         <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2050,16 +2050,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2070,19 +2070,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
         <v>35</v>
       </c>
-      <c r="D12" t="s">
+      <c r="G12" t="s">
         <v>36</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,16 +2093,16 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2116,19 +2116,19 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
         <v>41</v>
       </c>
-      <c r="D14" t="s">
+      <c r="G14" t="s">
         <v>42</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2139,16 +2139,16 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
         <v>44</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>46</v>
@@ -2162,19 +2162,19 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
         <v>48</v>
       </c>
-      <c r="D16" t="s">
+      <c r="G16" t="s">
         <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2185,13 +2185,13 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
         <v>51</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>52</v>
-      </c>
-      <c r="E17" t="s">
-        <v>33</v>
       </c>
       <c r="F17" t="s">
         <v>53</v>
@@ -2208,13 +2208,13 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
         <v>51</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>52</v>
-      </c>
-      <c r="E18" t="s">
-        <v>33</v>
       </c>
       <c r="F18" t="s">
         <v>53</v>
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" t="s">
         <v>57</v>
       </c>
-      <c r="D19" t="s">
+      <c r="G19" t="s">
         <v>58</v>
-      </c>
-      <c r="E19" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2254,19 +2254,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" t="s">
         <v>60</v>
       </c>
-      <c r="D20" t="s">
+      <c r="G20" t="s">
         <v>61</v>
-      </c>
-      <c r="E20" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2277,13 +2277,13 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
         <v>51</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>52</v>
-      </c>
-      <c r="E21" t="s">
-        <v>33</v>
       </c>
       <c r="F21" t="s">
         <v>53</v>
@@ -2303,16 +2303,16 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" t="s">
         <v>32</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>33</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" t="s">
         <v>66</v>
       </c>
-      <c r="D23" t="s">
+      <c r="G23" t="s">
         <v>67</v>
-      </c>
-      <c r="E23" t="s">
-        <v>33</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2349,16 +2349,16 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>33</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2372,16 +2372,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>33</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2395,16 +2395,16 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" t="s">
         <v>32</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>33</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2418,16 +2418,16 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
         <v>33</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2441,16 +2441,16 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" t="s">
         <v>32</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>33</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2464,16 +2464,16 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" t="s">
         <v>32</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>33</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2484,19 +2484,19 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" t="s">
         <v>51</v>
       </c>
-      <c r="D30" t="s">
-        <v>52</v>
-      </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F30" t="s">
         <v>53</v>
       </c>
       <c r="G30" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2510,16 +2510,16 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" t="s">
         <v>32</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>33</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
-      </c>
-      <c r="G31" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2533,16 +2533,16 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" t="s">
         <v>32</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>33</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2556,16 +2556,16 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" t="s">
         <v>32</v>
       </c>
-      <c r="E33" t="s">
+      <c r="G33" t="s">
         <v>33</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
-      </c>
-      <c r="G33" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2579,16 +2579,16 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" t="s">
         <v>32</v>
       </c>
-      <c r="E34" t="s">
+      <c r="G34" t="s">
         <v>33</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
-      </c>
-      <c r="G34" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2602,16 +2602,16 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" t="s">
         <v>32</v>
       </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>33</v>
-      </c>
-      <c r="F35" t="s">
-        <v>53</v>
-      </c>
-      <c r="G35" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" t="s">
         <v>57</v>
       </c>
-      <c r="D36" t="s">
+      <c r="G36" t="s">
         <v>58</v>
-      </c>
-      <c r="E36" t="s">
-        <v>33</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
-      </c>
-      <c r="G36" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2648,13 +2648,13 @@
         <v>31</v>
       </c>
       <c r="D37" t="s">
+        <v>83</v>
+      </c>
+      <c r="F37" t="s">
         <v>32</v>
       </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>33</v>
-      </c>
-      <c r="F37" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2668,13 +2668,13 @@
         <v>31</v>
       </c>
       <c r="D38" t="s">
+        <v>83</v>
+      </c>
+      <c r="F38" t="s">
         <v>32</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>33</v>
-      </c>
-      <c r="F38" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2688,13 +2688,13 @@
         <v>31</v>
       </c>
       <c r="D39" t="s">
+        <v>83</v>
+      </c>
+      <c r="F39" t="s">
         <v>32</v>
       </c>
-      <c r="E39" t="s">
+      <c r="G39" t="s">
         <v>33</v>
-      </c>
-      <c r="F39" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2708,13 +2708,13 @@
         <v>31</v>
       </c>
       <c r="D40" t="s">
+        <v>83</v>
+      </c>
+      <c r="F40" t="s">
         <v>32</v>
       </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
         <v>33</v>
-      </c>
-      <c r="F40" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2725,16 +2725,16 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
-      </c>
-      <c r="E41" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="F41" t="s">
-        <v>83</v>
+        <v>53</v>
+      </c>
+      <c r="G41" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2745,16 +2745,16 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" t="s">
         <v>57</v>
       </c>
-      <c r="D42" t="s">
+      <c r="G42" t="s">
         <v>58</v>
-      </c>
-      <c r="E42" t="s">
-        <v>33</v>
-      </c>
-      <c r="F42" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2770,10 +2770,10 @@
       <c r="D43" t="s">
         <v>91</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>92</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2788,13 +2788,13 @@
         <v>95</v>
       </c>
       <c r="D44" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" t="s">
         <v>96</v>
       </c>
-      <c r="E44" t="s">
+      <c r="G44" t="s">
         <v>97</v>
-      </c>
-      <c r="F44" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2810,10 +2810,10 @@
       <c r="D45" t="s">
         <v>91</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>92</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2830,10 +2830,10 @@
       <c r="D46" t="s">
         <v>91</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>92</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2845,16 +2845,16 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
+        <v>95</v>
+      </c>
+      <c r="D47" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" t="s">
         <v>101</v>
       </c>
-      <c r="D47" t="s">
+      <c r="G47" t="s">
         <v>102</v>
-      </c>
-      <c r="E47" t="s">
-        <v>97</v>
-      </c>
-      <c r="F47" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2870,10 +2870,10 @@
       <c r="D48" t="s">
         <v>91</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>92</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2890,10 +2890,10 @@
       <c r="D49" t="s">
         <v>91</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>92</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2905,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" t="s">
+        <v>91</v>
+      </c>
+      <c r="F50" t="s">
         <v>101</v>
       </c>
-      <c r="D50" t="s">
+      <c r="G50" t="s">
         <v>102</v>
-      </c>
-      <c r="E50" t="s">
-        <v>97</v>
-      </c>
-      <c r="F50" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2930,10 +2930,10 @@
       <c r="D51" t="s">
         <v>91</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>92</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" t="s">
         <v>108</v>
       </c>
-      <c r="D52" t="s">
+      <c r="G52" t="s">
         <v>109</v>
-      </c>
-      <c r="E52" t="s">
-        <v>97</v>
-      </c>
-      <c r="F52" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2968,13 +2968,13 @@
         <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="F53" t="s">
-        <v>93</v>
+        <v>12</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3008,19 +3008,19 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E55" t="s">
         <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G55" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3031,19 +3031,19 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D56" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E56" t="s">
         <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G56" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3057,16 +3057,16 @@
         <v>124</v>
       </c>
       <c r="D57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" t="s">
         <v>125</v>
       </c>
-      <c r="E57" t="s">
+      <c r="G57" t="s">
         <v>126</v>
-      </c>
-      <c r="F57" t="s">
-        <v>115</v>
-      </c>
-      <c r="G57" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3077,19 +3077,19 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E58" t="s">
         <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G58" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3100,19 +3100,19 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D59" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E59" t="s">
         <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G59" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3123,19 +3123,19 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D60" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E60" t="s">
         <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G60" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3146,19 +3146,19 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D61" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G61" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3169,19 +3169,19 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E62" t="s">
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G62" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3192,19 +3192,19 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D63" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E63" t="s">
         <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G63" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3215,19 +3215,19 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E64" t="s">
         <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G64" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3238,19 +3238,19 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="E65" t="s">
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="G65" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3284,19 +3284,19 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D67" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E67" t="s">
         <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G67" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3307,7 +3307,7 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="D68" t="s">
         <v>113</v>
@@ -3319,7 +3319,7 @@
         <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3330,7 +3330,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D69" t="s">
         <v>113</v>
@@ -3342,7 +3342,7 @@
         <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3353,19 +3353,19 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D70" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E70" t="s">
         <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G70" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3376,19 +3376,19 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D71" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E71" t="s">
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G71" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3422,19 +3422,19 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
+        <v>124</v>
+      </c>
+      <c r="D73" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" t="s">
+        <v>114</v>
+      </c>
+      <c r="F73" t="s">
         <v>148</v>
       </c>
-      <c r="D73" t="s">
+      <c r="G73" t="s">
         <v>149</v>
-      </c>
-      <c r="E73" t="s">
-        <v>126</v>
-      </c>
-      <c r="F73" t="s">
-        <v>115</v>
-      </c>
-      <c r="G73" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3445,19 +3445,19 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74" t="s">
+        <v>113</v>
+      </c>
+      <c r="E74" t="s">
+        <v>114</v>
+      </c>
+      <c r="F74" t="s">
         <v>151</v>
       </c>
-      <c r="D74" t="s">
+      <c r="G74" t="s">
         <v>152</v>
-      </c>
-      <c r="E74" t="s">
-        <v>126</v>
-      </c>
-      <c r="F74" t="s">
-        <v>115</v>
-      </c>
-      <c r="G74" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3468,19 +3468,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
+        <v>124</v>
+      </c>
+      <c r="D75" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" t="s">
+        <v>114</v>
+      </c>
+      <c r="F75" t="s">
         <v>154</v>
       </c>
-      <c r="D75" t="s">
+      <c r="G75" t="s">
         <v>155</v>
-      </c>
-      <c r="E75" t="s">
-        <v>126</v>
-      </c>
-      <c r="F75" t="s">
-        <v>115</v>
-      </c>
-      <c r="G75" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3491,19 +3491,19 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
+        <v>124</v>
+      </c>
+      <c r="D76" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76" t="s">
+        <v>114</v>
+      </c>
+      <c r="F76" t="s">
         <v>148</v>
       </c>
-      <c r="D76" t="s">
+      <c r="G76" t="s">
         <v>149</v>
-      </c>
-      <c r="E76" t="s">
-        <v>126</v>
-      </c>
-      <c r="F76" t="s">
-        <v>115</v>
-      </c>
-      <c r="G76" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3514,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
+        <v>124</v>
+      </c>
+      <c r="D77" t="s">
+        <v>113</v>
+      </c>
+      <c r="E77" t="s">
+        <v>114</v>
+      </c>
+      <c r="F77" t="s">
         <v>148</v>
       </c>
-      <c r="D77" t="s">
+      <c r="G77" t="s">
         <v>149</v>
-      </c>
-      <c r="E77" t="s">
-        <v>126</v>
-      </c>
-      <c r="F77" t="s">
-        <v>115</v>
-      </c>
-      <c r="G77" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3537,19 +3537,19 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
+        <v>124</v>
+      </c>
+      <c r="D78" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" t="s">
+        <v>114</v>
+      </c>
+      <c r="F78" t="s">
         <v>151</v>
       </c>
-      <c r="D78" t="s">
+      <c r="G78" t="s">
         <v>152</v>
-      </c>
-      <c r="E78" t="s">
-        <v>126</v>
-      </c>
-      <c r="F78" t="s">
-        <v>115</v>
-      </c>
-      <c r="G78" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3560,19 +3560,19 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
+        <v>124</v>
+      </c>
+      <c r="D79" t="s">
+        <v>113</v>
+      </c>
+      <c r="E79" t="s">
+        <v>114</v>
+      </c>
+      <c r="F79" t="s">
         <v>160</v>
       </c>
-      <c r="D79" t="s">
+      <c r="G79" t="s">
         <v>161</v>
-      </c>
-      <c r="E79" t="s">
-        <v>126</v>
-      </c>
-      <c r="F79" t="s">
-        <v>115</v>
-      </c>
-      <c r="G79" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3586,16 +3586,16 @@
         <v>163</v>
       </c>
       <c r="D80" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80" t="s">
+        <v>114</v>
+      </c>
+      <c r="F80" t="s">
         <v>164</v>
       </c>
-      <c r="E80" t="s">
+      <c r="G80" t="s">
         <v>165</v>
-      </c>
-      <c r="F80" t="s">
-        <v>115</v>
-      </c>
-      <c r="G80" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3609,16 +3609,16 @@
         <v>163</v>
       </c>
       <c r="D81" t="s">
+        <v>113</v>
+      </c>
+      <c r="E81" t="s">
+        <v>114</v>
+      </c>
+      <c r="F81" t="s">
         <v>164</v>
       </c>
-      <c r="E81" t="s">
+      <c r="G81" t="s">
         <v>165</v>
-      </c>
-      <c r="F81" t="s">
-        <v>115</v>
-      </c>
-      <c r="G81" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3632,16 +3632,16 @@
         <v>163</v>
       </c>
       <c r="D82" t="s">
+        <v>113</v>
+      </c>
+      <c r="E82" t="s">
+        <v>114</v>
+      </c>
+      <c r="F82" t="s">
         <v>164</v>
       </c>
-      <c r="E82" t="s">
+      <c r="G82" t="s">
         <v>165</v>
-      </c>
-      <c r="F82" t="s">
-        <v>115</v>
-      </c>
-      <c r="G82" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D83" t="s">
         <v>113</v>
@@ -3664,7 +3664,7 @@
         <v>115</v>
       </c>
       <c r="G83" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3675,19 +3675,19 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="D84" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="E84" t="s">
         <v>114</v>
       </c>
       <c r="F84" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="G84" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3698,19 +3698,19 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="D85" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E85" t="s">
         <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G85" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
+        <v>163</v>
+      </c>
+      <c r="D86" t="s">
+        <v>113</v>
+      </c>
+      <c r="E86" t="s">
+        <v>114</v>
+      </c>
+      <c r="F86" t="s">
         <v>175</v>
       </c>
-      <c r="D86" t="s">
+      <c r="G86" t="s">
         <v>176</v>
-      </c>
-      <c r="E86" t="s">
-        <v>165</v>
-      </c>
-      <c r="F86" t="s">
-        <v>115</v>
-      </c>
-      <c r="G86" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,19 +3744,19 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E87" t="s">
         <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G87" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3767,19 +3767,19 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D88" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E88" t="s">
         <v>114</v>
       </c>
       <c r="F88" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G88" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3790,19 +3790,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D89" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E89" t="s">
         <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G89" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3816,16 +3816,16 @@
         <v>124</v>
       </c>
       <c r="D90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E90" t="s">
+        <v>114</v>
+      </c>
+      <c r="F90" t="s">
         <v>125</v>
       </c>
-      <c r="E90" t="s">
+      <c r="G90" t="s">
         <v>126</v>
-      </c>
-      <c r="F90" t="s">
-        <v>115</v>
-      </c>
-      <c r="G90" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3839,16 +3839,16 @@
         <v>182</v>
       </c>
       <c r="D91" t="s">
+        <v>113</v>
+      </c>
+      <c r="E91" t="s">
+        <v>114</v>
+      </c>
+      <c r="F91" t="s">
         <v>183</v>
       </c>
-      <c r="E91" t="s">
+      <c r="G91" t="s">
         <v>184</v>
-      </c>
-      <c r="F91" t="s">
-        <v>115</v>
-      </c>
-      <c r="G91" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3862,16 +3862,16 @@
         <v>124</v>
       </c>
       <c r="D92" t="s">
+        <v>113</v>
+      </c>
+      <c r="E92" t="s">
+        <v>114</v>
+      </c>
+      <c r="F92" t="s">
         <v>125</v>
       </c>
-      <c r="E92" t="s">
+      <c r="G92" t="s">
         <v>126</v>
-      </c>
-      <c r="F92" t="s">
-        <v>115</v>
-      </c>
-      <c r="G92" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3882,19 +3882,19 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D93" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G93" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3908,16 +3908,16 @@
         <v>124</v>
       </c>
       <c r="D94" t="s">
+        <v>113</v>
+      </c>
+      <c r="E94" t="s">
+        <v>114</v>
+      </c>
+      <c r="F94" t="s">
         <v>125</v>
       </c>
-      <c r="E94" t="s">
+      <c r="G94" t="s">
         <v>126</v>
-      </c>
-      <c r="F94" t="s">
-        <v>115</v>
-      </c>
-      <c r="G94" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3928,19 +3928,19 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="D95" t="s">
-        <v>190</v>
+        <v>113</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="G95" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3954,16 +3954,16 @@
         <v>124</v>
       </c>
       <c r="D96" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" t="s">
+        <v>192</v>
+      </c>
+      <c r="F96" t="s">
         <v>125</v>
       </c>
-      <c r="E96" t="s">
+      <c r="G96" t="s">
         <v>126</v>
-      </c>
-      <c r="F96" t="s">
-        <v>115</v>
-      </c>
-      <c r="G96" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3977,16 +3977,16 @@
         <v>124</v>
       </c>
       <c r="D97" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" t="s">
+        <v>192</v>
+      </c>
+      <c r="F97" t="s">
         <v>125</v>
       </c>
-      <c r="E97" t="s">
+      <c r="G97" t="s">
         <v>126</v>
-      </c>
-      <c r="F97" t="s">
-        <v>115</v>
-      </c>
-      <c r="G97" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4000,16 +4000,16 @@
         <v>195</v>
       </c>
       <c r="D98" t="s">
+        <v>113</v>
+      </c>
+      <c r="E98" t="s">
+        <v>192</v>
+      </c>
+      <c r="F98" t="s">
         <v>196</v>
       </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
         <v>197</v>
-      </c>
-      <c r="F98" t="s">
-        <v>115</v>
-      </c>
-      <c r="G98" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4023,16 +4023,16 @@
         <v>124</v>
       </c>
       <c r="D99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99" t="s">
+        <v>192</v>
+      </c>
+      <c r="F99" t="s">
         <v>125</v>
       </c>
-      <c r="E99" t="s">
+      <c r="G99" t="s">
         <v>126</v>
-      </c>
-      <c r="F99" t="s">
-        <v>115</v>
-      </c>
-      <c r="G99" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>124</v>
+      </c>
+      <c r="D100" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" t="s">
+        <v>192</v>
+      </c>
+      <c r="F100" t="s">
         <v>154</v>
       </c>
-      <c r="D100" t="s">
+      <c r="G100" t="s">
         <v>155</v>
-      </c>
-      <c r="E100" t="s">
-        <v>126</v>
-      </c>
-      <c r="F100" t="s">
-        <v>115</v>
-      </c>
-      <c r="G100" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4069,16 +4069,16 @@
         <v>124</v>
       </c>
       <c r="D101" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" t="s">
+        <v>192</v>
+      </c>
+      <c r="F101" t="s">
         <v>125</v>
       </c>
-      <c r="E101" t="s">
+      <c r="G101" t="s">
         <v>126</v>
-      </c>
-      <c r="F101" t="s">
-        <v>115</v>
-      </c>
-      <c r="G101" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4089,15 +4089,15 @@
         <v>8</v>
       </c>
       <c r="C102" t="s">
+        <v>182</v>
+      </c>
+      <c r="D102" t="s">
         <v>202</v>
       </c>
-      <c r="D102" t="s">
+      <c r="F102" t="s">
         <v>203</v>
       </c>
-      <c r="E102" t="s">
-        <v>184</v>
-      </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4109,15 +4109,15 @@
         <v>8</v>
       </c>
       <c r="C103" t="s">
+        <v>182</v>
+      </c>
+      <c r="D103" t="s">
         <v>202</v>
       </c>
-      <c r="D103" t="s">
+      <c r="F103" t="s">
         <v>203</v>
       </c>
-      <c r="E103" t="s">
-        <v>184</v>
-      </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4129,15 +4129,15 @@
         <v>8</v>
       </c>
       <c r="C104" t="s">
+        <v>182</v>
+      </c>
+      <c r="D104" t="s">
         <v>202</v>
       </c>
-      <c r="D104" t="s">
+      <c r="F104" t="s">
         <v>203</v>
       </c>
-      <c r="E104" t="s">
-        <v>184</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4149,16 +4149,16 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
+        <v>182</v>
+      </c>
+      <c r="D105" t="s">
+        <v>202</v>
+      </c>
+      <c r="F105" t="s">
         <v>208</v>
       </c>
-      <c r="D105" t="s">
+      <c r="G105" t="s">
         <v>209</v>
-      </c>
-      <c r="E105" t="s">
-        <v>184</v>
-      </c>
-      <c r="F105" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4169,15 +4169,15 @@
         <v>8</v>
       </c>
       <c r="C106" t="s">
+        <v>182</v>
+      </c>
+      <c r="D106" t="s">
         <v>202</v>
       </c>
-      <c r="D106" t="s">
+      <c r="F106" t="s">
         <v>203</v>
       </c>
-      <c r="E106" t="s">
-        <v>184</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4192,13 +4192,13 @@
         <v>182</v>
       </c>
       <c r="D107" t="s">
+        <v>202</v>
+      </c>
+      <c r="F107" t="s">
         <v>183</v>
       </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>184</v>
-      </c>
-      <c r="F107" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4209,16 +4209,16 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
+        <v>182</v>
+      </c>
+      <c r="D108" t="s">
+        <v>202</v>
+      </c>
+      <c r="F108" t="s">
         <v>213</v>
       </c>
-      <c r="D108" t="s">
+      <c r="G108" t="s">
         <v>214</v>
-      </c>
-      <c r="E108" t="s">
-        <v>184</v>
-      </c>
-      <c r="F108" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4229,16 +4229,16 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
+        <v>90</v>
+      </c>
+      <c r="D109" t="s">
+        <v>202</v>
+      </c>
+      <c r="F109" t="s">
         <v>216</v>
       </c>
-      <c r="D109" t="s">
+      <c r="G109" t="s">
         <v>217</v>
-      </c>
-      <c r="E109" t="s">
-        <v>92</v>
-      </c>
-      <c r="F109" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4249,16 +4249,16 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
+        <v>90</v>
+      </c>
+      <c r="D110" t="s">
+        <v>202</v>
+      </c>
+      <c r="F110" t="s">
         <v>219</v>
       </c>
-      <c r="D110" t="s">
+      <c r="G110" t="s">
         <v>220</v>
-      </c>
-      <c r="E110" t="s">
-        <v>92</v>
-      </c>
-      <c r="F110" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4269,15 +4269,15 @@
         <v>8</v>
       </c>
       <c r="C111" t="s">
+        <v>182</v>
+      </c>
+      <c r="D111" t="s">
         <v>202</v>
       </c>
-      <c r="D111" t="s">
+      <c r="F111" t="s">
         <v>203</v>
       </c>
-      <c r="E111" t="s">
-        <v>184</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4292,16 +4292,16 @@
         <v>223</v>
       </c>
       <c r="D112" t="s">
+        <v>202</v>
+      </c>
+      <c r="F112" t="s">
         <v>224</v>
       </c>
-      <c r="E112" t="s">
+      <c r="G112" t="s">
         <v>225</v>
       </c>
-      <c r="F112" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
         <v>226</v>
       </c>
@@ -4309,19 +4309,19 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113" t="s">
+        <v>202</v>
+      </c>
+      <c r="F113" t="s">
+        <v>115</v>
+      </c>
+      <c r="G113" t="s">
         <v>143</v>
       </c>
-      <c r="D113" t="s">
-        <v>113</v>
-      </c>
-      <c r="E113" t="s">
-        <v>114</v>
-      </c>
-      <c r="F113" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -4329,19 +4329,19 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
+        <v>124</v>
+      </c>
+      <c r="D114" t="s">
+        <v>202</v>
+      </c>
+      <c r="F114" t="s">
         <v>151</v>
       </c>
-      <c r="D114" t="s">
+      <c r="G114" t="s">
         <v>152</v>
       </c>
-      <c r="E114" t="s">
-        <v>126</v>
-      </c>
-      <c r="F114" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
         <v>228</v>
       </c>
@@ -4352,16 +4352,16 @@
         <v>182</v>
       </c>
       <c r="D115" t="s">
+        <v>202</v>
+      </c>
+      <c r="F115" t="s">
         <v>183</v>
       </c>
-      <c r="E115" t="s">
+      <c r="G115" t="s">
         <v>184</v>
       </c>
-      <c r="F115" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>229</v>
       </c>
@@ -4369,19 +4369,19 @@
         <v>8</v>
       </c>
       <c r="C116" t="s">
+        <v>223</v>
+      </c>
+      <c r="D116" t="s">
+        <v>202</v>
+      </c>
+      <c r="F116" t="s">
         <v>230</v>
       </c>
-      <c r="D116" t="s">
+      <c r="G116" t="s">
         <v>231</v>
       </c>
-      <c r="E116" t="s">
-        <v>225</v>
-      </c>
-      <c r="F116" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>232</v>
       </c>
@@ -4392,16 +4392,16 @@
         <v>223</v>
       </c>
       <c r="D117" t="s">
+        <v>202</v>
+      </c>
+      <c r="F117" t="s">
         <v>224</v>
       </c>
-      <c r="E117" t="s">
+      <c r="G117" t="s">
         <v>225</v>
       </c>
-      <c r="F117" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
+    </row>
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>233</v>
       </c>
@@ -4409,19 +4409,19 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
+        <v>163</v>
+      </c>
+      <c r="D118" t="s">
+        <v>202</v>
+      </c>
+      <c r="F118" t="s">
+        <v>164</v>
+      </c>
+      <c r="G118" t="s">
         <v>234</v>
       </c>
-      <c r="D118" t="s">
-        <v>164</v>
-      </c>
-      <c r="E118" t="s">
-        <v>165</v>
-      </c>
-      <c r="F118" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>235</v>
       </c>
@@ -4432,16 +4432,16 @@
         <v>182</v>
       </c>
       <c r="D119" t="s">
+        <v>202</v>
+      </c>
+      <c r="F119" t="s">
         <v>183</v>
       </c>
-      <c r="E119" t="s">
+      <c r="G119" t="s">
         <v>184</v>
       </c>
-      <c r="F119" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
+    </row>
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>236</v>
       </c>
@@ -4449,19 +4449,19 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
+        <v>112</v>
+      </c>
+      <c r="D120" t="s">
+        <v>237</v>
+      </c>
+      <c r="F120" t="s">
         <v>170</v>
       </c>
-      <c r="D120" t="s">
+      <c r="G120" t="s">
         <v>171</v>
       </c>
-      <c r="E120" t="s">
-        <v>114</v>
-      </c>
-      <c r="F120" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>238</v>
       </c>
@@ -4469,19 +4469,19 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
+        <v>112</v>
+      </c>
+      <c r="D121" t="s">
+        <v>237</v>
+      </c>
+      <c r="F121" t="s">
+        <v>115</v>
+      </c>
+      <c r="G121" t="s">
         <v>143</v>
       </c>
-      <c r="D121" t="s">
-        <v>113</v>
-      </c>
-      <c r="E121" t="s">
-        <v>114</v>
-      </c>
-      <c r="F121" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>239</v>
       </c>
@@ -4489,19 +4489,19 @@
         <v>8</v>
       </c>
       <c r="C122" t="s">
+        <v>112</v>
+      </c>
+      <c r="D122" t="s">
+        <v>237</v>
+      </c>
+      <c r="F122" t="s">
         <v>170</v>
       </c>
-      <c r="D122" t="s">
+      <c r="G122" t="s">
         <v>171</v>
       </c>
-      <c r="E122" t="s">
-        <v>114</v>
-      </c>
-      <c r="F122" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>240</v>
       </c>
@@ -4509,19 +4509,19 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
+        <v>112</v>
+      </c>
+      <c r="D123" t="s">
+        <v>237</v>
+      </c>
+      <c r="F123" t="s">
         <v>170</v>
       </c>
-      <c r="D123" t="s">
+      <c r="G123" t="s">
         <v>171</v>
       </c>
-      <c r="E123" t="s">
-        <v>114</v>
-      </c>
-      <c r="F123" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>241</v>
       </c>
@@ -4529,19 +4529,19 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
+        <v>163</v>
+      </c>
+      <c r="D124" t="s">
+        <v>237</v>
+      </c>
+      <c r="F124" t="s">
         <v>242</v>
       </c>
-      <c r="D124" t="s">
+      <c r="G124" t="s">
         <v>243</v>
       </c>
-      <c r="E124" t="s">
-        <v>165</v>
-      </c>
-      <c r="F124" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -4549,19 +4549,19 @@
         <v>8</v>
       </c>
       <c r="C125" t="s">
+        <v>163</v>
+      </c>
+      <c r="D125" t="s">
+        <v>237</v>
+      </c>
+      <c r="F125" t="s">
         <v>242</v>
       </c>
-      <c r="D125" t="s">
+      <c r="G125" t="s">
         <v>243</v>
       </c>
-      <c r="E125" t="s">
-        <v>165</v>
-      </c>
-      <c r="F125" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -4569,19 +4569,19 @@
         <v>8</v>
       </c>
       <c r="C126" t="s">
+        <v>163</v>
+      </c>
+      <c r="D126" t="s">
+        <v>237</v>
+      </c>
+      <c r="F126" t="s">
         <v>242</v>
       </c>
-      <c r="D126" t="s">
+      <c r="G126" t="s">
         <v>243</v>
       </c>
-      <c r="E126" t="s">
-        <v>165</v>
-      </c>
-      <c r="F126" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>246</v>
       </c>
@@ -4589,19 +4589,19 @@
         <v>8</v>
       </c>
       <c r="C127" t="s">
+        <v>163</v>
+      </c>
+      <c r="D127" t="s">
+        <v>237</v>
+      </c>
+      <c r="F127" t="s">
         <v>242</v>
       </c>
-      <c r="D127" t="s">
+      <c r="G127" t="s">
         <v>243</v>
       </c>
-      <c r="E127" t="s">
-        <v>165</v>
-      </c>
-      <c r="F127" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -4609,16 +4609,16 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
+        <v>163</v>
+      </c>
+      <c r="D128" t="s">
+        <v>237</v>
+      </c>
+      <c r="F128" t="s">
         <v>242</v>
       </c>
-      <c r="D128" t="s">
+      <c r="G128" t="s">
         <v>243</v>
-      </c>
-      <c r="E128" t="s">
-        <v>165</v>
-      </c>
-      <c r="F128" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>163</v>
+      </c>
+      <c r="D129" t="s">
+        <v>237</v>
+      </c>
+      <c r="F129" t="s">
+        <v>242</v>
+      </c>
+      <c r="G129" t="s">
         <v>249</v>
-      </c>
-      <c r="D129" t="s">
-        <v>243</v>
-      </c>
-      <c r="E129" t="s">
-        <v>165</v>
-      </c>
-      <c r="F129" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
+        <v>163</v>
+      </c>
+      <c r="D130" t="s">
+        <v>237</v>
+      </c>
+      <c r="F130" t="s">
+        <v>242</v>
+      </c>
+      <c r="G130" t="s">
         <v>251</v>
-      </c>
-      <c r="D130" t="s">
-        <v>243</v>
-      </c>
-      <c r="E130" t="s">
-        <v>165</v>
-      </c>
-      <c r="F130" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
+        <v>163</v>
+      </c>
+      <c r="D131" t="s">
+        <v>237</v>
+      </c>
+      <c r="F131" t="s">
+        <v>242</v>
+      </c>
+      <c r="G131" t="s">
         <v>253</v>
-      </c>
-      <c r="D131" t="s">
-        <v>243</v>
-      </c>
-      <c r="E131" t="s">
-        <v>165</v>
-      </c>
-      <c r="F131" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,16 +4689,16 @@
         <v>8</v>
       </c>
       <c r="C132" t="s">
+        <v>163</v>
+      </c>
+      <c r="D132" t="s">
+        <v>237</v>
+      </c>
+      <c r="F132" t="s">
         <v>255</v>
       </c>
-      <c r="D132" t="s">
+      <c r="G132" t="s">
         <v>256</v>
-      </c>
-      <c r="E132" t="s">
-        <v>165</v>
-      </c>
-      <c r="F132" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4709,16 +4709,16 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
+        <v>112</v>
+      </c>
+      <c r="D133" t="s">
+        <v>237</v>
+      </c>
+      <c r="F133" t="s">
         <v>189</v>
       </c>
-      <c r="D133" t="s">
+      <c r="G133" t="s">
         <v>190</v>
-      </c>
-      <c r="E133" t="s">
-        <v>114</v>
-      </c>
-      <c r="F133" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4729,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="C134" t="s">
+        <v>163</v>
+      </c>
+      <c r="D134" t="s">
+        <v>259</v>
+      </c>
+      <c r="F134" t="s">
         <v>175</v>
       </c>
-      <c r="D134" t="s">
+      <c r="G134" t="s">
         <v>176</v>
-      </c>
-      <c r="E134" t="s">
-        <v>165</v>
-      </c>
-      <c r="F134" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4749,16 +4749,16 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
+        <v>163</v>
+      </c>
+      <c r="D135" t="s">
+        <v>259</v>
+      </c>
+      <c r="F135" t="s">
         <v>175</v>
       </c>
-      <c r="D135" t="s">
+      <c r="G135" t="s">
         <v>176</v>
-      </c>
-      <c r="E135" t="s">
-        <v>165</v>
-      </c>
-      <c r="F135" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4769,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="C136" t="s">
+        <v>163</v>
+      </c>
+      <c r="D136" t="s">
+        <v>259</v>
+      </c>
+      <c r="F136" t="s">
         <v>175</v>
       </c>
-      <c r="D136" t="s">
+      <c r="G136" t="s">
         <v>176</v>
-      </c>
-      <c r="E136" t="s">
-        <v>165</v>
-      </c>
-      <c r="F136" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4789,16 +4789,16 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
+        <v>163</v>
+      </c>
+      <c r="D137" t="s">
+        <v>259</v>
+      </c>
+      <c r="F137" t="s">
         <v>175</v>
       </c>
-      <c r="D137" t="s">
+      <c r="G137" t="s">
         <v>176</v>
-      </c>
-      <c r="E137" t="s">
-        <v>165</v>
-      </c>
-      <c r="F137" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4809,16 +4809,16 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
+        <v>163</v>
+      </c>
+      <c r="D138" t="s">
+        <v>259</v>
+      </c>
+      <c r="F138" t="s">
         <v>175</v>
       </c>
-      <c r="D138" t="s">
+      <c r="G138" t="s">
         <v>176</v>
-      </c>
-      <c r="E138" t="s">
-        <v>165</v>
-      </c>
-      <c r="F138" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4829,16 +4829,16 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
+        <v>223</v>
+      </c>
+      <c r="D139" t="s">
+        <v>259</v>
+      </c>
+      <c r="F139" t="s">
         <v>265</v>
       </c>
-      <c r="D139" t="s">
+      <c r="G139" t="s">
         <v>266</v>
-      </c>
-      <c r="E139" t="s">
-        <v>225</v>
-      </c>
-      <c r="F139" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
+        <v>163</v>
+      </c>
+      <c r="D140" t="s">
+        <v>259</v>
+      </c>
+      <c r="F140" t="s">
         <v>175</v>
       </c>
-      <c r="D140" t="s">
+      <c r="G140" t="s">
         <v>176</v>
-      </c>
-      <c r="E140" t="s">
-        <v>165</v>
-      </c>
-      <c r="F140" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4869,13 +4869,13 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
+        <v>163</v>
+      </c>
+      <c r="D141" t="s">
         <v>269</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" t="s">
         <v>270</v>
-      </c>
-      <c r="E141" t="s">
-        <v>165</v>
       </c>
       <c r="F141" t="s">
         <v>271</v>
@@ -4892,13 +4892,13 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
+        <v>163</v>
+      </c>
+      <c r="D142" t="s">
         <v>269</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>270</v>
-      </c>
-      <c r="E142" t="s">
-        <v>165</v>
       </c>
       <c r="F142" t="s">
         <v>271</v>
@@ -4915,19 +4915,19 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
+        <v>163</v>
+      </c>
+      <c r="D143" t="s">
+        <v>269</v>
+      </c>
+      <c r="E143" t="s">
+        <v>270</v>
+      </c>
+      <c r="F143" t="s">
         <v>275</v>
       </c>
-      <c r="D143" t="s">
+      <c r="G143" t="s">
         <v>276</v>
-      </c>
-      <c r="E143" t="s">
-        <v>165</v>
-      </c>
-      <c r="F143" t="s">
-        <v>271</v>
-      </c>
-      <c r="G143" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4938,19 +4938,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
+        <v>163</v>
+      </c>
+      <c r="D144" t="s">
+        <v>269</v>
+      </c>
+      <c r="E144" t="s">
+        <v>270</v>
+      </c>
+      <c r="F144" t="s">
         <v>275</v>
       </c>
-      <c r="D144" t="s">
+      <c r="G144" t="s">
         <v>276</v>
-      </c>
-      <c r="E144" t="s">
-        <v>165</v>
-      </c>
-      <c r="F144" t="s">
-        <v>271</v>
-      </c>
-      <c r="G144" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4961,19 +4961,19 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
+        <v>163</v>
+      </c>
+      <c r="D145" t="s">
+        <v>269</v>
+      </c>
+      <c r="E145" t="s">
+        <v>270</v>
+      </c>
+      <c r="F145" t="s">
         <v>275</v>
       </c>
-      <c r="D145" t="s">
+      <c r="G145" t="s">
         <v>276</v>
-      </c>
-      <c r="E145" t="s">
-        <v>165</v>
-      </c>
-      <c r="F145" t="s">
-        <v>271</v>
-      </c>
-      <c r="G145" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4984,13 +4984,13 @@
         <v>8</v>
       </c>
       <c r="C146" t="s">
+        <v>163</v>
+      </c>
+      <c r="D146" t="s">
         <v>269</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>270</v>
-      </c>
-      <c r="E146" t="s">
-        <v>165</v>
       </c>
       <c r="F146" t="s">
         <v>271</v>
@@ -5007,19 +5007,19 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
+        <v>163</v>
+      </c>
+      <c r="D147" t="s">
         <v>269</v>
       </c>
-      <c r="D147" t="s">
-        <v>270</v>
-      </c>
       <c r="E147" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F147" t="s">
         <v>271</v>
       </c>
       <c r="G147" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5030,19 +5030,19 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
+        <v>163</v>
+      </c>
+      <c r="D148" t="s">
         <v>269</v>
       </c>
-      <c r="D148" t="s">
-        <v>270</v>
-      </c>
       <c r="E148" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F148" t="s">
         <v>271</v>
       </c>
       <c r="G148" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5053,19 +5053,19 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
+        <v>163</v>
+      </c>
+      <c r="D149" t="s">
         <v>269</v>
       </c>
-      <c r="D149" t="s">
-        <v>270</v>
-      </c>
       <c r="E149" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F149" t="s">
         <v>271</v>
       </c>
       <c r="G149" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5076,19 +5076,19 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
+        <v>163</v>
+      </c>
+      <c r="D150" t="s">
         <v>269</v>
       </c>
-      <c r="D150" t="s">
-        <v>270</v>
-      </c>
       <c r="E150" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F150" t="s">
         <v>271</v>
       </c>
       <c r="G150" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5099,19 +5099,19 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
+        <v>163</v>
+      </c>
+      <c r="D151" t="s">
         <v>269</v>
       </c>
-      <c r="D151" t="s">
-        <v>270</v>
-      </c>
       <c r="E151" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F151" t="s">
         <v>271</v>
       </c>
       <c r="G151" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5122,19 +5122,19 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
+        <v>163</v>
+      </c>
+      <c r="D152" t="s">
         <v>269</v>
       </c>
-      <c r="D152" t="s">
-        <v>270</v>
-      </c>
       <c r="E152" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F152" t="s">
         <v>271</v>
       </c>
       <c r="G152" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5145,19 +5145,19 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
+        <v>163</v>
+      </c>
+      <c r="D153" t="s">
         <v>269</v>
       </c>
-      <c r="D153" t="s">
-        <v>270</v>
-      </c>
       <c r="E153" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F153" t="s">
         <v>271</v>
       </c>
       <c r="G153" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5168,19 +5168,19 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
+        <v>163</v>
+      </c>
+      <c r="D154" t="s">
         <v>269</v>
       </c>
-      <c r="D154" t="s">
-        <v>270</v>
-      </c>
       <c r="E154" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F154" t="s">
         <v>271</v>
       </c>
       <c r="G154" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5191,19 +5191,19 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
+        <v>163</v>
+      </c>
+      <c r="D155" t="s">
         <v>269</v>
       </c>
-      <c r="D155" t="s">
-        <v>270</v>
-      </c>
       <c r="E155" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="F155" t="s">
         <v>271</v>
       </c>
       <c r="G155" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5214,19 +5214,19 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
+        <v>163</v>
+      </c>
+      <c r="D156" t="s">
         <v>269</v>
       </c>
-      <c r="D156" t="s">
-        <v>270</v>
-      </c>
       <c r="E156" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="F156" t="s">
         <v>271</v>
       </c>
       <c r="G156" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>293</v>
+        <v>163</v>
       </c>
       <c r="D157" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E157" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="F157" t="s">
         <v>271</v>
       </c>
       <c r="G157" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5260,19 +5260,19 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
+        <v>163</v>
+      </c>
+      <c r="D158" t="s">
         <v>269</v>
       </c>
-      <c r="D158" t="s">
-        <v>270</v>
-      </c>
       <c r="E158" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="F158" t="s">
         <v>271</v>
       </c>
       <c r="G158" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5283,19 +5283,19 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
+        <v>163</v>
+      </c>
+      <c r="D159" t="s">
         <v>269</v>
       </c>
-      <c r="D159" t="s">
-        <v>270</v>
-      </c>
       <c r="E159" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="F159" t="s">
         <v>271</v>
       </c>
       <c r="G159" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5306,19 +5306,19 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
+        <v>163</v>
+      </c>
+      <c r="D160" t="s">
         <v>269</v>
       </c>
-      <c r="D160" t="s">
-        <v>270</v>
-      </c>
       <c r="E160" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="F160" t="s">
         <v>271</v>
       </c>
       <c r="G160" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5329,19 +5329,19 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
+        <v>163</v>
+      </c>
+      <c r="D161" t="s">
         <v>269</v>
       </c>
-      <c r="D161" t="s">
-        <v>270</v>
-      </c>
       <c r="E161" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="F161" t="s">
         <v>271</v>
       </c>
       <c r="G161" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5352,19 +5352,19 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
+        <v>163</v>
+      </c>
+      <c r="D162" t="s">
         <v>269</v>
       </c>
-      <c r="D162" t="s">
-        <v>270</v>
-      </c>
       <c r="E162" t="s">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F162" t="s">
         <v>271</v>
       </c>
       <c r="G162" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,13 +5375,13 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
+        <v>163</v>
+      </c>
+      <c r="D163" t="s">
+        <v>269</v>
+      </c>
+      <c r="E163" t="s">
         <v>301</v>
-      </c>
-      <c r="D163" t="s">
-        <v>270</v>
-      </c>
-      <c r="E163" t="s">
-        <v>165</v>
       </c>
       <c r="F163" t="s">
         <v>271</v>
@@ -5398,19 +5398,19 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
+        <v>163</v>
+      </c>
+      <c r="D164" t="s">
         <v>269</v>
       </c>
-      <c r="D164" t="s">
-        <v>270</v>
-      </c>
       <c r="E164" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F164" t="s">
         <v>271</v>
       </c>
       <c r="G164" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5421,19 +5421,19 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
+        <v>163</v>
+      </c>
+      <c r="D165" t="s">
         <v>269</v>
       </c>
-      <c r="D165" t="s">
-        <v>270</v>
-      </c>
       <c r="E165" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F165" t="s">
         <v>271</v>
       </c>
       <c r="G165" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5444,19 +5444,19 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
+        <v>163</v>
+      </c>
+      <c r="D166" t="s">
         <v>269</v>
       </c>
-      <c r="D166" t="s">
-        <v>270</v>
-      </c>
       <c r="E166" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F166" t="s">
         <v>271</v>
       </c>
       <c r="G166" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5467,19 +5467,19 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
+        <v>163</v>
+      </c>
+      <c r="D167" t="s">
         <v>269</v>
       </c>
-      <c r="D167" t="s">
-        <v>270</v>
-      </c>
       <c r="E167" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F167" t="s">
         <v>271</v>
       </c>
       <c r="G167" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>309</v>
+        <v>163</v>
       </c>
       <c r="D168" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E168" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F168" t="s">
         <v>271</v>
       </c>
       <c r="G168" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>309</v>
+        <v>163</v>
       </c>
       <c r="D169" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E169" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F169" t="s">
         <v>271</v>
       </c>
       <c r="G169" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5536,19 +5536,19 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
+        <v>163</v>
+      </c>
+      <c r="D170" t="s">
         <v>269</v>
       </c>
-      <c r="D170" t="s">
-        <v>270</v>
-      </c>
       <c r="E170" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="F170" t="s">
         <v>271</v>
       </c>
       <c r="G170" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5562,13 +5562,13 @@
         <v>163</v>
       </c>
       <c r="D171" t="s">
+        <v>313</v>
+      </c>
+      <c r="F171" t="s">
         <v>164</v>
       </c>
-      <c r="E171" t="s">
+      <c r="G171" t="s">
         <v>165</v>
-      </c>
-      <c r="F171" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5579,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
+        <v>112</v>
+      </c>
+      <c r="D172" t="s">
+        <v>313</v>
+      </c>
+      <c r="F172" t="s">
         <v>118</v>
       </c>
-      <c r="D172" t="s">
+      <c r="G172" t="s">
         <v>119</v>
-      </c>
-      <c r="E172" t="s">
-        <v>114</v>
-      </c>
-      <c r="F172" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5602,13 +5602,13 @@
         <v>163</v>
       </c>
       <c r="D173" t="s">
+        <v>313</v>
+      </c>
+      <c r="F173" t="s">
         <v>164</v>
       </c>
-      <c r="E173" t="s">
+      <c r="G173" t="s">
         <v>165</v>
-      </c>
-      <c r="F173" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5622,13 +5622,13 @@
         <v>163</v>
       </c>
       <c r="D174" t="s">
+        <v>313</v>
+      </c>
+      <c r="F174" t="s">
         <v>164</v>
       </c>
-      <c r="E174" t="s">
+      <c r="G174" t="s">
         <v>165</v>
-      </c>
-      <c r="F174" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5642,13 +5642,13 @@
         <v>163</v>
       </c>
       <c r="D175" t="s">
+        <v>313</v>
+      </c>
+      <c r="F175" t="s">
         <v>164</v>
       </c>
-      <c r="E175" t="s">
+      <c r="G175" t="s">
         <v>165</v>
-      </c>
-      <c r="F175" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5662,13 +5662,13 @@
         <v>163</v>
       </c>
       <c r="D176" t="s">
+        <v>313</v>
+      </c>
+      <c r="F176" t="s">
         <v>164</v>
       </c>
-      <c r="E176" t="s">
+      <c r="G176" t="s">
         <v>165</v>
-      </c>
-      <c r="F176" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5682,13 +5682,13 @@
         <v>163</v>
       </c>
       <c r="D177" t="s">
+        <v>320</v>
+      </c>
+      <c r="F177" t="s">
         <v>164</v>
       </c>
-      <c r="E177" t="s">
+      <c r="G177" t="s">
         <v>165</v>
-      </c>
-      <c r="F177" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5702,13 +5702,13 @@
         <v>163</v>
       </c>
       <c r="D178" t="s">
+        <v>320</v>
+      </c>
+      <c r="F178" t="s">
         <v>164</v>
       </c>
-      <c r="E178" t="s">
+      <c r="G178" t="s">
         <v>165</v>
-      </c>
-      <c r="F178" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5722,13 +5722,13 @@
         <v>163</v>
       </c>
       <c r="D179" t="s">
+        <v>320</v>
+      </c>
+      <c r="F179" t="s">
         <v>164</v>
       </c>
-      <c r="E179" t="s">
+      <c r="G179" t="s">
         <v>165</v>
-      </c>
-      <c r="F179" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5742,13 +5742,13 @@
         <v>163</v>
       </c>
       <c r="D180" t="s">
+        <v>320</v>
+      </c>
+      <c r="F180" t="s">
         <v>164</v>
       </c>
-      <c r="E180" t="s">
+      <c r="G180" t="s">
         <v>165</v>
-      </c>
-      <c r="F180" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5759,13 +5759,13 @@
         <v>8</v>
       </c>
       <c r="C181" t="s">
+        <v>163</v>
+      </c>
+      <c r="D181" t="s">
         <v>325</v>
       </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
         <v>326</v>
-      </c>
-      <c r="E181" t="s">
-        <v>165</v>
       </c>
       <c r="F181" t="s">
         <v>327</v>
@@ -5782,13 +5782,13 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
+        <v>163</v>
+      </c>
+      <c r="D182" t="s">
         <v>325</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>326</v>
-      </c>
-      <c r="E182" t="s">
-        <v>165</v>
       </c>
       <c r="F182" t="s">
         <v>327</v>
@@ -5805,13 +5805,13 @@
         <v>8</v>
       </c>
       <c r="C183" t="s">
+        <v>163</v>
+      </c>
+      <c r="D183" t="s">
         <v>325</v>
       </c>
-      <c r="D183" t="s">
+      <c r="E183" t="s">
         <v>326</v>
-      </c>
-      <c r="E183" t="s">
-        <v>165</v>
       </c>
       <c r="F183" t="s">
         <v>327</v>
@@ -5828,13 +5828,13 @@
         <v>8</v>
       </c>
       <c r="C184" t="s">
+        <v>163</v>
+      </c>
+      <c r="D184" t="s">
         <v>325</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
         <v>326</v>
-      </c>
-      <c r="E184" t="s">
-        <v>165</v>
       </c>
       <c r="F184" t="s">
         <v>327</v>
@@ -5851,13 +5851,13 @@
         <v>8</v>
       </c>
       <c r="C185" t="s">
+        <v>163</v>
+      </c>
+      <c r="D185" t="s">
         <v>325</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
         <v>326</v>
-      </c>
-      <c r="E185" t="s">
-        <v>165</v>
       </c>
       <c r="F185" t="s">
         <v>327</v>
@@ -5874,13 +5874,13 @@
         <v>8</v>
       </c>
       <c r="C186" t="s">
+        <v>163</v>
+      </c>
+      <c r="D186" t="s">
         <v>325</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
         <v>326</v>
-      </c>
-      <c r="E186" t="s">
-        <v>165</v>
       </c>
       <c r="F186" t="s">
         <v>327</v>
@@ -5897,13 +5897,13 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
+        <v>163</v>
+      </c>
+      <c r="D187" t="s">
         <v>325</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
         <v>326</v>
-      </c>
-      <c r="E187" t="s">
-        <v>165</v>
       </c>
       <c r="F187" t="s">
         <v>327</v>
@@ -5920,13 +5920,13 @@
         <v>8</v>
       </c>
       <c r="C188" t="s">
+        <v>163</v>
+      </c>
+      <c r="D188" t="s">
         <v>325</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
         <v>326</v>
-      </c>
-      <c r="E188" t="s">
-        <v>165</v>
       </c>
       <c r="F188" t="s">
         <v>327</v>
@@ -5943,13 +5943,13 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
+        <v>163</v>
+      </c>
+      <c r="D189" t="s">
         <v>325</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
         <v>326</v>
-      </c>
-      <c r="E189" t="s">
-        <v>165</v>
       </c>
       <c r="F189" t="s">
         <v>327</v>
@@ -5966,13 +5966,13 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
+        <v>163</v>
+      </c>
+      <c r="D190" t="s">
         <v>325</v>
       </c>
-      <c r="D190" t="s">
+      <c r="E190" t="s">
         <v>326</v>
-      </c>
-      <c r="E190" t="s">
-        <v>165</v>
       </c>
       <c r="F190" t="s">
         <v>327</v>
@@ -5989,13 +5989,13 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
+        <v>163</v>
+      </c>
+      <c r="D191" t="s">
         <v>325</v>
       </c>
-      <c r="D191" t="s">
+      <c r="E191" t="s">
         <v>326</v>
-      </c>
-      <c r="E191" t="s">
-        <v>165</v>
       </c>
       <c r="F191" t="s">
         <v>327</v>
@@ -6012,13 +6012,13 @@
         <v>8</v>
       </c>
       <c r="C192" t="s">
+        <v>163</v>
+      </c>
+      <c r="D192" t="s">
         <v>325</v>
       </c>
-      <c r="D192" t="s">
+      <c r="E192" t="s">
         <v>326</v>
-      </c>
-      <c r="E192" t="s">
-        <v>165</v>
       </c>
       <c r="F192" t="s">
         <v>327</v>
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
+        <v>163</v>
+      </c>
+      <c r="D193" t="s">
+        <v>325</v>
+      </c>
+      <c r="E193" t="s">
+        <v>326</v>
+      </c>
+      <c r="F193" t="s">
+        <v>275</v>
+      </c>
+      <c r="G193" t="s">
         <v>341</v>
-      </c>
-      <c r="D193" t="s">
-        <v>276</v>
-      </c>
-      <c r="E193" t="s">
-        <v>165</v>
-      </c>
-      <c r="F193" t="s">
-        <v>327</v>
-      </c>
-      <c r="G193" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6058,13 +6058,13 @@
         <v>8</v>
       </c>
       <c r="C194" t="s">
+        <v>163</v>
+      </c>
+      <c r="D194" t="s">
         <v>325</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
         <v>326</v>
-      </c>
-      <c r="E194" t="s">
-        <v>165</v>
       </c>
       <c r="F194" t="s">
         <v>327</v>
@@ -6081,13 +6081,13 @@
         <v>8</v>
       </c>
       <c r="C195" t="s">
+        <v>163</v>
+      </c>
+      <c r="D195" t="s">
         <v>325</v>
       </c>
-      <c r="D195" t="s">
+      <c r="E195" t="s">
         <v>326</v>
-      </c>
-      <c r="E195" t="s">
-        <v>165</v>
       </c>
       <c r="F195" t="s">
         <v>327</v>
@@ -6104,13 +6104,13 @@
         <v>8</v>
       </c>
       <c r="C196" t="s">
+        <v>163</v>
+      </c>
+      <c r="D196" t="s">
         <v>325</v>
       </c>
-      <c r="D196" t="s">
+      <c r="E196" t="s">
         <v>326</v>
-      </c>
-      <c r="E196" t="s">
-        <v>165</v>
       </c>
       <c r="F196" t="s">
         <v>327</v>
@@ -6127,13 +6127,13 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
+        <v>163</v>
+      </c>
+      <c r="D197" t="s">
         <v>325</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
         <v>326</v>
-      </c>
-      <c r="E197" t="s">
-        <v>165</v>
       </c>
       <c r="F197" t="s">
         <v>327</v>
@@ -6150,13 +6150,13 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
+        <v>163</v>
+      </c>
+      <c r="D198" t="s">
         <v>325</v>
       </c>
-      <c r="D198" t="s">
+      <c r="E198" t="s">
         <v>326</v>
-      </c>
-      <c r="E198" t="s">
-        <v>165</v>
       </c>
       <c r="F198" t="s">
         <v>327</v>
@@ -6173,13 +6173,13 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
+        <v>163</v>
+      </c>
+      <c r="D199" t="s">
+        <v>325</v>
+      </c>
+      <c r="E199" t="s">
         <v>348</v>
-      </c>
-      <c r="D199" t="s">
-        <v>326</v>
-      </c>
-      <c r="E199" t="s">
-        <v>165</v>
       </c>
       <c r="F199" t="s">
         <v>327</v>
@@ -6196,13 +6196,13 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
+        <v>163</v>
+      </c>
+      <c r="D200" t="s">
+        <v>325</v>
+      </c>
+      <c r="E200" t="s">
         <v>348</v>
-      </c>
-      <c r="D200" t="s">
-        <v>326</v>
-      </c>
-      <c r="E200" t="s">
-        <v>165</v>
       </c>
       <c r="F200" t="s">
         <v>327</v>
@@ -6219,13 +6219,13 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
+        <v>163</v>
+      </c>
+      <c r="D201" t="s">
+        <v>325</v>
+      </c>
+      <c r="E201" t="s">
         <v>348</v>
-      </c>
-      <c r="D201" t="s">
-        <v>326</v>
-      </c>
-      <c r="E201" t="s">
-        <v>165</v>
       </c>
       <c r="F201" t="s">
         <v>327</v>
@@ -6242,13 +6242,13 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
+        <v>163</v>
+      </c>
+      <c r="D202" t="s">
+        <v>325</v>
+      </c>
+      <c r="E202" t="s">
         <v>348</v>
-      </c>
-      <c r="D202" t="s">
-        <v>326</v>
-      </c>
-      <c r="E202" t="s">
-        <v>165</v>
       </c>
       <c r="F202" t="s">
         <v>327</v>
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>163</v>
+      </c>
+      <c r="D203" t="s">
+        <v>325</v>
+      </c>
+      <c r="E203" t="s">
+        <v>348</v>
+      </c>
+      <c r="F203" t="s">
+        <v>275</v>
+      </c>
+      <c r="G203" t="s">
         <v>341</v>
-      </c>
-      <c r="D203" t="s">
-        <v>276</v>
-      </c>
-      <c r="E203" t="s">
-        <v>165</v>
-      </c>
-      <c r="F203" t="s">
-        <v>327</v>
-      </c>
-      <c r="G203" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,13 +6288,13 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
+        <v>163</v>
+      </c>
+      <c r="D204" t="s">
+        <v>325</v>
+      </c>
+      <c r="E204" t="s">
         <v>348</v>
-      </c>
-      <c r="D204" t="s">
-        <v>326</v>
-      </c>
-      <c r="E204" t="s">
-        <v>165</v>
       </c>
       <c r="F204" t="s">
         <v>327</v>
@@ -6311,13 +6311,13 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
+        <v>163</v>
+      </c>
+      <c r="D205" t="s">
+        <v>325</v>
+      </c>
+      <c r="E205" t="s">
         <v>356</v>
-      </c>
-      <c r="D205" t="s">
-        <v>326</v>
-      </c>
-      <c r="E205" t="s">
-        <v>165</v>
       </c>
       <c r="F205" t="s">
         <v>327</v>
@@ -6334,13 +6334,13 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
+        <v>163</v>
+      </c>
+      <c r="D206" t="s">
+        <v>325</v>
+      </c>
+      <c r="E206" t="s">
         <v>356</v>
-      </c>
-      <c r="D206" t="s">
-        <v>326</v>
-      </c>
-      <c r="E206" t="s">
-        <v>165</v>
       </c>
       <c r="F206" t="s">
         <v>327</v>
@@ -6357,13 +6357,13 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
+        <v>163</v>
+      </c>
+      <c r="D207" t="s">
+        <v>325</v>
+      </c>
+      <c r="E207" t="s">
         <v>356</v>
-      </c>
-      <c r="D207" t="s">
-        <v>326</v>
-      </c>
-      <c r="E207" t="s">
-        <v>165</v>
       </c>
       <c r="F207" t="s">
         <v>327</v>
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>163</v>
+      </c>
+      <c r="D208" t="s">
+        <v>325</v>
+      </c>
+      <c r="E208" t="s">
+        <v>356</v>
+      </c>
+      <c r="F208" t="s">
+        <v>275</v>
+      </c>
+      <c r="G208" t="s">
         <v>341</v>
-      </c>
-      <c r="D208" t="s">
-        <v>276</v>
-      </c>
-      <c r="E208" t="s">
-        <v>165</v>
-      </c>
-      <c r="F208" t="s">
-        <v>327</v>
-      </c>
-      <c r="G208" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,13 +6403,13 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
+        <v>163</v>
+      </c>
+      <c r="D209" t="s">
+        <v>325</v>
+      </c>
+      <c r="E209" t="s">
         <v>356</v>
-      </c>
-      <c r="D209" t="s">
-        <v>326</v>
-      </c>
-      <c r="E209" t="s">
-        <v>165</v>
       </c>
       <c r="F209" t="s">
         <v>327</v>
@@ -6426,13 +6426,13 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
+        <v>163</v>
+      </c>
+      <c r="D210" t="s">
         <v>363</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
         <v>364</v>
-      </c>
-      <c r="E210" t="s">
-        <v>165</v>
       </c>
       <c r="F210" t="s">
         <v>365</v>
@@ -6449,13 +6449,13 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
+        <v>163</v>
+      </c>
+      <c r="D211" t="s">
         <v>363</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
         <v>364</v>
-      </c>
-      <c r="E211" t="s">
-        <v>165</v>
       </c>
       <c r="F211" t="s">
         <v>365</v>
@@ -6472,13 +6472,13 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
+        <v>163</v>
+      </c>
+      <c r="D212" t="s">
         <v>363</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
         <v>364</v>
-      </c>
-      <c r="E212" t="s">
-        <v>165</v>
       </c>
       <c r="F212" t="s">
         <v>365</v>
@@ -6495,13 +6495,13 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
+        <v>163</v>
+      </c>
+      <c r="D213" t="s">
         <v>363</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
         <v>364</v>
-      </c>
-      <c r="E213" t="s">
-        <v>165</v>
       </c>
       <c r="F213" t="s">
         <v>365</v>
@@ -6518,13 +6518,13 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
+        <v>163</v>
+      </c>
+      <c r="D214" t="s">
         <v>363</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
         <v>364</v>
-      </c>
-      <c r="E214" t="s">
-        <v>165</v>
       </c>
       <c r="F214" t="s">
         <v>365</v>
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>348</v>
+        <v>163</v>
       </c>
       <c r="D215" t="s">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="E215" t="s">
-        <v>165</v>
+        <v>364</v>
       </c>
       <c r="F215" t="s">
-        <v>365</v>
+        <v>327</v>
       </c>
       <c r="G215" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6564,13 +6564,13 @@
         <v>8</v>
       </c>
       <c r="C216" t="s">
+        <v>163</v>
+      </c>
+      <c r="D216" t="s">
         <v>363</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
         <v>364</v>
-      </c>
-      <c r="E216" t="s">
-        <v>165</v>
       </c>
       <c r="F216" t="s">
         <v>365</v>
@@ -6587,13 +6587,13 @@
         <v>8</v>
       </c>
       <c r="C217" t="s">
+        <v>163</v>
+      </c>
+      <c r="D217" t="s">
         <v>363</v>
       </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
         <v>364</v>
-      </c>
-      <c r="E217" t="s">
-        <v>165</v>
       </c>
       <c r="F217" t="s">
         <v>365</v>
@@ -6610,13 +6610,13 @@
         <v>8</v>
       </c>
       <c r="C218" t="s">
+        <v>163</v>
+      </c>
+      <c r="D218" t="s">
         <v>363</v>
       </c>
-      <c r="D218" t="s">
+      <c r="E218" t="s">
         <v>364</v>
-      </c>
-      <c r="E218" t="s">
-        <v>165</v>
       </c>
       <c r="F218" t="s">
         <v>365</v>
@@ -6633,13 +6633,13 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
+        <v>163</v>
+      </c>
+      <c r="D219" t="s">
         <v>363</v>
       </c>
-      <c r="D219" t="s">
+      <c r="E219" t="s">
         <v>364</v>
-      </c>
-      <c r="E219" t="s">
-        <v>165</v>
       </c>
       <c r="F219" t="s">
         <v>365</v>
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
+        <v>163</v>
+      </c>
+      <c r="D220" t="s">
+        <v>363</v>
+      </c>
+      <c r="E220" t="s">
+        <v>364</v>
+      </c>
+      <c r="F220" t="s">
+        <v>271</v>
+      </c>
+      <c r="G220" t="s">
         <v>309</v>
-      </c>
-      <c r="D220" t="s">
-        <v>270</v>
-      </c>
-      <c r="E220" t="s">
-        <v>165</v>
-      </c>
-      <c r="F220" t="s">
-        <v>365</v>
-      </c>
-      <c r="G220" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6679,13 +6679,13 @@
         <v>8</v>
       </c>
       <c r="C221" t="s">
+        <v>163</v>
+      </c>
+      <c r="D221" t="s">
         <v>363</v>
       </c>
-      <c r="D221" t="s">
+      <c r="E221" t="s">
         <v>364</v>
-      </c>
-      <c r="E221" t="s">
-        <v>165</v>
       </c>
       <c r="F221" t="s">
         <v>365</v>
@@ -6702,13 +6702,13 @@
         <v>8</v>
       </c>
       <c r="C222" t="s">
+        <v>163</v>
+      </c>
+      <c r="D222" t="s">
         <v>363</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
         <v>364</v>
-      </c>
-      <c r="E222" t="s">
-        <v>165</v>
       </c>
       <c r="F222" t="s">
         <v>365</v>
@@ -6725,13 +6725,13 @@
         <v>8</v>
       </c>
       <c r="C223" t="s">
+        <v>163</v>
+      </c>
+      <c r="D223" t="s">
         <v>363</v>
       </c>
-      <c r="D223" t="s">
+      <c r="E223" t="s">
         <v>364</v>
-      </c>
-      <c r="E223" t="s">
-        <v>165</v>
       </c>
       <c r="F223" t="s">
         <v>365</v>
@@ -6748,13 +6748,13 @@
         <v>8</v>
       </c>
       <c r="C224" t="s">
+        <v>163</v>
+      </c>
+      <c r="D224" t="s">
         <v>363</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
         <v>364</v>
-      </c>
-      <c r="E224" t="s">
-        <v>165</v>
       </c>
       <c r="F224" t="s">
         <v>365</v>
@@ -6771,13 +6771,13 @@
         <v>8</v>
       </c>
       <c r="C225" t="s">
+        <v>163</v>
+      </c>
+      <c r="D225" t="s">
         <v>363</v>
       </c>
-      <c r="D225" t="s">
+      <c r="E225" t="s">
         <v>364</v>
-      </c>
-      <c r="E225" t="s">
-        <v>165</v>
       </c>
       <c r="F225" t="s">
         <v>365</v>
@@ -6794,19 +6794,19 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
+        <v>163</v>
+      </c>
+      <c r="D226" t="s">
+        <v>363</v>
+      </c>
+      <c r="E226" t="s">
+        <v>364</v>
+      </c>
+      <c r="F226" t="s">
         <v>275</v>
       </c>
-      <c r="D226" t="s">
+      <c r="G226" t="s">
         <v>276</v>
-      </c>
-      <c r="E226" t="s">
-        <v>165</v>
-      </c>
-      <c r="F226" t="s">
-        <v>365</v>
-      </c>
-      <c r="G226" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6817,13 +6817,13 @@
         <v>8</v>
       </c>
       <c r="C227" t="s">
+        <v>163</v>
+      </c>
+      <c r="D227" t="s">
         <v>363</v>
       </c>
-      <c r="D227" t="s">
+      <c r="E227" t="s">
         <v>364</v>
-      </c>
-      <c r="E227" t="s">
-        <v>165</v>
       </c>
       <c r="F227" t="s">
         <v>365</v>
@@ -6843,16 +6843,16 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
+        <v>363</v>
+      </c>
+      <c r="E228" t="s">
+        <v>364</v>
+      </c>
+      <c r="F228" t="s">
         <v>164</v>
       </c>
-      <c r="E228" t="s">
+      <c r="G228" t="s">
         <v>165</v>
-      </c>
-      <c r="F228" t="s">
-        <v>365</v>
-      </c>
-      <c r="G228" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,13 +6863,13 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
+        <v>163</v>
+      </c>
+      <c r="D229" t="s">
+        <v>363</v>
+      </c>
+      <c r="E229" t="s">
         <v>386</v>
-      </c>
-      <c r="D229" t="s">
-        <v>364</v>
-      </c>
-      <c r="E229" t="s">
-        <v>165</v>
       </c>
       <c r="F229" t="s">
         <v>365</v>
@@ -6886,13 +6886,13 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
+        <v>163</v>
+      </c>
+      <c r="D230" t="s">
+        <v>363</v>
+      </c>
+      <c r="E230" t="s">
         <v>386</v>
-      </c>
-      <c r="D230" t="s">
-        <v>364</v>
-      </c>
-      <c r="E230" t="s">
-        <v>165</v>
       </c>
       <c r="F230" t="s">
         <v>365</v>
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
+        <v>163</v>
+      </c>
+      <c r="D231" t="s">
+        <v>363</v>
+      </c>
+      <c r="E231" t="s">
+        <v>386</v>
+      </c>
+      <c r="F231" t="s">
+        <v>271</v>
+      </c>
+      <c r="G231" t="s">
         <v>293</v>
-      </c>
-      <c r="D231" t="s">
-        <v>270</v>
-      </c>
-      <c r="E231" t="s">
-        <v>165</v>
-      </c>
-      <c r="F231" t="s">
-        <v>365</v>
-      </c>
-      <c r="G231" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
+        <v>163</v>
+      </c>
+      <c r="D232" t="s">
+        <v>363</v>
+      </c>
+      <c r="E232" t="s">
+        <v>386</v>
+      </c>
+      <c r="F232" t="s">
+        <v>271</v>
+      </c>
+      <c r="G232" t="s">
         <v>309</v>
-      </c>
-      <c r="D232" t="s">
-        <v>270</v>
-      </c>
-      <c r="E232" t="s">
-        <v>165</v>
-      </c>
-      <c r="F232" t="s">
-        <v>365</v>
-      </c>
-      <c r="G232" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,13 +6955,13 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
+        <v>163</v>
+      </c>
+      <c r="D233" t="s">
+        <v>363</v>
+      </c>
+      <c r="E233" t="s">
         <v>386</v>
-      </c>
-      <c r="D233" t="s">
-        <v>364</v>
-      </c>
-      <c r="E233" t="s">
-        <v>165</v>
       </c>
       <c r="F233" t="s">
         <v>365</v>
@@ -6978,13 +6978,13 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
+        <v>163</v>
+      </c>
+      <c r="D234" t="s">
+        <v>363</v>
+      </c>
+      <c r="E234" t="s">
         <v>386</v>
-      </c>
-      <c r="D234" t="s">
-        <v>364</v>
-      </c>
-      <c r="E234" t="s">
-        <v>165</v>
       </c>
       <c r="F234" t="s">
         <v>365</v>
@@ -7001,13 +7001,13 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
+        <v>163</v>
+      </c>
+      <c r="D235" t="s">
+        <v>363</v>
+      </c>
+      <c r="E235" t="s">
         <v>386</v>
-      </c>
-      <c r="D235" t="s">
-        <v>364</v>
-      </c>
-      <c r="E235" t="s">
-        <v>165</v>
       </c>
       <c r="F235" t="s">
         <v>365</v>
@@ -7024,13 +7024,13 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
+        <v>163</v>
+      </c>
+      <c r="D236" t="s">
+        <v>363</v>
+      </c>
+      <c r="E236" t="s">
         <v>386</v>
-      </c>
-      <c r="D236" t="s">
-        <v>364</v>
-      </c>
-      <c r="E236" t="s">
-        <v>165</v>
       </c>
       <c r="F236" t="s">
         <v>365</v>
@@ -7047,13 +7047,13 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
+        <v>163</v>
+      </c>
+      <c r="D237" t="s">
+        <v>363</v>
+      </c>
+      <c r="E237" t="s">
         <v>386</v>
-      </c>
-      <c r="D237" t="s">
-        <v>364</v>
-      </c>
-      <c r="E237" t="s">
-        <v>165</v>
       </c>
       <c r="F237" t="s">
         <v>365</v>
@@ -7070,13 +7070,13 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
+        <v>163</v>
+      </c>
+      <c r="D238" t="s">
+        <v>363</v>
+      </c>
+      <c r="E238" t="s">
         <v>386</v>
-      </c>
-      <c r="D238" t="s">
-        <v>364</v>
-      </c>
-      <c r="E238" t="s">
-        <v>165</v>
       </c>
       <c r="F238" t="s">
         <v>365</v>
@@ -7093,13 +7093,13 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
+        <v>163</v>
+      </c>
+      <c r="D239" t="s">
+        <v>363</v>
+      </c>
+      <c r="E239" t="s">
         <v>398</v>
-      </c>
-      <c r="D239" t="s">
-        <v>364</v>
-      </c>
-      <c r="E239" t="s">
-        <v>165</v>
       </c>
       <c r="F239" t="s">
         <v>365</v>
@@ -7119,16 +7119,16 @@
         <v>163</v>
       </c>
       <c r="D240" t="s">
+        <v>401</v>
+      </c>
+      <c r="E240" t="s">
+        <v>402</v>
+      </c>
+      <c r="F240" t="s">
         <v>164</v>
       </c>
-      <c r="E240" t="s">
+      <c r="G240" t="s">
         <v>165</v>
-      </c>
-      <c r="F240" t="s">
-        <v>401</v>
-      </c>
-      <c r="G240" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7142,16 +7142,16 @@
         <v>163</v>
       </c>
       <c r="D241" t="s">
+        <v>401</v>
+      </c>
+      <c r="E241" t="s">
+        <v>402</v>
+      </c>
+      <c r="F241" t="s">
         <v>164</v>
       </c>
-      <c r="E241" t="s">
+      <c r="G241" t="s">
         <v>165</v>
-      </c>
-      <c r="F241" t="s">
-        <v>401</v>
-      </c>
-      <c r="G241" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7165,16 +7165,16 @@
         <v>163</v>
       </c>
       <c r="D242" t="s">
+        <v>401</v>
+      </c>
+      <c r="E242" t="s">
+        <v>402</v>
+      </c>
+      <c r="F242" t="s">
         <v>164</v>
       </c>
-      <c r="E242" t="s">
+      <c r="G242" t="s">
         <v>165</v>
-      </c>
-      <c r="F242" t="s">
-        <v>401</v>
-      </c>
-      <c r="G242" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7188,16 +7188,16 @@
         <v>163</v>
       </c>
       <c r="D243" t="s">
+        <v>401</v>
+      </c>
+      <c r="E243" t="s">
+        <v>402</v>
+      </c>
+      <c r="F243" t="s">
         <v>164</v>
       </c>
-      <c r="E243" t="s">
+      <c r="G243" t="s">
         <v>165</v>
-      </c>
-      <c r="F243" t="s">
-        <v>401</v>
-      </c>
-      <c r="G243" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7211,16 +7211,16 @@
         <v>163</v>
       </c>
       <c r="D244" t="s">
+        <v>401</v>
+      </c>
+      <c r="E244" t="s">
+        <v>402</v>
+      </c>
+      <c r="F244" t="s">
         <v>164</v>
       </c>
-      <c r="E244" t="s">
+      <c r="G244" t="s">
         <v>165</v>
-      </c>
-      <c r="F244" t="s">
-        <v>401</v>
-      </c>
-      <c r="G244" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7234,16 +7234,16 @@
         <v>163</v>
       </c>
       <c r="D245" t="s">
+        <v>401</v>
+      </c>
+      <c r="E245" t="s">
+        <v>402</v>
+      </c>
+      <c r="F245" t="s">
         <v>164</v>
       </c>
-      <c r="E245" t="s">
+      <c r="G245" t="s">
         <v>165</v>
-      </c>
-      <c r="F245" t="s">
-        <v>401</v>
-      </c>
-      <c r="G245" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,16 +7254,16 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>163</v>
+      </c>
+      <c r="D246" t="s">
+        <v>401</v>
+      </c>
+      <c r="E246" t="s">
         <v>409</v>
       </c>
-      <c r="D246" t="s">
-        <v>256</v>
-      </c>
-      <c r="E246" t="s">
-        <v>165</v>
-      </c>
       <c r="F246" t="s">
-        <v>401</v>
+        <v>255</v>
       </c>
       <c r="G246" t="s">
         <v>410</v>
@@ -7280,13 +7280,13 @@
         <v>95</v>
       </c>
       <c r="D247" t="s">
+        <v>412</v>
+      </c>
+      <c r="F247" t="s">
         <v>96</v>
       </c>
-      <c r="E247" t="s">
+      <c r="G247" t="s">
         <v>97</v>
-      </c>
-      <c r="F247" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7300,13 +7300,13 @@
         <v>95</v>
       </c>
       <c r="D248" t="s">
+        <v>412</v>
+      </c>
+      <c r="F248" t="s">
         <v>96</v>
       </c>
-      <c r="E248" t="s">
+      <c r="G248" t="s">
         <v>97</v>
-      </c>
-      <c r="F248" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7317,16 +7317,16 @@
         <v>8</v>
       </c>
       <c r="C249" t="s">
+        <v>95</v>
+      </c>
+      <c r="D249" t="s">
+        <v>412</v>
+      </c>
+      <c r="F249" t="s">
         <v>415</v>
       </c>
-      <c r="D249" t="s">
+      <c r="G249" t="s">
         <v>416</v>
-      </c>
-      <c r="E249" t="s">
-        <v>97</v>
-      </c>
-      <c r="F249" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7340,13 +7340,13 @@
         <v>95</v>
       </c>
       <c r="D250" t="s">
+        <v>412</v>
+      </c>
+      <c r="F250" t="s">
         <v>96</v>
       </c>
-      <c r="E250" t="s">
+      <c r="G250" t="s">
         <v>97</v>
-      </c>
-      <c r="F250" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7360,13 +7360,13 @@
         <v>95</v>
       </c>
       <c r="D251" t="s">
+        <v>412</v>
+      </c>
+      <c r="F251" t="s">
         <v>96</v>
       </c>
-      <c r="E251" t="s">
+      <c r="G251" t="s">
         <v>97</v>
-      </c>
-      <c r="F251" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7380,13 +7380,13 @@
         <v>95</v>
       </c>
       <c r="D252" t="s">
+        <v>412</v>
+      </c>
+      <c r="F252" t="s">
         <v>96</v>
       </c>
-      <c r="E252" t="s">
+      <c r="G252" t="s">
         <v>97</v>
-      </c>
-      <c r="F252" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7397,15 +7397,15 @@
         <v>8</v>
       </c>
       <c r="C253" t="s">
+        <v>163</v>
+      </c>
+      <c r="D253" t="s">
         <v>421</v>
       </c>
-      <c r="D253" t="s">
+      <c r="F253" t="s">
         <v>422</v>
       </c>
-      <c r="E253" t="s">
-        <v>165</v>
-      </c>
-      <c r="F253" t="s">
+      <c r="G253" t="s">
         <v>423</v>
       </c>
     </row>
@@ -7417,16 +7417,16 @@
         <v>8</v>
       </c>
       <c r="C254" t="s">
+        <v>90</v>
+      </c>
+      <c r="D254" t="s">
+        <v>421</v>
+      </c>
+      <c r="F254" t="s">
         <v>219</v>
       </c>
-      <c r="D254" t="s">
+      <c r="G254" t="s">
         <v>220</v>
-      </c>
-      <c r="E254" t="s">
-        <v>92</v>
-      </c>
-      <c r="F254" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7437,16 +7437,16 @@
         <v>8</v>
       </c>
       <c r="C255" t="s">
+        <v>90</v>
+      </c>
+      <c r="D255" t="s">
+        <v>421</v>
+      </c>
+      <c r="F255" t="s">
         <v>426</v>
       </c>
-      <c r="D255" t="s">
+      <c r="G255" t="s">
         <v>427</v>
-      </c>
-      <c r="E255" t="s">
-        <v>92</v>
-      </c>
-      <c r="F255" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7457,19 +7457,19 @@
         <v>8</v>
       </c>
       <c r="C256" t="s">
+        <v>90</v>
+      </c>
+      <c r="D256" t="s">
+        <v>421</v>
+      </c>
+      <c r="F256" t="s">
         <v>426</v>
       </c>
-      <c r="D256" t="s">
+      <c r="G256" t="s">
         <v>427</v>
       </c>
-      <c r="E256" t="s">
-        <v>92</v>
-      </c>
-      <c r="F256" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
+    </row>
+    <row r="257" spans="1:7">
       <c r="A257" t="s">
         <v>429</v>
       </c>
@@ -7477,19 +7477,19 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
+        <v>90</v>
+      </c>
+      <c r="D257" t="s">
+        <v>421</v>
+      </c>
+      <c r="F257" t="s">
         <v>426</v>
       </c>
-      <c r="D257" t="s">
+      <c r="G257" t="s">
         <v>427</v>
       </c>
-      <c r="E257" t="s">
-        <v>92</v>
-      </c>
-      <c r="F257" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
+    </row>
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
         <v>430</v>
       </c>
@@ -7497,19 +7497,19 @@
         <v>8</v>
       </c>
       <c r="C258" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="D258" t="s">
-        <v>326</v>
-      </c>
-      <c r="E258" t="s">
-        <v>165</v>
+        <v>421</v>
       </c>
       <c r="F258" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
+        <v>327</v>
+      </c>
+      <c r="G258" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
         <v>431</v>
       </c>
@@ -7517,19 +7517,19 @@
         <v>8</v>
       </c>
       <c r="C259" t="s">
+        <v>90</v>
+      </c>
+      <c r="D259" t="s">
+        <v>421</v>
+      </c>
+      <c r="F259" t="s">
         <v>426</v>
       </c>
-      <c r="D259" t="s">
+      <c r="G259" t="s">
         <v>427</v>
       </c>
-      <c r="E259" t="s">
-        <v>92</v>
-      </c>
-      <c r="F259" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6">
+    </row>
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
         <v>432</v>
       </c>
@@ -7540,16 +7540,16 @@
         <v>163</v>
       </c>
       <c r="D260" t="s">
+        <v>421</v>
+      </c>
+      <c r="F260" t="s">
         <v>164</v>
       </c>
-      <c r="E260" t="s">
+      <c r="G260" t="s">
         <v>165</v>
       </c>
-      <c r="F260" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
+    </row>
+    <row r="261" spans="1:7">
       <c r="A261" t="s">
         <v>433</v>
       </c>
@@ -7557,19 +7557,19 @@
         <v>8</v>
       </c>
       <c r="C261" t="s">
+        <v>195</v>
+      </c>
+      <c r="D261" t="s">
+        <v>421</v>
+      </c>
+      <c r="F261" t="s">
         <v>434</v>
       </c>
-      <c r="D261" t="s">
+      <c r="G261" t="s">
         <v>435</v>
       </c>
-      <c r="E261" t="s">
-        <v>197</v>
-      </c>
-      <c r="F261" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
+    </row>
+    <row r="262" spans="1:7">
       <c r="A262" t="s">
         <v>436</v>
       </c>
@@ -7580,16 +7580,16 @@
         <v>163</v>
       </c>
       <c r="D262" t="s">
+        <v>421</v>
+      </c>
+      <c r="F262" t="s">
         <v>164</v>
       </c>
-      <c r="E262" t="s">
+      <c r="G262" t="s">
         <v>165</v>
       </c>
-      <c r="F262" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
+    </row>
+    <row r="263" spans="1:7">
       <c r="A263" t="s">
         <v>437</v>
       </c>
@@ -7597,19 +7597,19 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
+        <v>182</v>
+      </c>
+      <c r="D263" t="s">
+        <v>421</v>
+      </c>
+      <c r="F263" t="s">
         <v>438</v>
       </c>
-      <c r="D263" t="s">
+      <c r="G263" t="s">
         <v>439</v>
       </c>
-      <c r="E263" t="s">
-        <v>184</v>
-      </c>
-      <c r="F263" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
+    </row>
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
         <v>440</v>
       </c>
@@ -7620,16 +7620,16 @@
         <v>31</v>
       </c>
       <c r="D264" t="s">
+        <v>421</v>
+      </c>
+      <c r="F264" t="s">
         <v>32</v>
       </c>
-      <c r="E264" t="s">
+      <c r="G264" t="s">
         <v>33</v>
       </c>
-      <c r="F264" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6">
+    </row>
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>441</v>
       </c>
@@ -7640,16 +7640,16 @@
         <v>9</v>
       </c>
       <c r="D265" t="s">
-        <v>10</v>
-      </c>
-      <c r="E265" t="s">
-        <v>11</v>
+        <v>421</v>
       </c>
       <c r="F265" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
+        <v>12</v>
+      </c>
+      <c r="G265" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
       <c r="A266" t="s">
         <v>442</v>
       </c>
@@ -7657,19 +7657,19 @@
         <v>8</v>
       </c>
       <c r="C266" t="s">
+        <v>112</v>
+      </c>
+      <c r="D266" t="s">
+        <v>421</v>
+      </c>
+      <c r="F266" t="s">
         <v>443</v>
       </c>
-      <c r="D266" t="s">
+      <c r="G266" t="s">
         <v>444</v>
       </c>
-      <c r="E266" t="s">
-        <v>114</v>
-      </c>
-      <c r="F266" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
+    </row>
+    <row r="267" spans="1:7">
       <c r="A267" t="s">
         <v>445</v>
       </c>
@@ -7677,19 +7677,19 @@
         <v>8</v>
       </c>
       <c r="C267" t="s">
+        <v>112</v>
+      </c>
+      <c r="D267" t="s">
+        <v>446</v>
+      </c>
+      <c r="F267" t="s">
         <v>118</v>
       </c>
-      <c r="D267" t="s">
+      <c r="G267" t="s">
         <v>119</v>
       </c>
-      <c r="E267" t="s">
-        <v>114</v>
-      </c>
-      <c r="F267" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6">
+    </row>
+    <row r="268" spans="1:7">
       <c r="A268" t="s">
         <v>447</v>
       </c>
@@ -7697,19 +7697,19 @@
         <v>8</v>
       </c>
       <c r="C268" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D268" t="s">
+        <v>448</v>
+      </c>
+      <c r="F268" t="s">
         <v>203</v>
       </c>
-      <c r="E268" t="s">
-        <v>184</v>
-      </c>
-      <c r="F268" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6">
+      <c r="G268" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
       <c r="A269" t="s">
         <v>449</v>
       </c>
@@ -7717,19 +7717,19 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
+        <v>112</v>
+      </c>
+      <c r="D269" t="s">
+        <v>450</v>
+      </c>
+      <c r="F269" t="s">
         <v>118</v>
       </c>
-      <c r="D269" t="s">
+      <c r="G269" t="s">
         <v>119</v>
       </c>
-      <c r="E269" t="s">
-        <v>114</v>
-      </c>
-      <c r="F269" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6">
+    </row>
+    <row r="270" spans="1:7">
       <c r="A270" t="s">
         <v>451</v>
       </c>
@@ -7737,19 +7737,19 @@
         <v>8</v>
       </c>
       <c r="C270" t="s">
+        <v>112</v>
+      </c>
+      <c r="D270" t="s">
+        <v>450</v>
+      </c>
+      <c r="F270" t="s">
         <v>118</v>
       </c>
-      <c r="D270" t="s">
+      <c r="G270" t="s">
         <v>119</v>
       </c>
-      <c r="E270" t="s">
-        <v>114</v>
-      </c>
-      <c r="F270" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
+    </row>
+    <row r="271" spans="1:7">
       <c r="A271" t="s">
         <v>452</v>
       </c>
@@ -7757,19 +7757,19 @@
         <v>8</v>
       </c>
       <c r="C271" t="s">
+        <v>112</v>
+      </c>
+      <c r="D271" t="s">
         <v>453</v>
       </c>
-      <c r="D271" t="s">
+      <c r="F271" t="s">
         <v>454</v>
       </c>
-      <c r="E271" t="s">
-        <v>114</v>
-      </c>
-      <c r="F271" t="s">
+      <c r="G271" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="272" spans="1:6">
+    <row r="272" spans="1:7">
       <c r="A272" t="s">
         <v>456</v>
       </c>
@@ -7777,19 +7777,19 @@
         <v>8</v>
       </c>
       <c r="C272" t="s">
+        <v>112</v>
+      </c>
+      <c r="D272" t="s">
         <v>453</v>
       </c>
-      <c r="D272" t="s">
+      <c r="F272" t="s">
         <v>454</v>
       </c>
-      <c r="E272" t="s">
-        <v>114</v>
-      </c>
-      <c r="F272" t="s">
+      <c r="G272" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="273" spans="1:6">
+    <row r="273" spans="1:7">
       <c r="A273" t="s">
         <v>457</v>
       </c>
@@ -7797,19 +7797,19 @@
         <v>8</v>
       </c>
       <c r="C273" t="s">
+        <v>112</v>
+      </c>
+      <c r="D273" t="s">
         <v>453</v>
       </c>
-      <c r="D273" t="s">
+      <c r="F273" t="s">
         <v>454</v>
       </c>
-      <c r="E273" t="s">
-        <v>114</v>
-      </c>
-      <c r="F273" t="s">
+      <c r="G273" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="274" spans="1:6">
+    <row r="274" spans="1:7">
       <c r="A274" t="s">
         <v>458</v>
       </c>
@@ -7817,19 +7817,19 @@
         <v>8</v>
       </c>
       <c r="C274" t="s">
+        <v>112</v>
+      </c>
+      <c r="D274" t="s">
         <v>453</v>
       </c>
-      <c r="D274" t="s">
+      <c r="F274" t="s">
         <v>454</v>
       </c>
-      <c r="E274" t="s">
-        <v>114</v>
-      </c>
-      <c r="F274" t="s">
+      <c r="G274" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="275" spans="1:6">
+    <row r="275" spans="1:7">
       <c r="A275" t="s">
         <v>459</v>
       </c>
@@ -7837,19 +7837,19 @@
         <v>8</v>
       </c>
       <c r="C275" t="s">
+        <v>112</v>
+      </c>
+      <c r="D275" t="s">
         <v>453</v>
       </c>
-      <c r="D275" t="s">
+      <c r="F275" t="s">
         <v>454</v>
       </c>
-      <c r="E275" t="s">
-        <v>114</v>
-      </c>
-      <c r="F275" t="s">
+      <c r="G275" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="276" spans="1:6">
+    <row r="276" spans="1:7">
       <c r="A276" t="s">
         <v>460</v>
       </c>
@@ -7857,19 +7857,19 @@
         <v>8</v>
       </c>
       <c r="C276" t="s">
+        <v>112</v>
+      </c>
+      <c r="D276" t="s">
         <v>453</v>
       </c>
-      <c r="D276" t="s">
+      <c r="F276" t="s">
         <v>454</v>
       </c>
-      <c r="E276" t="s">
-        <v>114</v>
-      </c>
-      <c r="F276" t="s">
+      <c r="G276" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="277" spans="1:6">
+    <row r="277" spans="1:7">
       <c r="A277" t="s">
         <v>461</v>
       </c>
@@ -7877,19 +7877,19 @@
         <v>8</v>
       </c>
       <c r="C277" t="s">
+        <v>112</v>
+      </c>
+      <c r="D277" t="s">
         <v>453</v>
       </c>
-      <c r="D277" t="s">
+      <c r="F277" t="s">
         <v>454</v>
       </c>
-      <c r="E277" t="s">
-        <v>114</v>
-      </c>
-      <c r="F277" t="s">
+      <c r="G277" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="278" spans="1:6">
+    <row r="278" spans="1:7">
       <c r="A278" t="s">
         <v>462</v>
       </c>
@@ -7897,19 +7897,19 @@
         <v>8</v>
       </c>
       <c r="C278" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D278" t="s">
+        <v>463</v>
+      </c>
+      <c r="F278" t="s">
         <v>203</v>
       </c>
-      <c r="E278" t="s">
-        <v>184</v>
-      </c>
-      <c r="F278" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6">
+      <c r="G278" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
       <c r="A279" t="s">
         <v>464</v>
       </c>
@@ -7917,19 +7917,19 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D279" t="s">
-        <v>52</v>
-      </c>
-      <c r="E279" t="s">
-        <v>33</v>
+        <v>463</v>
       </c>
       <c r="F279" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
+        <v>53</v>
+      </c>
+      <c r="G279" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
       <c r="A280" t="s">
         <v>465</v>
       </c>
@@ -7940,16 +7940,16 @@
         <v>9</v>
       </c>
       <c r="D280" t="s">
-        <v>10</v>
-      </c>
-      <c r="E280" t="s">
-        <v>11</v>
+        <v>463</v>
       </c>
       <c r="F280" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6">
+        <v>12</v>
+      </c>
+      <c r="G280" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
       <c r="A281" t="s">
         <v>466</v>
       </c>
@@ -7957,19 +7957,19 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
+        <v>112</v>
+      </c>
+      <c r="D281" t="s">
+        <v>463</v>
+      </c>
+      <c r="F281" t="s">
         <v>170</v>
       </c>
-      <c r="D281" t="s">
+      <c r="G281" t="s">
         <v>171</v>
       </c>
-      <c r="E281" t="s">
-        <v>114</v>
-      </c>
-      <c r="F281" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6">
+    </row>
+    <row r="282" spans="1:7">
       <c r="A282" t="s">
         <v>467</v>
       </c>
@@ -7980,16 +7980,16 @@
         <v>124</v>
       </c>
       <c r="D282" t="s">
+        <v>463</v>
+      </c>
+      <c r="F282" t="s">
         <v>125</v>
       </c>
-      <c r="E282" t="s">
+      <c r="G282" t="s">
         <v>126</v>
       </c>
-      <c r="F282" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6">
+    </row>
+    <row r="283" spans="1:7">
       <c r="A283" t="s">
         <v>468</v>
       </c>
@@ -7997,19 +7997,19 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>398</v>
+        <v>163</v>
       </c>
       <c r="D283" t="s">
-        <v>364</v>
-      </c>
-      <c r="E283" t="s">
-        <v>165</v>
+        <v>469</v>
       </c>
       <c r="F283" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6">
+        <v>365</v>
+      </c>
+      <c r="G283" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
       <c r="A284" t="s">
         <v>470</v>
       </c>
@@ -8020,16 +8020,16 @@
         <v>124</v>
       </c>
       <c r="D284" t="s">
+        <v>471</v>
+      </c>
+      <c r="F284" t="s">
         <v>125</v>
       </c>
-      <c r="E284" t="s">
+      <c r="G284" t="s">
         <v>126</v>
       </c>
-      <c r="F284" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6">
+    </row>
+    <row r="285" spans="1:7">
       <c r="A285" t="s">
         <v>472</v>
       </c>
@@ -8037,19 +8037,19 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
+        <v>112</v>
+      </c>
+      <c r="D285" t="s">
+        <v>473</v>
+      </c>
+      <c r="F285" t="s">
         <v>170</v>
       </c>
-      <c r="D285" t="s">
+      <c r="G285" t="s">
         <v>171</v>
       </c>
-      <c r="E285" t="s">
-        <v>114</v>
-      </c>
-      <c r="F285" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6">
+    </row>
+    <row r="286" spans="1:7">
       <c r="A286" t="s">
         <v>474</v>
       </c>
@@ -8057,19 +8057,19 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
+        <v>182</v>
+      </c>
+      <c r="D286" t="s">
+        <v>475</v>
+      </c>
+      <c r="F286" t="s">
         <v>438</v>
       </c>
-      <c r="D286" t="s">
+      <c r="G286" t="s">
         <v>439</v>
       </c>
-      <c r="E286" t="s">
-        <v>184</v>
-      </c>
-      <c r="F286" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6">
+    </row>
+    <row r="287" spans="1:7">
       <c r="A287" t="s">
         <v>476</v>
       </c>
@@ -8077,19 +8077,19 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
+        <v>182</v>
+      </c>
+      <c r="D287" t="s">
+        <v>475</v>
+      </c>
+      <c r="F287" t="s">
         <v>438</v>
       </c>
-      <c r="D287" t="s">
+      <c r="G287" t="s">
         <v>439</v>
       </c>
-      <c r="E287" t="s">
-        <v>184</v>
-      </c>
-      <c r="F287" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6">
+    </row>
+    <row r="288" spans="1:7">
       <c r="A288" t="s">
         <v>477</v>
       </c>
@@ -8097,19 +8097,19 @@
         <v>8</v>
       </c>
       <c r="C288" t="s">
+        <v>9</v>
+      </c>
+      <c r="D288" t="s">
+        <v>475</v>
+      </c>
+      <c r="F288" t="s">
         <v>41</v>
       </c>
-      <c r="D288" t="s">
+      <c r="G288" t="s">
         <v>42</v>
       </c>
-      <c r="E288" t="s">
-        <v>11</v>
-      </c>
-      <c r="F288" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6">
+    </row>
+    <row r="289" spans="1:7">
       <c r="A289" t="s">
         <v>478</v>
       </c>
@@ -8120,16 +8120,16 @@
         <v>31</v>
       </c>
       <c r="D289" t="s">
+        <v>475</v>
+      </c>
+      <c r="F289" t="s">
         <v>32</v>
       </c>
-      <c r="E289" t="s">
+      <c r="G289" t="s">
         <v>33</v>
       </c>
-      <c r="F289" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6">
+    </row>
+    <row r="290" spans="1:7">
       <c r="A290" t="s">
         <v>479</v>
       </c>
@@ -8140,16 +8140,16 @@
         <v>31</v>
       </c>
       <c r="D290" t="s">
+        <v>475</v>
+      </c>
+      <c r="F290" t="s">
         <v>32</v>
       </c>
-      <c r="E290" t="s">
+      <c r="G290" t="s">
         <v>33</v>
       </c>
-      <c r="F290" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6">
+    </row>
+    <row r="291" spans="1:7">
       <c r="A291" t="s">
         <v>480</v>
       </c>
@@ -8157,19 +8157,19 @@
         <v>8</v>
       </c>
       <c r="C291" t="s">
+        <v>112</v>
+      </c>
+      <c r="D291" t="s">
+        <v>475</v>
+      </c>
+      <c r="F291" t="s">
         <v>170</v>
       </c>
-      <c r="D291" t="s">
+      <c r="G291" t="s">
         <v>171</v>
       </c>
-      <c r="E291" t="s">
-        <v>114</v>
-      </c>
-      <c r="F291" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6">
+    </row>
+    <row r="292" spans="1:7">
       <c r="A292" t="s">
         <v>481</v>
       </c>
@@ -8177,19 +8177,19 @@
         <v>8</v>
       </c>
       <c r="C292" t="s">
+        <v>112</v>
+      </c>
+      <c r="D292" t="s">
+        <v>475</v>
+      </c>
+      <c r="F292" t="s">
         <v>170</v>
       </c>
-      <c r="D292" t="s">
+      <c r="G292" t="s">
         <v>171</v>
       </c>
-      <c r="E292" t="s">
-        <v>114</v>
-      </c>
-      <c r="F292" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6">
+    </row>
+    <row r="293" spans="1:7">
       <c r="A293" t="s">
         <v>482</v>
       </c>
@@ -8197,19 +8197,19 @@
         <v>8</v>
       </c>
       <c r="C293" t="s">
+        <v>112</v>
+      </c>
+      <c r="D293" t="s">
+        <v>475</v>
+      </c>
+      <c r="F293" t="s">
         <v>170</v>
       </c>
-      <c r="D293" t="s">
+      <c r="G293" t="s">
         <v>171</v>
       </c>
-      <c r="E293" t="s">
-        <v>114</v>
-      </c>
-      <c r="F293" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6">
+    </row>
+    <row r="294" spans="1:7">
       <c r="A294" t="s">
         <v>483</v>
       </c>
@@ -8217,19 +8217,19 @@
         <v>8</v>
       </c>
       <c r="C294" t="s">
+        <v>112</v>
+      </c>
+      <c r="D294" t="s">
+        <v>475</v>
+      </c>
+      <c r="F294" t="s">
         <v>170</v>
       </c>
-      <c r="D294" t="s">
+      <c r="G294" t="s">
         <v>171</v>
       </c>
-      <c r="E294" t="s">
-        <v>114</v>
-      </c>
-      <c r="F294" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
+    </row>
+    <row r="295" spans="1:7">
       <c r="A295" t="s">
         <v>484</v>
       </c>
@@ -8237,19 +8237,19 @@
         <v>8</v>
       </c>
       <c r="C295" t="s">
+        <v>112</v>
+      </c>
+      <c r="D295" t="s">
+        <v>485</v>
+      </c>
+      <c r="F295" t="s">
         <v>170</v>
       </c>
-      <c r="D295" t="s">
+      <c r="G295" t="s">
         <v>171</v>
       </c>
-      <c r="E295" t="s">
-        <v>114</v>
-      </c>
-      <c r="F295" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6">
+    </row>
+    <row r="296" spans="1:7">
       <c r="A296" t="s">
         <v>486</v>
       </c>
@@ -8257,16 +8257,16 @@
         <v>8</v>
       </c>
       <c r="C296" t="s">
+        <v>112</v>
+      </c>
+      <c r="D296" t="s">
+        <v>485</v>
+      </c>
+      <c r="F296" t="s">
         <v>170</v>
       </c>
-      <c r="D296" t="s">
+      <c r="G296" t="s">
         <v>171</v>
-      </c>
-      <c r="E296" t="s">
-        <v>114</v>
-      </c>
-      <c r="F296" t="s">
-        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -25,18 +25,18 @@
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,51 +46,51 @@
     <t>09 - Education</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,96 +112,96 @@
     <t>07 - Health</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -289,27 +289,27 @@
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,12 +340,12 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -355,48 +355,48 @@
     <t>01 - General public services</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -565,12 +565,12 @@
     <t>10 - Social protection</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>02 - Defence</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,30 +655,30 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,42 +811,42 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,21 +1210,21 @@
     <t>32310</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>04.7.3 - Tourism (CS)</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>60020</t>
@@ -1866,16 +1866,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1912,16 +1912,16 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1935,16 +1935,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1961,10 +1961,10 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -1981,16 +1981,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2004,16 +2004,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2027,16 +2027,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2050,16 +2050,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2073,16 +2073,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2096,16 +2096,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2119,16 +2119,16 @@
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2142,16 +2142,16 @@
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2165,16 +2165,16 @@
         <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2234,16 +2234,16 @@
         <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2257,16 +2257,16 @@
         <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2303,16 +2303,16 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
         <v>64</v>
       </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2326,16 +2326,16 @@
         <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="E23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" t="s">
         <v>64</v>
       </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2349,16 +2349,16 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" t="s">
         <v>64</v>
       </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2372,16 +2372,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" t="s">
         <v>64</v>
       </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2395,16 +2395,16 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" t="s">
         <v>64</v>
       </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2418,16 +2418,16 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" t="s">
         <v>64</v>
       </c>
-      <c r="F27" t="s">
-        <v>32</v>
-      </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2441,16 +2441,16 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" t="s">
         <v>64</v>
       </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2464,16 +2464,16 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" t="s">
         <v>64</v>
       </c>
-      <c r="F29" t="s">
-        <v>32</v>
-      </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2490,10 +2490,10 @@
         <v>51</v>
       </c>
       <c r="E30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" t="s">
         <v>64</v>
-      </c>
-      <c r="F30" t="s">
-        <v>53</v>
       </c>
       <c r="G30" t="s">
         <v>54</v>
@@ -2510,16 +2510,16 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" t="s">
         <v>76</v>
       </c>
-      <c r="F31" t="s">
-        <v>32</v>
-      </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2533,16 +2533,16 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" t="s">
         <v>76</v>
       </c>
-      <c r="F32" t="s">
-        <v>32</v>
-      </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2556,16 +2556,16 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" t="s">
         <v>76</v>
       </c>
-      <c r="F33" t="s">
-        <v>32</v>
-      </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2579,16 +2579,16 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" t="s">
         <v>76</v>
       </c>
-      <c r="F34" t="s">
-        <v>32</v>
-      </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2602,16 +2602,16 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E35" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" t="s">
         <v>76</v>
       </c>
-      <c r="F35" t="s">
-        <v>32</v>
-      </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2625,16 +2625,16 @@
         <v>31</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E36" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" t="s">
         <v>76</v>
       </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2648,13 +2648,13 @@
         <v>31</v>
       </c>
       <c r="D37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" t="s">
         <v>83</v>
-      </c>
-      <c r="F37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2668,13 +2668,13 @@
         <v>31</v>
       </c>
       <c r="D38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
         <v>83</v>
-      </c>
-      <c r="F38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2688,13 +2688,13 @@
         <v>31</v>
       </c>
       <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
         <v>83</v>
-      </c>
-      <c r="F39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2708,13 +2708,13 @@
         <v>31</v>
       </c>
       <c r="D40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
         <v>83</v>
-      </c>
-      <c r="F40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2728,13 +2728,13 @@
         <v>31</v>
       </c>
       <c r="D41" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" t="s">
         <v>83</v>
-      </c>
-      <c r="F41" t="s">
-        <v>53</v>
-      </c>
-      <c r="G41" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2748,13 +2748,13 @@
         <v>31</v>
       </c>
       <c r="D42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" t="s">
         <v>83</v>
-      </c>
-      <c r="F42" t="s">
-        <v>57</v>
-      </c>
-      <c r="G42" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2770,7 +2770,7 @@
       <c r="D43" t="s">
         <v>91</v>
       </c>
-      <c r="F43" t="s">
+      <c r="E43" t="s">
         <v>92</v>
       </c>
       <c r="G43" t="s">
@@ -2788,13 +2788,13 @@
         <v>95</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
-      </c>
-      <c r="F44" t="s">
         <v>96</v>
       </c>
+      <c r="E44" t="s">
+        <v>97</v>
+      </c>
       <c r="G44" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2810,7 +2810,7 @@
       <c r="D45" t="s">
         <v>91</v>
       </c>
-      <c r="F45" t="s">
+      <c r="E45" t="s">
         <v>92</v>
       </c>
       <c r="G45" t="s">
@@ -2830,7 +2830,7 @@
       <c r="D46" t="s">
         <v>91</v>
       </c>
-      <c r="F46" t="s">
+      <c r="E46" t="s">
         <v>92</v>
       </c>
       <c r="G46" t="s">
@@ -2848,13 +2848,13 @@
         <v>95</v>
       </c>
       <c r="D47" t="s">
-        <v>91</v>
-      </c>
-      <c r="F47" t="s">
         <v>101</v>
       </c>
+      <c r="E47" t="s">
+        <v>102</v>
+      </c>
       <c r="G47" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2870,7 +2870,7 @@
       <c r="D48" t="s">
         <v>91</v>
       </c>
-      <c r="F48" t="s">
+      <c r="E48" t="s">
         <v>92</v>
       </c>
       <c r="G48" t="s">
@@ -2890,7 +2890,7 @@
       <c r="D49" t="s">
         <v>91</v>
       </c>
-      <c r="F49" t="s">
+      <c r="E49" t="s">
         <v>92</v>
       </c>
       <c r="G49" t="s">
@@ -2908,13 +2908,13 @@
         <v>95</v>
       </c>
       <c r="D50" t="s">
-        <v>91</v>
-      </c>
-      <c r="F50" t="s">
         <v>101</v>
       </c>
+      <c r="E50" t="s">
+        <v>102</v>
+      </c>
       <c r="G50" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2930,7 +2930,7 @@
       <c r="D51" t="s">
         <v>91</v>
       </c>
-      <c r="F51" t="s">
+      <c r="E51" t="s">
         <v>92</v>
       </c>
       <c r="G51" t="s">
@@ -2948,13 +2948,13 @@
         <v>95</v>
       </c>
       <c r="D52" t="s">
-        <v>91</v>
-      </c>
-      <c r="F52" t="s">
         <v>108</v>
       </c>
+      <c r="E52" t="s">
+        <v>109</v>
+      </c>
       <c r="G52" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2968,13 +2968,13 @@
         <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>91</v>
-      </c>
-      <c r="F53" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3011,16 +3011,16 @@
         <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E55" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F55" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G55" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3034,16 +3034,16 @@
         <v>112</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E56" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F56" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G56" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3057,16 +3057,16 @@
         <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F57" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3080,16 +3080,16 @@
         <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E58" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F58" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3103,16 +3103,16 @@
         <v>112</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E59" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F59" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G59" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3126,16 +3126,16 @@
         <v>112</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F60" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3149,16 +3149,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E61" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F61" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3172,16 +3172,16 @@
         <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E62" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F62" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G62" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3195,16 +3195,16 @@
         <v>112</v>
       </c>
       <c r="D63" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G63" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3218,16 +3218,16 @@
         <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F64" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G64" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3241,16 +3241,16 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="F65" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3287,16 +3287,16 @@
         <v>112</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E67" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F67" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3310,7 +3310,7 @@
         <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
@@ -3319,7 +3319,7 @@
         <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3333,7 +3333,7 @@
         <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
@@ -3342,7 +3342,7 @@
         <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3356,16 +3356,16 @@
         <v>112</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E70" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F70" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3379,16 +3379,16 @@
         <v>112</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E71" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F71" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G71" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3425,16 +3425,16 @@
         <v>124</v>
       </c>
       <c r="D73" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F73" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3448,16 +3448,16 @@
         <v>124</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="F74" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3471,16 +3471,16 @@
         <v>124</v>
       </c>
       <c r="D75" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="F75" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="G75" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3494,16 +3494,16 @@
         <v>124</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E76" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F76" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3517,16 +3517,16 @@
         <v>124</v>
       </c>
       <c r="D77" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E77" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F77" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="G77" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3540,16 +3540,16 @@
         <v>124</v>
       </c>
       <c r="D78" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="E78" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="F78" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="G78" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3563,16 +3563,16 @@
         <v>124</v>
       </c>
       <c r="D79" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="E79" t="s">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="F79" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3586,16 +3586,16 @@
         <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="F80" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G80" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3609,16 +3609,16 @@
         <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E81" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="F81" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G81" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3632,16 +3632,16 @@
         <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E82" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="F82" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G82" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3655,7 +3655,7 @@
         <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
@@ -3664,7 +3664,7 @@
         <v>115</v>
       </c>
       <c r="G83" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3678,16 +3678,16 @@
         <v>112</v>
       </c>
       <c r="D84" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E84" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="F84" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G84" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3701,16 +3701,16 @@
         <v>112</v>
       </c>
       <c r="D85" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="E85" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F85" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G85" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3724,16 +3724,16 @@
         <v>163</v>
       </c>
       <c r="D86" t="s">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="E86" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="F86" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="G86" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3747,16 +3747,16 @@
         <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="E87" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F87" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G87" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3770,16 +3770,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E88" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F88" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G88" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3793,16 +3793,16 @@
         <v>112</v>
       </c>
       <c r="D89" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E89" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F89" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G89" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3816,16 +3816,16 @@
         <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E90" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F90" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G90" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3839,16 +3839,16 @@
         <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="F91" t="s">
-        <v>183</v>
+        <v>115</v>
       </c>
       <c r="G91" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3862,16 +3862,16 @@
         <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F92" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G92" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3885,16 +3885,16 @@
         <v>112</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E93" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F93" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G93" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3908,16 +3908,16 @@
         <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E94" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F94" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3931,16 +3931,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="E95" t="s">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="F95" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="G95" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3954,16 +3954,16 @@
         <v>124</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E96" t="s">
+        <v>126</v>
+      </c>
+      <c r="F96" t="s">
         <v>192</v>
       </c>
-      <c r="F96" t="s">
-        <v>125</v>
-      </c>
       <c r="G96" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3977,16 +3977,16 @@
         <v>124</v>
       </c>
       <c r="D97" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E97" t="s">
+        <v>126</v>
+      </c>
+      <c r="F97" t="s">
         <v>192</v>
       </c>
-      <c r="F97" t="s">
-        <v>125</v>
-      </c>
       <c r="G97" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4000,16 +4000,16 @@
         <v>195</v>
       </c>
       <c r="D98" t="s">
-        <v>113</v>
+        <v>196</v>
       </c>
       <c r="E98" t="s">
+        <v>197</v>
+      </c>
+      <c r="F98" t="s">
         <v>192</v>
       </c>
-      <c r="F98" t="s">
-        <v>196</v>
-      </c>
       <c r="G98" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4023,16 +4023,16 @@
         <v>124</v>
       </c>
       <c r="D99" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E99" t="s">
+        <v>126</v>
+      </c>
+      <c r="F99" t="s">
         <v>192</v>
       </c>
-      <c r="F99" t="s">
-        <v>125</v>
-      </c>
       <c r="G99" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4046,16 +4046,16 @@
         <v>124</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="E100" t="s">
+        <v>155</v>
+      </c>
+      <c r="F100" t="s">
         <v>192</v>
       </c>
-      <c r="F100" t="s">
-        <v>154</v>
-      </c>
       <c r="G100" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4069,16 +4069,16 @@
         <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E101" t="s">
+        <v>126</v>
+      </c>
+      <c r="F101" t="s">
         <v>192</v>
       </c>
-      <c r="F101" t="s">
-        <v>125</v>
-      </c>
       <c r="G101" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4094,7 +4094,7 @@
       <c r="D102" t="s">
         <v>202</v>
       </c>
-      <c r="F102" t="s">
+      <c r="E102" t="s">
         <v>203</v>
       </c>
       <c r="G102" t="s">
@@ -4114,7 +4114,7 @@
       <c r="D103" t="s">
         <v>202</v>
       </c>
-      <c r="F103" t="s">
+      <c r="E103" t="s">
         <v>203</v>
       </c>
       <c r="G103" t="s">
@@ -4134,7 +4134,7 @@
       <c r="D104" t="s">
         <v>202</v>
       </c>
-      <c r="F104" t="s">
+      <c r="E104" t="s">
         <v>203</v>
       </c>
       <c r="G104" t="s">
@@ -4152,13 +4152,13 @@
         <v>182</v>
       </c>
       <c r="D105" t="s">
-        <v>202</v>
-      </c>
-      <c r="F105" t="s">
         <v>208</v>
       </c>
+      <c r="E105" t="s">
+        <v>209</v>
+      </c>
       <c r="G105" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4174,7 +4174,7 @@
       <c r="D106" t="s">
         <v>202</v>
       </c>
-      <c r="F106" t="s">
+      <c r="E106" t="s">
         <v>203</v>
       </c>
       <c r="G106" t="s">
@@ -4192,13 +4192,13 @@
         <v>182</v>
       </c>
       <c r="D107" t="s">
-        <v>202</v>
-      </c>
-      <c r="F107" t="s">
         <v>183</v>
       </c>
+      <c r="E107" t="s">
+        <v>184</v>
+      </c>
       <c r="G107" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4212,13 +4212,13 @@
         <v>182</v>
       </c>
       <c r="D108" t="s">
-        <v>202</v>
-      </c>
-      <c r="F108" t="s">
         <v>213</v>
       </c>
+      <c r="E108" t="s">
+        <v>214</v>
+      </c>
       <c r="G108" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4232,13 +4232,13 @@
         <v>90</v>
       </c>
       <c r="D109" t="s">
-        <v>202</v>
-      </c>
-      <c r="F109" t="s">
         <v>216</v>
       </c>
+      <c r="E109" t="s">
+        <v>217</v>
+      </c>
       <c r="G109" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4252,13 +4252,13 @@
         <v>90</v>
       </c>
       <c r="D110" t="s">
-        <v>202</v>
-      </c>
-      <c r="F110" t="s">
         <v>219</v>
       </c>
+      <c r="E110" t="s">
+        <v>220</v>
+      </c>
       <c r="G110" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4274,7 +4274,7 @@
       <c r="D111" t="s">
         <v>202</v>
       </c>
-      <c r="F111" t="s">
+      <c r="E111" t="s">
         <v>203</v>
       </c>
       <c r="G111" t="s">
@@ -4292,13 +4292,13 @@
         <v>223</v>
       </c>
       <c r="D112" t="s">
-        <v>202</v>
-      </c>
-      <c r="F112" t="s">
         <v>224</v>
       </c>
+      <c r="E112" t="s">
+        <v>225</v>
+      </c>
       <c r="G112" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4312,13 +4312,13 @@
         <v>112</v>
       </c>
       <c r="D113" t="s">
-        <v>202</v>
-      </c>
-      <c r="F113" t="s">
-        <v>115</v>
+        <v>143</v>
+      </c>
+      <c r="E113" t="s">
+        <v>114</v>
       </c>
       <c r="G113" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4332,13 +4332,13 @@
         <v>124</v>
       </c>
       <c r="D114" t="s">
-        <v>202</v>
-      </c>
-      <c r="F114" t="s">
         <v>151</v>
       </c>
+      <c r="E114" t="s">
+        <v>152</v>
+      </c>
       <c r="G114" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4352,13 +4352,13 @@
         <v>182</v>
       </c>
       <c r="D115" t="s">
-        <v>202</v>
-      </c>
-      <c r="F115" t="s">
         <v>183</v>
       </c>
+      <c r="E115" t="s">
+        <v>184</v>
+      </c>
       <c r="G115" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4372,13 +4372,13 @@
         <v>223</v>
       </c>
       <c r="D116" t="s">
-        <v>202</v>
-      </c>
-      <c r="F116" t="s">
         <v>230</v>
       </c>
+      <c r="E116" t="s">
+        <v>231</v>
+      </c>
       <c r="G116" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4392,13 +4392,13 @@
         <v>223</v>
       </c>
       <c r="D117" t="s">
-        <v>202</v>
-      </c>
-      <c r="F117" t="s">
         <v>224</v>
       </c>
+      <c r="E117" t="s">
+        <v>225</v>
+      </c>
       <c r="G117" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4412,13 +4412,13 @@
         <v>163</v>
       </c>
       <c r="D118" t="s">
-        <v>202</v>
-      </c>
-      <c r="F118" t="s">
-        <v>164</v>
+        <v>234</v>
+      </c>
+      <c r="E118" t="s">
+        <v>165</v>
       </c>
       <c r="G118" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4432,13 +4432,13 @@
         <v>182</v>
       </c>
       <c r="D119" t="s">
-        <v>202</v>
-      </c>
-      <c r="F119" t="s">
         <v>183</v>
       </c>
+      <c r="E119" t="s">
+        <v>184</v>
+      </c>
       <c r="G119" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4452,13 +4452,13 @@
         <v>112</v>
       </c>
       <c r="D120" t="s">
+        <v>170</v>
+      </c>
+      <c r="E120" t="s">
+        <v>171</v>
+      </c>
+      <c r="G120" t="s">
         <v>237</v>
-      </c>
-      <c r="F120" t="s">
-        <v>170</v>
-      </c>
-      <c r="G120" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4472,13 +4472,13 @@
         <v>112</v>
       </c>
       <c r="D121" t="s">
+        <v>143</v>
+      </c>
+      <c r="E121" t="s">
+        <v>114</v>
+      </c>
+      <c r="G121" t="s">
         <v>237</v>
-      </c>
-      <c r="F121" t="s">
-        <v>115</v>
-      </c>
-      <c r="G121" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4492,13 +4492,13 @@
         <v>112</v>
       </c>
       <c r="D122" t="s">
+        <v>170</v>
+      </c>
+      <c r="E122" t="s">
+        <v>171</v>
+      </c>
+      <c r="G122" t="s">
         <v>237</v>
-      </c>
-      <c r="F122" t="s">
-        <v>170</v>
-      </c>
-      <c r="G122" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4512,13 +4512,13 @@
         <v>112</v>
       </c>
       <c r="D123" t="s">
+        <v>170</v>
+      </c>
+      <c r="E123" t="s">
+        <v>171</v>
+      </c>
+      <c r="G123" t="s">
         <v>237</v>
-      </c>
-      <c r="F123" t="s">
-        <v>170</v>
-      </c>
-      <c r="G123" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4532,13 +4532,13 @@
         <v>163</v>
       </c>
       <c r="D124" t="s">
+        <v>242</v>
+      </c>
+      <c r="E124" t="s">
+        <v>243</v>
+      </c>
+      <c r="G124" t="s">
         <v>237</v>
-      </c>
-      <c r="F124" t="s">
-        <v>242</v>
-      </c>
-      <c r="G124" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4552,13 +4552,13 @@
         <v>163</v>
       </c>
       <c r="D125" t="s">
+        <v>242</v>
+      </c>
+      <c r="E125" t="s">
+        <v>243</v>
+      </c>
+      <c r="G125" t="s">
         <v>237</v>
-      </c>
-      <c r="F125" t="s">
-        <v>242</v>
-      </c>
-      <c r="G125" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4572,13 +4572,13 @@
         <v>163</v>
       </c>
       <c r="D126" t="s">
+        <v>242</v>
+      </c>
+      <c r="E126" t="s">
+        <v>243</v>
+      </c>
+      <c r="G126" t="s">
         <v>237</v>
-      </c>
-      <c r="F126" t="s">
-        <v>242</v>
-      </c>
-      <c r="G126" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4592,13 +4592,13 @@
         <v>163</v>
       </c>
       <c r="D127" t="s">
+        <v>242</v>
+      </c>
+      <c r="E127" t="s">
+        <v>243</v>
+      </c>
+      <c r="G127" t="s">
         <v>237</v>
-      </c>
-      <c r="F127" t="s">
-        <v>242</v>
-      </c>
-      <c r="G127" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4612,13 +4612,13 @@
         <v>163</v>
       </c>
       <c r="D128" t="s">
+        <v>242</v>
+      </c>
+      <c r="E128" t="s">
+        <v>243</v>
+      </c>
+      <c r="G128" t="s">
         <v>237</v>
-      </c>
-      <c r="F128" t="s">
-        <v>242</v>
-      </c>
-      <c r="G128" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4632,13 +4632,13 @@
         <v>163</v>
       </c>
       <c r="D129" t="s">
+        <v>249</v>
+      </c>
+      <c r="E129" t="s">
+        <v>243</v>
+      </c>
+      <c r="G129" t="s">
         <v>237</v>
-      </c>
-      <c r="F129" t="s">
-        <v>242</v>
-      </c>
-      <c r="G129" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4652,13 +4652,13 @@
         <v>163</v>
       </c>
       <c r="D130" t="s">
+        <v>251</v>
+      </c>
+      <c r="E130" t="s">
+        <v>243</v>
+      </c>
+      <c r="G130" t="s">
         <v>237</v>
-      </c>
-      <c r="F130" t="s">
-        <v>242</v>
-      </c>
-      <c r="G130" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4672,13 +4672,13 @@
         <v>163</v>
       </c>
       <c r="D131" t="s">
+        <v>253</v>
+      </c>
+      <c r="E131" t="s">
+        <v>243</v>
+      </c>
+      <c r="G131" t="s">
         <v>237</v>
-      </c>
-      <c r="F131" t="s">
-        <v>242</v>
-      </c>
-      <c r="G131" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4692,13 +4692,13 @@
         <v>163</v>
       </c>
       <c r="D132" t="s">
+        <v>255</v>
+      </c>
+      <c r="E132" t="s">
+        <v>256</v>
+      </c>
+      <c r="G132" t="s">
         <v>237</v>
-      </c>
-      <c r="F132" t="s">
-        <v>255</v>
-      </c>
-      <c r="G132" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4712,13 +4712,13 @@
         <v>112</v>
       </c>
       <c r="D133" t="s">
+        <v>189</v>
+      </c>
+      <c r="E133" t="s">
+        <v>190</v>
+      </c>
+      <c r="G133" t="s">
         <v>237</v>
-      </c>
-      <c r="F133" t="s">
-        <v>189</v>
-      </c>
-      <c r="G133" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4732,13 +4732,13 @@
         <v>163</v>
       </c>
       <c r="D134" t="s">
+        <v>175</v>
+      </c>
+      <c r="E134" t="s">
+        <v>176</v>
+      </c>
+      <c r="G134" t="s">
         <v>259</v>
-      </c>
-      <c r="F134" t="s">
-        <v>175</v>
-      </c>
-      <c r="G134" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4752,13 +4752,13 @@
         <v>163</v>
       </c>
       <c r="D135" t="s">
+        <v>175</v>
+      </c>
+      <c r="E135" t="s">
+        <v>176</v>
+      </c>
+      <c r="G135" t="s">
         <v>259</v>
-      </c>
-      <c r="F135" t="s">
-        <v>175</v>
-      </c>
-      <c r="G135" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4772,13 +4772,13 @@
         <v>163</v>
       </c>
       <c r="D136" t="s">
+        <v>175</v>
+      </c>
+      <c r="E136" t="s">
+        <v>176</v>
+      </c>
+      <c r="G136" t="s">
         <v>259</v>
-      </c>
-      <c r="F136" t="s">
-        <v>175</v>
-      </c>
-      <c r="G136" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4792,13 +4792,13 @@
         <v>163</v>
       </c>
       <c r="D137" t="s">
+        <v>175</v>
+      </c>
+      <c r="E137" t="s">
+        <v>176</v>
+      </c>
+      <c r="G137" t="s">
         <v>259</v>
-      </c>
-      <c r="F137" t="s">
-        <v>175</v>
-      </c>
-      <c r="G137" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4812,13 +4812,13 @@
         <v>163</v>
       </c>
       <c r="D138" t="s">
+        <v>175</v>
+      </c>
+      <c r="E138" t="s">
+        <v>176</v>
+      </c>
+      <c r="G138" t="s">
         <v>259</v>
-      </c>
-      <c r="F138" t="s">
-        <v>175</v>
-      </c>
-      <c r="G138" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4832,13 +4832,13 @@
         <v>223</v>
       </c>
       <c r="D139" t="s">
+        <v>265</v>
+      </c>
+      <c r="E139" t="s">
+        <v>266</v>
+      </c>
+      <c r="G139" t="s">
         <v>259</v>
-      </c>
-      <c r="F139" t="s">
-        <v>265</v>
-      </c>
-      <c r="G139" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4852,13 +4852,13 @@
         <v>163</v>
       </c>
       <c r="D140" t="s">
+        <v>175</v>
+      </c>
+      <c r="E140" t="s">
+        <v>176</v>
+      </c>
+      <c r="G140" t="s">
         <v>259</v>
-      </c>
-      <c r="F140" t="s">
-        <v>175</v>
-      </c>
-      <c r="G140" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4918,16 +4918,16 @@
         <v>163</v>
       </c>
       <c r="D143" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E143" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="F143" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G143" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4941,16 +4941,16 @@
         <v>163</v>
       </c>
       <c r="D144" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E144" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="F144" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G144" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4964,16 +4964,16 @@
         <v>163</v>
       </c>
       <c r="D145" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E145" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="F145" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G145" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -5013,10 +5013,10 @@
         <v>269</v>
       </c>
       <c r="E147" t="s">
+        <v>270</v>
+      </c>
+      <c r="F147" t="s">
         <v>281</v>
-      </c>
-      <c r="F147" t="s">
-        <v>271</v>
       </c>
       <c r="G147" t="s">
         <v>272</v>
@@ -5036,10 +5036,10 @@
         <v>269</v>
       </c>
       <c r="E148" t="s">
+        <v>270</v>
+      </c>
+      <c r="F148" t="s">
         <v>281</v>
-      </c>
-      <c r="F148" t="s">
-        <v>271</v>
       </c>
       <c r="G148" t="s">
         <v>272</v>
@@ -5059,10 +5059,10 @@
         <v>269</v>
       </c>
       <c r="E149" t="s">
+        <v>270</v>
+      </c>
+      <c r="F149" t="s">
         <v>281</v>
-      </c>
-      <c r="F149" t="s">
-        <v>271</v>
       </c>
       <c r="G149" t="s">
         <v>272</v>
@@ -5082,10 +5082,10 @@
         <v>269</v>
       </c>
       <c r="E150" t="s">
+        <v>270</v>
+      </c>
+      <c r="F150" t="s">
         <v>281</v>
-      </c>
-      <c r="F150" t="s">
-        <v>271</v>
       </c>
       <c r="G150" t="s">
         <v>272</v>
@@ -5105,10 +5105,10 @@
         <v>269</v>
       </c>
       <c r="E151" t="s">
+        <v>270</v>
+      </c>
+      <c r="F151" t="s">
         <v>281</v>
-      </c>
-      <c r="F151" t="s">
-        <v>271</v>
       </c>
       <c r="G151" t="s">
         <v>272</v>
@@ -5128,10 +5128,10 @@
         <v>269</v>
       </c>
       <c r="E152" t="s">
+        <v>270</v>
+      </c>
+      <c r="F152" t="s">
         <v>281</v>
-      </c>
-      <c r="F152" t="s">
-        <v>271</v>
       </c>
       <c r="G152" t="s">
         <v>272</v>
@@ -5151,10 +5151,10 @@
         <v>269</v>
       </c>
       <c r="E153" t="s">
+        <v>270</v>
+      </c>
+      <c r="F153" t="s">
         <v>281</v>
-      </c>
-      <c r="F153" t="s">
-        <v>271</v>
       </c>
       <c r="G153" t="s">
         <v>272</v>
@@ -5174,10 +5174,10 @@
         <v>269</v>
       </c>
       <c r="E154" t="s">
+        <v>270</v>
+      </c>
+      <c r="F154" t="s">
         <v>281</v>
-      </c>
-      <c r="F154" t="s">
-        <v>271</v>
       </c>
       <c r="G154" t="s">
         <v>272</v>
@@ -5197,10 +5197,10 @@
         <v>269</v>
       </c>
       <c r="E155" t="s">
+        <v>270</v>
+      </c>
+      <c r="F155" t="s">
         <v>281</v>
-      </c>
-      <c r="F155" t="s">
-        <v>271</v>
       </c>
       <c r="G155" t="s">
         <v>272</v>
@@ -5220,10 +5220,10 @@
         <v>269</v>
       </c>
       <c r="E156" t="s">
+        <v>270</v>
+      </c>
+      <c r="F156" t="s">
         <v>291</v>
-      </c>
-      <c r="F156" t="s">
-        <v>271</v>
       </c>
       <c r="G156" t="s">
         <v>272</v>
@@ -5240,16 +5240,16 @@
         <v>163</v>
       </c>
       <c r="D157" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="E157" t="s">
+        <v>270</v>
+      </c>
+      <c r="F157" t="s">
         <v>291</v>
       </c>
-      <c r="F157" t="s">
-        <v>271</v>
-      </c>
       <c r="G157" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5266,10 +5266,10 @@
         <v>269</v>
       </c>
       <c r="E158" t="s">
+        <v>270</v>
+      </c>
+      <c r="F158" t="s">
         <v>291</v>
-      </c>
-      <c r="F158" t="s">
-        <v>271</v>
       </c>
       <c r="G158" t="s">
         <v>272</v>
@@ -5289,10 +5289,10 @@
         <v>269</v>
       </c>
       <c r="E159" t="s">
+        <v>270</v>
+      </c>
+      <c r="F159" t="s">
         <v>291</v>
-      </c>
-      <c r="F159" t="s">
-        <v>271</v>
       </c>
       <c r="G159" t="s">
         <v>272</v>
@@ -5312,10 +5312,10 @@
         <v>269</v>
       </c>
       <c r="E160" t="s">
+        <v>270</v>
+      </c>
+      <c r="F160" t="s">
         <v>291</v>
-      </c>
-      <c r="F160" t="s">
-        <v>271</v>
       </c>
       <c r="G160" t="s">
         <v>272</v>
@@ -5335,10 +5335,10 @@
         <v>269</v>
       </c>
       <c r="E161" t="s">
+        <v>270</v>
+      </c>
+      <c r="F161" t="s">
         <v>291</v>
-      </c>
-      <c r="F161" t="s">
-        <v>271</v>
       </c>
       <c r="G161" t="s">
         <v>272</v>
@@ -5358,10 +5358,10 @@
         <v>269</v>
       </c>
       <c r="E162" t="s">
+        <v>270</v>
+      </c>
+      <c r="F162" t="s">
         <v>299</v>
-      </c>
-      <c r="F162" t="s">
-        <v>271</v>
       </c>
       <c r="G162" t="s">
         <v>272</v>
@@ -5378,16 +5378,16 @@
         <v>163</v>
       </c>
       <c r="D163" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="E163" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="F163" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="G163" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5404,10 +5404,10 @@
         <v>269</v>
       </c>
       <c r="E164" t="s">
+        <v>270</v>
+      </c>
+      <c r="F164" t="s">
         <v>304</v>
-      </c>
-      <c r="F164" t="s">
-        <v>271</v>
       </c>
       <c r="G164" t="s">
         <v>272</v>
@@ -5427,10 +5427,10 @@
         <v>269</v>
       </c>
       <c r="E165" t="s">
+        <v>270</v>
+      </c>
+      <c r="F165" t="s">
         <v>304</v>
-      </c>
-      <c r="F165" t="s">
-        <v>271</v>
       </c>
       <c r="G165" t="s">
         <v>272</v>
@@ -5450,10 +5450,10 @@
         <v>269</v>
       </c>
       <c r="E166" t="s">
+        <v>270</v>
+      </c>
+      <c r="F166" t="s">
         <v>304</v>
-      </c>
-      <c r="F166" t="s">
-        <v>271</v>
       </c>
       <c r="G166" t="s">
         <v>272</v>
@@ -5473,10 +5473,10 @@
         <v>269</v>
       </c>
       <c r="E167" t="s">
+        <v>270</v>
+      </c>
+      <c r="F167" t="s">
         <v>304</v>
-      </c>
-      <c r="F167" t="s">
-        <v>271</v>
       </c>
       <c r="G167" t="s">
         <v>272</v>
@@ -5493,16 +5493,16 @@
         <v>163</v>
       </c>
       <c r="D168" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="E168" t="s">
+        <v>270</v>
+      </c>
+      <c r="F168" t="s">
         <v>304</v>
       </c>
-      <c r="F168" t="s">
-        <v>271</v>
-      </c>
       <c r="G168" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5516,16 +5516,16 @@
         <v>163</v>
       </c>
       <c r="D169" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="E169" t="s">
+        <v>270</v>
+      </c>
+      <c r="F169" t="s">
         <v>304</v>
       </c>
-      <c r="F169" t="s">
-        <v>271</v>
-      </c>
       <c r="G169" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5542,10 +5542,10 @@
         <v>269</v>
       </c>
       <c r="E170" t="s">
+        <v>270</v>
+      </c>
+      <c r="F170" t="s">
         <v>304</v>
-      </c>
-      <c r="F170" t="s">
-        <v>271</v>
       </c>
       <c r="G170" t="s">
         <v>272</v>
@@ -5562,13 +5562,13 @@
         <v>163</v>
       </c>
       <c r="D171" t="s">
+        <v>164</v>
+      </c>
+      <c r="E171" t="s">
+        <v>165</v>
+      </c>
+      <c r="G171" t="s">
         <v>313</v>
-      </c>
-      <c r="F171" t="s">
-        <v>164</v>
-      </c>
-      <c r="G171" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5582,13 +5582,13 @@
         <v>112</v>
       </c>
       <c r="D172" t="s">
+        <v>118</v>
+      </c>
+      <c r="E172" t="s">
+        <v>119</v>
+      </c>
+      <c r="G172" t="s">
         <v>313</v>
-      </c>
-      <c r="F172" t="s">
-        <v>118</v>
-      </c>
-      <c r="G172" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5602,13 +5602,13 @@
         <v>163</v>
       </c>
       <c r="D173" t="s">
+        <v>164</v>
+      </c>
+      <c r="E173" t="s">
+        <v>165</v>
+      </c>
+      <c r="G173" t="s">
         <v>313</v>
-      </c>
-      <c r="F173" t="s">
-        <v>164</v>
-      </c>
-      <c r="G173" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5622,13 +5622,13 @@
         <v>163</v>
       </c>
       <c r="D174" t="s">
+        <v>164</v>
+      </c>
+      <c r="E174" t="s">
+        <v>165</v>
+      </c>
+      <c r="G174" t="s">
         <v>313</v>
-      </c>
-      <c r="F174" t="s">
-        <v>164</v>
-      </c>
-      <c r="G174" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5642,13 +5642,13 @@
         <v>163</v>
       </c>
       <c r="D175" t="s">
+        <v>164</v>
+      </c>
+      <c r="E175" t="s">
+        <v>165</v>
+      </c>
+      <c r="G175" t="s">
         <v>313</v>
-      </c>
-      <c r="F175" t="s">
-        <v>164</v>
-      </c>
-      <c r="G175" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5662,13 +5662,13 @@
         <v>163</v>
       </c>
       <c r="D176" t="s">
+        <v>164</v>
+      </c>
+      <c r="E176" t="s">
+        <v>165</v>
+      </c>
+      <c r="G176" t="s">
         <v>313</v>
-      </c>
-      <c r="F176" t="s">
-        <v>164</v>
-      </c>
-      <c r="G176" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5682,13 +5682,13 @@
         <v>163</v>
       </c>
       <c r="D177" t="s">
+        <v>164</v>
+      </c>
+      <c r="E177" t="s">
+        <v>165</v>
+      </c>
+      <c r="G177" t="s">
         <v>320</v>
-      </c>
-      <c r="F177" t="s">
-        <v>164</v>
-      </c>
-      <c r="G177" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5702,13 +5702,13 @@
         <v>163</v>
       </c>
       <c r="D178" t="s">
+        <v>164</v>
+      </c>
+      <c r="E178" t="s">
+        <v>165</v>
+      </c>
+      <c r="G178" t="s">
         <v>320</v>
-      </c>
-      <c r="F178" t="s">
-        <v>164</v>
-      </c>
-      <c r="G178" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5722,13 +5722,13 @@
         <v>163</v>
       </c>
       <c r="D179" t="s">
+        <v>164</v>
+      </c>
+      <c r="E179" t="s">
+        <v>165</v>
+      </c>
+      <c r="G179" t="s">
         <v>320</v>
-      </c>
-      <c r="F179" t="s">
-        <v>164</v>
-      </c>
-      <c r="G179" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5742,13 +5742,13 @@
         <v>163</v>
       </c>
       <c r="D180" t="s">
+        <v>164</v>
+      </c>
+      <c r="E180" t="s">
+        <v>165</v>
+      </c>
+      <c r="G180" t="s">
         <v>320</v>
-      </c>
-      <c r="F180" t="s">
-        <v>164</v>
-      </c>
-      <c r="G180" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6038,16 +6038,16 @@
         <v>163</v>
       </c>
       <c r="D193" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="E193" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
       <c r="F193" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="G193" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6176,16 +6176,16 @@
         <v>163</v>
       </c>
       <c r="D199" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="E199" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="F199" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="G199" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6199,16 +6199,16 @@
         <v>163</v>
       </c>
       <c r="D200" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="E200" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="F200" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="G200" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6222,16 +6222,16 @@
         <v>163</v>
       </c>
       <c r="D201" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="E201" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="F201" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="G201" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6245,16 +6245,16 @@
         <v>163</v>
       </c>
       <c r="D202" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="E202" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="F202" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="G202" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6268,16 +6268,16 @@
         <v>163</v>
       </c>
       <c r="D203" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="E203" t="s">
-        <v>348</v>
+        <v>276</v>
       </c>
       <c r="F203" t="s">
-        <v>275</v>
+        <v>349</v>
       </c>
       <c r="G203" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6291,16 +6291,16 @@
         <v>163</v>
       </c>
       <c r="D204" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="E204" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="F204" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="G204" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6314,16 +6314,16 @@
         <v>163</v>
       </c>
       <c r="D205" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="E205" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="F205" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="G205" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6337,16 +6337,16 @@
         <v>163</v>
       </c>
       <c r="D206" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="E206" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="F206" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="G206" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6360,16 +6360,16 @@
         <v>163</v>
       </c>
       <c r="D207" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="E207" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="F207" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="G207" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6383,16 +6383,16 @@
         <v>163</v>
       </c>
       <c r="D208" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="E208" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="F208" t="s">
-        <v>275</v>
+        <v>357</v>
       </c>
       <c r="G208" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6406,16 +6406,16 @@
         <v>163</v>
       </c>
       <c r="D209" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="E209" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="F209" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="G209" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6544,16 +6544,16 @@
         <v>163</v>
       </c>
       <c r="D215" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="E215" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
       <c r="F215" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="G215" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6659,16 +6659,16 @@
         <v>163</v>
       </c>
       <c r="D220" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="E220" t="s">
-        <v>364</v>
+        <v>270</v>
       </c>
       <c r="F220" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="G220" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6797,16 +6797,16 @@
         <v>163</v>
       </c>
       <c r="D226" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="E226" t="s">
-        <v>364</v>
+        <v>276</v>
       </c>
       <c r="F226" t="s">
-        <v>275</v>
+        <v>365</v>
       </c>
       <c r="G226" t="s">
-        <v>276</v>
+        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6843,16 +6843,16 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>363</v>
+        <v>164</v>
       </c>
       <c r="E228" t="s">
-        <v>364</v>
+        <v>165</v>
       </c>
       <c r="F228" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="G228" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6866,16 +6866,16 @@
         <v>163</v>
       </c>
       <c r="D229" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="E229" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F229" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="G229" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6889,16 +6889,16 @@
         <v>163</v>
       </c>
       <c r="D230" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="E230" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F230" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="G230" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6912,16 +6912,16 @@
         <v>163</v>
       </c>
       <c r="D231" t="s">
-        <v>363</v>
+        <v>293</v>
       </c>
       <c r="E231" t="s">
-        <v>386</v>
+        <v>270</v>
       </c>
       <c r="F231" t="s">
-        <v>271</v>
+        <v>387</v>
       </c>
       <c r="G231" t="s">
-        <v>293</v>
+        <v>366</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6935,16 +6935,16 @@
         <v>163</v>
       </c>
       <c r="D232" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="E232" t="s">
-        <v>386</v>
+        <v>270</v>
       </c>
       <c r="F232" t="s">
-        <v>271</v>
+        <v>387</v>
       </c>
       <c r="G232" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6958,16 +6958,16 @@
         <v>163</v>
       </c>
       <c r="D233" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="E233" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F233" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="G233" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6981,16 +6981,16 @@
         <v>163</v>
       </c>
       <c r="D234" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="E234" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F234" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="G234" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7004,16 +7004,16 @@
         <v>163</v>
       </c>
       <c r="D235" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="E235" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F235" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="G235" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7027,16 +7027,16 @@
         <v>163</v>
       </c>
       <c r="D236" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="E236" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F236" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="G236" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7050,16 +7050,16 @@
         <v>163</v>
       </c>
       <c r="D237" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="E237" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F237" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="G237" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7073,16 +7073,16 @@
         <v>163</v>
       </c>
       <c r="D238" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="E238" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F238" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="G238" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7096,16 +7096,16 @@
         <v>163</v>
       </c>
       <c r="D239" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="E239" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="F239" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="G239" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7119,16 +7119,16 @@
         <v>163</v>
       </c>
       <c r="D240" t="s">
+        <v>164</v>
+      </c>
+      <c r="E240" t="s">
+        <v>165</v>
+      </c>
+      <c r="F240" t="s">
         <v>401</v>
       </c>
-      <c r="E240" t="s">
+      <c r="G240" t="s">
         <v>402</v>
-      </c>
-      <c r="F240" t="s">
-        <v>164</v>
-      </c>
-      <c r="G240" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7142,16 +7142,16 @@
         <v>163</v>
       </c>
       <c r="D241" t="s">
+        <v>164</v>
+      </c>
+      <c r="E241" t="s">
+        <v>165</v>
+      </c>
+      <c r="F241" t="s">
         <v>401</v>
       </c>
-      <c r="E241" t="s">
+      <c r="G241" t="s">
         <v>402</v>
-      </c>
-      <c r="F241" t="s">
-        <v>164</v>
-      </c>
-      <c r="G241" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7165,16 +7165,16 @@
         <v>163</v>
       </c>
       <c r="D242" t="s">
+        <v>164</v>
+      </c>
+      <c r="E242" t="s">
+        <v>165</v>
+      </c>
+      <c r="F242" t="s">
         <v>401</v>
       </c>
-      <c r="E242" t="s">
+      <c r="G242" t="s">
         <v>402</v>
-      </c>
-      <c r="F242" t="s">
-        <v>164</v>
-      </c>
-      <c r="G242" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7188,16 +7188,16 @@
         <v>163</v>
       </c>
       <c r="D243" t="s">
+        <v>164</v>
+      </c>
+      <c r="E243" t="s">
+        <v>165</v>
+      </c>
+      <c r="F243" t="s">
         <v>401</v>
       </c>
-      <c r="E243" t="s">
+      <c r="G243" t="s">
         <v>402</v>
-      </c>
-      <c r="F243" t="s">
-        <v>164</v>
-      </c>
-      <c r="G243" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7211,16 +7211,16 @@
         <v>163</v>
       </c>
       <c r="D244" t="s">
+        <v>164</v>
+      </c>
+      <c r="E244" t="s">
+        <v>165</v>
+      </c>
+      <c r="F244" t="s">
         <v>401</v>
       </c>
-      <c r="E244" t="s">
+      <c r="G244" t="s">
         <v>402</v>
-      </c>
-      <c r="F244" t="s">
-        <v>164</v>
-      </c>
-      <c r="G244" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7234,16 +7234,16 @@
         <v>163</v>
       </c>
       <c r="D245" t="s">
+        <v>164</v>
+      </c>
+      <c r="E245" t="s">
+        <v>165</v>
+      </c>
+      <c r="F245" t="s">
         <v>401</v>
       </c>
-      <c r="E245" t="s">
+      <c r="G245" t="s">
         <v>402</v>
-      </c>
-      <c r="F245" t="s">
-        <v>164</v>
-      </c>
-      <c r="G245" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7257,16 +7257,16 @@
         <v>163</v>
       </c>
       <c r="D246" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="E246" t="s">
-        <v>409</v>
+        <v>256</v>
       </c>
       <c r="F246" t="s">
-        <v>255</v>
+        <v>410</v>
       </c>
       <c r="G246" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7280,13 +7280,13 @@
         <v>95</v>
       </c>
       <c r="D247" t="s">
+        <v>96</v>
+      </c>
+      <c r="E247" t="s">
+        <v>97</v>
+      </c>
+      <c r="G247" t="s">
         <v>412</v>
-      </c>
-      <c r="F247" t="s">
-        <v>96</v>
-      </c>
-      <c r="G247" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7300,13 +7300,13 @@
         <v>95</v>
       </c>
       <c r="D248" t="s">
+        <v>96</v>
+      </c>
+      <c r="E248" t="s">
+        <v>97</v>
+      </c>
+      <c r="G248" t="s">
         <v>412</v>
-      </c>
-      <c r="F248" t="s">
-        <v>96</v>
-      </c>
-      <c r="G248" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7320,13 +7320,13 @@
         <v>95</v>
       </c>
       <c r="D249" t="s">
+        <v>415</v>
+      </c>
+      <c r="E249" t="s">
+        <v>416</v>
+      </c>
+      <c r="G249" t="s">
         <v>412</v>
-      </c>
-      <c r="F249" t="s">
-        <v>415</v>
-      </c>
-      <c r="G249" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7340,13 +7340,13 @@
         <v>95</v>
       </c>
       <c r="D250" t="s">
+        <v>96</v>
+      </c>
+      <c r="E250" t="s">
+        <v>97</v>
+      </c>
+      <c r="G250" t="s">
         <v>412</v>
-      </c>
-      <c r="F250" t="s">
-        <v>96</v>
-      </c>
-      <c r="G250" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7360,13 +7360,13 @@
         <v>95</v>
       </c>
       <c r="D251" t="s">
+        <v>96</v>
+      </c>
+      <c r="E251" t="s">
+        <v>97</v>
+      </c>
+      <c r="G251" t="s">
         <v>412</v>
-      </c>
-      <c r="F251" t="s">
-        <v>96</v>
-      </c>
-      <c r="G251" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7380,13 +7380,13 @@
         <v>95</v>
       </c>
       <c r="D252" t="s">
+        <v>96</v>
+      </c>
+      <c r="E252" t="s">
+        <v>97</v>
+      </c>
+      <c r="G252" t="s">
         <v>412</v>
-      </c>
-      <c r="F252" t="s">
-        <v>96</v>
-      </c>
-      <c r="G252" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7402,7 +7402,7 @@
       <c r="D253" t="s">
         <v>421</v>
       </c>
-      <c r="F253" t="s">
+      <c r="E253" t="s">
         <v>422</v>
       </c>
       <c r="G253" t="s">
@@ -7420,13 +7420,13 @@
         <v>90</v>
       </c>
       <c r="D254" t="s">
-        <v>421</v>
-      </c>
-      <c r="F254" t="s">
         <v>219</v>
       </c>
+      <c r="E254" t="s">
+        <v>220</v>
+      </c>
       <c r="G254" t="s">
-        <v>220</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7440,13 +7440,13 @@
         <v>90</v>
       </c>
       <c r="D255" t="s">
-        <v>421</v>
-      </c>
-      <c r="F255" t="s">
         <v>426</v>
       </c>
+      <c r="E255" t="s">
+        <v>427</v>
+      </c>
       <c r="G255" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7460,13 +7460,13 @@
         <v>90</v>
       </c>
       <c r="D256" t="s">
-        <v>421</v>
-      </c>
-      <c r="F256" t="s">
         <v>426</v>
       </c>
+      <c r="E256" t="s">
+        <v>427</v>
+      </c>
       <c r="G256" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7480,13 +7480,13 @@
         <v>90</v>
       </c>
       <c r="D257" t="s">
-        <v>421</v>
-      </c>
-      <c r="F257" t="s">
         <v>426</v>
       </c>
+      <c r="E257" t="s">
+        <v>427</v>
+      </c>
       <c r="G257" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7500,13 +7500,13 @@
         <v>163</v>
       </c>
       <c r="D258" t="s">
-        <v>421</v>
-      </c>
-      <c r="F258" t="s">
-        <v>327</v>
+        <v>325</v>
+      </c>
+      <c r="E258" t="s">
+        <v>326</v>
       </c>
       <c r="G258" t="s">
-        <v>328</v>
+        <v>423</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7520,13 +7520,13 @@
         <v>90</v>
       </c>
       <c r="D259" t="s">
-        <v>421</v>
-      </c>
-      <c r="F259" t="s">
         <v>426</v>
       </c>
+      <c r="E259" t="s">
+        <v>427</v>
+      </c>
       <c r="G259" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7540,13 +7540,13 @@
         <v>163</v>
       </c>
       <c r="D260" t="s">
-        <v>421</v>
-      </c>
-      <c r="F260" t="s">
         <v>164</v>
       </c>
+      <c r="E260" t="s">
+        <v>165</v>
+      </c>
       <c r="G260" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7560,13 +7560,13 @@
         <v>195</v>
       </c>
       <c r="D261" t="s">
-        <v>421</v>
-      </c>
-      <c r="F261" t="s">
         <v>434</v>
       </c>
+      <c r="E261" t="s">
+        <v>435</v>
+      </c>
       <c r="G261" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7580,13 +7580,13 @@
         <v>163</v>
       </c>
       <c r="D262" t="s">
-        <v>421</v>
-      </c>
-      <c r="F262" t="s">
         <v>164</v>
       </c>
+      <c r="E262" t="s">
+        <v>165</v>
+      </c>
       <c r="G262" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7600,13 +7600,13 @@
         <v>182</v>
       </c>
       <c r="D263" t="s">
-        <v>421</v>
-      </c>
-      <c r="F263" t="s">
         <v>438</v>
       </c>
+      <c r="E263" t="s">
+        <v>439</v>
+      </c>
       <c r="G263" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7620,13 +7620,13 @@
         <v>31</v>
       </c>
       <c r="D264" t="s">
-        <v>421</v>
-      </c>
-      <c r="F264" t="s">
         <v>32</v>
       </c>
+      <c r="E264" t="s">
+        <v>33</v>
+      </c>
       <c r="G264" t="s">
-        <v>33</v>
+        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7640,13 +7640,13 @@
         <v>9</v>
       </c>
       <c r="D265" t="s">
-        <v>421</v>
-      </c>
-      <c r="F265" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="E265" t="s">
+        <v>11</v>
       </c>
       <c r="G265" t="s">
-        <v>13</v>
+        <v>423</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7660,13 +7660,13 @@
         <v>112</v>
       </c>
       <c r="D266" t="s">
-        <v>421</v>
-      </c>
-      <c r="F266" t="s">
         <v>443</v>
       </c>
+      <c r="E266" t="s">
+        <v>444</v>
+      </c>
       <c r="G266" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7680,13 +7680,13 @@
         <v>112</v>
       </c>
       <c r="D267" t="s">
+        <v>118</v>
+      </c>
+      <c r="E267" t="s">
+        <v>119</v>
+      </c>
+      <c r="G267" t="s">
         <v>446</v>
-      </c>
-      <c r="F267" t="s">
-        <v>118</v>
-      </c>
-      <c r="G267" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7700,13 +7700,13 @@
         <v>182</v>
       </c>
       <c r="D268" t="s">
+        <v>202</v>
+      </c>
+      <c r="E268" t="s">
+        <v>203</v>
+      </c>
+      <c r="G268" t="s">
         <v>448</v>
-      </c>
-      <c r="F268" t="s">
-        <v>203</v>
-      </c>
-      <c r="G268" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7720,13 +7720,13 @@
         <v>112</v>
       </c>
       <c r="D269" t="s">
+        <v>118</v>
+      </c>
+      <c r="E269" t="s">
+        <v>119</v>
+      </c>
+      <c r="G269" t="s">
         <v>450</v>
-      </c>
-      <c r="F269" t="s">
-        <v>118</v>
-      </c>
-      <c r="G269" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7740,13 +7740,13 @@
         <v>112</v>
       </c>
       <c r="D270" t="s">
+        <v>118</v>
+      </c>
+      <c r="E270" t="s">
+        <v>119</v>
+      </c>
+      <c r="G270" t="s">
         <v>450</v>
-      </c>
-      <c r="F270" t="s">
-        <v>118</v>
-      </c>
-      <c r="G270" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7762,7 +7762,7 @@
       <c r="D271" t="s">
         <v>453</v>
       </c>
-      <c r="F271" t="s">
+      <c r="E271" t="s">
         <v>454</v>
       </c>
       <c r="G271" t="s">
@@ -7782,7 +7782,7 @@
       <c r="D272" t="s">
         <v>453</v>
       </c>
-      <c r="F272" t="s">
+      <c r="E272" t="s">
         <v>454</v>
       </c>
       <c r="G272" t="s">
@@ -7802,7 +7802,7 @@
       <c r="D273" t="s">
         <v>453</v>
       </c>
-      <c r="F273" t="s">
+      <c r="E273" t="s">
         <v>454</v>
       </c>
       <c r="G273" t="s">
@@ -7822,7 +7822,7 @@
       <c r="D274" t="s">
         <v>453</v>
       </c>
-      <c r="F274" t="s">
+      <c r="E274" t="s">
         <v>454</v>
       </c>
       <c r="G274" t="s">
@@ -7842,7 +7842,7 @@
       <c r="D275" t="s">
         <v>453</v>
       </c>
-      <c r="F275" t="s">
+      <c r="E275" t="s">
         <v>454</v>
       </c>
       <c r="G275" t="s">
@@ -7862,7 +7862,7 @@
       <c r="D276" t="s">
         <v>453</v>
       </c>
-      <c r="F276" t="s">
+      <c r="E276" t="s">
         <v>454</v>
       </c>
       <c r="G276" t="s">
@@ -7882,7 +7882,7 @@
       <c r="D277" t="s">
         <v>453</v>
       </c>
-      <c r="F277" t="s">
+      <c r="E277" t="s">
         <v>454</v>
       </c>
       <c r="G277" t="s">
@@ -7900,13 +7900,13 @@
         <v>182</v>
       </c>
       <c r="D278" t="s">
+        <v>202</v>
+      </c>
+      <c r="E278" t="s">
+        <v>203</v>
+      </c>
+      <c r="G278" t="s">
         <v>463</v>
-      </c>
-      <c r="F278" t="s">
-        <v>203</v>
-      </c>
-      <c r="G278" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7920,13 +7920,13 @@
         <v>31</v>
       </c>
       <c r="D279" t="s">
+        <v>51</v>
+      </c>
+      <c r="E279" t="s">
+        <v>52</v>
+      </c>
+      <c r="G279" t="s">
         <v>463</v>
-      </c>
-      <c r="F279" t="s">
-        <v>53</v>
-      </c>
-      <c r="G279" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7940,13 +7940,13 @@
         <v>9</v>
       </c>
       <c r="D280" t="s">
+        <v>10</v>
+      </c>
+      <c r="E280" t="s">
+        <v>11</v>
+      </c>
+      <c r="G280" t="s">
         <v>463</v>
-      </c>
-      <c r="F280" t="s">
-        <v>12</v>
-      </c>
-      <c r="G280" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7960,13 +7960,13 @@
         <v>112</v>
       </c>
       <c r="D281" t="s">
+        <v>170</v>
+      </c>
+      <c r="E281" t="s">
+        <v>171</v>
+      </c>
+      <c r="G281" t="s">
         <v>463</v>
-      </c>
-      <c r="F281" t="s">
-        <v>170</v>
-      </c>
-      <c r="G281" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7980,13 +7980,13 @@
         <v>124</v>
       </c>
       <c r="D282" t="s">
+        <v>125</v>
+      </c>
+      <c r="E282" t="s">
+        <v>126</v>
+      </c>
+      <c r="G282" t="s">
         <v>463</v>
-      </c>
-      <c r="F282" t="s">
-        <v>125</v>
-      </c>
-      <c r="G282" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -8000,13 +8000,13 @@
         <v>163</v>
       </c>
       <c r="D283" t="s">
+        <v>398</v>
+      </c>
+      <c r="E283" t="s">
+        <v>364</v>
+      </c>
+      <c r="G283" t="s">
         <v>469</v>
-      </c>
-      <c r="F283" t="s">
-        <v>365</v>
-      </c>
-      <c r="G283" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8020,13 +8020,13 @@
         <v>124</v>
       </c>
       <c r="D284" t="s">
+        <v>125</v>
+      </c>
+      <c r="E284" t="s">
+        <v>126</v>
+      </c>
+      <c r="G284" t="s">
         <v>471</v>
-      </c>
-      <c r="F284" t="s">
-        <v>125</v>
-      </c>
-      <c r="G284" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8040,13 +8040,13 @@
         <v>112</v>
       </c>
       <c r="D285" t="s">
+        <v>170</v>
+      </c>
+      <c r="E285" t="s">
+        <v>171</v>
+      </c>
+      <c r="G285" t="s">
         <v>473</v>
-      </c>
-      <c r="F285" t="s">
-        <v>170</v>
-      </c>
-      <c r="G285" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8060,13 +8060,13 @@
         <v>182</v>
       </c>
       <c r="D286" t="s">
+        <v>438</v>
+      </c>
+      <c r="E286" t="s">
+        <v>439</v>
+      </c>
+      <c r="G286" t="s">
         <v>475</v>
-      </c>
-      <c r="F286" t="s">
-        <v>438</v>
-      </c>
-      <c r="G286" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8080,13 +8080,13 @@
         <v>182</v>
       </c>
       <c r="D287" t="s">
+        <v>438</v>
+      </c>
+      <c r="E287" t="s">
+        <v>439</v>
+      </c>
+      <c r="G287" t="s">
         <v>475</v>
-      </c>
-      <c r="F287" t="s">
-        <v>438</v>
-      </c>
-      <c r="G287" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8100,13 +8100,13 @@
         <v>9</v>
       </c>
       <c r="D288" t="s">
+        <v>41</v>
+      </c>
+      <c r="E288" t="s">
+        <v>42</v>
+      </c>
+      <c r="G288" t="s">
         <v>475</v>
-      </c>
-      <c r="F288" t="s">
-        <v>41</v>
-      </c>
-      <c r="G288" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8120,13 +8120,13 @@
         <v>31</v>
       </c>
       <c r="D289" t="s">
+        <v>32</v>
+      </c>
+      <c r="E289" t="s">
+        <v>33</v>
+      </c>
+      <c r="G289" t="s">
         <v>475</v>
-      </c>
-      <c r="F289" t="s">
-        <v>32</v>
-      </c>
-      <c r="G289" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8140,13 +8140,13 @@
         <v>31</v>
       </c>
       <c r="D290" t="s">
+        <v>32</v>
+      </c>
+      <c r="E290" t="s">
+        <v>33</v>
+      </c>
+      <c r="G290" t="s">
         <v>475</v>
-      </c>
-      <c r="F290" t="s">
-        <v>32</v>
-      </c>
-      <c r="G290" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8160,13 +8160,13 @@
         <v>112</v>
       </c>
       <c r="D291" t="s">
+        <v>170</v>
+      </c>
+      <c r="E291" t="s">
+        <v>171</v>
+      </c>
+      <c r="G291" t="s">
         <v>475</v>
-      </c>
-      <c r="F291" t="s">
-        <v>170</v>
-      </c>
-      <c r="G291" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8180,13 +8180,13 @@
         <v>112</v>
       </c>
       <c r="D292" t="s">
+        <v>170</v>
+      </c>
+      <c r="E292" t="s">
+        <v>171</v>
+      </c>
+      <c r="G292" t="s">
         <v>475</v>
-      </c>
-      <c r="F292" t="s">
-        <v>170</v>
-      </c>
-      <c r="G292" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8200,13 +8200,13 @@
         <v>112</v>
       </c>
       <c r="D293" t="s">
+        <v>170</v>
+      </c>
+      <c r="E293" t="s">
+        <v>171</v>
+      </c>
+      <c r="G293" t="s">
         <v>475</v>
-      </c>
-      <c r="F293" t="s">
-        <v>170</v>
-      </c>
-      <c r="G293" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8220,13 +8220,13 @@
         <v>112</v>
       </c>
       <c r="D294" t="s">
+        <v>170</v>
+      </c>
+      <c r="E294" t="s">
+        <v>171</v>
+      </c>
+      <c r="G294" t="s">
         <v>475</v>
-      </c>
-      <c r="F294" t="s">
-        <v>170</v>
-      </c>
-      <c r="G294" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8240,13 +8240,13 @@
         <v>112</v>
       </c>
       <c r="D295" t="s">
+        <v>170</v>
+      </c>
+      <c r="E295" t="s">
+        <v>171</v>
+      </c>
+      <c r="G295" t="s">
         <v>485</v>
-      </c>
-      <c r="F295" t="s">
-        <v>170</v>
-      </c>
-      <c r="G295" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8260,13 +8260,13 @@
         <v>112</v>
       </c>
       <c r="D296" t="s">
+        <v>170</v>
+      </c>
+      <c r="E296" t="s">
+        <v>171</v>
+      </c>
+      <c r="G296" t="s">
         <v>485</v>
-      </c>
-      <c r="F296" t="s">
-        <v>170</v>
-      </c>
-      <c r="G296" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,18 +22,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
@@ -43,54 +43,54 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,72 +112,72 @@
     <t>07 - Health</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>09.2.2 - Upper‐secondary education (IS)</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -187,21 +187,21 @@
     <t>12182</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -289,12 +289,12 @@
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>140</t>
   </si>
   <si>
@@ -304,12 +304,12 @@
     <t>05 - Environmental protection</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -565,12 +565,12 @@
     <t>10 - Social protection</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>02 - Defence</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,12 +622,12 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>160</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,30 +655,30 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,27 +811,27 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>230</t>
   </si>
   <si>
@@ -841,12 +841,12 @@
     <t>23112</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>04.3.3 - Nuclear fuel (CS)</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,15 +991,15 @@
     <t>31110</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>310</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>04.2.2 - Forestry (CS)</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>04.2.3 - Fishing and hunting (CS)</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,15 +1105,15 @@
     <t>32110</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,12 +1210,12 @@
     <t>32310</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>04.4.3 - Construction (CS)</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,12 +1279,12 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>430</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>43031</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,10 +1375,10 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>600</t>
@@ -1866,13 +1866,13 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -1912,13 +1912,13 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -1932,10 +1932,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -1955,7 +1955,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1964,7 +1964,7 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -1978,10 +1978,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -2001,10 +2001,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
@@ -2024,16 +2024,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2047,16 +2047,16 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -2070,16 +2070,16 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>36</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2093,13 +2093,13 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
         <v>39</v>
@@ -2116,16 +2116,16 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
         <v>41</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>42</v>
-      </c>
-      <c r="F14" t="s">
-        <v>39</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -2139,10 +2139,10 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>45</v>
@@ -2162,16 +2162,16 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
         <v>48</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>49</v>
-      </c>
-      <c r="F16" t="s">
-        <v>46</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -2185,10 +2185,10 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
         <v>31</v>
-      </c>
-      <c r="D17" t="s">
-        <v>51</v>
       </c>
       <c r="E17" t="s">
         <v>52</v>
@@ -2208,10 +2208,10 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
         <v>31</v>
-      </c>
-      <c r="D18" t="s">
-        <v>51</v>
       </c>
       <c r="E18" t="s">
         <v>52</v>
@@ -2231,16 +2231,16 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
         <v>31</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>57</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>58</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
       </c>
       <c r="G19" t="s">
         <v>54</v>
@@ -2254,16 +2254,16 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
         <v>31</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>60</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>61</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
       </c>
       <c r="G20" t="s">
         <v>54</v>
@@ -2277,10 +2277,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
         <v>31</v>
-      </c>
-      <c r="D21" t="s">
-        <v>51</v>
       </c>
       <c r="E21" t="s">
         <v>52</v>
@@ -2300,16 +2300,16 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
         <v>31</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>32</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>33</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
       </c>
       <c r="G22" t="s">
         <v>54</v>
@@ -2323,16 +2323,16 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
         <v>31</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>66</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>67</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
       </c>
       <c r="G23" t="s">
         <v>54</v>
@@ -2346,16 +2346,16 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
         <v>31</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>33</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
       </c>
       <c r="G24" t="s">
         <v>54</v>
@@ -2369,16 +2369,16 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
         <v>31</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>33</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
       </c>
       <c r="G25" t="s">
         <v>54</v>
@@ -2392,16 +2392,16 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" t="s">
         <v>31</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>32</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>33</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
       </c>
       <c r="G26" t="s">
         <v>54</v>
@@ -2415,16 +2415,16 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
         <v>31</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>33</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
       </c>
       <c r="G27" t="s">
         <v>54</v>
@@ -2438,16 +2438,16 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
         <v>31</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>32</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>33</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
       </c>
       <c r="G28" t="s">
         <v>54</v>
@@ -2461,16 +2461,16 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
         <v>31</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>32</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>33</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
       </c>
       <c r="G29" t="s">
         <v>54</v>
@@ -2484,16 +2484,16 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" t="s">
         <v>31</v>
-      </c>
-      <c r="D30" t="s">
-        <v>51</v>
       </c>
       <c r="E30" t="s">
         <v>52</v>
       </c>
       <c r="F30" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="G30" t="s">
         <v>54</v>
@@ -2507,16 +2507,16 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" t="s">
         <v>31</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>32</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>33</v>
-      </c>
-      <c r="F31" t="s">
-        <v>76</v>
       </c>
       <c r="G31" t="s">
         <v>54</v>
@@ -2530,16 +2530,16 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" t="s">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>32</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>33</v>
-      </c>
-      <c r="F32" t="s">
-        <v>76</v>
       </c>
       <c r="G32" t="s">
         <v>54</v>
@@ -2553,16 +2553,16 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" t="s">
         <v>31</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>32</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>33</v>
-      </c>
-      <c r="F33" t="s">
-        <v>76</v>
       </c>
       <c r="G33" t="s">
         <v>54</v>
@@ -2576,16 +2576,16 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" t="s">
         <v>31</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>32</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>33</v>
-      </c>
-      <c r="F34" t="s">
-        <v>76</v>
       </c>
       <c r="G34" t="s">
         <v>54</v>
@@ -2599,16 +2599,16 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
         <v>31</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>32</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>33</v>
-      </c>
-      <c r="F35" t="s">
-        <v>76</v>
       </c>
       <c r="G35" t="s">
         <v>54</v>
@@ -2622,16 +2622,16 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" t="s">
         <v>31</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>57</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>58</v>
-      </c>
-      <c r="F36" t="s">
-        <v>76</v>
       </c>
       <c r="G36" t="s">
         <v>54</v>
@@ -2644,13 +2644,13 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>31</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>32</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>33</v>
       </c>
       <c r="G37" t="s">
@@ -2664,13 +2664,13 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>31</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>32</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>33</v>
       </c>
       <c r="G38" t="s">
@@ -2684,13 +2684,13 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>31</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>32</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>33</v>
       </c>
       <c r="G39" t="s">
@@ -2704,13 +2704,13 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>31</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>32</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>33</v>
       </c>
       <c r="G40" t="s">
@@ -2724,14 +2724,14 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>31</v>
-      </c>
-      <c r="D41" t="s">
-        <v>51</v>
       </c>
       <c r="E41" t="s">
         <v>52</v>
+      </c>
+      <c r="F41" t="s">
+        <v>53</v>
       </c>
       <c r="G41" t="s">
         <v>83</v>
@@ -2744,13 +2744,13 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>31</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>57</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>58</v>
       </c>
       <c r="G42" t="s">
@@ -2764,13 +2764,13 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>90</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>91</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>92</v>
       </c>
       <c r="G43" t="s">
@@ -2784,13 +2784,13 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>95</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>96</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>97</v>
       </c>
       <c r="G44" t="s">
@@ -2804,13 +2804,13 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>90</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>91</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>92</v>
       </c>
       <c r="G45" t="s">
@@ -2824,13 +2824,13 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>90</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>91</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>92</v>
       </c>
       <c r="G46" t="s">
@@ -2844,13 +2844,13 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>95</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>101</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>102</v>
       </c>
       <c r="G47" t="s">
@@ -2864,13 +2864,13 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>90</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>91</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>92</v>
       </c>
       <c r="G48" t="s">
@@ -2884,13 +2884,13 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>90</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>91</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>92</v>
       </c>
       <c r="G49" t="s">
@@ -2904,13 +2904,13 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>95</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>101</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>102</v>
       </c>
       <c r="G50" t="s">
@@ -2924,13 +2924,13 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>90</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>91</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>92</v>
       </c>
       <c r="G51" t="s">
@@ -2944,13 +2944,13 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>95</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>108</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>109</v>
       </c>
       <c r="G52" t="s">
@@ -2964,14 +2964,14 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C53" t="s">
-        <v>9</v>
-      </c>
       <c r="D53" t="s">
         <v>10</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
+      </c>
+      <c r="F53" t="s">
+        <v>12</v>
       </c>
       <c r="G53" t="s">
         <v>93</v>
@@ -3011,13 +3011,13 @@
         <v>112</v>
       </c>
       <c r="D55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E55" t="s">
         <v>118</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>119</v>
-      </c>
-      <c r="F55" t="s">
-        <v>115</v>
       </c>
       <c r="G55" t="s">
         <v>116</v>
@@ -3034,13 +3034,13 @@
         <v>112</v>
       </c>
       <c r="D56" t="s">
+        <v>113</v>
+      </c>
+      <c r="E56" t="s">
         <v>121</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>122</v>
-      </c>
-      <c r="F56" t="s">
-        <v>115</v>
       </c>
       <c r="G56" t="s">
         <v>116</v>
@@ -3054,16 +3054,16 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
         <v>124</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>125</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>126</v>
-      </c>
-      <c r="F57" t="s">
-        <v>115</v>
       </c>
       <c r="G57" t="s">
         <v>116</v>
@@ -3080,13 +3080,13 @@
         <v>112</v>
       </c>
       <c r="D58" t="s">
+        <v>113</v>
+      </c>
+      <c r="E58" t="s">
         <v>118</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>119</v>
-      </c>
-      <c r="F58" t="s">
-        <v>115</v>
       </c>
       <c r="G58" t="s">
         <v>116</v>
@@ -3103,13 +3103,13 @@
         <v>112</v>
       </c>
       <c r="D59" t="s">
+        <v>113</v>
+      </c>
+      <c r="E59" t="s">
         <v>118</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>119</v>
-      </c>
-      <c r="F59" t="s">
-        <v>115</v>
       </c>
       <c r="G59" t="s">
         <v>116</v>
@@ -3126,13 +3126,13 @@
         <v>112</v>
       </c>
       <c r="D60" t="s">
+        <v>113</v>
+      </c>
+      <c r="E60" t="s">
         <v>118</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>119</v>
-      </c>
-      <c r="F60" t="s">
-        <v>115</v>
       </c>
       <c r="G60" t="s">
         <v>116</v>
@@ -3149,13 +3149,13 @@
         <v>112</v>
       </c>
       <c r="D61" t="s">
+        <v>113</v>
+      </c>
+      <c r="E61" t="s">
         <v>118</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>119</v>
-      </c>
-      <c r="F61" t="s">
-        <v>115</v>
       </c>
       <c r="G61" t="s">
         <v>116</v>
@@ -3172,13 +3172,13 @@
         <v>112</v>
       </c>
       <c r="D62" t="s">
+        <v>113</v>
+      </c>
+      <c r="E62" t="s">
         <v>118</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>119</v>
-      </c>
-      <c r="F62" t="s">
-        <v>115</v>
       </c>
       <c r="G62" t="s">
         <v>116</v>
@@ -3195,13 +3195,13 @@
         <v>112</v>
       </c>
       <c r="D63" t="s">
+        <v>113</v>
+      </c>
+      <c r="E63" t="s">
+        <v>118</v>
+      </c>
+      <c r="F63" t="s">
         <v>133</v>
-      </c>
-      <c r="E63" t="s">
-        <v>119</v>
-      </c>
-      <c r="F63" t="s">
-        <v>115</v>
       </c>
       <c r="G63" t="s">
         <v>116</v>
@@ -3218,13 +3218,13 @@
         <v>112</v>
       </c>
       <c r="D64" t="s">
+        <v>113</v>
+      </c>
+      <c r="E64" t="s">
+        <v>118</v>
+      </c>
+      <c r="F64" t="s">
         <v>133</v>
-      </c>
-      <c r="E64" t="s">
-        <v>119</v>
-      </c>
-      <c r="F64" t="s">
-        <v>115</v>
       </c>
       <c r="G64" t="s">
         <v>116</v>
@@ -3241,13 +3241,13 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
+        <v>113</v>
+      </c>
+      <c r="E65" t="s">
         <v>136</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>137</v>
-      </c>
-      <c r="F65" t="s">
-        <v>115</v>
       </c>
       <c r="G65" t="s">
         <v>116</v>
@@ -3287,13 +3287,13 @@
         <v>112</v>
       </c>
       <c r="D67" t="s">
+        <v>113</v>
+      </c>
+      <c r="E67" t="s">
         <v>118</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>119</v>
-      </c>
-      <c r="F67" t="s">
-        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>116</v>
@@ -3310,13 +3310,13 @@
         <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="G68" t="s">
         <v>116</v>
@@ -3333,13 +3333,13 @@
         <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G69" t="s">
         <v>116</v>
@@ -3356,13 +3356,13 @@
         <v>112</v>
       </c>
       <c r="D70" t="s">
+        <v>113</v>
+      </c>
+      <c r="E70" t="s">
         <v>121</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>122</v>
-      </c>
-      <c r="F70" t="s">
-        <v>115</v>
       </c>
       <c r="G70" t="s">
         <v>116</v>
@@ -3379,13 +3379,13 @@
         <v>112</v>
       </c>
       <c r="D71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E71" t="s">
         <v>121</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>122</v>
-      </c>
-      <c r="F71" t="s">
-        <v>115</v>
       </c>
       <c r="G71" t="s">
         <v>116</v>
@@ -3422,16 +3422,16 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" t="s">
         <v>124</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>148</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>149</v>
-      </c>
-      <c r="F73" t="s">
-        <v>115</v>
       </c>
       <c r="G73" t="s">
         <v>116</v>
@@ -3445,16 +3445,16 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" t="s">
         <v>124</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>151</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>152</v>
-      </c>
-      <c r="F74" t="s">
-        <v>115</v>
       </c>
       <c r="G74" t="s">
         <v>116</v>
@@ -3468,16 +3468,16 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" t="s">
         <v>124</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>154</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>155</v>
-      </c>
-      <c r="F75" t="s">
-        <v>115</v>
       </c>
       <c r="G75" t="s">
         <v>116</v>
@@ -3491,16 +3491,16 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" t="s">
         <v>124</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>148</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>149</v>
-      </c>
-      <c r="F76" t="s">
-        <v>115</v>
       </c>
       <c r="G76" t="s">
         <v>116</v>
@@ -3514,16 +3514,16 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" t="s">
         <v>124</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>148</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>149</v>
-      </c>
-      <c r="F77" t="s">
-        <v>115</v>
       </c>
       <c r="G77" t="s">
         <v>116</v>
@@ -3537,16 +3537,16 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" t="s">
         <v>124</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>151</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>152</v>
-      </c>
-      <c r="F78" t="s">
-        <v>115</v>
       </c>
       <c r="G78" t="s">
         <v>116</v>
@@ -3560,16 +3560,16 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" t="s">
         <v>124</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>160</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>161</v>
-      </c>
-      <c r="F79" t="s">
-        <v>115</v>
       </c>
       <c r="G79" t="s">
         <v>116</v>
@@ -3583,16 +3583,16 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D80" t="s">
+        <v>163</v>
+      </c>
+      <c r="E80" t="s">
         <v>164</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>165</v>
-      </c>
-      <c r="F80" t="s">
-        <v>115</v>
       </c>
       <c r="G80" t="s">
         <v>116</v>
@@ -3606,16 +3606,16 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D81" t="s">
+        <v>163</v>
+      </c>
+      <c r="E81" t="s">
         <v>164</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>165</v>
-      </c>
-      <c r="F81" t="s">
-        <v>115</v>
       </c>
       <c r="G81" t="s">
         <v>116</v>
@@ -3629,16 +3629,16 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
+        <v>163</v>
+      </c>
+      <c r="E82" t="s">
         <v>164</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>165</v>
-      </c>
-      <c r="F82" t="s">
-        <v>115</v>
       </c>
       <c r="G82" t="s">
         <v>116</v>
@@ -3655,13 +3655,13 @@
         <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
       </c>
       <c r="F83" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G83" t="s">
         <v>116</v>
@@ -3678,13 +3678,13 @@
         <v>112</v>
       </c>
       <c r="D84" t="s">
+        <v>113</v>
+      </c>
+      <c r="E84" t="s">
         <v>170</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>171</v>
-      </c>
-      <c r="F84" t="s">
-        <v>115</v>
       </c>
       <c r="G84" t="s">
         <v>116</v>
@@ -3701,13 +3701,13 @@
         <v>112</v>
       </c>
       <c r="D85" t="s">
+        <v>113</v>
+      </c>
+      <c r="E85" t="s">
+        <v>118</v>
+      </c>
+      <c r="F85" t="s">
         <v>173</v>
-      </c>
-      <c r="E85" t="s">
-        <v>119</v>
-      </c>
-      <c r="F85" t="s">
-        <v>115</v>
       </c>
       <c r="G85" t="s">
         <v>116</v>
@@ -3721,16 +3721,16 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D86" t="s">
+        <v>163</v>
+      </c>
+      <c r="E86" t="s">
         <v>175</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>176</v>
-      </c>
-      <c r="F86" t="s">
-        <v>115</v>
       </c>
       <c r="G86" t="s">
         <v>116</v>
@@ -3747,13 +3747,13 @@
         <v>112</v>
       </c>
       <c r="D87" t="s">
+        <v>113</v>
+      </c>
+      <c r="E87" t="s">
+        <v>118</v>
+      </c>
+      <c r="F87" t="s">
         <v>173</v>
-      </c>
-      <c r="E87" t="s">
-        <v>119</v>
-      </c>
-      <c r="F87" t="s">
-        <v>115</v>
       </c>
       <c r="G87" t="s">
         <v>116</v>
@@ -3770,13 +3770,13 @@
         <v>112</v>
       </c>
       <c r="D88" t="s">
+        <v>113</v>
+      </c>
+      <c r="E88" t="s">
         <v>118</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>119</v>
-      </c>
-      <c r="F88" t="s">
-        <v>115</v>
       </c>
       <c r="G88" t="s">
         <v>116</v>
@@ -3793,13 +3793,13 @@
         <v>112</v>
       </c>
       <c r="D89" t="s">
+        <v>113</v>
+      </c>
+      <c r="E89" t="s">
         <v>118</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>119</v>
-      </c>
-      <c r="F89" t="s">
-        <v>115</v>
       </c>
       <c r="G89" t="s">
         <v>116</v>
@@ -3813,16 +3813,16 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
+        <v>112</v>
+      </c>
+      <c r="D90" t="s">
         <v>124</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>125</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>126</v>
-      </c>
-      <c r="F90" t="s">
-        <v>115</v>
       </c>
       <c r="G90" t="s">
         <v>116</v>
@@ -3836,16 +3836,16 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
+        <v>112</v>
+      </c>
+      <c r="D91" t="s">
         <v>182</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>183</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>184</v>
-      </c>
-      <c r="F91" t="s">
-        <v>115</v>
       </c>
       <c r="G91" t="s">
         <v>116</v>
@@ -3859,16 +3859,16 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" t="s">
         <v>124</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>125</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>126</v>
-      </c>
-      <c r="F92" t="s">
-        <v>115</v>
       </c>
       <c r="G92" t="s">
         <v>116</v>
@@ -3885,13 +3885,13 @@
         <v>112</v>
       </c>
       <c r="D93" t="s">
+        <v>113</v>
+      </c>
+      <c r="E93" t="s">
         <v>121</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>122</v>
-      </c>
-      <c r="F93" t="s">
-        <v>115</v>
       </c>
       <c r="G93" t="s">
         <v>116</v>
@@ -3905,16 +3905,16 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
         <v>124</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>125</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>126</v>
-      </c>
-      <c r="F94" t="s">
-        <v>115</v>
       </c>
       <c r="G94" t="s">
         <v>116</v>
@@ -3931,13 +3931,13 @@
         <v>112</v>
       </c>
       <c r="D95" t="s">
+        <v>113</v>
+      </c>
+      <c r="E95" t="s">
         <v>189</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>190</v>
-      </c>
-      <c r="F95" t="s">
-        <v>115</v>
       </c>
       <c r="G95" t="s">
         <v>116</v>
@@ -3951,16 +3951,16 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" t="s">
         <v>124</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>125</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>126</v>
-      </c>
-      <c r="F96" t="s">
-        <v>192</v>
       </c>
       <c r="G96" t="s">
         <v>116</v>
@@ -3974,16 +3974,16 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" t="s">
         <v>124</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>125</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>126</v>
-      </c>
-      <c r="F97" t="s">
-        <v>192</v>
       </c>
       <c r="G97" t="s">
         <v>116</v>
@@ -3997,16 +3997,16 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>192</v>
+      </c>
+      <c r="D98" t="s">
         <v>195</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>196</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>197</v>
-      </c>
-      <c r="F98" t="s">
-        <v>192</v>
       </c>
       <c r="G98" t="s">
         <v>116</v>
@@ -4020,16 +4020,16 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>192</v>
+      </c>
+      <c r="D99" t="s">
         <v>124</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>125</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>126</v>
-      </c>
-      <c r="F99" t="s">
-        <v>192</v>
       </c>
       <c r="G99" t="s">
         <v>116</v>
@@ -4043,16 +4043,16 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>192</v>
+      </c>
+      <c r="D100" t="s">
         <v>124</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>154</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>155</v>
-      </c>
-      <c r="F100" t="s">
-        <v>192</v>
       </c>
       <c r="G100" t="s">
         <v>116</v>
@@ -4066,16 +4066,16 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>192</v>
+      </c>
+      <c r="D101" t="s">
         <v>124</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>125</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>126</v>
-      </c>
-      <c r="F101" t="s">
-        <v>192</v>
       </c>
       <c r="G101" t="s">
         <v>116</v>
@@ -4088,13 +4088,13 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>182</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>202</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>203</v>
       </c>
       <c r="G102" t="s">
@@ -4108,13 +4108,13 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>182</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>202</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>203</v>
       </c>
       <c r="G103" t="s">
@@ -4128,13 +4128,13 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>182</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>202</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>203</v>
       </c>
       <c r="G104" t="s">
@@ -4148,13 +4148,13 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>182</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>208</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>209</v>
       </c>
       <c r="G105" t="s">
@@ -4168,13 +4168,13 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>182</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>202</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>203</v>
       </c>
       <c r="G106" t="s">
@@ -4188,13 +4188,13 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>182</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>183</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>184</v>
       </c>
       <c r="G107" t="s">
@@ -4208,13 +4208,13 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>182</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>213</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>214</v>
       </c>
       <c r="G108" t="s">
@@ -4228,13 +4228,13 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>90</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>216</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>217</v>
       </c>
       <c r="G109" t="s">
@@ -4248,13 +4248,13 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>90</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>219</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>220</v>
       </c>
       <c r="G110" t="s">
@@ -4268,13 +4268,13 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>182</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>202</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>203</v>
       </c>
       <c r="G111" t="s">
@@ -4288,13 +4288,13 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>223</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>224</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>225</v>
       </c>
       <c r="G112" t="s">
@@ -4308,14 +4308,14 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="C113" t="s">
-        <v>112</v>
-      </c>
       <c r="D113" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E113" t="s">
         <v>114</v>
+      </c>
+      <c r="F113" t="s">
+        <v>143</v>
       </c>
       <c r="G113" t="s">
         <v>204</v>
@@ -4328,13 +4328,13 @@
       <c r="B114" t="s">
         <v>8</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>124</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>151</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>152</v>
       </c>
       <c r="G114" t="s">
@@ -4348,13 +4348,13 @@
       <c r="B115" t="s">
         <v>8</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>182</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>183</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>184</v>
       </c>
       <c r="G115" t="s">
@@ -4368,13 +4368,13 @@
       <c r="B116" t="s">
         <v>8</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>223</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>230</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>231</v>
       </c>
       <c r="G116" t="s">
@@ -4388,13 +4388,13 @@
       <c r="B117" t="s">
         <v>8</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>223</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>224</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>225</v>
       </c>
       <c r="G117" t="s">
@@ -4408,14 +4408,14 @@
       <c r="B118" t="s">
         <v>8</v>
       </c>
-      <c r="C118" t="s">
-        <v>163</v>
-      </c>
       <c r="D118" t="s">
+        <v>163</v>
+      </c>
+      <c r="E118" t="s">
+        <v>164</v>
+      </c>
+      <c r="F118" t="s">
         <v>234</v>
-      </c>
-      <c r="E118" t="s">
-        <v>165</v>
       </c>
       <c r="G118" t="s">
         <v>204</v>
@@ -4428,13 +4428,13 @@
       <c r="B119" t="s">
         <v>8</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>182</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>183</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>184</v>
       </c>
       <c r="G119" t="s">
@@ -4448,13 +4448,13 @@
       <c r="B120" t="s">
         <v>8</v>
       </c>
-      <c r="C120" t="s">
-        <v>112</v>
-      </c>
       <c r="D120" t="s">
+        <v>113</v>
+      </c>
+      <c r="E120" t="s">
         <v>170</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>171</v>
       </c>
       <c r="G120" t="s">
@@ -4468,14 +4468,14 @@
       <c r="B121" t="s">
         <v>8</v>
       </c>
-      <c r="C121" t="s">
-        <v>112</v>
-      </c>
       <c r="D121" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E121" t="s">
         <v>114</v>
+      </c>
+      <c r="F121" t="s">
+        <v>143</v>
       </c>
       <c r="G121" t="s">
         <v>237</v>
@@ -4488,13 +4488,13 @@
       <c r="B122" t="s">
         <v>8</v>
       </c>
-      <c r="C122" t="s">
-        <v>112</v>
-      </c>
       <c r="D122" t="s">
+        <v>113</v>
+      </c>
+      <c r="E122" t="s">
         <v>170</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>171</v>
       </c>
       <c r="G122" t="s">
@@ -4508,13 +4508,13 @@
       <c r="B123" t="s">
         <v>8</v>
       </c>
-      <c r="C123" t="s">
-        <v>112</v>
-      </c>
       <c r="D123" t="s">
+        <v>113</v>
+      </c>
+      <c r="E123" t="s">
         <v>170</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
         <v>171</v>
       </c>
       <c r="G123" t="s">
@@ -4528,13 +4528,13 @@
       <c r="B124" t="s">
         <v>8</v>
       </c>
-      <c r="C124" t="s">
-        <v>163</v>
-      </c>
       <c r="D124" t="s">
+        <v>163</v>
+      </c>
+      <c r="E124" t="s">
         <v>242</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>243</v>
       </c>
       <c r="G124" t="s">
@@ -4548,13 +4548,13 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="C125" t="s">
-        <v>163</v>
-      </c>
       <c r="D125" t="s">
+        <v>163</v>
+      </c>
+      <c r="E125" t="s">
         <v>242</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>243</v>
       </c>
       <c r="G125" t="s">
@@ -4568,13 +4568,13 @@
       <c r="B126" t="s">
         <v>8</v>
       </c>
-      <c r="C126" t="s">
-        <v>163</v>
-      </c>
       <c r="D126" t="s">
+        <v>163</v>
+      </c>
+      <c r="E126" t="s">
         <v>242</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>243</v>
       </c>
       <c r="G126" t="s">
@@ -4588,13 +4588,13 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
-      <c r="C127" t="s">
-        <v>163</v>
-      </c>
       <c r="D127" t="s">
+        <v>163</v>
+      </c>
+      <c r="E127" t="s">
         <v>242</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>243</v>
       </c>
       <c r="G127" t="s">
@@ -4608,13 +4608,13 @@
       <c r="B128" t="s">
         <v>8</v>
       </c>
-      <c r="C128" t="s">
-        <v>163</v>
-      </c>
       <c r="D128" t="s">
+        <v>163</v>
+      </c>
+      <c r="E128" t="s">
         <v>242</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>243</v>
       </c>
       <c r="G128" t="s">
@@ -4628,14 +4628,14 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
-      <c r="C129" t="s">
-        <v>163</v>
-      </c>
       <c r="D129" t="s">
+        <v>163</v>
+      </c>
+      <c r="E129" t="s">
+        <v>242</v>
+      </c>
+      <c r="F129" t="s">
         <v>249</v>
-      </c>
-      <c r="E129" t="s">
-        <v>243</v>
       </c>
       <c r="G129" t="s">
         <v>237</v>
@@ -4648,14 +4648,14 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
-      <c r="C130" t="s">
-        <v>163</v>
-      </c>
       <c r="D130" t="s">
+        <v>163</v>
+      </c>
+      <c r="E130" t="s">
+        <v>242</v>
+      </c>
+      <c r="F130" t="s">
         <v>251</v>
-      </c>
-      <c r="E130" t="s">
-        <v>243</v>
       </c>
       <c r="G130" t="s">
         <v>237</v>
@@ -4668,14 +4668,14 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
-      <c r="C131" t="s">
-        <v>163</v>
-      </c>
       <c r="D131" t="s">
+        <v>163</v>
+      </c>
+      <c r="E131" t="s">
+        <v>242</v>
+      </c>
+      <c r="F131" t="s">
         <v>253</v>
-      </c>
-      <c r="E131" t="s">
-        <v>243</v>
       </c>
       <c r="G131" t="s">
         <v>237</v>
@@ -4688,13 +4688,13 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
-      <c r="C132" t="s">
-        <v>163</v>
-      </c>
       <c r="D132" t="s">
+        <v>163</v>
+      </c>
+      <c r="E132" t="s">
         <v>255</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>256</v>
       </c>
       <c r="G132" t="s">
@@ -4708,13 +4708,13 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
-      <c r="C133" t="s">
-        <v>112</v>
-      </c>
       <c r="D133" t="s">
+        <v>113</v>
+      </c>
+      <c r="E133" t="s">
         <v>189</v>
       </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
         <v>190</v>
       </c>
       <c r="G133" t="s">
@@ -4728,13 +4728,13 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
-      <c r="C134" t="s">
-        <v>163</v>
-      </c>
       <c r="D134" t="s">
+        <v>163</v>
+      </c>
+      <c r="E134" t="s">
         <v>175</v>
       </c>
-      <c r="E134" t="s">
+      <c r="F134" t="s">
         <v>176</v>
       </c>
       <c r="G134" t="s">
@@ -4748,13 +4748,13 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
-      <c r="C135" t="s">
-        <v>163</v>
-      </c>
       <c r="D135" t="s">
+        <v>163</v>
+      </c>
+      <c r="E135" t="s">
         <v>175</v>
       </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
         <v>176</v>
       </c>
       <c r="G135" t="s">
@@ -4768,13 +4768,13 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
-      <c r="C136" t="s">
-        <v>163</v>
-      </c>
       <c r="D136" t="s">
+        <v>163</v>
+      </c>
+      <c r="E136" t="s">
         <v>175</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>176</v>
       </c>
       <c r="G136" t="s">
@@ -4788,13 +4788,13 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="C137" t="s">
-        <v>163</v>
-      </c>
       <c r="D137" t="s">
+        <v>163</v>
+      </c>
+      <c r="E137" t="s">
         <v>175</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
         <v>176</v>
       </c>
       <c r="G137" t="s">
@@ -4808,13 +4808,13 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
-      <c r="C138" t="s">
-        <v>163</v>
-      </c>
       <c r="D138" t="s">
+        <v>163</v>
+      </c>
+      <c r="E138" t="s">
         <v>175</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
         <v>176</v>
       </c>
       <c r="G138" t="s">
@@ -4828,13 +4828,13 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" t="s">
         <v>223</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>265</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>266</v>
       </c>
       <c r="G139" t="s">
@@ -4848,13 +4848,13 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
-      <c r="C140" t="s">
-        <v>163</v>
-      </c>
       <c r="D140" t="s">
+        <v>163</v>
+      </c>
+      <c r="E140" t="s">
         <v>175</v>
       </c>
-      <c r="E140" t="s">
+      <c r="F140" t="s">
         <v>176</v>
       </c>
       <c r="G140" t="s">
@@ -4869,10 +4869,10 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D141" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E141" t="s">
         <v>270</v>
@@ -4892,10 +4892,10 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D142" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E142" t="s">
         <v>270</v>
@@ -4915,16 +4915,16 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D143" t="s">
+        <v>163</v>
+      </c>
+      <c r="E143" t="s">
         <v>275</v>
       </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>276</v>
-      </c>
-      <c r="F143" t="s">
-        <v>271</v>
       </c>
       <c r="G143" t="s">
         <v>272</v>
@@ -4938,16 +4938,16 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D144" t="s">
+        <v>163</v>
+      </c>
+      <c r="E144" t="s">
         <v>275</v>
       </c>
-      <c r="E144" t="s">
+      <c r="F144" t="s">
         <v>276</v>
-      </c>
-      <c r="F144" t="s">
-        <v>271</v>
       </c>
       <c r="G144" t="s">
         <v>272</v>
@@ -4961,16 +4961,16 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D145" t="s">
+        <v>163</v>
+      </c>
+      <c r="E145" t="s">
         <v>275</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" t="s">
         <v>276</v>
-      </c>
-      <c r="F145" t="s">
-        <v>271</v>
       </c>
       <c r="G145" t="s">
         <v>272</v>
@@ -4984,10 +4984,10 @@
         <v>8</v>
       </c>
       <c r="C146" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D146" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E146" t="s">
         <v>270</v>
@@ -5007,16 +5007,16 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D147" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E147" t="s">
         <v>270</v>
       </c>
       <c r="F147" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G147" t="s">
         <v>272</v>
@@ -5030,16 +5030,16 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D148" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E148" t="s">
         <v>270</v>
       </c>
       <c r="F148" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G148" t="s">
         <v>272</v>
@@ -5053,16 +5053,16 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D149" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E149" t="s">
         <v>270</v>
       </c>
       <c r="F149" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G149" t="s">
         <v>272</v>
@@ -5076,16 +5076,16 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D150" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E150" t="s">
         <v>270</v>
       </c>
       <c r="F150" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G150" t="s">
         <v>272</v>
@@ -5099,16 +5099,16 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D151" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E151" t="s">
         <v>270</v>
       </c>
       <c r="F151" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G151" t="s">
         <v>272</v>
@@ -5122,16 +5122,16 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D152" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E152" t="s">
         <v>270</v>
       </c>
       <c r="F152" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G152" t="s">
         <v>272</v>
@@ -5145,16 +5145,16 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D153" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E153" t="s">
         <v>270</v>
       </c>
       <c r="F153" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G153" t="s">
         <v>272</v>
@@ -5168,16 +5168,16 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D154" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E154" t="s">
         <v>270</v>
       </c>
       <c r="F154" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G154" t="s">
         <v>272</v>
@@ -5191,16 +5191,16 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E155" t="s">
         <v>270</v>
       </c>
       <c r="F155" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G155" t="s">
         <v>272</v>
@@ -5214,16 +5214,16 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D156" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E156" t="s">
         <v>270</v>
       </c>
       <c r="F156" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="G156" t="s">
         <v>272</v>
@@ -5237,16 +5237,16 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D157" t="s">
-        <v>293</v>
+        <v>163</v>
       </c>
       <c r="E157" t="s">
         <v>270</v>
       </c>
       <c r="F157" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G157" t="s">
         <v>272</v>
@@ -5260,16 +5260,16 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D158" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E158" t="s">
         <v>270</v>
       </c>
       <c r="F158" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="G158" t="s">
         <v>272</v>
@@ -5283,16 +5283,16 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D159" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E159" t="s">
         <v>270</v>
       </c>
       <c r="F159" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="G159" t="s">
         <v>272</v>
@@ -5306,16 +5306,16 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D160" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E160" t="s">
         <v>270</v>
       </c>
       <c r="F160" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="G160" t="s">
         <v>272</v>
@@ -5329,16 +5329,16 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D161" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E161" t="s">
         <v>270</v>
       </c>
       <c r="F161" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="G161" t="s">
         <v>272</v>
@@ -5352,16 +5352,16 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>163</v>
+        <v>299</v>
       </c>
       <c r="D162" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E162" t="s">
         <v>270</v>
       </c>
       <c r="F162" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
       <c r="G162" t="s">
         <v>272</v>
@@ -5375,10 +5375,10 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>163</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>301</v>
+        <v>163</v>
       </c>
       <c r="E163" t="s">
         <v>270</v>
@@ -5398,16 +5398,16 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D164" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E164" t="s">
         <v>270</v>
       </c>
       <c r="F164" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="G164" t="s">
         <v>272</v>
@@ -5421,16 +5421,16 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D165" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E165" t="s">
         <v>270</v>
       </c>
       <c r="F165" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="G165" t="s">
         <v>272</v>
@@ -5444,16 +5444,16 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E166" t="s">
         <v>270</v>
       </c>
       <c r="F166" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="G166" t="s">
         <v>272</v>
@@ -5467,16 +5467,16 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D167" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E167" t="s">
         <v>270</v>
       </c>
       <c r="F167" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="G167" t="s">
         <v>272</v>
@@ -5490,16 +5490,16 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D168" t="s">
-        <v>309</v>
+        <v>163</v>
       </c>
       <c r="E168" t="s">
         <v>270</v>
       </c>
       <c r="F168" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G168" t="s">
         <v>272</v>
@@ -5513,16 +5513,16 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D169" t="s">
-        <v>309</v>
+        <v>163</v>
       </c>
       <c r="E169" t="s">
         <v>270</v>
       </c>
       <c r="F169" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G169" t="s">
         <v>272</v>
@@ -5536,16 +5536,16 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D170" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E170" t="s">
         <v>270</v>
       </c>
       <c r="F170" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="G170" t="s">
         <v>272</v>
@@ -5558,13 +5558,13 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
-      <c r="C171" t="s">
-        <v>163</v>
-      </c>
       <c r="D171" t="s">
+        <v>163</v>
+      </c>
+      <c r="E171" t="s">
         <v>164</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>165</v>
       </c>
       <c r="G171" t="s">
@@ -5578,13 +5578,13 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
-      <c r="C172" t="s">
-        <v>112</v>
-      </c>
       <c r="D172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E172" t="s">
         <v>118</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
         <v>119</v>
       </c>
       <c r="G172" t="s">
@@ -5598,13 +5598,13 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
-      <c r="C173" t="s">
-        <v>163</v>
-      </c>
       <c r="D173" t="s">
+        <v>163</v>
+      </c>
+      <c r="E173" t="s">
         <v>164</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
         <v>165</v>
       </c>
       <c r="G173" t="s">
@@ -5618,13 +5618,13 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
-      <c r="C174" t="s">
-        <v>163</v>
-      </c>
       <c r="D174" t="s">
+        <v>163</v>
+      </c>
+      <c r="E174" t="s">
         <v>164</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
         <v>165</v>
       </c>
       <c r="G174" t="s">
@@ -5638,13 +5638,13 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
-      <c r="C175" t="s">
-        <v>163</v>
-      </c>
       <c r="D175" t="s">
+        <v>163</v>
+      </c>
+      <c r="E175" t="s">
         <v>164</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
         <v>165</v>
       </c>
       <c r="G175" t="s">
@@ -5658,13 +5658,13 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
-      <c r="C176" t="s">
-        <v>163</v>
-      </c>
       <c r="D176" t="s">
+        <v>163</v>
+      </c>
+      <c r="E176" t="s">
         <v>164</v>
       </c>
-      <c r="E176" t="s">
+      <c r="F176" t="s">
         <v>165</v>
       </c>
       <c r="G176" t="s">
@@ -5678,13 +5678,13 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
-      <c r="C177" t="s">
-        <v>163</v>
-      </c>
       <c r="D177" t="s">
+        <v>163</v>
+      </c>
+      <c r="E177" t="s">
         <v>164</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>165</v>
       </c>
       <c r="G177" t="s">
@@ -5698,13 +5698,13 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
-      <c r="C178" t="s">
-        <v>163</v>
-      </c>
       <c r="D178" t="s">
+        <v>163</v>
+      </c>
+      <c r="E178" t="s">
         <v>164</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>165</v>
       </c>
       <c r="G178" t="s">
@@ -5718,13 +5718,13 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
-      <c r="C179" t="s">
-        <v>163</v>
-      </c>
       <c r="D179" t="s">
+        <v>163</v>
+      </c>
+      <c r="E179" t="s">
         <v>164</v>
       </c>
-      <c r="E179" t="s">
+      <c r="F179" t="s">
         <v>165</v>
       </c>
       <c r="G179" t="s">
@@ -5738,13 +5738,13 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
-      <c r="C180" t="s">
-        <v>163</v>
-      </c>
       <c r="D180" t="s">
+        <v>163</v>
+      </c>
+      <c r="E180" t="s">
         <v>164</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
         <v>165</v>
       </c>
       <c r="G180" t="s">
@@ -5759,10 +5759,10 @@
         <v>8</v>
       </c>
       <c r="C181" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D181" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E181" t="s">
         <v>326</v>
@@ -5782,10 +5782,10 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D182" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E182" t="s">
         <v>326</v>
@@ -5805,10 +5805,10 @@
         <v>8</v>
       </c>
       <c r="C183" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D183" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E183" t="s">
         <v>326</v>
@@ -5828,10 +5828,10 @@
         <v>8</v>
       </c>
       <c r="C184" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D184" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E184" t="s">
         <v>326</v>
@@ -5851,10 +5851,10 @@
         <v>8</v>
       </c>
       <c r="C185" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D185" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E185" t="s">
         <v>326</v>
@@ -5874,10 +5874,10 @@
         <v>8</v>
       </c>
       <c r="C186" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D186" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E186" t="s">
         <v>326</v>
@@ -5897,10 +5897,10 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D187" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E187" t="s">
         <v>326</v>
@@ -5920,10 +5920,10 @@
         <v>8</v>
       </c>
       <c r="C188" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D188" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E188" t="s">
         <v>326</v>
@@ -5943,10 +5943,10 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D189" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E189" t="s">
         <v>326</v>
@@ -5966,10 +5966,10 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D190" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E190" t="s">
         <v>326</v>
@@ -5989,10 +5989,10 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D191" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E191" t="s">
         <v>326</v>
@@ -6012,10 +6012,10 @@
         <v>8</v>
       </c>
       <c r="C192" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D192" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E192" t="s">
         <v>326</v>
@@ -6035,16 +6035,16 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D193" t="s">
+        <v>163</v>
+      </c>
+      <c r="E193" t="s">
+        <v>275</v>
+      </c>
+      <c r="F193" t="s">
         <v>341</v>
-      </c>
-      <c r="E193" t="s">
-        <v>276</v>
-      </c>
-      <c r="F193" t="s">
-        <v>327</v>
       </c>
       <c r="G193" t="s">
         <v>328</v>
@@ -6058,10 +6058,10 @@
         <v>8</v>
       </c>
       <c r="C194" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D194" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E194" t="s">
         <v>326</v>
@@ -6081,10 +6081,10 @@
         <v>8</v>
       </c>
       <c r="C195" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D195" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E195" t="s">
         <v>326</v>
@@ -6104,10 +6104,10 @@
         <v>8</v>
       </c>
       <c r="C196" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D196" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E196" t="s">
         <v>326</v>
@@ -6127,10 +6127,10 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D197" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E197" t="s">
         <v>326</v>
@@ -6150,10 +6150,10 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D198" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E198" t="s">
         <v>326</v>
@@ -6173,10 +6173,10 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>348</v>
+        <v>163</v>
       </c>
       <c r="E199" t="s">
         <v>326</v>
@@ -6196,10 +6196,10 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>348</v>
+        <v>163</v>
       </c>
       <c r="E200" t="s">
         <v>326</v>
@@ -6219,10 +6219,10 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>348</v>
+        <v>163</v>
       </c>
       <c r="E201" t="s">
         <v>326</v>
@@ -6242,10 +6242,10 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>348</v>
+        <v>163</v>
       </c>
       <c r="E202" t="s">
         <v>326</v>
@@ -6265,16 +6265,16 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D203" t="s">
+        <v>163</v>
+      </c>
+      <c r="E203" t="s">
+        <v>275</v>
+      </c>
+      <c r="F203" t="s">
         <v>341</v>
-      </c>
-      <c r="E203" t="s">
-        <v>276</v>
-      </c>
-      <c r="F203" t="s">
-        <v>349</v>
       </c>
       <c r="G203" t="s">
         <v>328</v>
@@ -6288,10 +6288,10 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>348</v>
+        <v>163</v>
       </c>
       <c r="E204" t="s">
         <v>326</v>
@@ -6311,10 +6311,10 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>356</v>
+        <v>163</v>
       </c>
       <c r="E205" t="s">
         <v>326</v>
@@ -6334,10 +6334,10 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>356</v>
+        <v>163</v>
       </c>
       <c r="E206" t="s">
         <v>326</v>
@@ -6357,10 +6357,10 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>356</v>
+        <v>163</v>
       </c>
       <c r="E207" t="s">
         <v>326</v>
@@ -6380,16 +6380,16 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D208" t="s">
+        <v>163</v>
+      </c>
+      <c r="E208" t="s">
+        <v>275</v>
+      </c>
+      <c r="F208" t="s">
         <v>341</v>
-      </c>
-      <c r="E208" t="s">
-        <v>276</v>
-      </c>
-      <c r="F208" t="s">
-        <v>357</v>
       </c>
       <c r="G208" t="s">
         <v>328</v>
@@ -6403,10 +6403,10 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>356</v>
+        <v>163</v>
       </c>
       <c r="E209" t="s">
         <v>326</v>
@@ -6426,10 +6426,10 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D210" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E210" t="s">
         <v>364</v>
@@ -6449,10 +6449,10 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D211" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E211" t="s">
         <v>364</v>
@@ -6472,10 +6472,10 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D212" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E212" t="s">
         <v>364</v>
@@ -6495,10 +6495,10 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D213" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E213" t="s">
         <v>364</v>
@@ -6518,10 +6518,10 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D214" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E214" t="s">
         <v>364</v>
@@ -6541,16 +6541,16 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D215" t="s">
-        <v>348</v>
+        <v>163</v>
       </c>
       <c r="E215" t="s">
         <v>326</v>
       </c>
       <c r="F215" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="G215" t="s">
         <v>366</v>
@@ -6564,10 +6564,10 @@
         <v>8</v>
       </c>
       <c r="C216" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D216" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E216" t="s">
         <v>364</v>
@@ -6587,10 +6587,10 @@
         <v>8</v>
       </c>
       <c r="C217" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D217" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E217" t="s">
         <v>364</v>
@@ -6610,10 +6610,10 @@
         <v>8</v>
       </c>
       <c r="C218" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D218" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E218" t="s">
         <v>364</v>
@@ -6633,10 +6633,10 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D219" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E219" t="s">
         <v>364</v>
@@ -6656,16 +6656,16 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D220" t="s">
-        <v>309</v>
+        <v>163</v>
       </c>
       <c r="E220" t="s">
         <v>270</v>
       </c>
       <c r="F220" t="s">
-        <v>365</v>
+        <v>309</v>
       </c>
       <c r="G220" t="s">
         <v>366</v>
@@ -6679,10 +6679,10 @@
         <v>8</v>
       </c>
       <c r="C221" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D221" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E221" t="s">
         <v>364</v>
@@ -6702,10 +6702,10 @@
         <v>8</v>
       </c>
       <c r="C222" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D222" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E222" t="s">
         <v>364</v>
@@ -6725,10 +6725,10 @@
         <v>8</v>
       </c>
       <c r="C223" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D223" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E223" t="s">
         <v>364</v>
@@ -6748,10 +6748,10 @@
         <v>8</v>
       </c>
       <c r="C224" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D224" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E224" t="s">
         <v>364</v>
@@ -6771,10 +6771,10 @@
         <v>8</v>
       </c>
       <c r="C225" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D225" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E225" t="s">
         <v>364</v>
@@ -6794,16 +6794,16 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D226" t="s">
+        <v>163</v>
+      </c>
+      <c r="E226" t="s">
         <v>275</v>
       </c>
-      <c r="E226" t="s">
+      <c r="F226" t="s">
         <v>276</v>
-      </c>
-      <c r="F226" t="s">
-        <v>365</v>
       </c>
       <c r="G226" t="s">
         <v>366</v>
@@ -6817,10 +6817,10 @@
         <v>8</v>
       </c>
       <c r="C227" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D227" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E227" t="s">
         <v>364</v>
@@ -6840,16 +6840,16 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D228" t="s">
+        <v>163</v>
+      </c>
+      <c r="E228" t="s">
         <v>164</v>
       </c>
-      <c r="E228" t="s">
+      <c r="F228" t="s">
         <v>165</v>
-      </c>
-      <c r="F228" t="s">
-        <v>365</v>
       </c>
       <c r="G228" t="s">
         <v>366</v>
@@ -6863,10 +6863,10 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="E229" t="s">
         <v>364</v>
@@ -6886,10 +6886,10 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="E230" t="s">
         <v>364</v>
@@ -6909,16 +6909,16 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D231" t="s">
-        <v>293</v>
+        <v>163</v>
       </c>
       <c r="E231" t="s">
         <v>270</v>
       </c>
       <c r="F231" t="s">
-        <v>387</v>
+        <v>293</v>
       </c>
       <c r="G231" t="s">
         <v>366</v>
@@ -6932,16 +6932,16 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D232" t="s">
-        <v>309</v>
+        <v>163</v>
       </c>
       <c r="E232" t="s">
         <v>270</v>
       </c>
       <c r="F232" t="s">
-        <v>387</v>
+        <v>309</v>
       </c>
       <c r="G232" t="s">
         <v>366</v>
@@ -6955,10 +6955,10 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="E233" t="s">
         <v>364</v>
@@ -6978,10 +6978,10 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="E234" t="s">
         <v>364</v>
@@ -7001,10 +7001,10 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="E235" t="s">
         <v>364</v>
@@ -7024,10 +7024,10 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="E236" t="s">
         <v>364</v>
@@ -7047,10 +7047,10 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="E237" t="s">
         <v>364</v>
@@ -7070,10 +7070,10 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="E238" t="s">
         <v>364</v>
@@ -7093,10 +7093,10 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>163</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>398</v>
+        <v>163</v>
       </c>
       <c r="E239" t="s">
         <v>364</v>
@@ -7116,16 +7116,16 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D240" t="s">
+        <v>163</v>
+      </c>
+      <c r="E240" t="s">
         <v>164</v>
       </c>
-      <c r="E240" t="s">
+      <c r="F240" t="s">
         <v>165</v>
-      </c>
-      <c r="F240" t="s">
-        <v>401</v>
       </c>
       <c r="G240" t="s">
         <v>402</v>
@@ -7139,16 +7139,16 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D241" t="s">
+        <v>163</v>
+      </c>
+      <c r="E241" t="s">
         <v>164</v>
       </c>
-      <c r="E241" t="s">
+      <c r="F241" t="s">
         <v>165</v>
-      </c>
-      <c r="F241" t="s">
-        <v>401</v>
       </c>
       <c r="G241" t="s">
         <v>402</v>
@@ -7162,16 +7162,16 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D242" t="s">
+        <v>163</v>
+      </c>
+      <c r="E242" t="s">
         <v>164</v>
       </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>165</v>
-      </c>
-      <c r="F242" t="s">
-        <v>401</v>
       </c>
       <c r="G242" t="s">
         <v>402</v>
@@ -7185,16 +7185,16 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D243" t="s">
+        <v>163</v>
+      </c>
+      <c r="E243" t="s">
         <v>164</v>
       </c>
-      <c r="E243" t="s">
+      <c r="F243" t="s">
         <v>165</v>
-      </c>
-      <c r="F243" t="s">
-        <v>401</v>
       </c>
       <c r="G243" t="s">
         <v>402</v>
@@ -7208,16 +7208,16 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D244" t="s">
+        <v>163</v>
+      </c>
+      <c r="E244" t="s">
         <v>164</v>
       </c>
-      <c r="E244" t="s">
+      <c r="F244" t="s">
         <v>165</v>
-      </c>
-      <c r="F244" t="s">
-        <v>401</v>
       </c>
       <c r="G244" t="s">
         <v>402</v>
@@ -7231,16 +7231,16 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D245" t="s">
+        <v>163</v>
+      </c>
+      <c r="E245" t="s">
         <v>164</v>
       </c>
-      <c r="E245" t="s">
+      <c r="F245" t="s">
         <v>165</v>
-      </c>
-      <c r="F245" t="s">
-        <v>401</v>
       </c>
       <c r="G245" t="s">
         <v>402</v>
@@ -7254,13 +7254,13 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>163</v>
+        <v>409</v>
       </c>
       <c r="D246" t="s">
-        <v>409</v>
+        <v>163</v>
       </c>
       <c r="E246" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F246" t="s">
         <v>410</v>
@@ -7276,13 +7276,13 @@
       <c r="B247" t="s">
         <v>8</v>
       </c>
-      <c r="C247" t="s">
+      <c r="D247" t="s">
         <v>95</v>
       </c>
-      <c r="D247" t="s">
+      <c r="E247" t="s">
         <v>96</v>
       </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
         <v>97</v>
       </c>
       <c r="G247" t="s">
@@ -7296,13 +7296,13 @@
       <c r="B248" t="s">
         <v>8</v>
       </c>
-      <c r="C248" t="s">
+      <c r="D248" t="s">
         <v>95</v>
       </c>
-      <c r="D248" t="s">
+      <c r="E248" t="s">
         <v>96</v>
       </c>
-      <c r="E248" t="s">
+      <c r="F248" t="s">
         <v>97</v>
       </c>
       <c r="G248" t="s">
@@ -7316,13 +7316,13 @@
       <c r="B249" t="s">
         <v>8</v>
       </c>
-      <c r="C249" t="s">
+      <c r="D249" t="s">
         <v>95</v>
       </c>
-      <c r="D249" t="s">
+      <c r="E249" t="s">
         <v>415</v>
       </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
         <v>416</v>
       </c>
       <c r="G249" t="s">
@@ -7336,13 +7336,13 @@
       <c r="B250" t="s">
         <v>8</v>
       </c>
-      <c r="C250" t="s">
+      <c r="D250" t="s">
         <v>95</v>
       </c>
-      <c r="D250" t="s">
+      <c r="E250" t="s">
         <v>96</v>
       </c>
-      <c r="E250" t="s">
+      <c r="F250" t="s">
         <v>97</v>
       </c>
       <c r="G250" t="s">
@@ -7356,13 +7356,13 @@
       <c r="B251" t="s">
         <v>8</v>
       </c>
-      <c r="C251" t="s">
+      <c r="D251" t="s">
         <v>95</v>
       </c>
-      <c r="D251" t="s">
+      <c r="E251" t="s">
         <v>96</v>
       </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
         <v>97</v>
       </c>
       <c r="G251" t="s">
@@ -7376,13 +7376,13 @@
       <c r="B252" t="s">
         <v>8</v>
       </c>
-      <c r="C252" t="s">
+      <c r="D252" t="s">
         <v>95</v>
       </c>
-      <c r="D252" t="s">
+      <c r="E252" t="s">
         <v>96</v>
       </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
         <v>97</v>
       </c>
       <c r="G252" t="s">
@@ -7396,13 +7396,13 @@
       <c r="B253" t="s">
         <v>8</v>
       </c>
-      <c r="C253" t="s">
-        <v>163</v>
-      </c>
       <c r="D253" t="s">
+        <v>163</v>
+      </c>
+      <c r="E253" t="s">
         <v>421</v>
       </c>
-      <c r="E253" t="s">
+      <c r="F253" t="s">
         <v>422</v>
       </c>
       <c r="G253" t="s">
@@ -7416,13 +7416,13 @@
       <c r="B254" t="s">
         <v>8</v>
       </c>
-      <c r="C254" t="s">
+      <c r="D254" t="s">
         <v>90</v>
       </c>
-      <c r="D254" t="s">
+      <c r="E254" t="s">
         <v>219</v>
       </c>
-      <c r="E254" t="s">
+      <c r="F254" t="s">
         <v>220</v>
       </c>
       <c r="G254" t="s">
@@ -7436,13 +7436,13 @@
       <c r="B255" t="s">
         <v>8</v>
       </c>
-      <c r="C255" t="s">
+      <c r="D255" t="s">
         <v>90</v>
       </c>
-      <c r="D255" t="s">
+      <c r="E255" t="s">
         <v>426</v>
       </c>
-      <c r="E255" t="s">
+      <c r="F255" t="s">
         <v>427</v>
       </c>
       <c r="G255" t="s">
@@ -7456,13 +7456,13 @@
       <c r="B256" t="s">
         <v>8</v>
       </c>
-      <c r="C256" t="s">
+      <c r="D256" t="s">
         <v>90</v>
       </c>
-      <c r="D256" t="s">
+      <c r="E256" t="s">
         <v>426</v>
       </c>
-      <c r="E256" t="s">
+      <c r="F256" t="s">
         <v>427</v>
       </c>
       <c r="G256" t="s">
@@ -7476,13 +7476,13 @@
       <c r="B257" t="s">
         <v>8</v>
       </c>
-      <c r="C257" t="s">
+      <c r="D257" t="s">
         <v>90</v>
       </c>
-      <c r="D257" t="s">
+      <c r="E257" t="s">
         <v>426</v>
       </c>
-      <c r="E257" t="s">
+      <c r="F257" t="s">
         <v>427</v>
       </c>
       <c r="G257" t="s">
@@ -7496,14 +7496,14 @@
       <c r="B258" t="s">
         <v>8</v>
       </c>
-      <c r="C258" t="s">
-        <v>163</v>
-      </c>
       <c r="D258" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E258" t="s">
         <v>326</v>
+      </c>
+      <c r="F258" t="s">
+        <v>327</v>
       </c>
       <c r="G258" t="s">
         <v>423</v>
@@ -7516,13 +7516,13 @@
       <c r="B259" t="s">
         <v>8</v>
       </c>
-      <c r="C259" t="s">
+      <c r="D259" t="s">
         <v>90</v>
       </c>
-      <c r="D259" t="s">
+      <c r="E259" t="s">
         <v>426</v>
       </c>
-      <c r="E259" t="s">
+      <c r="F259" t="s">
         <v>427</v>
       </c>
       <c r="G259" t="s">
@@ -7536,13 +7536,13 @@
       <c r="B260" t="s">
         <v>8</v>
       </c>
-      <c r="C260" t="s">
-        <v>163</v>
-      </c>
       <c r="D260" t="s">
+        <v>163</v>
+      </c>
+      <c r="E260" t="s">
         <v>164</v>
       </c>
-      <c r="E260" t="s">
+      <c r="F260" t="s">
         <v>165</v>
       </c>
       <c r="G260" t="s">
@@ -7556,13 +7556,13 @@
       <c r="B261" t="s">
         <v>8</v>
       </c>
-      <c r="C261" t="s">
+      <c r="D261" t="s">
         <v>195</v>
       </c>
-      <c r="D261" t="s">
+      <c r="E261" t="s">
         <v>434</v>
       </c>
-      <c r="E261" t="s">
+      <c r="F261" t="s">
         <v>435</v>
       </c>
       <c r="G261" t="s">
@@ -7576,13 +7576,13 @@
       <c r="B262" t="s">
         <v>8</v>
       </c>
-      <c r="C262" t="s">
-        <v>163</v>
-      </c>
       <c r="D262" t="s">
+        <v>163</v>
+      </c>
+      <c r="E262" t="s">
         <v>164</v>
       </c>
-      <c r="E262" t="s">
+      <c r="F262" t="s">
         <v>165</v>
       </c>
       <c r="G262" t="s">
@@ -7596,13 +7596,13 @@
       <c r="B263" t="s">
         <v>8</v>
       </c>
-      <c r="C263" t="s">
+      <c r="D263" t="s">
         <v>182</v>
       </c>
-      <c r="D263" t="s">
+      <c r="E263" t="s">
         <v>438</v>
       </c>
-      <c r="E263" t="s">
+      <c r="F263" t="s">
         <v>439</v>
       </c>
       <c r="G263" t="s">
@@ -7616,13 +7616,13 @@
       <c r="B264" t="s">
         <v>8</v>
       </c>
-      <c r="C264" t="s">
+      <c r="D264" t="s">
         <v>31</v>
       </c>
-      <c r="D264" t="s">
+      <c r="E264" t="s">
         <v>32</v>
       </c>
-      <c r="E264" t="s">
+      <c r="F264" t="s">
         <v>33</v>
       </c>
       <c r="G264" t="s">
@@ -7636,14 +7636,14 @@
       <c r="B265" t="s">
         <v>8</v>
       </c>
-      <c r="C265" t="s">
-        <v>9</v>
-      </c>
       <c r="D265" t="s">
         <v>10</v>
       </c>
       <c r="E265" t="s">
         <v>11</v>
+      </c>
+      <c r="F265" t="s">
+        <v>12</v>
       </c>
       <c r="G265" t="s">
         <v>423</v>
@@ -7656,13 +7656,13 @@
       <c r="B266" t="s">
         <v>8</v>
       </c>
-      <c r="C266" t="s">
-        <v>112</v>
-      </c>
       <c r="D266" t="s">
+        <v>113</v>
+      </c>
+      <c r="E266" t="s">
         <v>443</v>
       </c>
-      <c r="E266" t="s">
+      <c r="F266" t="s">
         <v>444</v>
       </c>
       <c r="G266" t="s">
@@ -7676,13 +7676,13 @@
       <c r="B267" t="s">
         <v>8</v>
       </c>
-      <c r="C267" t="s">
-        <v>112</v>
-      </c>
       <c r="D267" t="s">
+        <v>113</v>
+      </c>
+      <c r="E267" t="s">
         <v>118</v>
       </c>
-      <c r="E267" t="s">
+      <c r="F267" t="s">
         <v>119</v>
       </c>
       <c r="G267" t="s">
@@ -7696,13 +7696,13 @@
       <c r="B268" t="s">
         <v>8</v>
       </c>
-      <c r="C268" t="s">
+      <c r="D268" t="s">
         <v>182</v>
       </c>
-      <c r="D268" t="s">
+      <c r="E268" t="s">
         <v>202</v>
       </c>
-      <c r="E268" t="s">
+      <c r="F268" t="s">
         <v>203</v>
       </c>
       <c r="G268" t="s">
@@ -7716,13 +7716,13 @@
       <c r="B269" t="s">
         <v>8</v>
       </c>
-      <c r="C269" t="s">
-        <v>112</v>
-      </c>
       <c r="D269" t="s">
+        <v>113</v>
+      </c>
+      <c r="E269" t="s">
         <v>118</v>
       </c>
-      <c r="E269" t="s">
+      <c r="F269" t="s">
         <v>119</v>
       </c>
       <c r="G269" t="s">
@@ -7736,13 +7736,13 @@
       <c r="B270" t="s">
         <v>8</v>
       </c>
-      <c r="C270" t="s">
-        <v>112</v>
-      </c>
       <c r="D270" t="s">
+        <v>113</v>
+      </c>
+      <c r="E270" t="s">
         <v>118</v>
       </c>
-      <c r="E270" t="s">
+      <c r="F270" t="s">
         <v>119</v>
       </c>
       <c r="G270" t="s">
@@ -7756,13 +7756,13 @@
       <c r="B271" t="s">
         <v>8</v>
       </c>
-      <c r="C271" t="s">
-        <v>112</v>
-      </c>
       <c r="D271" t="s">
+        <v>113</v>
+      </c>
+      <c r="E271" t="s">
         <v>453</v>
       </c>
-      <c r="E271" t="s">
+      <c r="F271" t="s">
         <v>454</v>
       </c>
       <c r="G271" t="s">
@@ -7776,13 +7776,13 @@
       <c r="B272" t="s">
         <v>8</v>
       </c>
-      <c r="C272" t="s">
-        <v>112</v>
-      </c>
       <c r="D272" t="s">
+        <v>113</v>
+      </c>
+      <c r="E272" t="s">
         <v>453</v>
       </c>
-      <c r="E272" t="s">
+      <c r="F272" t="s">
         <v>454</v>
       </c>
       <c r="G272" t="s">
@@ -7796,13 +7796,13 @@
       <c r="B273" t="s">
         <v>8</v>
       </c>
-      <c r="C273" t="s">
-        <v>112</v>
-      </c>
       <c r="D273" t="s">
+        <v>113</v>
+      </c>
+      <c r="E273" t="s">
         <v>453</v>
       </c>
-      <c r="E273" t="s">
+      <c r="F273" t="s">
         <v>454</v>
       </c>
       <c r="G273" t="s">
@@ -7816,13 +7816,13 @@
       <c r="B274" t="s">
         <v>8</v>
       </c>
-      <c r="C274" t="s">
-        <v>112</v>
-      </c>
       <c r="D274" t="s">
+        <v>113</v>
+      </c>
+      <c r="E274" t="s">
         <v>453</v>
       </c>
-      <c r="E274" t="s">
+      <c r="F274" t="s">
         <v>454</v>
       </c>
       <c r="G274" t="s">
@@ -7836,13 +7836,13 @@
       <c r="B275" t="s">
         <v>8</v>
       </c>
-      <c r="C275" t="s">
-        <v>112</v>
-      </c>
       <c r="D275" t="s">
+        <v>113</v>
+      </c>
+      <c r="E275" t="s">
         <v>453</v>
       </c>
-      <c r="E275" t="s">
+      <c r="F275" t="s">
         <v>454</v>
       </c>
       <c r="G275" t="s">
@@ -7856,13 +7856,13 @@
       <c r="B276" t="s">
         <v>8</v>
       </c>
-      <c r="C276" t="s">
-        <v>112</v>
-      </c>
       <c r="D276" t="s">
+        <v>113</v>
+      </c>
+      <c r="E276" t="s">
         <v>453</v>
       </c>
-      <c r="E276" t="s">
+      <c r="F276" t="s">
         <v>454</v>
       </c>
       <c r="G276" t="s">
@@ -7876,13 +7876,13 @@
       <c r="B277" t="s">
         <v>8</v>
       </c>
-      <c r="C277" t="s">
-        <v>112</v>
-      </c>
       <c r="D277" t="s">
+        <v>113</v>
+      </c>
+      <c r="E277" t="s">
         <v>453</v>
       </c>
-      <c r="E277" t="s">
+      <c r="F277" t="s">
         <v>454</v>
       </c>
       <c r="G277" t="s">
@@ -7896,13 +7896,13 @@
       <c r="B278" t="s">
         <v>8</v>
       </c>
-      <c r="C278" t="s">
+      <c r="D278" t="s">
         <v>182</v>
       </c>
-      <c r="D278" t="s">
+      <c r="E278" t="s">
         <v>202</v>
       </c>
-      <c r="E278" t="s">
+      <c r="F278" t="s">
         <v>203</v>
       </c>
       <c r="G278" t="s">
@@ -7916,14 +7916,14 @@
       <c r="B279" t="s">
         <v>8</v>
       </c>
-      <c r="C279" t="s">
+      <c r="D279" t="s">
         <v>31</v>
-      </c>
-      <c r="D279" t="s">
-        <v>51</v>
       </c>
       <c r="E279" t="s">
         <v>52</v>
+      </c>
+      <c r="F279" t="s">
+        <v>53</v>
       </c>
       <c r="G279" t="s">
         <v>463</v>
@@ -7936,14 +7936,14 @@
       <c r="B280" t="s">
         <v>8</v>
       </c>
-      <c r="C280" t="s">
-        <v>9</v>
-      </c>
       <c r="D280" t="s">
         <v>10</v>
       </c>
       <c r="E280" t="s">
         <v>11</v>
+      </c>
+      <c r="F280" t="s">
+        <v>12</v>
       </c>
       <c r="G280" t="s">
         <v>463</v>
@@ -7956,13 +7956,13 @@
       <c r="B281" t="s">
         <v>8</v>
       </c>
-      <c r="C281" t="s">
-        <v>112</v>
-      </c>
       <c r="D281" t="s">
+        <v>113</v>
+      </c>
+      <c r="E281" t="s">
         <v>170</v>
       </c>
-      <c r="E281" t="s">
+      <c r="F281" t="s">
         <v>171</v>
       </c>
       <c r="G281" t="s">
@@ -7976,13 +7976,13 @@
       <c r="B282" t="s">
         <v>8</v>
       </c>
-      <c r="C282" t="s">
+      <c r="D282" t="s">
         <v>124</v>
       </c>
-      <c r="D282" t="s">
+      <c r="E282" t="s">
         <v>125</v>
       </c>
-      <c r="E282" t="s">
+      <c r="F282" t="s">
         <v>126</v>
       </c>
       <c r="G282" t="s">
@@ -7996,14 +7996,14 @@
       <c r="B283" t="s">
         <v>8</v>
       </c>
-      <c r="C283" t="s">
-        <v>163</v>
-      </c>
       <c r="D283" t="s">
-        <v>398</v>
+        <v>163</v>
       </c>
       <c r="E283" t="s">
         <v>364</v>
+      </c>
+      <c r="F283" t="s">
+        <v>399</v>
       </c>
       <c r="G283" t="s">
         <v>469</v>
@@ -8016,13 +8016,13 @@
       <c r="B284" t="s">
         <v>8</v>
       </c>
-      <c r="C284" t="s">
+      <c r="D284" t="s">
         <v>124</v>
       </c>
-      <c r="D284" t="s">
+      <c r="E284" t="s">
         <v>125</v>
       </c>
-      <c r="E284" t="s">
+      <c r="F284" t="s">
         <v>126</v>
       </c>
       <c r="G284" t="s">
@@ -8036,13 +8036,13 @@
       <c r="B285" t="s">
         <v>8</v>
       </c>
-      <c r="C285" t="s">
-        <v>112</v>
-      </c>
       <c r="D285" t="s">
+        <v>113</v>
+      </c>
+      <c r="E285" t="s">
         <v>170</v>
       </c>
-      <c r="E285" t="s">
+      <c r="F285" t="s">
         <v>171</v>
       </c>
       <c r="G285" t="s">
@@ -8056,13 +8056,13 @@
       <c r="B286" t="s">
         <v>8</v>
       </c>
-      <c r="C286" t="s">
+      <c r="D286" t="s">
         <v>182</v>
       </c>
-      <c r="D286" t="s">
+      <c r="E286" t="s">
         <v>438</v>
       </c>
-      <c r="E286" t="s">
+      <c r="F286" t="s">
         <v>439</v>
       </c>
       <c r="G286" t="s">
@@ -8076,13 +8076,13 @@
       <c r="B287" t="s">
         <v>8</v>
       </c>
-      <c r="C287" t="s">
+      <c r="D287" t="s">
         <v>182</v>
       </c>
-      <c r="D287" t="s">
+      <c r="E287" t="s">
         <v>438</v>
       </c>
-      <c r="E287" t="s">
+      <c r="F287" t="s">
         <v>439</v>
       </c>
       <c r="G287" t="s">
@@ -8096,13 +8096,13 @@
       <c r="B288" t="s">
         <v>8</v>
       </c>
-      <c r="C288" t="s">
-        <v>9</v>
-      </c>
       <c r="D288" t="s">
+        <v>10</v>
+      </c>
+      <c r="E288" t="s">
         <v>41</v>
       </c>
-      <c r="E288" t="s">
+      <c r="F288" t="s">
         <v>42</v>
       </c>
       <c r="G288" t="s">
@@ -8116,13 +8116,13 @@
       <c r="B289" t="s">
         <v>8</v>
       </c>
-      <c r="C289" t="s">
+      <c r="D289" t="s">
         <v>31</v>
       </c>
-      <c r="D289" t="s">
+      <c r="E289" t="s">
         <v>32</v>
       </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
         <v>33</v>
       </c>
       <c r="G289" t="s">
@@ -8136,13 +8136,13 @@
       <c r="B290" t="s">
         <v>8</v>
       </c>
-      <c r="C290" t="s">
+      <c r="D290" t="s">
         <v>31</v>
       </c>
-      <c r="D290" t="s">
+      <c r="E290" t="s">
         <v>32</v>
       </c>
-      <c r="E290" t="s">
+      <c r="F290" t="s">
         <v>33</v>
       </c>
       <c r="G290" t="s">
@@ -8156,13 +8156,13 @@
       <c r="B291" t="s">
         <v>8</v>
       </c>
-      <c r="C291" t="s">
-        <v>112</v>
-      </c>
       <c r="D291" t="s">
+        <v>113</v>
+      </c>
+      <c r="E291" t="s">
         <v>170</v>
       </c>
-      <c r="E291" t="s">
+      <c r="F291" t="s">
         <v>171</v>
       </c>
       <c r="G291" t="s">
@@ -8176,13 +8176,13 @@
       <c r="B292" t="s">
         <v>8</v>
       </c>
-      <c r="C292" t="s">
-        <v>112</v>
-      </c>
       <c r="D292" t="s">
+        <v>113</v>
+      </c>
+      <c r="E292" t="s">
         <v>170</v>
       </c>
-      <c r="E292" t="s">
+      <c r="F292" t="s">
         <v>171</v>
       </c>
       <c r="G292" t="s">
@@ -8196,13 +8196,13 @@
       <c r="B293" t="s">
         <v>8</v>
       </c>
-      <c r="C293" t="s">
-        <v>112</v>
-      </c>
       <c r="D293" t="s">
+        <v>113</v>
+      </c>
+      <c r="E293" t="s">
         <v>170</v>
       </c>
-      <c r="E293" t="s">
+      <c r="F293" t="s">
         <v>171</v>
       </c>
       <c r="G293" t="s">
@@ -8216,13 +8216,13 @@
       <c r="B294" t="s">
         <v>8</v>
       </c>
-      <c r="C294" t="s">
-        <v>112</v>
-      </c>
       <c r="D294" t="s">
+        <v>113</v>
+      </c>
+      <c r="E294" t="s">
         <v>170</v>
       </c>
-      <c r="E294" t="s">
+      <c r="F294" t="s">
         <v>171</v>
       </c>
       <c r="G294" t="s">
@@ -8236,13 +8236,13 @@
       <c r="B295" t="s">
         <v>8</v>
       </c>
-      <c r="C295" t="s">
-        <v>112</v>
-      </c>
       <c r="D295" t="s">
+        <v>113</v>
+      </c>
+      <c r="E295" t="s">
         <v>170</v>
       </c>
-      <c r="E295" t="s">
+      <c r="F295" t="s">
         <v>171</v>
       </c>
       <c r="G295" t="s">
@@ -8256,13 +8256,13 @@
       <c r="B296" t="s">
         <v>8</v>
       </c>
-      <c r="C296" t="s">
-        <v>112</v>
-      </c>
       <c r="D296" t="s">
+        <v>113</v>
+      </c>
+      <c r="E296" t="s">
         <v>170</v>
       </c>
-      <c r="E296" t="s">
+      <c r="F296" t="s">
         <v>171</v>
       </c>
       <c r="G296" t="s">

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,18 +22,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
@@ -43,54 +43,54 @@
     <t>active</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,72 +112,72 @@
     <t>07 - Health</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -187,21 +187,21 @@
     <t>12182</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -289,12 +289,12 @@
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>140</t>
   </si>
   <si>
@@ -304,12 +304,12 @@
     <t>05 - Environmental protection</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -565,12 +565,12 @@
     <t>10 - Social protection</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>02 - Defence</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,12 +622,12 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>160</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,30 +655,30 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,27 +811,27 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>230</t>
   </si>
   <si>
@@ -841,12 +841,12 @@
     <t>23112</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,15 +991,15 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>310</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,15 +1105,15 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,12 +1210,12 @@
     <t>32310</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>04.7.3 - Tourism (CS)</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,12 +1279,12 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>430</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>43031</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,10 +1375,10 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>600</t>
@@ -1866,10 +1866,10 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -1912,10 +1912,10 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
@@ -1932,10 +1932,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -1955,13 +1955,13 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -1978,10 +1978,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -2001,10 +2001,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
         <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
@@ -2024,16 +2024,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2047,13 +2047,13 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
@@ -2070,13 +2070,13 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
         <v>36</v>
@@ -2093,16 +2093,16 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2116,13 +2116,13 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
         <v>42</v>
@@ -2139,10 +2139,10 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
         <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>45</v>
@@ -2162,13 +2162,13 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F16" t="s">
         <v>49</v>
@@ -2185,10 +2185,10 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
         <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>31</v>
       </c>
       <c r="E17" t="s">
         <v>52</v>
@@ -2208,10 +2208,10 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
         <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>31</v>
       </c>
       <c r="E18" t="s">
         <v>52</v>
@@ -2231,13 +2231,13 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F19" t="s">
         <v>58</v>
@@ -2254,13 +2254,13 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
         <v>61</v>
@@ -2277,10 +2277,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
         <v>51</v>
-      </c>
-      <c r="D21" t="s">
-        <v>31</v>
       </c>
       <c r="E21" t="s">
         <v>52</v>
@@ -2300,13 +2300,13 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
         <v>64</v>
-      </c>
-      <c r="D22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" t="s">
-        <v>32</v>
       </c>
       <c r="F22" t="s">
         <v>33</v>
@@ -2323,13 +2323,13 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
         <v>64</v>
-      </c>
-      <c r="D23" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" t="s">
-        <v>66</v>
       </c>
       <c r="F23" t="s">
         <v>67</v>
@@ -2346,13 +2346,13 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
         <v>64</v>
-      </c>
-      <c r="D24" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" t="s">
-        <v>32</v>
       </c>
       <c r="F24" t="s">
         <v>33</v>
@@ -2369,13 +2369,13 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
         <v>64</v>
-      </c>
-      <c r="D25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" t="s">
-        <v>32</v>
       </c>
       <c r="F25" t="s">
         <v>33</v>
@@ -2392,13 +2392,13 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
         <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" t="s">
-        <v>32</v>
       </c>
       <c r="F26" t="s">
         <v>33</v>
@@ -2415,13 +2415,13 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" t="s">
         <v>64</v>
-      </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" t="s">
-        <v>32</v>
       </c>
       <c r="F27" t="s">
         <v>33</v>
@@ -2438,13 +2438,13 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
         <v>64</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" t="s">
-        <v>32</v>
       </c>
       <c r="F28" t="s">
         <v>33</v>
@@ -2461,13 +2461,13 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" t="s">
         <v>64</v>
-      </c>
-      <c r="D29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" t="s">
-        <v>32</v>
       </c>
       <c r="F29" t="s">
         <v>33</v>
@@ -2484,13 +2484,13 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" t="s">
         <v>64</v>
-      </c>
-      <c r="D30" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" t="s">
-        <v>52</v>
       </c>
       <c r="F30" t="s">
         <v>53</v>
@@ -2507,13 +2507,13 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" t="s">
         <v>76</v>
-      </c>
-      <c r="D31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" t="s">
-        <v>32</v>
       </c>
       <c r="F31" t="s">
         <v>33</v>
@@ -2530,13 +2530,13 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
         <v>76</v>
-      </c>
-      <c r="D32" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" t="s">
-        <v>32</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
@@ -2553,13 +2553,13 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" t="s">
         <v>76</v>
-      </c>
-      <c r="D33" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" t="s">
-        <v>32</v>
       </c>
       <c r="F33" t="s">
         <v>33</v>
@@ -2576,13 +2576,13 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
         <v>76</v>
-      </c>
-      <c r="D34" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" t="s">
-        <v>32</v>
       </c>
       <c r="F34" t="s">
         <v>33</v>
@@ -2599,13 +2599,13 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" t="s">
         <v>76</v>
-      </c>
-      <c r="D35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" t="s">
-        <v>32</v>
       </c>
       <c r="F35" t="s">
         <v>33</v>
@@ -2622,13 +2622,13 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" t="s">
         <v>76</v>
-      </c>
-      <c r="D36" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" t="s">
-        <v>57</v>
       </c>
       <c r="F36" t="s">
         <v>58</v>
@@ -2644,10 +2644,10 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
+      <c r="C37" t="s">
+        <v>31</v>
+      </c>
       <c r="D37" t="s">
-        <v>31</v>
-      </c>
-      <c r="E37" t="s">
         <v>32</v>
       </c>
       <c r="F37" t="s">
@@ -2664,10 +2664,10 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
+      <c r="C38" t="s">
+        <v>31</v>
+      </c>
       <c r="D38" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" t="s">
         <v>32</v>
       </c>
       <c r="F38" t="s">
@@ -2684,10 +2684,10 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
       <c r="D39" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" t="s">
         <v>32</v>
       </c>
       <c r="F39" t="s">
@@ -2704,10 +2704,10 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
       <c r="D40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" t="s">
         <v>32</v>
       </c>
       <c r="F40" t="s">
@@ -2724,11 +2724,11 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
+      <c r="C41" t="s">
+        <v>31</v>
+      </c>
       <c r="D41" t="s">
-        <v>31</v>
-      </c>
-      <c r="E41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F41" t="s">
         <v>53</v>
@@ -2744,10 +2744,10 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
+      <c r="C42" t="s">
+        <v>31</v>
+      </c>
       <c r="D42" t="s">
-        <v>31</v>
-      </c>
-      <c r="E42" t="s">
         <v>57</v>
       </c>
       <c r="F42" t="s">
@@ -2764,10 +2764,10 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
+      <c r="C43" t="s">
+        <v>90</v>
+      </c>
       <c r="D43" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" t="s">
         <v>91</v>
       </c>
       <c r="F43" t="s">
@@ -2784,10 +2784,10 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
+      <c r="C44" t="s">
+        <v>95</v>
+      </c>
       <c r="D44" t="s">
-        <v>95</v>
-      </c>
-      <c r="E44" t="s">
         <v>96</v>
       </c>
       <c r="F44" t="s">
@@ -2804,10 +2804,10 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
       <c r="D45" t="s">
-        <v>90</v>
-      </c>
-      <c r="E45" t="s">
         <v>91</v>
       </c>
       <c r="F45" t="s">
@@ -2824,10 +2824,10 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
+      <c r="C46" t="s">
+        <v>90</v>
+      </c>
       <c r="D46" t="s">
-        <v>90</v>
-      </c>
-      <c r="E46" t="s">
         <v>91</v>
       </c>
       <c r="F46" t="s">
@@ -2844,10 +2844,10 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
+      <c r="C47" t="s">
+        <v>95</v>
+      </c>
       <c r="D47" t="s">
-        <v>95</v>
-      </c>
-      <c r="E47" t="s">
         <v>101</v>
       </c>
       <c r="F47" t="s">
@@ -2864,10 +2864,10 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
+      <c r="C48" t="s">
+        <v>90</v>
+      </c>
       <c r="D48" t="s">
-        <v>90</v>
-      </c>
-      <c r="E48" t="s">
         <v>91</v>
       </c>
       <c r="F48" t="s">
@@ -2884,10 +2884,10 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
+      <c r="C49" t="s">
+        <v>90</v>
+      </c>
       <c r="D49" t="s">
-        <v>90</v>
-      </c>
-      <c r="E49" t="s">
         <v>91</v>
       </c>
       <c r="F49" t="s">
@@ -2904,10 +2904,10 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
+      <c r="C50" t="s">
+        <v>95</v>
+      </c>
       <c r="D50" t="s">
-        <v>95</v>
-      </c>
-      <c r="E50" t="s">
         <v>101</v>
       </c>
       <c r="F50" t="s">
@@ -2924,10 +2924,10 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
+      <c r="C51" t="s">
+        <v>90</v>
+      </c>
       <c r="D51" t="s">
-        <v>90</v>
-      </c>
-      <c r="E51" t="s">
         <v>91</v>
       </c>
       <c r="F51" t="s">
@@ -2944,10 +2944,10 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
+      <c r="C52" t="s">
+        <v>95</v>
+      </c>
       <c r="D52" t="s">
-        <v>95</v>
-      </c>
-      <c r="E52" t="s">
         <v>108</v>
       </c>
       <c r="F52" t="s">
@@ -2964,11 +2964,11 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
       <c r="D53" t="s">
         <v>10</v>
-      </c>
-      <c r="E53" t="s">
-        <v>11</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
@@ -3011,10 +3011,10 @@
         <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E55" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F55" t="s">
         <v>119</v>
@@ -3034,10 +3034,10 @@
         <v>112</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E56" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F56" t="s">
         <v>122</v>
@@ -3054,13 +3054,13 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F57" t="s">
         <v>126</v>
@@ -3080,10 +3080,10 @@
         <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E58" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
         <v>119</v>
@@ -3103,10 +3103,10 @@
         <v>112</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E59" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
         <v>119</v>
@@ -3126,10 +3126,10 @@
         <v>112</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F60" t="s">
         <v>119</v>
@@ -3149,10 +3149,10 @@
         <v>112</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E61" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F61" t="s">
         <v>119</v>
@@ -3172,10 +3172,10 @@
         <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E62" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F62" t="s">
         <v>119</v>
@@ -3195,13 +3195,13 @@
         <v>112</v>
       </c>
       <c r="D63" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E63" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="G63" t="s">
         <v>116</v>
@@ -3218,13 +3218,13 @@
         <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E64" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="G64" t="s">
         <v>116</v>
@@ -3241,10 +3241,10 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="E65" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="F65" t="s">
         <v>137</v>
@@ -3287,10 +3287,10 @@
         <v>112</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E67" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F67" t="s">
         <v>119</v>
@@ -3310,13 +3310,13 @@
         <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="G68" t="s">
         <v>116</v>
@@ -3333,13 +3333,13 @@
         <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G69" t="s">
         <v>116</v>
@@ -3356,10 +3356,10 @@
         <v>112</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E70" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F70" t="s">
         <v>122</v>
@@ -3379,10 +3379,10 @@
         <v>112</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E71" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F71" t="s">
         <v>122</v>
@@ -3422,13 +3422,13 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D73" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="E73" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="F73" t="s">
         <v>149</v>
@@ -3445,13 +3445,13 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D74" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E74" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="F74" t="s">
         <v>152</v>
@@ -3468,13 +3468,13 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D75" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="E75" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="F75" t="s">
         <v>155</v>
@@ -3491,13 +3491,13 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D76" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="E76" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="F76" t="s">
         <v>149</v>
@@ -3514,13 +3514,13 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D77" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="E77" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="F77" t="s">
         <v>149</v>
@@ -3537,13 +3537,13 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D78" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E78" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="F78" t="s">
         <v>152</v>
@@ -3560,13 +3560,13 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D79" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E79" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="F79" t="s">
         <v>161</v>
@@ -3583,13 +3583,13 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="F80" t="s">
         <v>165</v>
@@ -3606,13 +3606,13 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E81" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="F81" t="s">
         <v>165</v>
@@ -3629,13 +3629,13 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E82" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="F82" t="s">
         <v>165</v>
@@ -3655,13 +3655,13 @@
         <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
       </c>
       <c r="F83" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G83" t="s">
         <v>116</v>
@@ -3678,10 +3678,10 @@
         <v>112</v>
       </c>
       <c r="D84" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E84" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="F84" t="s">
         <v>171</v>
@@ -3701,13 +3701,13 @@
         <v>112</v>
       </c>
       <c r="D85" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="E85" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="G85" t="s">
         <v>116</v>
@@ -3721,13 +3721,13 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D86" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E86" t="s">
-        <v>175</v>
+        <v>114</v>
       </c>
       <c r="F86" t="s">
         <v>176</v>
@@ -3747,13 +3747,13 @@
         <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="E87" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="G87" t="s">
         <v>116</v>
@@ -3770,10 +3770,10 @@
         <v>112</v>
       </c>
       <c r="D88" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E88" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F88" t="s">
         <v>119</v>
@@ -3793,10 +3793,10 @@
         <v>112</v>
       </c>
       <c r="D89" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E89" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F89" t="s">
         <v>119</v>
@@ -3813,13 +3813,13 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E90" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F90" t="s">
         <v>126</v>
@@ -3836,13 +3836,13 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>183</v>
+        <v>114</v>
       </c>
       <c r="F91" t="s">
         <v>184</v>
@@ -3859,13 +3859,13 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F92" t="s">
         <v>126</v>
@@ -3885,10 +3885,10 @@
         <v>112</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E93" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F93" t="s">
         <v>122</v>
@@ -3905,13 +3905,13 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E94" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F94" t="s">
         <v>126</v>
@@ -3931,10 +3931,10 @@
         <v>112</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="E95" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="F95" t="s">
         <v>190</v>
@@ -3951,13 +3951,13 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>124</v>
+      </c>
+      <c r="D96" t="s">
+        <v>125</v>
+      </c>
+      <c r="E96" t="s">
         <v>192</v>
-      </c>
-      <c r="D96" t="s">
-        <v>124</v>
-      </c>
-      <c r="E96" t="s">
-        <v>125</v>
       </c>
       <c r="F96" t="s">
         <v>126</v>
@@ -3974,13 +3974,13 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>124</v>
+      </c>
+      <c r="D97" t="s">
+        <v>125</v>
+      </c>
+      <c r="E97" t="s">
         <v>192</v>
-      </c>
-      <c r="D97" t="s">
-        <v>124</v>
-      </c>
-      <c r="E97" t="s">
-        <v>125</v>
       </c>
       <c r="F97" t="s">
         <v>126</v>
@@ -3997,13 +3997,13 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>195</v>
+      </c>
+      <c r="D98" t="s">
+        <v>196</v>
+      </c>
+      <c r="E98" t="s">
         <v>192</v>
-      </c>
-      <c r="D98" t="s">
-        <v>195</v>
-      </c>
-      <c r="E98" t="s">
-        <v>196</v>
       </c>
       <c r="F98" t="s">
         <v>197</v>
@@ -4020,13 +4020,13 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>124</v>
+      </c>
+      <c r="D99" t="s">
+        <v>125</v>
+      </c>
+      <c r="E99" t="s">
         <v>192</v>
-      </c>
-      <c r="D99" t="s">
-        <v>124</v>
-      </c>
-      <c r="E99" t="s">
-        <v>125</v>
       </c>
       <c r="F99" t="s">
         <v>126</v>
@@ -4043,13 +4043,13 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>124</v>
+      </c>
+      <c r="D100" t="s">
+        <v>154</v>
+      </c>
+      <c r="E100" t="s">
         <v>192</v>
-      </c>
-      <c r="D100" t="s">
-        <v>124</v>
-      </c>
-      <c r="E100" t="s">
-        <v>154</v>
       </c>
       <c r="F100" t="s">
         <v>155</v>
@@ -4066,13 +4066,13 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>124</v>
+      </c>
+      <c r="D101" t="s">
+        <v>125</v>
+      </c>
+      <c r="E101" t="s">
         <v>192</v>
-      </c>
-      <c r="D101" t="s">
-        <v>124</v>
-      </c>
-      <c r="E101" t="s">
-        <v>125</v>
       </c>
       <c r="F101" t="s">
         <v>126</v>
@@ -4088,10 +4088,10 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
+      <c r="C102" t="s">
+        <v>182</v>
+      </c>
       <c r="D102" t="s">
-        <v>182</v>
-      </c>
-      <c r="E102" t="s">
         <v>202</v>
       </c>
       <c r="F102" t="s">
@@ -4108,10 +4108,10 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
+      <c r="C103" t="s">
+        <v>182</v>
+      </c>
       <c r="D103" t="s">
-        <v>182</v>
-      </c>
-      <c r="E103" t="s">
         <v>202</v>
       </c>
       <c r="F103" t="s">
@@ -4128,10 +4128,10 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
+      <c r="C104" t="s">
+        <v>182</v>
+      </c>
       <c r="D104" t="s">
-        <v>182</v>
-      </c>
-      <c r="E104" t="s">
         <v>202</v>
       </c>
       <c r="F104" t="s">
@@ -4148,10 +4148,10 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
+      <c r="C105" t="s">
+        <v>182</v>
+      </c>
       <c r="D105" t="s">
-        <v>182</v>
-      </c>
-      <c r="E105" t="s">
         <v>208</v>
       </c>
       <c r="F105" t="s">
@@ -4168,10 +4168,10 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
+      <c r="C106" t="s">
+        <v>182</v>
+      </c>
       <c r="D106" t="s">
-        <v>182</v>
-      </c>
-      <c r="E106" t="s">
         <v>202</v>
       </c>
       <c r="F106" t="s">
@@ -4188,10 +4188,10 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
+      <c r="C107" t="s">
+        <v>182</v>
+      </c>
       <c r="D107" t="s">
-        <v>182</v>
-      </c>
-      <c r="E107" t="s">
         <v>183</v>
       </c>
       <c r="F107" t="s">
@@ -4208,10 +4208,10 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
+      <c r="C108" t="s">
+        <v>182</v>
+      </c>
       <c r="D108" t="s">
-        <v>182</v>
-      </c>
-      <c r="E108" t="s">
         <v>213</v>
       </c>
       <c r="F108" t="s">
@@ -4228,10 +4228,10 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
+      <c r="C109" t="s">
+        <v>90</v>
+      </c>
       <c r="D109" t="s">
-        <v>90</v>
-      </c>
-      <c r="E109" t="s">
         <v>216</v>
       </c>
       <c r="F109" t="s">
@@ -4248,10 +4248,10 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
+      <c r="C110" t="s">
+        <v>90</v>
+      </c>
       <c r="D110" t="s">
-        <v>90</v>
-      </c>
-      <c r="E110" t="s">
         <v>219</v>
       </c>
       <c r="F110" t="s">
@@ -4268,10 +4268,10 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
+      <c r="C111" t="s">
+        <v>182</v>
+      </c>
       <c r="D111" t="s">
-        <v>182</v>
-      </c>
-      <c r="E111" t="s">
         <v>202</v>
       </c>
       <c r="F111" t="s">
@@ -4288,10 +4288,10 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
+      <c r="C112" t="s">
+        <v>223</v>
+      </c>
       <c r="D112" t="s">
-        <v>223</v>
-      </c>
-      <c r="E112" t="s">
         <v>224</v>
       </c>
       <c r="F112" t="s">
@@ -4308,14 +4308,14 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
+      <c r="C113" t="s">
+        <v>112</v>
+      </c>
       <c r="D113" t="s">
-        <v>113</v>
-      </c>
-      <c r="E113" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="F113" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G113" t="s">
         <v>204</v>
@@ -4328,10 +4328,10 @@
       <c r="B114" t="s">
         <v>8</v>
       </c>
+      <c r="C114" t="s">
+        <v>124</v>
+      </c>
       <c r="D114" t="s">
-        <v>124</v>
-      </c>
-      <c r="E114" t="s">
         <v>151</v>
       </c>
       <c r="F114" t="s">
@@ -4348,10 +4348,10 @@
       <c r="B115" t="s">
         <v>8</v>
       </c>
+      <c r="C115" t="s">
+        <v>182</v>
+      </c>
       <c r="D115" t="s">
-        <v>182</v>
-      </c>
-      <c r="E115" t="s">
         <v>183</v>
       </c>
       <c r="F115" t="s">
@@ -4368,10 +4368,10 @@
       <c r="B116" t="s">
         <v>8</v>
       </c>
+      <c r="C116" t="s">
+        <v>223</v>
+      </c>
       <c r="D116" t="s">
-        <v>223</v>
-      </c>
-      <c r="E116" t="s">
         <v>230</v>
       </c>
       <c r="F116" t="s">
@@ -4388,10 +4388,10 @@
       <c r="B117" t="s">
         <v>8</v>
       </c>
+      <c r="C117" t="s">
+        <v>223</v>
+      </c>
       <c r="D117" t="s">
-        <v>223</v>
-      </c>
-      <c r="E117" t="s">
         <v>224</v>
       </c>
       <c r="F117" t="s">
@@ -4408,14 +4408,14 @@
       <c r="B118" t="s">
         <v>8</v>
       </c>
+      <c r="C118" t="s">
+        <v>163</v>
+      </c>
       <c r="D118" t="s">
-        <v>163</v>
-      </c>
-      <c r="E118" t="s">
-        <v>164</v>
+        <v>234</v>
       </c>
       <c r="F118" t="s">
-        <v>234</v>
+        <v>165</v>
       </c>
       <c r="G118" t="s">
         <v>204</v>
@@ -4428,10 +4428,10 @@
       <c r="B119" t="s">
         <v>8</v>
       </c>
+      <c r="C119" t="s">
+        <v>182</v>
+      </c>
       <c r="D119" t="s">
-        <v>182</v>
-      </c>
-      <c r="E119" t="s">
         <v>183</v>
       </c>
       <c r="F119" t="s">
@@ -4448,10 +4448,10 @@
       <c r="B120" t="s">
         <v>8</v>
       </c>
+      <c r="C120" t="s">
+        <v>112</v>
+      </c>
       <c r="D120" t="s">
-        <v>113</v>
-      </c>
-      <c r="E120" t="s">
         <v>170</v>
       </c>
       <c r="F120" t="s">
@@ -4468,14 +4468,14 @@
       <c r="B121" t="s">
         <v>8</v>
       </c>
+      <c r="C121" t="s">
+        <v>112</v>
+      </c>
       <c r="D121" t="s">
-        <v>113</v>
-      </c>
-      <c r="E121" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="F121" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G121" t="s">
         <v>237</v>
@@ -4488,10 +4488,10 @@
       <c r="B122" t="s">
         <v>8</v>
       </c>
+      <c r="C122" t="s">
+        <v>112</v>
+      </c>
       <c r="D122" t="s">
-        <v>113</v>
-      </c>
-      <c r="E122" t="s">
         <v>170</v>
       </c>
       <c r="F122" t="s">
@@ -4508,10 +4508,10 @@
       <c r="B123" t="s">
         <v>8</v>
       </c>
+      <c r="C123" t="s">
+        <v>112</v>
+      </c>
       <c r="D123" t="s">
-        <v>113</v>
-      </c>
-      <c r="E123" t="s">
         <v>170</v>
       </c>
       <c r="F123" t="s">
@@ -4528,10 +4528,10 @@
       <c r="B124" t="s">
         <v>8</v>
       </c>
+      <c r="C124" t="s">
+        <v>163</v>
+      </c>
       <c r="D124" t="s">
-        <v>163</v>
-      </c>
-      <c r="E124" t="s">
         <v>242</v>
       </c>
       <c r="F124" t="s">
@@ -4548,10 +4548,10 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
+      <c r="C125" t="s">
+        <v>163</v>
+      </c>
       <c r="D125" t="s">
-        <v>163</v>
-      </c>
-      <c r="E125" t="s">
         <v>242</v>
       </c>
       <c r="F125" t="s">
@@ -4568,10 +4568,10 @@
       <c r="B126" t="s">
         <v>8</v>
       </c>
+      <c r="C126" t="s">
+        <v>163</v>
+      </c>
       <c r="D126" t="s">
-        <v>163</v>
-      </c>
-      <c r="E126" t="s">
         <v>242</v>
       </c>
       <c r="F126" t="s">
@@ -4588,10 +4588,10 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
+      <c r="C127" t="s">
+        <v>163</v>
+      </c>
       <c r="D127" t="s">
-        <v>163</v>
-      </c>
-      <c r="E127" t="s">
         <v>242</v>
       </c>
       <c r="F127" t="s">
@@ -4608,10 +4608,10 @@
       <c r="B128" t="s">
         <v>8</v>
       </c>
+      <c r="C128" t="s">
+        <v>163</v>
+      </c>
       <c r="D128" t="s">
-        <v>163</v>
-      </c>
-      <c r="E128" t="s">
         <v>242</v>
       </c>
       <c r="F128" t="s">
@@ -4628,14 +4628,14 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
+      <c r="C129" t="s">
+        <v>163</v>
+      </c>
       <c r="D129" t="s">
-        <v>163</v>
-      </c>
-      <c r="E129" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F129" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G129" t="s">
         <v>237</v>
@@ -4648,14 +4648,14 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
+      <c r="C130" t="s">
+        <v>163</v>
+      </c>
       <c r="D130" t="s">
-        <v>163</v>
-      </c>
-      <c r="E130" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F130" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G130" t="s">
         <v>237</v>
@@ -4668,14 +4668,14 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
+      <c r="C131" t="s">
+        <v>163</v>
+      </c>
       <c r="D131" t="s">
-        <v>163</v>
-      </c>
-      <c r="E131" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="F131" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="G131" t="s">
         <v>237</v>
@@ -4688,10 +4688,10 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
+      <c r="C132" t="s">
+        <v>163</v>
+      </c>
       <c r="D132" t="s">
-        <v>163</v>
-      </c>
-      <c r="E132" t="s">
         <v>255</v>
       </c>
       <c r="F132" t="s">
@@ -4708,10 +4708,10 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
+      <c r="C133" t="s">
+        <v>112</v>
+      </c>
       <c r="D133" t="s">
-        <v>113</v>
-      </c>
-      <c r="E133" t="s">
         <v>189</v>
       </c>
       <c r="F133" t="s">
@@ -4728,10 +4728,10 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
+      <c r="C134" t="s">
+        <v>163</v>
+      </c>
       <c r="D134" t="s">
-        <v>163</v>
-      </c>
-      <c r="E134" t="s">
         <v>175</v>
       </c>
       <c r="F134" t="s">
@@ -4748,10 +4748,10 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
+      <c r="C135" t="s">
+        <v>163</v>
+      </c>
       <c r="D135" t="s">
-        <v>163</v>
-      </c>
-      <c r="E135" t="s">
         <v>175</v>
       </c>
       <c r="F135" t="s">
@@ -4768,10 +4768,10 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
+      <c r="C136" t="s">
+        <v>163</v>
+      </c>
       <c r="D136" t="s">
-        <v>163</v>
-      </c>
-      <c r="E136" t="s">
         <v>175</v>
       </c>
       <c r="F136" t="s">
@@ -4788,10 +4788,10 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
+      <c r="C137" t="s">
+        <v>163</v>
+      </c>
       <c r="D137" t="s">
-        <v>163</v>
-      </c>
-      <c r="E137" t="s">
         <v>175</v>
       </c>
       <c r="F137" t="s">
@@ -4808,10 +4808,10 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
+      <c r="C138" t="s">
+        <v>163</v>
+      </c>
       <c r="D138" t="s">
-        <v>163</v>
-      </c>
-      <c r="E138" t="s">
         <v>175</v>
       </c>
       <c r="F138" t="s">
@@ -4828,10 +4828,10 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
+      <c r="C139" t="s">
+        <v>223</v>
+      </c>
       <c r="D139" t="s">
-        <v>223</v>
-      </c>
-      <c r="E139" t="s">
         <v>265</v>
       </c>
       <c r="F139" t="s">
@@ -4848,10 +4848,10 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
+      <c r="C140" t="s">
+        <v>163</v>
+      </c>
       <c r="D140" t="s">
-        <v>163</v>
-      </c>
-      <c r="E140" t="s">
         <v>175</v>
       </c>
       <c r="F140" t="s">
@@ -4869,10 +4869,10 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
+        <v>163</v>
+      </c>
+      <c r="D141" t="s">
         <v>269</v>
-      </c>
-      <c r="D141" t="s">
-        <v>163</v>
       </c>
       <c r="E141" t="s">
         <v>270</v>
@@ -4892,10 +4892,10 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
+        <v>163</v>
+      </c>
+      <c r="D142" t="s">
         <v>269</v>
-      </c>
-      <c r="D142" t="s">
-        <v>163</v>
       </c>
       <c r="E142" t="s">
         <v>270</v>
@@ -4915,13 +4915,13 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="D143" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="E143" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F143" t="s">
         <v>276</v>
@@ -4938,13 +4938,13 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="D144" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="E144" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F144" t="s">
         <v>276</v>
@@ -4961,13 +4961,13 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="D145" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="E145" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F145" t="s">
         <v>276</v>
@@ -4984,10 +4984,10 @@
         <v>8</v>
       </c>
       <c r="C146" t="s">
+        <v>163</v>
+      </c>
+      <c r="D146" t="s">
         <v>269</v>
-      </c>
-      <c r="D146" t="s">
-        <v>163</v>
       </c>
       <c r="E146" t="s">
         <v>270</v>
@@ -5007,13 +5007,13 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
+        <v>163</v>
+      </c>
+      <c r="D147" t="s">
+        <v>269</v>
+      </c>
+      <c r="E147" t="s">
         <v>281</v>
-      </c>
-      <c r="D147" t="s">
-        <v>163</v>
-      </c>
-      <c r="E147" t="s">
-        <v>270</v>
       </c>
       <c r="F147" t="s">
         <v>271</v>
@@ -5030,13 +5030,13 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
+        <v>163</v>
+      </c>
+      <c r="D148" t="s">
+        <v>269</v>
+      </c>
+      <c r="E148" t="s">
         <v>281</v>
-      </c>
-      <c r="D148" t="s">
-        <v>163</v>
-      </c>
-      <c r="E148" t="s">
-        <v>270</v>
       </c>
       <c r="F148" t="s">
         <v>271</v>
@@ -5053,13 +5053,13 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
+        <v>163</v>
+      </c>
+      <c r="D149" t="s">
+        <v>269</v>
+      </c>
+      <c r="E149" t="s">
         <v>281</v>
-      </c>
-      <c r="D149" t="s">
-        <v>163</v>
-      </c>
-      <c r="E149" t="s">
-        <v>270</v>
       </c>
       <c r="F149" t="s">
         <v>271</v>
@@ -5076,13 +5076,13 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
+        <v>163</v>
+      </c>
+      <c r="D150" t="s">
+        <v>269</v>
+      </c>
+      <c r="E150" t="s">
         <v>281</v>
-      </c>
-      <c r="D150" t="s">
-        <v>163</v>
-      </c>
-      <c r="E150" t="s">
-        <v>270</v>
       </c>
       <c r="F150" t="s">
         <v>271</v>
@@ -5099,13 +5099,13 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
+        <v>163</v>
+      </c>
+      <c r="D151" t="s">
+        <v>269</v>
+      </c>
+      <c r="E151" t="s">
         <v>281</v>
-      </c>
-      <c r="D151" t="s">
-        <v>163</v>
-      </c>
-      <c r="E151" t="s">
-        <v>270</v>
       </c>
       <c r="F151" t="s">
         <v>271</v>
@@ -5122,13 +5122,13 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
+        <v>163</v>
+      </c>
+      <c r="D152" t="s">
+        <v>269</v>
+      </c>
+      <c r="E152" t="s">
         <v>281</v>
-      </c>
-      <c r="D152" t="s">
-        <v>163</v>
-      </c>
-      <c r="E152" t="s">
-        <v>270</v>
       </c>
       <c r="F152" t="s">
         <v>271</v>
@@ -5145,13 +5145,13 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
+        <v>163</v>
+      </c>
+      <c r="D153" t="s">
+        <v>269</v>
+      </c>
+      <c r="E153" t="s">
         <v>281</v>
-      </c>
-      <c r="D153" t="s">
-        <v>163</v>
-      </c>
-      <c r="E153" t="s">
-        <v>270</v>
       </c>
       <c r="F153" t="s">
         <v>271</v>
@@ -5168,13 +5168,13 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
+        <v>163</v>
+      </c>
+      <c r="D154" t="s">
+        <v>269</v>
+      </c>
+      <c r="E154" t="s">
         <v>281</v>
-      </c>
-      <c r="D154" t="s">
-        <v>163</v>
-      </c>
-      <c r="E154" t="s">
-        <v>270</v>
       </c>
       <c r="F154" t="s">
         <v>271</v>
@@ -5191,13 +5191,13 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
+        <v>163</v>
+      </c>
+      <c r="D155" t="s">
+        <v>269</v>
+      </c>
+      <c r="E155" t="s">
         <v>281</v>
-      </c>
-      <c r="D155" t="s">
-        <v>163</v>
-      </c>
-      <c r="E155" t="s">
-        <v>270</v>
       </c>
       <c r="F155" t="s">
         <v>271</v>
@@ -5214,13 +5214,13 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
+        <v>163</v>
+      </c>
+      <c r="D156" t="s">
+        <v>269</v>
+      </c>
+      <c r="E156" t="s">
         <v>291</v>
-      </c>
-      <c r="D156" t="s">
-        <v>163</v>
-      </c>
-      <c r="E156" t="s">
-        <v>270</v>
       </c>
       <c r="F156" t="s">
         <v>271</v>
@@ -5237,16 +5237,16 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
+        <v>163</v>
+      </c>
+      <c r="D157" t="s">
+        <v>293</v>
+      </c>
+      <c r="E157" t="s">
         <v>291</v>
       </c>
-      <c r="D157" t="s">
-        <v>163</v>
-      </c>
-      <c r="E157" t="s">
-        <v>270</v>
-      </c>
       <c r="F157" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="G157" t="s">
         <v>272</v>
@@ -5260,13 +5260,13 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
+        <v>163</v>
+      </c>
+      <c r="D158" t="s">
+        <v>269</v>
+      </c>
+      <c r="E158" t="s">
         <v>291</v>
-      </c>
-      <c r="D158" t="s">
-        <v>163</v>
-      </c>
-      <c r="E158" t="s">
-        <v>270</v>
       </c>
       <c r="F158" t="s">
         <v>271</v>
@@ -5283,13 +5283,13 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
+        <v>163</v>
+      </c>
+      <c r="D159" t="s">
+        <v>269</v>
+      </c>
+      <c r="E159" t="s">
         <v>291</v>
-      </c>
-      <c r="D159" t="s">
-        <v>163</v>
-      </c>
-      <c r="E159" t="s">
-        <v>270</v>
       </c>
       <c r="F159" t="s">
         <v>271</v>
@@ -5306,13 +5306,13 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
+        <v>163</v>
+      </c>
+      <c r="D160" t="s">
+        <v>269</v>
+      </c>
+      <c r="E160" t="s">
         <v>291</v>
-      </c>
-      <c r="D160" t="s">
-        <v>163</v>
-      </c>
-      <c r="E160" t="s">
-        <v>270</v>
       </c>
       <c r="F160" t="s">
         <v>271</v>
@@ -5329,13 +5329,13 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
+        <v>163</v>
+      </c>
+      <c r="D161" t="s">
+        <v>269</v>
+      </c>
+      <c r="E161" t="s">
         <v>291</v>
-      </c>
-      <c r="D161" t="s">
-        <v>163</v>
-      </c>
-      <c r="E161" t="s">
-        <v>270</v>
       </c>
       <c r="F161" t="s">
         <v>271</v>
@@ -5352,13 +5352,13 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
+        <v>163</v>
+      </c>
+      <c r="D162" t="s">
+        <v>269</v>
+      </c>
+      <c r="E162" t="s">
         <v>299</v>
-      </c>
-      <c r="D162" t="s">
-        <v>163</v>
-      </c>
-      <c r="E162" t="s">
-        <v>270</v>
       </c>
       <c r="F162" t="s">
         <v>271</v>
@@ -5375,16 +5375,16 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
+        <v>163</v>
+      </c>
+      <c r="D163" t="s">
         <v>301</v>
       </c>
-      <c r="D163" t="s">
-        <v>163</v>
-      </c>
       <c r="E163" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="F163" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="G163" t="s">
         <v>272</v>
@@ -5398,13 +5398,13 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
+        <v>163</v>
+      </c>
+      <c r="D164" t="s">
+        <v>269</v>
+      </c>
+      <c r="E164" t="s">
         <v>304</v>
-      </c>
-      <c r="D164" t="s">
-        <v>163</v>
-      </c>
-      <c r="E164" t="s">
-        <v>270</v>
       </c>
       <c r="F164" t="s">
         <v>271</v>
@@ -5421,13 +5421,13 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
+        <v>163</v>
+      </c>
+      <c r="D165" t="s">
+        <v>269</v>
+      </c>
+      <c r="E165" t="s">
         <v>304</v>
-      </c>
-      <c r="D165" t="s">
-        <v>163</v>
-      </c>
-      <c r="E165" t="s">
-        <v>270</v>
       </c>
       <c r="F165" t="s">
         <v>271</v>
@@ -5444,13 +5444,13 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
+        <v>163</v>
+      </c>
+      <c r="D166" t="s">
+        <v>269</v>
+      </c>
+      <c r="E166" t="s">
         <v>304</v>
-      </c>
-      <c r="D166" t="s">
-        <v>163</v>
-      </c>
-      <c r="E166" t="s">
-        <v>270</v>
       </c>
       <c r="F166" t="s">
         <v>271</v>
@@ -5467,13 +5467,13 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
+        <v>163</v>
+      </c>
+      <c r="D167" t="s">
+        <v>269</v>
+      </c>
+      <c r="E167" t="s">
         <v>304</v>
-      </c>
-      <c r="D167" t="s">
-        <v>163</v>
-      </c>
-      <c r="E167" t="s">
-        <v>270</v>
       </c>
       <c r="F167" t="s">
         <v>271</v>
@@ -5490,16 +5490,16 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
+        <v>163</v>
+      </c>
+      <c r="D168" t="s">
+        <v>309</v>
+      </c>
+      <c r="E168" t="s">
         <v>304</v>
       </c>
-      <c r="D168" t="s">
-        <v>163</v>
-      </c>
-      <c r="E168" t="s">
-        <v>270</v>
-      </c>
       <c r="F168" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="G168" t="s">
         <v>272</v>
@@ -5513,16 +5513,16 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
+        <v>163</v>
+      </c>
+      <c r="D169" t="s">
+        <v>309</v>
+      </c>
+      <c r="E169" t="s">
         <v>304</v>
       </c>
-      <c r="D169" t="s">
-        <v>163</v>
-      </c>
-      <c r="E169" t="s">
-        <v>270</v>
-      </c>
       <c r="F169" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="G169" t="s">
         <v>272</v>
@@ -5536,13 +5536,13 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
+        <v>163</v>
+      </c>
+      <c r="D170" t="s">
+        <v>269</v>
+      </c>
+      <c r="E170" t="s">
         <v>304</v>
-      </c>
-      <c r="D170" t="s">
-        <v>163</v>
-      </c>
-      <c r="E170" t="s">
-        <v>270</v>
       </c>
       <c r="F170" t="s">
         <v>271</v>
@@ -5558,10 +5558,10 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
+      <c r="C171" t="s">
+        <v>163</v>
+      </c>
       <c r="D171" t="s">
-        <v>163</v>
-      </c>
-      <c r="E171" t="s">
         <v>164</v>
       </c>
       <c r="F171" t="s">
@@ -5578,10 +5578,10 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
+      <c r="C172" t="s">
+        <v>112</v>
+      </c>
       <c r="D172" t="s">
-        <v>113</v>
-      </c>
-      <c r="E172" t="s">
         <v>118</v>
       </c>
       <c r="F172" t="s">
@@ -5598,10 +5598,10 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
+      <c r="C173" t="s">
+        <v>163</v>
+      </c>
       <c r="D173" t="s">
-        <v>163</v>
-      </c>
-      <c r="E173" t="s">
         <v>164</v>
       </c>
       <c r="F173" t="s">
@@ -5618,10 +5618,10 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
+      <c r="C174" t="s">
+        <v>163</v>
+      </c>
       <c r="D174" t="s">
-        <v>163</v>
-      </c>
-      <c r="E174" t="s">
         <v>164</v>
       </c>
       <c r="F174" t="s">
@@ -5638,10 +5638,10 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
+      <c r="C175" t="s">
+        <v>163</v>
+      </c>
       <c r="D175" t="s">
-        <v>163</v>
-      </c>
-      <c r="E175" t="s">
         <v>164</v>
       </c>
       <c r="F175" t="s">
@@ -5658,10 +5658,10 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
+      <c r="C176" t="s">
+        <v>163</v>
+      </c>
       <c r="D176" t="s">
-        <v>163</v>
-      </c>
-      <c r="E176" t="s">
         <v>164</v>
       </c>
       <c r="F176" t="s">
@@ -5678,10 +5678,10 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
+      <c r="C177" t="s">
+        <v>163</v>
+      </c>
       <c r="D177" t="s">
-        <v>163</v>
-      </c>
-      <c r="E177" t="s">
         <v>164</v>
       </c>
       <c r="F177" t="s">
@@ -5698,10 +5698,10 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
+      <c r="C178" t="s">
+        <v>163</v>
+      </c>
       <c r="D178" t="s">
-        <v>163</v>
-      </c>
-      <c r="E178" t="s">
         <v>164</v>
       </c>
       <c r="F178" t="s">
@@ -5718,10 +5718,10 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
+      <c r="C179" t="s">
+        <v>163</v>
+      </c>
       <c r="D179" t="s">
-        <v>163</v>
-      </c>
-      <c r="E179" t="s">
         <v>164</v>
       </c>
       <c r="F179" t="s">
@@ -5738,10 +5738,10 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
+      <c r="C180" t="s">
+        <v>163</v>
+      </c>
       <c r="D180" t="s">
-        <v>163</v>
-      </c>
-      <c r="E180" t="s">
         <v>164</v>
       </c>
       <c r="F180" t="s">
@@ -5759,10 +5759,10 @@
         <v>8</v>
       </c>
       <c r="C181" t="s">
+        <v>163</v>
+      </c>
+      <c r="D181" t="s">
         <v>325</v>
-      </c>
-      <c r="D181" t="s">
-        <v>163</v>
       </c>
       <c r="E181" t="s">
         <v>326</v>
@@ -5782,10 +5782,10 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
+        <v>163</v>
+      </c>
+      <c r="D182" t="s">
         <v>325</v>
-      </c>
-      <c r="D182" t="s">
-        <v>163</v>
       </c>
       <c r="E182" t="s">
         <v>326</v>
@@ -5805,10 +5805,10 @@
         <v>8</v>
       </c>
       <c r="C183" t="s">
+        <v>163</v>
+      </c>
+      <c r="D183" t="s">
         <v>325</v>
-      </c>
-      <c r="D183" t="s">
-        <v>163</v>
       </c>
       <c r="E183" t="s">
         <v>326</v>
@@ -5828,10 +5828,10 @@
         <v>8</v>
       </c>
       <c r="C184" t="s">
+        <v>163</v>
+      </c>
+      <c r="D184" t="s">
         <v>325</v>
-      </c>
-      <c r="D184" t="s">
-        <v>163</v>
       </c>
       <c r="E184" t="s">
         <v>326</v>
@@ -5851,10 +5851,10 @@
         <v>8</v>
       </c>
       <c r="C185" t="s">
+        <v>163</v>
+      </c>
+      <c r="D185" t="s">
         <v>325</v>
-      </c>
-      <c r="D185" t="s">
-        <v>163</v>
       </c>
       <c r="E185" t="s">
         <v>326</v>
@@ -5874,10 +5874,10 @@
         <v>8</v>
       </c>
       <c r="C186" t="s">
+        <v>163</v>
+      </c>
+      <c r="D186" t="s">
         <v>325</v>
-      </c>
-      <c r="D186" t="s">
-        <v>163</v>
       </c>
       <c r="E186" t="s">
         <v>326</v>
@@ -5897,10 +5897,10 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
+        <v>163</v>
+      </c>
+      <c r="D187" t="s">
         <v>325</v>
-      </c>
-      <c r="D187" t="s">
-        <v>163</v>
       </c>
       <c r="E187" t="s">
         <v>326</v>
@@ -5920,10 +5920,10 @@
         <v>8</v>
       </c>
       <c r="C188" t="s">
+        <v>163</v>
+      </c>
+      <c r="D188" t="s">
         <v>325</v>
-      </c>
-      <c r="D188" t="s">
-        <v>163</v>
       </c>
       <c r="E188" t="s">
         <v>326</v>
@@ -5943,10 +5943,10 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
+        <v>163</v>
+      </c>
+      <c r="D189" t="s">
         <v>325</v>
-      </c>
-      <c r="D189" t="s">
-        <v>163</v>
       </c>
       <c r="E189" t="s">
         <v>326</v>
@@ -5966,10 +5966,10 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
+        <v>163</v>
+      </c>
+      <c r="D190" t="s">
         <v>325</v>
-      </c>
-      <c r="D190" t="s">
-        <v>163</v>
       </c>
       <c r="E190" t="s">
         <v>326</v>
@@ -5989,10 +5989,10 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
+        <v>163</v>
+      </c>
+      <c r="D191" t="s">
         <v>325</v>
-      </c>
-      <c r="D191" t="s">
-        <v>163</v>
       </c>
       <c r="E191" t="s">
         <v>326</v>
@@ -6012,10 +6012,10 @@
         <v>8</v>
       </c>
       <c r="C192" t="s">
+        <v>163</v>
+      </c>
+      <c r="D192" t="s">
         <v>325</v>
-      </c>
-      <c r="D192" t="s">
-        <v>163</v>
       </c>
       <c r="E192" t="s">
         <v>326</v>
@@ -6035,16 +6035,16 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="D193" t="s">
-        <v>163</v>
+        <v>341</v>
       </c>
       <c r="E193" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="F193" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="G193" t="s">
         <v>328</v>
@@ -6058,10 +6058,10 @@
         <v>8</v>
       </c>
       <c r="C194" t="s">
+        <v>163</v>
+      </c>
+      <c r="D194" t="s">
         <v>325</v>
-      </c>
-      <c r="D194" t="s">
-        <v>163</v>
       </c>
       <c r="E194" t="s">
         <v>326</v>
@@ -6081,10 +6081,10 @@
         <v>8</v>
       </c>
       <c r="C195" t="s">
+        <v>163</v>
+      </c>
+      <c r="D195" t="s">
         <v>325</v>
-      </c>
-      <c r="D195" t="s">
-        <v>163</v>
       </c>
       <c r="E195" t="s">
         <v>326</v>
@@ -6104,10 +6104,10 @@
         <v>8</v>
       </c>
       <c r="C196" t="s">
+        <v>163</v>
+      </c>
+      <c r="D196" t="s">
         <v>325</v>
-      </c>
-      <c r="D196" t="s">
-        <v>163</v>
       </c>
       <c r="E196" t="s">
         <v>326</v>
@@ -6127,10 +6127,10 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
+        <v>163</v>
+      </c>
+      <c r="D197" t="s">
         <v>325</v>
-      </c>
-      <c r="D197" t="s">
-        <v>163</v>
       </c>
       <c r="E197" t="s">
         <v>326</v>
@@ -6150,10 +6150,10 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
+        <v>163</v>
+      </c>
+      <c r="D198" t="s">
         <v>325</v>
-      </c>
-      <c r="D198" t="s">
-        <v>163</v>
       </c>
       <c r="E198" t="s">
         <v>326</v>
@@ -6173,16 +6173,16 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
+        <v>163</v>
+      </c>
+      <c r="D199" t="s">
         <v>348</v>
       </c>
-      <c r="D199" t="s">
-        <v>163</v>
-      </c>
       <c r="E199" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="F199" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="G199" t="s">
         <v>328</v>
@@ -6196,16 +6196,16 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
+        <v>163</v>
+      </c>
+      <c r="D200" t="s">
         <v>348</v>
       </c>
-      <c r="D200" t="s">
-        <v>163</v>
-      </c>
       <c r="E200" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="F200" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="G200" t="s">
         <v>328</v>
@@ -6219,16 +6219,16 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
+        <v>163</v>
+      </c>
+      <c r="D201" t="s">
         <v>348</v>
       </c>
-      <c r="D201" t="s">
-        <v>163</v>
-      </c>
       <c r="E201" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="F201" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="G201" t="s">
         <v>328</v>
@@ -6242,16 +6242,16 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
+        <v>163</v>
+      </c>
+      <c r="D202" t="s">
         <v>348</v>
       </c>
-      <c r="D202" t="s">
-        <v>163</v>
-      </c>
       <c r="E202" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="F202" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="G202" t="s">
         <v>328</v>
@@ -6265,16 +6265,16 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>348</v>
+        <v>163</v>
       </c>
       <c r="D203" t="s">
-        <v>163</v>
+        <v>341</v>
       </c>
       <c r="E203" t="s">
-        <v>275</v>
+        <v>349</v>
       </c>
       <c r="F203" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="G203" t="s">
         <v>328</v>
@@ -6288,16 +6288,16 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
+        <v>163</v>
+      </c>
+      <c r="D204" t="s">
         <v>348</v>
       </c>
-      <c r="D204" t="s">
-        <v>163</v>
-      </c>
       <c r="E204" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="F204" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="G204" t="s">
         <v>328</v>
@@ -6311,16 +6311,16 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
+        <v>163</v>
+      </c>
+      <c r="D205" t="s">
         <v>356</v>
       </c>
-      <c r="D205" t="s">
-        <v>163</v>
-      </c>
       <c r="E205" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="F205" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="G205" t="s">
         <v>328</v>
@@ -6334,16 +6334,16 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
+        <v>163</v>
+      </c>
+      <c r="D206" t="s">
         <v>356</v>
       </c>
-      <c r="D206" t="s">
-        <v>163</v>
-      </c>
       <c r="E206" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="F206" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="G206" t="s">
         <v>328</v>
@@ -6357,16 +6357,16 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
+        <v>163</v>
+      </c>
+      <c r="D207" t="s">
         <v>356</v>
       </c>
-      <c r="D207" t="s">
-        <v>163</v>
-      </c>
       <c r="E207" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="F207" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="G207" t="s">
         <v>328</v>
@@ -6380,16 +6380,16 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>356</v>
+        <v>163</v>
       </c>
       <c r="D208" t="s">
-        <v>163</v>
+        <v>341</v>
       </c>
       <c r="E208" t="s">
-        <v>275</v>
+        <v>357</v>
       </c>
       <c r="F208" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="G208" t="s">
         <v>328</v>
@@ -6403,16 +6403,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
+        <v>163</v>
+      </c>
+      <c r="D209" t="s">
         <v>356</v>
       </c>
-      <c r="D209" t="s">
-        <v>163</v>
-      </c>
       <c r="E209" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="F209" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="G209" t="s">
         <v>328</v>
@@ -6426,10 +6426,10 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
+        <v>163</v>
+      </c>
+      <c r="D210" t="s">
         <v>363</v>
-      </c>
-      <c r="D210" t="s">
-        <v>163</v>
       </c>
       <c r="E210" t="s">
         <v>364</v>
@@ -6449,10 +6449,10 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
+        <v>163</v>
+      </c>
+      <c r="D211" t="s">
         <v>363</v>
-      </c>
-      <c r="D211" t="s">
-        <v>163</v>
       </c>
       <c r="E211" t="s">
         <v>364</v>
@@ -6472,10 +6472,10 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
+        <v>163</v>
+      </c>
+      <c r="D212" t="s">
         <v>363</v>
-      </c>
-      <c r="D212" t="s">
-        <v>163</v>
       </c>
       <c r="E212" t="s">
         <v>364</v>
@@ -6495,10 +6495,10 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
+        <v>163</v>
+      </c>
+      <c r="D213" t="s">
         <v>363</v>
-      </c>
-      <c r="D213" t="s">
-        <v>163</v>
       </c>
       <c r="E213" t="s">
         <v>364</v>
@@ -6518,10 +6518,10 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
+        <v>163</v>
+      </c>
+      <c r="D214" t="s">
         <v>363</v>
-      </c>
-      <c r="D214" t="s">
-        <v>163</v>
       </c>
       <c r="E214" t="s">
         <v>364</v>
@@ -6541,16 +6541,16 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="D215" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="E215" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="F215" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="G215" t="s">
         <v>366</v>
@@ -6564,10 +6564,10 @@
         <v>8</v>
       </c>
       <c r="C216" t="s">
+        <v>163</v>
+      </c>
+      <c r="D216" t="s">
         <v>363</v>
-      </c>
-      <c r="D216" t="s">
-        <v>163</v>
       </c>
       <c r="E216" t="s">
         <v>364</v>
@@ -6587,10 +6587,10 @@
         <v>8</v>
       </c>
       <c r="C217" t="s">
+        <v>163</v>
+      </c>
+      <c r="D217" t="s">
         <v>363</v>
-      </c>
-      <c r="D217" t="s">
-        <v>163</v>
       </c>
       <c r="E217" t="s">
         <v>364</v>
@@ -6610,10 +6610,10 @@
         <v>8</v>
       </c>
       <c r="C218" t="s">
+        <v>163</v>
+      </c>
+      <c r="D218" t="s">
         <v>363</v>
-      </c>
-      <c r="D218" t="s">
-        <v>163</v>
       </c>
       <c r="E218" t="s">
         <v>364</v>
@@ -6633,10 +6633,10 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
+        <v>163</v>
+      </c>
+      <c r="D219" t="s">
         <v>363</v>
-      </c>
-      <c r="D219" t="s">
-        <v>163</v>
       </c>
       <c r="E219" t="s">
         <v>364</v>
@@ -6656,16 +6656,16 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="D220" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="E220" t="s">
-        <v>270</v>
+        <v>364</v>
       </c>
       <c r="F220" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="G220" t="s">
         <v>366</v>
@@ -6679,10 +6679,10 @@
         <v>8</v>
       </c>
       <c r="C221" t="s">
+        <v>163</v>
+      </c>
+      <c r="D221" t="s">
         <v>363</v>
-      </c>
-      <c r="D221" t="s">
-        <v>163</v>
       </c>
       <c r="E221" t="s">
         <v>364</v>
@@ -6702,10 +6702,10 @@
         <v>8</v>
       </c>
       <c r="C222" t="s">
+        <v>163</v>
+      </c>
+      <c r="D222" t="s">
         <v>363</v>
-      </c>
-      <c r="D222" t="s">
-        <v>163</v>
       </c>
       <c r="E222" t="s">
         <v>364</v>
@@ -6725,10 +6725,10 @@
         <v>8</v>
       </c>
       <c r="C223" t="s">
+        <v>163</v>
+      </c>
+      <c r="D223" t="s">
         <v>363</v>
-      </c>
-      <c r="D223" t="s">
-        <v>163</v>
       </c>
       <c r="E223" t="s">
         <v>364</v>
@@ -6748,10 +6748,10 @@
         <v>8</v>
       </c>
       <c r="C224" t="s">
+        <v>163</v>
+      </c>
+      <c r="D224" t="s">
         <v>363</v>
-      </c>
-      <c r="D224" t="s">
-        <v>163</v>
       </c>
       <c r="E224" t="s">
         <v>364</v>
@@ -6771,10 +6771,10 @@
         <v>8</v>
       </c>
       <c r="C225" t="s">
+        <v>163</v>
+      </c>
+      <c r="D225" t="s">
         <v>363</v>
-      </c>
-      <c r="D225" t="s">
-        <v>163</v>
       </c>
       <c r="E225" t="s">
         <v>364</v>
@@ -6794,13 +6794,13 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="D226" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="E226" t="s">
-        <v>275</v>
+        <v>364</v>
       </c>
       <c r="F226" t="s">
         <v>276</v>
@@ -6817,10 +6817,10 @@
         <v>8</v>
       </c>
       <c r="C227" t="s">
+        <v>163</v>
+      </c>
+      <c r="D227" t="s">
         <v>363</v>
-      </c>
-      <c r="D227" t="s">
-        <v>163</v>
       </c>
       <c r="E227" t="s">
         <v>364</v>
@@ -6840,13 +6840,13 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E228" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="F228" t="s">
         <v>165</v>
@@ -6863,16 +6863,16 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
+        <v>163</v>
+      </c>
+      <c r="D229" t="s">
         <v>386</v>
       </c>
-      <c r="D229" t="s">
-        <v>163</v>
-      </c>
       <c r="E229" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="F229" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="G229" t="s">
         <v>366</v>
@@ -6886,16 +6886,16 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
+        <v>163</v>
+      </c>
+      <c r="D230" t="s">
         <v>386</v>
       </c>
-      <c r="D230" t="s">
-        <v>163</v>
-      </c>
       <c r="E230" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="F230" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="G230" t="s">
         <v>366</v>
@@ -6909,16 +6909,16 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="D231" t="s">
-        <v>163</v>
+        <v>293</v>
       </c>
       <c r="E231" t="s">
-        <v>270</v>
+        <v>387</v>
       </c>
       <c r="F231" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="G231" t="s">
         <v>366</v>
@@ -6932,16 +6932,16 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="D232" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="E232" t="s">
-        <v>270</v>
+        <v>387</v>
       </c>
       <c r="F232" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="G232" t="s">
         <v>366</v>
@@ -6955,16 +6955,16 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
+        <v>163</v>
+      </c>
+      <c r="D233" t="s">
         <v>386</v>
       </c>
-      <c r="D233" t="s">
-        <v>163</v>
-      </c>
       <c r="E233" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="F233" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="G233" t="s">
         <v>366</v>
@@ -6978,16 +6978,16 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
+        <v>163</v>
+      </c>
+      <c r="D234" t="s">
         <v>386</v>
       </c>
-      <c r="D234" t="s">
-        <v>163</v>
-      </c>
       <c r="E234" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="F234" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="G234" t="s">
         <v>366</v>
@@ -7001,16 +7001,16 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
+        <v>163</v>
+      </c>
+      <c r="D235" t="s">
         <v>386</v>
       </c>
-      <c r="D235" t="s">
-        <v>163</v>
-      </c>
       <c r="E235" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="F235" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="G235" t="s">
         <v>366</v>
@@ -7024,16 +7024,16 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
+        <v>163</v>
+      </c>
+      <c r="D236" t="s">
         <v>386</v>
       </c>
-      <c r="D236" t="s">
-        <v>163</v>
-      </c>
       <c r="E236" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="F236" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="G236" t="s">
         <v>366</v>
@@ -7047,16 +7047,16 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
+        <v>163</v>
+      </c>
+      <c r="D237" t="s">
         <v>386</v>
       </c>
-      <c r="D237" t="s">
-        <v>163</v>
-      </c>
       <c r="E237" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="F237" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="G237" t="s">
         <v>366</v>
@@ -7070,16 +7070,16 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
+        <v>163</v>
+      </c>
+      <c r="D238" t="s">
         <v>386</v>
       </c>
-      <c r="D238" t="s">
-        <v>163</v>
-      </c>
       <c r="E238" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="F238" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="G238" t="s">
         <v>366</v>
@@ -7093,16 +7093,16 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
+        <v>163</v>
+      </c>
+      <c r="D239" t="s">
         <v>398</v>
       </c>
-      <c r="D239" t="s">
-        <v>163</v>
-      </c>
       <c r="E239" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="F239" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="G239" t="s">
         <v>366</v>
@@ -7116,13 +7116,13 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>163</v>
+      </c>
+      <c r="D240" t="s">
+        <v>164</v>
+      </c>
+      <c r="E240" t="s">
         <v>401</v>
-      </c>
-      <c r="D240" t="s">
-        <v>163</v>
-      </c>
-      <c r="E240" t="s">
-        <v>164</v>
       </c>
       <c r="F240" t="s">
         <v>165</v>
@@ -7139,13 +7139,13 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>163</v>
+      </c>
+      <c r="D241" t="s">
+        <v>164</v>
+      </c>
+      <c r="E241" t="s">
         <v>401</v>
-      </c>
-      <c r="D241" t="s">
-        <v>163</v>
-      </c>
-      <c r="E241" t="s">
-        <v>164</v>
       </c>
       <c r="F241" t="s">
         <v>165</v>
@@ -7162,13 +7162,13 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>163</v>
+      </c>
+      <c r="D242" t="s">
+        <v>164</v>
+      </c>
+      <c r="E242" t="s">
         <v>401</v>
-      </c>
-      <c r="D242" t="s">
-        <v>163</v>
-      </c>
-      <c r="E242" t="s">
-        <v>164</v>
       </c>
       <c r="F242" t="s">
         <v>165</v>
@@ -7185,13 +7185,13 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>163</v>
+      </c>
+      <c r="D243" t="s">
+        <v>164</v>
+      </c>
+      <c r="E243" t="s">
         <v>401</v>
-      </c>
-      <c r="D243" t="s">
-        <v>163</v>
-      </c>
-      <c r="E243" t="s">
-        <v>164</v>
       </c>
       <c r="F243" t="s">
         <v>165</v>
@@ -7208,13 +7208,13 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>163</v>
+      </c>
+      <c r="D244" t="s">
+        <v>164</v>
+      </c>
+      <c r="E244" t="s">
         <v>401</v>
-      </c>
-      <c r="D244" t="s">
-        <v>163</v>
-      </c>
-      <c r="E244" t="s">
-        <v>164</v>
       </c>
       <c r="F244" t="s">
         <v>165</v>
@@ -7231,13 +7231,13 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>163</v>
+      </c>
+      <c r="D245" t="s">
+        <v>164</v>
+      </c>
+      <c r="E245" t="s">
         <v>401</v>
-      </c>
-      <c r="D245" t="s">
-        <v>163</v>
-      </c>
-      <c r="E245" t="s">
-        <v>164</v>
       </c>
       <c r="F245" t="s">
         <v>165</v>
@@ -7254,16 +7254,16 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>163</v>
+      </c>
+      <c r="D246" t="s">
         <v>409</v>
       </c>
-      <c r="D246" t="s">
-        <v>163</v>
-      </c>
       <c r="E246" t="s">
-        <v>255</v>
+        <v>410</v>
       </c>
       <c r="F246" t="s">
-        <v>410</v>
+        <v>256</v>
       </c>
       <c r="G246" t="s">
         <v>402</v>
@@ -7276,10 +7276,10 @@
       <c r="B247" t="s">
         <v>8</v>
       </c>
+      <c r="C247" t="s">
+        <v>95</v>
+      </c>
       <c r="D247" t="s">
-        <v>95</v>
-      </c>
-      <c r="E247" t="s">
         <v>96</v>
       </c>
       <c r="F247" t="s">
@@ -7296,10 +7296,10 @@
       <c r="B248" t="s">
         <v>8</v>
       </c>
+      <c r="C248" t="s">
+        <v>95</v>
+      </c>
       <c r="D248" t="s">
-        <v>95</v>
-      </c>
-      <c r="E248" t="s">
         <v>96</v>
       </c>
       <c r="F248" t="s">
@@ -7316,10 +7316,10 @@
       <c r="B249" t="s">
         <v>8</v>
       </c>
+      <c r="C249" t="s">
+        <v>95</v>
+      </c>
       <c r="D249" t="s">
-        <v>95</v>
-      </c>
-      <c r="E249" t="s">
         <v>415</v>
       </c>
       <c r="F249" t="s">
@@ -7336,10 +7336,10 @@
       <c r="B250" t="s">
         <v>8</v>
       </c>
+      <c r="C250" t="s">
+        <v>95</v>
+      </c>
       <c r="D250" t="s">
-        <v>95</v>
-      </c>
-      <c r="E250" t="s">
         <v>96</v>
       </c>
       <c r="F250" t="s">
@@ -7356,10 +7356,10 @@
       <c r="B251" t="s">
         <v>8</v>
       </c>
+      <c r="C251" t="s">
+        <v>95</v>
+      </c>
       <c r="D251" t="s">
-        <v>95</v>
-      </c>
-      <c r="E251" t="s">
         <v>96</v>
       </c>
       <c r="F251" t="s">
@@ -7376,10 +7376,10 @@
       <c r="B252" t="s">
         <v>8</v>
       </c>
+      <c r="C252" t="s">
+        <v>95</v>
+      </c>
       <c r="D252" t="s">
-        <v>95</v>
-      </c>
-      <c r="E252" t="s">
         <v>96</v>
       </c>
       <c r="F252" t="s">
@@ -7396,10 +7396,10 @@
       <c r="B253" t="s">
         <v>8</v>
       </c>
+      <c r="C253" t="s">
+        <v>163</v>
+      </c>
       <c r="D253" t="s">
-        <v>163</v>
-      </c>
-      <c r="E253" t="s">
         <v>421</v>
       </c>
       <c r="F253" t="s">
@@ -7416,10 +7416,10 @@
       <c r="B254" t="s">
         <v>8</v>
       </c>
+      <c r="C254" t="s">
+        <v>90</v>
+      </c>
       <c r="D254" t="s">
-        <v>90</v>
-      </c>
-      <c r="E254" t="s">
         <v>219</v>
       </c>
       <c r="F254" t="s">
@@ -7436,10 +7436,10 @@
       <c r="B255" t="s">
         <v>8</v>
       </c>
+      <c r="C255" t="s">
+        <v>90</v>
+      </c>
       <c r="D255" t="s">
-        <v>90</v>
-      </c>
-      <c r="E255" t="s">
         <v>426</v>
       </c>
       <c r="F255" t="s">
@@ -7456,10 +7456,10 @@
       <c r="B256" t="s">
         <v>8</v>
       </c>
+      <c r="C256" t="s">
+        <v>90</v>
+      </c>
       <c r="D256" t="s">
-        <v>90</v>
-      </c>
-      <c r="E256" t="s">
         <v>426</v>
       </c>
       <c r="F256" t="s">
@@ -7476,10 +7476,10 @@
       <c r="B257" t="s">
         <v>8</v>
       </c>
+      <c r="C257" t="s">
+        <v>90</v>
+      </c>
       <c r="D257" t="s">
-        <v>90</v>
-      </c>
-      <c r="E257" t="s">
         <v>426</v>
       </c>
       <c r="F257" t="s">
@@ -7496,11 +7496,11 @@
       <c r="B258" t="s">
         <v>8</v>
       </c>
+      <c r="C258" t="s">
+        <v>163</v>
+      </c>
       <c r="D258" t="s">
-        <v>163</v>
-      </c>
-      <c r="E258" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F258" t="s">
         <v>327</v>
@@ -7516,10 +7516,10 @@
       <c r="B259" t="s">
         <v>8</v>
       </c>
+      <c r="C259" t="s">
+        <v>90</v>
+      </c>
       <c r="D259" t="s">
-        <v>90</v>
-      </c>
-      <c r="E259" t="s">
         <v>426</v>
       </c>
       <c r="F259" t="s">
@@ -7536,10 +7536,10 @@
       <c r="B260" t="s">
         <v>8</v>
       </c>
+      <c r="C260" t="s">
+        <v>163</v>
+      </c>
       <c r="D260" t="s">
-        <v>163</v>
-      </c>
-      <c r="E260" t="s">
         <v>164</v>
       </c>
       <c r="F260" t="s">
@@ -7556,10 +7556,10 @@
       <c r="B261" t="s">
         <v>8</v>
       </c>
+      <c r="C261" t="s">
+        <v>195</v>
+      </c>
       <c r="D261" t="s">
-        <v>195</v>
-      </c>
-      <c r="E261" t="s">
         <v>434</v>
       </c>
       <c r="F261" t="s">
@@ -7576,10 +7576,10 @@
       <c r="B262" t="s">
         <v>8</v>
       </c>
+      <c r="C262" t="s">
+        <v>163</v>
+      </c>
       <c r="D262" t="s">
-        <v>163</v>
-      </c>
-      <c r="E262" t="s">
         <v>164</v>
       </c>
       <c r="F262" t="s">
@@ -7596,10 +7596,10 @@
       <c r="B263" t="s">
         <v>8</v>
       </c>
+      <c r="C263" t="s">
+        <v>182</v>
+      </c>
       <c r="D263" t="s">
-        <v>182</v>
-      </c>
-      <c r="E263" t="s">
         <v>438</v>
       </c>
       <c r="F263" t="s">
@@ -7616,10 +7616,10 @@
       <c r="B264" t="s">
         <v>8</v>
       </c>
+      <c r="C264" t="s">
+        <v>31</v>
+      </c>
       <c r="D264" t="s">
-        <v>31</v>
-      </c>
-      <c r="E264" t="s">
         <v>32</v>
       </c>
       <c r="F264" t="s">
@@ -7636,11 +7636,11 @@
       <c r="B265" t="s">
         <v>8</v>
       </c>
+      <c r="C265" t="s">
+        <v>9</v>
+      </c>
       <c r="D265" t="s">
         <v>10</v>
-      </c>
-      <c r="E265" t="s">
-        <v>11</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
@@ -7656,10 +7656,10 @@
       <c r="B266" t="s">
         <v>8</v>
       </c>
+      <c r="C266" t="s">
+        <v>112</v>
+      </c>
       <c r="D266" t="s">
-        <v>113</v>
-      </c>
-      <c r="E266" t="s">
         <v>443</v>
       </c>
       <c r="F266" t="s">
@@ -7676,10 +7676,10 @@
       <c r="B267" t="s">
         <v>8</v>
       </c>
+      <c r="C267" t="s">
+        <v>112</v>
+      </c>
       <c r="D267" t="s">
-        <v>113</v>
-      </c>
-      <c r="E267" t="s">
         <v>118</v>
       </c>
       <c r="F267" t="s">
@@ -7696,10 +7696,10 @@
       <c r="B268" t="s">
         <v>8</v>
       </c>
+      <c r="C268" t="s">
+        <v>182</v>
+      </c>
       <c r="D268" t="s">
-        <v>182</v>
-      </c>
-      <c r="E268" t="s">
         <v>202</v>
       </c>
       <c r="F268" t="s">
@@ -7716,10 +7716,10 @@
       <c r="B269" t="s">
         <v>8</v>
       </c>
+      <c r="C269" t="s">
+        <v>112</v>
+      </c>
       <c r="D269" t="s">
-        <v>113</v>
-      </c>
-      <c r="E269" t="s">
         <v>118</v>
       </c>
       <c r="F269" t="s">
@@ -7736,10 +7736,10 @@
       <c r="B270" t="s">
         <v>8</v>
       </c>
+      <c r="C270" t="s">
+        <v>112</v>
+      </c>
       <c r="D270" t="s">
-        <v>113</v>
-      </c>
-      <c r="E270" t="s">
         <v>118</v>
       </c>
       <c r="F270" t="s">
@@ -7756,10 +7756,10 @@
       <c r="B271" t="s">
         <v>8</v>
       </c>
+      <c r="C271" t="s">
+        <v>112</v>
+      </c>
       <c r="D271" t="s">
-        <v>113</v>
-      </c>
-      <c r="E271" t="s">
         <v>453</v>
       </c>
       <c r="F271" t="s">
@@ -7776,10 +7776,10 @@
       <c r="B272" t="s">
         <v>8</v>
       </c>
+      <c r="C272" t="s">
+        <v>112</v>
+      </c>
       <c r="D272" t="s">
-        <v>113</v>
-      </c>
-      <c r="E272" t="s">
         <v>453</v>
       </c>
       <c r="F272" t="s">
@@ -7796,10 +7796,10 @@
       <c r="B273" t="s">
         <v>8</v>
       </c>
+      <c r="C273" t="s">
+        <v>112</v>
+      </c>
       <c r="D273" t="s">
-        <v>113</v>
-      </c>
-      <c r="E273" t="s">
         <v>453</v>
       </c>
       <c r="F273" t="s">
@@ -7816,10 +7816,10 @@
       <c r="B274" t="s">
         <v>8</v>
       </c>
+      <c r="C274" t="s">
+        <v>112</v>
+      </c>
       <c r="D274" t="s">
-        <v>113</v>
-      </c>
-      <c r="E274" t="s">
         <v>453</v>
       </c>
       <c r="F274" t="s">
@@ -7836,10 +7836,10 @@
       <c r="B275" t="s">
         <v>8</v>
       </c>
+      <c r="C275" t="s">
+        <v>112</v>
+      </c>
       <c r="D275" t="s">
-        <v>113</v>
-      </c>
-      <c r="E275" t="s">
         <v>453</v>
       </c>
       <c r="F275" t="s">
@@ -7856,10 +7856,10 @@
       <c r="B276" t="s">
         <v>8</v>
       </c>
+      <c r="C276" t="s">
+        <v>112</v>
+      </c>
       <c r="D276" t="s">
-        <v>113</v>
-      </c>
-      <c r="E276" t="s">
         <v>453</v>
       </c>
       <c r="F276" t="s">
@@ -7876,10 +7876,10 @@
       <c r="B277" t="s">
         <v>8</v>
       </c>
+      <c r="C277" t="s">
+        <v>112</v>
+      </c>
       <c r="D277" t="s">
-        <v>113</v>
-      </c>
-      <c r="E277" t="s">
         <v>453</v>
       </c>
       <c r="F277" t="s">
@@ -7896,10 +7896,10 @@
       <c r="B278" t="s">
         <v>8</v>
       </c>
+      <c r="C278" t="s">
+        <v>182</v>
+      </c>
       <c r="D278" t="s">
-        <v>182</v>
-      </c>
-      <c r="E278" t="s">
         <v>202</v>
       </c>
       <c r="F278" t="s">
@@ -7916,11 +7916,11 @@
       <c r="B279" t="s">
         <v>8</v>
       </c>
+      <c r="C279" t="s">
+        <v>31</v>
+      </c>
       <c r="D279" t="s">
-        <v>31</v>
-      </c>
-      <c r="E279" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F279" t="s">
         <v>53</v>
@@ -7936,11 +7936,11 @@
       <c r="B280" t="s">
         <v>8</v>
       </c>
+      <c r="C280" t="s">
+        <v>9</v>
+      </c>
       <c r="D280" t="s">
         <v>10</v>
-      </c>
-      <c r="E280" t="s">
-        <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
@@ -7956,10 +7956,10 @@
       <c r="B281" t="s">
         <v>8</v>
       </c>
+      <c r="C281" t="s">
+        <v>112</v>
+      </c>
       <c r="D281" t="s">
-        <v>113</v>
-      </c>
-      <c r="E281" t="s">
         <v>170</v>
       </c>
       <c r="F281" t="s">
@@ -7976,10 +7976,10 @@
       <c r="B282" t="s">
         <v>8</v>
       </c>
+      <c r="C282" t="s">
+        <v>124</v>
+      </c>
       <c r="D282" t="s">
-        <v>124</v>
-      </c>
-      <c r="E282" t="s">
         <v>125</v>
       </c>
       <c r="F282" t="s">
@@ -7996,14 +7996,14 @@
       <c r="B283" t="s">
         <v>8</v>
       </c>
+      <c r="C283" t="s">
+        <v>163</v>
+      </c>
       <c r="D283" t="s">
-        <v>163</v>
-      </c>
-      <c r="E283" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="F283" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="G283" t="s">
         <v>469</v>
@@ -8016,10 +8016,10 @@
       <c r="B284" t="s">
         <v>8</v>
       </c>
+      <c r="C284" t="s">
+        <v>124</v>
+      </c>
       <c r="D284" t="s">
-        <v>124</v>
-      </c>
-      <c r="E284" t="s">
         <v>125</v>
       </c>
       <c r="F284" t="s">
@@ -8036,10 +8036,10 @@
       <c r="B285" t="s">
         <v>8</v>
       </c>
+      <c r="C285" t="s">
+        <v>112</v>
+      </c>
       <c r="D285" t="s">
-        <v>113</v>
-      </c>
-      <c r="E285" t="s">
         <v>170</v>
       </c>
       <c r="F285" t="s">
@@ -8056,10 +8056,10 @@
       <c r="B286" t="s">
         <v>8</v>
       </c>
+      <c r="C286" t="s">
+        <v>182</v>
+      </c>
       <c r="D286" t="s">
-        <v>182</v>
-      </c>
-      <c r="E286" t="s">
         <v>438</v>
       </c>
       <c r="F286" t="s">
@@ -8076,10 +8076,10 @@
       <c r="B287" t="s">
         <v>8</v>
       </c>
+      <c r="C287" t="s">
+        <v>182</v>
+      </c>
       <c r="D287" t="s">
-        <v>182</v>
-      </c>
-      <c r="E287" t="s">
         <v>438</v>
       </c>
       <c r="F287" t="s">
@@ -8096,10 +8096,10 @@
       <c r="B288" t="s">
         <v>8</v>
       </c>
+      <c r="C288" t="s">
+        <v>9</v>
+      </c>
       <c r="D288" t="s">
-        <v>10</v>
-      </c>
-      <c r="E288" t="s">
         <v>41</v>
       </c>
       <c r="F288" t="s">
@@ -8116,10 +8116,10 @@
       <c r="B289" t="s">
         <v>8</v>
       </c>
+      <c r="C289" t="s">
+        <v>31</v>
+      </c>
       <c r="D289" t="s">
-        <v>31</v>
-      </c>
-      <c r="E289" t="s">
         <v>32</v>
       </c>
       <c r="F289" t="s">
@@ -8136,10 +8136,10 @@
       <c r="B290" t="s">
         <v>8</v>
       </c>
+      <c r="C290" t="s">
+        <v>31</v>
+      </c>
       <c r="D290" t="s">
-        <v>31</v>
-      </c>
-      <c r="E290" t="s">
         <v>32</v>
       </c>
       <c r="F290" t="s">
@@ -8156,10 +8156,10 @@
       <c r="B291" t="s">
         <v>8</v>
       </c>
+      <c r="C291" t="s">
+        <v>112</v>
+      </c>
       <c r="D291" t="s">
-        <v>113</v>
-      </c>
-      <c r="E291" t="s">
         <v>170</v>
       </c>
       <c r="F291" t="s">
@@ -8176,10 +8176,10 @@
       <c r="B292" t="s">
         <v>8</v>
       </c>
+      <c r="C292" t="s">
+        <v>112</v>
+      </c>
       <c r="D292" t="s">
-        <v>113</v>
-      </c>
-      <c r="E292" t="s">
         <v>170</v>
       </c>
       <c r="F292" t="s">
@@ -8196,10 +8196,10 @@
       <c r="B293" t="s">
         <v>8</v>
       </c>
+      <c r="C293" t="s">
+        <v>112</v>
+      </c>
       <c r="D293" t="s">
-        <v>113</v>
-      </c>
-      <c r="E293" t="s">
         <v>170</v>
       </c>
       <c r="F293" t="s">
@@ -8216,10 +8216,10 @@
       <c r="B294" t="s">
         <v>8</v>
       </c>
+      <c r="C294" t="s">
+        <v>112</v>
+      </c>
       <c r="D294" t="s">
-        <v>113</v>
-      </c>
-      <c r="E294" t="s">
         <v>170</v>
       </c>
       <c r="F294" t="s">
@@ -8236,10 +8236,10 @@
       <c r="B295" t="s">
         <v>8</v>
       </c>
+      <c r="C295" t="s">
+        <v>112</v>
+      </c>
       <c r="D295" t="s">
-        <v>113</v>
-      </c>
-      <c r="E295" t="s">
         <v>170</v>
       </c>
       <c r="F295" t="s">
@@ -8256,10 +8256,10 @@
       <c r="B296" t="s">
         <v>8</v>
       </c>
+      <c r="C296" t="s">
+        <v>112</v>
+      </c>
       <c r="D296" t="s">
-        <v>113</v>
-      </c>
-      <c r="E296" t="s">
         <v>170</v>
       </c>
       <c r="F296" t="s">

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,42 +22,42 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>11220</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>11320</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>09.2.2 - Upper‐secondary education (IS)</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>11420</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
@@ -169,18 +169,18 @@
     <t>12110</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -286,27 +286,27 @@
     <t>14010</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
@@ -352,21 +352,21 @@
     <t>15110</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>15113</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
@@ -505,12 +505,12 @@
     <t>15142</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -685,12 +685,12 @@
     <t>16061</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
@@ -823,18 +823,18 @@
     <t>23110</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>04.3.3 - Nuclear fuel (CS)</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>04.2.2 - Forestry (CS)</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>04.2.3 - Fishing and hunting (CS)</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,12 +1210,12 @@
     <t>32310</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>04.4.3 - Construction (CS)</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1279,15 +1279,15 @@
     <t>43010</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
   </si>
   <si>
     <t>60020</t>
@@ -1866,16 +1866,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
       <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1912,16 +1912,16 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
       <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
         <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1932,19 +1932,19 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1955,13 +1955,13 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -1978,19 +1978,19 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
       </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2001,19 +2001,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2024,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>29</v>
       </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2047,19 +2047,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2070,19 +2070,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>36</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>39</v>
       </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>36</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2116,19 +2116,19 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
         <v>41</v>
       </c>
-      <c r="E14" t="s">
-        <v>39</v>
-      </c>
       <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
         <v>42</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2139,19 +2139,19 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>45</v>
       </c>
       <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
         <v>46</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2162,19 +2162,19 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
         <v>48</v>
       </c>
-      <c r="E16" t="s">
-        <v>45</v>
-      </c>
       <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
         <v>49</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2185,16 +2185,16 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2208,16 +2208,16 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" t="s">
         <v>57</v>
       </c>
-      <c r="E19" t="s">
-        <v>52</v>
-      </c>
       <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
         <v>58</v>
-      </c>
-      <c r="G19" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2254,19 +2254,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" t="s">
         <v>60</v>
       </c>
-      <c r="E20" t="s">
-        <v>52</v>
-      </c>
       <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
         <v>61</v>
-      </c>
-      <c r="G20" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2277,16 +2277,16 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2300,19 +2300,19 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" t="s">
         <v>31</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>32</v>
       </c>
-      <c r="E22" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>33</v>
-      </c>
-      <c r="G22" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" t="s">
         <v>66</v>
       </c>
-      <c r="E23" t="s">
-        <v>64</v>
-      </c>
       <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
         <v>67</v>
-      </c>
-      <c r="G23" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2346,19 +2346,19 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
         <v>31</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
-        <v>64</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>33</v>
-      </c>
-      <c r="G24" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2369,19 +2369,19 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" t="s">
         <v>31</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
-        <v>64</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>33</v>
-      </c>
-      <c r="G25" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2392,19 +2392,19 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" t="s">
         <v>31</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>32</v>
       </c>
-      <c r="E26" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>33</v>
-      </c>
-      <c r="G26" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2415,19 +2415,19 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
         <v>31</v>
       </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>33</v>
-      </c>
-      <c r="G27" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2438,19 +2438,19 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
         <v>31</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>32</v>
       </c>
-      <c r="E28" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>33</v>
-      </c>
-      <c r="G28" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2461,19 +2461,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" t="s">
         <v>31</v>
       </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
         <v>32</v>
       </c>
-      <c r="E29" t="s">
-        <v>64</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>33</v>
-      </c>
-      <c r="G29" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2484,16 +2484,16 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G30" t="s">
         <v>54</v>
@@ -2507,19 +2507,19 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" t="s">
         <v>31</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
         <v>32</v>
       </c>
-      <c r="E31" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>33</v>
-      </c>
-      <c r="G31" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2530,19 +2530,19 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" t="s">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
         <v>32</v>
       </c>
-      <c r="E32" t="s">
-        <v>76</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>33</v>
-      </c>
-      <c r="G32" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2553,19 +2553,19 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" t="s">
         <v>31</v>
       </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
         <v>32</v>
       </c>
-      <c r="E33" t="s">
-        <v>76</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>33</v>
-      </c>
-      <c r="G33" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2576,19 +2576,19 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" t="s">
         <v>31</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
         <v>32</v>
       </c>
-      <c r="E34" t="s">
-        <v>76</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>33</v>
-      </c>
-      <c r="G34" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2599,19 +2599,19 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" t="s">
         <v>31</v>
       </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
         <v>32</v>
       </c>
-      <c r="E35" t="s">
-        <v>76</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>33</v>
-      </c>
-      <c r="G35" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" t="s">
         <v>57</v>
       </c>
-      <c r="E36" t="s">
-        <v>76</v>
-      </c>
       <c r="F36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" t="s">
         <v>58</v>
-      </c>
-      <c r="G36" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2644,17 +2644,17 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" t="s">
         <v>31</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>32</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>33</v>
-      </c>
-      <c r="G37" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2664,17 +2664,17 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" t="s">
         <v>31</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>32</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>33</v>
-      </c>
-      <c r="G38" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2684,17 +2684,17 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" t="s">
         <v>31</v>
       </c>
-      <c r="D39" t="s">
+      <c r="F39" t="s">
         <v>32</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>33</v>
-      </c>
-      <c r="G39" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2704,17 +2704,17 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" t="s">
         <v>31</v>
       </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>32</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>33</v>
-      </c>
-      <c r="G40" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2724,17 +2724,17 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="C41" t="s">
-        <v>31</v>
-      </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>83</v>
+      </c>
+      <c r="E41" t="s">
+        <v>53</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G41" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2744,17 +2744,17 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
-      <c r="C42" t="s">
-        <v>31</v>
-      </c>
       <c r="D42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" t="s">
         <v>57</v>
       </c>
       <c r="F42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" t="s">
         <v>58</v>
-      </c>
-      <c r="G42" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2764,10 +2764,10 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>90</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>91</v>
       </c>
       <c r="F43" t="s">
@@ -2784,17 +2784,17 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" t="s">
         <v>95</v>
       </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
         <v>96</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>97</v>
-      </c>
-      <c r="G44" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2804,10 +2804,10 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>90</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>91</v>
       </c>
       <c r="F45" t="s">
@@ -2824,10 +2824,10 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>90</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>91</v>
       </c>
       <c r="F46" t="s">
@@ -2844,17 +2844,17 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
-      <c r="C47" t="s">
-        <v>95</v>
-      </c>
       <c r="D47" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" t="s">
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>96</v>
+      </c>
+      <c r="G47" t="s">
         <v>102</v>
-      </c>
-      <c r="G47" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2864,10 +2864,10 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>90</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>91</v>
       </c>
       <c r="F48" t="s">
@@ -2884,10 +2884,10 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>90</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>91</v>
       </c>
       <c r="F49" t="s">
@@ -2904,17 +2904,17 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
-      <c r="C50" t="s">
-        <v>95</v>
-      </c>
       <c r="D50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" t="s">
         <v>101</v>
       </c>
       <c r="F50" t="s">
+        <v>96</v>
+      </c>
+      <c r="G50" t="s">
         <v>102</v>
-      </c>
-      <c r="G50" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2924,10 +2924,10 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>90</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>91</v>
       </c>
       <c r="F51" t="s">
@@ -2944,17 +2944,17 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
-      <c r="C52" t="s">
-        <v>95</v>
-      </c>
       <c r="D52" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" t="s">
         <v>108</v>
       </c>
       <c r="F52" t="s">
+        <v>96</v>
+      </c>
+      <c r="G52" t="s">
         <v>109</v>
-      </c>
-      <c r="G52" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2964,17 +2964,17 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C53" t="s">
-        <v>9</v>
-      </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>90</v>
+      </c>
+      <c r="E53" t="s">
+        <v>11</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3011,16 +3011,16 @@
         <v>112</v>
       </c>
       <c r="D55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E55" t="s">
         <v>118</v>
       </c>
-      <c r="E55" t="s">
-        <v>114</v>
-      </c>
       <c r="F55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G55" t="s">
         <v>119</v>
-      </c>
-      <c r="G55" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3034,16 +3034,16 @@
         <v>112</v>
       </c>
       <c r="D56" t="s">
+        <v>113</v>
+      </c>
+      <c r="E56" t="s">
         <v>121</v>
       </c>
-      <c r="E56" t="s">
-        <v>114</v>
-      </c>
       <c r="F56" t="s">
+        <v>115</v>
+      </c>
+      <c r="G56" t="s">
         <v>122</v>
-      </c>
-      <c r="G56" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3054,19 +3054,19 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" t="s">
         <v>124</v>
       </c>
-      <c r="D57" t="s">
+      <c r="F57" t="s">
         <v>125</v>
       </c>
-      <c r="E57" t="s">
-        <v>114</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>126</v>
-      </c>
-      <c r="G57" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3080,16 +3080,16 @@
         <v>112</v>
       </c>
       <c r="D58" t="s">
+        <v>113</v>
+      </c>
+      <c r="E58" t="s">
         <v>118</v>
       </c>
-      <c r="E58" t="s">
-        <v>114</v>
-      </c>
       <c r="F58" t="s">
+        <v>115</v>
+      </c>
+      <c r="G58" t="s">
         <v>119</v>
-      </c>
-      <c r="G58" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3103,16 +3103,16 @@
         <v>112</v>
       </c>
       <c r="D59" t="s">
+        <v>113</v>
+      </c>
+      <c r="E59" t="s">
         <v>118</v>
       </c>
-      <c r="E59" t="s">
-        <v>114</v>
-      </c>
       <c r="F59" t="s">
+        <v>115</v>
+      </c>
+      <c r="G59" t="s">
         <v>119</v>
-      </c>
-      <c r="G59" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3126,16 +3126,16 @@
         <v>112</v>
       </c>
       <c r="D60" t="s">
+        <v>113</v>
+      </c>
+      <c r="E60" t="s">
         <v>118</v>
       </c>
-      <c r="E60" t="s">
-        <v>114</v>
-      </c>
       <c r="F60" t="s">
+        <v>115</v>
+      </c>
+      <c r="G60" t="s">
         <v>119</v>
-      </c>
-      <c r="G60" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3149,16 +3149,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="s">
+        <v>113</v>
+      </c>
+      <c r="E61" t="s">
         <v>118</v>
       </c>
-      <c r="E61" t="s">
-        <v>114</v>
-      </c>
       <c r="F61" t="s">
+        <v>115</v>
+      </c>
+      <c r="G61" t="s">
         <v>119</v>
-      </c>
-      <c r="G61" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3172,16 +3172,16 @@
         <v>112</v>
       </c>
       <c r="D62" t="s">
+        <v>113</v>
+      </c>
+      <c r="E62" t="s">
         <v>118</v>
       </c>
-      <c r="E62" t="s">
-        <v>114</v>
-      </c>
       <c r="F62" t="s">
+        <v>115</v>
+      </c>
+      <c r="G62" t="s">
         <v>119</v>
-      </c>
-      <c r="G62" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3195,16 +3195,16 @@
         <v>112</v>
       </c>
       <c r="D63" t="s">
+        <v>113</v>
+      </c>
+      <c r="E63" t="s">
         <v>133</v>
       </c>
-      <c r="E63" t="s">
-        <v>114</v>
-      </c>
       <c r="F63" t="s">
+        <v>115</v>
+      </c>
+      <c r="G63" t="s">
         <v>119</v>
-      </c>
-      <c r="G63" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3218,16 +3218,16 @@
         <v>112</v>
       </c>
       <c r="D64" t="s">
+        <v>113</v>
+      </c>
+      <c r="E64" t="s">
         <v>133</v>
       </c>
-      <c r="E64" t="s">
-        <v>114</v>
-      </c>
       <c r="F64" t="s">
+        <v>115</v>
+      </c>
+      <c r="G64" t="s">
         <v>119</v>
-      </c>
-      <c r="G64" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3241,16 +3241,16 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
+        <v>113</v>
+      </c>
+      <c r="E65" t="s">
         <v>136</v>
       </c>
-      <c r="E65" t="s">
-        <v>114</v>
-      </c>
       <c r="F65" t="s">
+        <v>115</v>
+      </c>
+      <c r="G65" t="s">
         <v>137</v>
-      </c>
-      <c r="G65" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3287,16 +3287,16 @@
         <v>112</v>
       </c>
       <c r="D67" t="s">
+        <v>113</v>
+      </c>
+      <c r="E67" t="s">
         <v>118</v>
       </c>
-      <c r="E67" t="s">
-        <v>114</v>
-      </c>
       <c r="F67" t="s">
+        <v>115</v>
+      </c>
+      <c r="G67" t="s">
         <v>119</v>
-      </c>
-      <c r="G67" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3310,10 +3310,10 @@
         <v>112</v>
       </c>
       <c r="D68" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" t="s">
         <v>141</v>
-      </c>
-      <c r="E68" t="s">
-        <v>114</v>
       </c>
       <c r="F68" t="s">
         <v>115</v>
@@ -3333,10 +3333,10 @@
         <v>112</v>
       </c>
       <c r="D69" t="s">
+        <v>113</v>
+      </c>
+      <c r="E69" t="s">
         <v>143</v>
-      </c>
-      <c r="E69" t="s">
-        <v>114</v>
       </c>
       <c r="F69" t="s">
         <v>115</v>
@@ -3356,16 +3356,16 @@
         <v>112</v>
       </c>
       <c r="D70" t="s">
+        <v>113</v>
+      </c>
+      <c r="E70" t="s">
         <v>121</v>
       </c>
-      <c r="E70" t="s">
-        <v>114</v>
-      </c>
       <c r="F70" t="s">
+        <v>115</v>
+      </c>
+      <c r="G70" t="s">
         <v>122</v>
-      </c>
-      <c r="G70" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3379,16 +3379,16 @@
         <v>112</v>
       </c>
       <c r="D71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E71" t="s">
         <v>121</v>
       </c>
-      <c r="E71" t="s">
-        <v>114</v>
-      </c>
       <c r="F71" t="s">
+        <v>115</v>
+      </c>
+      <c r="G71" t="s">
         <v>122</v>
-      </c>
-      <c r="G71" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3422,19 +3422,19 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D73" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" t="s">
         <v>148</v>
       </c>
-      <c r="E73" t="s">
-        <v>114</v>
-      </c>
       <c r="F73" t="s">
+        <v>125</v>
+      </c>
+      <c r="G73" t="s">
         <v>149</v>
-      </c>
-      <c r="G73" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3445,19 +3445,19 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D74" t="s">
+        <v>113</v>
+      </c>
+      <c r="E74" t="s">
         <v>151</v>
       </c>
-      <c r="E74" t="s">
-        <v>114</v>
-      </c>
       <c r="F74" t="s">
+        <v>125</v>
+      </c>
+      <c r="G74" t="s">
         <v>152</v>
-      </c>
-      <c r="G74" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3468,19 +3468,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D75" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" t="s">
         <v>154</v>
       </c>
-      <c r="E75" t="s">
-        <v>114</v>
-      </c>
       <c r="F75" t="s">
+        <v>125</v>
+      </c>
+      <c r="G75" t="s">
         <v>155</v>
-      </c>
-      <c r="G75" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3491,19 +3491,19 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D76" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76" t="s">
         <v>148</v>
       </c>
-      <c r="E76" t="s">
-        <v>114</v>
-      </c>
       <c r="F76" t="s">
+        <v>125</v>
+      </c>
+      <c r="G76" t="s">
         <v>149</v>
-      </c>
-      <c r="G76" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3514,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D77" t="s">
+        <v>113</v>
+      </c>
+      <c r="E77" t="s">
         <v>148</v>
       </c>
-      <c r="E77" t="s">
-        <v>114</v>
-      </c>
       <c r="F77" t="s">
+        <v>125</v>
+      </c>
+      <c r="G77" t="s">
         <v>149</v>
-      </c>
-      <c r="G77" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3537,19 +3537,19 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D78" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" t="s">
         <v>151</v>
       </c>
-      <c r="E78" t="s">
-        <v>114</v>
-      </c>
       <c r="F78" t="s">
+        <v>125</v>
+      </c>
+      <c r="G78" t="s">
         <v>152</v>
-      </c>
-      <c r="G78" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3560,19 +3560,19 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D79" t="s">
+        <v>113</v>
+      </c>
+      <c r="E79" t="s">
         <v>160</v>
       </c>
-      <c r="E79" t="s">
-        <v>114</v>
-      </c>
       <c r="F79" t="s">
+        <v>125</v>
+      </c>
+      <c r="G79" t="s">
         <v>161</v>
-      </c>
-      <c r="G79" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3583,19 +3583,19 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
+        <v>112</v>
+      </c>
+      <c r="D80" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80" t="s">
         <v>163</v>
       </c>
-      <c r="D80" t="s">
-        <v>164</v>
-      </c>
-      <c r="E80" t="s">
-        <v>114</v>
-      </c>
       <c r="F80" t="s">
+        <v>164</v>
+      </c>
+      <c r="G80" t="s">
         <v>165</v>
-      </c>
-      <c r="G80" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3606,19 +3606,19 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
+        <v>112</v>
+      </c>
+      <c r="D81" t="s">
+        <v>113</v>
+      </c>
+      <c r="E81" t="s">
         <v>163</v>
       </c>
-      <c r="D81" t="s">
-        <v>164</v>
-      </c>
-      <c r="E81" t="s">
-        <v>114</v>
-      </c>
       <c r="F81" t="s">
+        <v>164</v>
+      </c>
+      <c r="G81" t="s">
         <v>165</v>
-      </c>
-      <c r="G81" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3629,19 +3629,19 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
+        <v>112</v>
+      </c>
+      <c r="D82" t="s">
+        <v>113</v>
+      </c>
+      <c r="E82" t="s">
         <v>163</v>
       </c>
-      <c r="D82" t="s">
-        <v>164</v>
-      </c>
-      <c r="E82" t="s">
-        <v>114</v>
-      </c>
       <c r="F82" t="s">
+        <v>164</v>
+      </c>
+      <c r="G82" t="s">
         <v>165</v>
-      </c>
-      <c r="G82" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3655,10 +3655,10 @@
         <v>112</v>
       </c>
       <c r="D83" t="s">
+        <v>113</v>
+      </c>
+      <c r="E83" t="s">
         <v>143</v>
-      </c>
-      <c r="E83" t="s">
-        <v>114</v>
       </c>
       <c r="F83" t="s">
         <v>115</v>
@@ -3678,16 +3678,16 @@
         <v>112</v>
       </c>
       <c r="D84" t="s">
+        <v>113</v>
+      </c>
+      <c r="E84" t="s">
         <v>170</v>
       </c>
-      <c r="E84" t="s">
-        <v>114</v>
-      </c>
       <c r="F84" t="s">
+        <v>115</v>
+      </c>
+      <c r="G84" t="s">
         <v>171</v>
-      </c>
-      <c r="G84" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3701,16 +3701,16 @@
         <v>112</v>
       </c>
       <c r="D85" t="s">
+        <v>113</v>
+      </c>
+      <c r="E85" t="s">
         <v>173</v>
       </c>
-      <c r="E85" t="s">
-        <v>114</v>
-      </c>
       <c r="F85" t="s">
+        <v>115</v>
+      </c>
+      <c r="G85" t="s">
         <v>119</v>
-      </c>
-      <c r="G85" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D86" t="s">
+        <v>113</v>
+      </c>
+      <c r="E86" t="s">
         <v>175</v>
       </c>
-      <c r="E86" t="s">
-        <v>114</v>
-      </c>
       <c r="F86" t="s">
+        <v>164</v>
+      </c>
+      <c r="G86" t="s">
         <v>176</v>
-      </c>
-      <c r="G86" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3747,16 +3747,16 @@
         <v>112</v>
       </c>
       <c r="D87" t="s">
+        <v>113</v>
+      </c>
+      <c r="E87" t="s">
         <v>173</v>
       </c>
-      <c r="E87" t="s">
-        <v>114</v>
-      </c>
       <c r="F87" t="s">
+        <v>115</v>
+      </c>
+      <c r="G87" t="s">
         <v>119</v>
-      </c>
-      <c r="G87" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3770,16 +3770,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="s">
+        <v>113</v>
+      </c>
+      <c r="E88" t="s">
         <v>118</v>
       </c>
-      <c r="E88" t="s">
-        <v>114</v>
-      </c>
       <c r="F88" t="s">
+        <v>115</v>
+      </c>
+      <c r="G88" t="s">
         <v>119</v>
-      </c>
-      <c r="G88" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3793,16 +3793,16 @@
         <v>112</v>
       </c>
       <c r="D89" t="s">
+        <v>113</v>
+      </c>
+      <c r="E89" t="s">
         <v>118</v>
       </c>
-      <c r="E89" t="s">
-        <v>114</v>
-      </c>
       <c r="F89" t="s">
+        <v>115</v>
+      </c>
+      <c r="G89" t="s">
         <v>119</v>
-      </c>
-      <c r="G89" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3813,19 +3813,19 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
+        <v>112</v>
+      </c>
+      <c r="D90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E90" t="s">
         <v>124</v>
       </c>
-      <c r="D90" t="s">
+      <c r="F90" t="s">
         <v>125</v>
       </c>
-      <c r="E90" t="s">
-        <v>114</v>
-      </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>126</v>
-      </c>
-      <c r="G90" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3836,19 +3836,19 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
+        <v>112</v>
+      </c>
+      <c r="D91" t="s">
+        <v>113</v>
+      </c>
+      <c r="E91" t="s">
         <v>182</v>
       </c>
-      <c r="D91" t="s">
+      <c r="F91" t="s">
         <v>183</v>
       </c>
-      <c r="E91" t="s">
-        <v>114</v>
-      </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>184</v>
-      </c>
-      <c r="G91" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3859,19 +3859,19 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" t="s">
+        <v>113</v>
+      </c>
+      <c r="E92" t="s">
         <v>124</v>
       </c>
-      <c r="D92" t="s">
+      <c r="F92" t="s">
         <v>125</v>
       </c>
-      <c r="E92" t="s">
-        <v>114</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>126</v>
-      </c>
-      <c r="G92" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3885,16 +3885,16 @@
         <v>112</v>
       </c>
       <c r="D93" t="s">
+        <v>113</v>
+      </c>
+      <c r="E93" t="s">
         <v>121</v>
       </c>
-      <c r="E93" t="s">
-        <v>114</v>
-      </c>
       <c r="F93" t="s">
+        <v>115</v>
+      </c>
+      <c r="G93" t="s">
         <v>122</v>
-      </c>
-      <c r="G93" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3905,19 +3905,19 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
+        <v>113</v>
+      </c>
+      <c r="E94" t="s">
         <v>124</v>
       </c>
-      <c r="D94" t="s">
+      <c r="F94" t="s">
         <v>125</v>
       </c>
-      <c r="E94" t="s">
-        <v>114</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>126</v>
-      </c>
-      <c r="G94" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3931,16 +3931,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="s">
+        <v>113</v>
+      </c>
+      <c r="E95" t="s">
         <v>189</v>
       </c>
-      <c r="E95" t="s">
-        <v>114</v>
-      </c>
       <c r="F95" t="s">
+        <v>115</v>
+      </c>
+      <c r="G95" t="s">
         <v>190</v>
-      </c>
-      <c r="G95" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3951,19 +3951,19 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" t="s">
         <v>124</v>
       </c>
-      <c r="D96" t="s">
+      <c r="F96" t="s">
         <v>125</v>
       </c>
-      <c r="E96" t="s">
-        <v>192</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>126</v>
-      </c>
-      <c r="G96" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3974,19 +3974,19 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" t="s">
         <v>124</v>
       </c>
-      <c r="D97" t="s">
+      <c r="F97" t="s">
         <v>125</v>
       </c>
-      <c r="E97" t="s">
-        <v>192</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>126</v>
-      </c>
-      <c r="G97" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3997,19 +3997,19 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>192</v>
+      </c>
+      <c r="D98" t="s">
+        <v>113</v>
+      </c>
+      <c r="E98" t="s">
         <v>195</v>
       </c>
-      <c r="D98" t="s">
+      <c r="F98" t="s">
         <v>196</v>
       </c>
-      <c r="E98" t="s">
-        <v>192</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>197</v>
-      </c>
-      <c r="G98" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4020,19 +4020,19 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>192</v>
+      </c>
+      <c r="D99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99" t="s">
         <v>124</v>
       </c>
-      <c r="D99" t="s">
+      <c r="F99" t="s">
         <v>125</v>
       </c>
-      <c r="E99" t="s">
-        <v>192</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>126</v>
-      </c>
-      <c r="G99" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="D100" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" t="s">
         <v>154</v>
       </c>
-      <c r="E100" t="s">
-        <v>192</v>
-      </c>
       <c r="F100" t="s">
+        <v>125</v>
+      </c>
+      <c r="G100" t="s">
         <v>155</v>
-      </c>
-      <c r="G100" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4066,19 +4066,19 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>192</v>
+      </c>
+      <c r="D101" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" t="s">
         <v>124</v>
       </c>
-      <c r="D101" t="s">
+      <c r="F101" t="s">
         <v>125</v>
       </c>
-      <c r="E101" t="s">
-        <v>192</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>126</v>
-      </c>
-      <c r="G101" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4088,14 +4088,14 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
-      <c r="C102" t="s">
-        <v>182</v>
-      </c>
       <c r="D102" t="s">
         <v>202</v>
       </c>
+      <c r="E102" t="s">
+        <v>203</v>
+      </c>
       <c r="F102" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G102" t="s">
         <v>204</v>
@@ -4108,14 +4108,14 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
-      <c r="C103" t="s">
-        <v>182</v>
-      </c>
       <c r="D103" t="s">
         <v>202</v>
       </c>
+      <c r="E103" t="s">
+        <v>203</v>
+      </c>
       <c r="F103" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G103" t="s">
         <v>204</v>
@@ -4128,14 +4128,14 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
-      <c r="C104" t="s">
-        <v>182</v>
-      </c>
       <c r="D104" t="s">
         <v>202</v>
       </c>
+      <c r="E104" t="s">
+        <v>203</v>
+      </c>
       <c r="F104" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G104" t="s">
         <v>204</v>
@@ -4148,17 +4148,17 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
-      <c r="C105" t="s">
-        <v>182</v>
-      </c>
       <c r="D105" t="s">
+        <v>202</v>
+      </c>
+      <c r="E105" t="s">
         <v>208</v>
       </c>
       <c r="F105" t="s">
+        <v>183</v>
+      </c>
+      <c r="G105" t="s">
         <v>209</v>
-      </c>
-      <c r="G105" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4168,14 +4168,14 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
-      <c r="C106" t="s">
-        <v>182</v>
-      </c>
       <c r="D106" t="s">
         <v>202</v>
       </c>
+      <c r="E106" t="s">
+        <v>203</v>
+      </c>
       <c r="F106" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G106" t="s">
         <v>204</v>
@@ -4188,17 +4188,17 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
+        <v>202</v>
+      </c>
+      <c r="E107" t="s">
         <v>182</v>
       </c>
-      <c r="D107" t="s">
+      <c r="F107" t="s">
         <v>183</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>184</v>
-      </c>
-      <c r="G107" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4208,17 +4208,17 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
-      <c r="C108" t="s">
-        <v>182</v>
-      </c>
       <c r="D108" t="s">
+        <v>202</v>
+      </c>
+      <c r="E108" t="s">
         <v>213</v>
       </c>
       <c r="F108" t="s">
+        <v>183</v>
+      </c>
+      <c r="G108" t="s">
         <v>214</v>
-      </c>
-      <c r="G108" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4228,17 +4228,17 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
-      <c r="C109" t="s">
-        <v>90</v>
-      </c>
       <c r="D109" t="s">
+        <v>202</v>
+      </c>
+      <c r="E109" t="s">
         <v>216</v>
       </c>
       <c r="F109" t="s">
+        <v>92</v>
+      </c>
+      <c r="G109" t="s">
         <v>217</v>
-      </c>
-      <c r="G109" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4248,17 +4248,17 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
-      <c r="C110" t="s">
-        <v>90</v>
-      </c>
       <c r="D110" t="s">
+        <v>202</v>
+      </c>
+      <c r="E110" t="s">
         <v>219</v>
       </c>
       <c r="F110" t="s">
+        <v>92</v>
+      </c>
+      <c r="G110" t="s">
         <v>220</v>
-      </c>
-      <c r="G110" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4268,14 +4268,14 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
-      <c r="C111" t="s">
-        <v>182</v>
-      </c>
       <c r="D111" t="s">
         <v>202</v>
       </c>
+      <c r="E111" t="s">
+        <v>203</v>
+      </c>
       <c r="F111" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G111" t="s">
         <v>204</v>
@@ -4288,17 +4288,17 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
+        <v>202</v>
+      </c>
+      <c r="E112" t="s">
         <v>223</v>
       </c>
-      <c r="D112" t="s">
+      <c r="F112" t="s">
         <v>224</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>225</v>
-      </c>
-      <c r="G112" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4308,17 +4308,17 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="C113" t="s">
-        <v>112</v>
-      </c>
       <c r="D113" t="s">
+        <v>202</v>
+      </c>
+      <c r="E113" t="s">
         <v>143</v>
       </c>
       <c r="F113" t="s">
         <v>115</v>
       </c>
       <c r="G113" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4328,17 +4328,17 @@
       <c r="B114" t="s">
         <v>8</v>
       </c>
-      <c r="C114" t="s">
-        <v>124</v>
-      </c>
       <c r="D114" t="s">
+        <v>202</v>
+      </c>
+      <c r="E114" t="s">
         <v>151</v>
       </c>
       <c r="F114" t="s">
+        <v>125</v>
+      </c>
+      <c r="G114" t="s">
         <v>152</v>
-      </c>
-      <c r="G114" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4348,17 +4348,17 @@
       <c r="B115" t="s">
         <v>8</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
+        <v>202</v>
+      </c>
+      <c r="E115" t="s">
         <v>182</v>
       </c>
-      <c r="D115" t="s">
+      <c r="F115" t="s">
         <v>183</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>184</v>
-      </c>
-      <c r="G115" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4368,17 +4368,17 @@
       <c r="B116" t="s">
         <v>8</v>
       </c>
-      <c r="C116" t="s">
-        <v>223</v>
-      </c>
       <c r="D116" t="s">
+        <v>202</v>
+      </c>
+      <c r="E116" t="s">
         <v>230</v>
       </c>
       <c r="F116" t="s">
+        <v>224</v>
+      </c>
+      <c r="G116" t="s">
         <v>231</v>
-      </c>
-      <c r="G116" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4388,17 +4388,17 @@
       <c r="B117" t="s">
         <v>8</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
+        <v>202</v>
+      </c>
+      <c r="E117" t="s">
         <v>223</v>
       </c>
-      <c r="D117" t="s">
+      <c r="F117" t="s">
         <v>224</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>225</v>
-      </c>
-      <c r="G117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4408,17 +4408,17 @@
       <c r="B118" t="s">
         <v>8</v>
       </c>
-      <c r="C118" t="s">
-        <v>163</v>
-      </c>
       <c r="D118" t="s">
+        <v>202</v>
+      </c>
+      <c r="E118" t="s">
         <v>234</v>
       </c>
       <c r="F118" t="s">
+        <v>164</v>
+      </c>
+      <c r="G118" t="s">
         <v>165</v>
-      </c>
-      <c r="G118" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4428,17 +4428,17 @@
       <c r="B119" t="s">
         <v>8</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
+        <v>202</v>
+      </c>
+      <c r="E119" t="s">
         <v>182</v>
       </c>
-      <c r="D119" t="s">
+      <c r="F119" t="s">
         <v>183</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>184</v>
-      </c>
-      <c r="G119" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4448,17 +4448,17 @@
       <c r="B120" t="s">
         <v>8</v>
       </c>
-      <c r="C120" t="s">
-        <v>112</v>
-      </c>
       <c r="D120" t="s">
+        <v>237</v>
+      </c>
+      <c r="E120" t="s">
         <v>170</v>
       </c>
       <c r="F120" t="s">
+        <v>115</v>
+      </c>
+      <c r="G120" t="s">
         <v>171</v>
-      </c>
-      <c r="G120" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4468,17 +4468,17 @@
       <c r="B121" t="s">
         <v>8</v>
       </c>
-      <c r="C121" t="s">
-        <v>112</v>
-      </c>
       <c r="D121" t="s">
+        <v>237</v>
+      </c>
+      <c r="E121" t="s">
         <v>143</v>
       </c>
       <c r="F121" t="s">
         <v>115</v>
       </c>
       <c r="G121" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4488,17 +4488,17 @@
       <c r="B122" t="s">
         <v>8</v>
       </c>
-      <c r="C122" t="s">
-        <v>112</v>
-      </c>
       <c r="D122" t="s">
+        <v>237</v>
+      </c>
+      <c r="E122" t="s">
         <v>170</v>
       </c>
       <c r="F122" t="s">
+        <v>115</v>
+      </c>
+      <c r="G122" t="s">
         <v>171</v>
-      </c>
-      <c r="G122" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4508,17 +4508,17 @@
       <c r="B123" t="s">
         <v>8</v>
       </c>
-      <c r="C123" t="s">
-        <v>112</v>
-      </c>
       <c r="D123" t="s">
+        <v>237</v>
+      </c>
+      <c r="E123" t="s">
         <v>170</v>
       </c>
       <c r="F123" t="s">
+        <v>115</v>
+      </c>
+      <c r="G123" t="s">
         <v>171</v>
-      </c>
-      <c r="G123" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4528,17 +4528,17 @@
       <c r="B124" t="s">
         <v>8</v>
       </c>
-      <c r="C124" t="s">
-        <v>163</v>
-      </c>
       <c r="D124" t="s">
+        <v>237</v>
+      </c>
+      <c r="E124" t="s">
         <v>242</v>
       </c>
       <c r="F124" t="s">
+        <v>164</v>
+      </c>
+      <c r="G124" t="s">
         <v>243</v>
-      </c>
-      <c r="G124" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4548,17 +4548,17 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="C125" t="s">
-        <v>163</v>
-      </c>
       <c r="D125" t="s">
+        <v>237</v>
+      </c>
+      <c r="E125" t="s">
         <v>242</v>
       </c>
       <c r="F125" t="s">
+        <v>164</v>
+      </c>
+      <c r="G125" t="s">
         <v>243</v>
-      </c>
-      <c r="G125" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4568,17 +4568,17 @@
       <c r="B126" t="s">
         <v>8</v>
       </c>
-      <c r="C126" t="s">
-        <v>163</v>
-      </c>
       <c r="D126" t="s">
+        <v>237</v>
+      </c>
+      <c r="E126" t="s">
         <v>242</v>
       </c>
       <c r="F126" t="s">
+        <v>164</v>
+      </c>
+      <c r="G126" t="s">
         <v>243</v>
-      </c>
-      <c r="G126" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4588,17 +4588,17 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
-      <c r="C127" t="s">
-        <v>163</v>
-      </c>
       <c r="D127" t="s">
+        <v>237</v>
+      </c>
+      <c r="E127" t="s">
         <v>242</v>
       </c>
       <c r="F127" t="s">
+        <v>164</v>
+      </c>
+      <c r="G127" t="s">
         <v>243</v>
-      </c>
-      <c r="G127" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4608,17 +4608,17 @@
       <c r="B128" t="s">
         <v>8</v>
       </c>
-      <c r="C128" t="s">
-        <v>163</v>
-      </c>
       <c r="D128" t="s">
+        <v>237</v>
+      </c>
+      <c r="E128" t="s">
         <v>242</v>
       </c>
       <c r="F128" t="s">
+        <v>164</v>
+      </c>
+      <c r="G128" t="s">
         <v>243</v>
-      </c>
-      <c r="G128" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4628,17 +4628,17 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
-      <c r="C129" t="s">
-        <v>163</v>
-      </c>
       <c r="D129" t="s">
+        <v>237</v>
+      </c>
+      <c r="E129" t="s">
         <v>249</v>
       </c>
       <c r="F129" t="s">
+        <v>164</v>
+      </c>
+      <c r="G129" t="s">
         <v>243</v>
-      </c>
-      <c r="G129" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4648,17 +4648,17 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
-      <c r="C130" t="s">
-        <v>163</v>
-      </c>
       <c r="D130" t="s">
+        <v>237</v>
+      </c>
+      <c r="E130" t="s">
         <v>251</v>
       </c>
       <c r="F130" t="s">
+        <v>164</v>
+      </c>
+      <c r="G130" t="s">
         <v>243</v>
-      </c>
-      <c r="G130" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4668,17 +4668,17 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
-      <c r="C131" t="s">
-        <v>163</v>
-      </c>
       <c r="D131" t="s">
+        <v>237</v>
+      </c>
+      <c r="E131" t="s">
         <v>253</v>
       </c>
       <c r="F131" t="s">
+        <v>164</v>
+      </c>
+      <c r="G131" t="s">
         <v>243</v>
-      </c>
-      <c r="G131" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4688,17 +4688,17 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
-      <c r="C132" t="s">
-        <v>163</v>
-      </c>
       <c r="D132" t="s">
+        <v>237</v>
+      </c>
+      <c r="E132" t="s">
         <v>255</v>
       </c>
       <c r="F132" t="s">
+        <v>164</v>
+      </c>
+      <c r="G132" t="s">
         <v>256</v>
-      </c>
-      <c r="G132" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4708,17 +4708,17 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
-      <c r="C133" t="s">
-        <v>112</v>
-      </c>
       <c r="D133" t="s">
+        <v>237</v>
+      </c>
+      <c r="E133" t="s">
         <v>189</v>
       </c>
       <c r="F133" t="s">
+        <v>115</v>
+      </c>
+      <c r="G133" t="s">
         <v>190</v>
-      </c>
-      <c r="G133" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4728,17 +4728,17 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
-      <c r="C134" t="s">
-        <v>163</v>
-      </c>
       <c r="D134" t="s">
+        <v>259</v>
+      </c>
+      <c r="E134" t="s">
         <v>175</v>
       </c>
       <c r="F134" t="s">
+        <v>164</v>
+      </c>
+      <c r="G134" t="s">
         <v>176</v>
-      </c>
-      <c r="G134" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4748,17 +4748,17 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
-      <c r="C135" t="s">
-        <v>163</v>
-      </c>
       <c r="D135" t="s">
+        <v>259</v>
+      </c>
+      <c r="E135" t="s">
         <v>175</v>
       </c>
       <c r="F135" t="s">
+        <v>164</v>
+      </c>
+      <c r="G135" t="s">
         <v>176</v>
-      </c>
-      <c r="G135" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4768,17 +4768,17 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
-      <c r="C136" t="s">
-        <v>163</v>
-      </c>
       <c r="D136" t="s">
+        <v>259</v>
+      </c>
+      <c r="E136" t="s">
         <v>175</v>
       </c>
       <c r="F136" t="s">
+        <v>164</v>
+      </c>
+      <c r="G136" t="s">
         <v>176</v>
-      </c>
-      <c r="G136" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4788,17 +4788,17 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="C137" t="s">
-        <v>163</v>
-      </c>
       <c r="D137" t="s">
+        <v>259</v>
+      </c>
+      <c r="E137" t="s">
         <v>175</v>
       </c>
       <c r="F137" t="s">
+        <v>164</v>
+      </c>
+      <c r="G137" t="s">
         <v>176</v>
-      </c>
-      <c r="G137" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4808,17 +4808,17 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
-      <c r="C138" t="s">
-        <v>163</v>
-      </c>
       <c r="D138" t="s">
+        <v>259</v>
+      </c>
+      <c r="E138" t="s">
         <v>175</v>
       </c>
       <c r="F138" t="s">
+        <v>164</v>
+      </c>
+      <c r="G138" t="s">
         <v>176</v>
-      </c>
-      <c r="G138" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4828,17 +4828,17 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
-      <c r="C139" t="s">
-        <v>223</v>
-      </c>
       <c r="D139" t="s">
+        <v>259</v>
+      </c>
+      <c r="E139" t="s">
         <v>265</v>
       </c>
       <c r="F139" t="s">
+        <v>224</v>
+      </c>
+      <c r="G139" t="s">
         <v>266</v>
-      </c>
-      <c r="G139" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4848,17 +4848,17 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
-      <c r="C140" t="s">
-        <v>163</v>
-      </c>
       <c r="D140" t="s">
+        <v>259</v>
+      </c>
+      <c r="E140" t="s">
         <v>175</v>
       </c>
       <c r="F140" t="s">
+        <v>164</v>
+      </c>
+      <c r="G140" t="s">
         <v>176</v>
-      </c>
-      <c r="G140" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4869,16 +4869,16 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D141" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4892,16 +4892,16 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D142" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4915,19 +4915,19 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D143" t="s">
+        <v>270</v>
+      </c>
+      <c r="E143" t="s">
         <v>275</v>
       </c>
-      <c r="E143" t="s">
-        <v>270</v>
-      </c>
       <c r="F143" t="s">
+        <v>164</v>
+      </c>
+      <c r="G143" t="s">
         <v>276</v>
-      </c>
-      <c r="G143" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4938,19 +4938,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D144" t="s">
+        <v>270</v>
+      </c>
+      <c r="E144" t="s">
         <v>275</v>
       </c>
-      <c r="E144" t="s">
-        <v>270</v>
-      </c>
       <c r="F144" t="s">
+        <v>164</v>
+      </c>
+      <c r="G144" t="s">
         <v>276</v>
-      </c>
-      <c r="G144" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4961,19 +4961,19 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D145" t="s">
+        <v>270</v>
+      </c>
+      <c r="E145" t="s">
         <v>275</v>
       </c>
-      <c r="E145" t="s">
-        <v>270</v>
-      </c>
       <c r="F145" t="s">
+        <v>164</v>
+      </c>
+      <c r="G145" t="s">
         <v>276</v>
-      </c>
-      <c r="G145" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4984,16 +4984,16 @@
         <v>8</v>
       </c>
       <c r="C146" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D146" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5007,16 +5007,16 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D147" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G147" t="s">
         <v>272</v>
@@ -5030,16 +5030,16 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D148" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G148" t="s">
         <v>272</v>
@@ -5053,16 +5053,16 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D149" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G149" t="s">
         <v>272</v>
@@ -5076,16 +5076,16 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D150" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G150" t="s">
         <v>272</v>
@@ -5099,16 +5099,16 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D151" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G151" t="s">
         <v>272</v>
@@ -5122,16 +5122,16 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D152" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G152" t="s">
         <v>272</v>
@@ -5145,16 +5145,16 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D153" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G153" t="s">
         <v>272</v>
@@ -5168,16 +5168,16 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D154" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G154" t="s">
         <v>272</v>
@@ -5191,16 +5191,16 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G155" t="s">
         <v>272</v>
@@ -5214,16 +5214,16 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D156" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G156" t="s">
         <v>272</v>
@@ -5237,16 +5237,16 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D157" t="s">
+        <v>270</v>
+      </c>
+      <c r="E157" t="s">
         <v>293</v>
       </c>
-      <c r="E157" t="s">
-        <v>291</v>
-      </c>
       <c r="F157" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G157" t="s">
         <v>272</v>
@@ -5260,16 +5260,16 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G158" t="s">
         <v>272</v>
@@ -5283,16 +5283,16 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D159" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G159" t="s">
         <v>272</v>
@@ -5306,16 +5306,16 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D160" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G160" t="s">
         <v>272</v>
@@ -5329,16 +5329,16 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D161" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G161" t="s">
         <v>272</v>
@@ -5352,16 +5352,16 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>163</v>
+        <v>299</v>
       </c>
       <c r="D162" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G162" t="s">
         <v>272</v>
@@ -5375,16 +5375,16 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>163</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="E163" t="s">
         <v>302</v>
       </c>
       <c r="F163" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G163" t="s">
         <v>272</v>
@@ -5398,16 +5398,16 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D164" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G164" t="s">
         <v>272</v>
@@ -5421,16 +5421,16 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D165" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G165" t="s">
         <v>272</v>
@@ -5444,16 +5444,16 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G166" t="s">
         <v>272</v>
@@ -5467,16 +5467,16 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D167" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G167" t="s">
         <v>272</v>
@@ -5490,16 +5490,16 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D168" t="s">
+        <v>270</v>
+      </c>
+      <c r="E168" t="s">
         <v>309</v>
       </c>
-      <c r="E168" t="s">
-        <v>304</v>
-      </c>
       <c r="F168" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G168" t="s">
         <v>272</v>
@@ -5513,16 +5513,16 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D169" t="s">
+        <v>270</v>
+      </c>
+      <c r="E169" t="s">
         <v>309</v>
       </c>
-      <c r="E169" t="s">
-        <v>304</v>
-      </c>
       <c r="F169" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G169" t="s">
         <v>272</v>
@@ -5536,16 +5536,16 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D170" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G170" t="s">
         <v>272</v>
@@ -5558,17 +5558,17 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
+        <v>313</v>
+      </c>
+      <c r="E171" t="s">
         <v>163</v>
       </c>
-      <c r="D171" t="s">
-        <v>164</v>
-      </c>
       <c r="F171" t="s">
+        <v>164</v>
+      </c>
+      <c r="G171" t="s">
         <v>165</v>
-      </c>
-      <c r="G171" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5578,17 +5578,17 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
-      <c r="C172" t="s">
-        <v>112</v>
-      </c>
       <c r="D172" t="s">
+        <v>313</v>
+      </c>
+      <c r="E172" t="s">
         <v>118</v>
       </c>
       <c r="F172" t="s">
+        <v>115</v>
+      </c>
+      <c r="G172" t="s">
         <v>119</v>
-      </c>
-      <c r="G172" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5598,17 +5598,17 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" t="s">
+        <v>313</v>
+      </c>
+      <c r="E173" t="s">
         <v>163</v>
       </c>
-      <c r="D173" t="s">
-        <v>164</v>
-      </c>
       <c r="F173" t="s">
+        <v>164</v>
+      </c>
+      <c r="G173" t="s">
         <v>165</v>
-      </c>
-      <c r="G173" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5618,17 +5618,17 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174" t="s">
+        <v>313</v>
+      </c>
+      <c r="E174" t="s">
         <v>163</v>
       </c>
-      <c r="D174" t="s">
-        <v>164</v>
-      </c>
       <c r="F174" t="s">
+        <v>164</v>
+      </c>
+      <c r="G174" t="s">
         <v>165</v>
-      </c>
-      <c r="G174" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5638,17 +5638,17 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D175" t="s">
+        <v>313</v>
+      </c>
+      <c r="E175" t="s">
         <v>163</v>
       </c>
-      <c r="D175" t="s">
-        <v>164</v>
-      </c>
       <c r="F175" t="s">
+        <v>164</v>
+      </c>
+      <c r="G175" t="s">
         <v>165</v>
-      </c>
-      <c r="G175" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5658,17 +5658,17 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
+        <v>313</v>
+      </c>
+      <c r="E176" t="s">
         <v>163</v>
       </c>
-      <c r="D176" t="s">
-        <v>164</v>
-      </c>
       <c r="F176" t="s">
+        <v>164</v>
+      </c>
+      <c r="G176" t="s">
         <v>165</v>
-      </c>
-      <c r="G176" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5678,17 +5678,17 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177" t="s">
+        <v>320</v>
+      </c>
+      <c r="E177" t="s">
         <v>163</v>
       </c>
-      <c r="D177" t="s">
-        <v>164</v>
-      </c>
       <c r="F177" t="s">
+        <v>164</v>
+      </c>
+      <c r="G177" t="s">
         <v>165</v>
-      </c>
-      <c r="G177" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5698,17 +5698,17 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178" t="s">
+        <v>320</v>
+      </c>
+      <c r="E178" t="s">
         <v>163</v>
       </c>
-      <c r="D178" t="s">
-        <v>164</v>
-      </c>
       <c r="F178" t="s">
+        <v>164</v>
+      </c>
+      <c r="G178" t="s">
         <v>165</v>
-      </c>
-      <c r="G178" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5718,17 +5718,17 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D179" t="s">
+        <v>320</v>
+      </c>
+      <c r="E179" t="s">
         <v>163</v>
       </c>
-      <c r="D179" t="s">
-        <v>164</v>
-      </c>
       <c r="F179" t="s">
+        <v>164</v>
+      </c>
+      <c r="G179" t="s">
         <v>165</v>
-      </c>
-      <c r="G179" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5738,17 +5738,17 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
+        <v>320</v>
+      </c>
+      <c r="E180" t="s">
         <v>163</v>
       </c>
-      <c r="D180" t="s">
-        <v>164</v>
-      </c>
       <c r="F180" t="s">
+        <v>164</v>
+      </c>
+      <c r="G180" t="s">
         <v>165</v>
-      </c>
-      <c r="G180" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5759,16 +5759,16 @@
         <v>8</v>
       </c>
       <c r="C181" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D181" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5782,16 +5782,16 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D182" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5805,16 +5805,16 @@
         <v>8</v>
       </c>
       <c r="C183" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D183" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5828,16 +5828,16 @@
         <v>8</v>
       </c>
       <c r="C184" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D184" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5851,16 +5851,16 @@
         <v>8</v>
       </c>
       <c r="C185" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D185" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5874,16 +5874,16 @@
         <v>8</v>
       </c>
       <c r="C186" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D186" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5897,16 +5897,16 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D187" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5920,16 +5920,16 @@
         <v>8</v>
       </c>
       <c r="C188" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D188" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5943,16 +5943,16 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D189" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5966,16 +5966,16 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D190" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5989,16 +5989,16 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D191" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6012,16 +6012,16 @@
         <v>8</v>
       </c>
       <c r="C192" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D192" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D193" t="s">
+        <v>326</v>
+      </c>
+      <c r="E193" t="s">
         <v>341</v>
       </c>
-      <c r="E193" t="s">
-        <v>326</v>
-      </c>
       <c r="F193" t="s">
+        <v>164</v>
+      </c>
+      <c r="G193" t="s">
         <v>276</v>
-      </c>
-      <c r="G193" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6058,16 +6058,16 @@
         <v>8</v>
       </c>
       <c r="C194" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D194" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E194" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G194" t="s">
         <v>328</v>
@@ -6081,16 +6081,16 @@
         <v>8</v>
       </c>
       <c r="C195" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D195" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E195" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G195" t="s">
         <v>328</v>
@@ -6104,16 +6104,16 @@
         <v>8</v>
       </c>
       <c r="C196" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D196" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E196" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G196" t="s">
         <v>328</v>
@@ -6127,16 +6127,16 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D197" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G197" t="s">
         <v>328</v>
@@ -6150,16 +6150,16 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D198" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E198" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G198" t="s">
         <v>328</v>
@@ -6173,16 +6173,16 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E199" t="s">
         <v>349</v>
       </c>
       <c r="F199" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G199" t="s">
         <v>328</v>
@@ -6196,16 +6196,16 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E200" t="s">
         <v>349</v>
       </c>
       <c r="F200" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G200" t="s">
         <v>328</v>
@@ -6219,16 +6219,16 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E201" t="s">
         <v>349</v>
       </c>
       <c r="F201" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G201" t="s">
         <v>328</v>
@@ -6242,16 +6242,16 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E202" t="s">
         <v>349</v>
       </c>
       <c r="F202" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G202" t="s">
         <v>328</v>
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D203" t="s">
+        <v>326</v>
+      </c>
+      <c r="E203" t="s">
         <v>341</v>
       </c>
-      <c r="E203" t="s">
-        <v>349</v>
-      </c>
       <c r="F203" t="s">
+        <v>164</v>
+      </c>
+      <c r="G203" t="s">
         <v>276</v>
-      </c>
-      <c r="G203" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,16 +6288,16 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E204" t="s">
         <v>349</v>
       </c>
       <c r="F204" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G204" t="s">
         <v>328</v>
@@ -6311,16 +6311,16 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E205" t="s">
         <v>357</v>
       </c>
       <c r="F205" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G205" t="s">
         <v>328</v>
@@ -6334,16 +6334,16 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E206" t="s">
         <v>357</v>
       </c>
       <c r="F206" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G206" t="s">
         <v>328</v>
@@ -6357,16 +6357,16 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E207" t="s">
         <v>357</v>
       </c>
       <c r="F207" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G207" t="s">
         <v>328</v>
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D208" t="s">
+        <v>326</v>
+      </c>
+      <c r="E208" t="s">
         <v>341</v>
       </c>
-      <c r="E208" t="s">
-        <v>357</v>
-      </c>
       <c r="F208" t="s">
+        <v>164</v>
+      </c>
+      <c r="G208" t="s">
         <v>276</v>
-      </c>
-      <c r="G208" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,16 +6403,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E209" t="s">
         <v>357</v>
       </c>
       <c r="F209" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G209" t="s">
         <v>328</v>
@@ -6426,16 +6426,16 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D210" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E210" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G210" t="s">
         <v>366</v>
@@ -6449,16 +6449,16 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D211" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E211" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G211" t="s">
         <v>366</v>
@@ -6472,16 +6472,16 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D212" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E212" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G212" t="s">
         <v>366</v>
@@ -6495,16 +6495,16 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D213" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E213" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G213" t="s">
         <v>366</v>
@@ -6518,16 +6518,16 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D214" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E214" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G214" t="s">
         <v>366</v>
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D215" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="E215" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="F215" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G215" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6564,16 +6564,16 @@
         <v>8</v>
       </c>
       <c r="C216" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D216" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E216" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G216" t="s">
         <v>366</v>
@@ -6587,16 +6587,16 @@
         <v>8</v>
       </c>
       <c r="C217" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D217" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E217" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G217" t="s">
         <v>366</v>
@@ -6610,16 +6610,16 @@
         <v>8</v>
       </c>
       <c r="C218" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D218" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E218" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G218" t="s">
         <v>366</v>
@@ -6633,16 +6633,16 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D219" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E219" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G219" t="s">
         <v>366</v>
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D220" t="s">
+        <v>364</v>
+      </c>
+      <c r="E220" t="s">
         <v>309</v>
       </c>
-      <c r="E220" t="s">
-        <v>364</v>
-      </c>
       <c r="F220" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G220" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6679,16 +6679,16 @@
         <v>8</v>
       </c>
       <c r="C221" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D221" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E221" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G221" t="s">
         <v>366</v>
@@ -6702,16 +6702,16 @@
         <v>8</v>
       </c>
       <c r="C222" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D222" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E222" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G222" t="s">
         <v>366</v>
@@ -6725,16 +6725,16 @@
         <v>8</v>
       </c>
       <c r="C223" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D223" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E223" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G223" t="s">
         <v>366</v>
@@ -6748,16 +6748,16 @@
         <v>8</v>
       </c>
       <c r="C224" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D224" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E224" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G224" t="s">
         <v>366</v>
@@ -6771,16 +6771,16 @@
         <v>8</v>
       </c>
       <c r="C225" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D225" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E225" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G225" t="s">
         <v>366</v>
@@ -6794,19 +6794,19 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D226" t="s">
+        <v>364</v>
+      </c>
+      <c r="E226" t="s">
         <v>275</v>
       </c>
-      <c r="E226" t="s">
-        <v>364</v>
-      </c>
       <c r="F226" t="s">
+        <v>164</v>
+      </c>
+      <c r="G226" t="s">
         <v>276</v>
-      </c>
-      <c r="G226" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6817,16 +6817,16 @@
         <v>8</v>
       </c>
       <c r="C227" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D227" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E227" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G227" t="s">
         <v>366</v>
@@ -6840,19 +6840,19 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
+        <v>363</v>
+      </c>
+      <c r="D228" t="s">
+        <v>364</v>
+      </c>
+      <c r="E228" t="s">
         <v>163</v>
       </c>
-      <c r="D228" t="s">
-        <v>164</v>
-      </c>
-      <c r="E228" t="s">
-        <v>364</v>
-      </c>
       <c r="F228" t="s">
+        <v>164</v>
+      </c>
+      <c r="G228" t="s">
         <v>165</v>
-      </c>
-      <c r="G228" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,16 +6863,16 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E229" t="s">
         <v>387</v>
       </c>
       <c r="F229" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G229" t="s">
         <v>366</v>
@@ -6886,16 +6886,16 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E230" t="s">
         <v>387</v>
       </c>
       <c r="F230" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G230" t="s">
         <v>366</v>
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D231" t="s">
+        <v>364</v>
+      </c>
+      <c r="E231" t="s">
         <v>293</v>
       </c>
-      <c r="E231" t="s">
-        <v>387</v>
-      </c>
       <c r="F231" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G231" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D232" t="s">
+        <v>364</v>
+      </c>
+      <c r="E232" t="s">
         <v>309</v>
       </c>
-      <c r="E232" t="s">
-        <v>387</v>
-      </c>
       <c r="F232" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G232" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,16 +6955,16 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E233" t="s">
         <v>387</v>
       </c>
       <c r="F233" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G233" t="s">
         <v>366</v>
@@ -6978,16 +6978,16 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E234" t="s">
         <v>387</v>
       </c>
       <c r="F234" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G234" t="s">
         <v>366</v>
@@ -7001,16 +7001,16 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E235" t="s">
         <v>387</v>
       </c>
       <c r="F235" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G235" t="s">
         <v>366</v>
@@ -7024,16 +7024,16 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E236" t="s">
         <v>387</v>
       </c>
       <c r="F236" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G236" t="s">
         <v>366</v>
@@ -7047,16 +7047,16 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E237" t="s">
         <v>387</v>
       </c>
       <c r="F237" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G237" t="s">
         <v>366</v>
@@ -7070,16 +7070,16 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E238" t="s">
         <v>387</v>
       </c>
       <c r="F238" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G238" t="s">
         <v>366</v>
@@ -7093,16 +7093,16 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>163</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="E239" t="s">
         <v>399</v>
       </c>
       <c r="F239" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G239" t="s">
         <v>366</v>
@@ -7116,19 +7116,19 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>401</v>
+      </c>
+      <c r="D240" t="s">
+        <v>402</v>
+      </c>
+      <c r="E240" t="s">
         <v>163</v>
       </c>
-      <c r="D240" t="s">
-        <v>164</v>
-      </c>
-      <c r="E240" t="s">
-        <v>401</v>
-      </c>
       <c r="F240" t="s">
+        <v>164</v>
+      </c>
+      <c r="G240" t="s">
         <v>165</v>
-      </c>
-      <c r="G240" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7139,19 +7139,19 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>401</v>
+      </c>
+      <c r="D241" t="s">
+        <v>402</v>
+      </c>
+      <c r="E241" t="s">
         <v>163</v>
       </c>
-      <c r="D241" t="s">
-        <v>164</v>
-      </c>
-      <c r="E241" t="s">
-        <v>401</v>
-      </c>
       <c r="F241" t="s">
+        <v>164</v>
+      </c>
+      <c r="G241" t="s">
         <v>165</v>
-      </c>
-      <c r="G241" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7162,19 +7162,19 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>401</v>
+      </c>
+      <c r="D242" t="s">
+        <v>402</v>
+      </c>
+      <c r="E242" t="s">
         <v>163</v>
       </c>
-      <c r="D242" t="s">
-        <v>164</v>
-      </c>
-      <c r="E242" t="s">
-        <v>401</v>
-      </c>
       <c r="F242" t="s">
+        <v>164</v>
+      </c>
+      <c r="G242" t="s">
         <v>165</v>
-      </c>
-      <c r="G242" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7185,19 +7185,19 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>401</v>
+      </c>
+      <c r="D243" t="s">
+        <v>402</v>
+      </c>
+      <c r="E243" t="s">
         <v>163</v>
       </c>
-      <c r="D243" t="s">
-        <v>164</v>
-      </c>
-      <c r="E243" t="s">
-        <v>401</v>
-      </c>
       <c r="F243" t="s">
+        <v>164</v>
+      </c>
+      <c r="G243" t="s">
         <v>165</v>
-      </c>
-      <c r="G243" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7208,19 +7208,19 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>401</v>
+      </c>
+      <c r="D244" t="s">
+        <v>402</v>
+      </c>
+      <c r="E244" t="s">
         <v>163</v>
       </c>
-      <c r="D244" t="s">
-        <v>164</v>
-      </c>
-      <c r="E244" t="s">
-        <v>401</v>
-      </c>
       <c r="F244" t="s">
+        <v>164</v>
+      </c>
+      <c r="G244" t="s">
         <v>165</v>
-      </c>
-      <c r="G244" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7231,19 +7231,19 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>401</v>
+      </c>
+      <c r="D245" t="s">
+        <v>402</v>
+      </c>
+      <c r="E245" t="s">
         <v>163</v>
       </c>
-      <c r="D245" t="s">
-        <v>164</v>
-      </c>
-      <c r="E245" t="s">
-        <v>401</v>
-      </c>
       <c r="F245" t="s">
+        <v>164</v>
+      </c>
+      <c r="G245" t="s">
         <v>165</v>
-      </c>
-      <c r="G245" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>163</v>
+        <v>409</v>
       </c>
       <c r="D246" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="E246" t="s">
         <v>410</v>
       </c>
       <c r="F246" t="s">
+        <v>164</v>
+      </c>
+      <c r="G246" t="s">
         <v>256</v>
-      </c>
-      <c r="G246" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7276,17 +7276,17 @@
       <c r="B247" t="s">
         <v>8</v>
       </c>
-      <c r="C247" t="s">
+      <c r="D247" t="s">
+        <v>412</v>
+      </c>
+      <c r="E247" t="s">
         <v>95</v>
       </c>
-      <c r="D247" t="s">
+      <c r="F247" t="s">
         <v>96</v>
       </c>
-      <c r="F247" t="s">
+      <c r="G247" t="s">
         <v>97</v>
-      </c>
-      <c r="G247" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7296,17 +7296,17 @@
       <c r="B248" t="s">
         <v>8</v>
       </c>
-      <c r="C248" t="s">
+      <c r="D248" t="s">
+        <v>412</v>
+      </c>
+      <c r="E248" t="s">
         <v>95</v>
       </c>
-      <c r="D248" t="s">
+      <c r="F248" t="s">
         <v>96</v>
       </c>
-      <c r="F248" t="s">
+      <c r="G248" t="s">
         <v>97</v>
-      </c>
-      <c r="G248" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7316,17 +7316,17 @@
       <c r="B249" t="s">
         <v>8</v>
       </c>
-      <c r="C249" t="s">
-        <v>95</v>
-      </c>
       <c r="D249" t="s">
+        <v>412</v>
+      </c>
+      <c r="E249" t="s">
         <v>415</v>
       </c>
       <c r="F249" t="s">
+        <v>96</v>
+      </c>
+      <c r="G249" t="s">
         <v>416</v>
-      </c>
-      <c r="G249" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7336,17 +7336,17 @@
       <c r="B250" t="s">
         <v>8</v>
       </c>
-      <c r="C250" t="s">
+      <c r="D250" t="s">
+        <v>412</v>
+      </c>
+      <c r="E250" t="s">
         <v>95</v>
       </c>
-      <c r="D250" t="s">
+      <c r="F250" t="s">
         <v>96</v>
       </c>
-      <c r="F250" t="s">
+      <c r="G250" t="s">
         <v>97</v>
-      </c>
-      <c r="G250" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7356,17 +7356,17 @@
       <c r="B251" t="s">
         <v>8</v>
       </c>
-      <c r="C251" t="s">
+      <c r="D251" t="s">
+        <v>412</v>
+      </c>
+      <c r="E251" t="s">
         <v>95</v>
       </c>
-      <c r="D251" t="s">
+      <c r="F251" t="s">
         <v>96</v>
       </c>
-      <c r="F251" t="s">
+      <c r="G251" t="s">
         <v>97</v>
-      </c>
-      <c r="G251" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7376,17 +7376,17 @@
       <c r="B252" t="s">
         <v>8</v>
       </c>
-      <c r="C252" t="s">
+      <c r="D252" t="s">
+        <v>412</v>
+      </c>
+      <c r="E252" t="s">
         <v>95</v>
       </c>
-      <c r="D252" t="s">
+      <c r="F252" t="s">
         <v>96</v>
       </c>
-      <c r="F252" t="s">
+      <c r="G252" t="s">
         <v>97</v>
-      </c>
-      <c r="G252" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7396,14 +7396,14 @@
       <c r="B253" t="s">
         <v>8</v>
       </c>
-      <c r="C253" t="s">
-        <v>163</v>
-      </c>
       <c r="D253" t="s">
         <v>421</v>
       </c>
+      <c r="E253" t="s">
+        <v>422</v>
+      </c>
       <c r="F253" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="G253" t="s">
         <v>423</v>
@@ -7416,17 +7416,17 @@
       <c r="B254" t="s">
         <v>8</v>
       </c>
-      <c r="C254" t="s">
-        <v>90</v>
-      </c>
       <c r="D254" t="s">
+        <v>421</v>
+      </c>
+      <c r="E254" t="s">
         <v>219</v>
       </c>
       <c r="F254" t="s">
+        <v>92</v>
+      </c>
+      <c r="G254" t="s">
         <v>220</v>
-      </c>
-      <c r="G254" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7436,17 +7436,17 @@
       <c r="B255" t="s">
         <v>8</v>
       </c>
-      <c r="C255" t="s">
-        <v>90</v>
-      </c>
       <c r="D255" t="s">
+        <v>421</v>
+      </c>
+      <c r="E255" t="s">
         <v>426</v>
       </c>
       <c r="F255" t="s">
+        <v>92</v>
+      </c>
+      <c r="G255" t="s">
         <v>427</v>
-      </c>
-      <c r="G255" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7456,17 +7456,17 @@
       <c r="B256" t="s">
         <v>8</v>
       </c>
-      <c r="C256" t="s">
-        <v>90</v>
-      </c>
       <c r="D256" t="s">
+        <v>421</v>
+      </c>
+      <c r="E256" t="s">
         <v>426</v>
       </c>
       <c r="F256" t="s">
+        <v>92</v>
+      </c>
+      <c r="G256" t="s">
         <v>427</v>
-      </c>
-      <c r="G256" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7476,17 +7476,17 @@
       <c r="B257" t="s">
         <v>8</v>
       </c>
-      <c r="C257" t="s">
-        <v>90</v>
-      </c>
       <c r="D257" t="s">
+        <v>421</v>
+      </c>
+      <c r="E257" t="s">
         <v>426</v>
       </c>
       <c r="F257" t="s">
+        <v>92</v>
+      </c>
+      <c r="G257" t="s">
         <v>427</v>
-      </c>
-      <c r="G257" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7496,17 +7496,17 @@
       <c r="B258" t="s">
         <v>8</v>
       </c>
-      <c r="C258" t="s">
-        <v>163</v>
-      </c>
       <c r="D258" t="s">
-        <v>325</v>
+        <v>421</v>
+      </c>
+      <c r="E258" t="s">
+        <v>327</v>
       </c>
       <c r="F258" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G258" t="s">
-        <v>423</v>
+        <v>328</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7516,17 +7516,17 @@
       <c r="B259" t="s">
         <v>8</v>
       </c>
-      <c r="C259" t="s">
-        <v>90</v>
-      </c>
       <c r="D259" t="s">
+        <v>421</v>
+      </c>
+      <c r="E259" t="s">
         <v>426</v>
       </c>
       <c r="F259" t="s">
+        <v>92</v>
+      </c>
+      <c r="G259" t="s">
         <v>427</v>
-      </c>
-      <c r="G259" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7536,17 +7536,17 @@
       <c r="B260" t="s">
         <v>8</v>
       </c>
-      <c r="C260" t="s">
+      <c r="D260" t="s">
+        <v>421</v>
+      </c>
+      <c r="E260" t="s">
         <v>163</v>
       </c>
-      <c r="D260" t="s">
-        <v>164</v>
-      </c>
       <c r="F260" t="s">
+        <v>164</v>
+      </c>
+      <c r="G260" t="s">
         <v>165</v>
-      </c>
-      <c r="G260" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7556,17 +7556,17 @@
       <c r="B261" t="s">
         <v>8</v>
       </c>
-      <c r="C261" t="s">
-        <v>195</v>
-      </c>
       <c r="D261" t="s">
+        <v>421</v>
+      </c>
+      <c r="E261" t="s">
         <v>434</v>
       </c>
       <c r="F261" t="s">
+        <v>196</v>
+      </c>
+      <c r="G261" t="s">
         <v>435</v>
-      </c>
-      <c r="G261" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7576,17 +7576,17 @@
       <c r="B262" t="s">
         <v>8</v>
       </c>
-      <c r="C262" t="s">
+      <c r="D262" t="s">
+        <v>421</v>
+      </c>
+      <c r="E262" t="s">
         <v>163</v>
       </c>
-      <c r="D262" t="s">
-        <v>164</v>
-      </c>
       <c r="F262" t="s">
+        <v>164</v>
+      </c>
+      <c r="G262" t="s">
         <v>165</v>
-      </c>
-      <c r="G262" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7596,17 +7596,17 @@
       <c r="B263" t="s">
         <v>8</v>
       </c>
-      <c r="C263" t="s">
-        <v>182</v>
-      </c>
       <c r="D263" t="s">
+        <v>421</v>
+      </c>
+      <c r="E263" t="s">
         <v>438</v>
       </c>
       <c r="F263" t="s">
+        <v>183</v>
+      </c>
+      <c r="G263" t="s">
         <v>439</v>
-      </c>
-      <c r="G263" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7616,17 +7616,17 @@
       <c r="B264" t="s">
         <v>8</v>
       </c>
-      <c r="C264" t="s">
+      <c r="D264" t="s">
+        <v>421</v>
+      </c>
+      <c r="E264" t="s">
         <v>31</v>
       </c>
-      <c r="D264" t="s">
+      <c r="F264" t="s">
         <v>32</v>
       </c>
-      <c r="F264" t="s">
+      <c r="G264" t="s">
         <v>33</v>
-      </c>
-      <c r="G264" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7636,17 +7636,17 @@
       <c r="B265" t="s">
         <v>8</v>
       </c>
-      <c r="C265" t="s">
-        <v>9</v>
-      </c>
       <c r="D265" t="s">
-        <v>10</v>
+        <v>421</v>
+      </c>
+      <c r="E265" t="s">
+        <v>11</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
       </c>
       <c r="G265" t="s">
-        <v>423</v>
+        <v>13</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7656,17 +7656,17 @@
       <c r="B266" t="s">
         <v>8</v>
       </c>
-      <c r="C266" t="s">
-        <v>112</v>
-      </c>
       <c r="D266" t="s">
+        <v>421</v>
+      </c>
+      <c r="E266" t="s">
         <v>443</v>
       </c>
       <c r="F266" t="s">
+        <v>115</v>
+      </c>
+      <c r="G266" t="s">
         <v>444</v>
-      </c>
-      <c r="G266" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7676,17 +7676,17 @@
       <c r="B267" t="s">
         <v>8</v>
       </c>
-      <c r="C267" t="s">
-        <v>112</v>
-      </c>
       <c r="D267" t="s">
+        <v>446</v>
+      </c>
+      <c r="E267" t="s">
         <v>118</v>
       </c>
       <c r="F267" t="s">
+        <v>115</v>
+      </c>
+      <c r="G267" t="s">
         <v>119</v>
-      </c>
-      <c r="G267" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7696,17 +7696,17 @@
       <c r="B268" t="s">
         <v>8</v>
       </c>
-      <c r="C268" t="s">
-        <v>182</v>
-      </c>
       <c r="D268" t="s">
-        <v>202</v>
+        <v>448</v>
+      </c>
+      <c r="E268" t="s">
+        <v>203</v>
       </c>
       <c r="F268" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G268" t="s">
-        <v>448</v>
+        <v>204</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7716,17 +7716,17 @@
       <c r="B269" t="s">
         <v>8</v>
       </c>
-      <c r="C269" t="s">
-        <v>112</v>
-      </c>
       <c r="D269" t="s">
+        <v>450</v>
+      </c>
+      <c r="E269" t="s">
         <v>118</v>
       </c>
       <c r="F269" t="s">
+        <v>115</v>
+      </c>
+      <c r="G269" t="s">
         <v>119</v>
-      </c>
-      <c r="G269" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7736,17 +7736,17 @@
       <c r="B270" t="s">
         <v>8</v>
       </c>
-      <c r="C270" t="s">
-        <v>112</v>
-      </c>
       <c r="D270" t="s">
+        <v>450</v>
+      </c>
+      <c r="E270" t="s">
         <v>118</v>
       </c>
       <c r="F270" t="s">
+        <v>115</v>
+      </c>
+      <c r="G270" t="s">
         <v>119</v>
-      </c>
-      <c r="G270" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7756,14 +7756,14 @@
       <c r="B271" t="s">
         <v>8</v>
       </c>
-      <c r="C271" t="s">
-        <v>112</v>
-      </c>
       <c r="D271" t="s">
         <v>453</v>
       </c>
+      <c r="E271" t="s">
+        <v>454</v>
+      </c>
       <c r="F271" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G271" t="s">
         <v>455</v>
@@ -7776,14 +7776,14 @@
       <c r="B272" t="s">
         <v>8</v>
       </c>
-      <c r="C272" t="s">
-        <v>112</v>
-      </c>
       <c r="D272" t="s">
         <v>453</v>
       </c>
+      <c r="E272" t="s">
+        <v>454</v>
+      </c>
       <c r="F272" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G272" t="s">
         <v>455</v>
@@ -7796,14 +7796,14 @@
       <c r="B273" t="s">
         <v>8</v>
       </c>
-      <c r="C273" t="s">
-        <v>112</v>
-      </c>
       <c r="D273" t="s">
         <v>453</v>
       </c>
+      <c r="E273" t="s">
+        <v>454</v>
+      </c>
       <c r="F273" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G273" t="s">
         <v>455</v>
@@ -7816,14 +7816,14 @@
       <c r="B274" t="s">
         <v>8</v>
       </c>
-      <c r="C274" t="s">
-        <v>112</v>
-      </c>
       <c r="D274" t="s">
         <v>453</v>
       </c>
+      <c r="E274" t="s">
+        <v>454</v>
+      </c>
       <c r="F274" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G274" t="s">
         <v>455</v>
@@ -7836,14 +7836,14 @@
       <c r="B275" t="s">
         <v>8</v>
       </c>
-      <c r="C275" t="s">
-        <v>112</v>
-      </c>
       <c r="D275" t="s">
         <v>453</v>
       </c>
+      <c r="E275" t="s">
+        <v>454</v>
+      </c>
       <c r="F275" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G275" t="s">
         <v>455</v>
@@ -7856,14 +7856,14 @@
       <c r="B276" t="s">
         <v>8</v>
       </c>
-      <c r="C276" t="s">
-        <v>112</v>
-      </c>
       <c r="D276" t="s">
         <v>453</v>
       </c>
+      <c r="E276" t="s">
+        <v>454</v>
+      </c>
       <c r="F276" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G276" t="s">
         <v>455</v>
@@ -7876,14 +7876,14 @@
       <c r="B277" t="s">
         <v>8</v>
       </c>
-      <c r="C277" t="s">
-        <v>112</v>
-      </c>
       <c r="D277" t="s">
         <v>453</v>
       </c>
+      <c r="E277" t="s">
+        <v>454</v>
+      </c>
       <c r="F277" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G277" t="s">
         <v>455</v>
@@ -7896,17 +7896,17 @@
       <c r="B278" t="s">
         <v>8</v>
       </c>
-      <c r="C278" t="s">
-        <v>182</v>
-      </c>
       <c r="D278" t="s">
-        <v>202</v>
+        <v>463</v>
+      </c>
+      <c r="E278" t="s">
+        <v>203</v>
       </c>
       <c r="F278" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G278" t="s">
-        <v>463</v>
+        <v>204</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7916,17 +7916,17 @@
       <c r="B279" t="s">
         <v>8</v>
       </c>
-      <c r="C279" t="s">
-        <v>31</v>
-      </c>
       <c r="D279" t="s">
-        <v>51</v>
+        <v>463</v>
+      </c>
+      <c r="E279" t="s">
+        <v>53</v>
       </c>
       <c r="F279" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G279" t="s">
-        <v>463</v>
+        <v>54</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7936,17 +7936,17 @@
       <c r="B280" t="s">
         <v>8</v>
       </c>
-      <c r="C280" t="s">
-        <v>9</v>
-      </c>
       <c r="D280" t="s">
-        <v>10</v>
+        <v>463</v>
+      </c>
+      <c r="E280" t="s">
+        <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
       </c>
       <c r="G280" t="s">
-        <v>463</v>
+        <v>13</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7956,17 +7956,17 @@
       <c r="B281" t="s">
         <v>8</v>
       </c>
-      <c r="C281" t="s">
-        <v>112</v>
-      </c>
       <c r="D281" t="s">
+        <v>463</v>
+      </c>
+      <c r="E281" t="s">
         <v>170</v>
       </c>
       <c r="F281" t="s">
+        <v>115</v>
+      </c>
+      <c r="G281" t="s">
         <v>171</v>
-      </c>
-      <c r="G281" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7976,17 +7976,17 @@
       <c r="B282" t="s">
         <v>8</v>
       </c>
-      <c r="C282" t="s">
+      <c r="D282" t="s">
+        <v>463</v>
+      </c>
+      <c r="E282" t="s">
         <v>124</v>
       </c>
-      <c r="D282" t="s">
+      <c r="F282" t="s">
         <v>125</v>
       </c>
-      <c r="F282" t="s">
+      <c r="G282" t="s">
         <v>126</v>
-      </c>
-      <c r="G282" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7996,17 +7996,17 @@
       <c r="B283" t="s">
         <v>8</v>
       </c>
-      <c r="C283" t="s">
-        <v>163</v>
-      </c>
       <c r="D283" t="s">
-        <v>398</v>
+        <v>469</v>
+      </c>
+      <c r="E283" t="s">
+        <v>399</v>
       </c>
       <c r="F283" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G283" t="s">
-        <v>469</v>
+        <v>366</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8016,17 +8016,17 @@
       <c r="B284" t="s">
         <v>8</v>
       </c>
-      <c r="C284" t="s">
+      <c r="D284" t="s">
+        <v>471</v>
+      </c>
+      <c r="E284" t="s">
         <v>124</v>
       </c>
-      <c r="D284" t="s">
+      <c r="F284" t="s">
         <v>125</v>
       </c>
-      <c r="F284" t="s">
+      <c r="G284" t="s">
         <v>126</v>
-      </c>
-      <c r="G284" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8036,17 +8036,17 @@
       <c r="B285" t="s">
         <v>8</v>
       </c>
-      <c r="C285" t="s">
-        <v>112</v>
-      </c>
       <c r="D285" t="s">
+        <v>473</v>
+      </c>
+      <c r="E285" t="s">
         <v>170</v>
       </c>
       <c r="F285" t="s">
+        <v>115</v>
+      </c>
+      <c r="G285" t="s">
         <v>171</v>
-      </c>
-      <c r="G285" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8056,17 +8056,17 @@
       <c r="B286" t="s">
         <v>8</v>
       </c>
-      <c r="C286" t="s">
-        <v>182</v>
-      </c>
       <c r="D286" t="s">
+        <v>475</v>
+      </c>
+      <c r="E286" t="s">
         <v>438</v>
       </c>
       <c r="F286" t="s">
+        <v>183</v>
+      </c>
+      <c r="G286" t="s">
         <v>439</v>
-      </c>
-      <c r="G286" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8076,17 +8076,17 @@
       <c r="B287" t="s">
         <v>8</v>
       </c>
-      <c r="C287" t="s">
-        <v>182</v>
-      </c>
       <c r="D287" t="s">
+        <v>475</v>
+      </c>
+      <c r="E287" t="s">
         <v>438</v>
       </c>
       <c r="F287" t="s">
+        <v>183</v>
+      </c>
+      <c r="G287" t="s">
         <v>439</v>
-      </c>
-      <c r="G287" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8096,17 +8096,17 @@
       <c r="B288" t="s">
         <v>8</v>
       </c>
-      <c r="C288" t="s">
-        <v>9</v>
-      </c>
       <c r="D288" t="s">
+        <v>475</v>
+      </c>
+      <c r="E288" t="s">
         <v>41</v>
       </c>
       <c r="F288" t="s">
+        <v>12</v>
+      </c>
+      <c r="G288" t="s">
         <v>42</v>
-      </c>
-      <c r="G288" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8116,17 +8116,17 @@
       <c r="B289" t="s">
         <v>8</v>
       </c>
-      <c r="C289" t="s">
+      <c r="D289" t="s">
+        <v>475</v>
+      </c>
+      <c r="E289" t="s">
         <v>31</v>
       </c>
-      <c r="D289" t="s">
+      <c r="F289" t="s">
         <v>32</v>
       </c>
-      <c r="F289" t="s">
+      <c r="G289" t="s">
         <v>33</v>
-      </c>
-      <c r="G289" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8136,17 +8136,17 @@
       <c r="B290" t="s">
         <v>8</v>
       </c>
-      <c r="C290" t="s">
+      <c r="D290" t="s">
+        <v>475</v>
+      </c>
+      <c r="E290" t="s">
         <v>31</v>
       </c>
-      <c r="D290" t="s">
+      <c r="F290" t="s">
         <v>32</v>
       </c>
-      <c r="F290" t="s">
+      <c r="G290" t="s">
         <v>33</v>
-      </c>
-      <c r="G290" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8156,17 +8156,17 @@
       <c r="B291" t="s">
         <v>8</v>
       </c>
-      <c r="C291" t="s">
-        <v>112</v>
-      </c>
       <c r="D291" t="s">
+        <v>475</v>
+      </c>
+      <c r="E291" t="s">
         <v>170</v>
       </c>
       <c r="F291" t="s">
+        <v>115</v>
+      </c>
+      <c r="G291" t="s">
         <v>171</v>
-      </c>
-      <c r="G291" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8176,17 +8176,17 @@
       <c r="B292" t="s">
         <v>8</v>
       </c>
-      <c r="C292" t="s">
-        <v>112</v>
-      </c>
       <c r="D292" t="s">
+        <v>475</v>
+      </c>
+      <c r="E292" t="s">
         <v>170</v>
       </c>
       <c r="F292" t="s">
+        <v>115</v>
+      </c>
+      <c r="G292" t="s">
         <v>171</v>
-      </c>
-      <c r="G292" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8196,17 +8196,17 @@
       <c r="B293" t="s">
         <v>8</v>
       </c>
-      <c r="C293" t="s">
-        <v>112</v>
-      </c>
       <c r="D293" t="s">
+        <v>475</v>
+      </c>
+      <c r="E293" t="s">
         <v>170</v>
       </c>
       <c r="F293" t="s">
+        <v>115</v>
+      </c>
+      <c r="G293" t="s">
         <v>171</v>
-      </c>
-      <c r="G293" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8216,17 +8216,17 @@
       <c r="B294" t="s">
         <v>8</v>
       </c>
-      <c r="C294" t="s">
-        <v>112</v>
-      </c>
       <c r="D294" t="s">
+        <v>475</v>
+      </c>
+      <c r="E294" t="s">
         <v>170</v>
       </c>
       <c r="F294" t="s">
+        <v>115</v>
+      </c>
+      <c r="G294" t="s">
         <v>171</v>
-      </c>
-      <c r="G294" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8236,17 +8236,17 @@
       <c r="B295" t="s">
         <v>8</v>
       </c>
-      <c r="C295" t="s">
-        <v>112</v>
-      </c>
       <c r="D295" t="s">
+        <v>485</v>
+      </c>
+      <c r="E295" t="s">
         <v>170</v>
       </c>
       <c r="F295" t="s">
+        <v>115</v>
+      </c>
+      <c r="G295" t="s">
         <v>171</v>
-      </c>
-      <c r="G295" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8256,17 +8256,17 @@
       <c r="B296" t="s">
         <v>8</v>
       </c>
-      <c r="C296" t="s">
-        <v>112</v>
-      </c>
       <c r="D296" t="s">
+        <v>485</v>
+      </c>
+      <c r="E296" t="s">
         <v>170</v>
       </c>
       <c r="F296" t="s">
+        <v>115</v>
+      </c>
+      <c r="G296" t="s">
         <v>171</v>
-      </c>
-      <c r="G296" t="s">
-        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,48 +49,48 @@
     <t>110</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
     <t>112</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -139,33 +139,33 @@
     <t>11330</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
     <t>114</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
@@ -175,33 +175,33 @@
     <t>120</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -289,27 +289,27 @@
     <t>140</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,12 +340,12 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -358,45 +358,45 @@
     <t>150</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -625,12 +625,12 @@
     <t>160</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,12 +811,12 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -829,24 +829,24 @@
     <t>230</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -997,12 +997,12 @@
     <t>310</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1111,12 +1111,12 @@
     <t>320</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1282,24 +1282,24 @@
     <t>430</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1378,10 +1378,10 @@
     <t>600</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -1872,10 +1872,10 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1918,10 +1918,10 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1941,10 +1941,10 @@
         <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1987,10 +1987,10 @@
         <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2010,10 +2010,10 @@
         <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2030,13 +2030,13 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
         <v>29</v>
       </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2079,10 +2079,10 @@
         <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2099,13 +2099,13 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
         <v>39</v>
       </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2125,10 +2125,10 @@
         <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2148,10 +2148,10 @@
         <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2171,10 +2171,10 @@
         <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2194,10 +2194,10 @@
         <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G17" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2217,10 +2217,10 @@
         <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G18" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2240,10 +2240,10 @@
         <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2263,10 +2263,10 @@
         <v>60</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2286,10 +2286,10 @@
         <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G21" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2332,10 +2332,10 @@
         <v>66</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2493,10 +2493,10 @@
         <v>53</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G30" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2631,10 +2631,10 @@
         <v>57</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2731,10 +2731,10 @@
         <v>53</v>
       </c>
       <c r="F41" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G41" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2751,10 +2751,10 @@
         <v>57</v>
       </c>
       <c r="F42" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G42" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2851,10 +2851,10 @@
         <v>101</v>
       </c>
       <c r="F47" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G47" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2911,10 +2911,10 @@
         <v>101</v>
       </c>
       <c r="F50" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G50" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>108</v>
       </c>
       <c r="F52" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G52" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3017,10 +3017,10 @@
         <v>118</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G55" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3040,10 +3040,10 @@
         <v>121</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G56" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3086,10 +3086,10 @@
         <v>118</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3109,10 +3109,10 @@
         <v>118</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G59" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3132,10 +3132,10 @@
         <v>118</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3155,10 +3155,10 @@
         <v>118</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G61" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3178,10 +3178,10 @@
         <v>118</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G62" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3198,13 +3198,13 @@
         <v>113</v>
       </c>
       <c r="E63" t="s">
+        <v>118</v>
+      </c>
+      <c r="F63" t="s">
         <v>133</v>
       </c>
-      <c r="F63" t="s">
-        <v>115</v>
-      </c>
       <c r="G63" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3221,13 +3221,13 @@
         <v>113</v>
       </c>
       <c r="E64" t="s">
+        <v>118</v>
+      </c>
+      <c r="F64" t="s">
         <v>133</v>
       </c>
-      <c r="F64" t="s">
-        <v>115</v>
-      </c>
       <c r="G64" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3247,10 +3247,10 @@
         <v>136</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3293,10 +3293,10 @@
         <v>118</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G67" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3313,10 +3313,10 @@
         <v>113</v>
       </c>
       <c r="E68" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" t="s">
         <v>141</v>
-      </c>
-      <c r="F68" t="s">
-        <v>115</v>
       </c>
       <c r="G68" t="s">
         <v>116</v>
@@ -3336,10 +3336,10 @@
         <v>113</v>
       </c>
       <c r="E69" t="s">
+        <v>114</v>
+      </c>
+      <c r="F69" t="s">
         <v>143</v>
-      </c>
-      <c r="F69" t="s">
-        <v>115</v>
       </c>
       <c r="G69" t="s">
         <v>116</v>
@@ -3362,10 +3362,10 @@
         <v>121</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3385,10 +3385,10 @@
         <v>121</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G71" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3431,10 +3431,10 @@
         <v>148</v>
       </c>
       <c r="F73" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G73" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3454,10 +3454,10 @@
         <v>151</v>
       </c>
       <c r="F74" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3477,10 +3477,10 @@
         <v>154</v>
       </c>
       <c r="F75" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="G75" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>148</v>
       </c>
       <c r="F76" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G76" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3523,10 +3523,10 @@
         <v>148</v>
       </c>
       <c r="F77" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G77" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3546,10 +3546,10 @@
         <v>151</v>
       </c>
       <c r="F78" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G78" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3569,10 +3569,10 @@
         <v>160</v>
       </c>
       <c r="F79" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="G79" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3658,10 +3658,10 @@
         <v>113</v>
       </c>
       <c r="E83" t="s">
+        <v>114</v>
+      </c>
+      <c r="F83" t="s">
         <v>143</v>
-      </c>
-      <c r="F83" t="s">
-        <v>115</v>
       </c>
       <c r="G83" t="s">
         <v>116</v>
@@ -3684,10 +3684,10 @@
         <v>170</v>
       </c>
       <c r="F84" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G84" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3704,13 +3704,13 @@
         <v>113</v>
       </c>
       <c r="E85" t="s">
+        <v>118</v>
+      </c>
+      <c r="F85" t="s">
         <v>173</v>
       </c>
-      <c r="F85" t="s">
-        <v>115</v>
-      </c>
       <c r="G85" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3730,10 +3730,10 @@
         <v>175</v>
       </c>
       <c r="F86" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G86" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3750,13 +3750,13 @@
         <v>113</v>
       </c>
       <c r="E87" t="s">
+        <v>118</v>
+      </c>
+      <c r="F87" t="s">
         <v>173</v>
       </c>
-      <c r="F87" t="s">
-        <v>115</v>
-      </c>
       <c r="G87" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3776,10 +3776,10 @@
         <v>118</v>
       </c>
       <c r="F88" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G88" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3799,10 +3799,10 @@
         <v>118</v>
       </c>
       <c r="F89" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G89" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3891,10 +3891,10 @@
         <v>121</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G93" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3937,10 +3937,10 @@
         <v>189</v>
       </c>
       <c r="F95" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="G95" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4052,10 +4052,10 @@
         <v>154</v>
       </c>
       <c r="F100" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="G100" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4095,10 +4095,10 @@
         <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G102" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4115,10 +4115,10 @@
         <v>203</v>
       </c>
       <c r="F103" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G103" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4135,10 +4135,10 @@
         <v>203</v>
       </c>
       <c r="F104" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G104" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4155,10 +4155,10 @@
         <v>208</v>
       </c>
       <c r="F105" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="G105" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4175,10 +4175,10 @@
         <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G106" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4215,10 +4215,10 @@
         <v>213</v>
       </c>
       <c r="F108" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="G108" t="s">
-        <v>214</v>
+        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4235,10 +4235,10 @@
         <v>216</v>
       </c>
       <c r="F109" t="s">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="G109" t="s">
-        <v>217</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4255,10 +4255,10 @@
         <v>219</v>
       </c>
       <c r="F110" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
       <c r="G110" t="s">
-        <v>220</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4275,10 +4275,10 @@
         <v>203</v>
       </c>
       <c r="F111" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G111" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4312,10 +4312,10 @@
         <v>202</v>
       </c>
       <c r="E113" t="s">
+        <v>114</v>
+      </c>
+      <c r="F113" t="s">
         <v>143</v>
-      </c>
-      <c r="F113" t="s">
-        <v>115</v>
       </c>
       <c r="G113" t="s">
         <v>116</v>
@@ -4335,10 +4335,10 @@
         <v>151</v>
       </c>
       <c r="F114" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G114" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4375,10 +4375,10 @@
         <v>230</v>
       </c>
       <c r="F116" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="G116" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4412,10 +4412,10 @@
         <v>202</v>
       </c>
       <c r="E118" t="s">
+        <v>163</v>
+      </c>
+      <c r="F118" t="s">
         <v>234</v>
-      </c>
-      <c r="F118" t="s">
-        <v>164</v>
       </c>
       <c r="G118" t="s">
         <v>165</v>
@@ -4455,10 +4455,10 @@
         <v>170</v>
       </c>
       <c r="F120" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G120" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4472,10 +4472,10 @@
         <v>237</v>
       </c>
       <c r="E121" t="s">
+        <v>114</v>
+      </c>
+      <c r="F121" t="s">
         <v>143</v>
-      </c>
-      <c r="F121" t="s">
-        <v>115</v>
       </c>
       <c r="G121" t="s">
         <v>116</v>
@@ -4495,10 +4495,10 @@
         <v>170</v>
       </c>
       <c r="F122" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G122" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4515,10 +4515,10 @@
         <v>170</v>
       </c>
       <c r="F123" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G123" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4535,10 +4535,10 @@
         <v>242</v>
       </c>
       <c r="F124" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G124" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4555,10 +4555,10 @@
         <v>242</v>
       </c>
       <c r="F125" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G125" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4575,10 +4575,10 @@
         <v>242</v>
       </c>
       <c r="F126" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G126" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4595,10 +4595,10 @@
         <v>242</v>
       </c>
       <c r="F127" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G127" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4615,10 +4615,10 @@
         <v>242</v>
       </c>
       <c r="F128" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G128" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4632,13 +4632,13 @@
         <v>237</v>
       </c>
       <c r="E129" t="s">
+        <v>242</v>
+      </c>
+      <c r="F129" t="s">
         <v>249</v>
       </c>
-      <c r="F129" t="s">
-        <v>164</v>
-      </c>
       <c r="G129" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4652,13 +4652,13 @@
         <v>237</v>
       </c>
       <c r="E130" t="s">
+        <v>242</v>
+      </c>
+      <c r="F130" t="s">
         <v>251</v>
       </c>
-      <c r="F130" t="s">
-        <v>164</v>
-      </c>
       <c r="G130" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4672,13 +4672,13 @@
         <v>237</v>
       </c>
       <c r="E131" t="s">
+        <v>242</v>
+      </c>
+      <c r="F131" t="s">
         <v>253</v>
       </c>
-      <c r="F131" t="s">
-        <v>164</v>
-      </c>
       <c r="G131" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4695,10 +4695,10 @@
         <v>255</v>
       </c>
       <c r="F132" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="G132" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4715,10 +4715,10 @@
         <v>189</v>
       </c>
       <c r="F133" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="G133" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4735,10 +4735,10 @@
         <v>175</v>
       </c>
       <c r="F134" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G134" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4755,10 +4755,10 @@
         <v>175</v>
       </c>
       <c r="F135" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G135" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4775,10 +4775,10 @@
         <v>175</v>
       </c>
       <c r="F136" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G136" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4795,10 +4795,10 @@
         <v>175</v>
       </c>
       <c r="F137" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G137" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4815,10 +4815,10 @@
         <v>175</v>
       </c>
       <c r="F138" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G138" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4835,10 +4835,10 @@
         <v>265</v>
       </c>
       <c r="F139" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="G139" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4855,10 +4855,10 @@
         <v>175</v>
       </c>
       <c r="F140" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G140" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4878,10 +4878,10 @@
         <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G141" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4901,10 +4901,10 @@
         <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G142" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4924,10 +4924,10 @@
         <v>275</v>
       </c>
       <c r="F143" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G143" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4947,10 +4947,10 @@
         <v>275</v>
       </c>
       <c r="F144" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G144" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4970,10 +4970,10 @@
         <v>275</v>
       </c>
       <c r="F145" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G145" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4993,10 +4993,10 @@
         <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G146" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5016,10 +5016,10 @@
         <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G147" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5039,10 +5039,10 @@
         <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G148" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5062,10 +5062,10 @@
         <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G149" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5085,10 +5085,10 @@
         <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G150" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5108,10 +5108,10 @@
         <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G151" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5131,10 +5131,10 @@
         <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G152" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5154,10 +5154,10 @@
         <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G153" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5177,10 +5177,10 @@
         <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G154" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5200,10 +5200,10 @@
         <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G155" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5223,10 +5223,10 @@
         <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G156" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5243,13 +5243,13 @@
         <v>270</v>
       </c>
       <c r="E157" t="s">
+        <v>271</v>
+      </c>
+      <c r="F157" t="s">
         <v>293</v>
       </c>
-      <c r="F157" t="s">
-        <v>164</v>
-      </c>
       <c r="G157" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5269,10 +5269,10 @@
         <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G158" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5292,10 +5292,10 @@
         <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G159" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5315,10 +5315,10 @@
         <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G160" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5338,10 +5338,10 @@
         <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G161" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5361,10 +5361,10 @@
         <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G162" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5381,13 +5381,13 @@
         <v>270</v>
       </c>
       <c r="E163" t="s">
+        <v>271</v>
+      </c>
+      <c r="F163" t="s">
         <v>302</v>
       </c>
-      <c r="F163" t="s">
-        <v>164</v>
-      </c>
       <c r="G163" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5407,10 +5407,10 @@
         <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G164" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5430,10 +5430,10 @@
         <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G165" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5453,10 +5453,10 @@
         <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G166" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5476,10 +5476,10 @@
         <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G167" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5496,13 +5496,13 @@
         <v>270</v>
       </c>
       <c r="E168" t="s">
+        <v>271</v>
+      </c>
+      <c r="F168" t="s">
         <v>309</v>
       </c>
-      <c r="F168" t="s">
-        <v>164</v>
-      </c>
       <c r="G168" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5519,13 +5519,13 @@
         <v>270</v>
       </c>
       <c r="E169" t="s">
+        <v>271</v>
+      </c>
+      <c r="F169" t="s">
         <v>309</v>
       </c>
-      <c r="F169" t="s">
-        <v>164</v>
-      </c>
       <c r="G169" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5545,10 +5545,10 @@
         <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G170" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5585,10 +5585,10 @@
         <v>118</v>
       </c>
       <c r="F172" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G172" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5768,10 +5768,10 @@
         <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G181" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5791,10 +5791,10 @@
         <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G182" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5814,10 +5814,10 @@
         <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G183" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5837,10 +5837,10 @@
         <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G184" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5860,10 +5860,10 @@
         <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G185" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5883,10 +5883,10 @@
         <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G186" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5906,10 +5906,10 @@
         <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G187" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5929,10 +5929,10 @@
         <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G188" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5952,10 +5952,10 @@
         <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G189" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5975,10 +5975,10 @@
         <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G190" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5998,10 +5998,10 @@
         <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G191" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6021,10 +6021,10 @@
         <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G192" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6041,13 +6041,13 @@
         <v>326</v>
       </c>
       <c r="E193" t="s">
+        <v>275</v>
+      </c>
+      <c r="F193" t="s">
         <v>341</v>
       </c>
-      <c r="F193" t="s">
-        <v>164</v>
-      </c>
       <c r="G193" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6067,10 +6067,10 @@
         <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G194" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6090,10 +6090,10 @@
         <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G195" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6113,10 +6113,10 @@
         <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G196" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6136,10 +6136,10 @@
         <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G197" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6159,10 +6159,10 @@
         <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G198" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6179,13 +6179,13 @@
         <v>326</v>
       </c>
       <c r="E199" t="s">
+        <v>327</v>
+      </c>
+      <c r="F199" t="s">
         <v>349</v>
       </c>
-      <c r="F199" t="s">
-        <v>164</v>
-      </c>
       <c r="G199" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6202,13 +6202,13 @@
         <v>326</v>
       </c>
       <c r="E200" t="s">
+        <v>327</v>
+      </c>
+      <c r="F200" t="s">
         <v>349</v>
       </c>
-      <c r="F200" t="s">
-        <v>164</v>
-      </c>
       <c r="G200" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6225,13 +6225,13 @@
         <v>326</v>
       </c>
       <c r="E201" t="s">
+        <v>327</v>
+      </c>
+      <c r="F201" t="s">
         <v>349</v>
       </c>
-      <c r="F201" t="s">
-        <v>164</v>
-      </c>
       <c r="G201" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6248,13 +6248,13 @@
         <v>326</v>
       </c>
       <c r="E202" t="s">
+        <v>327</v>
+      </c>
+      <c r="F202" t="s">
         <v>349</v>
       </c>
-      <c r="F202" t="s">
-        <v>164</v>
-      </c>
       <c r="G202" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6271,13 +6271,13 @@
         <v>326</v>
       </c>
       <c r="E203" t="s">
+        <v>275</v>
+      </c>
+      <c r="F203" t="s">
         <v>341</v>
       </c>
-      <c r="F203" t="s">
-        <v>164</v>
-      </c>
       <c r="G203" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6294,13 +6294,13 @@
         <v>326</v>
       </c>
       <c r="E204" t="s">
+        <v>327</v>
+      </c>
+      <c r="F204" t="s">
         <v>349</v>
       </c>
-      <c r="F204" t="s">
-        <v>164</v>
-      </c>
       <c r="G204" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6317,13 +6317,13 @@
         <v>326</v>
       </c>
       <c r="E205" t="s">
+        <v>327</v>
+      </c>
+      <c r="F205" t="s">
         <v>357</v>
       </c>
-      <c r="F205" t="s">
-        <v>164</v>
-      </c>
       <c r="G205" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6340,13 +6340,13 @@
         <v>326</v>
       </c>
       <c r="E206" t="s">
+        <v>327</v>
+      </c>
+      <c r="F206" t="s">
         <v>357</v>
       </c>
-      <c r="F206" t="s">
-        <v>164</v>
-      </c>
       <c r="G206" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6363,13 +6363,13 @@
         <v>326</v>
       </c>
       <c r="E207" t="s">
+        <v>327</v>
+      </c>
+      <c r="F207" t="s">
         <v>357</v>
       </c>
-      <c r="F207" t="s">
-        <v>164</v>
-      </c>
       <c r="G207" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6386,13 +6386,13 @@
         <v>326</v>
       </c>
       <c r="E208" t="s">
+        <v>275</v>
+      </c>
+      <c r="F208" t="s">
         <v>341</v>
       </c>
-      <c r="F208" t="s">
-        <v>164</v>
-      </c>
       <c r="G208" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6409,13 +6409,13 @@
         <v>326</v>
       </c>
       <c r="E209" t="s">
+        <v>327</v>
+      </c>
+      <c r="F209" t="s">
         <v>357</v>
       </c>
-      <c r="F209" t="s">
-        <v>164</v>
-      </c>
       <c r="G209" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6435,10 +6435,10 @@
         <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G210" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6458,10 +6458,10 @@
         <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G211" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6481,10 +6481,10 @@
         <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G212" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6504,10 +6504,10 @@
         <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G213" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6527,10 +6527,10 @@
         <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G214" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6547,13 +6547,13 @@
         <v>364</v>
       </c>
       <c r="E215" t="s">
+        <v>327</v>
+      </c>
+      <c r="F215" t="s">
         <v>349</v>
       </c>
-      <c r="F215" t="s">
-        <v>164</v>
-      </c>
       <c r="G215" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6573,10 +6573,10 @@
         <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G216" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6596,10 +6596,10 @@
         <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G217" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6619,10 +6619,10 @@
         <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G218" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6642,10 +6642,10 @@
         <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G219" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6662,13 +6662,13 @@
         <v>364</v>
       </c>
       <c r="E220" t="s">
+        <v>271</v>
+      </c>
+      <c r="F220" t="s">
         <v>309</v>
       </c>
-      <c r="F220" t="s">
-        <v>164</v>
-      </c>
       <c r="G220" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6688,10 +6688,10 @@
         <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G221" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6711,10 +6711,10 @@
         <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G222" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6734,10 +6734,10 @@
         <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G223" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6757,10 +6757,10 @@
         <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G224" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6780,10 +6780,10 @@
         <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G225" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6803,10 +6803,10 @@
         <v>275</v>
       </c>
       <c r="F226" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G226" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6826,10 +6826,10 @@
         <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G227" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6869,13 +6869,13 @@
         <v>364</v>
       </c>
       <c r="E229" t="s">
+        <v>365</v>
+      </c>
+      <c r="F229" t="s">
         <v>387</v>
       </c>
-      <c r="F229" t="s">
-        <v>164</v>
-      </c>
       <c r="G229" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6892,13 +6892,13 @@
         <v>364</v>
       </c>
       <c r="E230" t="s">
+        <v>365</v>
+      </c>
+      <c r="F230" t="s">
         <v>387</v>
       </c>
-      <c r="F230" t="s">
-        <v>164</v>
-      </c>
       <c r="G230" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6915,13 +6915,13 @@
         <v>364</v>
       </c>
       <c r="E231" t="s">
+        <v>271</v>
+      </c>
+      <c r="F231" t="s">
         <v>293</v>
       </c>
-      <c r="F231" t="s">
-        <v>164</v>
-      </c>
       <c r="G231" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6938,13 +6938,13 @@
         <v>364</v>
       </c>
       <c r="E232" t="s">
+        <v>271</v>
+      </c>
+      <c r="F232" t="s">
         <v>309</v>
       </c>
-      <c r="F232" t="s">
-        <v>164</v>
-      </c>
       <c r="G232" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6961,13 +6961,13 @@
         <v>364</v>
       </c>
       <c r="E233" t="s">
+        <v>365</v>
+      </c>
+      <c r="F233" t="s">
         <v>387</v>
       </c>
-      <c r="F233" t="s">
-        <v>164</v>
-      </c>
       <c r="G233" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6984,13 +6984,13 @@
         <v>364</v>
       </c>
       <c r="E234" t="s">
+        <v>365</v>
+      </c>
+      <c r="F234" t="s">
         <v>387</v>
       </c>
-      <c r="F234" t="s">
-        <v>164</v>
-      </c>
       <c r="G234" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7007,13 +7007,13 @@
         <v>364</v>
       </c>
       <c r="E235" t="s">
+        <v>365</v>
+      </c>
+      <c r="F235" t="s">
         <v>387</v>
       </c>
-      <c r="F235" t="s">
-        <v>164</v>
-      </c>
       <c r="G235" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7030,13 +7030,13 @@
         <v>364</v>
       </c>
       <c r="E236" t="s">
+        <v>365</v>
+      </c>
+      <c r="F236" t="s">
         <v>387</v>
       </c>
-      <c r="F236" t="s">
-        <v>164</v>
-      </c>
       <c r="G236" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7053,13 +7053,13 @@
         <v>364</v>
       </c>
       <c r="E237" t="s">
+        <v>365</v>
+      </c>
+      <c r="F237" t="s">
         <v>387</v>
       </c>
-      <c r="F237" t="s">
-        <v>164</v>
-      </c>
       <c r="G237" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7076,13 +7076,13 @@
         <v>364</v>
       </c>
       <c r="E238" t="s">
+        <v>365</v>
+      </c>
+      <c r="F238" t="s">
         <v>387</v>
       </c>
-      <c r="F238" t="s">
-        <v>164</v>
-      </c>
       <c r="G238" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7099,13 +7099,13 @@
         <v>364</v>
       </c>
       <c r="E239" t="s">
+        <v>365</v>
+      </c>
+      <c r="F239" t="s">
         <v>399</v>
       </c>
-      <c r="F239" t="s">
-        <v>164</v>
-      </c>
       <c r="G239" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7260,13 +7260,13 @@
         <v>402</v>
       </c>
       <c r="E246" t="s">
+        <v>255</v>
+      </c>
+      <c r="F246" t="s">
         <v>410</v>
       </c>
-      <c r="F246" t="s">
-        <v>164</v>
-      </c>
       <c r="G246" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7323,10 +7323,10 @@
         <v>415</v>
       </c>
       <c r="F249" t="s">
-        <v>96</v>
+        <v>416</v>
       </c>
       <c r="G249" t="s">
-        <v>416</v>
+        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7403,10 +7403,10 @@
         <v>422</v>
       </c>
       <c r="F253" t="s">
-        <v>164</v>
+        <v>423</v>
       </c>
       <c r="G253" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7423,10 +7423,10 @@
         <v>219</v>
       </c>
       <c r="F254" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
       <c r="G254" t="s">
-        <v>220</v>
+        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7443,10 +7443,10 @@
         <v>426</v>
       </c>
       <c r="F255" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G255" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7463,10 +7463,10 @@
         <v>426</v>
       </c>
       <c r="F256" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G256" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7483,10 +7483,10 @@
         <v>426</v>
       </c>
       <c r="F257" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G257" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7503,10 +7503,10 @@
         <v>327</v>
       </c>
       <c r="F258" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G258" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7523,10 +7523,10 @@
         <v>426</v>
       </c>
       <c r="F259" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G259" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7563,10 +7563,10 @@
         <v>434</v>
       </c>
       <c r="F261" t="s">
-        <v>196</v>
+        <v>435</v>
       </c>
       <c r="G261" t="s">
-        <v>435</v>
+        <v>197</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7603,10 +7603,10 @@
         <v>438</v>
       </c>
       <c r="F263" t="s">
-        <v>183</v>
+        <v>439</v>
       </c>
       <c r="G263" t="s">
-        <v>439</v>
+        <v>184</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7663,10 +7663,10 @@
         <v>443</v>
       </c>
       <c r="F266" t="s">
-        <v>115</v>
+        <v>444</v>
       </c>
       <c r="G266" t="s">
-        <v>444</v>
+        <v>116</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7683,10 +7683,10 @@
         <v>118</v>
       </c>
       <c r="F267" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G267" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7703,10 +7703,10 @@
         <v>203</v>
       </c>
       <c r="F268" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G268" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7723,10 +7723,10 @@
         <v>118</v>
       </c>
       <c r="F269" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G269" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7743,10 +7743,10 @@
         <v>118</v>
       </c>
       <c r="F270" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G270" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7763,10 +7763,10 @@
         <v>454</v>
       </c>
       <c r="F271" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G271" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7783,10 +7783,10 @@
         <v>454</v>
       </c>
       <c r="F272" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G272" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7803,10 +7803,10 @@
         <v>454</v>
       </c>
       <c r="F273" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G273" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7823,10 +7823,10 @@
         <v>454</v>
       </c>
       <c r="F274" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G274" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7843,10 +7843,10 @@
         <v>454</v>
       </c>
       <c r="F275" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G275" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7863,10 +7863,10 @@
         <v>454</v>
       </c>
       <c r="F276" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G276" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7883,10 +7883,10 @@
         <v>454</v>
       </c>
       <c r="F277" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G277" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7903,10 +7903,10 @@
         <v>203</v>
       </c>
       <c r="F278" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G278" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7923,10 +7923,10 @@
         <v>53</v>
       </c>
       <c r="F279" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G279" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7963,10 +7963,10 @@
         <v>170</v>
       </c>
       <c r="F281" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G281" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -8000,13 +8000,13 @@
         <v>469</v>
       </c>
       <c r="E283" t="s">
+        <v>365</v>
+      </c>
+      <c r="F283" t="s">
         <v>399</v>
       </c>
-      <c r="F283" t="s">
-        <v>164</v>
-      </c>
       <c r="G283" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8043,10 +8043,10 @@
         <v>170</v>
       </c>
       <c r="F285" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G285" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8063,10 +8063,10 @@
         <v>438</v>
       </c>
       <c r="F286" t="s">
-        <v>183</v>
+        <v>439</v>
       </c>
       <c r="G286" t="s">
-        <v>439</v>
+        <v>184</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8083,10 +8083,10 @@
         <v>438</v>
       </c>
       <c r="F287" t="s">
-        <v>183</v>
+        <v>439</v>
       </c>
       <c r="G287" t="s">
-        <v>439</v>
+        <v>184</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8103,10 +8103,10 @@
         <v>41</v>
       </c>
       <c r="F288" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G288" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8163,10 +8163,10 @@
         <v>170</v>
       </c>
       <c r="F291" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G291" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8183,10 +8183,10 @@
         <v>170</v>
       </c>
       <c r="F292" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G292" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8203,10 +8203,10 @@
         <v>170</v>
       </c>
       <c r="F293" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G293" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8223,10 +8223,10 @@
         <v>170</v>
       </c>
       <c r="F294" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G294" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8243,10 +8243,10 @@
         <v>170</v>
       </c>
       <c r="F295" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G295" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8263,10 +8263,10 @@
         <v>170</v>
       </c>
       <c r="F296" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G296" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -25,6 +25,9 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
@@ -34,9 +37,6 @@
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,6 +46,9 @@
     <t>111</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
@@ -55,9 +58,6 @@
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -109,15 +109,15 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -286,6 +286,9 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
@@ -295,21 +298,18 @@
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -355,6 +355,9 @@
     <t>151</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
@@ -364,9 +367,6 @@
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>15113</t>
   </si>
   <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -505,15 +505,15 @@
     <t>15142</t>
   </si>
   <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -685,13 +685,13 @@
     <t>16061</t>
   </si>
   <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
     <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
-    <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
     <t>16062</t>
@@ -1869,13 +1869,13 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1915,13 +1915,13 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1938,13 +1938,13 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1984,13 +1984,13 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>23</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2007,13 +2007,13 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>23</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2030,13 +2030,13 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>23</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>29</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2050,10 +2050,10 @@
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
@@ -2076,13 +2076,13 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>35</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>36</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2099,13 +2099,13 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>35</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2122,13 +2122,13 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
         <v>41</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>42</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2145,13 +2145,13 @@
         <v>10</v>
       </c>
       <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
         <v>45</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>46</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2168,13 +2168,13 @@
         <v>10</v>
       </c>
       <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
         <v>48</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>49</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2188,16 +2188,16 @@
         <v>51</v>
       </c>
       <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
         <v>52</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>53</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>54</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2211,16 +2211,16 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
         <v>52</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>53</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>54</v>
-      </c>
-      <c r="G18" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2234,16 +2234,16 @@
         <v>51</v>
       </c>
       <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" t="s">
         <v>52</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>57</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>58</v>
-      </c>
-      <c r="G19" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2257,16 +2257,16 @@
         <v>51</v>
       </c>
       <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
         <v>52</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>60</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>61</v>
-      </c>
-      <c r="G20" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2280,16 +2280,16 @@
         <v>51</v>
       </c>
       <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
         <v>52</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>53</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>54</v>
-      </c>
-      <c r="G21" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2303,10 +2303,10 @@
         <v>64</v>
       </c>
       <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
         <v>52</v>
-      </c>
-      <c r="E22" t="s">
-        <v>31</v>
       </c>
       <c r="F22" t="s">
         <v>32</v>
@@ -2326,16 +2326,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" t="s">
         <v>52</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>66</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>67</v>
-      </c>
-      <c r="G23" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2349,10 +2349,10 @@
         <v>64</v>
       </c>
       <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
         <v>52</v>
-      </c>
-      <c r="E24" t="s">
-        <v>31</v>
       </c>
       <c r="F24" t="s">
         <v>32</v>
@@ -2372,10 +2372,10 @@
         <v>64</v>
       </c>
       <c r="D25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" t="s">
         <v>52</v>
-      </c>
-      <c r="E25" t="s">
-        <v>31</v>
       </c>
       <c r="F25" t="s">
         <v>32</v>
@@ -2395,10 +2395,10 @@
         <v>64</v>
       </c>
       <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
         <v>52</v>
-      </c>
-      <c r="E26" t="s">
-        <v>31</v>
       </c>
       <c r="F26" t="s">
         <v>32</v>
@@ -2418,10 +2418,10 @@
         <v>64</v>
       </c>
       <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" t="s">
         <v>52</v>
-      </c>
-      <c r="E27" t="s">
-        <v>31</v>
       </c>
       <c r="F27" t="s">
         <v>32</v>
@@ -2441,10 +2441,10 @@
         <v>64</v>
       </c>
       <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" t="s">
         <v>52</v>
-      </c>
-      <c r="E28" t="s">
-        <v>31</v>
       </c>
       <c r="F28" t="s">
         <v>32</v>
@@ -2464,10 +2464,10 @@
         <v>64</v>
       </c>
       <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" t="s">
         <v>52</v>
-      </c>
-      <c r="E29" t="s">
-        <v>31</v>
       </c>
       <c r="F29" t="s">
         <v>32</v>
@@ -2487,16 +2487,16 @@
         <v>64</v>
       </c>
       <c r="D30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" t="s">
         <v>52</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>53</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>54</v>
-      </c>
-      <c r="G30" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2510,10 +2510,10 @@
         <v>76</v>
       </c>
       <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" t="s">
         <v>52</v>
-      </c>
-      <c r="E31" t="s">
-        <v>31</v>
       </c>
       <c r="F31" t="s">
         <v>32</v>
@@ -2533,10 +2533,10 @@
         <v>76</v>
       </c>
       <c r="D32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" t="s">
         <v>52</v>
-      </c>
-      <c r="E32" t="s">
-        <v>31</v>
       </c>
       <c r="F32" t="s">
         <v>32</v>
@@ -2556,10 +2556,10 @@
         <v>76</v>
       </c>
       <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" t="s">
         <v>52</v>
-      </c>
-      <c r="E33" t="s">
-        <v>31</v>
       </c>
       <c r="F33" t="s">
         <v>32</v>
@@ -2579,10 +2579,10 @@
         <v>76</v>
       </c>
       <c r="D34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" t="s">
         <v>52</v>
-      </c>
-      <c r="E34" t="s">
-        <v>31</v>
       </c>
       <c r="F34" t="s">
         <v>32</v>
@@ -2602,10 +2602,10 @@
         <v>76</v>
       </c>
       <c r="D35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" t="s">
         <v>52</v>
-      </c>
-      <c r="E35" t="s">
-        <v>31</v>
       </c>
       <c r="F35" t="s">
         <v>32</v>
@@ -2625,16 +2625,16 @@
         <v>76</v>
       </c>
       <c r="D36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" t="s">
         <v>52</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>57</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>58</v>
-      </c>
-      <c r="G36" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2645,10 +2645,10 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" t="s">
         <v>83</v>
-      </c>
-      <c r="E37" t="s">
-        <v>31</v>
       </c>
       <c r="F37" t="s">
         <v>32</v>
@@ -2665,10 +2665,10 @@
         <v>8</v>
       </c>
       <c r="D38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" t="s">
         <v>83</v>
-      </c>
-      <c r="E38" t="s">
-        <v>31</v>
       </c>
       <c r="F38" t="s">
         <v>32</v>
@@ -2685,10 +2685,10 @@
         <v>8</v>
       </c>
       <c r="D39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" t="s">
         <v>83</v>
-      </c>
-      <c r="E39" t="s">
-        <v>31</v>
       </c>
       <c r="F39" t="s">
         <v>32</v>
@@ -2705,10 +2705,10 @@
         <v>8</v>
       </c>
       <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" t="s">
         <v>83</v>
-      </c>
-      <c r="E40" t="s">
-        <v>31</v>
       </c>
       <c r="F40" t="s">
         <v>32</v>
@@ -2725,16 +2725,16 @@
         <v>8</v>
       </c>
       <c r="D41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" t="s">
         <v>83</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>53</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>54</v>
-      </c>
-      <c r="G41" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2745,16 +2745,16 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" t="s">
         <v>83</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>57</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>58</v>
-      </c>
-      <c r="G42" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2785,10 +2785,10 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E44" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F44" t="s">
         <v>96</v>
@@ -2845,16 +2845,16 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E47" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" t="s">
         <v>101</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>102</v>
-      </c>
-      <c r="G47" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2905,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E50" t="s">
+        <v>91</v>
+      </c>
+      <c r="F50" t="s">
         <v>101</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>102</v>
-      </c>
-      <c r="G50" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E52" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" t="s">
         <v>108</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>109</v>
-      </c>
-      <c r="G52" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2965,10 +2965,10 @@
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
@@ -3014,13 +3014,13 @@
         <v>113</v>
       </c>
       <c r="E55" t="s">
+        <v>114</v>
+      </c>
+      <c r="F55" t="s">
         <v>118</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>119</v>
-      </c>
-      <c r="G55" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3037,13 +3037,13 @@
         <v>113</v>
       </c>
       <c r="E56" t="s">
+        <v>114</v>
+      </c>
+      <c r="F56" t="s">
         <v>121</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>122</v>
-      </c>
-      <c r="G56" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3057,10 +3057,10 @@
         <v>112</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E57" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F57" t="s">
         <v>125</v>
@@ -3083,13 +3083,13 @@
         <v>113</v>
       </c>
       <c r="E58" t="s">
+        <v>114</v>
+      </c>
+      <c r="F58" t="s">
         <v>118</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>119</v>
-      </c>
-      <c r="G58" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3106,13 +3106,13 @@
         <v>113</v>
       </c>
       <c r="E59" t="s">
+        <v>114</v>
+      </c>
+      <c r="F59" t="s">
         <v>118</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>119</v>
-      </c>
-      <c r="G59" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3129,13 +3129,13 @@
         <v>113</v>
       </c>
       <c r="E60" t="s">
+        <v>114</v>
+      </c>
+      <c r="F60" t="s">
         <v>118</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>119</v>
-      </c>
-      <c r="G60" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3152,13 +3152,13 @@
         <v>113</v>
       </c>
       <c r="E61" t="s">
+        <v>114</v>
+      </c>
+      <c r="F61" t="s">
         <v>118</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>119</v>
-      </c>
-      <c r="G61" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3175,13 +3175,13 @@
         <v>113</v>
       </c>
       <c r="E62" t="s">
+        <v>114</v>
+      </c>
+      <c r="F62" t="s">
         <v>118</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>119</v>
-      </c>
-      <c r="G62" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3198,13 +3198,13 @@
         <v>113</v>
       </c>
       <c r="E63" t="s">
+        <v>114</v>
+      </c>
+      <c r="F63" t="s">
         <v>118</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>133</v>
-      </c>
-      <c r="G63" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3221,13 +3221,13 @@
         <v>113</v>
       </c>
       <c r="E64" t="s">
+        <v>114</v>
+      </c>
+      <c r="F64" t="s">
         <v>118</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>133</v>
-      </c>
-      <c r="G64" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3244,13 +3244,13 @@
         <v>113</v>
       </c>
       <c r="E65" t="s">
+        <v>114</v>
+      </c>
+      <c r="F65" t="s">
         <v>136</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>137</v>
-      </c>
-      <c r="G65" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3290,13 +3290,13 @@
         <v>113</v>
       </c>
       <c r="E67" t="s">
+        <v>114</v>
+      </c>
+      <c r="F67" t="s">
         <v>118</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>119</v>
-      </c>
-      <c r="G67" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3316,10 +3316,10 @@
         <v>114</v>
       </c>
       <c r="F68" t="s">
+        <v>115</v>
+      </c>
+      <c r="G68" t="s">
         <v>141</v>
-      </c>
-      <c r="G68" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3339,10 +3339,10 @@
         <v>114</v>
       </c>
       <c r="F69" t="s">
+        <v>115</v>
+      </c>
+      <c r="G69" t="s">
         <v>143</v>
-      </c>
-      <c r="G69" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3359,13 +3359,13 @@
         <v>113</v>
       </c>
       <c r="E70" t="s">
+        <v>114</v>
+      </c>
+      <c r="F70" t="s">
         <v>121</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>122</v>
-      </c>
-      <c r="G70" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3382,13 +3382,13 @@
         <v>113</v>
       </c>
       <c r="E71" t="s">
+        <v>114</v>
+      </c>
+      <c r="F71" t="s">
         <v>121</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>122</v>
-      </c>
-      <c r="G71" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3425,16 +3425,16 @@
         <v>112</v>
       </c>
       <c r="D73" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E73" t="s">
+        <v>114</v>
+      </c>
+      <c r="F73" t="s">
         <v>148</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>149</v>
-      </c>
-      <c r="G73" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3448,16 +3448,16 @@
         <v>112</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E74" t="s">
+        <v>114</v>
+      </c>
+      <c r="F74" t="s">
         <v>151</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>152</v>
-      </c>
-      <c r="G74" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3471,16 +3471,16 @@
         <v>112</v>
       </c>
       <c r="D75" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E75" t="s">
+        <v>114</v>
+      </c>
+      <c r="F75" t="s">
         <v>154</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>155</v>
-      </c>
-      <c r="G75" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3494,16 +3494,16 @@
         <v>112</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E76" t="s">
+        <v>114</v>
+      </c>
+      <c r="F76" t="s">
         <v>148</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>149</v>
-      </c>
-      <c r="G76" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3517,16 +3517,16 @@
         <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E77" t="s">
+        <v>114</v>
+      </c>
+      <c r="F77" t="s">
         <v>148</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>149</v>
-      </c>
-      <c r="G77" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3540,16 +3540,16 @@
         <v>112</v>
       </c>
       <c r="D78" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E78" t="s">
+        <v>114</v>
+      </c>
+      <c r="F78" t="s">
         <v>151</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>152</v>
-      </c>
-      <c r="G78" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3563,16 +3563,16 @@
         <v>112</v>
       </c>
       <c r="D79" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E79" t="s">
+        <v>114</v>
+      </c>
+      <c r="F79" t="s">
         <v>160</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>161</v>
-      </c>
-      <c r="G79" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3586,10 +3586,10 @@
         <v>112</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E80" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="F80" t="s">
         <v>164</v>
@@ -3609,10 +3609,10 @@
         <v>112</v>
       </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E81" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="F81" t="s">
         <v>164</v>
@@ -3632,10 +3632,10 @@
         <v>112</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E82" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="F82" t="s">
         <v>164</v>
@@ -3661,10 +3661,10 @@
         <v>114</v>
       </c>
       <c r="F83" t="s">
+        <v>115</v>
+      </c>
+      <c r="G83" t="s">
         <v>143</v>
-      </c>
-      <c r="G83" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3681,13 +3681,13 @@
         <v>113</v>
       </c>
       <c r="E84" t="s">
+        <v>114</v>
+      </c>
+      <c r="F84" t="s">
         <v>170</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>171</v>
-      </c>
-      <c r="G84" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3704,13 +3704,13 @@
         <v>113</v>
       </c>
       <c r="E85" t="s">
+        <v>114</v>
+      </c>
+      <c r="F85" t="s">
         <v>118</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>173</v>
-      </c>
-      <c r="G85" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3724,16 +3724,16 @@
         <v>112</v>
       </c>
       <c r="D86" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E86" t="s">
+        <v>114</v>
+      </c>
+      <c r="F86" t="s">
         <v>175</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>176</v>
-      </c>
-      <c r="G86" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3750,13 +3750,13 @@
         <v>113</v>
       </c>
       <c r="E87" t="s">
+        <v>114</v>
+      </c>
+      <c r="F87" t="s">
         <v>118</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>173</v>
-      </c>
-      <c r="G87" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3773,13 +3773,13 @@
         <v>113</v>
       </c>
       <c r="E88" t="s">
+        <v>114</v>
+      </c>
+      <c r="F88" t="s">
         <v>118</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>119</v>
-      </c>
-      <c r="G88" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3796,13 +3796,13 @@
         <v>113</v>
       </c>
       <c r="E89" t="s">
+        <v>114</v>
+      </c>
+      <c r="F89" t="s">
         <v>118</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>119</v>
-      </c>
-      <c r="G89" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3816,10 +3816,10 @@
         <v>112</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E90" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F90" t="s">
         <v>125</v>
@@ -3839,10 +3839,10 @@
         <v>112</v>
       </c>
       <c r="D91" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="E91" t="s">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="F91" t="s">
         <v>183</v>
@@ -3862,10 +3862,10 @@
         <v>112</v>
       </c>
       <c r="D92" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E92" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F92" t="s">
         <v>125</v>
@@ -3888,13 +3888,13 @@
         <v>113</v>
       </c>
       <c r="E93" t="s">
+        <v>114</v>
+      </c>
+      <c r="F93" t="s">
         <v>121</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>122</v>
-      </c>
-      <c r="G93" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3908,10 +3908,10 @@
         <v>112</v>
       </c>
       <c r="D94" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E94" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F94" t="s">
         <v>125</v>
@@ -3934,13 +3934,13 @@
         <v>113</v>
       </c>
       <c r="E95" t="s">
+        <v>114</v>
+      </c>
+      <c r="F95" t="s">
         <v>189</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
         <v>190</v>
-      </c>
-      <c r="G95" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3954,10 +3954,10 @@
         <v>192</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E96" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F96" t="s">
         <v>125</v>
@@ -3977,10 +3977,10 @@
         <v>192</v>
       </c>
       <c r="D97" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E97" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F97" t="s">
         <v>125</v>
@@ -4000,10 +4000,10 @@
         <v>192</v>
       </c>
       <c r="D98" t="s">
-        <v>113</v>
+        <v>195</v>
       </c>
       <c r="E98" t="s">
-        <v>195</v>
+        <v>114</v>
       </c>
       <c r="F98" t="s">
         <v>196</v>
@@ -4023,10 +4023,10 @@
         <v>192</v>
       </c>
       <c r="D99" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E99" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F99" t="s">
         <v>125</v>
@@ -4046,16 +4046,16 @@
         <v>192</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E100" t="s">
+        <v>114</v>
+      </c>
+      <c r="F100" t="s">
         <v>154</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>155</v>
-      </c>
-      <c r="G100" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4069,10 +4069,10 @@
         <v>192</v>
       </c>
       <c r="D101" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E101" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F101" t="s">
         <v>125</v>
@@ -4089,16 +4089,16 @@
         <v>8</v>
       </c>
       <c r="D102" t="s">
+        <v>182</v>
+      </c>
+      <c r="E102" t="s">
         <v>202</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>203</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>204</v>
-      </c>
-      <c r="G102" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4109,16 +4109,16 @@
         <v>8</v>
       </c>
       <c r="D103" t="s">
+        <v>182</v>
+      </c>
+      <c r="E103" t="s">
         <v>202</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>203</v>
       </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
         <v>204</v>
-      </c>
-      <c r="G103" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4129,16 +4129,16 @@
         <v>8</v>
       </c>
       <c r="D104" t="s">
+        <v>182</v>
+      </c>
+      <c r="E104" t="s">
         <v>202</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>203</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>204</v>
-      </c>
-      <c r="G104" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4149,16 +4149,16 @@
         <v>8</v>
       </c>
       <c r="D105" t="s">
+        <v>182</v>
+      </c>
+      <c r="E105" t="s">
         <v>202</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>208</v>
       </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>209</v>
-      </c>
-      <c r="G105" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4169,16 +4169,16 @@
         <v>8</v>
       </c>
       <c r="D106" t="s">
+        <v>182</v>
+      </c>
+      <c r="E106" t="s">
         <v>202</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>203</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>204</v>
-      </c>
-      <c r="G106" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4189,10 +4189,10 @@
         <v>8</v>
       </c>
       <c r="D107" t="s">
+        <v>182</v>
+      </c>
+      <c r="E107" t="s">
         <v>202</v>
-      </c>
-      <c r="E107" t="s">
-        <v>182</v>
       </c>
       <c r="F107" t="s">
         <v>183</v>
@@ -4209,16 +4209,16 @@
         <v>8</v>
       </c>
       <c r="D108" t="s">
+        <v>182</v>
+      </c>
+      <c r="E108" t="s">
         <v>202</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>213</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>214</v>
-      </c>
-      <c r="G108" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4229,16 +4229,16 @@
         <v>8</v>
       </c>
       <c r="D109" t="s">
+        <v>90</v>
+      </c>
+      <c r="E109" t="s">
         <v>202</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>216</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>217</v>
-      </c>
-      <c r="G109" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4249,16 +4249,16 @@
         <v>8</v>
       </c>
       <c r="D110" t="s">
+        <v>90</v>
+      </c>
+      <c r="E110" t="s">
         <v>202</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>219</v>
       </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>220</v>
-      </c>
-      <c r="G110" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4269,16 +4269,16 @@
         <v>8</v>
       </c>
       <c r="D111" t="s">
+        <v>182</v>
+      </c>
+      <c r="E111" t="s">
         <v>202</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>203</v>
       </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>204</v>
-      </c>
-      <c r="G111" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4289,10 +4289,10 @@
         <v>8</v>
       </c>
       <c r="D112" t="s">
+        <v>223</v>
+      </c>
+      <c r="E112" t="s">
         <v>202</v>
-      </c>
-      <c r="E112" t="s">
-        <v>223</v>
       </c>
       <c r="F112" t="s">
         <v>224</v>
@@ -4309,16 +4309,16 @@
         <v>8</v>
       </c>
       <c r="D113" t="s">
+        <v>113</v>
+      </c>
+      <c r="E113" t="s">
         <v>202</v>
       </c>
-      <c r="E113" t="s">
-        <v>114</v>
-      </c>
       <c r="F113" t="s">
+        <v>115</v>
+      </c>
+      <c r="G113" t="s">
         <v>143</v>
-      </c>
-      <c r="G113" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4329,16 +4329,16 @@
         <v>8</v>
       </c>
       <c r="D114" t="s">
+        <v>124</v>
+      </c>
+      <c r="E114" t="s">
         <v>202</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>151</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
         <v>152</v>
-      </c>
-      <c r="G114" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4349,10 +4349,10 @@
         <v>8</v>
       </c>
       <c r="D115" t="s">
+        <v>182</v>
+      </c>
+      <c r="E115" t="s">
         <v>202</v>
-      </c>
-      <c r="E115" t="s">
-        <v>182</v>
       </c>
       <c r="F115" t="s">
         <v>183</v>
@@ -4369,16 +4369,16 @@
         <v>8</v>
       </c>
       <c r="D116" t="s">
+        <v>223</v>
+      </c>
+      <c r="E116" t="s">
         <v>202</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>230</v>
       </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>231</v>
-      </c>
-      <c r="G116" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4389,10 +4389,10 @@
         <v>8</v>
       </c>
       <c r="D117" t="s">
+        <v>223</v>
+      </c>
+      <c r="E117" t="s">
         <v>202</v>
-      </c>
-      <c r="E117" t="s">
-        <v>223</v>
       </c>
       <c r="F117" t="s">
         <v>224</v>
@@ -4409,16 +4409,16 @@
         <v>8</v>
       </c>
       <c r="D118" t="s">
+        <v>163</v>
+      </c>
+      <c r="E118" t="s">
         <v>202</v>
       </c>
-      <c r="E118" t="s">
-        <v>163</v>
-      </c>
       <c r="F118" t="s">
+        <v>164</v>
+      </c>
+      <c r="G118" t="s">
         <v>234</v>
-      </c>
-      <c r="G118" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4429,10 +4429,10 @@
         <v>8</v>
       </c>
       <c r="D119" t="s">
+        <v>182</v>
+      </c>
+      <c r="E119" t="s">
         <v>202</v>
-      </c>
-      <c r="E119" t="s">
-        <v>182</v>
       </c>
       <c r="F119" t="s">
         <v>183</v>
@@ -4449,16 +4449,16 @@
         <v>8</v>
       </c>
       <c r="D120" t="s">
+        <v>113</v>
+      </c>
+      <c r="E120" t="s">
         <v>237</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>170</v>
       </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>171</v>
-      </c>
-      <c r="G120" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4469,16 +4469,16 @@
         <v>8</v>
       </c>
       <c r="D121" t="s">
+        <v>113</v>
+      </c>
+      <c r="E121" t="s">
         <v>237</v>
       </c>
-      <c r="E121" t="s">
-        <v>114</v>
-      </c>
       <c r="F121" t="s">
+        <v>115</v>
+      </c>
+      <c r="G121" t="s">
         <v>143</v>
-      </c>
-      <c r="G121" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>8</v>
       </c>
       <c r="D122" t="s">
+        <v>113</v>
+      </c>
+      <c r="E122" t="s">
         <v>237</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>170</v>
       </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
         <v>171</v>
-      </c>
-      <c r="G122" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>8</v>
       </c>
       <c r="D123" t="s">
+        <v>113</v>
+      </c>
+      <c r="E123" t="s">
         <v>237</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
         <v>170</v>
       </c>
-      <c r="F123" t="s">
+      <c r="G123" t="s">
         <v>171</v>
-      </c>
-      <c r="G123" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4529,16 +4529,16 @@
         <v>8</v>
       </c>
       <c r="D124" t="s">
+        <v>163</v>
+      </c>
+      <c r="E124" t="s">
         <v>237</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>242</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>243</v>
-      </c>
-      <c r="G124" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4549,16 +4549,16 @@
         <v>8</v>
       </c>
       <c r="D125" t="s">
+        <v>163</v>
+      </c>
+      <c r="E125" t="s">
         <v>237</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>242</v>
       </c>
-      <c r="F125" t="s">
+      <c r="G125" t="s">
         <v>243</v>
-      </c>
-      <c r="G125" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4569,16 +4569,16 @@
         <v>8</v>
       </c>
       <c r="D126" t="s">
+        <v>163</v>
+      </c>
+      <c r="E126" t="s">
         <v>237</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>242</v>
       </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
         <v>243</v>
-      </c>
-      <c r="G126" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4589,16 +4589,16 @@
         <v>8</v>
       </c>
       <c r="D127" t="s">
+        <v>163</v>
+      </c>
+      <c r="E127" t="s">
         <v>237</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>242</v>
       </c>
-      <c r="F127" t="s">
+      <c r="G127" t="s">
         <v>243</v>
-      </c>
-      <c r="G127" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4609,16 +4609,16 @@
         <v>8</v>
       </c>
       <c r="D128" t="s">
+        <v>163</v>
+      </c>
+      <c r="E128" t="s">
         <v>237</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>242</v>
       </c>
-      <c r="F128" t="s">
+      <c r="G128" t="s">
         <v>243</v>
-      </c>
-      <c r="G128" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="D129" t="s">
+        <v>163</v>
+      </c>
+      <c r="E129" t="s">
         <v>237</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>242</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
         <v>249</v>
-      </c>
-      <c r="G129" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="D130" t="s">
+        <v>163</v>
+      </c>
+      <c r="E130" t="s">
         <v>237</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>242</v>
       </c>
-      <c r="F130" t="s">
+      <c r="G130" t="s">
         <v>251</v>
-      </c>
-      <c r="G130" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="D131" t="s">
+        <v>163</v>
+      </c>
+      <c r="E131" t="s">
         <v>237</v>
       </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
         <v>242</v>
       </c>
-      <c r="F131" t="s">
+      <c r="G131" t="s">
         <v>253</v>
-      </c>
-      <c r="G131" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,16 +4689,16 @@
         <v>8</v>
       </c>
       <c r="D132" t="s">
+        <v>163</v>
+      </c>
+      <c r="E132" t="s">
         <v>237</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>255</v>
       </c>
-      <c r="F132" t="s">
+      <c r="G132" t="s">
         <v>256</v>
-      </c>
-      <c r="G132" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4709,16 +4709,16 @@
         <v>8</v>
       </c>
       <c r="D133" t="s">
+        <v>113</v>
+      </c>
+      <c r="E133" t="s">
         <v>237</v>
       </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
         <v>189</v>
       </c>
-      <c r="F133" t="s">
+      <c r="G133" t="s">
         <v>190</v>
-      </c>
-      <c r="G133" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4729,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="D134" t="s">
+        <v>163</v>
+      </c>
+      <c r="E134" t="s">
         <v>259</v>
       </c>
-      <c r="E134" t="s">
+      <c r="F134" t="s">
         <v>175</v>
       </c>
-      <c r="F134" t="s">
+      <c r="G134" t="s">
         <v>176</v>
-      </c>
-      <c r="G134" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4749,16 +4749,16 @@
         <v>8</v>
       </c>
       <c r="D135" t="s">
+        <v>163</v>
+      </c>
+      <c r="E135" t="s">
         <v>259</v>
       </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
         <v>175</v>
       </c>
-      <c r="F135" t="s">
+      <c r="G135" t="s">
         <v>176</v>
-      </c>
-      <c r="G135" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4769,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="D136" t="s">
+        <v>163</v>
+      </c>
+      <c r="E136" t="s">
         <v>259</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>175</v>
       </c>
-      <c r="F136" t="s">
+      <c r="G136" t="s">
         <v>176</v>
-      </c>
-      <c r="G136" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4789,16 +4789,16 @@
         <v>8</v>
       </c>
       <c r="D137" t="s">
+        <v>163</v>
+      </c>
+      <c r="E137" t="s">
         <v>259</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
         <v>175</v>
       </c>
-      <c r="F137" t="s">
+      <c r="G137" t="s">
         <v>176</v>
-      </c>
-      <c r="G137" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4809,16 +4809,16 @@
         <v>8</v>
       </c>
       <c r="D138" t="s">
+        <v>163</v>
+      </c>
+      <c r="E138" t="s">
         <v>259</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
         <v>175</v>
       </c>
-      <c r="F138" t="s">
+      <c r="G138" t="s">
         <v>176</v>
-      </c>
-      <c r="G138" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4829,16 +4829,16 @@
         <v>8</v>
       </c>
       <c r="D139" t="s">
+        <v>223</v>
+      </c>
+      <c r="E139" t="s">
         <v>259</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>265</v>
       </c>
-      <c r="F139" t="s">
+      <c r="G139" t="s">
         <v>266</v>
-      </c>
-      <c r="G139" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>8</v>
       </c>
       <c r="D140" t="s">
+        <v>163</v>
+      </c>
+      <c r="E140" t="s">
         <v>259</v>
       </c>
-      <c r="E140" t="s">
+      <c r="F140" t="s">
         <v>175</v>
       </c>
-      <c r="F140" t="s">
+      <c r="G140" t="s">
         <v>176</v>
-      </c>
-      <c r="G140" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4872,16 +4872,16 @@
         <v>269</v>
       </c>
       <c r="D141" t="s">
+        <v>163</v>
+      </c>
+      <c r="E141" t="s">
         <v>270</v>
       </c>
-      <c r="E141" t="s">
+      <c r="F141" t="s">
         <v>271</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>272</v>
-      </c>
-      <c r="G141" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4895,16 +4895,16 @@
         <v>269</v>
       </c>
       <c r="D142" t="s">
+        <v>163</v>
+      </c>
+      <c r="E142" t="s">
         <v>270</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>271</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>272</v>
-      </c>
-      <c r="G142" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4918,16 +4918,16 @@
         <v>269</v>
       </c>
       <c r="D143" t="s">
+        <v>163</v>
+      </c>
+      <c r="E143" t="s">
         <v>270</v>
       </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>275</v>
       </c>
-      <c r="F143" t="s">
+      <c r="G143" t="s">
         <v>276</v>
-      </c>
-      <c r="G143" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4941,16 +4941,16 @@
         <v>269</v>
       </c>
       <c r="D144" t="s">
+        <v>163</v>
+      </c>
+      <c r="E144" t="s">
         <v>270</v>
       </c>
-      <c r="E144" t="s">
+      <c r="F144" t="s">
         <v>275</v>
       </c>
-      <c r="F144" t="s">
+      <c r="G144" t="s">
         <v>276</v>
-      </c>
-      <c r="G144" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4964,16 +4964,16 @@
         <v>269</v>
       </c>
       <c r="D145" t="s">
+        <v>163</v>
+      </c>
+      <c r="E145" t="s">
         <v>270</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" t="s">
         <v>275</v>
       </c>
-      <c r="F145" t="s">
+      <c r="G145" t="s">
         <v>276</v>
-      </c>
-      <c r="G145" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4987,16 +4987,16 @@
         <v>269</v>
       </c>
       <c r="D146" t="s">
+        <v>163</v>
+      </c>
+      <c r="E146" t="s">
         <v>270</v>
       </c>
-      <c r="E146" t="s">
+      <c r="F146" t="s">
         <v>271</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>272</v>
-      </c>
-      <c r="G146" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5010,16 +5010,16 @@
         <v>281</v>
       </c>
       <c r="D147" t="s">
+        <v>163</v>
+      </c>
+      <c r="E147" t="s">
         <v>270</v>
       </c>
-      <c r="E147" t="s">
+      <c r="F147" t="s">
         <v>271</v>
       </c>
-      <c r="F147" t="s">
+      <c r="G147" t="s">
         <v>272</v>
-      </c>
-      <c r="G147" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5033,16 +5033,16 @@
         <v>281</v>
       </c>
       <c r="D148" t="s">
+        <v>163</v>
+      </c>
+      <c r="E148" t="s">
         <v>270</v>
       </c>
-      <c r="E148" t="s">
+      <c r="F148" t="s">
         <v>271</v>
       </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
         <v>272</v>
-      </c>
-      <c r="G148" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5056,16 +5056,16 @@
         <v>281</v>
       </c>
       <c r="D149" t="s">
+        <v>163</v>
+      </c>
+      <c r="E149" t="s">
         <v>270</v>
       </c>
-      <c r="E149" t="s">
+      <c r="F149" t="s">
         <v>271</v>
       </c>
-      <c r="F149" t="s">
+      <c r="G149" t="s">
         <v>272</v>
-      </c>
-      <c r="G149" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5079,16 +5079,16 @@
         <v>281</v>
       </c>
       <c r="D150" t="s">
+        <v>163</v>
+      </c>
+      <c r="E150" t="s">
         <v>270</v>
       </c>
-      <c r="E150" t="s">
+      <c r="F150" t="s">
         <v>271</v>
       </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
         <v>272</v>
-      </c>
-      <c r="G150" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5102,16 +5102,16 @@
         <v>281</v>
       </c>
       <c r="D151" t="s">
+        <v>163</v>
+      </c>
+      <c r="E151" t="s">
         <v>270</v>
       </c>
-      <c r="E151" t="s">
+      <c r="F151" t="s">
         <v>271</v>
       </c>
-      <c r="F151" t="s">
+      <c r="G151" t="s">
         <v>272</v>
-      </c>
-      <c r="G151" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5125,16 +5125,16 @@
         <v>281</v>
       </c>
       <c r="D152" t="s">
+        <v>163</v>
+      </c>
+      <c r="E152" t="s">
         <v>270</v>
       </c>
-      <c r="E152" t="s">
+      <c r="F152" t="s">
         <v>271</v>
       </c>
-      <c r="F152" t="s">
+      <c r="G152" t="s">
         <v>272</v>
-      </c>
-      <c r="G152" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5148,16 +5148,16 @@
         <v>281</v>
       </c>
       <c r="D153" t="s">
+        <v>163</v>
+      </c>
+      <c r="E153" t="s">
         <v>270</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" t="s">
         <v>271</v>
       </c>
-      <c r="F153" t="s">
+      <c r="G153" t="s">
         <v>272</v>
-      </c>
-      <c r="G153" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5171,16 +5171,16 @@
         <v>281</v>
       </c>
       <c r="D154" t="s">
+        <v>163</v>
+      </c>
+      <c r="E154" t="s">
         <v>270</v>
       </c>
-      <c r="E154" t="s">
+      <c r="F154" t="s">
         <v>271</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>272</v>
-      </c>
-      <c r="G154" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5194,16 +5194,16 @@
         <v>281</v>
       </c>
       <c r="D155" t="s">
+        <v>163</v>
+      </c>
+      <c r="E155" t="s">
         <v>270</v>
       </c>
-      <c r="E155" t="s">
+      <c r="F155" t="s">
         <v>271</v>
       </c>
-      <c r="F155" t="s">
+      <c r="G155" t="s">
         <v>272</v>
-      </c>
-      <c r="G155" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5217,16 +5217,16 @@
         <v>291</v>
       </c>
       <c r="D156" t="s">
+        <v>163</v>
+      </c>
+      <c r="E156" t="s">
         <v>270</v>
       </c>
-      <c r="E156" t="s">
+      <c r="F156" t="s">
         <v>271</v>
       </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
         <v>272</v>
-      </c>
-      <c r="G156" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5240,16 +5240,16 @@
         <v>291</v>
       </c>
       <c r="D157" t="s">
+        <v>163</v>
+      </c>
+      <c r="E157" t="s">
         <v>270</v>
       </c>
-      <c r="E157" t="s">
+      <c r="F157" t="s">
         <v>271</v>
       </c>
-      <c r="F157" t="s">
+      <c r="G157" t="s">
         <v>293</v>
-      </c>
-      <c r="G157" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5263,16 +5263,16 @@
         <v>291</v>
       </c>
       <c r="D158" t="s">
+        <v>163</v>
+      </c>
+      <c r="E158" t="s">
         <v>270</v>
       </c>
-      <c r="E158" t="s">
+      <c r="F158" t="s">
         <v>271</v>
       </c>
-      <c r="F158" t="s">
+      <c r="G158" t="s">
         <v>272</v>
-      </c>
-      <c r="G158" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5286,16 +5286,16 @@
         <v>291</v>
       </c>
       <c r="D159" t="s">
+        <v>163</v>
+      </c>
+      <c r="E159" t="s">
         <v>270</v>
       </c>
-      <c r="E159" t="s">
+      <c r="F159" t="s">
         <v>271</v>
       </c>
-      <c r="F159" t="s">
+      <c r="G159" t="s">
         <v>272</v>
-      </c>
-      <c r="G159" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5309,16 +5309,16 @@
         <v>291</v>
       </c>
       <c r="D160" t="s">
+        <v>163</v>
+      </c>
+      <c r="E160" t="s">
         <v>270</v>
       </c>
-      <c r="E160" t="s">
+      <c r="F160" t="s">
         <v>271</v>
       </c>
-      <c r="F160" t="s">
+      <c r="G160" t="s">
         <v>272</v>
-      </c>
-      <c r="G160" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5332,16 +5332,16 @@
         <v>291</v>
       </c>
       <c r="D161" t="s">
+        <v>163</v>
+      </c>
+      <c r="E161" t="s">
         <v>270</v>
       </c>
-      <c r="E161" t="s">
+      <c r="F161" t="s">
         <v>271</v>
       </c>
-      <c r="F161" t="s">
+      <c r="G161" t="s">
         <v>272</v>
-      </c>
-      <c r="G161" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5355,16 +5355,16 @@
         <v>299</v>
       </c>
       <c r="D162" t="s">
+        <v>163</v>
+      </c>
+      <c r="E162" t="s">
         <v>270</v>
       </c>
-      <c r="E162" t="s">
+      <c r="F162" t="s">
         <v>271</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>272</v>
-      </c>
-      <c r="G162" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5378,16 +5378,16 @@
         <v>301</v>
       </c>
       <c r="D163" t="s">
+        <v>163</v>
+      </c>
+      <c r="E163" t="s">
         <v>270</v>
       </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
         <v>271</v>
       </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
         <v>302</v>
-      </c>
-      <c r="G163" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5401,16 +5401,16 @@
         <v>304</v>
       </c>
       <c r="D164" t="s">
+        <v>163</v>
+      </c>
+      <c r="E164" t="s">
         <v>270</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
         <v>271</v>
       </c>
-      <c r="F164" t="s">
+      <c r="G164" t="s">
         <v>272</v>
-      </c>
-      <c r="G164" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5424,16 +5424,16 @@
         <v>304</v>
       </c>
       <c r="D165" t="s">
+        <v>163</v>
+      </c>
+      <c r="E165" t="s">
         <v>270</v>
       </c>
-      <c r="E165" t="s">
+      <c r="F165" t="s">
         <v>271</v>
       </c>
-      <c r="F165" t="s">
+      <c r="G165" t="s">
         <v>272</v>
-      </c>
-      <c r="G165" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5447,16 +5447,16 @@
         <v>304</v>
       </c>
       <c r="D166" t="s">
+        <v>163</v>
+      </c>
+      <c r="E166" t="s">
         <v>270</v>
       </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
         <v>271</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>272</v>
-      </c>
-      <c r="G166" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5470,16 +5470,16 @@
         <v>304</v>
       </c>
       <c r="D167" t="s">
+        <v>163</v>
+      </c>
+      <c r="E167" t="s">
         <v>270</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" t="s">
         <v>271</v>
       </c>
-      <c r="F167" t="s">
+      <c r="G167" t="s">
         <v>272</v>
-      </c>
-      <c r="G167" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5493,16 +5493,16 @@
         <v>304</v>
       </c>
       <c r="D168" t="s">
+        <v>163</v>
+      </c>
+      <c r="E168" t="s">
         <v>270</v>
       </c>
-      <c r="E168" t="s">
+      <c r="F168" t="s">
         <v>271</v>
       </c>
-      <c r="F168" t="s">
+      <c r="G168" t="s">
         <v>309</v>
-      </c>
-      <c r="G168" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5516,16 +5516,16 @@
         <v>304</v>
       </c>
       <c r="D169" t="s">
+        <v>163</v>
+      </c>
+      <c r="E169" t="s">
         <v>270</v>
       </c>
-      <c r="E169" t="s">
+      <c r="F169" t="s">
         <v>271</v>
       </c>
-      <c r="F169" t="s">
+      <c r="G169" t="s">
         <v>309</v>
-      </c>
-      <c r="G169" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5539,16 +5539,16 @@
         <v>304</v>
       </c>
       <c r="D170" t="s">
+        <v>163</v>
+      </c>
+      <c r="E170" t="s">
         <v>270</v>
       </c>
-      <c r="E170" t="s">
+      <c r="F170" t="s">
         <v>271</v>
       </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>272</v>
-      </c>
-      <c r="G170" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5559,10 +5559,10 @@
         <v>8</v>
       </c>
       <c r="D171" t="s">
+        <v>163</v>
+      </c>
+      <c r="E171" t="s">
         <v>313</v>
-      </c>
-      <c r="E171" t="s">
-        <v>163</v>
       </c>
       <c r="F171" t="s">
         <v>164</v>
@@ -5579,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="D172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E172" t="s">
         <v>313</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
         <v>118</v>
       </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>119</v>
-      </c>
-      <c r="G172" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5599,10 +5599,10 @@
         <v>8</v>
       </c>
       <c r="D173" t="s">
+        <v>163</v>
+      </c>
+      <c r="E173" t="s">
         <v>313</v>
-      </c>
-      <c r="E173" t="s">
-        <v>163</v>
       </c>
       <c r="F173" t="s">
         <v>164</v>
@@ -5619,10 +5619,10 @@
         <v>8</v>
       </c>
       <c r="D174" t="s">
+        <v>163</v>
+      </c>
+      <c r="E174" t="s">
         <v>313</v>
-      </c>
-      <c r="E174" t="s">
-        <v>163</v>
       </c>
       <c r="F174" t="s">
         <v>164</v>
@@ -5639,10 +5639,10 @@
         <v>8</v>
       </c>
       <c r="D175" t="s">
+        <v>163</v>
+      </c>
+      <c r="E175" t="s">
         <v>313</v>
-      </c>
-      <c r="E175" t="s">
-        <v>163</v>
       </c>
       <c r="F175" t="s">
         <v>164</v>
@@ -5659,10 +5659,10 @@
         <v>8</v>
       </c>
       <c r="D176" t="s">
+        <v>163</v>
+      </c>
+      <c r="E176" t="s">
         <v>313</v>
-      </c>
-      <c r="E176" t="s">
-        <v>163</v>
       </c>
       <c r="F176" t="s">
         <v>164</v>
@@ -5679,10 +5679,10 @@
         <v>8</v>
       </c>
       <c r="D177" t="s">
+        <v>163</v>
+      </c>
+      <c r="E177" t="s">
         <v>320</v>
-      </c>
-      <c r="E177" t="s">
-        <v>163</v>
       </c>
       <c r="F177" t="s">
         <v>164</v>
@@ -5699,10 +5699,10 @@
         <v>8</v>
       </c>
       <c r="D178" t="s">
+        <v>163</v>
+      </c>
+      <c r="E178" t="s">
         <v>320</v>
-      </c>
-      <c r="E178" t="s">
-        <v>163</v>
       </c>
       <c r="F178" t="s">
         <v>164</v>
@@ -5719,10 +5719,10 @@
         <v>8</v>
       </c>
       <c r="D179" t="s">
+        <v>163</v>
+      </c>
+      <c r="E179" t="s">
         <v>320</v>
-      </c>
-      <c r="E179" t="s">
-        <v>163</v>
       </c>
       <c r="F179" t="s">
         <v>164</v>
@@ -5739,10 +5739,10 @@
         <v>8</v>
       </c>
       <c r="D180" t="s">
+        <v>163</v>
+      </c>
+      <c r="E180" t="s">
         <v>320</v>
-      </c>
-      <c r="E180" t="s">
-        <v>163</v>
       </c>
       <c r="F180" t="s">
         <v>164</v>
@@ -5762,16 +5762,16 @@
         <v>325</v>
       </c>
       <c r="D181" t="s">
+        <v>163</v>
+      </c>
+      <c r="E181" t="s">
         <v>326</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>327</v>
       </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
         <v>328</v>
-      </c>
-      <c r="G181" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5785,16 +5785,16 @@
         <v>325</v>
       </c>
       <c r="D182" t="s">
+        <v>163</v>
+      </c>
+      <c r="E182" t="s">
         <v>326</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" t="s">
         <v>327</v>
       </c>
-      <c r="F182" t="s">
+      <c r="G182" t="s">
         <v>328</v>
-      </c>
-      <c r="G182" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5808,16 +5808,16 @@
         <v>325</v>
       </c>
       <c r="D183" t="s">
+        <v>163</v>
+      </c>
+      <c r="E183" t="s">
         <v>326</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
         <v>327</v>
       </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
         <v>328</v>
-      </c>
-      <c r="G183" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5831,16 +5831,16 @@
         <v>325</v>
       </c>
       <c r="D184" t="s">
+        <v>163</v>
+      </c>
+      <c r="E184" t="s">
         <v>326</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
         <v>327</v>
       </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
         <v>328</v>
-      </c>
-      <c r="G184" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5854,16 +5854,16 @@
         <v>325</v>
       </c>
       <c r="D185" t="s">
+        <v>163</v>
+      </c>
+      <c r="E185" t="s">
         <v>326</v>
       </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
         <v>327</v>
       </c>
-      <c r="F185" t="s">
+      <c r="G185" t="s">
         <v>328</v>
-      </c>
-      <c r="G185" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5877,16 +5877,16 @@
         <v>325</v>
       </c>
       <c r="D186" t="s">
+        <v>163</v>
+      </c>
+      <c r="E186" t="s">
         <v>326</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
         <v>327</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>328</v>
-      </c>
-      <c r="G186" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5900,16 +5900,16 @@
         <v>325</v>
       </c>
       <c r="D187" t="s">
+        <v>163</v>
+      </c>
+      <c r="E187" t="s">
         <v>326</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
         <v>327</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>328</v>
-      </c>
-      <c r="G187" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5923,16 +5923,16 @@
         <v>325</v>
       </c>
       <c r="D188" t="s">
+        <v>163</v>
+      </c>
+      <c r="E188" t="s">
         <v>326</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
         <v>327</v>
       </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>328</v>
-      </c>
-      <c r="G188" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5946,16 +5946,16 @@
         <v>325</v>
       </c>
       <c r="D189" t="s">
+        <v>163</v>
+      </c>
+      <c r="E189" t="s">
         <v>326</v>
       </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
         <v>327</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>328</v>
-      </c>
-      <c r="G189" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5969,16 +5969,16 @@
         <v>325</v>
       </c>
       <c r="D190" t="s">
+        <v>163</v>
+      </c>
+      <c r="E190" t="s">
         <v>326</v>
       </c>
-      <c r="E190" t="s">
+      <c r="F190" t="s">
         <v>327</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>328</v>
-      </c>
-      <c r="G190" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5992,16 +5992,16 @@
         <v>325</v>
       </c>
       <c r="D191" t="s">
+        <v>163</v>
+      </c>
+      <c r="E191" t="s">
         <v>326</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
         <v>327</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>328</v>
-      </c>
-      <c r="G191" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6015,16 +6015,16 @@
         <v>325</v>
       </c>
       <c r="D192" t="s">
+        <v>163</v>
+      </c>
+      <c r="E192" t="s">
         <v>326</v>
       </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
         <v>327</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>328</v>
-      </c>
-      <c r="G192" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6038,16 +6038,16 @@
         <v>325</v>
       </c>
       <c r="D193" t="s">
+        <v>163</v>
+      </c>
+      <c r="E193" t="s">
         <v>326</v>
       </c>
-      <c r="E193" t="s">
+      <c r="F193" t="s">
         <v>275</v>
       </c>
-      <c r="F193" t="s">
+      <c r="G193" t="s">
         <v>341</v>
-      </c>
-      <c r="G193" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6061,16 +6061,16 @@
         <v>325</v>
       </c>
       <c r="D194" t="s">
+        <v>163</v>
+      </c>
+      <c r="E194" t="s">
         <v>326</v>
       </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
         <v>327</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>328</v>
-      </c>
-      <c r="G194" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6084,16 +6084,16 @@
         <v>325</v>
       </c>
       <c r="D195" t="s">
+        <v>163</v>
+      </c>
+      <c r="E195" t="s">
         <v>326</v>
       </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
         <v>327</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>328</v>
-      </c>
-      <c r="G195" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6107,16 +6107,16 @@
         <v>325</v>
       </c>
       <c r="D196" t="s">
+        <v>163</v>
+      </c>
+      <c r="E196" t="s">
         <v>326</v>
       </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
         <v>327</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>328</v>
-      </c>
-      <c r="G196" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6130,16 +6130,16 @@
         <v>325</v>
       </c>
       <c r="D197" t="s">
+        <v>163</v>
+      </c>
+      <c r="E197" t="s">
         <v>326</v>
       </c>
-      <c r="E197" t="s">
+      <c r="F197" t="s">
         <v>327</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
         <v>328</v>
-      </c>
-      <c r="G197" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6153,16 +6153,16 @@
         <v>325</v>
       </c>
       <c r="D198" t="s">
+        <v>163</v>
+      </c>
+      <c r="E198" t="s">
         <v>326</v>
       </c>
-      <c r="E198" t="s">
+      <c r="F198" t="s">
         <v>327</v>
       </c>
-      <c r="F198" t="s">
+      <c r="G198" t="s">
         <v>328</v>
-      </c>
-      <c r="G198" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6176,16 +6176,16 @@
         <v>348</v>
       </c>
       <c r="D199" t="s">
+        <v>163</v>
+      </c>
+      <c r="E199" t="s">
         <v>326</v>
       </c>
-      <c r="E199" t="s">
+      <c r="F199" t="s">
         <v>327</v>
       </c>
-      <c r="F199" t="s">
+      <c r="G199" t="s">
         <v>349</v>
-      </c>
-      <c r="G199" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6199,16 +6199,16 @@
         <v>348</v>
       </c>
       <c r="D200" t="s">
+        <v>163</v>
+      </c>
+      <c r="E200" t="s">
         <v>326</v>
       </c>
-      <c r="E200" t="s">
+      <c r="F200" t="s">
         <v>327</v>
       </c>
-      <c r="F200" t="s">
+      <c r="G200" t="s">
         <v>349</v>
-      </c>
-      <c r="G200" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6222,16 +6222,16 @@
         <v>348</v>
       </c>
       <c r="D201" t="s">
+        <v>163</v>
+      </c>
+      <c r="E201" t="s">
         <v>326</v>
       </c>
-      <c r="E201" t="s">
+      <c r="F201" t="s">
         <v>327</v>
       </c>
-      <c r="F201" t="s">
+      <c r="G201" t="s">
         <v>349</v>
-      </c>
-      <c r="G201" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6245,16 +6245,16 @@
         <v>348</v>
       </c>
       <c r="D202" t="s">
+        <v>163</v>
+      </c>
+      <c r="E202" t="s">
         <v>326</v>
       </c>
-      <c r="E202" t="s">
+      <c r="F202" t="s">
         <v>327</v>
       </c>
-      <c r="F202" t="s">
+      <c r="G202" t="s">
         <v>349</v>
-      </c>
-      <c r="G202" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6268,16 +6268,16 @@
         <v>348</v>
       </c>
       <c r="D203" t="s">
+        <v>163</v>
+      </c>
+      <c r="E203" t="s">
         <v>326</v>
       </c>
-      <c r="E203" t="s">
+      <c r="F203" t="s">
         <v>275</v>
       </c>
-      <c r="F203" t="s">
+      <c r="G203" t="s">
         <v>341</v>
-      </c>
-      <c r="G203" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6291,16 +6291,16 @@
         <v>348</v>
       </c>
       <c r="D204" t="s">
+        <v>163</v>
+      </c>
+      <c r="E204" t="s">
         <v>326</v>
       </c>
-      <c r="E204" t="s">
+      <c r="F204" t="s">
         <v>327</v>
       </c>
-      <c r="F204" t="s">
+      <c r="G204" t="s">
         <v>349</v>
-      </c>
-      <c r="G204" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6314,16 +6314,16 @@
         <v>356</v>
       </c>
       <c r="D205" t="s">
+        <v>163</v>
+      </c>
+      <c r="E205" t="s">
         <v>326</v>
       </c>
-      <c r="E205" t="s">
+      <c r="F205" t="s">
         <v>327</v>
       </c>
-      <c r="F205" t="s">
+      <c r="G205" t="s">
         <v>357</v>
-      </c>
-      <c r="G205" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6337,16 +6337,16 @@
         <v>356</v>
       </c>
       <c r="D206" t="s">
+        <v>163</v>
+      </c>
+      <c r="E206" t="s">
         <v>326</v>
       </c>
-      <c r="E206" t="s">
+      <c r="F206" t="s">
         <v>327</v>
       </c>
-      <c r="F206" t="s">
+      <c r="G206" t="s">
         <v>357</v>
-      </c>
-      <c r="G206" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6360,16 +6360,16 @@
         <v>356</v>
       </c>
       <c r="D207" t="s">
+        <v>163</v>
+      </c>
+      <c r="E207" t="s">
         <v>326</v>
       </c>
-      <c r="E207" t="s">
+      <c r="F207" t="s">
         <v>327</v>
       </c>
-      <c r="F207" t="s">
+      <c r="G207" t="s">
         <v>357</v>
-      </c>
-      <c r="G207" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6383,16 +6383,16 @@
         <v>356</v>
       </c>
       <c r="D208" t="s">
+        <v>163</v>
+      </c>
+      <c r="E208" t="s">
         <v>326</v>
       </c>
-      <c r="E208" t="s">
+      <c r="F208" t="s">
         <v>275</v>
       </c>
-      <c r="F208" t="s">
+      <c r="G208" t="s">
         <v>341</v>
-      </c>
-      <c r="G208" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6406,16 +6406,16 @@
         <v>356</v>
       </c>
       <c r="D209" t="s">
+        <v>163</v>
+      </c>
+      <c r="E209" t="s">
         <v>326</v>
       </c>
-      <c r="E209" t="s">
+      <c r="F209" t="s">
         <v>327</v>
       </c>
-      <c r="F209" t="s">
+      <c r="G209" t="s">
         <v>357</v>
-      </c>
-      <c r="G209" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6429,16 +6429,16 @@
         <v>363</v>
       </c>
       <c r="D210" t="s">
+        <v>163</v>
+      </c>
+      <c r="E210" t="s">
         <v>364</v>
       </c>
-      <c r="E210" t="s">
+      <c r="F210" t="s">
         <v>365</v>
       </c>
-      <c r="F210" t="s">
+      <c r="G210" t="s">
         <v>366</v>
-      </c>
-      <c r="G210" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6452,16 +6452,16 @@
         <v>363</v>
       </c>
       <c r="D211" t="s">
+        <v>163</v>
+      </c>
+      <c r="E211" t="s">
         <v>364</v>
       </c>
-      <c r="E211" t="s">
+      <c r="F211" t="s">
         <v>365</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>366</v>
-      </c>
-      <c r="G211" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6475,16 +6475,16 @@
         <v>363</v>
       </c>
       <c r="D212" t="s">
+        <v>163</v>
+      </c>
+      <c r="E212" t="s">
         <v>364</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
         <v>365</v>
       </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>366</v>
-      </c>
-      <c r="G212" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6498,16 +6498,16 @@
         <v>363</v>
       </c>
       <c r="D213" t="s">
+        <v>163</v>
+      </c>
+      <c r="E213" t="s">
         <v>364</v>
       </c>
-      <c r="E213" t="s">
+      <c r="F213" t="s">
         <v>365</v>
       </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>366</v>
-      </c>
-      <c r="G213" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6521,16 +6521,16 @@
         <v>363</v>
       </c>
       <c r="D214" t="s">
+        <v>163</v>
+      </c>
+      <c r="E214" t="s">
         <v>364</v>
       </c>
-      <c r="E214" t="s">
+      <c r="F214" t="s">
         <v>365</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>366</v>
-      </c>
-      <c r="G214" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6544,16 +6544,16 @@
         <v>363</v>
       </c>
       <c r="D215" t="s">
+        <v>163</v>
+      </c>
+      <c r="E215" t="s">
         <v>364</v>
       </c>
-      <c r="E215" t="s">
+      <c r="F215" t="s">
         <v>327</v>
       </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
         <v>349</v>
-      </c>
-      <c r="G215" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6567,16 +6567,16 @@
         <v>363</v>
       </c>
       <c r="D216" t="s">
+        <v>163</v>
+      </c>
+      <c r="E216" t="s">
         <v>364</v>
       </c>
-      <c r="E216" t="s">
+      <c r="F216" t="s">
         <v>365</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>366</v>
-      </c>
-      <c r="G216" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6590,16 +6590,16 @@
         <v>363</v>
       </c>
       <c r="D217" t="s">
+        <v>163</v>
+      </c>
+      <c r="E217" t="s">
         <v>364</v>
       </c>
-      <c r="E217" t="s">
+      <c r="F217" t="s">
         <v>365</v>
       </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
         <v>366</v>
-      </c>
-      <c r="G217" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6613,16 +6613,16 @@
         <v>363</v>
       </c>
       <c r="D218" t="s">
+        <v>163</v>
+      </c>
+      <c r="E218" t="s">
         <v>364</v>
       </c>
-      <c r="E218" t="s">
+      <c r="F218" t="s">
         <v>365</v>
       </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>366</v>
-      </c>
-      <c r="G218" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6636,16 +6636,16 @@
         <v>363</v>
       </c>
       <c r="D219" t="s">
+        <v>163</v>
+      </c>
+      <c r="E219" t="s">
         <v>364</v>
       </c>
-      <c r="E219" t="s">
+      <c r="F219" t="s">
         <v>365</v>
       </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>366</v>
-      </c>
-      <c r="G219" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6659,16 +6659,16 @@
         <v>363</v>
       </c>
       <c r="D220" t="s">
+        <v>163</v>
+      </c>
+      <c r="E220" t="s">
         <v>364</v>
       </c>
-      <c r="E220" t="s">
+      <c r="F220" t="s">
         <v>271</v>
       </c>
-      <c r="F220" t="s">
+      <c r="G220" t="s">
         <v>309</v>
-      </c>
-      <c r="G220" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6682,16 +6682,16 @@
         <v>363</v>
       </c>
       <c r="D221" t="s">
+        <v>163</v>
+      </c>
+      <c r="E221" t="s">
         <v>364</v>
       </c>
-      <c r="E221" t="s">
+      <c r="F221" t="s">
         <v>365</v>
       </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>366</v>
-      </c>
-      <c r="G221" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6705,16 +6705,16 @@
         <v>363</v>
       </c>
       <c r="D222" t="s">
+        <v>163</v>
+      </c>
+      <c r="E222" t="s">
         <v>364</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
         <v>365</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>366</v>
-      </c>
-      <c r="G222" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6728,16 +6728,16 @@
         <v>363</v>
       </c>
       <c r="D223" t="s">
+        <v>163</v>
+      </c>
+      <c r="E223" t="s">
         <v>364</v>
       </c>
-      <c r="E223" t="s">
+      <c r="F223" t="s">
         <v>365</v>
       </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>366</v>
-      </c>
-      <c r="G223" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6751,16 +6751,16 @@
         <v>363</v>
       </c>
       <c r="D224" t="s">
+        <v>163</v>
+      </c>
+      <c r="E224" t="s">
         <v>364</v>
       </c>
-      <c r="E224" t="s">
+      <c r="F224" t="s">
         <v>365</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>366</v>
-      </c>
-      <c r="G224" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6774,16 +6774,16 @@
         <v>363</v>
       </c>
       <c r="D225" t="s">
+        <v>163</v>
+      </c>
+      <c r="E225" t="s">
         <v>364</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" t="s">
         <v>365</v>
       </c>
-      <c r="F225" t="s">
+      <c r="G225" t="s">
         <v>366</v>
-      </c>
-      <c r="G225" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6797,16 +6797,16 @@
         <v>363</v>
       </c>
       <c r="D226" t="s">
+        <v>163</v>
+      </c>
+      <c r="E226" t="s">
         <v>364</v>
       </c>
-      <c r="E226" t="s">
+      <c r="F226" t="s">
         <v>275</v>
       </c>
-      <c r="F226" t="s">
+      <c r="G226" t="s">
         <v>276</v>
-      </c>
-      <c r="G226" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6820,16 +6820,16 @@
         <v>363</v>
       </c>
       <c r="D227" t="s">
+        <v>163</v>
+      </c>
+      <c r="E227" t="s">
         <v>364</v>
       </c>
-      <c r="E227" t="s">
+      <c r="F227" t="s">
         <v>365</v>
       </c>
-      <c r="F227" t="s">
+      <c r="G227" t="s">
         <v>366</v>
-      </c>
-      <c r="G227" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6843,10 +6843,10 @@
         <v>363</v>
       </c>
       <c r="D228" t="s">
+        <v>163</v>
+      </c>
+      <c r="E228" t="s">
         <v>364</v>
-      </c>
-      <c r="E228" t="s">
-        <v>163</v>
       </c>
       <c r="F228" t="s">
         <v>164</v>
@@ -6866,16 +6866,16 @@
         <v>386</v>
       </c>
       <c r="D229" t="s">
+        <v>163</v>
+      </c>
+      <c r="E229" t="s">
         <v>364</v>
       </c>
-      <c r="E229" t="s">
+      <c r="F229" t="s">
         <v>365</v>
       </c>
-      <c r="F229" t="s">
+      <c r="G229" t="s">
         <v>387</v>
-      </c>
-      <c r="G229" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6889,16 +6889,16 @@
         <v>386</v>
       </c>
       <c r="D230" t="s">
+        <v>163</v>
+      </c>
+      <c r="E230" t="s">
         <v>364</v>
       </c>
-      <c r="E230" t="s">
+      <c r="F230" t="s">
         <v>365</v>
       </c>
-      <c r="F230" t="s">
+      <c r="G230" t="s">
         <v>387</v>
-      </c>
-      <c r="G230" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6912,16 +6912,16 @@
         <v>386</v>
       </c>
       <c r="D231" t="s">
+        <v>163</v>
+      </c>
+      <c r="E231" t="s">
         <v>364</v>
       </c>
-      <c r="E231" t="s">
+      <c r="F231" t="s">
         <v>271</v>
       </c>
-      <c r="F231" t="s">
+      <c r="G231" t="s">
         <v>293</v>
-      </c>
-      <c r="G231" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6935,16 +6935,16 @@
         <v>386</v>
       </c>
       <c r="D232" t="s">
+        <v>163</v>
+      </c>
+      <c r="E232" t="s">
         <v>364</v>
       </c>
-      <c r="E232" t="s">
+      <c r="F232" t="s">
         <v>271</v>
       </c>
-      <c r="F232" t="s">
+      <c r="G232" t="s">
         <v>309</v>
-      </c>
-      <c r="G232" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6958,16 +6958,16 @@
         <v>386</v>
       </c>
       <c r="D233" t="s">
+        <v>163</v>
+      </c>
+      <c r="E233" t="s">
         <v>364</v>
       </c>
-      <c r="E233" t="s">
+      <c r="F233" t="s">
         <v>365</v>
       </c>
-      <c r="F233" t="s">
+      <c r="G233" t="s">
         <v>387</v>
-      </c>
-      <c r="G233" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6981,16 +6981,16 @@
         <v>386</v>
       </c>
       <c r="D234" t="s">
+        <v>163</v>
+      </c>
+      <c r="E234" t="s">
         <v>364</v>
       </c>
-      <c r="E234" t="s">
+      <c r="F234" t="s">
         <v>365</v>
       </c>
-      <c r="F234" t="s">
+      <c r="G234" t="s">
         <v>387</v>
-      </c>
-      <c r="G234" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7004,16 +7004,16 @@
         <v>386</v>
       </c>
       <c r="D235" t="s">
+        <v>163</v>
+      </c>
+      <c r="E235" t="s">
         <v>364</v>
       </c>
-      <c r="E235" t="s">
+      <c r="F235" t="s">
         <v>365</v>
       </c>
-      <c r="F235" t="s">
+      <c r="G235" t="s">
         <v>387</v>
-      </c>
-      <c r="G235" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7027,16 +7027,16 @@
         <v>386</v>
       </c>
       <c r="D236" t="s">
+        <v>163</v>
+      </c>
+      <c r="E236" t="s">
         <v>364</v>
       </c>
-      <c r="E236" t="s">
+      <c r="F236" t="s">
         <v>365</v>
       </c>
-      <c r="F236" t="s">
+      <c r="G236" t="s">
         <v>387</v>
-      </c>
-      <c r="G236" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7050,16 +7050,16 @@
         <v>386</v>
       </c>
       <c r="D237" t="s">
+        <v>163</v>
+      </c>
+      <c r="E237" t="s">
         <v>364</v>
       </c>
-      <c r="E237" t="s">
+      <c r="F237" t="s">
         <v>365</v>
       </c>
-      <c r="F237" t="s">
+      <c r="G237" t="s">
         <v>387</v>
-      </c>
-      <c r="G237" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7073,16 +7073,16 @@
         <v>386</v>
       </c>
       <c r="D238" t="s">
+        <v>163</v>
+      </c>
+      <c r="E238" t="s">
         <v>364</v>
       </c>
-      <c r="E238" t="s">
+      <c r="F238" t="s">
         <v>365</v>
       </c>
-      <c r="F238" t="s">
+      <c r="G238" t="s">
         <v>387</v>
-      </c>
-      <c r="G238" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7096,16 +7096,16 @@
         <v>398</v>
       </c>
       <c r="D239" t="s">
+        <v>163</v>
+      </c>
+      <c r="E239" t="s">
         <v>364</v>
       </c>
-      <c r="E239" t="s">
+      <c r="F239" t="s">
         <v>365</v>
       </c>
-      <c r="F239" t="s">
+      <c r="G239" t="s">
         <v>399</v>
-      </c>
-      <c r="G239" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7119,10 +7119,10 @@
         <v>401</v>
       </c>
       <c r="D240" t="s">
+        <v>163</v>
+      </c>
+      <c r="E240" t="s">
         <v>402</v>
-      </c>
-      <c r="E240" t="s">
-        <v>163</v>
       </c>
       <c r="F240" t="s">
         <v>164</v>
@@ -7142,10 +7142,10 @@
         <v>401</v>
       </c>
       <c r="D241" t="s">
+        <v>163</v>
+      </c>
+      <c r="E241" t="s">
         <v>402</v>
-      </c>
-      <c r="E241" t="s">
-        <v>163</v>
       </c>
       <c r="F241" t="s">
         <v>164</v>
@@ -7165,10 +7165,10 @@
         <v>401</v>
       </c>
       <c r="D242" t="s">
+        <v>163</v>
+      </c>
+      <c r="E242" t="s">
         <v>402</v>
-      </c>
-      <c r="E242" t="s">
-        <v>163</v>
       </c>
       <c r="F242" t="s">
         <v>164</v>
@@ -7188,10 +7188,10 @@
         <v>401</v>
       </c>
       <c r="D243" t="s">
+        <v>163</v>
+      </c>
+      <c r="E243" t="s">
         <v>402</v>
-      </c>
-      <c r="E243" t="s">
-        <v>163</v>
       </c>
       <c r="F243" t="s">
         <v>164</v>
@@ -7211,10 +7211,10 @@
         <v>401</v>
       </c>
       <c r="D244" t="s">
+        <v>163</v>
+      </c>
+      <c r="E244" t="s">
         <v>402</v>
-      </c>
-      <c r="E244" t="s">
-        <v>163</v>
       </c>
       <c r="F244" t="s">
         <v>164</v>
@@ -7234,10 +7234,10 @@
         <v>401</v>
       </c>
       <c r="D245" t="s">
+        <v>163</v>
+      </c>
+      <c r="E245" t="s">
         <v>402</v>
-      </c>
-      <c r="E245" t="s">
-        <v>163</v>
       </c>
       <c r="F245" t="s">
         <v>164</v>
@@ -7257,16 +7257,16 @@
         <v>409</v>
       </c>
       <c r="D246" t="s">
+        <v>163</v>
+      </c>
+      <c r="E246" t="s">
         <v>402</v>
       </c>
-      <c r="E246" t="s">
+      <c r="F246" t="s">
         <v>255</v>
       </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
         <v>410</v>
-      </c>
-      <c r="G246" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7277,10 +7277,10 @@
         <v>8</v>
       </c>
       <c r="D247" t="s">
+        <v>95</v>
+      </c>
+      <c r="E247" t="s">
         <v>412</v>
-      </c>
-      <c r="E247" t="s">
-        <v>95</v>
       </c>
       <c r="F247" t="s">
         <v>96</v>
@@ -7297,10 +7297,10 @@
         <v>8</v>
       </c>
       <c r="D248" t="s">
+        <v>95</v>
+      </c>
+      <c r="E248" t="s">
         <v>412</v>
-      </c>
-      <c r="E248" t="s">
-        <v>95</v>
       </c>
       <c r="F248" t="s">
         <v>96</v>
@@ -7317,16 +7317,16 @@
         <v>8</v>
       </c>
       <c r="D249" t="s">
+        <v>95</v>
+      </c>
+      <c r="E249" t="s">
         <v>412</v>
       </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
         <v>415</v>
       </c>
-      <c r="F249" t="s">
+      <c r="G249" t="s">
         <v>416</v>
-      </c>
-      <c r="G249" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7337,10 +7337,10 @@
         <v>8</v>
       </c>
       <c r="D250" t="s">
+        <v>95</v>
+      </c>
+      <c r="E250" t="s">
         <v>412</v>
-      </c>
-      <c r="E250" t="s">
-        <v>95</v>
       </c>
       <c r="F250" t="s">
         <v>96</v>
@@ -7357,10 +7357,10 @@
         <v>8</v>
       </c>
       <c r="D251" t="s">
+        <v>95</v>
+      </c>
+      <c r="E251" t="s">
         <v>412</v>
-      </c>
-      <c r="E251" t="s">
-        <v>95</v>
       </c>
       <c r="F251" t="s">
         <v>96</v>
@@ -7377,10 +7377,10 @@
         <v>8</v>
       </c>
       <c r="D252" t="s">
+        <v>95</v>
+      </c>
+      <c r="E252" t="s">
         <v>412</v>
-      </c>
-      <c r="E252" t="s">
-        <v>95</v>
       </c>
       <c r="F252" t="s">
         <v>96</v>
@@ -7397,16 +7397,16 @@
         <v>8</v>
       </c>
       <c r="D253" t="s">
+        <v>163</v>
+      </c>
+      <c r="E253" t="s">
         <v>421</v>
       </c>
-      <c r="E253" t="s">
+      <c r="F253" t="s">
         <v>422</v>
       </c>
-      <c r="F253" t="s">
+      <c r="G253" t="s">
         <v>423</v>
-      </c>
-      <c r="G253" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7417,16 +7417,16 @@
         <v>8</v>
       </c>
       <c r="D254" t="s">
+        <v>90</v>
+      </c>
+      <c r="E254" t="s">
         <v>421</v>
       </c>
-      <c r="E254" t="s">
+      <c r="F254" t="s">
         <v>219</v>
       </c>
-      <c r="F254" t="s">
+      <c r="G254" t="s">
         <v>220</v>
-      </c>
-      <c r="G254" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7437,16 +7437,16 @@
         <v>8</v>
       </c>
       <c r="D255" t="s">
+        <v>90</v>
+      </c>
+      <c r="E255" t="s">
         <v>421</v>
       </c>
-      <c r="E255" t="s">
+      <c r="F255" t="s">
         <v>426</v>
       </c>
-      <c r="F255" t="s">
+      <c r="G255" t="s">
         <v>427</v>
-      </c>
-      <c r="G255" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7457,16 +7457,16 @@
         <v>8</v>
       </c>
       <c r="D256" t="s">
+        <v>90</v>
+      </c>
+      <c r="E256" t="s">
         <v>421</v>
       </c>
-      <c r="E256" t="s">
+      <c r="F256" t="s">
         <v>426</v>
       </c>
-      <c r="F256" t="s">
+      <c r="G256" t="s">
         <v>427</v>
-      </c>
-      <c r="G256" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7477,16 +7477,16 @@
         <v>8</v>
       </c>
       <c r="D257" t="s">
+        <v>90</v>
+      </c>
+      <c r="E257" t="s">
         <v>421</v>
       </c>
-      <c r="E257" t="s">
+      <c r="F257" t="s">
         <v>426</v>
       </c>
-      <c r="F257" t="s">
+      <c r="G257" t="s">
         <v>427</v>
-      </c>
-      <c r="G257" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7497,16 +7497,16 @@
         <v>8</v>
       </c>
       <c r="D258" t="s">
+        <v>163</v>
+      </c>
+      <c r="E258" t="s">
         <v>421</v>
       </c>
-      <c r="E258" t="s">
+      <c r="F258" t="s">
         <v>327</v>
       </c>
-      <c r="F258" t="s">
+      <c r="G258" t="s">
         <v>328</v>
-      </c>
-      <c r="G258" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7517,16 +7517,16 @@
         <v>8</v>
       </c>
       <c r="D259" t="s">
+        <v>90</v>
+      </c>
+      <c r="E259" t="s">
         <v>421</v>
       </c>
-      <c r="E259" t="s">
+      <c r="F259" t="s">
         <v>426</v>
       </c>
-      <c r="F259" t="s">
+      <c r="G259" t="s">
         <v>427</v>
-      </c>
-      <c r="G259" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7537,10 +7537,10 @@
         <v>8</v>
       </c>
       <c r="D260" t="s">
+        <v>163</v>
+      </c>
+      <c r="E260" t="s">
         <v>421</v>
-      </c>
-      <c r="E260" t="s">
-        <v>163</v>
       </c>
       <c r="F260" t="s">
         <v>164</v>
@@ -7557,16 +7557,16 @@
         <v>8</v>
       </c>
       <c r="D261" t="s">
+        <v>195</v>
+      </c>
+      <c r="E261" t="s">
         <v>421</v>
       </c>
-      <c r="E261" t="s">
+      <c r="F261" t="s">
         <v>434</v>
       </c>
-      <c r="F261" t="s">
+      <c r="G261" t="s">
         <v>435</v>
-      </c>
-      <c r="G261" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7577,10 +7577,10 @@
         <v>8</v>
       </c>
       <c r="D262" t="s">
+        <v>163</v>
+      </c>
+      <c r="E262" t="s">
         <v>421</v>
-      </c>
-      <c r="E262" t="s">
-        <v>163</v>
       </c>
       <c r="F262" t="s">
         <v>164</v>
@@ -7597,16 +7597,16 @@
         <v>8</v>
       </c>
       <c r="D263" t="s">
+        <v>182</v>
+      </c>
+      <c r="E263" t="s">
         <v>421</v>
       </c>
-      <c r="E263" t="s">
+      <c r="F263" t="s">
         <v>438</v>
       </c>
-      <c r="F263" t="s">
+      <c r="G263" t="s">
         <v>439</v>
-      </c>
-      <c r="G263" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7617,10 +7617,10 @@
         <v>8</v>
       </c>
       <c r="D264" t="s">
+        <v>31</v>
+      </c>
+      <c r="E264" t="s">
         <v>421</v>
-      </c>
-      <c r="E264" t="s">
-        <v>31</v>
       </c>
       <c r="F264" t="s">
         <v>32</v>
@@ -7637,10 +7637,10 @@
         <v>8</v>
       </c>
       <c r="D265" t="s">
+        <v>10</v>
+      </c>
+      <c r="E265" t="s">
         <v>421</v>
-      </c>
-      <c r="E265" t="s">
-        <v>11</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
@@ -7657,16 +7657,16 @@
         <v>8</v>
       </c>
       <c r="D266" t="s">
+        <v>113</v>
+      </c>
+      <c r="E266" t="s">
         <v>421</v>
       </c>
-      <c r="E266" t="s">
+      <c r="F266" t="s">
         <v>443</v>
       </c>
-      <c r="F266" t="s">
+      <c r="G266" t="s">
         <v>444</v>
-      </c>
-      <c r="G266" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7677,16 +7677,16 @@
         <v>8</v>
       </c>
       <c r="D267" t="s">
+        <v>113</v>
+      </c>
+      <c r="E267" t="s">
         <v>446</v>
       </c>
-      <c r="E267" t="s">
+      <c r="F267" t="s">
         <v>118</v>
       </c>
-      <c r="F267" t="s">
+      <c r="G267" t="s">
         <v>119</v>
-      </c>
-      <c r="G267" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7697,16 +7697,16 @@
         <v>8</v>
       </c>
       <c r="D268" t="s">
+        <v>182</v>
+      </c>
+      <c r="E268" t="s">
         <v>448</v>
       </c>
-      <c r="E268" t="s">
+      <c r="F268" t="s">
         <v>203</v>
       </c>
-      <c r="F268" t="s">
+      <c r="G268" t="s">
         <v>204</v>
-      </c>
-      <c r="G268" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7717,16 +7717,16 @@
         <v>8</v>
       </c>
       <c r="D269" t="s">
+        <v>113</v>
+      </c>
+      <c r="E269" t="s">
         <v>450</v>
       </c>
-      <c r="E269" t="s">
+      <c r="F269" t="s">
         <v>118</v>
       </c>
-      <c r="F269" t="s">
+      <c r="G269" t="s">
         <v>119</v>
-      </c>
-      <c r="G269" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7737,16 +7737,16 @@
         <v>8</v>
       </c>
       <c r="D270" t="s">
+        <v>113</v>
+      </c>
+      <c r="E270" t="s">
         <v>450</v>
       </c>
-      <c r="E270" t="s">
+      <c r="F270" t="s">
         <v>118</v>
       </c>
-      <c r="F270" t="s">
+      <c r="G270" t="s">
         <v>119</v>
-      </c>
-      <c r="G270" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7757,16 +7757,16 @@
         <v>8</v>
       </c>
       <c r="D271" t="s">
+        <v>113</v>
+      </c>
+      <c r="E271" t="s">
         <v>453</v>
       </c>
-      <c r="E271" t="s">
+      <c r="F271" t="s">
         <v>454</v>
       </c>
-      <c r="F271" t="s">
+      <c r="G271" t="s">
         <v>455</v>
-      </c>
-      <c r="G271" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7777,16 +7777,16 @@
         <v>8</v>
       </c>
       <c r="D272" t="s">
+        <v>113</v>
+      </c>
+      <c r="E272" t="s">
         <v>453</v>
       </c>
-      <c r="E272" t="s">
+      <c r="F272" t="s">
         <v>454</v>
       </c>
-      <c r="F272" t="s">
+      <c r="G272" t="s">
         <v>455</v>
-      </c>
-      <c r="G272" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7797,16 +7797,16 @@
         <v>8</v>
       </c>
       <c r="D273" t="s">
+        <v>113</v>
+      </c>
+      <c r="E273" t="s">
         <v>453</v>
       </c>
-      <c r="E273" t="s">
+      <c r="F273" t="s">
         <v>454</v>
       </c>
-      <c r="F273" t="s">
+      <c r="G273" t="s">
         <v>455</v>
-      </c>
-      <c r="G273" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7817,16 +7817,16 @@
         <v>8</v>
       </c>
       <c r="D274" t="s">
+        <v>113</v>
+      </c>
+      <c r="E274" t="s">
         <v>453</v>
       </c>
-      <c r="E274" t="s">
+      <c r="F274" t="s">
         <v>454</v>
       </c>
-      <c r="F274" t="s">
+      <c r="G274" t="s">
         <v>455</v>
-      </c>
-      <c r="G274" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7837,16 +7837,16 @@
         <v>8</v>
       </c>
       <c r="D275" t="s">
+        <v>113</v>
+      </c>
+      <c r="E275" t="s">
         <v>453</v>
       </c>
-      <c r="E275" t="s">
+      <c r="F275" t="s">
         <v>454</v>
       </c>
-      <c r="F275" t="s">
+      <c r="G275" t="s">
         <v>455</v>
-      </c>
-      <c r="G275" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7857,16 +7857,16 @@
         <v>8</v>
       </c>
       <c r="D276" t="s">
+        <v>113</v>
+      </c>
+      <c r="E276" t="s">
         <v>453</v>
       </c>
-      <c r="E276" t="s">
+      <c r="F276" t="s">
         <v>454</v>
       </c>
-      <c r="F276" t="s">
+      <c r="G276" t="s">
         <v>455</v>
-      </c>
-      <c r="G276" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7877,16 +7877,16 @@
         <v>8</v>
       </c>
       <c r="D277" t="s">
+        <v>113</v>
+      </c>
+      <c r="E277" t="s">
         <v>453</v>
       </c>
-      <c r="E277" t="s">
+      <c r="F277" t="s">
         <v>454</v>
       </c>
-      <c r="F277" t="s">
+      <c r="G277" t="s">
         <v>455</v>
-      </c>
-      <c r="G277" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7897,16 +7897,16 @@
         <v>8</v>
       </c>
       <c r="D278" t="s">
+        <v>182</v>
+      </c>
+      <c r="E278" t="s">
         <v>463</v>
       </c>
-      <c r="E278" t="s">
+      <c r="F278" t="s">
         <v>203</v>
       </c>
-      <c r="F278" t="s">
+      <c r="G278" t="s">
         <v>204</v>
-      </c>
-      <c r="G278" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7917,16 +7917,16 @@
         <v>8</v>
       </c>
       <c r="D279" t="s">
+        <v>31</v>
+      </c>
+      <c r="E279" t="s">
         <v>463</v>
       </c>
-      <c r="E279" t="s">
+      <c r="F279" t="s">
         <v>53</v>
       </c>
-      <c r="F279" t="s">
+      <c r="G279" t="s">
         <v>54</v>
-      </c>
-      <c r="G279" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7937,10 +7937,10 @@
         <v>8</v>
       </c>
       <c r="D280" t="s">
+        <v>10</v>
+      </c>
+      <c r="E280" t="s">
         <v>463</v>
-      </c>
-      <c r="E280" t="s">
-        <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
@@ -7957,16 +7957,16 @@
         <v>8</v>
       </c>
       <c r="D281" t="s">
+        <v>113</v>
+      </c>
+      <c r="E281" t="s">
         <v>463</v>
       </c>
-      <c r="E281" t="s">
+      <c r="F281" t="s">
         <v>170</v>
       </c>
-      <c r="F281" t="s">
+      <c r="G281" t="s">
         <v>171</v>
-      </c>
-      <c r="G281" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7977,10 +7977,10 @@
         <v>8</v>
       </c>
       <c r="D282" t="s">
+        <v>124</v>
+      </c>
+      <c r="E282" t="s">
         <v>463</v>
-      </c>
-      <c r="E282" t="s">
-        <v>124</v>
       </c>
       <c r="F282" t="s">
         <v>125</v>
@@ -7997,16 +7997,16 @@
         <v>8</v>
       </c>
       <c r="D283" t="s">
+        <v>163</v>
+      </c>
+      <c r="E283" t="s">
         <v>469</v>
       </c>
-      <c r="E283" t="s">
+      <c r="F283" t="s">
         <v>365</v>
       </c>
-      <c r="F283" t="s">
+      <c r="G283" t="s">
         <v>399</v>
-      </c>
-      <c r="G283" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8017,10 +8017,10 @@
         <v>8</v>
       </c>
       <c r="D284" t="s">
+        <v>124</v>
+      </c>
+      <c r="E284" t="s">
         <v>471</v>
-      </c>
-      <c r="E284" t="s">
-        <v>124</v>
       </c>
       <c r="F284" t="s">
         <v>125</v>
@@ -8037,16 +8037,16 @@
         <v>8</v>
       </c>
       <c r="D285" t="s">
+        <v>113</v>
+      </c>
+      <c r="E285" t="s">
         <v>473</v>
       </c>
-      <c r="E285" t="s">
+      <c r="F285" t="s">
         <v>170</v>
       </c>
-      <c r="F285" t="s">
+      <c r="G285" t="s">
         <v>171</v>
-      </c>
-      <c r="G285" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8057,16 +8057,16 @@
         <v>8</v>
       </c>
       <c r="D286" t="s">
+        <v>182</v>
+      </c>
+      <c r="E286" t="s">
         <v>475</v>
       </c>
-      <c r="E286" t="s">
+      <c r="F286" t="s">
         <v>438</v>
       </c>
-      <c r="F286" t="s">
+      <c r="G286" t="s">
         <v>439</v>
-      </c>
-      <c r="G286" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8077,16 +8077,16 @@
         <v>8</v>
       </c>
       <c r="D287" t="s">
+        <v>182</v>
+      </c>
+      <c r="E287" t="s">
         <v>475</v>
       </c>
-      <c r="E287" t="s">
+      <c r="F287" t="s">
         <v>438</v>
       </c>
-      <c r="F287" t="s">
+      <c r="G287" t="s">
         <v>439</v>
-      </c>
-      <c r="G287" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8097,16 +8097,16 @@
         <v>8</v>
       </c>
       <c r="D288" t="s">
+        <v>10</v>
+      </c>
+      <c r="E288" t="s">
         <v>475</v>
       </c>
-      <c r="E288" t="s">
+      <c r="F288" t="s">
         <v>41</v>
       </c>
-      <c r="F288" t="s">
+      <c r="G288" t="s">
         <v>42</v>
-      </c>
-      <c r="G288" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8117,10 +8117,10 @@
         <v>8</v>
       </c>
       <c r="D289" t="s">
+        <v>31</v>
+      </c>
+      <c r="E289" t="s">
         <v>475</v>
-      </c>
-      <c r="E289" t="s">
-        <v>31</v>
       </c>
       <c r="F289" t="s">
         <v>32</v>
@@ -8137,10 +8137,10 @@
         <v>8</v>
       </c>
       <c r="D290" t="s">
+        <v>31</v>
+      </c>
+      <c r="E290" t="s">
         <v>475</v>
-      </c>
-      <c r="E290" t="s">
-        <v>31</v>
       </c>
       <c r="F290" t="s">
         <v>32</v>
@@ -8157,16 +8157,16 @@
         <v>8</v>
       </c>
       <c r="D291" t="s">
+        <v>113</v>
+      </c>
+      <c r="E291" t="s">
         <v>475</v>
       </c>
-      <c r="E291" t="s">
+      <c r="F291" t="s">
         <v>170</v>
       </c>
-      <c r="F291" t="s">
+      <c r="G291" t="s">
         <v>171</v>
-      </c>
-      <c r="G291" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8177,16 +8177,16 @@
         <v>8</v>
       </c>
       <c r="D292" t="s">
+        <v>113</v>
+      </c>
+      <c r="E292" t="s">
         <v>475</v>
       </c>
-      <c r="E292" t="s">
+      <c r="F292" t="s">
         <v>170</v>
       </c>
-      <c r="F292" t="s">
+      <c r="G292" t="s">
         <v>171</v>
-      </c>
-      <c r="G292" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8197,16 +8197,16 @@
         <v>8</v>
       </c>
       <c r="D293" t="s">
+        <v>113</v>
+      </c>
+      <c r="E293" t="s">
         <v>475</v>
       </c>
-      <c r="E293" t="s">
+      <c r="F293" t="s">
         <v>170</v>
       </c>
-      <c r="F293" t="s">
+      <c r="G293" t="s">
         <v>171</v>
-      </c>
-      <c r="G293" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8217,16 +8217,16 @@
         <v>8</v>
       </c>
       <c r="D294" t="s">
+        <v>113</v>
+      </c>
+      <c r="E294" t="s">
         <v>475</v>
       </c>
-      <c r="E294" t="s">
+      <c r="F294" t="s">
         <v>170</v>
       </c>
-      <c r="F294" t="s">
+      <c r="G294" t="s">
         <v>171</v>
-      </c>
-      <c r="G294" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8237,16 +8237,16 @@
         <v>8</v>
       </c>
       <c r="D295" t="s">
+        <v>113</v>
+      </c>
+      <c r="E295" t="s">
         <v>485</v>
       </c>
-      <c r="E295" t="s">
+      <c r="F295" t="s">
         <v>170</v>
       </c>
-      <c r="F295" t="s">
+      <c r="G295" t="s">
         <v>171</v>
-      </c>
-      <c r="G295" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8257,16 +8257,16 @@
         <v>8</v>
       </c>
       <c r="D296" t="s">
+        <v>113</v>
+      </c>
+      <c r="E296" t="s">
         <v>485</v>
       </c>
-      <c r="E296" t="s">
+      <c r="F296" t="s">
         <v>170</v>
       </c>
-      <c r="F296" t="s">
+      <c r="G296" t="s">
         <v>171</v>
-      </c>
-      <c r="G296" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,18 +22,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
@@ -43,18 +43,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>11220</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>11420</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
@@ -169,15 +169,15 @@
     <t>12110</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
@@ -286,27 +286,27 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
@@ -352,18 +352,18 @@
     <t>15110</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>15113</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
@@ -505,12 +505,12 @@
     <t>15142</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
@@ -622,12 +622,12 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
@@ -685,12 +685,12 @@
     <t>16061</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
@@ -823,15 +823,15 @@
     <t>23110</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
     <t>230</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
@@ -991,15 +991,15 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
     <t>310</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
@@ -1105,15 +1105,15 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
     <t>320</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
@@ -1279,12 +1279,12 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
@@ -1375,10 +1375,10 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
@@ -1863,7 +1863,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1872,7 +1872,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -1909,7 +1909,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1918,7 +1918,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
@@ -1935,13 +1935,13 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1955,10 +1955,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1981,13 +1981,13 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -2004,13 +2004,13 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -2027,13 +2027,13 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
@@ -2047,10 +2047,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -2070,16 +2070,16 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>36</v>
@@ -2093,16 +2093,16 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
         <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2116,16 +2116,16 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
         <v>42</v>
@@ -2142,13 +2142,13 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>46</v>
@@ -2162,16 +2162,16 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s">
         <v>49</v>
@@ -2188,13 +2188,13 @@
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2211,13 +2211,13 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2231,16 +2231,16 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G19" t="s">
         <v>58</v>
@@ -2254,16 +2254,16 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G20" t="s">
         <v>61</v>
@@ -2280,13 +2280,13 @@
         <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2300,13 +2300,13 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
         <v>64</v>
       </c>
-      <c r="D22" t="s">
-        <v>31</v>
-      </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
         <v>32</v>
@@ -2323,16 +2323,16 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" t="s">
         <v>64</v>
       </c>
-      <c r="D23" t="s">
-        <v>31</v>
-      </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
         <v>67</v>
@@ -2346,13 +2346,13 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
         <v>64</v>
       </c>
-      <c r="D24" t="s">
-        <v>31</v>
-      </c>
       <c r="E24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s">
         <v>32</v>
@@ -2369,13 +2369,13 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" t="s">
         <v>64</v>
       </c>
-      <c r="D25" t="s">
-        <v>31</v>
-      </c>
       <c r="E25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F25" t="s">
         <v>32</v>
@@ -2392,13 +2392,13 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
         <v>64</v>
       </c>
-      <c r="D26" t="s">
-        <v>31</v>
-      </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
         <v>32</v>
@@ -2415,13 +2415,13 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" t="s">
         <v>64</v>
       </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F27" t="s">
         <v>32</v>
@@ -2438,13 +2438,13 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s">
         <v>64</v>
       </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
       <c r="E28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F28" t="s">
         <v>32</v>
@@ -2461,13 +2461,13 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" t="s">
         <v>64</v>
       </c>
-      <c r="D29" t="s">
-        <v>31</v>
-      </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F29" t="s">
         <v>32</v>
@@ -2484,16 +2484,16 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" t="s">
         <v>64</v>
       </c>
-      <c r="D30" t="s">
-        <v>31</v>
-      </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G30" t="s">
         <v>54</v>
@@ -2507,13 +2507,13 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" t="s">
         <v>76</v>
       </c>
-      <c r="D31" t="s">
-        <v>31</v>
-      </c>
       <c r="E31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s">
         <v>32</v>
@@ -2530,13 +2530,13 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" t="s">
         <v>76</v>
       </c>
-      <c r="D32" t="s">
-        <v>31</v>
-      </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s">
         <v>32</v>
@@ -2553,13 +2553,13 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
         <v>76</v>
       </c>
-      <c r="D33" t="s">
-        <v>31</v>
-      </c>
       <c r="E33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
         <v>32</v>
@@ -2576,13 +2576,13 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
         <v>76</v>
       </c>
-      <c r="D34" t="s">
-        <v>31</v>
-      </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
         <v>32</v>
@@ -2599,13 +2599,13 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" t="s">
         <v>76</v>
       </c>
-      <c r="D35" t="s">
-        <v>31</v>
-      </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F35" t="s">
         <v>32</v>
@@ -2622,16 +2622,16 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" t="s">
         <v>76</v>
       </c>
-      <c r="D36" t="s">
-        <v>31</v>
-      </c>
       <c r="E36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G36" t="s">
         <v>58</v>
@@ -2644,7 +2644,7 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
-      <c r="D37" t="s">
+      <c r="C37" t="s">
         <v>31</v>
       </c>
       <c r="E37" t="s">
@@ -2664,7 +2664,7 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
-      <c r="D38" t="s">
+      <c r="C38" t="s">
         <v>31</v>
       </c>
       <c r="E38" t="s">
@@ -2684,7 +2684,7 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
-      <c r="D39" t="s">
+      <c r="C39" t="s">
         <v>31</v>
       </c>
       <c r="E39" t="s">
@@ -2704,7 +2704,7 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
-      <c r="D40" t="s">
+      <c r="C40" t="s">
         <v>31</v>
       </c>
       <c r="E40" t="s">
@@ -2724,14 +2724,14 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="D41" t="s">
-        <v>31</v>
+      <c r="C41" t="s">
+        <v>51</v>
       </c>
       <c r="E41" t="s">
         <v>83</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G41" t="s">
         <v>54</v>
@@ -2744,14 +2744,14 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
-      <c r="D42" t="s">
-        <v>31</v>
+      <c r="C42" t="s">
+        <v>57</v>
       </c>
       <c r="E42" t="s">
         <v>83</v>
       </c>
       <c r="F42" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G42" t="s">
         <v>58</v>
@@ -2764,7 +2764,7 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
-      <c r="D43" t="s">
+      <c r="C43" t="s">
         <v>90</v>
       </c>
       <c r="E43" t="s">
@@ -2784,7 +2784,7 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
-      <c r="D44" t="s">
+      <c r="C44" t="s">
         <v>95</v>
       </c>
       <c r="E44" t="s">
@@ -2804,7 +2804,7 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
-      <c r="D45" t="s">
+      <c r="C45" t="s">
         <v>90</v>
       </c>
       <c r="E45" t="s">
@@ -2824,7 +2824,7 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
-      <c r="D46" t="s">
+      <c r="C46" t="s">
         <v>90</v>
       </c>
       <c r="E46" t="s">
@@ -2844,14 +2844,14 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
-      <c r="D47" t="s">
-        <v>95</v>
+      <c r="C47" t="s">
+        <v>101</v>
       </c>
       <c r="E47" t="s">
         <v>91</v>
       </c>
       <c r="F47" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G47" t="s">
         <v>102</v>
@@ -2864,7 +2864,7 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
-      <c r="D48" t="s">
+      <c r="C48" t="s">
         <v>90</v>
       </c>
       <c r="E48" t="s">
@@ -2884,7 +2884,7 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
-      <c r="D49" t="s">
+      <c r="C49" t="s">
         <v>90</v>
       </c>
       <c r="E49" t="s">
@@ -2904,14 +2904,14 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
-      <c r="D50" t="s">
-        <v>95</v>
+      <c r="C50" t="s">
+        <v>101</v>
       </c>
       <c r="E50" t="s">
         <v>91</v>
       </c>
       <c r="F50" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G50" t="s">
         <v>102</v>
@@ -2924,7 +2924,7 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
-      <c r="D51" t="s">
+      <c r="C51" t="s">
         <v>90</v>
       </c>
       <c r="E51" t="s">
@@ -2944,14 +2944,14 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
-      <c r="D52" t="s">
-        <v>95</v>
+      <c r="C52" t="s">
+        <v>108</v>
       </c>
       <c r="E52" t="s">
         <v>91</v>
       </c>
       <c r="F52" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G52" t="s">
         <v>109</v>
@@ -2964,8 +2964,8 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="D53" t="s">
-        <v>10</v>
+      <c r="C53" t="s">
+        <v>9</v>
       </c>
       <c r="E53" t="s">
         <v>91</v>
@@ -3008,7 +3008,7 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
         <v>113</v>
@@ -3017,7 +3017,7 @@
         <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G55" t="s">
         <v>119</v>
@@ -3031,7 +3031,7 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
         <v>113</v>
@@ -3040,7 +3040,7 @@
         <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G56" t="s">
         <v>122</v>
@@ -3054,10 +3054,10 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E57" t="s">
         <v>114</v>
@@ -3077,7 +3077,7 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
         <v>113</v>
@@ -3086,7 +3086,7 @@
         <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G58" t="s">
         <v>119</v>
@@ -3100,7 +3100,7 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
         <v>113</v>
@@ -3109,7 +3109,7 @@
         <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G59" t="s">
         <v>119</v>
@@ -3123,7 +3123,7 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
         <v>113</v>
@@ -3132,7 +3132,7 @@
         <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G60" t="s">
         <v>119</v>
@@ -3146,7 +3146,7 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
         <v>113</v>
@@ -3155,7 +3155,7 @@
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
         <v>119</v>
@@ -3169,7 +3169,7 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
         <v>113</v>
@@ -3178,7 +3178,7 @@
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G62" t="s">
         <v>119</v>
@@ -3192,7 +3192,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
         <v>113</v>
@@ -3201,7 +3201,7 @@
         <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G63" t="s">
         <v>133</v>
@@ -3215,7 +3215,7 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D64" t="s">
         <v>113</v>
@@ -3224,7 +3224,7 @@
         <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G64" t="s">
         <v>133</v>
@@ -3238,7 +3238,7 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
         <v>113</v>
@@ -3247,7 +3247,7 @@
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="G65" t="s">
         <v>137</v>
@@ -3284,7 +3284,7 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
         <v>113</v>
@@ -3293,7 +3293,7 @@
         <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>119</v>
@@ -3353,7 +3353,7 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
         <v>113</v>
@@ -3362,7 +3362,7 @@
         <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G70" t="s">
         <v>122</v>
@@ -3376,7 +3376,7 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
         <v>113</v>
@@ -3385,7 +3385,7 @@
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G71" t="s">
         <v>122</v>
@@ -3422,16 +3422,16 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E73" t="s">
         <v>114</v>
       </c>
       <c r="F73" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G73" t="s">
         <v>149</v>
@@ -3445,16 +3445,16 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E74" t="s">
         <v>114</v>
       </c>
       <c r="F74" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="G74" t="s">
         <v>152</v>
@@ -3468,16 +3468,16 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E75" t="s">
         <v>114</v>
       </c>
       <c r="F75" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="G75" t="s">
         <v>155</v>
@@ -3491,16 +3491,16 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E76" t="s">
         <v>114</v>
       </c>
       <c r="F76" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G76" t="s">
         <v>149</v>
@@ -3514,16 +3514,16 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D77" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E77" t="s">
         <v>114</v>
       </c>
       <c r="F77" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G77" t="s">
         <v>149</v>
@@ -3537,16 +3537,16 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E78" t="s">
         <v>114</v>
       </c>
       <c r="F78" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="G78" t="s">
         <v>152</v>
@@ -3560,16 +3560,16 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E79" t="s">
         <v>114</v>
       </c>
       <c r="F79" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="G79" t="s">
         <v>161</v>
@@ -3583,10 +3583,10 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E80" t="s">
         <v>114</v>
@@ -3606,10 +3606,10 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E81" t="s">
         <v>114</v>
@@ -3629,10 +3629,10 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E82" t="s">
         <v>114</v>
@@ -3675,7 +3675,7 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
         <v>113</v>
@@ -3684,7 +3684,7 @@
         <v>114</v>
       </c>
       <c r="F84" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G84" t="s">
         <v>171</v>
@@ -3698,7 +3698,7 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D85" t="s">
         <v>113</v>
@@ -3707,7 +3707,7 @@
         <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G85" t="s">
         <v>173</v>
@@ -3721,16 +3721,16 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E86" t="s">
         <v>114</v>
       </c>
       <c r="F86" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G86" t="s">
         <v>176</v>
@@ -3744,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D87" t="s">
         <v>113</v>
@@ -3753,7 +3753,7 @@
         <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G87" t="s">
         <v>173</v>
@@ -3767,7 +3767,7 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
         <v>113</v>
@@ -3776,7 +3776,7 @@
         <v>114</v>
       </c>
       <c r="F88" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G88" t="s">
         <v>119</v>
@@ -3790,7 +3790,7 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D89" t="s">
         <v>113</v>
@@ -3799,7 +3799,7 @@
         <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G89" t="s">
         <v>119</v>
@@ -3813,10 +3813,10 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E90" t="s">
         <v>114</v>
@@ -3836,10 +3836,10 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="E91" t="s">
         <v>114</v>
@@ -3859,10 +3859,10 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E92" t="s">
         <v>114</v>
@@ -3882,7 +3882,7 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
         <v>113</v>
@@ -3891,7 +3891,7 @@
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G93" t="s">
         <v>122</v>
@@ -3905,10 +3905,10 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E94" t="s">
         <v>114</v>
@@ -3928,7 +3928,7 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
         <v>113</v>
@@ -3937,7 +3937,7 @@
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="G95" t="s">
         <v>190</v>
@@ -3951,10 +3951,10 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>124</v>
+      </c>
+      <c r="D96" t="s">
         <v>192</v>
-      </c>
-      <c r="D96" t="s">
-        <v>124</v>
       </c>
       <c r="E96" t="s">
         <v>114</v>
@@ -3974,10 +3974,10 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>124</v>
+      </c>
+      <c r="D97" t="s">
         <v>192</v>
-      </c>
-      <c r="D97" t="s">
-        <v>124</v>
       </c>
       <c r="E97" t="s">
         <v>114</v>
@@ -3997,10 +3997,10 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>195</v>
+      </c>
+      <c r="D98" t="s">
         <v>192</v>
-      </c>
-      <c r="D98" t="s">
-        <v>195</v>
       </c>
       <c r="E98" t="s">
         <v>114</v>
@@ -4020,10 +4020,10 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>124</v>
+      </c>
+      <c r="D99" t="s">
         <v>192</v>
-      </c>
-      <c r="D99" t="s">
-        <v>124</v>
       </c>
       <c r="E99" t="s">
         <v>114</v>
@@ -4043,16 +4043,16 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>154</v>
+      </c>
+      <c r="D100" t="s">
         <v>192</v>
-      </c>
-      <c r="D100" t="s">
-        <v>124</v>
       </c>
       <c r="E100" t="s">
         <v>114</v>
       </c>
       <c r="F100" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="G100" t="s">
         <v>155</v>
@@ -4066,10 +4066,10 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>124</v>
+      </c>
+      <c r="D101" t="s">
         <v>192</v>
-      </c>
-      <c r="D101" t="s">
-        <v>124</v>
       </c>
       <c r="E101" t="s">
         <v>114</v>
@@ -4088,14 +4088,14 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
-      <c r="D102" t="s">
-        <v>182</v>
+      <c r="C102" t="s">
+        <v>202</v>
       </c>
       <c r="E102" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G102" t="s">
         <v>204</v>
@@ -4108,14 +4108,14 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
-      <c r="D103" t="s">
-        <v>182</v>
+      <c r="C103" t="s">
+        <v>202</v>
       </c>
       <c r="E103" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F103" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G103" t="s">
         <v>204</v>
@@ -4128,14 +4128,14 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
-      <c r="D104" t="s">
-        <v>182</v>
+      <c r="C104" t="s">
+        <v>202</v>
       </c>
       <c r="E104" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F104" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G104" t="s">
         <v>204</v>
@@ -4148,14 +4148,14 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
-      <c r="D105" t="s">
-        <v>182</v>
+      <c r="C105" t="s">
+        <v>208</v>
       </c>
       <c r="E105" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F105" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="G105" t="s">
         <v>209</v>
@@ -4168,14 +4168,14 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
-      <c r="D106" t="s">
-        <v>182</v>
+      <c r="C106" t="s">
+        <v>202</v>
       </c>
       <c r="E106" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G106" t="s">
         <v>204</v>
@@ -4188,11 +4188,11 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
-      <c r="D107" t="s">
+      <c r="C107" t="s">
         <v>182</v>
       </c>
       <c r="E107" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F107" t="s">
         <v>183</v>
@@ -4208,14 +4208,14 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
-      <c r="D108" t="s">
-        <v>182</v>
+      <c r="C108" t="s">
+        <v>213</v>
       </c>
       <c r="E108" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F108" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="G108" t="s">
         <v>214</v>
@@ -4228,14 +4228,14 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
-      <c r="D109" t="s">
-        <v>90</v>
+      <c r="C109" t="s">
+        <v>216</v>
       </c>
       <c r="E109" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F109" t="s">
-        <v>216</v>
+        <v>92</v>
       </c>
       <c r="G109" t="s">
         <v>217</v>
@@ -4248,14 +4248,14 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
-      <c r="D110" t="s">
-        <v>90</v>
+      <c r="C110" t="s">
+        <v>219</v>
       </c>
       <c r="E110" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F110" t="s">
-        <v>219</v>
+        <v>92</v>
       </c>
       <c r="G110" t="s">
         <v>220</v>
@@ -4268,14 +4268,14 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
-      <c r="D111" t="s">
-        <v>182</v>
+      <c r="C111" t="s">
+        <v>202</v>
       </c>
       <c r="E111" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F111" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G111" t="s">
         <v>204</v>
@@ -4288,11 +4288,11 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
-      <c r="D112" t="s">
+      <c r="C112" t="s">
         <v>223</v>
       </c>
       <c r="E112" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F112" t="s">
         <v>224</v>
@@ -4308,11 +4308,11 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="D113" t="s">
-        <v>113</v>
+      <c r="C113" t="s">
+        <v>112</v>
       </c>
       <c r="E113" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F113" t="s">
         <v>115</v>
@@ -4328,14 +4328,14 @@
       <c r="B114" t="s">
         <v>8</v>
       </c>
-      <c r="D114" t="s">
-        <v>124</v>
+      <c r="C114" t="s">
+        <v>151</v>
       </c>
       <c r="E114" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F114" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="G114" t="s">
         <v>152</v>
@@ -4348,11 +4348,11 @@
       <c r="B115" t="s">
         <v>8</v>
       </c>
-      <c r="D115" t="s">
+      <c r="C115" t="s">
         <v>182</v>
       </c>
       <c r="E115" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F115" t="s">
         <v>183</v>
@@ -4368,14 +4368,14 @@
       <c r="B116" t="s">
         <v>8</v>
       </c>
-      <c r="D116" t="s">
-        <v>223</v>
+      <c r="C116" t="s">
+        <v>230</v>
       </c>
       <c r="E116" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F116" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="G116" t="s">
         <v>231</v>
@@ -4388,11 +4388,11 @@
       <c r="B117" t="s">
         <v>8</v>
       </c>
-      <c r="D117" t="s">
+      <c r="C117" t="s">
         <v>223</v>
       </c>
       <c r="E117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F117" t="s">
         <v>224</v>
@@ -4408,11 +4408,11 @@
       <c r="B118" t="s">
         <v>8</v>
       </c>
-      <c r="D118" t="s">
+      <c r="C118" t="s">
         <v>163</v>
       </c>
       <c r="E118" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F118" t="s">
         <v>164</v>
@@ -4428,11 +4428,11 @@
       <c r="B119" t="s">
         <v>8</v>
       </c>
-      <c r="D119" t="s">
+      <c r="C119" t="s">
         <v>182</v>
       </c>
       <c r="E119" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F119" t="s">
         <v>183</v>
@@ -4448,14 +4448,14 @@
       <c r="B120" t="s">
         <v>8</v>
       </c>
-      <c r="D120" t="s">
-        <v>113</v>
+      <c r="C120" t="s">
+        <v>170</v>
       </c>
       <c r="E120" t="s">
         <v>237</v>
       </c>
       <c r="F120" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G120" t="s">
         <v>171</v>
@@ -4468,8 +4468,8 @@
       <c r="B121" t="s">
         <v>8</v>
       </c>
-      <c r="D121" t="s">
-        <v>113</v>
+      <c r="C121" t="s">
+        <v>112</v>
       </c>
       <c r="E121" t="s">
         <v>237</v>
@@ -4488,14 +4488,14 @@
       <c r="B122" t="s">
         <v>8</v>
       </c>
-      <c r="D122" t="s">
-        <v>113</v>
+      <c r="C122" t="s">
+        <v>170</v>
       </c>
       <c r="E122" t="s">
         <v>237</v>
       </c>
       <c r="F122" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G122" t="s">
         <v>171</v>
@@ -4508,14 +4508,14 @@
       <c r="B123" t="s">
         <v>8</v>
       </c>
-      <c r="D123" t="s">
-        <v>113</v>
+      <c r="C123" t="s">
+        <v>170</v>
       </c>
       <c r="E123" t="s">
         <v>237</v>
       </c>
       <c r="F123" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G123" t="s">
         <v>171</v>
@@ -4528,14 +4528,14 @@
       <c r="B124" t="s">
         <v>8</v>
       </c>
-      <c r="D124" t="s">
-        <v>163</v>
+      <c r="C124" t="s">
+        <v>242</v>
       </c>
       <c r="E124" t="s">
         <v>237</v>
       </c>
       <c r="F124" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G124" t="s">
         <v>243</v>
@@ -4548,14 +4548,14 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="D125" t="s">
-        <v>163</v>
+      <c r="C125" t="s">
+        <v>242</v>
       </c>
       <c r="E125" t="s">
         <v>237</v>
       </c>
       <c r="F125" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G125" t="s">
         <v>243</v>
@@ -4568,14 +4568,14 @@
       <c r="B126" t="s">
         <v>8</v>
       </c>
-      <c r="D126" t="s">
-        <v>163</v>
+      <c r="C126" t="s">
+        <v>242</v>
       </c>
       <c r="E126" t="s">
         <v>237</v>
       </c>
       <c r="F126" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G126" t="s">
         <v>243</v>
@@ -4588,14 +4588,14 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
-      <c r="D127" t="s">
-        <v>163</v>
+      <c r="C127" t="s">
+        <v>242</v>
       </c>
       <c r="E127" t="s">
         <v>237</v>
       </c>
       <c r="F127" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G127" t="s">
         <v>243</v>
@@ -4608,14 +4608,14 @@
       <c r="B128" t="s">
         <v>8</v>
       </c>
-      <c r="D128" t="s">
-        <v>163</v>
+      <c r="C128" t="s">
+        <v>242</v>
       </c>
       <c r="E128" t="s">
         <v>237</v>
       </c>
       <c r="F128" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G128" t="s">
         <v>243</v>
@@ -4628,14 +4628,14 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
-      <c r="D129" t="s">
-        <v>163</v>
+      <c r="C129" t="s">
+        <v>242</v>
       </c>
       <c r="E129" t="s">
         <v>237</v>
       </c>
       <c r="F129" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G129" t="s">
         <v>249</v>
@@ -4648,14 +4648,14 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
-      <c r="D130" t="s">
-        <v>163</v>
+      <c r="C130" t="s">
+        <v>242</v>
       </c>
       <c r="E130" t="s">
         <v>237</v>
       </c>
       <c r="F130" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G130" t="s">
         <v>251</v>
@@ -4668,14 +4668,14 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
-      <c r="D131" t="s">
-        <v>163</v>
+      <c r="C131" t="s">
+        <v>242</v>
       </c>
       <c r="E131" t="s">
         <v>237</v>
       </c>
       <c r="F131" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G131" t="s">
         <v>253</v>
@@ -4688,14 +4688,14 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
-      <c r="D132" t="s">
-        <v>163</v>
+      <c r="C132" t="s">
+        <v>255</v>
       </c>
       <c r="E132" t="s">
         <v>237</v>
       </c>
       <c r="F132" t="s">
-        <v>255</v>
+        <v>164</v>
       </c>
       <c r="G132" t="s">
         <v>256</v>
@@ -4708,14 +4708,14 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
-      <c r="D133" t="s">
-        <v>113</v>
+      <c r="C133" t="s">
+        <v>189</v>
       </c>
       <c r="E133" t="s">
         <v>237</v>
       </c>
       <c r="F133" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="G133" t="s">
         <v>190</v>
@@ -4728,14 +4728,14 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
-      <c r="D134" t="s">
-        <v>163</v>
+      <c r="C134" t="s">
+        <v>175</v>
       </c>
       <c r="E134" t="s">
         <v>259</v>
       </c>
       <c r="F134" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G134" t="s">
         <v>176</v>
@@ -4748,14 +4748,14 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
-      <c r="D135" t="s">
-        <v>163</v>
+      <c r="C135" t="s">
+        <v>175</v>
       </c>
       <c r="E135" t="s">
         <v>259</v>
       </c>
       <c r="F135" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G135" t="s">
         <v>176</v>
@@ -4768,14 +4768,14 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
-      <c r="D136" t="s">
-        <v>163</v>
+      <c r="C136" t="s">
+        <v>175</v>
       </c>
       <c r="E136" t="s">
         <v>259</v>
       </c>
       <c r="F136" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G136" t="s">
         <v>176</v>
@@ -4788,14 +4788,14 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="D137" t="s">
-        <v>163</v>
+      <c r="C137" t="s">
+        <v>175</v>
       </c>
       <c r="E137" t="s">
         <v>259</v>
       </c>
       <c r="F137" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G137" t="s">
         <v>176</v>
@@ -4808,14 +4808,14 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
-      <c r="D138" t="s">
-        <v>163</v>
+      <c r="C138" t="s">
+        <v>175</v>
       </c>
       <c r="E138" t="s">
         <v>259</v>
       </c>
       <c r="F138" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G138" t="s">
         <v>176</v>
@@ -4828,14 +4828,14 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
-      <c r="D139" t="s">
-        <v>223</v>
+      <c r="C139" t="s">
+        <v>265</v>
       </c>
       <c r="E139" t="s">
         <v>259</v>
       </c>
       <c r="F139" t="s">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="G139" t="s">
         <v>266</v>
@@ -4848,14 +4848,14 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
-      <c r="D140" t="s">
-        <v>163</v>
+      <c r="C140" t="s">
+        <v>175</v>
       </c>
       <c r="E140" t="s">
         <v>259</v>
       </c>
       <c r="F140" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G140" t="s">
         <v>176</v>
@@ -4872,13 +4872,13 @@
         <v>269</v>
       </c>
       <c r="D141" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4895,13 +4895,13 @@
         <v>269</v>
       </c>
       <c r="D142" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4915,16 +4915,16 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E143" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F143" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="G143" t="s">
         <v>276</v>
@@ -4938,16 +4938,16 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E144" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F144" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="G144" t="s">
         <v>276</v>
@@ -4961,16 +4961,16 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E145" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F145" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="G145" t="s">
         <v>276</v>
@@ -4987,13 +4987,13 @@
         <v>269</v>
       </c>
       <c r="D146" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5007,16 +5007,16 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
+        <v>269</v>
+      </c>
+      <c r="D147" t="s">
         <v>281</v>
       </c>
-      <c r="D147" t="s">
-        <v>163</v>
-      </c>
       <c r="E147" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G147" t="s">
         <v>272</v>
@@ -5030,16 +5030,16 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
+        <v>269</v>
+      </c>
+      <c r="D148" t="s">
         <v>281</v>
       </c>
-      <c r="D148" t="s">
-        <v>163</v>
-      </c>
       <c r="E148" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G148" t="s">
         <v>272</v>
@@ -5053,16 +5053,16 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
+        <v>269</v>
+      </c>
+      <c r="D149" t="s">
         <v>281</v>
       </c>
-      <c r="D149" t="s">
-        <v>163</v>
-      </c>
       <c r="E149" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G149" t="s">
         <v>272</v>
@@ -5076,16 +5076,16 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
+        <v>269</v>
+      </c>
+      <c r="D150" t="s">
         <v>281</v>
       </c>
-      <c r="D150" t="s">
-        <v>163</v>
-      </c>
       <c r="E150" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G150" t="s">
         <v>272</v>
@@ -5099,16 +5099,16 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
+        <v>269</v>
+      </c>
+      <c r="D151" t="s">
         <v>281</v>
       </c>
-      <c r="D151" t="s">
-        <v>163</v>
-      </c>
       <c r="E151" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G151" t="s">
         <v>272</v>
@@ -5122,16 +5122,16 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
+        <v>269</v>
+      </c>
+      <c r="D152" t="s">
         <v>281</v>
       </c>
-      <c r="D152" t="s">
-        <v>163</v>
-      </c>
       <c r="E152" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G152" t="s">
         <v>272</v>
@@ -5145,16 +5145,16 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
+        <v>269</v>
+      </c>
+      <c r="D153" t="s">
         <v>281</v>
       </c>
-      <c r="D153" t="s">
-        <v>163</v>
-      </c>
       <c r="E153" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G153" t="s">
         <v>272</v>
@@ -5168,16 +5168,16 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
+        <v>269</v>
+      </c>
+      <c r="D154" t="s">
         <v>281</v>
       </c>
-      <c r="D154" t="s">
-        <v>163</v>
-      </c>
       <c r="E154" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G154" t="s">
         <v>272</v>
@@ -5191,16 +5191,16 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
+        <v>269</v>
+      </c>
+      <c r="D155" t="s">
         <v>281</v>
       </c>
-      <c r="D155" t="s">
-        <v>163</v>
-      </c>
       <c r="E155" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G155" t="s">
         <v>272</v>
@@ -5214,16 +5214,16 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
+        <v>269</v>
+      </c>
+      <c r="D156" t="s">
         <v>291</v>
       </c>
-      <c r="D156" t="s">
-        <v>163</v>
-      </c>
       <c r="E156" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G156" t="s">
         <v>272</v>
@@ -5237,16 +5237,16 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
+        <v>269</v>
+      </c>
+      <c r="D157" t="s">
         <v>291</v>
       </c>
-      <c r="D157" t="s">
-        <v>163</v>
-      </c>
       <c r="E157" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F157" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G157" t="s">
         <v>293</v>
@@ -5260,16 +5260,16 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
+        <v>269</v>
+      </c>
+      <c r="D158" t="s">
         <v>291</v>
       </c>
-      <c r="D158" t="s">
-        <v>163</v>
-      </c>
       <c r="E158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G158" t="s">
         <v>272</v>
@@ -5283,16 +5283,16 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
+        <v>269</v>
+      </c>
+      <c r="D159" t="s">
         <v>291</v>
       </c>
-      <c r="D159" t="s">
-        <v>163</v>
-      </c>
       <c r="E159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G159" t="s">
         <v>272</v>
@@ -5306,16 +5306,16 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
+        <v>269</v>
+      </c>
+      <c r="D160" t="s">
         <v>291</v>
       </c>
-      <c r="D160" t="s">
-        <v>163</v>
-      </c>
       <c r="E160" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G160" t="s">
         <v>272</v>
@@ -5329,16 +5329,16 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
+        <v>269</v>
+      </c>
+      <c r="D161" t="s">
         <v>291</v>
       </c>
-      <c r="D161" t="s">
-        <v>163</v>
-      </c>
       <c r="E161" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G161" t="s">
         <v>272</v>
@@ -5352,16 +5352,16 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
+        <v>269</v>
+      </c>
+      <c r="D162" t="s">
         <v>299</v>
       </c>
-      <c r="D162" t="s">
-        <v>163</v>
-      </c>
       <c r="E162" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G162" t="s">
         <v>272</v>
@@ -5375,16 +5375,16 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
+        <v>269</v>
+      </c>
+      <c r="D163" t="s">
         <v>301</v>
       </c>
-      <c r="D163" t="s">
-        <v>163</v>
-      </c>
       <c r="E163" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F163" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G163" t="s">
         <v>302</v>
@@ -5398,16 +5398,16 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
+        <v>269</v>
+      </c>
+      <c r="D164" t="s">
         <v>304</v>
       </c>
-      <c r="D164" t="s">
-        <v>163</v>
-      </c>
       <c r="E164" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G164" t="s">
         <v>272</v>
@@ -5421,16 +5421,16 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
+        <v>269</v>
+      </c>
+      <c r="D165" t="s">
         <v>304</v>
       </c>
-      <c r="D165" t="s">
-        <v>163</v>
-      </c>
       <c r="E165" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G165" t="s">
         <v>272</v>
@@ -5444,16 +5444,16 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
+        <v>269</v>
+      </c>
+      <c r="D166" t="s">
         <v>304</v>
       </c>
-      <c r="D166" t="s">
-        <v>163</v>
-      </c>
       <c r="E166" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G166" t="s">
         <v>272</v>
@@ -5467,16 +5467,16 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
+        <v>269</v>
+      </c>
+      <c r="D167" t="s">
         <v>304</v>
       </c>
-      <c r="D167" t="s">
-        <v>163</v>
-      </c>
       <c r="E167" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G167" t="s">
         <v>272</v>
@@ -5490,16 +5490,16 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
+        <v>269</v>
+      </c>
+      <c r="D168" t="s">
         <v>304</v>
       </c>
-      <c r="D168" t="s">
-        <v>163</v>
-      </c>
       <c r="E168" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F168" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G168" t="s">
         <v>309</v>
@@ -5513,16 +5513,16 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
+        <v>269</v>
+      </c>
+      <c r="D169" t="s">
         <v>304</v>
       </c>
-      <c r="D169" t="s">
-        <v>163</v>
-      </c>
       <c r="E169" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F169" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G169" t="s">
         <v>309</v>
@@ -5536,16 +5536,16 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
+        <v>269</v>
+      </c>
+      <c r="D170" t="s">
         <v>304</v>
       </c>
-      <c r="D170" t="s">
-        <v>163</v>
-      </c>
       <c r="E170" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G170" t="s">
         <v>272</v>
@@ -5558,7 +5558,7 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
-      <c r="D171" t="s">
+      <c r="C171" t="s">
         <v>163</v>
       </c>
       <c r="E171" t="s">
@@ -5578,14 +5578,14 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
-      <c r="D172" t="s">
-        <v>113</v>
+      <c r="C172" t="s">
+        <v>118</v>
       </c>
       <c r="E172" t="s">
         <v>313</v>
       </c>
       <c r="F172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G172" t="s">
         <v>119</v>
@@ -5598,7 +5598,7 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
-      <c r="D173" t="s">
+      <c r="C173" t="s">
         <v>163</v>
       </c>
       <c r="E173" t="s">
@@ -5618,7 +5618,7 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
-      <c r="D174" t="s">
+      <c r="C174" t="s">
         <v>163</v>
       </c>
       <c r="E174" t="s">
@@ -5638,7 +5638,7 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
-      <c r="D175" t="s">
+      <c r="C175" t="s">
         <v>163</v>
       </c>
       <c r="E175" t="s">
@@ -5658,7 +5658,7 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
-      <c r="D176" t="s">
+      <c r="C176" t="s">
         <v>163</v>
       </c>
       <c r="E176" t="s">
@@ -5678,7 +5678,7 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
-      <c r="D177" t="s">
+      <c r="C177" t="s">
         <v>163</v>
       </c>
       <c r="E177" t="s">
@@ -5698,7 +5698,7 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
-      <c r="D178" t="s">
+      <c r="C178" t="s">
         <v>163</v>
       </c>
       <c r="E178" t="s">
@@ -5718,7 +5718,7 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
-      <c r="D179" t="s">
+      <c r="C179" t="s">
         <v>163</v>
       </c>
       <c r="E179" t="s">
@@ -5738,7 +5738,7 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
-      <c r="D180" t="s">
+      <c r="C180" t="s">
         <v>163</v>
       </c>
       <c r="E180" t="s">
@@ -5762,13 +5762,13 @@
         <v>325</v>
       </c>
       <c r="D181" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5785,13 +5785,13 @@
         <v>325</v>
       </c>
       <c r="D182" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5808,13 +5808,13 @@
         <v>325</v>
       </c>
       <c r="D183" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5831,13 +5831,13 @@
         <v>325</v>
       </c>
       <c r="D184" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5854,13 +5854,13 @@
         <v>325</v>
       </c>
       <c r="D185" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5877,13 +5877,13 @@
         <v>325</v>
       </c>
       <c r="D186" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5900,13 +5900,13 @@
         <v>325</v>
       </c>
       <c r="D187" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5923,13 +5923,13 @@
         <v>325</v>
       </c>
       <c r="D188" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5946,13 +5946,13 @@
         <v>325</v>
       </c>
       <c r="D189" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5969,13 +5969,13 @@
         <v>325</v>
       </c>
       <c r="D190" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5992,13 +5992,13 @@
         <v>325</v>
       </c>
       <c r="D191" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6015,13 +6015,13 @@
         <v>325</v>
       </c>
       <c r="D192" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6035,16 +6035,16 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="D193" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E193" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F193" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="G193" t="s">
         <v>341</v>
@@ -6061,13 +6061,13 @@
         <v>325</v>
       </c>
       <c r="D194" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E194" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G194" t="s">
         <v>328</v>
@@ -6084,13 +6084,13 @@
         <v>325</v>
       </c>
       <c r="D195" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E195" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G195" t="s">
         <v>328</v>
@@ -6107,13 +6107,13 @@
         <v>325</v>
       </c>
       <c r="D196" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E196" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G196" t="s">
         <v>328</v>
@@ -6130,13 +6130,13 @@
         <v>325</v>
       </c>
       <c r="D197" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G197" t="s">
         <v>328</v>
@@ -6153,13 +6153,13 @@
         <v>325</v>
       </c>
       <c r="D198" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E198" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G198" t="s">
         <v>328</v>
@@ -6173,16 +6173,16 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
+        <v>325</v>
+      </c>
+      <c r="D199" t="s">
         <v>348</v>
       </c>
-      <c r="D199" t="s">
-        <v>163</v>
-      </c>
       <c r="E199" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F199" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G199" t="s">
         <v>349</v>
@@ -6196,16 +6196,16 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
+        <v>325</v>
+      </c>
+      <c r="D200" t="s">
         <v>348</v>
       </c>
-      <c r="D200" t="s">
-        <v>163</v>
-      </c>
       <c r="E200" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F200" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G200" t="s">
         <v>349</v>
@@ -6219,16 +6219,16 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
+        <v>325</v>
+      </c>
+      <c r="D201" t="s">
         <v>348</v>
       </c>
-      <c r="D201" t="s">
-        <v>163</v>
-      </c>
       <c r="E201" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F201" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G201" t="s">
         <v>349</v>
@@ -6242,16 +6242,16 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
+        <v>325</v>
+      </c>
+      <c r="D202" t="s">
         <v>348</v>
       </c>
-      <c r="D202" t="s">
-        <v>163</v>
-      </c>
       <c r="E202" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F202" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G202" t="s">
         <v>349</v>
@@ -6265,16 +6265,16 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>275</v>
+      </c>
+      <c r="D203" t="s">
         <v>348</v>
       </c>
-      <c r="D203" t="s">
-        <v>163</v>
-      </c>
       <c r="E203" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F203" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="G203" t="s">
         <v>341</v>
@@ -6288,16 +6288,16 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
+        <v>325</v>
+      </c>
+      <c r="D204" t="s">
         <v>348</v>
       </c>
-      <c r="D204" t="s">
-        <v>163</v>
-      </c>
       <c r="E204" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F204" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G204" t="s">
         <v>349</v>
@@ -6311,16 +6311,16 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
+        <v>325</v>
+      </c>
+      <c r="D205" t="s">
         <v>356</v>
       </c>
-      <c r="D205" t="s">
-        <v>163</v>
-      </c>
       <c r="E205" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F205" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G205" t="s">
         <v>357</v>
@@ -6334,16 +6334,16 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
+        <v>325</v>
+      </c>
+      <c r="D206" t="s">
         <v>356</v>
       </c>
-      <c r="D206" t="s">
-        <v>163</v>
-      </c>
       <c r="E206" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F206" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G206" t="s">
         <v>357</v>
@@ -6357,16 +6357,16 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
+        <v>325</v>
+      </c>
+      <c r="D207" t="s">
         <v>356</v>
       </c>
-      <c r="D207" t="s">
-        <v>163</v>
-      </c>
       <c r="E207" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F207" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G207" t="s">
         <v>357</v>
@@ -6380,16 +6380,16 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>275</v>
+      </c>
+      <c r="D208" t="s">
         <v>356</v>
       </c>
-      <c r="D208" t="s">
-        <v>163</v>
-      </c>
       <c r="E208" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F208" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="G208" t="s">
         <v>341</v>
@@ -6403,16 +6403,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
+        <v>325</v>
+      </c>
+      <c r="D209" t="s">
         <v>356</v>
       </c>
-      <c r="D209" t="s">
-        <v>163</v>
-      </c>
       <c r="E209" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F209" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G209" t="s">
         <v>357</v>
@@ -6429,13 +6429,13 @@
         <v>363</v>
       </c>
       <c r="D210" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E210" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G210" t="s">
         <v>366</v>
@@ -6452,13 +6452,13 @@
         <v>363</v>
       </c>
       <c r="D211" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E211" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G211" t="s">
         <v>366</v>
@@ -6475,13 +6475,13 @@
         <v>363</v>
       </c>
       <c r="D212" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E212" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G212" t="s">
         <v>366</v>
@@ -6498,13 +6498,13 @@
         <v>363</v>
       </c>
       <c r="D213" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E213" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G213" t="s">
         <v>366</v>
@@ -6521,13 +6521,13 @@
         <v>363</v>
       </c>
       <c r="D214" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E214" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G214" t="s">
         <v>366</v>
@@ -6541,16 +6541,16 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>363</v>
+        <v>325</v>
       </c>
       <c r="D215" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E215" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F215" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G215" t="s">
         <v>349</v>
@@ -6567,13 +6567,13 @@
         <v>363</v>
       </c>
       <c r="D216" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E216" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G216" t="s">
         <v>366</v>
@@ -6590,13 +6590,13 @@
         <v>363</v>
       </c>
       <c r="D217" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E217" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G217" t="s">
         <v>366</v>
@@ -6613,13 +6613,13 @@
         <v>363</v>
       </c>
       <c r="D218" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E218" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G218" t="s">
         <v>366</v>
@@ -6636,13 +6636,13 @@
         <v>363</v>
       </c>
       <c r="D219" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E219" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G219" t="s">
         <v>366</v>
@@ -6656,16 +6656,16 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>363</v>
+        <v>269</v>
       </c>
       <c r="D220" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E220" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F220" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G220" t="s">
         <v>309</v>
@@ -6682,13 +6682,13 @@
         <v>363</v>
       </c>
       <c r="D221" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E221" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G221" t="s">
         <v>366</v>
@@ -6705,13 +6705,13 @@
         <v>363</v>
       </c>
       <c r="D222" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E222" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G222" t="s">
         <v>366</v>
@@ -6728,13 +6728,13 @@
         <v>363</v>
       </c>
       <c r="D223" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E223" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G223" t="s">
         <v>366</v>
@@ -6751,13 +6751,13 @@
         <v>363</v>
       </c>
       <c r="D224" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E224" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G224" t="s">
         <v>366</v>
@@ -6774,13 +6774,13 @@
         <v>363</v>
       </c>
       <c r="D225" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E225" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G225" t="s">
         <v>366</v>
@@ -6794,16 +6794,16 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E226" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F226" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="G226" t="s">
         <v>276</v>
@@ -6820,13 +6820,13 @@
         <v>363</v>
       </c>
       <c r="D227" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E227" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G227" t="s">
         <v>366</v>
@@ -6840,13 +6840,13 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E228" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F228" t="s">
         <v>164</v>
@@ -6863,16 +6863,16 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
+        <v>363</v>
+      </c>
+      <c r="D229" t="s">
         <v>386</v>
       </c>
-      <c r="D229" t="s">
-        <v>163</v>
-      </c>
       <c r="E229" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F229" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G229" t="s">
         <v>387</v>
@@ -6886,16 +6886,16 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
+        <v>363</v>
+      </c>
+      <c r="D230" t="s">
         <v>386</v>
       </c>
-      <c r="D230" t="s">
-        <v>163</v>
-      </c>
       <c r="E230" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F230" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G230" t="s">
         <v>387</v>
@@ -6909,16 +6909,16 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
+        <v>269</v>
+      </c>
+      <c r="D231" t="s">
         <v>386</v>
       </c>
-      <c r="D231" t="s">
-        <v>163</v>
-      </c>
       <c r="E231" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F231" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G231" t="s">
         <v>293</v>
@@ -6932,16 +6932,16 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
+        <v>269</v>
+      </c>
+      <c r="D232" t="s">
         <v>386</v>
       </c>
-      <c r="D232" t="s">
-        <v>163</v>
-      </c>
       <c r="E232" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F232" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G232" t="s">
         <v>309</v>
@@ -6955,16 +6955,16 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
+        <v>363</v>
+      </c>
+      <c r="D233" t="s">
         <v>386</v>
       </c>
-      <c r="D233" t="s">
-        <v>163</v>
-      </c>
       <c r="E233" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F233" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G233" t="s">
         <v>387</v>
@@ -6978,16 +6978,16 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
+        <v>363</v>
+      </c>
+      <c r="D234" t="s">
         <v>386</v>
       </c>
-      <c r="D234" t="s">
-        <v>163</v>
-      </c>
       <c r="E234" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F234" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G234" t="s">
         <v>387</v>
@@ -7001,16 +7001,16 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
+        <v>363</v>
+      </c>
+      <c r="D235" t="s">
         <v>386</v>
       </c>
-      <c r="D235" t="s">
-        <v>163</v>
-      </c>
       <c r="E235" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F235" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G235" t="s">
         <v>387</v>
@@ -7024,16 +7024,16 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
+        <v>363</v>
+      </c>
+      <c r="D236" t="s">
         <v>386</v>
       </c>
-      <c r="D236" t="s">
-        <v>163</v>
-      </c>
       <c r="E236" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F236" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G236" t="s">
         <v>387</v>
@@ -7047,16 +7047,16 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
+        <v>363</v>
+      </c>
+      <c r="D237" t="s">
         <v>386</v>
       </c>
-      <c r="D237" t="s">
-        <v>163</v>
-      </c>
       <c r="E237" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F237" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G237" t="s">
         <v>387</v>
@@ -7070,16 +7070,16 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
+        <v>363</v>
+      </c>
+      <c r="D238" t="s">
         <v>386</v>
       </c>
-      <c r="D238" t="s">
-        <v>163</v>
-      </c>
       <c r="E238" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F238" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G238" t="s">
         <v>387</v>
@@ -7093,16 +7093,16 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
+        <v>363</v>
+      </c>
+      <c r="D239" t="s">
         <v>398</v>
       </c>
-      <c r="D239" t="s">
-        <v>163</v>
-      </c>
       <c r="E239" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F239" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G239" t="s">
         <v>399</v>
@@ -7116,10 +7116,10 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>163</v>
+      </c>
+      <c r="D240" t="s">
         <v>401</v>
-      </c>
-      <c r="D240" t="s">
-        <v>163</v>
       </c>
       <c r="E240" t="s">
         <v>402</v>
@@ -7139,10 +7139,10 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>163</v>
+      </c>
+      <c r="D241" t="s">
         <v>401</v>
-      </c>
-      <c r="D241" t="s">
-        <v>163</v>
       </c>
       <c r="E241" t="s">
         <v>402</v>
@@ -7162,10 +7162,10 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>163</v>
+      </c>
+      <c r="D242" t="s">
         <v>401</v>
-      </c>
-      <c r="D242" t="s">
-        <v>163</v>
       </c>
       <c r="E242" t="s">
         <v>402</v>
@@ -7185,10 +7185,10 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>163</v>
+      </c>
+      <c r="D243" t="s">
         <v>401</v>
-      </c>
-      <c r="D243" t="s">
-        <v>163</v>
       </c>
       <c r="E243" t="s">
         <v>402</v>
@@ -7208,10 +7208,10 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>163</v>
+      </c>
+      <c r="D244" t="s">
         <v>401</v>
-      </c>
-      <c r="D244" t="s">
-        <v>163</v>
       </c>
       <c r="E244" t="s">
         <v>402</v>
@@ -7231,10 +7231,10 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>163</v>
+      </c>
+      <c r="D245" t="s">
         <v>401</v>
-      </c>
-      <c r="D245" t="s">
-        <v>163</v>
       </c>
       <c r="E245" t="s">
         <v>402</v>
@@ -7254,16 +7254,16 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>255</v>
+      </c>
+      <c r="D246" t="s">
         <v>409</v>
-      </c>
-      <c r="D246" t="s">
-        <v>163</v>
       </c>
       <c r="E246" t="s">
         <v>402</v>
       </c>
       <c r="F246" t="s">
-        <v>255</v>
+        <v>164</v>
       </c>
       <c r="G246" t="s">
         <v>410</v>
@@ -7276,7 +7276,7 @@
       <c r="B247" t="s">
         <v>8</v>
       </c>
-      <c r="D247" t="s">
+      <c r="C247" t="s">
         <v>95</v>
       </c>
       <c r="E247" t="s">
@@ -7296,7 +7296,7 @@
       <c r="B248" t="s">
         <v>8</v>
       </c>
-      <c r="D248" t="s">
+      <c r="C248" t="s">
         <v>95</v>
       </c>
       <c r="E248" t="s">
@@ -7316,14 +7316,14 @@
       <c r="B249" t="s">
         <v>8</v>
       </c>
-      <c r="D249" t="s">
-        <v>95</v>
+      <c r="C249" t="s">
+        <v>415</v>
       </c>
       <c r="E249" t="s">
         <v>412</v>
       </c>
       <c r="F249" t="s">
-        <v>415</v>
+        <v>96</v>
       </c>
       <c r="G249" t="s">
         <v>416</v>
@@ -7336,7 +7336,7 @@
       <c r="B250" t="s">
         <v>8</v>
       </c>
-      <c r="D250" t="s">
+      <c r="C250" t="s">
         <v>95</v>
       </c>
       <c r="E250" t="s">
@@ -7356,7 +7356,7 @@
       <c r="B251" t="s">
         <v>8</v>
       </c>
-      <c r="D251" t="s">
+      <c r="C251" t="s">
         <v>95</v>
       </c>
       <c r="E251" t="s">
@@ -7376,7 +7376,7 @@
       <c r="B252" t="s">
         <v>8</v>
       </c>
-      <c r="D252" t="s">
+      <c r="C252" t="s">
         <v>95</v>
       </c>
       <c r="E252" t="s">
@@ -7396,14 +7396,14 @@
       <c r="B253" t="s">
         <v>8</v>
       </c>
-      <c r="D253" t="s">
-        <v>163</v>
+      <c r="C253" t="s">
+        <v>421</v>
       </c>
       <c r="E253" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F253" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="G253" t="s">
         <v>423</v>
@@ -7416,14 +7416,14 @@
       <c r="B254" t="s">
         <v>8</v>
       </c>
-      <c r="D254" t="s">
-        <v>90</v>
+      <c r="C254" t="s">
+        <v>219</v>
       </c>
       <c r="E254" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F254" t="s">
-        <v>219</v>
+        <v>92</v>
       </c>
       <c r="G254" t="s">
         <v>220</v>
@@ -7436,14 +7436,14 @@
       <c r="B255" t="s">
         <v>8</v>
       </c>
-      <c r="D255" t="s">
-        <v>90</v>
+      <c r="C255" t="s">
+        <v>426</v>
       </c>
       <c r="E255" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F255" t="s">
-        <v>426</v>
+        <v>92</v>
       </c>
       <c r="G255" t="s">
         <v>427</v>
@@ -7456,14 +7456,14 @@
       <c r="B256" t="s">
         <v>8</v>
       </c>
-      <c r="D256" t="s">
-        <v>90</v>
+      <c r="C256" t="s">
+        <v>426</v>
       </c>
       <c r="E256" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F256" t="s">
-        <v>426</v>
+        <v>92</v>
       </c>
       <c r="G256" t="s">
         <v>427</v>
@@ -7476,14 +7476,14 @@
       <c r="B257" t="s">
         <v>8</v>
       </c>
-      <c r="D257" t="s">
-        <v>90</v>
+      <c r="C257" t="s">
+        <v>426</v>
       </c>
       <c r="E257" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F257" t="s">
-        <v>426</v>
+        <v>92</v>
       </c>
       <c r="G257" t="s">
         <v>427</v>
@@ -7496,14 +7496,14 @@
       <c r="B258" t="s">
         <v>8</v>
       </c>
-      <c r="D258" t="s">
-        <v>163</v>
+      <c r="C258" t="s">
+        <v>325</v>
       </c>
       <c r="E258" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F258" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G258" t="s">
         <v>328</v>
@@ -7516,14 +7516,14 @@
       <c r="B259" t="s">
         <v>8</v>
       </c>
-      <c r="D259" t="s">
-        <v>90</v>
+      <c r="C259" t="s">
+        <v>426</v>
       </c>
       <c r="E259" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F259" t="s">
-        <v>426</v>
+        <v>92</v>
       </c>
       <c r="G259" t="s">
         <v>427</v>
@@ -7536,11 +7536,11 @@
       <c r="B260" t="s">
         <v>8</v>
       </c>
-      <c r="D260" t="s">
+      <c r="C260" t="s">
         <v>163</v>
       </c>
       <c r="E260" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F260" t="s">
         <v>164</v>
@@ -7556,14 +7556,14 @@
       <c r="B261" t="s">
         <v>8</v>
       </c>
-      <c r="D261" t="s">
-        <v>195</v>
+      <c r="C261" t="s">
+        <v>434</v>
       </c>
       <c r="E261" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F261" t="s">
-        <v>434</v>
+        <v>196</v>
       </c>
       <c r="G261" t="s">
         <v>435</v>
@@ -7576,11 +7576,11 @@
       <c r="B262" t="s">
         <v>8</v>
       </c>
-      <c r="D262" t="s">
+      <c r="C262" t="s">
         <v>163</v>
       </c>
       <c r="E262" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F262" t="s">
         <v>164</v>
@@ -7596,14 +7596,14 @@
       <c r="B263" t="s">
         <v>8</v>
       </c>
-      <c r="D263" t="s">
-        <v>182</v>
+      <c r="C263" t="s">
+        <v>438</v>
       </c>
       <c r="E263" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F263" t="s">
-        <v>438</v>
+        <v>183</v>
       </c>
       <c r="G263" t="s">
         <v>439</v>
@@ -7616,11 +7616,11 @@
       <c r="B264" t="s">
         <v>8</v>
       </c>
-      <c r="D264" t="s">
+      <c r="C264" t="s">
         <v>31</v>
       </c>
       <c r="E264" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F264" t="s">
         <v>32</v>
@@ -7636,11 +7636,11 @@
       <c r="B265" t="s">
         <v>8</v>
       </c>
-      <c r="D265" t="s">
-        <v>10</v>
+      <c r="C265" t="s">
+        <v>9</v>
       </c>
       <c r="E265" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
@@ -7656,14 +7656,14 @@
       <c r="B266" t="s">
         <v>8</v>
       </c>
-      <c r="D266" t="s">
-        <v>113</v>
+      <c r="C266" t="s">
+        <v>443</v>
       </c>
       <c r="E266" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F266" t="s">
-        <v>443</v>
+        <v>115</v>
       </c>
       <c r="G266" t="s">
         <v>444</v>
@@ -7676,14 +7676,14 @@
       <c r="B267" t="s">
         <v>8</v>
       </c>
-      <c r="D267" t="s">
-        <v>113</v>
+      <c r="C267" t="s">
+        <v>118</v>
       </c>
       <c r="E267" t="s">
         <v>446</v>
       </c>
       <c r="F267" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G267" t="s">
         <v>119</v>
@@ -7696,14 +7696,14 @@
       <c r="B268" t="s">
         <v>8</v>
       </c>
-      <c r="D268" t="s">
-        <v>182</v>
+      <c r="C268" t="s">
+        <v>202</v>
       </c>
       <c r="E268" t="s">
         <v>448</v>
       </c>
       <c r="F268" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G268" t="s">
         <v>204</v>
@@ -7716,14 +7716,14 @@
       <c r="B269" t="s">
         <v>8</v>
       </c>
-      <c r="D269" t="s">
-        <v>113</v>
+      <c r="C269" t="s">
+        <v>118</v>
       </c>
       <c r="E269" t="s">
         <v>450</v>
       </c>
       <c r="F269" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G269" t="s">
         <v>119</v>
@@ -7736,14 +7736,14 @@
       <c r="B270" t="s">
         <v>8</v>
       </c>
-      <c r="D270" t="s">
-        <v>113</v>
+      <c r="C270" t="s">
+        <v>118</v>
       </c>
       <c r="E270" t="s">
         <v>450</v>
       </c>
       <c r="F270" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G270" t="s">
         <v>119</v>
@@ -7756,14 +7756,14 @@
       <c r="B271" t="s">
         <v>8</v>
       </c>
-      <c r="D271" t="s">
-        <v>113</v>
+      <c r="C271" t="s">
+        <v>453</v>
       </c>
       <c r="E271" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F271" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G271" t="s">
         <v>455</v>
@@ -7776,14 +7776,14 @@
       <c r="B272" t="s">
         <v>8</v>
       </c>
-      <c r="D272" t="s">
-        <v>113</v>
+      <c r="C272" t="s">
+        <v>453</v>
       </c>
       <c r="E272" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F272" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G272" t="s">
         <v>455</v>
@@ -7796,14 +7796,14 @@
       <c r="B273" t="s">
         <v>8</v>
       </c>
-      <c r="D273" t="s">
-        <v>113</v>
+      <c r="C273" t="s">
+        <v>453</v>
       </c>
       <c r="E273" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F273" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G273" t="s">
         <v>455</v>
@@ -7816,14 +7816,14 @@
       <c r="B274" t="s">
         <v>8</v>
       </c>
-      <c r="D274" t="s">
-        <v>113</v>
+      <c r="C274" t="s">
+        <v>453</v>
       </c>
       <c r="E274" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F274" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G274" t="s">
         <v>455</v>
@@ -7836,14 +7836,14 @@
       <c r="B275" t="s">
         <v>8</v>
       </c>
-      <c r="D275" t="s">
-        <v>113</v>
+      <c r="C275" t="s">
+        <v>453</v>
       </c>
       <c r="E275" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F275" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G275" t="s">
         <v>455</v>
@@ -7856,14 +7856,14 @@
       <c r="B276" t="s">
         <v>8</v>
       </c>
-      <c r="D276" t="s">
-        <v>113</v>
+      <c r="C276" t="s">
+        <v>453</v>
       </c>
       <c r="E276" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F276" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G276" t="s">
         <v>455</v>
@@ -7876,14 +7876,14 @@
       <c r="B277" t="s">
         <v>8</v>
       </c>
-      <c r="D277" t="s">
-        <v>113</v>
+      <c r="C277" t="s">
+        <v>453</v>
       </c>
       <c r="E277" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F277" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G277" t="s">
         <v>455</v>
@@ -7896,14 +7896,14 @@
       <c r="B278" t="s">
         <v>8</v>
       </c>
-      <c r="D278" t="s">
-        <v>182</v>
+      <c r="C278" t="s">
+        <v>202</v>
       </c>
       <c r="E278" t="s">
         <v>463</v>
       </c>
       <c r="F278" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G278" t="s">
         <v>204</v>
@@ -7916,14 +7916,14 @@
       <c r="B279" t="s">
         <v>8</v>
       </c>
-      <c r="D279" t="s">
-        <v>31</v>
+      <c r="C279" t="s">
+        <v>51</v>
       </c>
       <c r="E279" t="s">
         <v>463</v>
       </c>
       <c r="F279" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G279" t="s">
         <v>54</v>
@@ -7936,8 +7936,8 @@
       <c r="B280" t="s">
         <v>8</v>
       </c>
-      <c r="D280" t="s">
-        <v>10</v>
+      <c r="C280" t="s">
+        <v>9</v>
       </c>
       <c r="E280" t="s">
         <v>463</v>
@@ -7956,14 +7956,14 @@
       <c r="B281" t="s">
         <v>8</v>
       </c>
-      <c r="D281" t="s">
-        <v>113</v>
+      <c r="C281" t="s">
+        <v>170</v>
       </c>
       <c r="E281" t="s">
         <v>463</v>
       </c>
       <c r="F281" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G281" t="s">
         <v>171</v>
@@ -7976,7 +7976,7 @@
       <c r="B282" t="s">
         <v>8</v>
       </c>
-      <c r="D282" t="s">
+      <c r="C282" t="s">
         <v>124</v>
       </c>
       <c r="E282" t="s">
@@ -7996,14 +7996,14 @@
       <c r="B283" t="s">
         <v>8</v>
       </c>
-      <c r="D283" t="s">
-        <v>163</v>
+      <c r="C283" t="s">
+        <v>363</v>
       </c>
       <c r="E283" t="s">
         <v>469</v>
       </c>
       <c r="F283" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G283" t="s">
         <v>399</v>
@@ -8016,7 +8016,7 @@
       <c r="B284" t="s">
         <v>8</v>
       </c>
-      <c r="D284" t="s">
+      <c r="C284" t="s">
         <v>124</v>
       </c>
       <c r="E284" t="s">
@@ -8036,14 +8036,14 @@
       <c r="B285" t="s">
         <v>8</v>
       </c>
-      <c r="D285" t="s">
-        <v>113</v>
+      <c r="C285" t="s">
+        <v>170</v>
       </c>
       <c r="E285" t="s">
         <v>473</v>
       </c>
       <c r="F285" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G285" t="s">
         <v>171</v>
@@ -8056,14 +8056,14 @@
       <c r="B286" t="s">
         <v>8</v>
       </c>
-      <c r="D286" t="s">
-        <v>182</v>
+      <c r="C286" t="s">
+        <v>438</v>
       </c>
       <c r="E286" t="s">
         <v>475</v>
       </c>
       <c r="F286" t="s">
-        <v>438</v>
+        <v>183</v>
       </c>
       <c r="G286" t="s">
         <v>439</v>
@@ -8076,14 +8076,14 @@
       <c r="B287" t="s">
         <v>8</v>
       </c>
-      <c r="D287" t="s">
-        <v>182</v>
+      <c r="C287" t="s">
+        <v>438</v>
       </c>
       <c r="E287" t="s">
         <v>475</v>
       </c>
       <c r="F287" t="s">
-        <v>438</v>
+        <v>183</v>
       </c>
       <c r="G287" t="s">
         <v>439</v>
@@ -8096,14 +8096,14 @@
       <c r="B288" t="s">
         <v>8</v>
       </c>
-      <c r="D288" t="s">
-        <v>10</v>
+      <c r="C288" t="s">
+        <v>41</v>
       </c>
       <c r="E288" t="s">
         <v>475</v>
       </c>
       <c r="F288" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G288" t="s">
         <v>42</v>
@@ -8116,7 +8116,7 @@
       <c r="B289" t="s">
         <v>8</v>
       </c>
-      <c r="D289" t="s">
+      <c r="C289" t="s">
         <v>31</v>
       </c>
       <c r="E289" t="s">
@@ -8136,7 +8136,7 @@
       <c r="B290" t="s">
         <v>8</v>
       </c>
-      <c r="D290" t="s">
+      <c r="C290" t="s">
         <v>31</v>
       </c>
       <c r="E290" t="s">
@@ -8156,14 +8156,14 @@
       <c r="B291" t="s">
         <v>8</v>
       </c>
-      <c r="D291" t="s">
-        <v>113</v>
+      <c r="C291" t="s">
+        <v>170</v>
       </c>
       <c r="E291" t="s">
         <v>475</v>
       </c>
       <c r="F291" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G291" t="s">
         <v>171</v>
@@ -8176,14 +8176,14 @@
       <c r="B292" t="s">
         <v>8</v>
       </c>
-      <c r="D292" t="s">
-        <v>113</v>
+      <c r="C292" t="s">
+        <v>170</v>
       </c>
       <c r="E292" t="s">
         <v>475</v>
       </c>
       <c r="F292" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G292" t="s">
         <v>171</v>
@@ -8196,14 +8196,14 @@
       <c r="B293" t="s">
         <v>8</v>
       </c>
-      <c r="D293" t="s">
-        <v>113</v>
+      <c r="C293" t="s">
+        <v>170</v>
       </c>
       <c r="E293" t="s">
         <v>475</v>
       </c>
       <c r="F293" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G293" t="s">
         <v>171</v>
@@ -8216,14 +8216,14 @@
       <c r="B294" t="s">
         <v>8</v>
       </c>
-      <c r="D294" t="s">
-        <v>113</v>
+      <c r="C294" t="s">
+        <v>170</v>
       </c>
       <c r="E294" t="s">
         <v>475</v>
       </c>
       <c r="F294" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G294" t="s">
         <v>171</v>
@@ -8236,14 +8236,14 @@
       <c r="B295" t="s">
         <v>8</v>
       </c>
-      <c r="D295" t="s">
-        <v>113</v>
+      <c r="C295" t="s">
+        <v>170</v>
       </c>
       <c r="E295" t="s">
         <v>485</v>
       </c>
       <c r="F295" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G295" t="s">
         <v>171</v>
@@ -8256,14 +8256,14 @@
       <c r="B296" t="s">
         <v>8</v>
       </c>
-      <c r="D296" t="s">
-        <v>113</v>
+      <c r="C296" t="s">
+        <v>170</v>
       </c>
       <c r="E296" t="s">
         <v>485</v>
       </c>
       <c r="F296" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G296" t="s">
         <v>171</v>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,42 +22,42 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>11220</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>07.4 - Public health services</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>11420</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
@@ -169,12 +169,12 @@
     <t>12110</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -292,24 +292,24 @@
     <t>140</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -352,21 +352,21 @@
     <t>15110</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -508,12 +508,12 @@
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -565,12 +565,12 @@
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>08.2 - Cultural services</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -823,12 +823,12 @@
     <t>23110</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>230</t>
   </si>
   <si>
@@ -991,12 +991,12 @@
     <t>31110</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>310</t>
   </si>
   <si>
@@ -1105,10 +1105,10 @@
     <t>32110</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>320</t>
@@ -1863,19 +1863,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1909,19 +1909,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1941,10 +1941,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1955,10 +1955,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1987,10 +1987,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2010,10 +2010,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2033,10 +2033,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2047,10 +2047,10 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
         <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -2070,19 +2070,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" t="s">
         <v>35</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" t="s">
-        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2116,19 +2116,19 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>38</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2148,10 +2148,10 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2162,19 +2162,19 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
         <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>45</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2194,10 +2194,10 @@
         <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G17" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2217,10 +2217,10 @@
         <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G18" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
         <v>57</v>
-      </c>
-      <c r="D19" t="s">
-        <v>52</v>
       </c>
       <c r="E19" t="s">
         <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2254,19 +2254,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
         <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>52</v>
       </c>
       <c r="E20" t="s">
         <v>53</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2286,10 +2286,10 @@
         <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G21" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2300,10 +2300,10 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
         <v>31</v>
-      </c>
-      <c r="D22" t="s">
-        <v>64</v>
       </c>
       <c r="E22" t="s">
         <v>53</v>
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
         <v>66</v>
-      </c>
-      <c r="D23" t="s">
-        <v>64</v>
       </c>
       <c r="E23" t="s">
         <v>53</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2346,10 +2346,10 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
         <v>31</v>
-      </c>
-      <c r="D24" t="s">
-        <v>64</v>
       </c>
       <c r="E24" t="s">
         <v>53</v>
@@ -2369,10 +2369,10 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
         <v>31</v>
-      </c>
-      <c r="D25" t="s">
-        <v>64</v>
       </c>
       <c r="E25" t="s">
         <v>53</v>
@@ -2392,10 +2392,10 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" t="s">
         <v>31</v>
-      </c>
-      <c r="D26" t="s">
-        <v>64</v>
       </c>
       <c r="E26" t="s">
         <v>53</v>
@@ -2415,10 +2415,10 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
         <v>31</v>
-      </c>
-      <c r="D27" t="s">
-        <v>64</v>
       </c>
       <c r="E27" t="s">
         <v>53</v>
@@ -2438,10 +2438,10 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
         <v>31</v>
-      </c>
-      <c r="D28" t="s">
-        <v>64</v>
       </c>
       <c r="E28" t="s">
         <v>53</v>
@@ -2461,10 +2461,10 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
         <v>31</v>
-      </c>
-      <c r="D29" t="s">
-        <v>64</v>
       </c>
       <c r="E29" t="s">
         <v>53</v>
@@ -2484,19 +2484,19 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
         <v>53</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G30" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2507,10 +2507,10 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" t="s">
         <v>31</v>
-      </c>
-      <c r="D31" t="s">
-        <v>76</v>
       </c>
       <c r="E31" t="s">
         <v>53</v>
@@ -2530,10 +2530,10 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" t="s">
         <v>31</v>
-      </c>
-      <c r="D32" t="s">
-        <v>76</v>
       </c>
       <c r="E32" t="s">
         <v>53</v>
@@ -2553,10 +2553,10 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" t="s">
         <v>31</v>
-      </c>
-      <c r="D33" t="s">
-        <v>76</v>
       </c>
       <c r="E33" t="s">
         <v>53</v>
@@ -2576,10 +2576,10 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" t="s">
         <v>31</v>
-      </c>
-      <c r="D34" t="s">
-        <v>76</v>
       </c>
       <c r="E34" t="s">
         <v>53</v>
@@ -2599,10 +2599,10 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
         <v>31</v>
-      </c>
-      <c r="D35" t="s">
-        <v>76</v>
       </c>
       <c r="E35" t="s">
         <v>53</v>
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" t="s">
         <v>57</v>
-      </c>
-      <c r="D36" t="s">
-        <v>76</v>
       </c>
       <c r="E36" t="s">
         <v>53</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2644,7 +2644,7 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>31</v>
       </c>
       <c r="E37" t="s">
@@ -2664,7 +2664,7 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>31</v>
       </c>
       <c r="E38" t="s">
@@ -2684,7 +2684,7 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>31</v>
       </c>
       <c r="E39" t="s">
@@ -2704,7 +2704,7 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>31</v>
       </c>
       <c r="E40" t="s">
@@ -2724,17 +2724,17 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="C41" t="s">
-        <v>51</v>
+      <c r="D41" t="s">
+        <v>52</v>
       </c>
       <c r="E41" t="s">
         <v>83</v>
       </c>
       <c r="F41" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G41" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2744,17 +2744,17 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>57</v>
       </c>
       <c r="E42" t="s">
         <v>83</v>
       </c>
       <c r="F42" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G42" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2764,7 +2764,7 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>90</v>
       </c>
       <c r="E43" t="s">
@@ -2784,7 +2784,7 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>95</v>
       </c>
       <c r="E44" t="s">
@@ -2804,7 +2804,7 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>90</v>
       </c>
       <c r="E45" t="s">
@@ -2824,7 +2824,7 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>90</v>
       </c>
       <c r="E46" t="s">
@@ -2844,17 +2844,17 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>101</v>
       </c>
       <c r="E47" t="s">
         <v>91</v>
       </c>
       <c r="F47" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G47" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2864,7 +2864,7 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>90</v>
       </c>
       <c r="E48" t="s">
@@ -2884,7 +2884,7 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>90</v>
       </c>
       <c r="E49" t="s">
@@ -2904,17 +2904,17 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>101</v>
       </c>
       <c r="E50" t="s">
         <v>91</v>
       </c>
       <c r="F50" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G50" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2924,7 +2924,7 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>90</v>
       </c>
       <c r="E51" t="s">
@@ -2944,17 +2944,17 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>108</v>
       </c>
       <c r="E52" t="s">
         <v>91</v>
       </c>
       <c r="F52" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G52" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2964,8 +2964,8 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C53" t="s">
-        <v>9</v>
+      <c r="D53" t="s">
+        <v>10</v>
       </c>
       <c r="E53" t="s">
         <v>91</v>
@@ -3008,19 +3008,19 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
         <v>118</v>
-      </c>
-      <c r="D55" t="s">
-        <v>113</v>
       </c>
       <c r="E55" t="s">
         <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G55" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3031,19 +3031,19 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="s">
         <v>121</v>
-      </c>
-      <c r="D56" t="s">
-        <v>113</v>
       </c>
       <c r="E56" t="s">
         <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G56" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3054,10 +3054,10 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
         <v>124</v>
-      </c>
-      <c r="D57" t="s">
-        <v>113</v>
       </c>
       <c r="E57" t="s">
         <v>114</v>
@@ -3077,19 +3077,19 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" t="s">
         <v>118</v>
-      </c>
-      <c r="D58" t="s">
-        <v>113</v>
       </c>
       <c r="E58" t="s">
         <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3100,19 +3100,19 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
+        <v>112</v>
+      </c>
+      <c r="D59" t="s">
         <v>118</v>
-      </c>
-      <c r="D59" t="s">
-        <v>113</v>
       </c>
       <c r="E59" t="s">
         <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G59" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3123,19 +3123,19 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" t="s">
         <v>118</v>
-      </c>
-      <c r="D60" t="s">
-        <v>113</v>
       </c>
       <c r="E60" t="s">
         <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3146,19 +3146,19 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
+        <v>112</v>
+      </c>
+      <c r="D61" t="s">
         <v>118</v>
-      </c>
-      <c r="D61" t="s">
-        <v>113</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G61" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3169,19 +3169,19 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" t="s">
         <v>118</v>
-      </c>
-      <c r="D62" t="s">
-        <v>113</v>
       </c>
       <c r="E62" t="s">
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G62" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3192,19 +3192,19 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
+        <v>112</v>
+      </c>
+      <c r="D63" t="s">
         <v>118</v>
-      </c>
-      <c r="D63" t="s">
-        <v>113</v>
       </c>
       <c r="E63" t="s">
         <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G63" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3215,19 +3215,19 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
+        <v>112</v>
+      </c>
+      <c r="D64" t="s">
         <v>118</v>
-      </c>
-      <c r="D64" t="s">
-        <v>113</v>
       </c>
       <c r="E64" t="s">
         <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G64" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3238,19 +3238,19 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" t="s">
         <v>136</v>
-      </c>
-      <c r="D65" t="s">
-        <v>113</v>
       </c>
       <c r="E65" t="s">
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3284,19 +3284,19 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" t="s">
         <v>118</v>
-      </c>
-      <c r="D67" t="s">
-        <v>113</v>
       </c>
       <c r="E67" t="s">
         <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G67" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3316,10 +3316,10 @@
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="G68" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3339,10 +3339,10 @@
         <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G69" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3353,19 +3353,19 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" t="s">
         <v>121</v>
-      </c>
-      <c r="D70" t="s">
-        <v>113</v>
       </c>
       <c r="E70" t="s">
         <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3376,19 +3376,19 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" t="s">
         <v>121</v>
-      </c>
-      <c r="D71" t="s">
-        <v>113</v>
       </c>
       <c r="E71" t="s">
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G71" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3422,19 +3422,19 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" t="s">
         <v>148</v>
-      </c>
-      <c r="D73" t="s">
-        <v>113</v>
       </c>
       <c r="E73" t="s">
         <v>114</v>
       </c>
       <c r="F73" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G73" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3445,19 +3445,19 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" t="s">
         <v>151</v>
-      </c>
-      <c r="D74" t="s">
-        <v>113</v>
       </c>
       <c r="E74" t="s">
         <v>114</v>
       </c>
       <c r="F74" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3468,19 +3468,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" t="s">
         <v>154</v>
-      </c>
-      <c r="D75" t="s">
-        <v>113</v>
       </c>
       <c r="E75" t="s">
         <v>114</v>
       </c>
       <c r="F75" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="G75" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3491,19 +3491,19 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" t="s">
         <v>148</v>
-      </c>
-      <c r="D76" t="s">
-        <v>113</v>
       </c>
       <c r="E76" t="s">
         <v>114</v>
       </c>
       <c r="F76" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G76" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3514,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" t="s">
         <v>148</v>
-      </c>
-      <c r="D77" t="s">
-        <v>113</v>
       </c>
       <c r="E77" t="s">
         <v>114</v>
       </c>
       <c r="F77" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G77" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3537,19 +3537,19 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" t="s">
         <v>151</v>
-      </c>
-      <c r="D78" t="s">
-        <v>113</v>
       </c>
       <c r="E78" t="s">
         <v>114</v>
       </c>
       <c r="F78" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G78" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3560,19 +3560,19 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" t="s">
         <v>160</v>
-      </c>
-      <c r="D79" t="s">
-        <v>113</v>
       </c>
       <c r="E79" t="s">
         <v>114</v>
       </c>
       <c r="F79" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="G79" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3583,10 +3583,10 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
+        <v>112</v>
+      </c>
+      <c r="D80" t="s">
         <v>163</v>
-      </c>
-      <c r="D80" t="s">
-        <v>113</v>
       </c>
       <c r="E80" t="s">
         <v>114</v>
@@ -3606,10 +3606,10 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
+        <v>112</v>
+      </c>
+      <c r="D81" t="s">
         <v>163</v>
-      </c>
-      <c r="D81" t="s">
-        <v>113</v>
       </c>
       <c r="E81" t="s">
         <v>114</v>
@@ -3629,10 +3629,10 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
+        <v>112</v>
+      </c>
+      <c r="D82" t="s">
         <v>163</v>
-      </c>
-      <c r="D82" t="s">
-        <v>113</v>
       </c>
       <c r="E82" t="s">
         <v>114</v>
@@ -3661,10 +3661,10 @@
         <v>114</v>
       </c>
       <c r="F83" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G83" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3675,19 +3675,19 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
+        <v>112</v>
+      </c>
+      <c r="D84" t="s">
         <v>170</v>
-      </c>
-      <c r="D84" t="s">
-        <v>113</v>
       </c>
       <c r="E84" t="s">
         <v>114</v>
       </c>
       <c r="F84" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G84" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3698,19 +3698,19 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
+        <v>112</v>
+      </c>
+      <c r="D85" t="s">
         <v>118</v>
-      </c>
-      <c r="D85" t="s">
-        <v>113</v>
       </c>
       <c r="E85" t="s">
         <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="G85" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
+        <v>112</v>
+      </c>
+      <c r="D86" t="s">
         <v>175</v>
-      </c>
-      <c r="D86" t="s">
-        <v>113</v>
       </c>
       <c r="E86" t="s">
         <v>114</v>
       </c>
       <c r="F86" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G86" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,19 +3744,19 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
+        <v>112</v>
+      </c>
+      <c r="D87" t="s">
         <v>118</v>
-      </c>
-      <c r="D87" t="s">
-        <v>113</v>
       </c>
       <c r="E87" t="s">
         <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="G87" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3767,19 +3767,19 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
+        <v>112</v>
+      </c>
+      <c r="D88" t="s">
         <v>118</v>
-      </c>
-      <c r="D88" t="s">
-        <v>113</v>
       </c>
       <c r="E88" t="s">
         <v>114</v>
       </c>
       <c r="F88" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G88" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3790,19 +3790,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
+        <v>112</v>
+      </c>
+      <c r="D89" t="s">
         <v>118</v>
-      </c>
-      <c r="D89" t="s">
-        <v>113</v>
       </c>
       <c r="E89" t="s">
         <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G89" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3813,10 +3813,10 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
+        <v>112</v>
+      </c>
+      <c r="D90" t="s">
         <v>124</v>
-      </c>
-      <c r="D90" t="s">
-        <v>113</v>
       </c>
       <c r="E90" t="s">
         <v>114</v>
@@ -3836,10 +3836,10 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
+        <v>112</v>
+      </c>
+      <c r="D91" t="s">
         <v>182</v>
-      </c>
-      <c r="D91" t="s">
-        <v>113</v>
       </c>
       <c r="E91" t="s">
         <v>114</v>
@@ -3859,10 +3859,10 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" t="s">
         <v>124</v>
-      </c>
-      <c r="D92" t="s">
-        <v>113</v>
       </c>
       <c r="E92" t="s">
         <v>114</v>
@@ -3882,19 +3882,19 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" t="s">
         <v>121</v>
-      </c>
-      <c r="D93" t="s">
-        <v>113</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G93" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3905,10 +3905,10 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
         <v>124</v>
-      </c>
-      <c r="D94" t="s">
-        <v>113</v>
       </c>
       <c r="E94" t="s">
         <v>114</v>
@@ -3928,19 +3928,19 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
+        <v>112</v>
+      </c>
+      <c r="D95" t="s">
         <v>189</v>
-      </c>
-      <c r="D95" t="s">
-        <v>113</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="G95" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3951,10 +3951,10 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" t="s">
         <v>124</v>
-      </c>
-      <c r="D96" t="s">
-        <v>192</v>
       </c>
       <c r="E96" t="s">
         <v>114</v>
@@ -3974,10 +3974,10 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" t="s">
         <v>124</v>
-      </c>
-      <c r="D97" t="s">
-        <v>192</v>
       </c>
       <c r="E97" t="s">
         <v>114</v>
@@ -3997,10 +3997,10 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>192</v>
+      </c>
+      <c r="D98" t="s">
         <v>195</v>
-      </c>
-      <c r="D98" t="s">
-        <v>192</v>
       </c>
       <c r="E98" t="s">
         <v>114</v>
@@ -4020,10 +4020,10 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>192</v>
+      </c>
+      <c r="D99" t="s">
         <v>124</v>
-      </c>
-      <c r="D99" t="s">
-        <v>192</v>
       </c>
       <c r="E99" t="s">
         <v>114</v>
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>192</v>
+      </c>
+      <c r="D100" t="s">
         <v>154</v>
-      </c>
-      <c r="D100" t="s">
-        <v>192</v>
       </c>
       <c r="E100" t="s">
         <v>114</v>
       </c>
       <c r="F100" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="G100" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4066,10 +4066,10 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>192</v>
+      </c>
+      <c r="D101" t="s">
         <v>124</v>
-      </c>
-      <c r="D101" t="s">
-        <v>192</v>
       </c>
       <c r="E101" t="s">
         <v>114</v>
@@ -4088,17 +4088,17 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>202</v>
       </c>
       <c r="E102" t="s">
         <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G102" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4108,17 +4108,17 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>202</v>
       </c>
       <c r="E103" t="s">
         <v>203</v>
       </c>
       <c r="F103" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G103" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4128,17 +4128,17 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>202</v>
       </c>
       <c r="E104" t="s">
         <v>203</v>
       </c>
       <c r="F104" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G104" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4148,17 +4148,17 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>208</v>
       </c>
       <c r="E105" t="s">
         <v>203</v>
       </c>
       <c r="F105" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="G105" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4168,17 +4168,17 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>202</v>
       </c>
       <c r="E106" t="s">
         <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G106" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4188,7 +4188,7 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>182</v>
       </c>
       <c r="E107" t="s">
@@ -4208,17 +4208,17 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>213</v>
       </c>
       <c r="E108" t="s">
         <v>203</v>
       </c>
       <c r="F108" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="G108" t="s">
-        <v>214</v>
+        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4228,17 +4228,17 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>216</v>
       </c>
       <c r="E109" t="s">
         <v>203</v>
       </c>
       <c r="F109" t="s">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="G109" t="s">
-        <v>217</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4248,17 +4248,17 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>219</v>
       </c>
       <c r="E110" t="s">
         <v>203</v>
       </c>
       <c r="F110" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
       <c r="G110" t="s">
-        <v>220</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4268,17 +4268,17 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>202</v>
       </c>
       <c r="E111" t="s">
         <v>203</v>
       </c>
       <c r="F111" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G111" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4288,7 +4288,7 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>223</v>
       </c>
       <c r="E112" t="s">
@@ -4308,17 +4308,17 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="C113" t="s">
-        <v>112</v>
+      <c r="D113" t="s">
+        <v>113</v>
       </c>
       <c r="E113" t="s">
         <v>203</v>
       </c>
       <c r="F113" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G113" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4328,17 +4328,17 @@
       <c r="B114" t="s">
         <v>8</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>151</v>
       </c>
       <c r="E114" t="s">
         <v>203</v>
       </c>
       <c r="F114" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G114" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4348,7 +4348,7 @@
       <c r="B115" t="s">
         <v>8</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>182</v>
       </c>
       <c r="E115" t="s">
@@ -4368,17 +4368,17 @@
       <c r="B116" t="s">
         <v>8</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>230</v>
       </c>
       <c r="E116" t="s">
         <v>203</v>
       </c>
       <c r="F116" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="G116" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4388,7 +4388,7 @@
       <c r="B117" t="s">
         <v>8</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>223</v>
       </c>
       <c r="E117" t="s">
@@ -4408,17 +4408,17 @@
       <c r="B118" t="s">
         <v>8</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>163</v>
       </c>
       <c r="E118" t="s">
         <v>203</v>
       </c>
       <c r="F118" t="s">
-        <v>164</v>
+        <v>234</v>
       </c>
       <c r="G118" t="s">
-        <v>234</v>
+        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4428,7 +4428,7 @@
       <c r="B119" t="s">
         <v>8</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>182</v>
       </c>
       <c r="E119" t="s">
@@ -4448,17 +4448,17 @@
       <c r="B120" t="s">
         <v>8</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>170</v>
       </c>
       <c r="E120" t="s">
         <v>237</v>
       </c>
       <c r="F120" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G120" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4468,17 +4468,17 @@
       <c r="B121" t="s">
         <v>8</v>
       </c>
-      <c r="C121" t="s">
-        <v>112</v>
+      <c r="D121" t="s">
+        <v>113</v>
       </c>
       <c r="E121" t="s">
         <v>237</v>
       </c>
       <c r="F121" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G121" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4488,17 +4488,17 @@
       <c r="B122" t="s">
         <v>8</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>170</v>
       </c>
       <c r="E122" t="s">
         <v>237</v>
       </c>
       <c r="F122" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G122" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4508,17 +4508,17 @@
       <c r="B123" t="s">
         <v>8</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
         <v>170</v>
       </c>
       <c r="E123" t="s">
         <v>237</v>
       </c>
       <c r="F123" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G123" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4528,17 +4528,17 @@
       <c r="B124" t="s">
         <v>8</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
         <v>242</v>
       </c>
       <c r="E124" t="s">
         <v>237</v>
       </c>
       <c r="F124" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G124" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4548,17 +4548,17 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
         <v>242</v>
       </c>
       <c r="E125" t="s">
         <v>237</v>
       </c>
       <c r="F125" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G125" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4568,17 +4568,17 @@
       <c r="B126" t="s">
         <v>8</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
         <v>242</v>
       </c>
       <c r="E126" t="s">
         <v>237</v>
       </c>
       <c r="F126" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G126" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4588,17 +4588,17 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127" t="s">
         <v>242</v>
       </c>
       <c r="E127" t="s">
         <v>237</v>
       </c>
       <c r="F127" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G127" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4608,17 +4608,17 @@
       <c r="B128" t="s">
         <v>8</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
         <v>242</v>
       </c>
       <c r="E128" t="s">
         <v>237</v>
       </c>
       <c r="F128" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G128" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4628,17 +4628,17 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
         <v>242</v>
       </c>
       <c r="E129" t="s">
         <v>237</v>
       </c>
       <c r="F129" t="s">
-        <v>164</v>
+        <v>249</v>
       </c>
       <c r="G129" t="s">
-        <v>249</v>
+        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4648,17 +4648,17 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
         <v>242</v>
       </c>
       <c r="E130" t="s">
         <v>237</v>
       </c>
       <c r="F130" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="G130" t="s">
-        <v>251</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4668,17 +4668,17 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131" t="s">
         <v>242</v>
       </c>
       <c r="E131" t="s">
         <v>237</v>
       </c>
       <c r="F131" t="s">
-        <v>164</v>
+        <v>253</v>
       </c>
       <c r="G131" t="s">
-        <v>253</v>
+        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4688,17 +4688,17 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>255</v>
       </c>
       <c r="E132" t="s">
         <v>237</v>
       </c>
       <c r="F132" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="G132" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4708,17 +4708,17 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
         <v>189</v>
       </c>
       <c r="E133" t="s">
         <v>237</v>
       </c>
       <c r="F133" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="G133" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4728,17 +4728,17 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
         <v>175</v>
       </c>
       <c r="E134" t="s">
         <v>259</v>
       </c>
       <c r="F134" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G134" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4748,17 +4748,17 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
         <v>175</v>
       </c>
       <c r="E135" t="s">
         <v>259</v>
       </c>
       <c r="F135" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G135" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4768,17 +4768,17 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
         <v>175</v>
       </c>
       <c r="E136" t="s">
         <v>259</v>
       </c>
       <c r="F136" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G136" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4788,17 +4788,17 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
         <v>175</v>
       </c>
       <c r="E137" t="s">
         <v>259</v>
       </c>
       <c r="F137" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G137" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4808,17 +4808,17 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
         <v>175</v>
       </c>
       <c r="E138" t="s">
         <v>259</v>
       </c>
       <c r="F138" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G138" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4828,17 +4828,17 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" t="s">
         <v>265</v>
       </c>
       <c r="E139" t="s">
         <v>259</v>
       </c>
       <c r="F139" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="G139" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4848,17 +4848,17 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
         <v>175</v>
       </c>
       <c r="E140" t="s">
         <v>259</v>
       </c>
       <c r="F140" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G140" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4878,10 +4878,10 @@
         <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G141" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4901,10 +4901,10 @@
         <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G142" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4915,19 +4915,19 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
+        <v>269</v>
+      </c>
+      <c r="D143" t="s">
         <v>275</v>
-      </c>
-      <c r="D143" t="s">
-        <v>270</v>
       </c>
       <c r="E143" t="s">
         <v>271</v>
       </c>
       <c r="F143" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G143" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4938,19 +4938,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
+        <v>269</v>
+      </c>
+      <c r="D144" t="s">
         <v>275</v>
-      </c>
-      <c r="D144" t="s">
-        <v>270</v>
       </c>
       <c r="E144" t="s">
         <v>271</v>
       </c>
       <c r="F144" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G144" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4961,19 +4961,19 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
+        <v>269</v>
+      </c>
+      <c r="D145" t="s">
         <v>275</v>
-      </c>
-      <c r="D145" t="s">
-        <v>270</v>
       </c>
       <c r="E145" t="s">
         <v>271</v>
       </c>
       <c r="F145" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G145" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4993,10 +4993,10 @@
         <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G146" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5007,19 +5007,19 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D147" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E147" t="s">
         <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G147" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5030,19 +5030,19 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D148" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E148" t="s">
         <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G148" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5053,19 +5053,19 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D149" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E149" t="s">
         <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G149" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5076,19 +5076,19 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D150" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E150" t="s">
         <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G150" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5099,19 +5099,19 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D151" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E151" t="s">
         <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G151" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5122,19 +5122,19 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D152" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E152" t="s">
         <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G152" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5145,19 +5145,19 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D153" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E153" t="s">
         <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G153" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5168,19 +5168,19 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D154" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E154" t="s">
         <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G154" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5191,19 +5191,19 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D155" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E155" t="s">
         <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G155" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5214,19 +5214,19 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D156" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E156" t="s">
         <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G156" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D157" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E157" t="s">
         <v>271</v>
       </c>
       <c r="F157" t="s">
-        <v>164</v>
+        <v>293</v>
       </c>
       <c r="G157" t="s">
-        <v>293</v>
+        <v>165</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5260,19 +5260,19 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D158" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E158" t="s">
         <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G158" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5283,19 +5283,19 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D159" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E159" t="s">
         <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G159" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5306,19 +5306,19 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D160" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E160" t="s">
         <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G160" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5329,19 +5329,19 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D161" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E161" t="s">
         <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G161" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5352,19 +5352,19 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="D162" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="E162" t="s">
         <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G162" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="E163" t="s">
         <v>271</v>
       </c>
       <c r="F163" t="s">
-        <v>164</v>
+        <v>302</v>
       </c>
       <c r="G163" t="s">
-        <v>302</v>
+        <v>165</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5398,19 +5398,19 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D164" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E164" t="s">
         <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G164" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5421,19 +5421,19 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D165" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E165" t="s">
         <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G165" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5444,19 +5444,19 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D166" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E166" t="s">
         <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G166" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5467,19 +5467,19 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D167" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E167" t="s">
         <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G167" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D168" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E168" t="s">
         <v>271</v>
       </c>
       <c r="F168" t="s">
-        <v>164</v>
+        <v>309</v>
       </c>
       <c r="G168" t="s">
-        <v>309</v>
+        <v>165</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D169" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E169" t="s">
         <v>271</v>
       </c>
       <c r="F169" t="s">
-        <v>164</v>
+        <v>309</v>
       </c>
       <c r="G169" t="s">
-        <v>309</v>
+        <v>165</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5536,19 +5536,19 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D170" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E170" t="s">
         <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G170" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5558,7 +5558,7 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
         <v>163</v>
       </c>
       <c r="E171" t="s">
@@ -5578,17 +5578,17 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
         <v>118</v>
       </c>
       <c r="E172" t="s">
         <v>313</v>
       </c>
       <c r="F172" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G172" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5598,7 +5598,7 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" t="s">
         <v>163</v>
       </c>
       <c r="E173" t="s">
@@ -5618,7 +5618,7 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174" t="s">
         <v>163</v>
       </c>
       <c r="E174" t="s">
@@ -5638,7 +5638,7 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D175" t="s">
         <v>163</v>
       </c>
       <c r="E175" t="s">
@@ -5658,7 +5658,7 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
         <v>163</v>
       </c>
       <c r="E176" t="s">
@@ -5678,7 +5678,7 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177" t="s">
         <v>163</v>
       </c>
       <c r="E177" t="s">
@@ -5698,7 +5698,7 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178" t="s">
         <v>163</v>
       </c>
       <c r="E178" t="s">
@@ -5718,7 +5718,7 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D179" t="s">
         <v>163</v>
       </c>
       <c r="E179" t="s">
@@ -5738,7 +5738,7 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
         <v>163</v>
       </c>
       <c r="E180" t="s">
@@ -5768,10 +5768,10 @@
         <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G181" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5791,10 +5791,10 @@
         <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G182" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5814,10 +5814,10 @@
         <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G183" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5837,10 +5837,10 @@
         <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G184" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5860,10 +5860,10 @@
         <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G185" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5883,10 +5883,10 @@
         <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G186" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5906,10 +5906,10 @@
         <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G187" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5929,10 +5929,10 @@
         <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G188" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5952,10 +5952,10 @@
         <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G189" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5975,10 +5975,10 @@
         <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G190" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5998,10 +5998,10 @@
         <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G191" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6021,10 +6021,10 @@
         <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G192" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
+        <v>325</v>
+      </c>
+      <c r="D193" t="s">
         <v>275</v>
-      </c>
-      <c r="D193" t="s">
-        <v>326</v>
       </c>
       <c r="E193" t="s">
         <v>327</v>
       </c>
       <c r="F193" t="s">
-        <v>164</v>
+        <v>341</v>
       </c>
       <c r="G193" t="s">
-        <v>341</v>
+        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6067,10 +6067,10 @@
         <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G194" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6090,10 +6090,10 @@
         <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G195" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6113,10 +6113,10 @@
         <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G196" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6136,10 +6136,10 @@
         <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G197" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6159,10 +6159,10 @@
         <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G198" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E199" t="s">
         <v>327</v>
       </c>
       <c r="F199" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G199" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E200" t="s">
         <v>327</v>
       </c>
       <c r="F200" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G200" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E201" t="s">
         <v>327</v>
       </c>
       <c r="F201" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G201" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E202" t="s">
         <v>327</v>
       </c>
       <c r="F202" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G202" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>348</v>
+      </c>
+      <c r="D203" t="s">
         <v>275</v>
-      </c>
-      <c r="D203" t="s">
-        <v>348</v>
       </c>
       <c r="E203" t="s">
         <v>327</v>
       </c>
       <c r="F203" t="s">
-        <v>164</v>
+        <v>341</v>
       </c>
       <c r="G203" t="s">
-        <v>341</v>
+        <v>165</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E204" t="s">
         <v>327</v>
       </c>
       <c r="F204" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G204" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E205" t="s">
         <v>327</v>
       </c>
       <c r="F205" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="G205" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E206" t="s">
         <v>327</v>
       </c>
       <c r="F206" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="G206" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E207" t="s">
         <v>327</v>
       </c>
       <c r="F207" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="G207" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>356</v>
+      </c>
+      <c r="D208" t="s">
         <v>275</v>
-      </c>
-      <c r="D208" t="s">
-        <v>356</v>
       </c>
       <c r="E208" t="s">
         <v>327</v>
       </c>
       <c r="F208" t="s">
-        <v>164</v>
+        <v>341</v>
       </c>
       <c r="G208" t="s">
-        <v>341</v>
+        <v>165</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E209" t="s">
         <v>327</v>
       </c>
       <c r="F209" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="G209" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6435,10 +6435,10 @@
         <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G210" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6458,10 +6458,10 @@
         <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G211" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6481,10 +6481,10 @@
         <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G212" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6504,10 +6504,10 @@
         <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G213" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6527,10 +6527,10 @@
         <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G214" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="D215" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
       <c r="E215" t="s">
         <v>365</v>
       </c>
       <c r="F215" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G215" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6573,10 +6573,10 @@
         <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G216" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6596,10 +6596,10 @@
         <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G217" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6619,10 +6619,10 @@
         <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G218" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6642,10 +6642,10 @@
         <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G219" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="D220" t="s">
-        <v>364</v>
+        <v>270</v>
       </c>
       <c r="E220" t="s">
         <v>365</v>
       </c>
       <c r="F220" t="s">
-        <v>164</v>
+        <v>309</v>
       </c>
       <c r="G220" t="s">
-        <v>309</v>
+        <v>165</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6688,10 +6688,10 @@
         <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G221" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6711,10 +6711,10 @@
         <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G222" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6734,10 +6734,10 @@
         <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G223" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6757,10 +6757,10 @@
         <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G224" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6780,10 +6780,10 @@
         <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G225" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6794,19 +6794,19 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
+        <v>363</v>
+      </c>
+      <c r="D226" t="s">
         <v>275</v>
-      </c>
-      <c r="D226" t="s">
-        <v>364</v>
       </c>
       <c r="E226" t="s">
         <v>365</v>
       </c>
       <c r="F226" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G226" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6826,10 +6826,10 @@
         <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G227" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6840,10 +6840,10 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
+        <v>363</v>
+      </c>
+      <c r="D228" t="s">
         <v>163</v>
-      </c>
-      <c r="D228" t="s">
-        <v>364</v>
       </c>
       <c r="E228" t="s">
         <v>365</v>
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E229" t="s">
         <v>365</v>
       </c>
       <c r="F229" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G229" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E230" t="s">
         <v>365</v>
       </c>
       <c r="F230" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G230" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>269</v>
+        <v>386</v>
       </c>
       <c r="D231" t="s">
-        <v>386</v>
+        <v>270</v>
       </c>
       <c r="E231" t="s">
         <v>365</v>
       </c>
       <c r="F231" t="s">
-        <v>164</v>
+        <v>293</v>
       </c>
       <c r="G231" t="s">
-        <v>293</v>
+        <v>165</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>269</v>
+        <v>386</v>
       </c>
       <c r="D232" t="s">
-        <v>386</v>
+        <v>270</v>
       </c>
       <c r="E232" t="s">
         <v>365</v>
       </c>
       <c r="F232" t="s">
-        <v>164</v>
+        <v>309</v>
       </c>
       <c r="G232" t="s">
-        <v>309</v>
+        <v>165</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E233" t="s">
         <v>365</v>
       </c>
       <c r="F233" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G233" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E234" t="s">
         <v>365</v>
       </c>
       <c r="F234" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G234" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E235" t="s">
         <v>365</v>
       </c>
       <c r="F235" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G235" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E236" t="s">
         <v>365</v>
       </c>
       <c r="F236" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G236" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E237" t="s">
         <v>365</v>
       </c>
       <c r="F237" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G237" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E238" t="s">
         <v>365</v>
       </c>
       <c r="F238" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G238" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="E239" t="s">
         <v>365</v>
       </c>
       <c r="F239" t="s">
-        <v>164</v>
+        <v>399</v>
       </c>
       <c r="G239" t="s">
-        <v>399</v>
+        <v>165</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7116,10 +7116,10 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>401</v>
+      </c>
+      <c r="D240" t="s">
         <v>163</v>
-      </c>
-      <c r="D240" t="s">
-        <v>401</v>
       </c>
       <c r="E240" t="s">
         <v>402</v>
@@ -7139,10 +7139,10 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>401</v>
+      </c>
+      <c r="D241" t="s">
         <v>163</v>
-      </c>
-      <c r="D241" t="s">
-        <v>401</v>
       </c>
       <c r="E241" t="s">
         <v>402</v>
@@ -7162,10 +7162,10 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>401</v>
+      </c>
+      <c r="D242" t="s">
         <v>163</v>
-      </c>
-      <c r="D242" t="s">
-        <v>401</v>
       </c>
       <c r="E242" t="s">
         <v>402</v>
@@ -7185,10 +7185,10 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>401</v>
+      </c>
+      <c r="D243" t="s">
         <v>163</v>
-      </c>
-      <c r="D243" t="s">
-        <v>401</v>
       </c>
       <c r="E243" t="s">
         <v>402</v>
@@ -7208,10 +7208,10 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>401</v>
+      </c>
+      <c r="D244" t="s">
         <v>163</v>
-      </c>
-      <c r="D244" t="s">
-        <v>401</v>
       </c>
       <c r="E244" t="s">
         <v>402</v>
@@ -7231,10 +7231,10 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>401</v>
+      </c>
+      <c r="D245" t="s">
         <v>163</v>
-      </c>
-      <c r="D245" t="s">
-        <v>401</v>
       </c>
       <c r="E245" t="s">
         <v>402</v>
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>409</v>
+      </c>
+      <c r="D246" t="s">
         <v>255</v>
-      </c>
-      <c r="D246" t="s">
-        <v>409</v>
       </c>
       <c r="E246" t="s">
         <v>402</v>
       </c>
       <c r="F246" t="s">
-        <v>164</v>
+        <v>410</v>
       </c>
       <c r="G246" t="s">
-        <v>410</v>
+        <v>165</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7276,7 +7276,7 @@
       <c r="B247" t="s">
         <v>8</v>
       </c>
-      <c r="C247" t="s">
+      <c r="D247" t="s">
         <v>95</v>
       </c>
       <c r="E247" t="s">
@@ -7296,7 +7296,7 @@
       <c r="B248" t="s">
         <v>8</v>
       </c>
-      <c r="C248" t="s">
+      <c r="D248" t="s">
         <v>95</v>
       </c>
       <c r="E248" t="s">
@@ -7316,17 +7316,17 @@
       <c r="B249" t="s">
         <v>8</v>
       </c>
-      <c r="C249" t="s">
+      <c r="D249" t="s">
         <v>415</v>
       </c>
       <c r="E249" t="s">
         <v>412</v>
       </c>
       <c r="F249" t="s">
-        <v>96</v>
+        <v>416</v>
       </c>
       <c r="G249" t="s">
-        <v>416</v>
+        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7336,7 +7336,7 @@
       <c r="B250" t="s">
         <v>8</v>
       </c>
-      <c r="C250" t="s">
+      <c r="D250" t="s">
         <v>95</v>
       </c>
       <c r="E250" t="s">
@@ -7356,7 +7356,7 @@
       <c r="B251" t="s">
         <v>8</v>
       </c>
-      <c r="C251" t="s">
+      <c r="D251" t="s">
         <v>95</v>
       </c>
       <c r="E251" t="s">
@@ -7376,7 +7376,7 @@
       <c r="B252" t="s">
         <v>8</v>
       </c>
-      <c r="C252" t="s">
+      <c r="D252" t="s">
         <v>95</v>
       </c>
       <c r="E252" t="s">
@@ -7396,17 +7396,17 @@
       <c r="B253" t="s">
         <v>8</v>
       </c>
-      <c r="C253" t="s">
+      <c r="D253" t="s">
         <v>421</v>
       </c>
       <c r="E253" t="s">
         <v>422</v>
       </c>
       <c r="F253" t="s">
-        <v>164</v>
+        <v>423</v>
       </c>
       <c r="G253" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7416,17 +7416,17 @@
       <c r="B254" t="s">
         <v>8</v>
       </c>
-      <c r="C254" t="s">
+      <c r="D254" t="s">
         <v>219</v>
       </c>
       <c r="E254" t="s">
         <v>422</v>
       </c>
       <c r="F254" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
       <c r="G254" t="s">
-        <v>220</v>
+        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7436,17 +7436,17 @@
       <c r="B255" t="s">
         <v>8</v>
       </c>
-      <c r="C255" t="s">
+      <c r="D255" t="s">
         <v>426</v>
       </c>
       <c r="E255" t="s">
         <v>422</v>
       </c>
       <c r="F255" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G255" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7456,17 +7456,17 @@
       <c r="B256" t="s">
         <v>8</v>
       </c>
-      <c r="C256" t="s">
+      <c r="D256" t="s">
         <v>426</v>
       </c>
       <c r="E256" t="s">
         <v>422</v>
       </c>
       <c r="F256" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G256" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7476,17 +7476,17 @@
       <c r="B257" t="s">
         <v>8</v>
       </c>
-      <c r="C257" t="s">
+      <c r="D257" t="s">
         <v>426</v>
       </c>
       <c r="E257" t="s">
         <v>422</v>
       </c>
       <c r="F257" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G257" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7496,17 +7496,17 @@
       <c r="B258" t="s">
         <v>8</v>
       </c>
-      <c r="C258" t="s">
-        <v>325</v>
+      <c r="D258" t="s">
+        <v>326</v>
       </c>
       <c r="E258" t="s">
         <v>422</v>
       </c>
       <c r="F258" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G258" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7516,17 +7516,17 @@
       <c r="B259" t="s">
         <v>8</v>
       </c>
-      <c r="C259" t="s">
+      <c r="D259" t="s">
         <v>426</v>
       </c>
       <c r="E259" t="s">
         <v>422</v>
       </c>
       <c r="F259" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G259" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7536,7 +7536,7 @@
       <c r="B260" t="s">
         <v>8</v>
       </c>
-      <c r="C260" t="s">
+      <c r="D260" t="s">
         <v>163</v>
       </c>
       <c r="E260" t="s">
@@ -7556,17 +7556,17 @@
       <c r="B261" t="s">
         <v>8</v>
       </c>
-      <c r="C261" t="s">
+      <c r="D261" t="s">
         <v>434</v>
       </c>
       <c r="E261" t="s">
         <v>422</v>
       </c>
       <c r="F261" t="s">
-        <v>196</v>
+        <v>435</v>
       </c>
       <c r="G261" t="s">
-        <v>435</v>
+        <v>197</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7576,7 +7576,7 @@
       <c r="B262" t="s">
         <v>8</v>
       </c>
-      <c r="C262" t="s">
+      <c r="D262" t="s">
         <v>163</v>
       </c>
       <c r="E262" t="s">
@@ -7596,17 +7596,17 @@
       <c r="B263" t="s">
         <v>8</v>
       </c>
-      <c r="C263" t="s">
+      <c r="D263" t="s">
         <v>438</v>
       </c>
       <c r="E263" t="s">
         <v>422</v>
       </c>
       <c r="F263" t="s">
-        <v>183</v>
+        <v>439</v>
       </c>
       <c r="G263" t="s">
-        <v>439</v>
+        <v>184</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7616,7 +7616,7 @@
       <c r="B264" t="s">
         <v>8</v>
       </c>
-      <c r="C264" t="s">
+      <c r="D264" t="s">
         <v>31</v>
       </c>
       <c r="E264" t="s">
@@ -7636,8 +7636,8 @@
       <c r="B265" t="s">
         <v>8</v>
       </c>
-      <c r="C265" t="s">
-        <v>9</v>
+      <c r="D265" t="s">
+        <v>10</v>
       </c>
       <c r="E265" t="s">
         <v>422</v>
@@ -7656,17 +7656,17 @@
       <c r="B266" t="s">
         <v>8</v>
       </c>
-      <c r="C266" t="s">
+      <c r="D266" t="s">
         <v>443</v>
       </c>
       <c r="E266" t="s">
         <v>422</v>
       </c>
       <c r="F266" t="s">
-        <v>115</v>
+        <v>444</v>
       </c>
       <c r="G266" t="s">
-        <v>444</v>
+        <v>116</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7676,17 +7676,17 @@
       <c r="B267" t="s">
         <v>8</v>
       </c>
-      <c r="C267" t="s">
+      <c r="D267" t="s">
         <v>118</v>
       </c>
       <c r="E267" t="s">
         <v>446</v>
       </c>
       <c r="F267" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G267" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7696,17 +7696,17 @@
       <c r="B268" t="s">
         <v>8</v>
       </c>
-      <c r="C268" t="s">
+      <c r="D268" t="s">
         <v>202</v>
       </c>
       <c r="E268" t="s">
         <v>448</v>
       </c>
       <c r="F268" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G268" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7716,17 +7716,17 @@
       <c r="B269" t="s">
         <v>8</v>
       </c>
-      <c r="C269" t="s">
+      <c r="D269" t="s">
         <v>118</v>
       </c>
       <c r="E269" t="s">
         <v>450</v>
       </c>
       <c r="F269" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G269" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7736,17 +7736,17 @@
       <c r="B270" t="s">
         <v>8</v>
       </c>
-      <c r="C270" t="s">
+      <c r="D270" t="s">
         <v>118</v>
       </c>
       <c r="E270" t="s">
         <v>450</v>
       </c>
       <c r="F270" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G270" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7756,17 +7756,17 @@
       <c r="B271" t="s">
         <v>8</v>
       </c>
-      <c r="C271" t="s">
+      <c r="D271" t="s">
         <v>453</v>
       </c>
       <c r="E271" t="s">
         <v>454</v>
       </c>
       <c r="F271" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G271" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7776,17 +7776,17 @@
       <c r="B272" t="s">
         <v>8</v>
       </c>
-      <c r="C272" t="s">
+      <c r="D272" t="s">
         <v>453</v>
       </c>
       <c r="E272" t="s">
         <v>454</v>
       </c>
       <c r="F272" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G272" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7796,17 +7796,17 @@
       <c r="B273" t="s">
         <v>8</v>
       </c>
-      <c r="C273" t="s">
+      <c r="D273" t="s">
         <v>453</v>
       </c>
       <c r="E273" t="s">
         <v>454</v>
       </c>
       <c r="F273" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G273" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7816,17 +7816,17 @@
       <c r="B274" t="s">
         <v>8</v>
       </c>
-      <c r="C274" t="s">
+      <c r="D274" t="s">
         <v>453</v>
       </c>
       <c r="E274" t="s">
         <v>454</v>
       </c>
       <c r="F274" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G274" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7836,17 +7836,17 @@
       <c r="B275" t="s">
         <v>8</v>
       </c>
-      <c r="C275" t="s">
+      <c r="D275" t="s">
         <v>453</v>
       </c>
       <c r="E275" t="s">
         <v>454</v>
       </c>
       <c r="F275" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G275" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7856,17 +7856,17 @@
       <c r="B276" t="s">
         <v>8</v>
       </c>
-      <c r="C276" t="s">
+      <c r="D276" t="s">
         <v>453</v>
       </c>
       <c r="E276" t="s">
         <v>454</v>
       </c>
       <c r="F276" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G276" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7876,17 +7876,17 @@
       <c r="B277" t="s">
         <v>8</v>
       </c>
-      <c r="C277" t="s">
+      <c r="D277" t="s">
         <v>453</v>
       </c>
       <c r="E277" t="s">
         <v>454</v>
       </c>
       <c r="F277" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G277" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7896,17 +7896,17 @@
       <c r="B278" t="s">
         <v>8</v>
       </c>
-      <c r="C278" t="s">
+      <c r="D278" t="s">
         <v>202</v>
       </c>
       <c r="E278" t="s">
         <v>463</v>
       </c>
       <c r="F278" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G278" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7916,17 +7916,17 @@
       <c r="B279" t="s">
         <v>8</v>
       </c>
-      <c r="C279" t="s">
-        <v>51</v>
+      <c r="D279" t="s">
+        <v>52</v>
       </c>
       <c r="E279" t="s">
         <v>463</v>
       </c>
       <c r="F279" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G279" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7936,8 +7936,8 @@
       <c r="B280" t="s">
         <v>8</v>
       </c>
-      <c r="C280" t="s">
-        <v>9</v>
+      <c r="D280" t="s">
+        <v>10</v>
       </c>
       <c r="E280" t="s">
         <v>463</v>
@@ -7956,17 +7956,17 @@
       <c r="B281" t="s">
         <v>8</v>
       </c>
-      <c r="C281" t="s">
+      <c r="D281" t="s">
         <v>170</v>
       </c>
       <c r="E281" t="s">
         <v>463</v>
       </c>
       <c r="F281" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G281" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7976,7 +7976,7 @@
       <c r="B282" t="s">
         <v>8</v>
       </c>
-      <c r="C282" t="s">
+      <c r="D282" t="s">
         <v>124</v>
       </c>
       <c r="E282" t="s">
@@ -7996,17 +7996,17 @@
       <c r="B283" t="s">
         <v>8</v>
       </c>
-      <c r="C283" t="s">
-        <v>363</v>
+      <c r="D283" t="s">
+        <v>364</v>
       </c>
       <c r="E283" t="s">
         <v>469</v>
       </c>
       <c r="F283" t="s">
-        <v>164</v>
+        <v>399</v>
       </c>
       <c r="G283" t="s">
-        <v>399</v>
+        <v>165</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8016,7 +8016,7 @@
       <c r="B284" t="s">
         <v>8</v>
       </c>
-      <c r="C284" t="s">
+      <c r="D284" t="s">
         <v>124</v>
       </c>
       <c r="E284" t="s">
@@ -8036,17 +8036,17 @@
       <c r="B285" t="s">
         <v>8</v>
       </c>
-      <c r="C285" t="s">
+      <c r="D285" t="s">
         <v>170</v>
       </c>
       <c r="E285" t="s">
         <v>473</v>
       </c>
       <c r="F285" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G285" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8056,17 +8056,17 @@
       <c r="B286" t="s">
         <v>8</v>
       </c>
-      <c r="C286" t="s">
+      <c r="D286" t="s">
         <v>438</v>
       </c>
       <c r="E286" t="s">
         <v>475</v>
       </c>
       <c r="F286" t="s">
-        <v>183</v>
+        <v>439</v>
       </c>
       <c r="G286" t="s">
-        <v>439</v>
+        <v>184</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8076,17 +8076,17 @@
       <c r="B287" t="s">
         <v>8</v>
       </c>
-      <c r="C287" t="s">
+      <c r="D287" t="s">
         <v>438</v>
       </c>
       <c r="E287" t="s">
         <v>475</v>
       </c>
       <c r="F287" t="s">
-        <v>183</v>
+        <v>439</v>
       </c>
       <c r="G287" t="s">
-        <v>439</v>
+        <v>184</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8096,17 +8096,17 @@
       <c r="B288" t="s">
         <v>8</v>
       </c>
-      <c r="C288" t="s">
+      <c r="D288" t="s">
         <v>41</v>
       </c>
       <c r="E288" t="s">
         <v>475</v>
       </c>
       <c r="F288" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G288" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8116,7 +8116,7 @@
       <c r="B289" t="s">
         <v>8</v>
       </c>
-      <c r="C289" t="s">
+      <c r="D289" t="s">
         <v>31</v>
       </c>
       <c r="E289" t="s">
@@ -8136,7 +8136,7 @@
       <c r="B290" t="s">
         <v>8</v>
       </c>
-      <c r="C290" t="s">
+      <c r="D290" t="s">
         <v>31</v>
       </c>
       <c r="E290" t="s">
@@ -8156,17 +8156,17 @@
       <c r="B291" t="s">
         <v>8</v>
       </c>
-      <c r="C291" t="s">
+      <c r="D291" t="s">
         <v>170</v>
       </c>
       <c r="E291" t="s">
         <v>475</v>
       </c>
       <c r="F291" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G291" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8176,17 +8176,17 @@
       <c r="B292" t="s">
         <v>8</v>
       </c>
-      <c r="C292" t="s">
+      <c r="D292" t="s">
         <v>170</v>
       </c>
       <c r="E292" t="s">
         <v>475</v>
       </c>
       <c r="F292" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G292" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8196,17 +8196,17 @@
       <c r="B293" t="s">
         <v>8</v>
       </c>
-      <c r="C293" t="s">
+      <c r="D293" t="s">
         <v>170</v>
       </c>
       <c r="E293" t="s">
         <v>475</v>
       </c>
       <c r="F293" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G293" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8216,17 +8216,17 @@
       <c r="B294" t="s">
         <v>8</v>
       </c>
-      <c r="C294" t="s">
+      <c r="D294" t="s">
         <v>170</v>
       </c>
       <c r="E294" t="s">
         <v>475</v>
       </c>
       <c r="F294" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G294" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8236,17 +8236,17 @@
       <c r="B295" t="s">
         <v>8</v>
       </c>
-      <c r="C295" t="s">
+      <c r="D295" t="s">
         <v>170</v>
       </c>
       <c r="E295" t="s">
         <v>485</v>
       </c>
       <c r="F295" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G295" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8256,17 +8256,17 @@
       <c r="B296" t="s">
         <v>8</v>
       </c>
-      <c r="C296" t="s">
+      <c r="D296" t="s">
         <v>170</v>
       </c>
       <c r="E296" t="s">
         <v>485</v>
       </c>
       <c r="F296" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G296" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,42 +22,42 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,15 +82,15 @@
     <t>11220</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>07.4 - Public health services</t>
   </si>
   <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>11320</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>11420</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -169,18 +169,18 @@
     <t>12110</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -292,24 +292,24 @@
     <t>140</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -352,21 +352,21 @@
     <t>15110</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -508,12 +508,12 @@
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -565,12 +565,12 @@
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>08.2 - Cultural services</t>
   </si>
   <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -823,18 +823,18 @@
     <t>23110</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,21 +1210,21 @@
     <t>32310</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1243,10 +1243,10 @@
     <t>33210</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
     <t>332</t>
-  </si>
-  <si>
-    <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
     <t>41010</t>
@@ -1863,10 +1863,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -1909,10 +1909,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1935,16 +1935,16 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1955,7 +1955,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1967,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1981,16 +1981,16 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2004,16 +2004,16 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2027,7 +2027,7 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -2036,7 +2036,7 @@
         <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2047,19 +2047,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2070,10 +2070,10 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -2082,7 +2082,7 @@
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2116,10 +2116,10 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -2128,7 +2128,7 @@
         <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2142,16 +2142,16 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" t="s">
         <v>46</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2162,10 +2162,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
@@ -2174,7 +2174,7 @@
         <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2191,13 +2191,13 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
         <v>53</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>54</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2214,13 +2214,13 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
         <v>53</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>54</v>
-      </c>
-      <c r="G18" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
         <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2254,19 +2254,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
         <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2283,13 +2283,13 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
         <v>53</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>54</v>
-      </c>
-      <c r="G21" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2300,19 +2300,19 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" t="s">
         <v>64</v>
-      </c>
-      <c r="D22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
         <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2346,19 +2346,19 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" t="s">
         <v>64</v>
-      </c>
-      <c r="D24" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2369,19 +2369,19 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
         <v>64</v>
-      </c>
-      <c r="D25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2392,19 +2392,19 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" t="s">
         <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2415,19 +2415,19 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" t="s">
         <v>64</v>
-      </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2438,19 +2438,19 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" t="s">
         <v>64</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2461,19 +2461,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" t="s">
         <v>64</v>
-      </c>
-      <c r="D29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" t="s">
-        <v>53</v>
-      </c>
-      <c r="F29" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2484,19 +2484,19 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
         <v>52</v>
       </c>
       <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
         <v>53</v>
       </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2507,19 +2507,19 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" t="s">
+        <v>32</v>
+      </c>
+      <c r="F31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" t="s">
         <v>76</v>
-      </c>
-      <c r="D31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2530,19 +2530,19 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" t="s">
         <v>76</v>
-      </c>
-      <c r="D32" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" t="s">
-        <v>53</v>
-      </c>
-      <c r="F32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G32" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2553,19 +2553,19 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" t="s">
         <v>76</v>
-      </c>
-      <c r="D33" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G33" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2576,19 +2576,19 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" t="s">
         <v>76</v>
-      </c>
-      <c r="D34" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" t="s">
-        <v>53</v>
-      </c>
-      <c r="F34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2599,19 +2599,19 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" t="s">
         <v>76</v>
-      </c>
-      <c r="D35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" t="s">
-        <v>32</v>
-      </c>
-      <c r="G35" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F36" t="s">
         <v>58</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2644,16 +2644,16 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
+      <c r="C37" t="s">
+        <v>31</v>
+      </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="E37" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2664,16 +2664,16 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
+      <c r="C38" t="s">
+        <v>31</v>
+      </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="E38" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2684,16 +2684,16 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="E39" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2704,16 +2704,16 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="E40" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2724,17 +2724,17 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
-      </c>
-      <c r="G41" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2744,17 +2744,17 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
       <c r="D42" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="E42" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F42" t="s">
         <v>58</v>
-      </c>
-      <c r="G42" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2764,16 +2764,16 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
+      <c r="C43" t="s">
+        <v>90</v>
+      </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F43" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2784,16 +2784,16 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
+      <c r="C44" t="s">
+        <v>95</v>
+      </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E44" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
-      </c>
-      <c r="G44" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2804,16 +2804,16 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F45" t="s">
-        <v>92</v>
-      </c>
-      <c r="G45" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2824,16 +2824,16 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
+      <c r="C46" t="s">
+        <v>90</v>
+      </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F46" t="s">
-        <v>92</v>
-      </c>
-      <c r="G46" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2844,17 +2844,17 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
+      <c r="C47" t="s">
+        <v>101</v>
+      </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E47" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F47" t="s">
         <v>102</v>
-      </c>
-      <c r="G47" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2864,16 +2864,16 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
+      <c r="C48" t="s">
+        <v>90</v>
+      </c>
       <c r="D48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F48" t="s">
-        <v>92</v>
-      </c>
-      <c r="G48" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2884,16 +2884,16 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
+      <c r="C49" t="s">
+        <v>90</v>
+      </c>
       <c r="D49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F49" t="s">
-        <v>92</v>
-      </c>
-      <c r="G49" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2904,17 +2904,17 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
+      <c r="C50" t="s">
+        <v>101</v>
+      </c>
       <c r="D50" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E50" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F50" t="s">
         <v>102</v>
-      </c>
-      <c r="G50" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2924,16 +2924,16 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
+      <c r="C51" t="s">
+        <v>90</v>
+      </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F51" t="s">
-        <v>92</v>
-      </c>
-      <c r="G51" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
+      <c r="C52" t="s">
+        <v>108</v>
+      </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="E52" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F52" t="s">
         <v>109</v>
-      </c>
-      <c r="G52" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2964,17 +2964,17 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="E53" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
-      </c>
-      <c r="G53" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3008,10 +3008,10 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E55" t="s">
         <v>114</v>
@@ -3031,10 +3031,10 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E56" t="s">
         <v>114</v>
@@ -3054,19 +3054,19 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3077,10 +3077,10 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E58" t="s">
         <v>114</v>
@@ -3100,10 +3100,10 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E59" t="s">
         <v>114</v>
@@ -3123,10 +3123,10 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E60" t="s">
         <v>114</v>
@@ -3146,10 +3146,10 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
@@ -3169,10 +3169,10 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E62" t="s">
         <v>114</v>
@@ -3192,10 +3192,10 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E63" t="s">
         <v>114</v>
@@ -3215,10 +3215,10 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D64" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E64" t="s">
         <v>114</v>
@@ -3238,10 +3238,10 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E65" t="s">
         <v>114</v>
@@ -3284,10 +3284,10 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E67" t="s">
         <v>114</v>
@@ -3353,10 +3353,10 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E70" t="s">
         <v>114</v>
@@ -3376,10 +3376,10 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E71" t="s">
         <v>114</v>
@@ -3422,19 +3422,19 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F73" t="s">
         <v>149</v>
       </c>
       <c r="G73" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3445,19 +3445,19 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F74" t="s">
         <v>152</v>
       </c>
       <c r="G74" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3468,19 +3468,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F75" t="s">
         <v>155</v>
       </c>
       <c r="G75" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3491,19 +3491,19 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E76" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F76" t="s">
         <v>149</v>
       </c>
       <c r="G76" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3514,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D77" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F77" t="s">
         <v>149</v>
       </c>
       <c r="G77" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3537,19 +3537,19 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="E78" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F78" t="s">
         <v>152</v>
       </c>
       <c r="G78" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3560,19 +3560,19 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="E79" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F79" t="s">
         <v>161</v>
       </c>
       <c r="G79" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3583,19 +3583,19 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E80" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F80" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G80" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3606,19 +3606,19 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E81" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G81" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3629,19 +3629,19 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E82" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F82" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G82" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3675,10 +3675,10 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="E84" t="s">
         <v>114</v>
@@ -3698,10 +3698,10 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D85" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E85" t="s">
         <v>114</v>
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>113</v>
       </c>
       <c r="E86" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F86" t="s">
         <v>176</v>
       </c>
       <c r="G86" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,10 +3744,10 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D87" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E87" t="s">
         <v>114</v>
@@ -3767,10 +3767,10 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E88" t="s">
         <v>114</v>
@@ -3790,10 +3790,10 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D89" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E89" t="s">
         <v>114</v>
@@ -3813,19 +3813,19 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E90" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F90" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G90" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3836,19 +3836,19 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="E91" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="F91" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G91" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3859,19 +3859,19 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E92" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F92" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G92" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3882,10 +3882,10 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
@@ -3905,19 +3905,19 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E94" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F94" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3928,10 +3928,10 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
@@ -3951,19 +3951,19 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>124</v>
+      </c>
+      <c r="D96" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" t="s">
+        <v>125</v>
+      </c>
+      <c r="F96" t="s">
+        <v>126</v>
+      </c>
+      <c r="G96" t="s">
         <v>192</v>
-      </c>
-      <c r="D96" t="s">
-        <v>124</v>
-      </c>
-      <c r="E96" t="s">
-        <v>114</v>
-      </c>
-      <c r="F96" t="s">
-        <v>125</v>
-      </c>
-      <c r="G96" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3974,19 +3974,19 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>124</v>
+      </c>
+      <c r="D97" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" t="s">
+        <v>125</v>
+      </c>
+      <c r="F97" t="s">
+        <v>126</v>
+      </c>
+      <c r="G97" t="s">
         <v>192</v>
-      </c>
-      <c r="D97" t="s">
-        <v>124</v>
-      </c>
-      <c r="E97" t="s">
-        <v>114</v>
-      </c>
-      <c r="F97" t="s">
-        <v>125</v>
-      </c>
-      <c r="G97" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3997,19 +3997,19 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>195</v>
+      </c>
+      <c r="D98" t="s">
+        <v>113</v>
+      </c>
+      <c r="E98" t="s">
+        <v>196</v>
+      </c>
+      <c r="F98" t="s">
+        <v>197</v>
+      </c>
+      <c r="G98" t="s">
         <v>192</v>
-      </c>
-      <c r="D98" t="s">
-        <v>195</v>
-      </c>
-      <c r="E98" t="s">
-        <v>114</v>
-      </c>
-      <c r="F98" t="s">
-        <v>196</v>
-      </c>
-      <c r="G98" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4020,19 +4020,19 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>124</v>
+      </c>
+      <c r="D99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99" t="s">
+        <v>125</v>
+      </c>
+      <c r="F99" t="s">
+        <v>126</v>
+      </c>
+      <c r="G99" t="s">
         <v>192</v>
-      </c>
-      <c r="D99" t="s">
-        <v>124</v>
-      </c>
-      <c r="E99" t="s">
-        <v>114</v>
-      </c>
-      <c r="F99" t="s">
-        <v>125</v>
-      </c>
-      <c r="G99" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="D100" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="E100" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F100" t="s">
         <v>155</v>
       </c>
       <c r="G100" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4066,19 +4066,19 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>124</v>
+      </c>
+      <c r="D101" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" t="s">
+        <v>125</v>
+      </c>
+      <c r="F101" t="s">
+        <v>126</v>
+      </c>
+      <c r="G101" t="s">
         <v>192</v>
-      </c>
-      <c r="D101" t="s">
-        <v>124</v>
-      </c>
-      <c r="E101" t="s">
-        <v>114</v>
-      </c>
-      <c r="F101" t="s">
-        <v>125</v>
-      </c>
-      <c r="G101" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4088,17 +4088,17 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
+      <c r="C102" t="s">
+        <v>202</v>
+      </c>
       <c r="D102" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E102" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F102" t="s">
         <v>204</v>
-      </c>
-      <c r="G102" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4108,17 +4108,17 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
+      <c r="C103" t="s">
+        <v>202</v>
+      </c>
       <c r="D103" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E103" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F103" t="s">
         <v>204</v>
-      </c>
-      <c r="G103" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4128,17 +4128,17 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
+      <c r="C104" t="s">
+        <v>202</v>
+      </c>
       <c r="D104" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E104" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F104" t="s">
         <v>204</v>
-      </c>
-      <c r="G104" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4148,17 +4148,17 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
+      <c r="C105" t="s">
+        <v>208</v>
+      </c>
       <c r="D105" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E105" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F105" t="s">
         <v>209</v>
-      </c>
-      <c r="G105" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4168,17 +4168,17 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
+      <c r="C106" t="s">
+        <v>202</v>
+      </c>
       <c r="D106" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E106" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F106" t="s">
         <v>204</v>
-      </c>
-      <c r="G106" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4188,16 +4188,16 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
+      <c r="C107" t="s">
+        <v>182</v>
+      </c>
       <c r="D107" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E107" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F107" t="s">
-        <v>183</v>
-      </c>
-      <c r="G107" t="s">
         <v>184</v>
       </c>
     </row>
@@ -4208,17 +4208,17 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
+      <c r="C108" t="s">
+        <v>213</v>
+      </c>
       <c r="D108" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="E108" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F108" t="s">
         <v>214</v>
-      </c>
-      <c r="G108" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4228,17 +4228,17 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
+      <c r="C109" t="s">
+        <v>216</v>
+      </c>
       <c r="D109" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="E109" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="F109" t="s">
         <v>217</v>
-      </c>
-      <c r="G109" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4248,17 +4248,17 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
+      <c r="C110" t="s">
+        <v>219</v>
+      </c>
       <c r="D110" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="E110" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="F110" t="s">
         <v>220</v>
-      </c>
-      <c r="G110" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4268,17 +4268,17 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
+      <c r="C111" t="s">
+        <v>202</v>
+      </c>
       <c r="D111" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E111" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F111" t="s">
         <v>204</v>
-      </c>
-      <c r="G111" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4288,337 +4288,337 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
+      <c r="C112" t="s">
+        <v>223</v>
+      </c>
       <c r="D112" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="E112" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="F112" t="s">
-        <v>224</v>
-      </c>
-      <c r="G112" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>226</v>
       </c>
       <c r="B113" t="s">
         <v>8</v>
       </c>
+      <c r="C113" t="s">
+        <v>112</v>
+      </c>
       <c r="D113" t="s">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="E113" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F113" t="s">
         <v>143</v>
       </c>
-      <c r="G113" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>227</v>
       </c>
       <c r="B114" t="s">
         <v>8</v>
       </c>
+      <c r="C114" t="s">
+        <v>151</v>
+      </c>
       <c r="D114" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="E114" t="s">
-        <v>203</v>
+        <v>125</v>
       </c>
       <c r="F114" t="s">
         <v>152</v>
       </c>
-      <c r="G114" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>228</v>
       </c>
       <c r="B115" t="s">
         <v>8</v>
       </c>
+      <c r="C115" t="s">
+        <v>182</v>
+      </c>
       <c r="D115" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E115" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F115" t="s">
-        <v>183</v>
-      </c>
-      <c r="G115" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>229</v>
       </c>
       <c r="B116" t="s">
         <v>8</v>
       </c>
+      <c r="C116" t="s">
+        <v>230</v>
+      </c>
       <c r="D116" t="s">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="E116" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="F116" t="s">
         <v>231</v>
       </c>
-      <c r="G116" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>232</v>
       </c>
       <c r="B117" t="s">
         <v>8</v>
       </c>
+      <c r="C117" t="s">
+        <v>223</v>
+      </c>
       <c r="D117" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="E117" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="F117" t="s">
-        <v>224</v>
-      </c>
-      <c r="G117" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>233</v>
       </c>
       <c r="B118" t="s">
         <v>8</v>
       </c>
+      <c r="C118" t="s">
+        <v>163</v>
+      </c>
       <c r="D118" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="E118" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="F118" t="s">
         <v>234</v>
       </c>
-      <c r="G118" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>235</v>
       </c>
       <c r="B119" t="s">
         <v>8</v>
       </c>
+      <c r="C119" t="s">
+        <v>182</v>
+      </c>
       <c r="D119" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E119" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F119" t="s">
-        <v>183</v>
-      </c>
-      <c r="G119" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>236</v>
       </c>
       <c r="B120" t="s">
         <v>8</v>
       </c>
+      <c r="C120" t="s">
+        <v>170</v>
+      </c>
       <c r="D120" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="E120" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="F120" t="s">
         <v>171</v>
       </c>
-      <c r="G120" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>238</v>
       </c>
       <c r="B121" t="s">
         <v>8</v>
       </c>
+      <c r="C121" t="s">
+        <v>112</v>
+      </c>
       <c r="D121" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="E121" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="F121" t="s">
         <v>143</v>
       </c>
-      <c r="G121" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>239</v>
       </c>
       <c r="B122" t="s">
         <v>8</v>
       </c>
+      <c r="C122" t="s">
+        <v>170</v>
+      </c>
       <c r="D122" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="E122" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="F122" t="s">
         <v>171</v>
       </c>
-      <c r="G122" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>240</v>
       </c>
       <c r="B123" t="s">
         <v>8</v>
       </c>
+      <c r="C123" t="s">
+        <v>170</v>
+      </c>
       <c r="D123" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="E123" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="F123" t="s">
         <v>171</v>
       </c>
-      <c r="G123" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>241</v>
       </c>
       <c r="B124" t="s">
         <v>8</v>
       </c>
+      <c r="C124" t="s">
+        <v>242</v>
+      </c>
       <c r="D124" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E124" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F124" t="s">
         <v>243</v>
       </c>
-      <c r="G124" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>244</v>
       </c>
       <c r="B125" t="s">
         <v>8</v>
       </c>
+      <c r="C125" t="s">
+        <v>242</v>
+      </c>
       <c r="D125" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E125" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F125" t="s">
         <v>243</v>
       </c>
-      <c r="G125" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>245</v>
       </c>
       <c r="B126" t="s">
         <v>8</v>
       </c>
+      <c r="C126" t="s">
+        <v>242</v>
+      </c>
       <c r="D126" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E126" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F126" t="s">
         <v>243</v>
       </c>
-      <c r="G126" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>246</v>
       </c>
       <c r="B127" t="s">
         <v>8</v>
       </c>
+      <c r="C127" t="s">
+        <v>242</v>
+      </c>
       <c r="D127" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E127" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F127" t="s">
         <v>243</v>
       </c>
-      <c r="G127" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>247</v>
       </c>
       <c r="B128" t="s">
         <v>8</v>
       </c>
+      <c r="C128" t="s">
+        <v>242</v>
+      </c>
       <c r="D128" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E128" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F128" t="s">
         <v>243</v>
-      </c>
-      <c r="G128" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4628,17 +4628,17 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
+      <c r="C129" t="s">
+        <v>242</v>
+      </c>
       <c r="D129" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E129" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F129" t="s">
         <v>249</v>
-      </c>
-      <c r="G129" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4648,17 +4648,17 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
+      <c r="C130" t="s">
+        <v>242</v>
+      </c>
       <c r="D130" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E130" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F130" t="s">
         <v>251</v>
-      </c>
-      <c r="G130" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4668,17 +4668,17 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
+      <c r="C131" t="s">
+        <v>242</v>
+      </c>
       <c r="D131" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E131" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F131" t="s">
         <v>253</v>
-      </c>
-      <c r="G131" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4688,17 +4688,17 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
+      <c r="C132" t="s">
+        <v>255</v>
+      </c>
       <c r="D132" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E132" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F132" t="s">
         <v>256</v>
-      </c>
-      <c r="G132" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4708,17 +4708,17 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
+      <c r="C133" t="s">
+        <v>189</v>
+      </c>
       <c r="D133" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="E133" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="F133" t="s">
         <v>190</v>
-      </c>
-      <c r="G133" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4728,17 +4728,17 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
+      <c r="C134" t="s">
+        <v>175</v>
+      </c>
       <c r="D134" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E134" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F134" t="s">
         <v>176</v>
-      </c>
-      <c r="G134" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4748,17 +4748,17 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
+      <c r="C135" t="s">
+        <v>175</v>
+      </c>
       <c r="D135" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E135" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F135" t="s">
         <v>176</v>
-      </c>
-      <c r="G135" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4768,17 +4768,17 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
+      <c r="C136" t="s">
+        <v>175</v>
+      </c>
       <c r="D136" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E136" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F136" t="s">
         <v>176</v>
-      </c>
-      <c r="G136" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4788,17 +4788,17 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
+      <c r="C137" t="s">
+        <v>175</v>
+      </c>
       <c r="D137" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E137" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F137" t="s">
         <v>176</v>
-      </c>
-      <c r="G137" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4808,17 +4808,17 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
+      <c r="C138" t="s">
+        <v>175</v>
+      </c>
       <c r="D138" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E138" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F138" t="s">
         <v>176</v>
-      </c>
-      <c r="G138" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4828,17 +4828,17 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
+      <c r="C139" t="s">
+        <v>265</v>
+      </c>
       <c r="D139" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E139" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="F139" t="s">
         <v>266</v>
-      </c>
-      <c r="G139" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4848,17 +4848,17 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
+      <c r="C140" t="s">
+        <v>175</v>
+      </c>
       <c r="D140" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E140" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="F140" t="s">
         <v>176</v>
-      </c>
-      <c r="G140" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4875,13 +4875,13 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
+        <v>164</v>
+      </c>
+      <c r="F141" t="s">
         <v>271</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>272</v>
-      </c>
-      <c r="G141" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4898,13 +4898,13 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
+        <v>164</v>
+      </c>
+      <c r="F142" t="s">
         <v>271</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>272</v>
-      </c>
-      <c r="G142" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4915,19 +4915,19 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E143" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F143" t="s">
         <v>276</v>
       </c>
       <c r="G143" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4938,19 +4938,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E144" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F144" t="s">
         <v>276</v>
       </c>
       <c r="G144" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4961,19 +4961,19 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E145" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F145" t="s">
         <v>276</v>
       </c>
       <c r="G145" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4990,13 +4990,13 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
+        <v>164</v>
+      </c>
+      <c r="F146" t="s">
         <v>271</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>272</v>
-      </c>
-      <c r="G146" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5007,19 +5007,19 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D147" t="s">
         <v>270</v>
       </c>
       <c r="E147" t="s">
+        <v>164</v>
+      </c>
+      <c r="F147" t="s">
         <v>271</v>
       </c>
-      <c r="F147" t="s">
-        <v>272</v>
-      </c>
       <c r="G147" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5030,19 +5030,19 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
         <v>270</v>
       </c>
       <c r="E148" t="s">
+        <v>164</v>
+      </c>
+      <c r="F148" t="s">
         <v>271</v>
       </c>
-      <c r="F148" t="s">
-        <v>272</v>
-      </c>
       <c r="G148" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5053,19 +5053,19 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D149" t="s">
         <v>270</v>
       </c>
       <c r="E149" t="s">
+        <v>164</v>
+      </c>
+      <c r="F149" t="s">
         <v>271</v>
       </c>
-      <c r="F149" t="s">
-        <v>272</v>
-      </c>
       <c r="G149" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5076,19 +5076,19 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D150" t="s">
         <v>270</v>
       </c>
       <c r="E150" t="s">
+        <v>164</v>
+      </c>
+      <c r="F150" t="s">
         <v>271</v>
       </c>
-      <c r="F150" t="s">
-        <v>272</v>
-      </c>
       <c r="G150" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5099,19 +5099,19 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D151" t="s">
         <v>270</v>
       </c>
       <c r="E151" t="s">
+        <v>164</v>
+      </c>
+      <c r="F151" t="s">
         <v>271</v>
       </c>
-      <c r="F151" t="s">
-        <v>272</v>
-      </c>
       <c r="G151" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5122,19 +5122,19 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D152" t="s">
         <v>270</v>
       </c>
       <c r="E152" t="s">
+        <v>164</v>
+      </c>
+      <c r="F152" t="s">
         <v>271</v>
       </c>
-      <c r="F152" t="s">
-        <v>272</v>
-      </c>
       <c r="G152" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5145,19 +5145,19 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D153" t="s">
         <v>270</v>
       </c>
       <c r="E153" t="s">
+        <v>164</v>
+      </c>
+      <c r="F153" t="s">
         <v>271</v>
       </c>
-      <c r="F153" t="s">
-        <v>272</v>
-      </c>
       <c r="G153" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5168,19 +5168,19 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D154" t="s">
         <v>270</v>
       </c>
       <c r="E154" t="s">
+        <v>164</v>
+      </c>
+      <c r="F154" t="s">
         <v>271</v>
       </c>
-      <c r="F154" t="s">
-        <v>272</v>
-      </c>
       <c r="G154" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5191,19 +5191,19 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D155" t="s">
         <v>270</v>
       </c>
       <c r="E155" t="s">
+        <v>164</v>
+      </c>
+      <c r="F155" t="s">
         <v>271</v>
       </c>
-      <c r="F155" t="s">
-        <v>272</v>
-      </c>
       <c r="G155" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5214,19 +5214,19 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D156" t="s">
         <v>270</v>
       </c>
       <c r="E156" t="s">
+        <v>164</v>
+      </c>
+      <c r="F156" t="s">
         <v>271</v>
       </c>
-      <c r="F156" t="s">
-        <v>272</v>
-      </c>
       <c r="G156" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D157" t="s">
         <v>270</v>
       </c>
       <c r="E157" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F157" t="s">
         <v>293</v>
       </c>
       <c r="G157" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5260,19 +5260,19 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D158" t="s">
         <v>270</v>
       </c>
       <c r="E158" t="s">
+        <v>164</v>
+      </c>
+      <c r="F158" t="s">
         <v>271</v>
       </c>
-      <c r="F158" t="s">
-        <v>272</v>
-      </c>
       <c r="G158" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5283,19 +5283,19 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D159" t="s">
         <v>270</v>
       </c>
       <c r="E159" t="s">
+        <v>164</v>
+      </c>
+      <c r="F159" t="s">
         <v>271</v>
       </c>
-      <c r="F159" t="s">
-        <v>272</v>
-      </c>
       <c r="G159" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5306,19 +5306,19 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D160" t="s">
         <v>270</v>
       </c>
       <c r="E160" t="s">
+        <v>164</v>
+      </c>
+      <c r="F160" t="s">
         <v>271</v>
       </c>
-      <c r="F160" t="s">
-        <v>272</v>
-      </c>
       <c r="G160" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5329,19 +5329,19 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D161" t="s">
         <v>270</v>
       </c>
       <c r="E161" t="s">
+        <v>164</v>
+      </c>
+      <c r="F161" t="s">
         <v>271</v>
       </c>
-      <c r="F161" t="s">
-        <v>272</v>
-      </c>
       <c r="G161" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5352,19 +5352,19 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="D162" t="s">
         <v>270</v>
       </c>
       <c r="E162" t="s">
+        <v>164</v>
+      </c>
+      <c r="F162" t="s">
         <v>271</v>
       </c>
-      <c r="F162" t="s">
-        <v>272</v>
-      </c>
       <c r="G162" t="s">
-        <v>165</v>
+        <v>299</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="D163" t="s">
         <v>270</v>
       </c>
       <c r="E163" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F163" t="s">
+        <v>301</v>
+      </c>
+      <c r="G163" t="s">
         <v>302</v>
-      </c>
-      <c r="G163" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5398,19 +5398,19 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D164" t="s">
         <v>270</v>
       </c>
       <c r="E164" t="s">
+        <v>164</v>
+      </c>
+      <c r="F164" t="s">
         <v>271</v>
       </c>
-      <c r="F164" t="s">
-        <v>272</v>
-      </c>
       <c r="G164" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5421,19 +5421,19 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D165" t="s">
         <v>270</v>
       </c>
       <c r="E165" t="s">
+        <v>164</v>
+      </c>
+      <c r="F165" t="s">
         <v>271</v>
       </c>
-      <c r="F165" t="s">
-        <v>272</v>
-      </c>
       <c r="G165" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5444,19 +5444,19 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D166" t="s">
         <v>270</v>
       </c>
       <c r="E166" t="s">
+        <v>164</v>
+      </c>
+      <c r="F166" t="s">
         <v>271</v>
       </c>
-      <c r="F166" t="s">
-        <v>272</v>
-      </c>
       <c r="G166" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5467,19 +5467,19 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D167" t="s">
         <v>270</v>
       </c>
       <c r="E167" t="s">
+        <v>164</v>
+      </c>
+      <c r="F167" t="s">
         <v>271</v>
       </c>
-      <c r="F167" t="s">
-        <v>272</v>
-      </c>
       <c r="G167" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D168" t="s">
         <v>270</v>
       </c>
       <c r="E168" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F168" t="s">
         <v>309</v>
       </c>
       <c r="G168" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D169" t="s">
         <v>270</v>
       </c>
       <c r="E169" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F169" t="s">
         <v>309</v>
       </c>
       <c r="G169" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5536,19 +5536,19 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D170" t="s">
         <v>270</v>
       </c>
       <c r="E170" t="s">
+        <v>164</v>
+      </c>
+      <c r="F170" t="s">
         <v>271</v>
       </c>
-      <c r="F170" t="s">
-        <v>272</v>
-      </c>
       <c r="G170" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5558,16 +5558,16 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
+      <c r="C171" t="s">
+        <v>163</v>
+      </c>
       <c r="D171" t="s">
-        <v>163</v>
+        <v>313</v>
       </c>
       <c r="E171" t="s">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="F171" t="s">
-        <v>164</v>
-      </c>
-      <c r="G171" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5578,17 +5578,17 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
+      <c r="C172" t="s">
+        <v>118</v>
+      </c>
       <c r="D172" t="s">
-        <v>118</v>
+        <v>313</v>
       </c>
       <c r="E172" t="s">
-        <v>313</v>
+        <v>114</v>
       </c>
       <c r="F172" t="s">
         <v>119</v>
-      </c>
-      <c r="G172" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5598,16 +5598,16 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
+      <c r="C173" t="s">
+        <v>163</v>
+      </c>
       <c r="D173" t="s">
-        <v>163</v>
+        <v>313</v>
       </c>
       <c r="E173" t="s">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="F173" t="s">
-        <v>164</v>
-      </c>
-      <c r="G173" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5618,16 +5618,16 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
+      <c r="C174" t="s">
+        <v>163</v>
+      </c>
       <c r="D174" t="s">
-        <v>163</v>
+        <v>313</v>
       </c>
       <c r="E174" t="s">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="F174" t="s">
-        <v>164</v>
-      </c>
-      <c r="G174" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5638,16 +5638,16 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
+      <c r="C175" t="s">
+        <v>163</v>
+      </c>
       <c r="D175" t="s">
-        <v>163</v>
+        <v>313</v>
       </c>
       <c r="E175" t="s">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="F175" t="s">
-        <v>164</v>
-      </c>
-      <c r="G175" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5658,16 +5658,16 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
+      <c r="C176" t="s">
+        <v>163</v>
+      </c>
       <c r="D176" t="s">
-        <v>163</v>
+        <v>313</v>
       </c>
       <c r="E176" t="s">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="F176" t="s">
-        <v>164</v>
-      </c>
-      <c r="G176" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5678,16 +5678,16 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
+      <c r="C177" t="s">
+        <v>163</v>
+      </c>
       <c r="D177" t="s">
-        <v>163</v>
+        <v>320</v>
       </c>
       <c r="E177" t="s">
-        <v>320</v>
+        <v>164</v>
       </c>
       <c r="F177" t="s">
-        <v>164</v>
-      </c>
-      <c r="G177" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5698,16 +5698,16 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
+      <c r="C178" t="s">
+        <v>163</v>
+      </c>
       <c r="D178" t="s">
-        <v>163</v>
+        <v>320</v>
       </c>
       <c r="E178" t="s">
-        <v>320</v>
+        <v>164</v>
       </c>
       <c r="F178" t="s">
-        <v>164</v>
-      </c>
-      <c r="G178" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5718,16 +5718,16 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
+      <c r="C179" t="s">
+        <v>163</v>
+      </c>
       <c r="D179" t="s">
-        <v>163</v>
+        <v>320</v>
       </c>
       <c r="E179" t="s">
-        <v>320</v>
+        <v>164</v>
       </c>
       <c r="F179" t="s">
-        <v>164</v>
-      </c>
-      <c r="G179" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5738,16 +5738,16 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
+      <c r="C180" t="s">
+        <v>163</v>
+      </c>
       <c r="D180" t="s">
-        <v>163</v>
+        <v>320</v>
       </c>
       <c r="E180" t="s">
-        <v>320</v>
+        <v>164</v>
       </c>
       <c r="F180" t="s">
-        <v>164</v>
-      </c>
-      <c r="G180" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5765,13 +5765,13 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
+        <v>164</v>
+      </c>
+      <c r="F181" t="s">
         <v>327</v>
       </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
         <v>328</v>
-      </c>
-      <c r="G181" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5788,13 +5788,13 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
+        <v>164</v>
+      </c>
+      <c r="F182" t="s">
         <v>327</v>
       </c>
-      <c r="F182" t="s">
+      <c r="G182" t="s">
         <v>328</v>
-      </c>
-      <c r="G182" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5811,13 +5811,13 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
+        <v>164</v>
+      </c>
+      <c r="F183" t="s">
         <v>327</v>
       </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
         <v>328</v>
-      </c>
-      <c r="G183" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5834,13 +5834,13 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
+        <v>164</v>
+      </c>
+      <c r="F184" t="s">
         <v>327</v>
       </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
         <v>328</v>
-      </c>
-      <c r="G184" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5857,13 +5857,13 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
+        <v>164</v>
+      </c>
+      <c r="F185" t="s">
         <v>327</v>
       </c>
-      <c r="F185" t="s">
+      <c r="G185" t="s">
         <v>328</v>
-      </c>
-      <c r="G185" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5880,13 +5880,13 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
+        <v>164</v>
+      </c>
+      <c r="F186" t="s">
         <v>327</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>328</v>
-      </c>
-      <c r="G186" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5903,13 +5903,13 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
+        <v>164</v>
+      </c>
+      <c r="F187" t="s">
         <v>327</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>328</v>
-      </c>
-      <c r="G187" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5926,13 +5926,13 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
+        <v>164</v>
+      </c>
+      <c r="F188" t="s">
         <v>327</v>
       </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>328</v>
-      </c>
-      <c r="G188" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5949,13 +5949,13 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
+        <v>164</v>
+      </c>
+      <c r="F189" t="s">
         <v>327</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>328</v>
-      </c>
-      <c r="G189" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5972,13 +5972,13 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
+        <v>164</v>
+      </c>
+      <c r="F190" t="s">
         <v>327</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>328</v>
-      </c>
-      <c r="G190" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5995,13 +5995,13 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
+        <v>164</v>
+      </c>
+      <c r="F191" t="s">
         <v>327</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>328</v>
-      </c>
-      <c r="G191" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6018,13 +6018,13 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
+        <v>164</v>
+      </c>
+      <c r="F192" t="s">
         <v>327</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>328</v>
-      </c>
-      <c r="G192" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="D193" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="E193" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F193" t="s">
         <v>341</v>
       </c>
       <c r="G193" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6064,13 +6064,13 @@
         <v>326</v>
       </c>
       <c r="E194" t="s">
+        <v>164</v>
+      </c>
+      <c r="F194" t="s">
         <v>327</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>328</v>
-      </c>
-      <c r="G194" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6087,13 +6087,13 @@
         <v>326</v>
       </c>
       <c r="E195" t="s">
+        <v>164</v>
+      </c>
+      <c r="F195" t="s">
         <v>327</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>328</v>
-      </c>
-      <c r="G195" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6110,13 +6110,13 @@
         <v>326</v>
       </c>
       <c r="E196" t="s">
+        <v>164</v>
+      </c>
+      <c r="F196" t="s">
         <v>327</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>328</v>
-      </c>
-      <c r="G196" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6133,13 +6133,13 @@
         <v>326</v>
       </c>
       <c r="E197" t="s">
+        <v>164</v>
+      </c>
+      <c r="F197" t="s">
         <v>327</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
         <v>328</v>
-      </c>
-      <c r="G197" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6156,13 +6156,13 @@
         <v>326</v>
       </c>
       <c r="E198" t="s">
+        <v>164</v>
+      </c>
+      <c r="F198" t="s">
         <v>327</v>
       </c>
-      <c r="F198" t="s">
+      <c r="G198" t="s">
         <v>328</v>
-      </c>
-      <c r="G198" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D199" t="s">
         <v>326</v>
       </c>
       <c r="E199" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F199" t="s">
+        <v>348</v>
+      </c>
+      <c r="G199" t="s">
         <v>349</v>
-      </c>
-      <c r="G199" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D200" t="s">
         <v>326</v>
       </c>
       <c r="E200" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F200" t="s">
+        <v>348</v>
+      </c>
+      <c r="G200" t="s">
         <v>349</v>
-      </c>
-      <c r="G200" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D201" t="s">
         <v>326</v>
       </c>
       <c r="E201" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F201" t="s">
+        <v>348</v>
+      </c>
+      <c r="G201" t="s">
         <v>349</v>
-      </c>
-      <c r="G201" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D202" t="s">
         <v>326</v>
       </c>
       <c r="E202" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F202" t="s">
+        <v>348</v>
+      </c>
+      <c r="G202" t="s">
         <v>349</v>
-      </c>
-      <c r="G202" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>348</v>
+        <v>275</v>
       </c>
       <c r="D203" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="E203" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F203" t="s">
         <v>341</v>
       </c>
       <c r="G203" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D204" t="s">
         <v>326</v>
       </c>
       <c r="E204" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F204" t="s">
+        <v>348</v>
+      </c>
+      <c r="G204" t="s">
         <v>349</v>
-      </c>
-      <c r="G204" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="D205" t="s">
         <v>326</v>
       </c>
       <c r="E205" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F205" t="s">
+        <v>356</v>
+      </c>
+      <c r="G205" t="s">
         <v>357</v>
-      </c>
-      <c r="G205" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="D206" t="s">
         <v>326</v>
       </c>
       <c r="E206" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F206" t="s">
+        <v>356</v>
+      </c>
+      <c r="G206" t="s">
         <v>357</v>
-      </c>
-      <c r="G206" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="D207" t="s">
         <v>326</v>
       </c>
       <c r="E207" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F207" t="s">
+        <v>356</v>
+      </c>
+      <c r="G207" t="s">
         <v>357</v>
-      </c>
-      <c r="G207" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>356</v>
+        <v>275</v>
       </c>
       <c r="D208" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="E208" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F208" t="s">
         <v>341</v>
       </c>
       <c r="G208" t="s">
-        <v>165</v>
+        <v>357</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="D209" t="s">
         <v>326</v>
       </c>
       <c r="E209" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F209" t="s">
+        <v>356</v>
+      </c>
+      <c r="G209" t="s">
         <v>357</v>
-      </c>
-      <c r="G209" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6432,13 +6432,13 @@
         <v>364</v>
       </c>
       <c r="E210" t="s">
+        <v>164</v>
+      </c>
+      <c r="F210" t="s">
         <v>365</v>
       </c>
-      <c r="F210" t="s">
+      <c r="G210" t="s">
         <v>366</v>
-      </c>
-      <c r="G210" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6455,13 +6455,13 @@
         <v>364</v>
       </c>
       <c r="E211" t="s">
+        <v>164</v>
+      </c>
+      <c r="F211" t="s">
         <v>365</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>366</v>
-      </c>
-      <c r="G211" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6478,13 +6478,13 @@
         <v>364</v>
       </c>
       <c r="E212" t="s">
+        <v>164</v>
+      </c>
+      <c r="F212" t="s">
         <v>365</v>
       </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>366</v>
-      </c>
-      <c r="G212" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6501,13 +6501,13 @@
         <v>364</v>
       </c>
       <c r="E213" t="s">
+        <v>164</v>
+      </c>
+      <c r="F213" t="s">
         <v>365</v>
       </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>366</v>
-      </c>
-      <c r="G213" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6524,13 +6524,13 @@
         <v>364</v>
       </c>
       <c r="E214" t="s">
+        <v>164</v>
+      </c>
+      <c r="F214" t="s">
         <v>365</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>366</v>
-      </c>
-      <c r="G214" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>363</v>
+        <v>325</v>
       </c>
       <c r="D215" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="E215" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F215" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G215" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6570,13 +6570,13 @@
         <v>364</v>
       </c>
       <c r="E216" t="s">
+        <v>164</v>
+      </c>
+      <c r="F216" t="s">
         <v>365</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>366</v>
-      </c>
-      <c r="G216" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6593,13 +6593,13 @@
         <v>364</v>
       </c>
       <c r="E217" t="s">
+        <v>164</v>
+      </c>
+      <c r="F217" t="s">
         <v>365</v>
       </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
         <v>366</v>
-      </c>
-      <c r="G217" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6616,13 +6616,13 @@
         <v>364</v>
       </c>
       <c r="E218" t="s">
+        <v>164</v>
+      </c>
+      <c r="F218" t="s">
         <v>365</v>
       </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>366</v>
-      </c>
-      <c r="G218" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6639,13 +6639,13 @@
         <v>364</v>
       </c>
       <c r="E219" t="s">
+        <v>164</v>
+      </c>
+      <c r="F219" t="s">
         <v>365</v>
       </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>366</v>
-      </c>
-      <c r="G219" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>363</v>
+        <v>269</v>
       </c>
       <c r="D220" t="s">
-        <v>270</v>
+        <v>364</v>
       </c>
       <c r="E220" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F220" t="s">
         <v>309</v>
       </c>
       <c r="G220" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6685,13 +6685,13 @@
         <v>364</v>
       </c>
       <c r="E221" t="s">
+        <v>164</v>
+      </c>
+      <c r="F221" t="s">
         <v>365</v>
       </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>366</v>
-      </c>
-      <c r="G221" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6708,13 +6708,13 @@
         <v>364</v>
       </c>
       <c r="E222" t="s">
+        <v>164</v>
+      </c>
+      <c r="F222" t="s">
         <v>365</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>366</v>
-      </c>
-      <c r="G222" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6731,13 +6731,13 @@
         <v>364</v>
       </c>
       <c r="E223" t="s">
+        <v>164</v>
+      </c>
+      <c r="F223" t="s">
         <v>365</v>
       </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>366</v>
-      </c>
-      <c r="G223" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6754,13 +6754,13 @@
         <v>364</v>
       </c>
       <c r="E224" t="s">
+        <v>164</v>
+      </c>
+      <c r="F224" t="s">
         <v>365</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>366</v>
-      </c>
-      <c r="G224" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6777,13 +6777,13 @@
         <v>364</v>
       </c>
       <c r="E225" t="s">
+        <v>164</v>
+      </c>
+      <c r="F225" t="s">
         <v>365</v>
       </c>
-      <c r="F225" t="s">
+      <c r="G225" t="s">
         <v>366</v>
-      </c>
-      <c r="G225" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6794,19 +6794,19 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>275</v>
+        <v>364</v>
       </c>
       <c r="E226" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F226" t="s">
         <v>276</v>
       </c>
       <c r="G226" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6823,13 +6823,13 @@
         <v>364</v>
       </c>
       <c r="E227" t="s">
+        <v>164</v>
+      </c>
+      <c r="F227" t="s">
         <v>365</v>
       </c>
-      <c r="F227" t="s">
+      <c r="G227" t="s">
         <v>366</v>
-      </c>
-      <c r="G227" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6840,19 +6840,19 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E228" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F228" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G228" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D229" t="s">
         <v>364</v>
       </c>
       <c r="E229" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F229" t="s">
+        <v>386</v>
+      </c>
+      <c r="G229" t="s">
         <v>387</v>
-      </c>
-      <c r="G229" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D230" t="s">
         <v>364</v>
       </c>
       <c r="E230" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F230" t="s">
+        <v>386</v>
+      </c>
+      <c r="G230" t="s">
         <v>387</v>
-      </c>
-      <c r="G230" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>386</v>
+        <v>269</v>
       </c>
       <c r="D231" t="s">
-        <v>270</v>
+        <v>364</v>
       </c>
       <c r="E231" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F231" t="s">
         <v>293</v>
       </c>
       <c r="G231" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>386</v>
+        <v>269</v>
       </c>
       <c r="D232" t="s">
-        <v>270</v>
+        <v>364</v>
       </c>
       <c r="E232" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F232" t="s">
         <v>309</v>
       </c>
       <c r="G232" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D233" t="s">
         <v>364</v>
       </c>
       <c r="E233" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F233" t="s">
+        <v>386</v>
+      </c>
+      <c r="G233" t="s">
         <v>387</v>
-      </c>
-      <c r="G233" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D234" t="s">
         <v>364</v>
       </c>
       <c r="E234" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F234" t="s">
+        <v>386</v>
+      </c>
+      <c r="G234" t="s">
         <v>387</v>
-      </c>
-      <c r="G234" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D235" t="s">
         <v>364</v>
       </c>
       <c r="E235" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F235" t="s">
+        <v>386</v>
+      </c>
+      <c r="G235" t="s">
         <v>387</v>
-      </c>
-      <c r="G235" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D236" t="s">
         <v>364</v>
       </c>
       <c r="E236" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F236" t="s">
+        <v>386</v>
+      </c>
+      <c r="G236" t="s">
         <v>387</v>
-      </c>
-      <c r="G236" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D237" t="s">
         <v>364</v>
       </c>
       <c r="E237" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F237" t="s">
+        <v>386</v>
+      </c>
+      <c r="G237" t="s">
         <v>387</v>
-      </c>
-      <c r="G237" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D238" t="s">
         <v>364</v>
       </c>
       <c r="E238" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F238" t="s">
+        <v>386</v>
+      </c>
+      <c r="G238" t="s">
         <v>387</v>
-      </c>
-      <c r="G238" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="D239" t="s">
         <v>364</v>
       </c>
       <c r="E239" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F239" t="s">
+        <v>398</v>
+      </c>
+      <c r="G239" t="s">
         <v>399</v>
-      </c>
-      <c r="G239" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7116,19 +7116,19 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>163</v>
+      </c>
+      <c r="D240" t="s">
         <v>401</v>
       </c>
-      <c r="D240" t="s">
-        <v>163</v>
-      </c>
       <c r="E240" t="s">
+        <v>164</v>
+      </c>
+      <c r="F240" t="s">
+        <v>165</v>
+      </c>
+      <c r="G240" t="s">
         <v>402</v>
-      </c>
-      <c r="F240" t="s">
-        <v>164</v>
-      </c>
-      <c r="G240" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7139,19 +7139,19 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>163</v>
+      </c>
+      <c r="D241" t="s">
         <v>401</v>
       </c>
-      <c r="D241" t="s">
-        <v>163</v>
-      </c>
       <c r="E241" t="s">
+        <v>164</v>
+      </c>
+      <c r="F241" t="s">
+        <v>165</v>
+      </c>
+      <c r="G241" t="s">
         <v>402</v>
-      </c>
-      <c r="F241" t="s">
-        <v>164</v>
-      </c>
-      <c r="G241" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7162,19 +7162,19 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>163</v>
+      </c>
+      <c r="D242" t="s">
         <v>401</v>
       </c>
-      <c r="D242" t="s">
-        <v>163</v>
-      </c>
       <c r="E242" t="s">
+        <v>164</v>
+      </c>
+      <c r="F242" t="s">
+        <v>165</v>
+      </c>
+      <c r="G242" t="s">
         <v>402</v>
-      </c>
-      <c r="F242" t="s">
-        <v>164</v>
-      </c>
-      <c r="G242" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7185,19 +7185,19 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>163</v>
+      </c>
+      <c r="D243" t="s">
         <v>401</v>
       </c>
-      <c r="D243" t="s">
-        <v>163</v>
-      </c>
       <c r="E243" t="s">
+        <v>164</v>
+      </c>
+      <c r="F243" t="s">
+        <v>165</v>
+      </c>
+      <c r="G243" t="s">
         <v>402</v>
-      </c>
-      <c r="F243" t="s">
-        <v>164</v>
-      </c>
-      <c r="G243" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7208,19 +7208,19 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>163</v>
+      </c>
+      <c r="D244" t="s">
         <v>401</v>
       </c>
-      <c r="D244" t="s">
-        <v>163</v>
-      </c>
       <c r="E244" t="s">
+        <v>164</v>
+      </c>
+      <c r="F244" t="s">
+        <v>165</v>
+      </c>
+      <c r="G244" t="s">
         <v>402</v>
-      </c>
-      <c r="F244" t="s">
-        <v>164</v>
-      </c>
-      <c r="G244" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7231,19 +7231,19 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>163</v>
+      </c>
+      <c r="D245" t="s">
         <v>401</v>
       </c>
-      <c r="D245" t="s">
-        <v>163</v>
-      </c>
       <c r="E245" t="s">
+        <v>164</v>
+      </c>
+      <c r="F245" t="s">
+        <v>165</v>
+      </c>
+      <c r="G245" t="s">
         <v>402</v>
-      </c>
-      <c r="F245" t="s">
-        <v>164</v>
-      </c>
-      <c r="G245" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>255</v>
+      </c>
+      <c r="D246" t="s">
+        <v>401</v>
+      </c>
+      <c r="E246" t="s">
+        <v>164</v>
+      </c>
+      <c r="F246" t="s">
         <v>409</v>
       </c>
-      <c r="D246" t="s">
-        <v>255</v>
-      </c>
-      <c r="E246" t="s">
-        <v>402</v>
-      </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
         <v>410</v>
-      </c>
-      <c r="G246" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7276,16 +7276,16 @@
       <c r="B247" t="s">
         <v>8</v>
       </c>
+      <c r="C247" t="s">
+        <v>95</v>
+      </c>
       <c r="D247" t="s">
-        <v>95</v>
+        <v>412</v>
       </c>
       <c r="E247" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F247" t="s">
-        <v>96</v>
-      </c>
-      <c r="G247" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7296,16 +7296,16 @@
       <c r="B248" t="s">
         <v>8</v>
       </c>
+      <c r="C248" t="s">
+        <v>95</v>
+      </c>
       <c r="D248" t="s">
-        <v>95</v>
+        <v>412</v>
       </c>
       <c r="E248" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F248" t="s">
-        <v>96</v>
-      </c>
-      <c r="G248" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7316,17 +7316,17 @@
       <c r="B249" t="s">
         <v>8</v>
       </c>
+      <c r="C249" t="s">
+        <v>415</v>
+      </c>
       <c r="D249" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E249" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F249" t="s">
         <v>416</v>
-      </c>
-      <c r="G249" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7336,16 +7336,16 @@
       <c r="B250" t="s">
         <v>8</v>
       </c>
+      <c r="C250" t="s">
+        <v>95</v>
+      </c>
       <c r="D250" t="s">
-        <v>95</v>
+        <v>412</v>
       </c>
       <c r="E250" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F250" t="s">
-        <v>96</v>
-      </c>
-      <c r="G250" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7356,16 +7356,16 @@
       <c r="B251" t="s">
         <v>8</v>
       </c>
+      <c r="C251" t="s">
+        <v>95</v>
+      </c>
       <c r="D251" t="s">
-        <v>95</v>
+        <v>412</v>
       </c>
       <c r="E251" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F251" t="s">
-        <v>96</v>
-      </c>
-      <c r="G251" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7376,16 +7376,16 @@
       <c r="B252" t="s">
         <v>8</v>
       </c>
+      <c r="C252" t="s">
+        <v>95</v>
+      </c>
       <c r="D252" t="s">
-        <v>95</v>
+        <v>412</v>
       </c>
       <c r="E252" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="F252" t="s">
-        <v>96</v>
-      </c>
-      <c r="G252" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7396,17 +7396,17 @@
       <c r="B253" t="s">
         <v>8</v>
       </c>
+      <c r="C253" t="s">
+        <v>421</v>
+      </c>
       <c r="D253" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E253" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="F253" t="s">
         <v>423</v>
-      </c>
-      <c r="G253" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7416,17 +7416,17 @@
       <c r="B254" t="s">
         <v>8</v>
       </c>
+      <c r="C254" t="s">
+        <v>219</v>
+      </c>
       <c r="D254" t="s">
-        <v>219</v>
+        <v>422</v>
       </c>
       <c r="E254" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="F254" t="s">
         <v>220</v>
-      </c>
-      <c r="G254" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7436,17 +7436,17 @@
       <c r="B255" t="s">
         <v>8</v>
       </c>
+      <c r="C255" t="s">
+        <v>426</v>
+      </c>
       <c r="D255" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E255" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="F255" t="s">
         <v>427</v>
-      </c>
-      <c r="G255" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7456,817 +7456,817 @@
       <c r="B256" t="s">
         <v>8</v>
       </c>
+      <c r="C256" t="s">
+        <v>426</v>
+      </c>
       <c r="D256" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E256" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="F256" t="s">
         <v>427</v>
       </c>
-      <c r="G256" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7">
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>429</v>
       </c>
       <c r="B257" t="s">
         <v>8</v>
       </c>
+      <c r="C257" t="s">
+        <v>426</v>
+      </c>
       <c r="D257" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E257" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="F257" t="s">
         <v>427</v>
       </c>
-      <c r="G257" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7">
+    </row>
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>430</v>
       </c>
       <c r="B258" t="s">
         <v>8</v>
       </c>
+      <c r="C258" t="s">
+        <v>325</v>
+      </c>
       <c r="D258" t="s">
-        <v>326</v>
+        <v>422</v>
       </c>
       <c r="E258" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="F258" t="s">
-        <v>328</v>
-      </c>
-      <c r="G258" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>431</v>
       </c>
       <c r="B259" t="s">
         <v>8</v>
       </c>
+      <c r="C259" t="s">
+        <v>426</v>
+      </c>
       <c r="D259" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E259" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="F259" t="s">
         <v>427</v>
       </c>
-      <c r="G259" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>432</v>
       </c>
       <c r="B260" t="s">
         <v>8</v>
       </c>
+      <c r="C260" t="s">
+        <v>163</v>
+      </c>
       <c r="D260" t="s">
-        <v>163</v>
+        <v>422</v>
       </c>
       <c r="E260" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="F260" t="s">
-        <v>164</v>
-      </c>
-      <c r="G260" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>433</v>
       </c>
       <c r="B261" t="s">
         <v>8</v>
       </c>
+      <c r="C261" t="s">
+        <v>434</v>
+      </c>
       <c r="D261" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="E261" t="s">
-        <v>422</v>
+        <v>196</v>
       </c>
       <c r="F261" t="s">
         <v>435</v>
       </c>
-      <c r="G261" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7">
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>436</v>
       </c>
       <c r="B262" t="s">
         <v>8</v>
       </c>
+      <c r="C262" t="s">
+        <v>163</v>
+      </c>
       <c r="D262" t="s">
-        <v>163</v>
+        <v>422</v>
       </c>
       <c r="E262" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="F262" t="s">
-        <v>164</v>
-      </c>
-      <c r="G262" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>437</v>
       </c>
       <c r="B263" t="s">
         <v>8</v>
       </c>
+      <c r="C263" t="s">
+        <v>438</v>
+      </c>
       <c r="D263" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="E263" t="s">
-        <v>422</v>
+        <v>183</v>
       </c>
       <c r="F263" t="s">
         <v>439</v>
       </c>
-      <c r="G263" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>440</v>
       </c>
       <c r="B264" t="s">
         <v>8</v>
       </c>
+      <c r="C264" t="s">
+        <v>31</v>
+      </c>
       <c r="D264" t="s">
-        <v>31</v>
+        <v>422</v>
       </c>
       <c r="E264" t="s">
-        <v>422</v>
+        <v>32</v>
       </c>
       <c r="F264" t="s">
-        <v>32</v>
-      </c>
-      <c r="G264" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>441</v>
       </c>
       <c r="B265" t="s">
         <v>8</v>
       </c>
+      <c r="C265" t="s">
+        <v>9</v>
+      </c>
       <c r="D265" t="s">
-        <v>10</v>
+        <v>422</v>
       </c>
       <c r="E265" t="s">
-        <v>422</v>
+        <v>11</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
       </c>
-      <c r="G265" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>442</v>
       </c>
       <c r="B266" t="s">
         <v>8</v>
       </c>
+      <c r="C266" t="s">
+        <v>443</v>
+      </c>
       <c r="D266" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="E266" t="s">
-        <v>422</v>
+        <v>114</v>
       </c>
       <c r="F266" t="s">
         <v>444</v>
       </c>
-      <c r="G266" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7">
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>445</v>
       </c>
       <c r="B267" t="s">
         <v>8</v>
       </c>
+      <c r="C267" t="s">
+        <v>118</v>
+      </c>
       <c r="D267" t="s">
-        <v>118</v>
+        <v>446</v>
       </c>
       <c r="E267" t="s">
-        <v>446</v>
+        <v>114</v>
       </c>
       <c r="F267" t="s">
         <v>119</v>
       </c>
-      <c r="G267" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7">
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>447</v>
       </c>
       <c r="B268" t="s">
         <v>8</v>
       </c>
+      <c r="C268" t="s">
+        <v>202</v>
+      </c>
       <c r="D268" t="s">
-        <v>202</v>
+        <v>448</v>
       </c>
       <c r="E268" t="s">
-        <v>448</v>
+        <v>183</v>
       </c>
       <c r="F268" t="s">
         <v>204</v>
       </c>
-      <c r="G268" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>449</v>
       </c>
       <c r="B269" t="s">
         <v>8</v>
       </c>
+      <c r="C269" t="s">
+        <v>118</v>
+      </c>
       <c r="D269" t="s">
-        <v>118</v>
+        <v>450</v>
       </c>
       <c r="E269" t="s">
-        <v>450</v>
+        <v>114</v>
       </c>
       <c r="F269" t="s">
         <v>119</v>
       </c>
-      <c r="G269" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7">
+    </row>
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>451</v>
       </c>
       <c r="B270" t="s">
         <v>8</v>
       </c>
+      <c r="C270" t="s">
+        <v>118</v>
+      </c>
       <c r="D270" t="s">
-        <v>118</v>
+        <v>450</v>
       </c>
       <c r="E270" t="s">
-        <v>450</v>
+        <v>114</v>
       </c>
       <c r="F270" t="s">
         <v>119</v>
       </c>
-      <c r="G270" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7">
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>452</v>
       </c>
       <c r="B271" t="s">
         <v>8</v>
       </c>
+      <c r="C271" t="s">
+        <v>453</v>
+      </c>
       <c r="D271" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E271" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F271" t="s">
         <v>455</v>
       </c>
-      <c r="G271" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7">
+    </row>
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>456</v>
       </c>
       <c r="B272" t="s">
         <v>8</v>
       </c>
+      <c r="C272" t="s">
+        <v>453</v>
+      </c>
       <c r="D272" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E272" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F272" t="s">
         <v>455</v>
       </c>
-      <c r="G272" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7">
+    </row>
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>457</v>
       </c>
       <c r="B273" t="s">
         <v>8</v>
       </c>
+      <c r="C273" t="s">
+        <v>453</v>
+      </c>
       <c r="D273" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E273" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F273" t="s">
         <v>455</v>
       </c>
-      <c r="G273" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7">
+    </row>
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>458</v>
       </c>
       <c r="B274" t="s">
         <v>8</v>
       </c>
+      <c r="C274" t="s">
+        <v>453</v>
+      </c>
       <c r="D274" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E274" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F274" t="s">
         <v>455</v>
       </c>
-      <c r="G274" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7">
+    </row>
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>459</v>
       </c>
       <c r="B275" t="s">
         <v>8</v>
       </c>
+      <c r="C275" t="s">
+        <v>453</v>
+      </c>
       <c r="D275" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E275" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F275" t="s">
         <v>455</v>
       </c>
-      <c r="G275" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7">
+    </row>
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>460</v>
       </c>
       <c r="B276" t="s">
         <v>8</v>
       </c>
+      <c r="C276" t="s">
+        <v>453</v>
+      </c>
       <c r="D276" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E276" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F276" t="s">
         <v>455</v>
       </c>
-      <c r="G276" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7">
+    </row>
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>461</v>
       </c>
       <c r="B277" t="s">
         <v>8</v>
       </c>
+      <c r="C277" t="s">
+        <v>453</v>
+      </c>
       <c r="D277" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E277" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="F277" t="s">
         <v>455</v>
       </c>
-      <c r="G277" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7">
+    </row>
+    <row r="278" spans="1:6">
       <c r="A278" t="s">
         <v>462</v>
       </c>
       <c r="B278" t="s">
         <v>8</v>
       </c>
+      <c r="C278" t="s">
+        <v>202</v>
+      </c>
       <c r="D278" t="s">
-        <v>202</v>
+        <v>463</v>
       </c>
       <c r="E278" t="s">
-        <v>463</v>
+        <v>183</v>
       </c>
       <c r="F278" t="s">
         <v>204</v>
       </c>
-      <c r="G278" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
+    </row>
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>464</v>
       </c>
       <c r="B279" t="s">
         <v>8</v>
       </c>
+      <c r="C279" t="s">
+        <v>51</v>
+      </c>
       <c r="D279" t="s">
-        <v>52</v>
+        <v>463</v>
       </c>
       <c r="E279" t="s">
-        <v>463</v>
+        <v>32</v>
       </c>
       <c r="F279" t="s">
-        <v>54</v>
-      </c>
-      <c r="G279" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280" t="s">
         <v>465</v>
       </c>
       <c r="B280" t="s">
         <v>8</v>
       </c>
+      <c r="C280" t="s">
+        <v>9</v>
+      </c>
       <c r="D280" t="s">
-        <v>10</v>
+        <v>463</v>
       </c>
       <c r="E280" t="s">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
       </c>
-      <c r="G280" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281" t="s">
         <v>466</v>
       </c>
       <c r="B281" t="s">
         <v>8</v>
       </c>
+      <c r="C281" t="s">
+        <v>170</v>
+      </c>
       <c r="D281" t="s">
-        <v>170</v>
+        <v>463</v>
       </c>
       <c r="E281" t="s">
-        <v>463</v>
+        <v>114</v>
       </c>
       <c r="F281" t="s">
         <v>171</v>
       </c>
-      <c r="G281" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7">
+    </row>
+    <row r="282" spans="1:6">
       <c r="A282" t="s">
         <v>467</v>
       </c>
       <c r="B282" t="s">
         <v>8</v>
       </c>
+      <c r="C282" t="s">
+        <v>124</v>
+      </c>
       <c r="D282" t="s">
-        <v>124</v>
+        <v>463</v>
       </c>
       <c r="E282" t="s">
-        <v>463</v>
+        <v>125</v>
       </c>
       <c r="F282" t="s">
-        <v>125</v>
-      </c>
-      <c r="G282" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" spans="1:6">
       <c r="A283" t="s">
         <v>468</v>
       </c>
       <c r="B283" t="s">
         <v>8</v>
       </c>
+      <c r="C283" t="s">
+        <v>363</v>
+      </c>
       <c r="D283" t="s">
-        <v>364</v>
+        <v>469</v>
       </c>
       <c r="E283" t="s">
-        <v>469</v>
+        <v>164</v>
       </c>
       <c r="F283" t="s">
-        <v>399</v>
-      </c>
-      <c r="G283" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
       <c r="A284" t="s">
         <v>470</v>
       </c>
       <c r="B284" t="s">
         <v>8</v>
       </c>
+      <c r="C284" t="s">
+        <v>124</v>
+      </c>
       <c r="D284" t="s">
-        <v>124</v>
+        <v>471</v>
       </c>
       <c r="E284" t="s">
-        <v>471</v>
+        <v>125</v>
       </c>
       <c r="F284" t="s">
-        <v>125</v>
-      </c>
-      <c r="G284" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" spans="1:6">
       <c r="A285" t="s">
         <v>472</v>
       </c>
       <c r="B285" t="s">
         <v>8</v>
       </c>
+      <c r="C285" t="s">
+        <v>170</v>
+      </c>
       <c r="D285" t="s">
-        <v>170</v>
+        <v>473</v>
       </c>
       <c r="E285" t="s">
-        <v>473</v>
+        <v>114</v>
       </c>
       <c r="F285" t="s">
         <v>171</v>
       </c>
-      <c r="G285" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
+    </row>
+    <row r="286" spans="1:6">
       <c r="A286" t="s">
         <v>474</v>
       </c>
       <c r="B286" t="s">
         <v>8</v>
       </c>
+      <c r="C286" t="s">
+        <v>438</v>
+      </c>
       <c r="D286" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="E286" t="s">
-        <v>475</v>
+        <v>183</v>
       </c>
       <c r="F286" t="s">
         <v>439</v>
       </c>
-      <c r="G286" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
+    </row>
+    <row r="287" spans="1:6">
       <c r="A287" t="s">
         <v>476</v>
       </c>
       <c r="B287" t="s">
         <v>8</v>
       </c>
+      <c r="C287" t="s">
+        <v>438</v>
+      </c>
       <c r="D287" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="E287" t="s">
-        <v>475</v>
+        <v>183</v>
       </c>
       <c r="F287" t="s">
         <v>439</v>
       </c>
-      <c r="G287" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7">
+    </row>
+    <row r="288" spans="1:6">
       <c r="A288" t="s">
         <v>477</v>
       </c>
       <c r="B288" t="s">
         <v>8</v>
       </c>
+      <c r="C288" t="s">
+        <v>41</v>
+      </c>
       <c r="D288" t="s">
-        <v>41</v>
+        <v>475</v>
       </c>
       <c r="E288" t="s">
-        <v>475</v>
+        <v>11</v>
       </c>
       <c r="F288" t="s">
         <v>42</v>
       </c>
-      <c r="G288" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7">
+    </row>
+    <row r="289" spans="1:6">
       <c r="A289" t="s">
         <v>478</v>
       </c>
       <c r="B289" t="s">
         <v>8</v>
       </c>
+      <c r="C289" t="s">
+        <v>31</v>
+      </c>
       <c r="D289" t="s">
-        <v>31</v>
+        <v>475</v>
       </c>
       <c r="E289" t="s">
-        <v>475</v>
+        <v>32</v>
       </c>
       <c r="F289" t="s">
-        <v>32</v>
-      </c>
-      <c r="G289" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" spans="1:6">
       <c r="A290" t="s">
         <v>479</v>
       </c>
       <c r="B290" t="s">
         <v>8</v>
       </c>
+      <c r="C290" t="s">
+        <v>31</v>
+      </c>
       <c r="D290" t="s">
-        <v>31</v>
+        <v>475</v>
       </c>
       <c r="E290" t="s">
-        <v>475</v>
+        <v>32</v>
       </c>
       <c r="F290" t="s">
-        <v>32</v>
-      </c>
-      <c r="G290" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" spans="1:6">
       <c r="A291" t="s">
         <v>480</v>
       </c>
       <c r="B291" t="s">
         <v>8</v>
       </c>
+      <c r="C291" t="s">
+        <v>170</v>
+      </c>
       <c r="D291" t="s">
-        <v>170</v>
+        <v>475</v>
       </c>
       <c r="E291" t="s">
-        <v>475</v>
+        <v>114</v>
       </c>
       <c r="F291" t="s">
         <v>171</v>
       </c>
-      <c r="G291" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7">
+    </row>
+    <row r="292" spans="1:6">
       <c r="A292" t="s">
         <v>481</v>
       </c>
       <c r="B292" t="s">
         <v>8</v>
       </c>
+      <c r="C292" t="s">
+        <v>170</v>
+      </c>
       <c r="D292" t="s">
-        <v>170</v>
+        <v>475</v>
       </c>
       <c r="E292" t="s">
-        <v>475</v>
+        <v>114</v>
       </c>
       <c r="F292" t="s">
         <v>171</v>
       </c>
-      <c r="G292" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7">
+    </row>
+    <row r="293" spans="1:6">
       <c r="A293" t="s">
         <v>482</v>
       </c>
       <c r="B293" t="s">
         <v>8</v>
       </c>
+      <c r="C293" t="s">
+        <v>170</v>
+      </c>
       <c r="D293" t="s">
-        <v>170</v>
+        <v>475</v>
       </c>
       <c r="E293" t="s">
-        <v>475</v>
+        <v>114</v>
       </c>
       <c r="F293" t="s">
         <v>171</v>
       </c>
-      <c r="G293" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7">
+    </row>
+    <row r="294" spans="1:6">
       <c r="A294" t="s">
         <v>483</v>
       </c>
       <c r="B294" t="s">
         <v>8</v>
       </c>
+      <c r="C294" t="s">
+        <v>170</v>
+      </c>
       <c r="D294" t="s">
-        <v>170</v>
+        <v>475</v>
       </c>
       <c r="E294" t="s">
-        <v>475</v>
+        <v>114</v>
       </c>
       <c r="F294" t="s">
         <v>171</v>
       </c>
-      <c r="G294" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7">
+    </row>
+    <row r="295" spans="1:6">
       <c r="A295" t="s">
         <v>484</v>
       </c>
       <c r="B295" t="s">
         <v>8</v>
       </c>
+      <c r="C295" t="s">
+        <v>170</v>
+      </c>
       <c r="D295" t="s">
-        <v>170</v>
+        <v>485</v>
       </c>
       <c r="E295" t="s">
-        <v>485</v>
+        <v>114</v>
       </c>
       <c r="F295" t="s">
         <v>171</v>
       </c>
-      <c r="G295" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7">
+    </row>
+    <row r="296" spans="1:6">
       <c r="A296" t="s">
         <v>486</v>
       </c>
       <c r="B296" t="s">
         <v>8</v>
       </c>
+      <c r="C296" t="s">
+        <v>170</v>
+      </c>
       <c r="D296" t="s">
-        <v>170</v>
+        <v>485</v>
       </c>
       <c r="E296" t="s">
-        <v>485</v>
+        <v>114</v>
       </c>
       <c r="F296" t="s">
         <v>171</v>
-      </c>
-      <c r="G296" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,72 +22,72 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
+    <t>codeforiati:category-code</t>
   </si>
   <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>110</t>
+    <t>111</t>
   </si>
   <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>112</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -139,45 +139,45 @@
     <t>11330</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>114</t>
   </si>
   <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -187,21 +187,21 @@
     <t>12182</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>150</t>
+    <t>151</t>
   </si>
   <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,27 +811,27 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -841,12 +841,12 @@
     <t>23112</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -991,15 +991,15 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1105,15 +1105,15 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>60020</t>
@@ -1869,10 +1869,10 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -1915,10 +1915,10 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -1938,13 +1938,13 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1964,10 +1964,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1984,13 +1984,13 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2007,13 +2007,13 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2024,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2056,10 +2056,10 @@
         <v>32</v>
       </c>
       <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2076,13 +2076,13 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2122,13 +2122,13 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2145,13 +2145,13 @@
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2168,13 +2168,13 @@
         <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2191,13 +2191,13 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G17" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2214,13 +2214,13 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2237,13 +2237,13 @@
         <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G19" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2260,13 +2260,13 @@
         <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G20" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2283,13 +2283,13 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G21" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2309,10 +2309,10 @@
         <v>32</v>
       </c>
       <c r="F22" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" t="s">
         <v>33</v>
-      </c>
-      <c r="G22" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2329,13 +2329,13 @@
         <v>52</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G23" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2355,10 +2355,10 @@
         <v>32</v>
       </c>
       <c r="F24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24" t="s">
         <v>33</v>
-      </c>
-      <c r="G24" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2378,10 +2378,10 @@
         <v>32</v>
       </c>
       <c r="F25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" t="s">
         <v>33</v>
-      </c>
-      <c r="G25" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2401,10 +2401,10 @@
         <v>32</v>
       </c>
       <c r="F26" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" t="s">
         <v>33</v>
-      </c>
-      <c r="G26" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2424,10 +2424,10 @@
         <v>32</v>
       </c>
       <c r="F27" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27" t="s">
         <v>33</v>
-      </c>
-      <c r="G27" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2447,10 +2447,10 @@
         <v>32</v>
       </c>
       <c r="F28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" t="s">
         <v>33</v>
-      </c>
-      <c r="G28" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2470,10 +2470,10 @@
         <v>32</v>
       </c>
       <c r="F29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29" t="s">
         <v>33</v>
-      </c>
-      <c r="G29" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2490,13 +2490,13 @@
         <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="G30" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2516,10 +2516,10 @@
         <v>32</v>
       </c>
       <c r="F31" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" t="s">
         <v>33</v>
-      </c>
-      <c r="G31" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2539,10 +2539,10 @@
         <v>32</v>
       </c>
       <c r="F32" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" t="s">
         <v>33</v>
-      </c>
-      <c r="G32" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2562,10 +2562,10 @@
         <v>32</v>
       </c>
       <c r="F33" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" t="s">
         <v>33</v>
-      </c>
-      <c r="G33" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2585,10 +2585,10 @@
         <v>32</v>
       </c>
       <c r="F34" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" t="s">
         <v>33</v>
-      </c>
-      <c r="G34" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2608,10 +2608,10 @@
         <v>32</v>
       </c>
       <c r="F35" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" t="s">
         <v>33</v>
-      </c>
-      <c r="G35" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2628,13 +2628,13 @@
         <v>52</v>
       </c>
       <c r="E36" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F36" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2653,7 +2653,7 @@
       <c r="E37" t="s">
         <v>32</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
       <c r="E38" t="s">
         <v>32</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       <c r="E39" t="s">
         <v>32</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       <c r="E40" t="s">
         <v>32</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2731,10 +2731,10 @@
         <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" t="s">
         <v>53</v>
+      </c>
+      <c r="G41" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2751,10 +2751,10 @@
         <v>83</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F42" t="s">
         <v>58</v>
+      </c>
+      <c r="G42" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2773,7 +2773,7 @@
       <c r="E43" t="s">
         <v>92</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       <c r="E44" t="s">
         <v>96</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       <c r="E45" t="s">
         <v>92</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       <c r="E46" t="s">
         <v>92</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2851,10 +2851,10 @@
         <v>91</v>
       </c>
       <c r="E47" t="s">
-        <v>96</v>
-      </c>
-      <c r="F47" t="s">
         <v>102</v>
+      </c>
+      <c r="G47" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2873,7 +2873,7 @@
       <c r="E48" t="s">
         <v>92</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       <c r="E49" t="s">
         <v>92</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2911,10 +2911,10 @@
         <v>91</v>
       </c>
       <c r="E50" t="s">
-        <v>96</v>
-      </c>
-      <c r="F50" t="s">
         <v>102</v>
+      </c>
+      <c r="G50" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2933,7 +2933,7 @@
       <c r="E51" t="s">
         <v>92</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2951,10 +2951,10 @@
         <v>91</v>
       </c>
       <c r="E52" t="s">
-        <v>96</v>
-      </c>
-      <c r="F52" t="s">
         <v>109</v>
+      </c>
+      <c r="G52" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2973,8 +2973,8 @@
       <c r="E53" t="s">
         <v>11</v>
       </c>
-      <c r="F53" t="s">
-        <v>12</v>
+      <c r="G53" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3014,10 +3014,10 @@
         <v>113</v>
       </c>
       <c r="E55" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F55" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G55" t="s">
         <v>116</v>
@@ -3037,10 +3037,10 @@
         <v>113</v>
       </c>
       <c r="E56" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F56" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G56" t="s">
         <v>116</v>
@@ -3063,10 +3063,10 @@
         <v>125</v>
       </c>
       <c r="F57" t="s">
+        <v>115</v>
+      </c>
+      <c r="G57" t="s">
         <v>126</v>
-      </c>
-      <c r="G57" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3083,10 +3083,10 @@
         <v>113</v>
       </c>
       <c r="E58" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F58" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G58" t="s">
         <v>116</v>
@@ -3106,10 +3106,10 @@
         <v>113</v>
       </c>
       <c r="E59" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F59" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G59" t="s">
         <v>116</v>
@@ -3129,10 +3129,10 @@
         <v>113</v>
       </c>
       <c r="E60" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F60" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G60" t="s">
         <v>116</v>
@@ -3152,10 +3152,10 @@
         <v>113</v>
       </c>
       <c r="E61" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F61" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
         <v>116</v>
@@ -3175,10 +3175,10 @@
         <v>113</v>
       </c>
       <c r="E62" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F62" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G62" t="s">
         <v>116</v>
@@ -3192,16 +3192,16 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D63" t="s">
         <v>113</v>
       </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G63" t="s">
         <v>116</v>
@@ -3215,16 +3215,16 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D64" t="s">
         <v>113</v>
       </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F64" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G64" t="s">
         <v>116</v>
@@ -3244,10 +3244,10 @@
         <v>113</v>
       </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="F65" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="G65" t="s">
         <v>116</v>
@@ -3290,10 +3290,10 @@
         <v>113</v>
       </c>
       <c r="E67" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F67" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>116</v>
@@ -3307,7 +3307,7 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="D68" t="s">
         <v>113</v>
@@ -3316,7 +3316,7 @@
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="G68" t="s">
         <v>116</v>
@@ -3330,7 +3330,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D69" t="s">
         <v>113</v>
@@ -3339,7 +3339,7 @@
         <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G69" t="s">
         <v>116</v>
@@ -3359,10 +3359,10 @@
         <v>113</v>
       </c>
       <c r="E70" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F70" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G70" t="s">
         <v>116</v>
@@ -3382,10 +3382,10 @@
         <v>113</v>
       </c>
       <c r="E71" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F71" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G71" t="s">
         <v>116</v>
@@ -3428,13 +3428,13 @@
         <v>113</v>
       </c>
       <c r="E73" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="F73" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3451,13 +3451,13 @@
         <v>113</v>
       </c>
       <c r="E74" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="F74" t="s">
-        <v>152</v>
+        <v>115</v>
       </c>
       <c r="G74" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3474,13 +3474,13 @@
         <v>113</v>
       </c>
       <c r="E75" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="F75" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="G75" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3497,13 +3497,13 @@
         <v>113</v>
       </c>
       <c r="E76" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="F76" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3520,13 +3520,13 @@
         <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="F77" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="G77" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3543,13 +3543,13 @@
         <v>113</v>
       </c>
       <c r="E78" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="F78" t="s">
-        <v>152</v>
+        <v>115</v>
       </c>
       <c r="G78" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3566,13 +3566,13 @@
         <v>113</v>
       </c>
       <c r="E79" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="F79" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3592,10 +3592,10 @@
         <v>164</v>
       </c>
       <c r="F80" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="G80" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3615,10 +3615,10 @@
         <v>164</v>
       </c>
       <c r="F81" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="G81" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3638,10 +3638,10 @@
         <v>164</v>
       </c>
       <c r="F82" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="G82" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
         <v>113</v>
@@ -3661,7 +3661,7 @@
         <v>114</v>
       </c>
       <c r="F83" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G83" t="s">
         <v>116</v>
@@ -3681,10 +3681,10 @@
         <v>113</v>
       </c>
       <c r="E84" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="F84" t="s">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="G84" t="s">
         <v>116</v>
@@ -3698,16 +3698,16 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
         <v>113</v>
       </c>
       <c r="E85" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F85" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="G85" t="s">
         <v>116</v>
@@ -3727,13 +3727,13 @@
         <v>113</v>
       </c>
       <c r="E86" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F86" t="s">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="G86" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,16 +3744,16 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D87" t="s">
         <v>113</v>
       </c>
       <c r="E87" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F87" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="G87" t="s">
         <v>116</v>
@@ -3773,10 +3773,10 @@
         <v>113</v>
       </c>
       <c r="E88" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F88" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G88" t="s">
         <v>116</v>
@@ -3796,10 +3796,10 @@
         <v>113</v>
       </c>
       <c r="E89" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F89" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G89" t="s">
         <v>116</v>
@@ -3822,10 +3822,10 @@
         <v>125</v>
       </c>
       <c r="F90" t="s">
+        <v>115</v>
+      </c>
+      <c r="G90" t="s">
         <v>126</v>
-      </c>
-      <c r="G90" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3845,10 +3845,10 @@
         <v>183</v>
       </c>
       <c r="F91" t="s">
+        <v>115</v>
+      </c>
+      <c r="G91" t="s">
         <v>184</v>
-      </c>
-      <c r="G91" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3868,10 +3868,10 @@
         <v>125</v>
       </c>
       <c r="F92" t="s">
+        <v>115</v>
+      </c>
+      <c r="G92" t="s">
         <v>126</v>
-      </c>
-      <c r="G92" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3888,10 +3888,10 @@
         <v>113</v>
       </c>
       <c r="E93" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F93" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G93" t="s">
         <v>116</v>
@@ -3914,10 +3914,10 @@
         <v>125</v>
       </c>
       <c r="F94" t="s">
+        <v>115</v>
+      </c>
+      <c r="G94" t="s">
         <v>126</v>
-      </c>
-      <c r="G94" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3934,10 +3934,10 @@
         <v>113</v>
       </c>
       <c r="E95" t="s">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="F95" t="s">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="G95" t="s">
         <v>116</v>
@@ -3960,10 +3960,10 @@
         <v>125</v>
       </c>
       <c r="F96" t="s">
+        <v>192</v>
+      </c>
+      <c r="G96" t="s">
         <v>126</v>
-      </c>
-      <c r="G96" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3983,10 +3983,10 @@
         <v>125</v>
       </c>
       <c r="F97" t="s">
+        <v>192</v>
+      </c>
+      <c r="G97" t="s">
         <v>126</v>
-      </c>
-      <c r="G97" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4006,10 +4006,10 @@
         <v>196</v>
       </c>
       <c r="F98" t="s">
+        <v>192</v>
+      </c>
+      <c r="G98" t="s">
         <v>197</v>
-      </c>
-      <c r="G98" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4029,10 +4029,10 @@
         <v>125</v>
       </c>
       <c r="F99" t="s">
+        <v>192</v>
+      </c>
+      <c r="G99" t="s">
         <v>126</v>
-      </c>
-      <c r="G99" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4049,13 +4049,13 @@
         <v>113</v>
       </c>
       <c r="E100" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="F100" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="G100" t="s">
-        <v>192</v>
+        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4075,10 +4075,10 @@
         <v>125</v>
       </c>
       <c r="F101" t="s">
+        <v>192</v>
+      </c>
+      <c r="G101" t="s">
         <v>126</v>
-      </c>
-      <c r="G101" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4095,10 +4095,10 @@
         <v>203</v>
       </c>
       <c r="E102" t="s">
-        <v>183</v>
-      </c>
-      <c r="F102" t="s">
         <v>204</v>
+      </c>
+      <c r="G102" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4115,10 +4115,10 @@
         <v>203</v>
       </c>
       <c r="E103" t="s">
-        <v>183</v>
-      </c>
-      <c r="F103" t="s">
         <v>204</v>
+      </c>
+      <c r="G103" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4135,10 +4135,10 @@
         <v>203</v>
       </c>
       <c r="E104" t="s">
-        <v>183</v>
-      </c>
-      <c r="F104" t="s">
         <v>204</v>
+      </c>
+      <c r="G104" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4155,10 +4155,10 @@
         <v>203</v>
       </c>
       <c r="E105" t="s">
-        <v>183</v>
-      </c>
-      <c r="F105" t="s">
         <v>209</v>
+      </c>
+      <c r="G105" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4175,10 +4175,10 @@
         <v>203</v>
       </c>
       <c r="E106" t="s">
-        <v>183</v>
-      </c>
-      <c r="F106" t="s">
         <v>204</v>
+      </c>
+      <c r="G106" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4197,7 +4197,7 @@
       <c r="E107" t="s">
         <v>183</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>184</v>
       </c>
     </row>
@@ -4215,10 +4215,10 @@
         <v>203</v>
       </c>
       <c r="E108" t="s">
-        <v>183</v>
-      </c>
-      <c r="F108" t="s">
         <v>214</v>
+      </c>
+      <c r="G108" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4235,10 +4235,10 @@
         <v>203</v>
       </c>
       <c r="E109" t="s">
-        <v>92</v>
-      </c>
-      <c r="F109" t="s">
         <v>217</v>
+      </c>
+      <c r="G109" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4255,10 +4255,10 @@
         <v>203</v>
       </c>
       <c r="E110" t="s">
-        <v>92</v>
-      </c>
-      <c r="F110" t="s">
         <v>220</v>
+      </c>
+      <c r="G110" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4275,10 +4275,10 @@
         <v>203</v>
       </c>
       <c r="E111" t="s">
-        <v>183</v>
-      </c>
-      <c r="F111" t="s">
         <v>204</v>
+      </c>
+      <c r="G111" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4297,11 +4297,11 @@
       <c r="E112" t="s">
         <v>224</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
         <v>226</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D113" t="s">
         <v>203</v>
@@ -4317,11 +4317,11 @@
       <c r="E113" t="s">
         <v>114</v>
       </c>
-      <c r="F113" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="G113" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -4335,13 +4335,13 @@
         <v>203</v>
       </c>
       <c r="E114" t="s">
-        <v>125</v>
-      </c>
-      <c r="F114" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="G114" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
         <v>228</v>
       </c>
@@ -4357,11 +4357,11 @@
       <c r="E115" t="s">
         <v>183</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>229</v>
       </c>
@@ -4375,13 +4375,13 @@
         <v>203</v>
       </c>
       <c r="E116" t="s">
-        <v>224</v>
-      </c>
-      <c r="F116" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="G116" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>232</v>
       </c>
@@ -4397,11 +4397,11 @@
       <c r="E117" t="s">
         <v>224</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>233</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
       <c r="D118" t="s">
         <v>203</v>
@@ -4417,11 +4417,11 @@
       <c r="E118" t="s">
         <v>164</v>
       </c>
-      <c r="F118" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+      <c r="G118" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>235</v>
       </c>
@@ -4437,11 +4437,11 @@
       <c r="E119" t="s">
         <v>183</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>236</v>
       </c>
@@ -4455,13 +4455,13 @@
         <v>237</v>
       </c>
       <c r="E120" t="s">
-        <v>114</v>
-      </c>
-      <c r="F120" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="G120" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>238</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D121" t="s">
         <v>237</v>
@@ -4477,11 +4477,11 @@
       <c r="E121" t="s">
         <v>114</v>
       </c>
-      <c r="F121" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="G121" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>239</v>
       </c>
@@ -4495,13 +4495,13 @@
         <v>237</v>
       </c>
       <c r="E122" t="s">
-        <v>114</v>
-      </c>
-      <c r="F122" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="G122" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>240</v>
       </c>
@@ -4515,13 +4515,13 @@
         <v>237</v>
       </c>
       <c r="E123" t="s">
-        <v>114</v>
-      </c>
-      <c r="F123" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="G123" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>241</v>
       </c>
@@ -4535,13 +4535,13 @@
         <v>237</v>
       </c>
       <c r="E124" t="s">
-        <v>164</v>
-      </c>
-      <c r="F124" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="G124" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -4555,13 +4555,13 @@
         <v>237</v>
       </c>
       <c r="E125" t="s">
-        <v>164</v>
-      </c>
-      <c r="F125" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="G125" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -4575,13 +4575,13 @@
         <v>237</v>
       </c>
       <c r="E126" t="s">
-        <v>164</v>
-      </c>
-      <c r="F126" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="G126" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>246</v>
       </c>
@@ -4595,13 +4595,13 @@
         <v>237</v>
       </c>
       <c r="E127" t="s">
-        <v>164</v>
-      </c>
-      <c r="F127" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="128" spans="1:6">
+      <c r="G127" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -4615,10 +4615,10 @@
         <v>237</v>
       </c>
       <c r="E128" t="s">
-        <v>164</v>
-      </c>
-      <c r="F128" t="s">
         <v>243</v>
+      </c>
+      <c r="G128" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D129" t="s">
         <v>237</v>
       </c>
       <c r="E129" t="s">
-        <v>164</v>
-      </c>
-      <c r="F129" t="s">
-        <v>249</v>
+        <v>243</v>
+      </c>
+      <c r="G129" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D130" t="s">
         <v>237</v>
       </c>
       <c r="E130" t="s">
-        <v>164</v>
-      </c>
-      <c r="F130" t="s">
-        <v>251</v>
+        <v>243</v>
+      </c>
+      <c r="G130" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D131" t="s">
         <v>237</v>
       </c>
       <c r="E131" t="s">
-        <v>164</v>
-      </c>
-      <c r="F131" t="s">
-        <v>253</v>
+        <v>243</v>
+      </c>
+      <c r="G131" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4695,10 +4695,10 @@
         <v>237</v>
       </c>
       <c r="E132" t="s">
-        <v>164</v>
-      </c>
-      <c r="F132" t="s">
         <v>256</v>
+      </c>
+      <c r="G132" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4715,10 +4715,10 @@
         <v>237</v>
       </c>
       <c r="E133" t="s">
-        <v>114</v>
-      </c>
-      <c r="F133" t="s">
         <v>190</v>
+      </c>
+      <c r="G133" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4735,10 +4735,10 @@
         <v>259</v>
       </c>
       <c r="E134" t="s">
-        <v>164</v>
-      </c>
-      <c r="F134" t="s">
         <v>176</v>
+      </c>
+      <c r="G134" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4755,10 +4755,10 @@
         <v>259</v>
       </c>
       <c r="E135" t="s">
-        <v>164</v>
-      </c>
-      <c r="F135" t="s">
         <v>176</v>
+      </c>
+      <c r="G135" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4775,10 +4775,10 @@
         <v>259</v>
       </c>
       <c r="E136" t="s">
-        <v>164</v>
-      </c>
-      <c r="F136" t="s">
         <v>176</v>
+      </c>
+      <c r="G136" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4795,10 +4795,10 @@
         <v>259</v>
       </c>
       <c r="E137" t="s">
-        <v>164</v>
-      </c>
-      <c r="F137" t="s">
         <v>176</v>
+      </c>
+      <c r="G137" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4815,10 +4815,10 @@
         <v>259</v>
       </c>
       <c r="E138" t="s">
-        <v>164</v>
-      </c>
-      <c r="F138" t="s">
         <v>176</v>
+      </c>
+      <c r="G138" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4835,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="E139" t="s">
-        <v>224</v>
-      </c>
-      <c r="F139" t="s">
         <v>266</v>
+      </c>
+      <c r="G139" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4855,10 +4855,10 @@
         <v>259</v>
       </c>
       <c r="E140" t="s">
-        <v>164</v>
-      </c>
-      <c r="F140" t="s">
         <v>176</v>
+      </c>
+      <c r="G140" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4875,13 +4875,13 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G141" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4898,13 +4898,13 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G142" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4921,13 +4921,13 @@
         <v>270</v>
       </c>
       <c r="E143" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="F143" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G143" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4944,13 +4944,13 @@
         <v>270</v>
       </c>
       <c r="E144" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="F144" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G144" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4967,13 +4967,13 @@
         <v>270</v>
       </c>
       <c r="E145" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="F145" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G145" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4990,13 +4990,13 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G146" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5013,13 +5013,13 @@
         <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G147" t="s">
-        <v>281</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5036,13 +5036,13 @@
         <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G148" t="s">
-        <v>281</v>
+        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5059,13 +5059,13 @@
         <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G149" t="s">
-        <v>281</v>
+        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5082,13 +5082,13 @@
         <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G150" t="s">
-        <v>281</v>
+        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5105,13 +5105,13 @@
         <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G151" t="s">
-        <v>281</v>
+        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5128,13 +5128,13 @@
         <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G152" t="s">
-        <v>281</v>
+        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5151,13 +5151,13 @@
         <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G153" t="s">
-        <v>281</v>
+        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5174,13 +5174,13 @@
         <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G154" t="s">
-        <v>281</v>
+        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5197,13 +5197,13 @@
         <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G155" t="s">
-        <v>281</v>
+        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5220,13 +5220,13 @@
         <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G156" t="s">
-        <v>291</v>
+        <v>165</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D157" t="s">
         <v>270</v>
       </c>
       <c r="E157" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F157" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G157" t="s">
-        <v>291</v>
+        <v>165</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5266,13 +5266,13 @@
         <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G158" t="s">
-        <v>291</v>
+        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5289,13 +5289,13 @@
         <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G159" t="s">
-        <v>291</v>
+        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5312,13 +5312,13 @@
         <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G160" t="s">
-        <v>291</v>
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5335,13 +5335,13 @@
         <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G161" t="s">
-        <v>291</v>
+        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5358,13 +5358,13 @@
         <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="G162" t="s">
-        <v>299</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
         <v>270</v>
       </c>
       <c r="E163" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F163" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G163" t="s">
-        <v>302</v>
+        <v>165</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5404,13 +5404,13 @@
         <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="G164" t="s">
-        <v>304</v>
+        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5427,13 +5427,13 @@
         <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="G165" t="s">
-        <v>304</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5450,13 +5450,13 @@
         <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="G166" t="s">
-        <v>304</v>
+        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5473,13 +5473,13 @@
         <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="G167" t="s">
-        <v>304</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D168" t="s">
         <v>270</v>
       </c>
       <c r="E168" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F168" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G168" t="s">
-        <v>304</v>
+        <v>165</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D169" t="s">
         <v>270</v>
       </c>
       <c r="E169" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F169" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G169" t="s">
-        <v>304</v>
+        <v>165</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5542,13 +5542,13 @@
         <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="G170" t="s">
-        <v>304</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5567,7 +5567,7 @@
       <c r="E171" t="s">
         <v>164</v>
       </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5585,10 +5585,10 @@
         <v>313</v>
       </c>
       <c r="E172" t="s">
-        <v>114</v>
-      </c>
-      <c r="F172" t="s">
         <v>119</v>
+      </c>
+      <c r="G172" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5607,7 +5607,7 @@
       <c r="E173" t="s">
         <v>164</v>
       </c>
-      <c r="F173" t="s">
+      <c r="G173" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       <c r="E174" t="s">
         <v>164</v>
       </c>
-      <c r="F174" t="s">
+      <c r="G174" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       <c r="E175" t="s">
         <v>164</v>
       </c>
-      <c r="F175" t="s">
+      <c r="G175" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       <c r="E176" t="s">
         <v>164</v>
       </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       <c r="E177" t="s">
         <v>164</v>
       </c>
-      <c r="F177" t="s">
+      <c r="G177" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
       <c r="E178" t="s">
         <v>164</v>
       </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       <c r="E179" t="s">
         <v>164</v>
       </c>
-      <c r="F179" t="s">
+      <c r="G179" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       <c r="E180" t="s">
         <v>164</v>
       </c>
-      <c r="F180" t="s">
+      <c r="G180" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5765,13 +5765,13 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G181" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5788,13 +5788,13 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G182" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5811,13 +5811,13 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G183" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5834,13 +5834,13 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G184" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5857,13 +5857,13 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G185" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5880,13 +5880,13 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G186" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5903,13 +5903,13 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G187" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5926,13 +5926,13 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G188" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5949,13 +5949,13 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G189" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5972,13 +5972,13 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G190" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5995,13 +5995,13 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G191" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6018,13 +6018,13 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G192" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D193" t="s">
         <v>326</v>
       </c>
       <c r="E193" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="F193" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="G193" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6064,13 +6064,13 @@
         <v>326</v>
       </c>
       <c r="E194" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G194" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6087,13 +6087,13 @@
         <v>326</v>
       </c>
       <c r="E195" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G195" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6110,13 +6110,13 @@
         <v>326</v>
       </c>
       <c r="E196" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G196" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6133,13 +6133,13 @@
         <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G197" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6156,13 +6156,13 @@
         <v>326</v>
       </c>
       <c r="E198" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G198" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D199" t="s">
         <v>326</v>
       </c>
       <c r="E199" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F199" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G199" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D200" t="s">
         <v>326</v>
       </c>
       <c r="E200" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F200" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G200" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D201" t="s">
         <v>326</v>
       </c>
       <c r="E201" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F201" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G201" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D202" t="s">
         <v>326</v>
       </c>
       <c r="E202" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F202" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G202" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D203" t="s">
         <v>326</v>
       </c>
       <c r="E203" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="F203" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="G203" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D204" t="s">
         <v>326</v>
       </c>
       <c r="E204" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F204" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G204" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D205" t="s">
         <v>326</v>
       </c>
       <c r="E205" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F205" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G205" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D206" t="s">
         <v>326</v>
       </c>
       <c r="E206" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F206" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G206" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D207" t="s">
         <v>326</v>
       </c>
       <c r="E207" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F207" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G207" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D208" t="s">
         <v>326</v>
       </c>
       <c r="E208" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="F208" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="G208" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
         <v>326</v>
       </c>
       <c r="E209" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F209" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G209" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6432,13 +6432,13 @@
         <v>364</v>
       </c>
       <c r="E210" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G210" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6455,13 +6455,13 @@
         <v>364</v>
       </c>
       <c r="E211" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G211" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6478,13 +6478,13 @@
         <v>364</v>
       </c>
       <c r="E212" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G212" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6501,13 +6501,13 @@
         <v>364</v>
       </c>
       <c r="E213" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G213" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6524,13 +6524,13 @@
         <v>364</v>
       </c>
       <c r="E214" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G214" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D215" t="s">
         <v>364</v>
       </c>
       <c r="E215" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F215" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="G215" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6570,13 +6570,13 @@
         <v>364</v>
       </c>
       <c r="E216" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G216" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6593,13 +6593,13 @@
         <v>364</v>
       </c>
       <c r="E217" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G217" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6616,13 +6616,13 @@
         <v>364</v>
       </c>
       <c r="E218" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G218" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6639,13 +6639,13 @@
         <v>364</v>
       </c>
       <c r="E219" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G219" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D220" t="s">
         <v>364</v>
       </c>
       <c r="E220" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F220" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
       <c r="G220" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6685,13 +6685,13 @@
         <v>364</v>
       </c>
       <c r="E221" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G221" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6708,13 +6708,13 @@
         <v>364</v>
       </c>
       <c r="E222" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G222" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6731,13 +6731,13 @@
         <v>364</v>
       </c>
       <c r="E223" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G223" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6754,13 +6754,13 @@
         <v>364</v>
       </c>
       <c r="E224" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G224" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6777,13 +6777,13 @@
         <v>364</v>
       </c>
       <c r="E225" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G225" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6800,13 +6800,13 @@
         <v>364</v>
       </c>
       <c r="E226" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="F226" t="s">
-        <v>276</v>
+        <v>366</v>
       </c>
       <c r="G226" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6823,13 +6823,13 @@
         <v>364</v>
       </c>
       <c r="E227" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G227" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6849,10 +6849,10 @@
         <v>164</v>
       </c>
       <c r="F228" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
       <c r="G228" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
         <v>364</v>
       </c>
       <c r="E229" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F229" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G229" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D230" t="s">
         <v>364</v>
       </c>
       <c r="E230" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F230" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G230" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D231" t="s">
         <v>364</v>
       </c>
       <c r="E231" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F231" t="s">
-        <v>293</v>
+        <v>387</v>
       </c>
       <c r="G231" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D232" t="s">
         <v>364</v>
       </c>
       <c r="E232" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F232" t="s">
-        <v>309</v>
+        <v>387</v>
       </c>
       <c r="G232" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D233" t="s">
         <v>364</v>
       </c>
       <c r="E233" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F233" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G233" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D234" t="s">
         <v>364</v>
       </c>
       <c r="E234" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F234" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G234" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D235" t="s">
         <v>364</v>
       </c>
       <c r="E235" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F235" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G235" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D236" t="s">
         <v>364</v>
       </c>
       <c r="E236" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F236" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G236" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D237" t="s">
         <v>364</v>
       </c>
       <c r="E237" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F237" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G237" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
         <v>364</v>
       </c>
       <c r="E238" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F238" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G238" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
         <v>364</v>
       </c>
       <c r="E239" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F239" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G239" t="s">
-        <v>399</v>
+        <v>165</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7125,10 +7125,10 @@
         <v>164</v>
       </c>
       <c r="F240" t="s">
-        <v>165</v>
+        <v>402</v>
       </c>
       <c r="G240" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7148,10 +7148,10 @@
         <v>164</v>
       </c>
       <c r="F241" t="s">
-        <v>165</v>
+        <v>402</v>
       </c>
       <c r="G241" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7171,10 +7171,10 @@
         <v>164</v>
       </c>
       <c r="F242" t="s">
-        <v>165</v>
+        <v>402</v>
       </c>
       <c r="G242" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7194,10 +7194,10 @@
         <v>164</v>
       </c>
       <c r="F243" t="s">
-        <v>165</v>
+        <v>402</v>
       </c>
       <c r="G243" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7217,10 +7217,10 @@
         <v>164</v>
       </c>
       <c r="F244" t="s">
-        <v>165</v>
+        <v>402</v>
       </c>
       <c r="G244" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7240,10 +7240,10 @@
         <v>164</v>
       </c>
       <c r="F245" t="s">
-        <v>165</v>
+        <v>402</v>
       </c>
       <c r="G245" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>255</v>
+        <v>409</v>
       </c>
       <c r="D246" t="s">
         <v>401</v>
       </c>
       <c r="E246" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="F246" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G246" t="s">
-        <v>410</v>
+        <v>165</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7285,7 +7285,7 @@
       <c r="E247" t="s">
         <v>96</v>
       </c>
-      <c r="F247" t="s">
+      <c r="G247" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       <c r="E248" t="s">
         <v>96</v>
       </c>
-      <c r="F248" t="s">
+      <c r="G248" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7323,10 +7323,10 @@
         <v>412</v>
       </c>
       <c r="E249" t="s">
-        <v>96</v>
-      </c>
-      <c r="F249" t="s">
         <v>416</v>
+      </c>
+      <c r="G249" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7345,7 +7345,7 @@
       <c r="E250" t="s">
         <v>96</v>
       </c>
-      <c r="F250" t="s">
+      <c r="G250" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
       <c r="E251" t="s">
         <v>96</v>
       </c>
-      <c r="F251" t="s">
+      <c r="G251" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       <c r="E252" t="s">
         <v>96</v>
       </c>
-      <c r="F252" t="s">
+      <c r="G252" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7403,10 +7403,10 @@
         <v>422</v>
       </c>
       <c r="E253" t="s">
-        <v>164</v>
-      </c>
-      <c r="F253" t="s">
         <v>423</v>
+      </c>
+      <c r="G253" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7423,10 +7423,10 @@
         <v>422</v>
       </c>
       <c r="E254" t="s">
-        <v>92</v>
-      </c>
-      <c r="F254" t="s">
         <v>220</v>
+      </c>
+      <c r="G254" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7443,10 +7443,10 @@
         <v>422</v>
       </c>
       <c r="E255" t="s">
-        <v>92</v>
-      </c>
-      <c r="F255" t="s">
         <v>427</v>
+      </c>
+      <c r="G255" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7463,13 +7463,13 @@
         <v>422</v>
       </c>
       <c r="E256" t="s">
-        <v>92</v>
-      </c>
-      <c r="F256" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="257" spans="1:6">
+      <c r="G256" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
       <c r="A257" t="s">
         <v>429</v>
       </c>
@@ -7483,13 +7483,13 @@
         <v>422</v>
       </c>
       <c r="E257" t="s">
-        <v>92</v>
-      </c>
-      <c r="F257" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="258" spans="1:6">
+      <c r="G257" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
         <v>430</v>
       </c>
@@ -7503,13 +7503,13 @@
         <v>422</v>
       </c>
       <c r="E258" t="s">
-        <v>164</v>
-      </c>
-      <c r="F258" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="259" spans="1:6">
+      <c r="G258" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
         <v>431</v>
       </c>
@@ -7523,13 +7523,13 @@
         <v>422</v>
       </c>
       <c r="E259" t="s">
-        <v>92</v>
-      </c>
-      <c r="F259" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="260" spans="1:6">
+      <c r="G259" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
         <v>432</v>
       </c>
@@ -7545,11 +7545,11 @@
       <c r="E260" t="s">
         <v>164</v>
       </c>
-      <c r="F260" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
+      <c r="G260" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
       <c r="A261" t="s">
         <v>433</v>
       </c>
@@ -7563,13 +7563,13 @@
         <v>422</v>
       </c>
       <c r="E261" t="s">
-        <v>196</v>
-      </c>
-      <c r="F261" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="262" spans="1:6">
+      <c r="G261" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
       <c r="A262" t="s">
         <v>436</v>
       </c>
@@ -7585,11 +7585,11 @@
       <c r="E262" t="s">
         <v>164</v>
       </c>
-      <c r="F262" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
+      <c r="G262" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
       <c r="A263" t="s">
         <v>437</v>
       </c>
@@ -7603,13 +7603,13 @@
         <v>422</v>
       </c>
       <c r="E263" t="s">
-        <v>183</v>
-      </c>
-      <c r="F263" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="264" spans="1:6">
+      <c r="G263" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
         <v>440</v>
       </c>
@@ -7625,11 +7625,11 @@
       <c r="E264" t="s">
         <v>32</v>
       </c>
-      <c r="F264" t="s">
+      <c r="G264" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>441</v>
       </c>
@@ -7645,11 +7645,11 @@
       <c r="E265" t="s">
         <v>11</v>
       </c>
-      <c r="F265" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
+      <c r="G265" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
       <c r="A266" t="s">
         <v>442</v>
       </c>
@@ -7663,13 +7663,13 @@
         <v>422</v>
       </c>
       <c r="E266" t="s">
-        <v>114</v>
-      </c>
-      <c r="F266" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="267" spans="1:6">
+      <c r="G266" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
       <c r="A267" t="s">
         <v>445</v>
       </c>
@@ -7683,13 +7683,13 @@
         <v>446</v>
       </c>
       <c r="E267" t="s">
-        <v>114</v>
-      </c>
-      <c r="F267" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="268" spans="1:6">
+      <c r="G267" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
       <c r="A268" t="s">
         <v>447</v>
       </c>
@@ -7703,13 +7703,13 @@
         <v>448</v>
       </c>
       <c r="E268" t="s">
-        <v>183</v>
-      </c>
-      <c r="F268" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="269" spans="1:6">
+      <c r="G268" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
       <c r="A269" t="s">
         <v>449</v>
       </c>
@@ -7723,13 +7723,13 @@
         <v>450</v>
       </c>
       <c r="E269" t="s">
-        <v>114</v>
-      </c>
-      <c r="F269" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="270" spans="1:6">
+      <c r="G269" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
       <c r="A270" t="s">
         <v>451</v>
       </c>
@@ -7743,13 +7743,13 @@
         <v>450</v>
       </c>
       <c r="E270" t="s">
-        <v>114</v>
-      </c>
-      <c r="F270" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="271" spans="1:6">
+      <c r="G270" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
       <c r="A271" t="s">
         <v>452</v>
       </c>
@@ -7763,13 +7763,13 @@
         <v>454</v>
       </c>
       <c r="E271" t="s">
-        <v>114</v>
-      </c>
-      <c r="F271" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="272" spans="1:6">
+      <c r="G271" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
       <c r="A272" t="s">
         <v>456</v>
       </c>
@@ -7783,13 +7783,13 @@
         <v>454</v>
       </c>
       <c r="E272" t="s">
-        <v>114</v>
-      </c>
-      <c r="F272" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="273" spans="1:6">
+      <c r="G272" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
       <c r="A273" t="s">
         <v>457</v>
       </c>
@@ -7803,13 +7803,13 @@
         <v>454</v>
       </c>
       <c r="E273" t="s">
-        <v>114</v>
-      </c>
-      <c r="F273" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="274" spans="1:6">
+      <c r="G273" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
       <c r="A274" t="s">
         <v>458</v>
       </c>
@@ -7823,13 +7823,13 @@
         <v>454</v>
       </c>
       <c r="E274" t="s">
-        <v>114</v>
-      </c>
-      <c r="F274" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="275" spans="1:6">
+      <c r="G274" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
       <c r="A275" t="s">
         <v>459</v>
       </c>
@@ -7843,13 +7843,13 @@
         <v>454</v>
       </c>
       <c r="E275" t="s">
-        <v>114</v>
-      </c>
-      <c r="F275" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="276" spans="1:6">
+      <c r="G275" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
       <c r="A276" t="s">
         <v>460</v>
       </c>
@@ -7863,13 +7863,13 @@
         <v>454</v>
       </c>
       <c r="E276" t="s">
-        <v>114</v>
-      </c>
-      <c r="F276" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="277" spans="1:6">
+      <c r="G276" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
       <c r="A277" t="s">
         <v>461</v>
       </c>
@@ -7883,13 +7883,13 @@
         <v>454</v>
       </c>
       <c r="E277" t="s">
-        <v>114</v>
-      </c>
-      <c r="F277" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="278" spans="1:6">
+      <c r="G277" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
       <c r="A278" t="s">
         <v>462</v>
       </c>
@@ -7903,13 +7903,13 @@
         <v>463</v>
       </c>
       <c r="E278" t="s">
-        <v>183</v>
-      </c>
-      <c r="F278" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="279" spans="1:6">
+      <c r="G278" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
       <c r="A279" t="s">
         <v>464</v>
       </c>
@@ -7923,13 +7923,13 @@
         <v>463</v>
       </c>
       <c r="E279" t="s">
-        <v>32</v>
-      </c>
-      <c r="F279" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="280" spans="1:6">
+      <c r="G279" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
       <c r="A280" t="s">
         <v>465</v>
       </c>
@@ -7945,11 +7945,11 @@
       <c r="E280" t="s">
         <v>11</v>
       </c>
-      <c r="F280" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6">
+      <c r="G280" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
       <c r="A281" t="s">
         <v>466</v>
       </c>
@@ -7963,13 +7963,13 @@
         <v>463</v>
       </c>
       <c r="E281" t="s">
-        <v>114</v>
-      </c>
-      <c r="F281" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="282" spans="1:6">
+      <c r="G281" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
       <c r="A282" t="s">
         <v>467</v>
       </c>
@@ -7985,11 +7985,11 @@
       <c r="E282" t="s">
         <v>125</v>
       </c>
-      <c r="F282" t="s">
+      <c r="G282" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="283" spans="1:6">
+    <row r="283" spans="1:7">
       <c r="A283" t="s">
         <v>468</v>
       </c>
@@ -7997,19 +7997,19 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="D283" t="s">
         <v>469</v>
       </c>
       <c r="E283" t="s">
-        <v>164</v>
-      </c>
-      <c r="F283" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6">
+        <v>365</v>
+      </c>
+      <c r="G283" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
       <c r="A284" t="s">
         <v>470</v>
       </c>
@@ -8025,11 +8025,11 @@
       <c r="E284" t="s">
         <v>125</v>
       </c>
-      <c r="F284" t="s">
+      <c r="G284" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="285" spans="1:6">
+    <row r="285" spans="1:7">
       <c r="A285" t="s">
         <v>472</v>
       </c>
@@ -8043,13 +8043,13 @@
         <v>473</v>
       </c>
       <c r="E285" t="s">
-        <v>114</v>
-      </c>
-      <c r="F285" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="286" spans="1:6">
+      <c r="G285" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
       <c r="A286" t="s">
         <v>474</v>
       </c>
@@ -8063,13 +8063,13 @@
         <v>475</v>
       </c>
       <c r="E286" t="s">
-        <v>183</v>
-      </c>
-      <c r="F286" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="287" spans="1:6">
+      <c r="G286" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
       <c r="A287" t="s">
         <v>476</v>
       </c>
@@ -8083,13 +8083,13 @@
         <v>475</v>
       </c>
       <c r="E287" t="s">
-        <v>183</v>
-      </c>
-      <c r="F287" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="288" spans="1:6">
+      <c r="G287" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
       <c r="A288" t="s">
         <v>477</v>
       </c>
@@ -8103,13 +8103,13 @@
         <v>475</v>
       </c>
       <c r="E288" t="s">
-        <v>11</v>
-      </c>
-      <c r="F288" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="289" spans="1:6">
+      <c r="G288" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
       <c r="A289" t="s">
         <v>478</v>
       </c>
@@ -8125,11 +8125,11 @@
       <c r="E289" t="s">
         <v>32</v>
       </c>
-      <c r="F289" t="s">
+      <c r="G289" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="290" spans="1:6">
+    <row r="290" spans="1:7">
       <c r="A290" t="s">
         <v>479</v>
       </c>
@@ -8145,11 +8145,11 @@
       <c r="E290" t="s">
         <v>32</v>
       </c>
-      <c r="F290" t="s">
+      <c r="G290" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="291" spans="1:6">
+    <row r="291" spans="1:7">
       <c r="A291" t="s">
         <v>480</v>
       </c>
@@ -8163,13 +8163,13 @@
         <v>475</v>
       </c>
       <c r="E291" t="s">
-        <v>114</v>
-      </c>
-      <c r="F291" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="292" spans="1:6">
+      <c r="G291" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
       <c r="A292" t="s">
         <v>481</v>
       </c>
@@ -8183,13 +8183,13 @@
         <v>475</v>
       </c>
       <c r="E292" t="s">
-        <v>114</v>
-      </c>
-      <c r="F292" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="293" spans="1:6">
+      <c r="G292" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
       <c r="A293" t="s">
         <v>482</v>
       </c>
@@ -8203,13 +8203,13 @@
         <v>475</v>
       </c>
       <c r="E293" t="s">
-        <v>114</v>
-      </c>
-      <c r="F293" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="294" spans="1:6">
+      <c r="G293" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
       <c r="A294" t="s">
         <v>483</v>
       </c>
@@ -8223,13 +8223,13 @@
         <v>475</v>
       </c>
       <c r="E294" t="s">
-        <v>114</v>
-      </c>
-      <c r="F294" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="295" spans="1:6">
+      <c r="G294" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
       <c r="A295" t="s">
         <v>484</v>
       </c>
@@ -8243,13 +8243,13 @@
         <v>485</v>
       </c>
       <c r="E295" t="s">
-        <v>114</v>
-      </c>
-      <c r="F295" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="296" spans="1:6">
+      <c r="G295" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
       <c r="A296" t="s">
         <v>486</v>
       </c>
@@ -8263,10 +8263,10 @@
         <v>485</v>
       </c>
       <c r="E296" t="s">
-        <v>114</v>
-      </c>
-      <c r="F296" t="s">
         <v>171</v>
+      </c>
+      <c r="G296" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -25,18 +25,18 @@
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -172,15 +172,15 @@
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -289,27 +289,27 @@
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -355,18 +355,18 @@
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -508,12 +508,12 @@
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -565,12 +565,12 @@
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -625,12 +625,12 @@
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -688,12 +688,12 @@
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -826,15 +826,15 @@
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -994,15 +994,15 @@
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1108,15 +1108,15 @@
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1219,12 +1219,12 @@
     <t>33110</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1282,12 +1282,12 @@
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1378,10 +1378,10 @@
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -2050,16 +2050,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2188,16 +2188,16 @@
         <v>51</v>
       </c>
       <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
         <v>52</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>53</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>54</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2211,16 +2211,16 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
         <v>52</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>53</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>54</v>
-      </c>
-      <c r="G18" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2234,16 +2234,16 @@
         <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
       </c>
       <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" t="s">
         <v>54</v>
-      </c>
-      <c r="G19" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2257,16 +2257,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
         <v>61</v>
       </c>
       <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
         <v>54</v>
-      </c>
-      <c r="G20" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2280,16 +2280,16 @@
         <v>51</v>
       </c>
       <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
         <v>52</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>53</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>54</v>
-      </c>
-      <c r="G21" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2303,16 +2303,16 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
         <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2326,7 +2326,7 @@
         <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E23" t="s">
         <v>67</v>
@@ -2335,7 +2335,7 @@
         <v>64</v>
       </c>
       <c r="G23" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2349,16 +2349,16 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
         <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2372,16 +2372,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
         <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2395,16 +2395,16 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
         <v>64</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2418,16 +2418,16 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
         <v>64</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2441,16 +2441,16 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
         <v>64</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2464,16 +2464,16 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
         <v>64</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2487,16 +2487,16 @@
         <v>51</v>
       </c>
       <c r="D30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" t="s">
         <v>52</v>
-      </c>
-      <c r="E30" t="s">
-        <v>53</v>
       </c>
       <c r="F30" t="s">
         <v>64</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2510,16 +2510,16 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
         <v>76</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2533,16 +2533,16 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
         <v>76</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2556,16 +2556,16 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s">
         <v>76</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2579,16 +2579,16 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
         <v>76</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2602,16 +2602,16 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
         <v>76</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2625,7 +2625,7 @@
         <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E36" t="s">
         <v>58</v>
@@ -2634,7 +2634,7 @@
         <v>76</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2648,13 +2648,13 @@
         <v>31</v>
       </c>
       <c r="D37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" t="s">
         <v>83</v>
-      </c>
-      <c r="E37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2668,13 +2668,13 @@
         <v>31</v>
       </c>
       <c r="D38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
         <v>83</v>
-      </c>
-      <c r="E38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2688,13 +2688,13 @@
         <v>31</v>
       </c>
       <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
         <v>83</v>
-      </c>
-      <c r="E39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2708,13 +2708,13 @@
         <v>31</v>
       </c>
       <c r="D40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
         <v>83</v>
-      </c>
-      <c r="E40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2728,13 +2728,13 @@
         <v>51</v>
       </c>
       <c r="D41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" t="s">
         <v>83</v>
-      </c>
-      <c r="E41" t="s">
-        <v>53</v>
-      </c>
-      <c r="G41" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2748,13 +2748,13 @@
         <v>57</v>
       </c>
       <c r="D42" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="E42" t="s">
         <v>58</v>
       </c>
       <c r="G42" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2788,13 +2788,13 @@
         <v>95</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G44" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2848,13 +2848,13 @@
         <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E47" t="s">
         <v>102</v>
       </c>
       <c r="G47" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2908,13 +2908,13 @@
         <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E50" t="s">
         <v>102</v>
       </c>
       <c r="G50" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>108</v>
       </c>
       <c r="D52" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E52" t="s">
         <v>109</v>
       </c>
       <c r="G52" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2968,13 +2968,13 @@
         <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3057,16 +3057,16 @@
         <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F57" t="s">
         <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3425,7 +3425,7 @@
         <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E73" t="s">
         <v>149</v>
@@ -3434,7 +3434,7 @@
         <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3448,7 +3448,7 @@
         <v>151</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E74" t="s">
         <v>152</v>
@@ -3457,7 +3457,7 @@
         <v>115</v>
       </c>
       <c r="G74" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3471,7 +3471,7 @@
         <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E75" t="s">
         <v>155</v>
@@ -3480,7 +3480,7 @@
         <v>115</v>
       </c>
       <c r="G75" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3494,7 +3494,7 @@
         <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E76" t="s">
         <v>149</v>
@@ -3503,7 +3503,7 @@
         <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3517,7 +3517,7 @@
         <v>148</v>
       </c>
       <c r="D77" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E77" t="s">
         <v>149</v>
@@ -3526,7 +3526,7 @@
         <v>115</v>
       </c>
       <c r="G77" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3540,7 +3540,7 @@
         <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E78" t="s">
         <v>152</v>
@@ -3549,7 +3549,7 @@
         <v>115</v>
       </c>
       <c r="G78" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3563,7 +3563,7 @@
         <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E79" t="s">
         <v>161</v>
@@ -3572,7 +3572,7 @@
         <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3586,16 +3586,16 @@
         <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F80" t="s">
         <v>115</v>
       </c>
       <c r="G80" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3609,16 +3609,16 @@
         <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F81" t="s">
         <v>115</v>
       </c>
       <c r="G81" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3632,16 +3632,16 @@
         <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E82" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F82" t="s">
         <v>115</v>
       </c>
       <c r="G82" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3724,7 +3724,7 @@
         <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E86" t="s">
         <v>176</v>
@@ -3733,7 +3733,7 @@
         <v>115</v>
       </c>
       <c r="G86" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3816,16 +3816,16 @@
         <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E90" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F90" t="s">
         <v>115</v>
       </c>
       <c r="G90" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3839,16 +3839,16 @@
         <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F91" t="s">
         <v>115</v>
       </c>
       <c r="G91" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3862,16 +3862,16 @@
         <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F92" t="s">
         <v>115</v>
       </c>
       <c r="G92" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3908,16 +3908,16 @@
         <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E94" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F94" t="s">
         <v>115</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3954,16 +3954,16 @@
         <v>124</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E96" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F96" t="s">
         <v>192</v>
       </c>
       <c r="G96" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3977,16 +3977,16 @@
         <v>124</v>
       </c>
       <c r="D97" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E97" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F97" t="s">
         <v>192</v>
       </c>
       <c r="G97" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4000,16 +4000,16 @@
         <v>195</v>
       </c>
       <c r="D98" t="s">
-        <v>113</v>
+        <v>196</v>
       </c>
       <c r="E98" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F98" t="s">
         <v>192</v>
       </c>
       <c r="G98" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4023,16 +4023,16 @@
         <v>124</v>
       </c>
       <c r="D99" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E99" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F99" t="s">
         <v>192</v>
       </c>
       <c r="G99" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4046,7 +4046,7 @@
         <v>154</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E100" t="s">
         <v>155</v>
@@ -4055,7 +4055,7 @@
         <v>192</v>
       </c>
       <c r="G100" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4069,16 +4069,16 @@
         <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E101" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F101" t="s">
         <v>192</v>
       </c>
       <c r="G101" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4092,13 +4092,13 @@
         <v>202</v>
       </c>
       <c r="D102" t="s">
+        <v>183</v>
+      </c>
+      <c r="E102" t="s">
         <v>203</v>
       </c>
-      <c r="E102" t="s">
+      <c r="G102" t="s">
         <v>204</v>
-      </c>
-      <c r="G102" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4112,13 +4112,13 @@
         <v>202</v>
       </c>
       <c r="D103" t="s">
+        <v>183</v>
+      </c>
+      <c r="E103" t="s">
         <v>203</v>
       </c>
-      <c r="E103" t="s">
+      <c r="G103" t="s">
         <v>204</v>
-      </c>
-      <c r="G103" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4132,13 +4132,13 @@
         <v>202</v>
       </c>
       <c r="D104" t="s">
+        <v>183</v>
+      </c>
+      <c r="E104" t="s">
         <v>203</v>
       </c>
-      <c r="E104" t="s">
+      <c r="G104" t="s">
         <v>204</v>
-      </c>
-      <c r="G104" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4152,13 +4152,13 @@
         <v>208</v>
       </c>
       <c r="D105" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E105" t="s">
         <v>209</v>
       </c>
       <c r="G105" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4172,13 +4172,13 @@
         <v>202</v>
       </c>
       <c r="D106" t="s">
+        <v>183</v>
+      </c>
+      <c r="E106" t="s">
         <v>203</v>
       </c>
-      <c r="E106" t="s">
+      <c r="G106" t="s">
         <v>204</v>
-      </c>
-      <c r="G106" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4192,13 +4192,13 @@
         <v>182</v>
       </c>
       <c r="D107" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E107" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G107" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4212,13 +4212,13 @@
         <v>213</v>
       </c>
       <c r="D108" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E108" t="s">
         <v>214</v>
       </c>
       <c r="G108" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4232,13 +4232,13 @@
         <v>216</v>
       </c>
       <c r="D109" t="s">
-        <v>203</v>
+        <v>91</v>
       </c>
       <c r="E109" t="s">
         <v>217</v>
       </c>
       <c r="G109" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4252,13 +4252,13 @@
         <v>219</v>
       </c>
       <c r="D110" t="s">
-        <v>203</v>
+        <v>91</v>
       </c>
       <c r="E110" t="s">
         <v>220</v>
       </c>
       <c r="G110" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4272,13 +4272,13 @@
         <v>202</v>
       </c>
       <c r="D111" t="s">
+        <v>183</v>
+      </c>
+      <c r="E111" t="s">
         <v>203</v>
       </c>
-      <c r="E111" t="s">
+      <c r="G111" t="s">
         <v>204</v>
-      </c>
-      <c r="G111" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4292,13 +4292,13 @@
         <v>223</v>
       </c>
       <c r="D112" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G112" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4312,13 +4312,13 @@
         <v>143</v>
       </c>
       <c r="D113" t="s">
-        <v>203</v>
+        <v>113</v>
       </c>
       <c r="E113" t="s">
         <v>114</v>
       </c>
       <c r="G113" t="s">
-        <v>116</v>
+        <v>204</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4332,13 +4332,13 @@
         <v>151</v>
       </c>
       <c r="D114" t="s">
-        <v>203</v>
+        <v>125</v>
       </c>
       <c r="E114" t="s">
         <v>152</v>
       </c>
       <c r="G114" t="s">
-        <v>126</v>
+        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4352,13 +4352,13 @@
         <v>182</v>
       </c>
       <c r="D115" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E115" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G115" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4372,13 +4372,13 @@
         <v>230</v>
       </c>
       <c r="D116" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E116" t="s">
         <v>231</v>
       </c>
       <c r="G116" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4392,13 +4392,13 @@
         <v>223</v>
       </c>
       <c r="D117" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G117" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4412,13 +4412,13 @@
         <v>234</v>
       </c>
       <c r="D118" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="E118" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G118" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4432,13 +4432,13 @@
         <v>182</v>
       </c>
       <c r="D119" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E119" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G119" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4452,13 +4452,13 @@
         <v>170</v>
       </c>
       <c r="D120" t="s">
-        <v>237</v>
+        <v>113</v>
       </c>
       <c r="E120" t="s">
         <v>171</v>
       </c>
       <c r="G120" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4472,13 +4472,13 @@
         <v>143</v>
       </c>
       <c r="D121" t="s">
-        <v>237</v>
+        <v>113</v>
       </c>
       <c r="E121" t="s">
         <v>114</v>
       </c>
       <c r="G121" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4492,13 +4492,13 @@
         <v>170</v>
       </c>
       <c r="D122" t="s">
-        <v>237</v>
+        <v>113</v>
       </c>
       <c r="E122" t="s">
         <v>171</v>
       </c>
       <c r="G122" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4512,13 +4512,13 @@
         <v>170</v>
       </c>
       <c r="D123" t="s">
-        <v>237</v>
+        <v>113</v>
       </c>
       <c r="E123" t="s">
         <v>171</v>
       </c>
       <c r="G123" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4532,13 +4532,13 @@
         <v>242</v>
       </c>
       <c r="D124" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="E124" t="s">
         <v>243</v>
       </c>
       <c r="G124" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4552,13 +4552,13 @@
         <v>242</v>
       </c>
       <c r="D125" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="E125" t="s">
         <v>243</v>
       </c>
       <c r="G125" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4572,13 +4572,13 @@
         <v>242</v>
       </c>
       <c r="D126" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="E126" t="s">
         <v>243</v>
       </c>
       <c r="G126" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4592,13 +4592,13 @@
         <v>242</v>
       </c>
       <c r="D127" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="E127" t="s">
         <v>243</v>
       </c>
       <c r="G127" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4612,13 +4612,13 @@
         <v>242</v>
       </c>
       <c r="D128" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="E128" t="s">
         <v>243</v>
       </c>
       <c r="G128" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4632,13 +4632,13 @@
         <v>249</v>
       </c>
       <c r="D129" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="E129" t="s">
         <v>243</v>
       </c>
       <c r="G129" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4652,13 +4652,13 @@
         <v>251</v>
       </c>
       <c r="D130" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="E130" t="s">
         <v>243</v>
       </c>
       <c r="G130" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4672,13 +4672,13 @@
         <v>253</v>
       </c>
       <c r="D131" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="E131" t="s">
         <v>243</v>
       </c>
       <c r="G131" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4692,13 +4692,13 @@
         <v>255</v>
       </c>
       <c r="D132" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="E132" t="s">
         <v>256</v>
       </c>
       <c r="G132" t="s">
-        <v>165</v>
+        <v>237</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4712,13 +4712,13 @@
         <v>189</v>
       </c>
       <c r="D133" t="s">
-        <v>237</v>
+        <v>113</v>
       </c>
       <c r="E133" t="s">
         <v>190</v>
       </c>
       <c r="G133" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4732,13 +4732,13 @@
         <v>175</v>
       </c>
       <c r="D134" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="E134" t="s">
         <v>176</v>
       </c>
       <c r="G134" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4752,13 +4752,13 @@
         <v>175</v>
       </c>
       <c r="D135" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="E135" t="s">
         <v>176</v>
       </c>
       <c r="G135" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4772,13 +4772,13 @@
         <v>175</v>
       </c>
       <c r="D136" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="E136" t="s">
         <v>176</v>
       </c>
       <c r="G136" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4792,13 +4792,13 @@
         <v>175</v>
       </c>
       <c r="D137" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="E137" t="s">
         <v>176</v>
       </c>
       <c r="G137" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4812,13 +4812,13 @@
         <v>175</v>
       </c>
       <c r="D138" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="E138" t="s">
         <v>176</v>
       </c>
       <c r="G138" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4832,13 +4832,13 @@
         <v>265</v>
       </c>
       <c r="D139" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="E139" t="s">
         <v>266</v>
       </c>
       <c r="G139" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4852,13 +4852,13 @@
         <v>175</v>
       </c>
       <c r="D140" t="s">
-        <v>259</v>
+        <v>164</v>
       </c>
       <c r="E140" t="s">
         <v>176</v>
       </c>
       <c r="G140" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4872,16 +4872,16 @@
         <v>269</v>
       </c>
       <c r="D141" t="s">
+        <v>164</v>
+      </c>
+      <c r="E141" t="s">
         <v>270</v>
       </c>
-      <c r="E141" t="s">
+      <c r="F141" t="s">
         <v>271</v>
       </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>272</v>
-      </c>
-      <c r="G141" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4895,16 +4895,16 @@
         <v>269</v>
       </c>
       <c r="D142" t="s">
+        <v>164</v>
+      </c>
+      <c r="E142" t="s">
         <v>270</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>271</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>272</v>
-      </c>
-      <c r="G142" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4918,16 +4918,16 @@
         <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="E143" t="s">
         <v>276</v>
       </c>
       <c r="F143" t="s">
+        <v>271</v>
+      </c>
+      <c r="G143" t="s">
         <v>272</v>
-      </c>
-      <c r="G143" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4941,16 +4941,16 @@
         <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="E144" t="s">
         <v>276</v>
       </c>
       <c r="F144" t="s">
+        <v>271</v>
+      </c>
+      <c r="G144" t="s">
         <v>272</v>
-      </c>
-      <c r="G144" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4964,16 +4964,16 @@
         <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="E145" t="s">
         <v>276</v>
       </c>
       <c r="F145" t="s">
+        <v>271</v>
+      </c>
+      <c r="G145" t="s">
         <v>272</v>
-      </c>
-      <c r="G145" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4987,16 +4987,16 @@
         <v>269</v>
       </c>
       <c r="D146" t="s">
+        <v>164</v>
+      </c>
+      <c r="E146" t="s">
         <v>270</v>
       </c>
-      <c r="E146" t="s">
+      <c r="F146" t="s">
         <v>271</v>
       </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>272</v>
-      </c>
-      <c r="G146" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5010,16 +5010,16 @@
         <v>269</v>
       </c>
       <c r="D147" t="s">
+        <v>164</v>
+      </c>
+      <c r="E147" t="s">
         <v>270</v>
-      </c>
-      <c r="E147" t="s">
-        <v>271</v>
       </c>
       <c r="F147" t="s">
         <v>281</v>
       </c>
       <c r="G147" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5033,16 +5033,16 @@
         <v>269</v>
       </c>
       <c r="D148" t="s">
+        <v>164</v>
+      </c>
+      <c r="E148" t="s">
         <v>270</v>
-      </c>
-      <c r="E148" t="s">
-        <v>271</v>
       </c>
       <c r="F148" t="s">
         <v>281</v>
       </c>
       <c r="G148" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5056,16 +5056,16 @@
         <v>269</v>
       </c>
       <c r="D149" t="s">
+        <v>164</v>
+      </c>
+      <c r="E149" t="s">
         <v>270</v>
-      </c>
-      <c r="E149" t="s">
-        <v>271</v>
       </c>
       <c r="F149" t="s">
         <v>281</v>
       </c>
       <c r="G149" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5079,16 +5079,16 @@
         <v>269</v>
       </c>
       <c r="D150" t="s">
+        <v>164</v>
+      </c>
+      <c r="E150" t="s">
         <v>270</v>
-      </c>
-      <c r="E150" t="s">
-        <v>271</v>
       </c>
       <c r="F150" t="s">
         <v>281</v>
       </c>
       <c r="G150" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5102,16 +5102,16 @@
         <v>269</v>
       </c>
       <c r="D151" t="s">
+        <v>164</v>
+      </c>
+      <c r="E151" t="s">
         <v>270</v>
-      </c>
-      <c r="E151" t="s">
-        <v>271</v>
       </c>
       <c r="F151" t="s">
         <v>281</v>
       </c>
       <c r="G151" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5125,16 +5125,16 @@
         <v>269</v>
       </c>
       <c r="D152" t="s">
+        <v>164</v>
+      </c>
+      <c r="E152" t="s">
         <v>270</v>
-      </c>
-      <c r="E152" t="s">
-        <v>271</v>
       </c>
       <c r="F152" t="s">
         <v>281</v>
       </c>
       <c r="G152" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5148,16 +5148,16 @@
         <v>269</v>
       </c>
       <c r="D153" t="s">
+        <v>164</v>
+      </c>
+      <c r="E153" t="s">
         <v>270</v>
-      </c>
-      <c r="E153" t="s">
-        <v>271</v>
       </c>
       <c r="F153" t="s">
         <v>281</v>
       </c>
       <c r="G153" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5171,16 +5171,16 @@
         <v>269</v>
       </c>
       <c r="D154" t="s">
+        <v>164</v>
+      </c>
+      <c r="E154" t="s">
         <v>270</v>
-      </c>
-      <c r="E154" t="s">
-        <v>271</v>
       </c>
       <c r="F154" t="s">
         <v>281</v>
       </c>
       <c r="G154" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5194,16 +5194,16 @@
         <v>269</v>
       </c>
       <c r="D155" t="s">
+        <v>164</v>
+      </c>
+      <c r="E155" t="s">
         <v>270</v>
-      </c>
-      <c r="E155" t="s">
-        <v>271</v>
       </c>
       <c r="F155" t="s">
         <v>281</v>
       </c>
       <c r="G155" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5217,16 +5217,16 @@
         <v>269</v>
       </c>
       <c r="D156" t="s">
+        <v>164</v>
+      </c>
+      <c r="E156" t="s">
         <v>270</v>
-      </c>
-      <c r="E156" t="s">
-        <v>271</v>
       </c>
       <c r="F156" t="s">
         <v>291</v>
       </c>
       <c r="G156" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5240,16 +5240,16 @@
         <v>293</v>
       </c>
       <c r="D157" t="s">
+        <v>164</v>
+      </c>
+      <c r="E157" t="s">
         <v>270</v>
-      </c>
-      <c r="E157" t="s">
-        <v>271</v>
       </c>
       <c r="F157" t="s">
         <v>291</v>
       </c>
       <c r="G157" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5263,16 +5263,16 @@
         <v>269</v>
       </c>
       <c r="D158" t="s">
+        <v>164</v>
+      </c>
+      <c r="E158" t="s">
         <v>270</v>
-      </c>
-      <c r="E158" t="s">
-        <v>271</v>
       </c>
       <c r="F158" t="s">
         <v>291</v>
       </c>
       <c r="G158" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5286,16 +5286,16 @@
         <v>269</v>
       </c>
       <c r="D159" t="s">
+        <v>164</v>
+      </c>
+      <c r="E159" t="s">
         <v>270</v>
-      </c>
-      <c r="E159" t="s">
-        <v>271</v>
       </c>
       <c r="F159" t="s">
         <v>291</v>
       </c>
       <c r="G159" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5309,16 +5309,16 @@
         <v>269</v>
       </c>
       <c r="D160" t="s">
+        <v>164</v>
+      </c>
+      <c r="E160" t="s">
         <v>270</v>
-      </c>
-      <c r="E160" t="s">
-        <v>271</v>
       </c>
       <c r="F160" t="s">
         <v>291</v>
       </c>
       <c r="G160" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5332,16 +5332,16 @@
         <v>269</v>
       </c>
       <c r="D161" t="s">
+        <v>164</v>
+      </c>
+      <c r="E161" t="s">
         <v>270</v>
-      </c>
-      <c r="E161" t="s">
-        <v>271</v>
       </c>
       <c r="F161" t="s">
         <v>291</v>
       </c>
       <c r="G161" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5355,16 +5355,16 @@
         <v>269</v>
       </c>
       <c r="D162" t="s">
+        <v>164</v>
+      </c>
+      <c r="E162" t="s">
         <v>270</v>
-      </c>
-      <c r="E162" t="s">
-        <v>271</v>
       </c>
       <c r="F162" t="s">
         <v>299</v>
       </c>
       <c r="G162" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5378,16 +5378,16 @@
         <v>301</v>
       </c>
       <c r="D163" t="s">
+        <v>164</v>
+      </c>
+      <c r="E163" t="s">
         <v>270</v>
-      </c>
-      <c r="E163" t="s">
-        <v>271</v>
       </c>
       <c r="F163" t="s">
         <v>302</v>
       </c>
       <c r="G163" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5401,16 +5401,16 @@
         <v>269</v>
       </c>
       <c r="D164" t="s">
+        <v>164</v>
+      </c>
+      <c r="E164" t="s">
         <v>270</v>
-      </c>
-      <c r="E164" t="s">
-        <v>271</v>
       </c>
       <c r="F164" t="s">
         <v>304</v>
       </c>
       <c r="G164" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5424,16 +5424,16 @@
         <v>269</v>
       </c>
       <c r="D165" t="s">
+        <v>164</v>
+      </c>
+      <c r="E165" t="s">
         <v>270</v>
-      </c>
-      <c r="E165" t="s">
-        <v>271</v>
       </c>
       <c r="F165" t="s">
         <v>304</v>
       </c>
       <c r="G165" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5447,16 +5447,16 @@
         <v>269</v>
       </c>
       <c r="D166" t="s">
+        <v>164</v>
+      </c>
+      <c r="E166" t="s">
         <v>270</v>
-      </c>
-      <c r="E166" t="s">
-        <v>271</v>
       </c>
       <c r="F166" t="s">
         <v>304</v>
       </c>
       <c r="G166" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5470,16 +5470,16 @@
         <v>269</v>
       </c>
       <c r="D167" t="s">
+        <v>164</v>
+      </c>
+      <c r="E167" t="s">
         <v>270</v>
-      </c>
-      <c r="E167" t="s">
-        <v>271</v>
       </c>
       <c r="F167" t="s">
         <v>304</v>
       </c>
       <c r="G167" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5493,16 +5493,16 @@
         <v>309</v>
       </c>
       <c r="D168" t="s">
+        <v>164</v>
+      </c>
+      <c r="E168" t="s">
         <v>270</v>
-      </c>
-      <c r="E168" t="s">
-        <v>271</v>
       </c>
       <c r="F168" t="s">
         <v>304</v>
       </c>
       <c r="G168" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5516,16 +5516,16 @@
         <v>309</v>
       </c>
       <c r="D169" t="s">
+        <v>164</v>
+      </c>
+      <c r="E169" t="s">
         <v>270</v>
-      </c>
-      <c r="E169" t="s">
-        <v>271</v>
       </c>
       <c r="F169" t="s">
         <v>304</v>
       </c>
       <c r="G169" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5539,16 +5539,16 @@
         <v>269</v>
       </c>
       <c r="D170" t="s">
+        <v>164</v>
+      </c>
+      <c r="E170" t="s">
         <v>270</v>
-      </c>
-      <c r="E170" t="s">
-        <v>271</v>
       </c>
       <c r="F170" t="s">
         <v>304</v>
       </c>
       <c r="G170" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5562,13 +5562,13 @@
         <v>163</v>
       </c>
       <c r="D171" t="s">
+        <v>164</v>
+      </c>
+      <c r="E171" t="s">
+        <v>165</v>
+      </c>
+      <c r="G171" t="s">
         <v>313</v>
-      </c>
-      <c r="E171" t="s">
-        <v>164</v>
-      </c>
-      <c r="G171" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5582,13 +5582,13 @@
         <v>118</v>
       </c>
       <c r="D172" t="s">
-        <v>313</v>
+        <v>113</v>
       </c>
       <c r="E172" t="s">
         <v>119</v>
       </c>
       <c r="G172" t="s">
-        <v>116</v>
+        <v>313</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5602,13 +5602,13 @@
         <v>163</v>
       </c>
       <c r="D173" t="s">
+        <v>164</v>
+      </c>
+      <c r="E173" t="s">
+        <v>165</v>
+      </c>
+      <c r="G173" t="s">
         <v>313</v>
-      </c>
-      <c r="E173" t="s">
-        <v>164</v>
-      </c>
-      <c r="G173" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5622,13 +5622,13 @@
         <v>163</v>
       </c>
       <c r="D174" t="s">
+        <v>164</v>
+      </c>
+      <c r="E174" t="s">
+        <v>165</v>
+      </c>
+      <c r="G174" t="s">
         <v>313</v>
-      </c>
-      <c r="E174" t="s">
-        <v>164</v>
-      </c>
-      <c r="G174" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5642,13 +5642,13 @@
         <v>163</v>
       </c>
       <c r="D175" t="s">
+        <v>164</v>
+      </c>
+      <c r="E175" t="s">
+        <v>165</v>
+      </c>
+      <c r="G175" t="s">
         <v>313</v>
-      </c>
-      <c r="E175" t="s">
-        <v>164</v>
-      </c>
-      <c r="G175" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5662,13 +5662,13 @@
         <v>163</v>
       </c>
       <c r="D176" t="s">
+        <v>164</v>
+      </c>
+      <c r="E176" t="s">
+        <v>165</v>
+      </c>
+      <c r="G176" t="s">
         <v>313</v>
-      </c>
-      <c r="E176" t="s">
-        <v>164</v>
-      </c>
-      <c r="G176" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5682,13 +5682,13 @@
         <v>163</v>
       </c>
       <c r="D177" t="s">
+        <v>164</v>
+      </c>
+      <c r="E177" t="s">
+        <v>165</v>
+      </c>
+      <c r="G177" t="s">
         <v>320</v>
-      </c>
-      <c r="E177" t="s">
-        <v>164</v>
-      </c>
-      <c r="G177" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5702,13 +5702,13 @@
         <v>163</v>
       </c>
       <c r="D178" t="s">
+        <v>164</v>
+      </c>
+      <c r="E178" t="s">
+        <v>165</v>
+      </c>
+      <c r="G178" t="s">
         <v>320</v>
-      </c>
-      <c r="E178" t="s">
-        <v>164</v>
-      </c>
-      <c r="G178" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5722,13 +5722,13 @@
         <v>163</v>
       </c>
       <c r="D179" t="s">
+        <v>164</v>
+      </c>
+      <c r="E179" t="s">
+        <v>165</v>
+      </c>
+      <c r="G179" t="s">
         <v>320</v>
-      </c>
-      <c r="E179" t="s">
-        <v>164</v>
-      </c>
-      <c r="G179" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5742,13 +5742,13 @@
         <v>163</v>
       </c>
       <c r="D180" t="s">
+        <v>164</v>
+      </c>
+      <c r="E180" t="s">
+        <v>165</v>
+      </c>
+      <c r="G180" t="s">
         <v>320</v>
-      </c>
-      <c r="E180" t="s">
-        <v>164</v>
-      </c>
-      <c r="G180" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5762,16 +5762,16 @@
         <v>325</v>
       </c>
       <c r="D181" t="s">
+        <v>164</v>
+      </c>
+      <c r="E181" t="s">
         <v>326</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>327</v>
       </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
         <v>328</v>
-      </c>
-      <c r="G181" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5785,16 +5785,16 @@
         <v>325</v>
       </c>
       <c r="D182" t="s">
+        <v>164</v>
+      </c>
+      <c r="E182" t="s">
         <v>326</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" t="s">
         <v>327</v>
       </c>
-      <c r="F182" t="s">
+      <c r="G182" t="s">
         <v>328</v>
-      </c>
-      <c r="G182" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5808,16 +5808,16 @@
         <v>325</v>
       </c>
       <c r="D183" t="s">
+        <v>164</v>
+      </c>
+      <c r="E183" t="s">
         <v>326</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
         <v>327</v>
       </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
         <v>328</v>
-      </c>
-      <c r="G183" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5831,16 +5831,16 @@
         <v>325</v>
       </c>
       <c r="D184" t="s">
+        <v>164</v>
+      </c>
+      <c r="E184" t="s">
         <v>326</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
         <v>327</v>
       </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
         <v>328</v>
-      </c>
-      <c r="G184" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5854,16 +5854,16 @@
         <v>325</v>
       </c>
       <c r="D185" t="s">
+        <v>164</v>
+      </c>
+      <c r="E185" t="s">
         <v>326</v>
       </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
         <v>327</v>
       </c>
-      <c r="F185" t="s">
+      <c r="G185" t="s">
         <v>328</v>
-      </c>
-      <c r="G185" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5877,16 +5877,16 @@
         <v>325</v>
       </c>
       <c r="D186" t="s">
+        <v>164</v>
+      </c>
+      <c r="E186" t="s">
         <v>326</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
         <v>327</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>328</v>
-      </c>
-      <c r="G186" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5900,16 +5900,16 @@
         <v>325</v>
       </c>
       <c r="D187" t="s">
+        <v>164</v>
+      </c>
+      <c r="E187" t="s">
         <v>326</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
         <v>327</v>
       </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>328</v>
-      </c>
-      <c r="G187" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5923,16 +5923,16 @@
         <v>325</v>
       </c>
       <c r="D188" t="s">
+        <v>164</v>
+      </c>
+      <c r="E188" t="s">
         <v>326</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
         <v>327</v>
       </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>328</v>
-      </c>
-      <c r="G188" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5946,16 +5946,16 @@
         <v>325</v>
       </c>
       <c r="D189" t="s">
+        <v>164</v>
+      </c>
+      <c r="E189" t="s">
         <v>326</v>
       </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
         <v>327</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>328</v>
-      </c>
-      <c r="G189" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5969,16 +5969,16 @@
         <v>325</v>
       </c>
       <c r="D190" t="s">
+        <v>164</v>
+      </c>
+      <c r="E190" t="s">
         <v>326</v>
       </c>
-      <c r="E190" t="s">
+      <c r="F190" t="s">
         <v>327</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>328</v>
-      </c>
-      <c r="G190" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5992,16 +5992,16 @@
         <v>325</v>
       </c>
       <c r="D191" t="s">
+        <v>164</v>
+      </c>
+      <c r="E191" t="s">
         <v>326</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
         <v>327</v>
       </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>328</v>
-      </c>
-      <c r="G191" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6015,16 +6015,16 @@
         <v>325</v>
       </c>
       <c r="D192" t="s">
+        <v>164</v>
+      </c>
+      <c r="E192" t="s">
         <v>326</v>
       </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
         <v>327</v>
       </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>328</v>
-      </c>
-      <c r="G192" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6038,16 +6038,16 @@
         <v>341</v>
       </c>
       <c r="D193" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="E193" t="s">
         <v>276</v>
       </c>
       <c r="F193" t="s">
+        <v>327</v>
+      </c>
+      <c r="G193" t="s">
         <v>328</v>
-      </c>
-      <c r="G193" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6061,16 +6061,16 @@
         <v>325</v>
       </c>
       <c r="D194" t="s">
+        <v>164</v>
+      </c>
+      <c r="E194" t="s">
         <v>326</v>
       </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
         <v>327</v>
       </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>328</v>
-      </c>
-      <c r="G194" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6084,16 +6084,16 @@
         <v>325</v>
       </c>
       <c r="D195" t="s">
+        <v>164</v>
+      </c>
+      <c r="E195" t="s">
         <v>326</v>
       </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
         <v>327</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>328</v>
-      </c>
-      <c r="G195" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6107,16 +6107,16 @@
         <v>325</v>
       </c>
       <c r="D196" t="s">
+        <v>164</v>
+      </c>
+      <c r="E196" t="s">
         <v>326</v>
       </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
         <v>327</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>328</v>
-      </c>
-      <c r="G196" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6130,16 +6130,16 @@
         <v>325</v>
       </c>
       <c r="D197" t="s">
+        <v>164</v>
+      </c>
+      <c r="E197" t="s">
         <v>326</v>
       </c>
-      <c r="E197" t="s">
+      <c r="F197" t="s">
         <v>327</v>
       </c>
-      <c r="F197" t="s">
+      <c r="G197" t="s">
         <v>328</v>
-      </c>
-      <c r="G197" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6153,16 +6153,16 @@
         <v>325</v>
       </c>
       <c r="D198" t="s">
+        <v>164</v>
+      </c>
+      <c r="E198" t="s">
         <v>326</v>
       </c>
-      <c r="E198" t="s">
+      <c r="F198" t="s">
         <v>327</v>
       </c>
-      <c r="F198" t="s">
+      <c r="G198" t="s">
         <v>328</v>
-      </c>
-      <c r="G198" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6176,16 +6176,16 @@
         <v>348</v>
       </c>
       <c r="D199" t="s">
+        <v>164</v>
+      </c>
+      <c r="E199" t="s">
         <v>326</v>
-      </c>
-      <c r="E199" t="s">
-        <v>327</v>
       </c>
       <c r="F199" t="s">
         <v>349</v>
       </c>
       <c r="G199" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6199,16 +6199,16 @@
         <v>348</v>
       </c>
       <c r="D200" t="s">
+        <v>164</v>
+      </c>
+      <c r="E200" t="s">
         <v>326</v>
-      </c>
-      <c r="E200" t="s">
-        <v>327</v>
       </c>
       <c r="F200" t="s">
         <v>349</v>
       </c>
       <c r="G200" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6222,16 +6222,16 @@
         <v>348</v>
       </c>
       <c r="D201" t="s">
+        <v>164</v>
+      </c>
+      <c r="E201" t="s">
         <v>326</v>
-      </c>
-      <c r="E201" t="s">
-        <v>327</v>
       </c>
       <c r="F201" t="s">
         <v>349</v>
       </c>
       <c r="G201" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6245,16 +6245,16 @@
         <v>348</v>
       </c>
       <c r="D202" t="s">
+        <v>164</v>
+      </c>
+      <c r="E202" t="s">
         <v>326</v>
-      </c>
-      <c r="E202" t="s">
-        <v>327</v>
       </c>
       <c r="F202" t="s">
         <v>349</v>
       </c>
       <c r="G202" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6268,7 +6268,7 @@
         <v>341</v>
       </c>
       <c r="D203" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="E203" t="s">
         <v>276</v>
@@ -6277,7 +6277,7 @@
         <v>349</v>
       </c>
       <c r="G203" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6291,16 +6291,16 @@
         <v>348</v>
       </c>
       <c r="D204" t="s">
+        <v>164</v>
+      </c>
+      <c r="E204" t="s">
         <v>326</v>
-      </c>
-      <c r="E204" t="s">
-        <v>327</v>
       </c>
       <c r="F204" t="s">
         <v>349</v>
       </c>
       <c r="G204" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6314,16 +6314,16 @@
         <v>356</v>
       </c>
       <c r="D205" t="s">
+        <v>164</v>
+      </c>
+      <c r="E205" t="s">
         <v>326</v>
-      </c>
-      <c r="E205" t="s">
-        <v>327</v>
       </c>
       <c r="F205" t="s">
         <v>357</v>
       </c>
       <c r="G205" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6337,16 +6337,16 @@
         <v>356</v>
       </c>
       <c r="D206" t="s">
+        <v>164</v>
+      </c>
+      <c r="E206" t="s">
         <v>326</v>
-      </c>
-      <c r="E206" t="s">
-        <v>327</v>
       </c>
       <c r="F206" t="s">
         <v>357</v>
       </c>
       <c r="G206" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6360,16 +6360,16 @@
         <v>356</v>
       </c>
       <c r="D207" t="s">
+        <v>164</v>
+      </c>
+      <c r="E207" t="s">
         <v>326</v>
-      </c>
-      <c r="E207" t="s">
-        <v>327</v>
       </c>
       <c r="F207" t="s">
         <v>357</v>
       </c>
       <c r="G207" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6383,7 +6383,7 @@
         <v>341</v>
       </c>
       <c r="D208" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="E208" t="s">
         <v>276</v>
@@ -6392,7 +6392,7 @@
         <v>357</v>
       </c>
       <c r="G208" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6406,16 +6406,16 @@
         <v>356</v>
       </c>
       <c r="D209" t="s">
+        <v>164</v>
+      </c>
+      <c r="E209" t="s">
         <v>326</v>
-      </c>
-      <c r="E209" t="s">
-        <v>327</v>
       </c>
       <c r="F209" t="s">
         <v>357</v>
       </c>
       <c r="G209" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6429,16 +6429,16 @@
         <v>363</v>
       </c>
       <c r="D210" t="s">
+        <v>164</v>
+      </c>
+      <c r="E210" t="s">
         <v>364</v>
       </c>
-      <c r="E210" t="s">
+      <c r="F210" t="s">
         <v>365</v>
       </c>
-      <c r="F210" t="s">
+      <c r="G210" t="s">
         <v>366</v>
-      </c>
-      <c r="G210" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6452,16 +6452,16 @@
         <v>363</v>
       </c>
       <c r="D211" t="s">
+        <v>164</v>
+      </c>
+      <c r="E211" t="s">
         <v>364</v>
       </c>
-      <c r="E211" t="s">
+      <c r="F211" t="s">
         <v>365</v>
       </c>
-      <c r="F211" t="s">
+      <c r="G211" t="s">
         <v>366</v>
-      </c>
-      <c r="G211" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6475,16 +6475,16 @@
         <v>363</v>
       </c>
       <c r="D212" t="s">
+        <v>164</v>
+      </c>
+      <c r="E212" t="s">
         <v>364</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
         <v>365</v>
       </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>366</v>
-      </c>
-      <c r="G212" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6498,16 +6498,16 @@
         <v>363</v>
       </c>
       <c r="D213" t="s">
+        <v>164</v>
+      </c>
+      <c r="E213" t="s">
         <v>364</v>
       </c>
-      <c r="E213" t="s">
+      <c r="F213" t="s">
         <v>365</v>
       </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>366</v>
-      </c>
-      <c r="G213" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6521,16 +6521,16 @@
         <v>363</v>
       </c>
       <c r="D214" t="s">
+        <v>164</v>
+      </c>
+      <c r="E214" t="s">
         <v>364</v>
       </c>
-      <c r="E214" t="s">
+      <c r="F214" t="s">
         <v>365</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>366</v>
-      </c>
-      <c r="G214" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6544,16 +6544,16 @@
         <v>348</v>
       </c>
       <c r="D215" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="E215" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F215" t="s">
+        <v>365</v>
+      </c>
+      <c r="G215" t="s">
         <v>366</v>
-      </c>
-      <c r="G215" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6567,16 +6567,16 @@
         <v>363</v>
       </c>
       <c r="D216" t="s">
+        <v>164</v>
+      </c>
+      <c r="E216" t="s">
         <v>364</v>
       </c>
-      <c r="E216" t="s">
+      <c r="F216" t="s">
         <v>365</v>
       </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>366</v>
-      </c>
-      <c r="G216" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6590,16 +6590,16 @@
         <v>363</v>
       </c>
       <c r="D217" t="s">
+        <v>164</v>
+      </c>
+      <c r="E217" t="s">
         <v>364</v>
       </c>
-      <c r="E217" t="s">
+      <c r="F217" t="s">
         <v>365</v>
       </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
         <v>366</v>
-      </c>
-      <c r="G217" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6613,16 +6613,16 @@
         <v>363</v>
       </c>
       <c r="D218" t="s">
+        <v>164</v>
+      </c>
+      <c r="E218" t="s">
         <v>364</v>
       </c>
-      <c r="E218" t="s">
+      <c r="F218" t="s">
         <v>365</v>
       </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>366</v>
-      </c>
-      <c r="G218" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6636,16 +6636,16 @@
         <v>363</v>
       </c>
       <c r="D219" t="s">
+        <v>164</v>
+      </c>
+      <c r="E219" t="s">
         <v>364</v>
       </c>
-      <c r="E219" t="s">
+      <c r="F219" t="s">
         <v>365</v>
       </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>366</v>
-      </c>
-      <c r="G219" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6659,16 +6659,16 @@
         <v>309</v>
       </c>
       <c r="D220" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="E220" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F220" t="s">
+        <v>365</v>
+      </c>
+      <c r="G220" t="s">
         <v>366</v>
-      </c>
-      <c r="G220" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6682,16 +6682,16 @@
         <v>363</v>
       </c>
       <c r="D221" t="s">
+        <v>164</v>
+      </c>
+      <c r="E221" t="s">
         <v>364</v>
       </c>
-      <c r="E221" t="s">
+      <c r="F221" t="s">
         <v>365</v>
       </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>366</v>
-      </c>
-      <c r="G221" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6705,16 +6705,16 @@
         <v>363</v>
       </c>
       <c r="D222" t="s">
+        <v>164</v>
+      </c>
+      <c r="E222" t="s">
         <v>364</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
         <v>365</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>366</v>
-      </c>
-      <c r="G222" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6728,16 +6728,16 @@
         <v>363</v>
       </c>
       <c r="D223" t="s">
+        <v>164</v>
+      </c>
+      <c r="E223" t="s">
         <v>364</v>
       </c>
-      <c r="E223" t="s">
+      <c r="F223" t="s">
         <v>365</v>
       </c>
-      <c r="F223" t="s">
+      <c r="G223" t="s">
         <v>366</v>
-      </c>
-      <c r="G223" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6751,16 +6751,16 @@
         <v>363</v>
       </c>
       <c r="D224" t="s">
+        <v>164</v>
+      </c>
+      <c r="E224" t="s">
         <v>364</v>
       </c>
-      <c r="E224" t="s">
+      <c r="F224" t="s">
         <v>365</v>
       </c>
-      <c r="F224" t="s">
+      <c r="G224" t="s">
         <v>366</v>
-      </c>
-      <c r="G224" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6774,16 +6774,16 @@
         <v>363</v>
       </c>
       <c r="D225" t="s">
+        <v>164</v>
+      </c>
+      <c r="E225" t="s">
         <v>364</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" t="s">
         <v>365</v>
       </c>
-      <c r="F225" t="s">
+      <c r="G225" t="s">
         <v>366</v>
-      </c>
-      <c r="G225" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6797,16 +6797,16 @@
         <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="E226" t="s">
         <v>276</v>
       </c>
       <c r="F226" t="s">
+        <v>365</v>
+      </c>
+      <c r="G226" t="s">
         <v>366</v>
-      </c>
-      <c r="G226" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6820,16 +6820,16 @@
         <v>363</v>
       </c>
       <c r="D227" t="s">
+        <v>164</v>
+      </c>
+      <c r="E227" t="s">
         <v>364</v>
       </c>
-      <c r="E227" t="s">
+      <c r="F227" t="s">
         <v>365</v>
       </c>
-      <c r="F227" t="s">
+      <c r="G227" t="s">
         <v>366</v>
-      </c>
-      <c r="G227" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6843,16 +6843,16 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="E228" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F228" t="s">
+        <v>365</v>
+      </c>
+      <c r="G228" t="s">
         <v>366</v>
-      </c>
-      <c r="G228" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6866,16 +6866,16 @@
         <v>386</v>
       </c>
       <c r="D229" t="s">
+        <v>164</v>
+      </c>
+      <c r="E229" t="s">
         <v>364</v>
-      </c>
-      <c r="E229" t="s">
-        <v>365</v>
       </c>
       <c r="F229" t="s">
         <v>387</v>
       </c>
       <c r="G229" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6889,16 +6889,16 @@
         <v>386</v>
       </c>
       <c r="D230" t="s">
+        <v>164</v>
+      </c>
+      <c r="E230" t="s">
         <v>364</v>
-      </c>
-      <c r="E230" t="s">
-        <v>365</v>
       </c>
       <c r="F230" t="s">
         <v>387</v>
       </c>
       <c r="G230" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6912,16 +6912,16 @@
         <v>293</v>
       </c>
       <c r="D231" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="E231" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F231" t="s">
         <v>387</v>
       </c>
       <c r="G231" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6935,16 +6935,16 @@
         <v>309</v>
       </c>
       <c r="D232" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="E232" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F232" t="s">
         <v>387</v>
       </c>
       <c r="G232" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6958,16 +6958,16 @@
         <v>386</v>
       </c>
       <c r="D233" t="s">
+        <v>164</v>
+      </c>
+      <c r="E233" t="s">
         <v>364</v>
-      </c>
-      <c r="E233" t="s">
-        <v>365</v>
       </c>
       <c r="F233" t="s">
         <v>387</v>
       </c>
       <c r="G233" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6981,16 +6981,16 @@
         <v>386</v>
       </c>
       <c r="D234" t="s">
+        <v>164</v>
+      </c>
+      <c r="E234" t="s">
         <v>364</v>
-      </c>
-      <c r="E234" t="s">
-        <v>365</v>
       </c>
       <c r="F234" t="s">
         <v>387</v>
       </c>
       <c r="G234" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7004,16 +7004,16 @@
         <v>386</v>
       </c>
       <c r="D235" t="s">
+        <v>164</v>
+      </c>
+      <c r="E235" t="s">
         <v>364</v>
-      </c>
-      <c r="E235" t="s">
-        <v>365</v>
       </c>
       <c r="F235" t="s">
         <v>387</v>
       </c>
       <c r="G235" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7027,16 +7027,16 @@
         <v>386</v>
       </c>
       <c r="D236" t="s">
+        <v>164</v>
+      </c>
+      <c r="E236" t="s">
         <v>364</v>
-      </c>
-      <c r="E236" t="s">
-        <v>365</v>
       </c>
       <c r="F236" t="s">
         <v>387</v>
       </c>
       <c r="G236" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7050,16 +7050,16 @@
         <v>386</v>
       </c>
       <c r="D237" t="s">
+        <v>164</v>
+      </c>
+      <c r="E237" t="s">
         <v>364</v>
-      </c>
-      <c r="E237" t="s">
-        <v>365</v>
       </c>
       <c r="F237" t="s">
         <v>387</v>
       </c>
       <c r="G237" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7073,16 +7073,16 @@
         <v>386</v>
       </c>
       <c r="D238" t="s">
+        <v>164</v>
+      </c>
+      <c r="E238" t="s">
         <v>364</v>
-      </c>
-      <c r="E238" t="s">
-        <v>365</v>
       </c>
       <c r="F238" t="s">
         <v>387</v>
       </c>
       <c r="G238" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7096,16 +7096,16 @@
         <v>398</v>
       </c>
       <c r="D239" t="s">
+        <v>164</v>
+      </c>
+      <c r="E239" t="s">
         <v>364</v>
-      </c>
-      <c r="E239" t="s">
-        <v>365</v>
       </c>
       <c r="F239" t="s">
         <v>399</v>
       </c>
       <c r="G239" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7119,16 +7119,16 @@
         <v>163</v>
       </c>
       <c r="D240" t="s">
+        <v>164</v>
+      </c>
+      <c r="E240" t="s">
+        <v>165</v>
+      </c>
+      <c r="F240" t="s">
         <v>401</v>
       </c>
-      <c r="E240" t="s">
-        <v>164</v>
-      </c>
-      <c r="F240" t="s">
+      <c r="G240" t="s">
         <v>402</v>
-      </c>
-      <c r="G240" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7142,16 +7142,16 @@
         <v>163</v>
       </c>
       <c r="D241" t="s">
+        <v>164</v>
+      </c>
+      <c r="E241" t="s">
+        <v>165</v>
+      </c>
+      <c r="F241" t="s">
         <v>401</v>
       </c>
-      <c r="E241" t="s">
-        <v>164</v>
-      </c>
-      <c r="F241" t="s">
+      <c r="G241" t="s">
         <v>402</v>
-      </c>
-      <c r="G241" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7165,16 +7165,16 @@
         <v>163</v>
       </c>
       <c r="D242" t="s">
+        <v>164</v>
+      </c>
+      <c r="E242" t="s">
+        <v>165</v>
+      </c>
+      <c r="F242" t="s">
         <v>401</v>
       </c>
-      <c r="E242" t="s">
-        <v>164</v>
-      </c>
-      <c r="F242" t="s">
+      <c r="G242" t="s">
         <v>402</v>
-      </c>
-      <c r="G242" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7188,16 +7188,16 @@
         <v>163</v>
       </c>
       <c r="D243" t="s">
+        <v>164</v>
+      </c>
+      <c r="E243" t="s">
+        <v>165</v>
+      </c>
+      <c r="F243" t="s">
         <v>401</v>
       </c>
-      <c r="E243" t="s">
-        <v>164</v>
-      </c>
-      <c r="F243" t="s">
+      <c r="G243" t="s">
         <v>402</v>
-      </c>
-      <c r="G243" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7211,16 +7211,16 @@
         <v>163</v>
       </c>
       <c r="D244" t="s">
+        <v>164</v>
+      </c>
+      <c r="E244" t="s">
+        <v>165</v>
+      </c>
+      <c r="F244" t="s">
         <v>401</v>
       </c>
-      <c r="E244" t="s">
-        <v>164</v>
-      </c>
-      <c r="F244" t="s">
+      <c r="G244" t="s">
         <v>402</v>
-      </c>
-      <c r="G244" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7234,16 +7234,16 @@
         <v>163</v>
       </c>
       <c r="D245" t="s">
+        <v>164</v>
+      </c>
+      <c r="E245" t="s">
+        <v>165</v>
+      </c>
+      <c r="F245" t="s">
         <v>401</v>
       </c>
-      <c r="E245" t="s">
-        <v>164</v>
-      </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
         <v>402</v>
-      </c>
-      <c r="G245" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7257,7 +7257,7 @@
         <v>409</v>
       </c>
       <c r="D246" t="s">
-        <v>401</v>
+        <v>164</v>
       </c>
       <c r="E246" t="s">
         <v>256</v>
@@ -7266,7 +7266,7 @@
         <v>410</v>
       </c>
       <c r="G246" t="s">
-        <v>165</v>
+        <v>402</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7280,13 +7280,13 @@
         <v>95</v>
       </c>
       <c r="D247" t="s">
+        <v>96</v>
+      </c>
+      <c r="E247" t="s">
+        <v>97</v>
+      </c>
+      <c r="G247" t="s">
         <v>412</v>
-      </c>
-      <c r="E247" t="s">
-        <v>96</v>
-      </c>
-      <c r="G247" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7300,13 +7300,13 @@
         <v>95</v>
       </c>
       <c r="D248" t="s">
+        <v>96</v>
+      </c>
+      <c r="E248" t="s">
+        <v>97</v>
+      </c>
+      <c r="G248" t="s">
         <v>412</v>
-      </c>
-      <c r="E248" t="s">
-        <v>96</v>
-      </c>
-      <c r="G248" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7320,13 +7320,13 @@
         <v>415</v>
       </c>
       <c r="D249" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="E249" t="s">
         <v>416</v>
       </c>
       <c r="G249" t="s">
-        <v>97</v>
+        <v>412</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7340,13 +7340,13 @@
         <v>95</v>
       </c>
       <c r="D250" t="s">
+        <v>96</v>
+      </c>
+      <c r="E250" t="s">
+        <v>97</v>
+      </c>
+      <c r="G250" t="s">
         <v>412</v>
-      </c>
-      <c r="E250" t="s">
-        <v>96</v>
-      </c>
-      <c r="G250" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7360,13 +7360,13 @@
         <v>95</v>
       </c>
       <c r="D251" t="s">
+        <v>96</v>
+      </c>
+      <c r="E251" t="s">
+        <v>97</v>
+      </c>
+      <c r="G251" t="s">
         <v>412</v>
-      </c>
-      <c r="E251" t="s">
-        <v>96</v>
-      </c>
-      <c r="G251" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7380,13 +7380,13 @@
         <v>95</v>
       </c>
       <c r="D252" t="s">
+        <v>96</v>
+      </c>
+      <c r="E252" t="s">
+        <v>97</v>
+      </c>
+      <c r="G252" t="s">
         <v>412</v>
-      </c>
-      <c r="E252" t="s">
-        <v>96</v>
-      </c>
-      <c r="G252" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7400,13 +7400,13 @@
         <v>421</v>
       </c>
       <c r="D253" t="s">
+        <v>164</v>
+      </c>
+      <c r="E253" t="s">
         <v>422</v>
       </c>
-      <c r="E253" t="s">
+      <c r="G253" t="s">
         <v>423</v>
-      </c>
-      <c r="G253" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7420,13 +7420,13 @@
         <v>219</v>
       </c>
       <c r="D254" t="s">
-        <v>422</v>
+        <v>91</v>
       </c>
       <c r="E254" t="s">
         <v>220</v>
       </c>
       <c r="G254" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7440,13 +7440,13 @@
         <v>426</v>
       </c>
       <c r="D255" t="s">
-        <v>422</v>
+        <v>91</v>
       </c>
       <c r="E255" t="s">
         <v>427</v>
       </c>
       <c r="G255" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7460,13 +7460,13 @@
         <v>426</v>
       </c>
       <c r="D256" t="s">
-        <v>422</v>
+        <v>91</v>
       </c>
       <c r="E256" t="s">
         <v>427</v>
       </c>
       <c r="G256" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7480,13 +7480,13 @@
         <v>426</v>
       </c>
       <c r="D257" t="s">
-        <v>422</v>
+        <v>91</v>
       </c>
       <c r="E257" t="s">
         <v>427</v>
       </c>
       <c r="G257" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7500,13 +7500,13 @@
         <v>325</v>
       </c>
       <c r="D258" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="E258" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G258" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7520,13 +7520,13 @@
         <v>426</v>
       </c>
       <c r="D259" t="s">
-        <v>422</v>
+        <v>91</v>
       </c>
       <c r="E259" t="s">
         <v>427</v>
       </c>
       <c r="G259" t="s">
-        <v>93</v>
+        <v>423</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7540,13 +7540,13 @@
         <v>163</v>
       </c>
       <c r="D260" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="E260" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G260" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7560,13 +7560,13 @@
         <v>434</v>
       </c>
       <c r="D261" t="s">
-        <v>422</v>
+        <v>196</v>
       </c>
       <c r="E261" t="s">
         <v>435</v>
       </c>
       <c r="G261" t="s">
-        <v>197</v>
+        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7580,13 +7580,13 @@
         <v>163</v>
       </c>
       <c r="D262" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="E262" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G262" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7600,13 +7600,13 @@
         <v>438</v>
       </c>
       <c r="D263" t="s">
-        <v>422</v>
+        <v>183</v>
       </c>
       <c r="E263" t="s">
         <v>439</v>
       </c>
       <c r="G263" t="s">
-        <v>184</v>
+        <v>423</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7620,13 +7620,13 @@
         <v>31</v>
       </c>
       <c r="D264" t="s">
-        <v>422</v>
+        <v>32</v>
       </c>
       <c r="E264" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G264" t="s">
-        <v>33</v>
+        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7640,13 +7640,13 @@
         <v>9</v>
       </c>
       <c r="D265" t="s">
-        <v>422</v>
+        <v>10</v>
       </c>
       <c r="E265" t="s">
         <v>11</v>
       </c>
       <c r="G265" t="s">
-        <v>13</v>
+        <v>423</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7660,13 +7660,13 @@
         <v>443</v>
       </c>
       <c r="D266" t="s">
-        <v>422</v>
+        <v>113</v>
       </c>
       <c r="E266" t="s">
         <v>444</v>
       </c>
       <c r="G266" t="s">
-        <v>116</v>
+        <v>423</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7680,13 +7680,13 @@
         <v>118</v>
       </c>
       <c r="D267" t="s">
-        <v>446</v>
+        <v>113</v>
       </c>
       <c r="E267" t="s">
         <v>119</v>
       </c>
       <c r="G267" t="s">
-        <v>116</v>
+        <v>446</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7700,13 +7700,13 @@
         <v>202</v>
       </c>
       <c r="D268" t="s">
+        <v>183</v>
+      </c>
+      <c r="E268" t="s">
+        <v>203</v>
+      </c>
+      <c r="G268" t="s">
         <v>448</v>
-      </c>
-      <c r="E268" t="s">
-        <v>204</v>
-      </c>
-      <c r="G268" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7720,13 +7720,13 @@
         <v>118</v>
       </c>
       <c r="D269" t="s">
-        <v>450</v>
+        <v>113</v>
       </c>
       <c r="E269" t="s">
         <v>119</v>
       </c>
       <c r="G269" t="s">
-        <v>116</v>
+        <v>450</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7740,13 +7740,13 @@
         <v>118</v>
       </c>
       <c r="D270" t="s">
-        <v>450</v>
+        <v>113</v>
       </c>
       <c r="E270" t="s">
         <v>119</v>
       </c>
       <c r="G270" t="s">
-        <v>116</v>
+        <v>450</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7760,13 +7760,13 @@
         <v>453</v>
       </c>
       <c r="D271" t="s">
+        <v>113</v>
+      </c>
+      <c r="E271" t="s">
         <v>454</v>
       </c>
-      <c r="E271" t="s">
+      <c r="G271" t="s">
         <v>455</v>
-      </c>
-      <c r="G271" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7780,13 +7780,13 @@
         <v>453</v>
       </c>
       <c r="D272" t="s">
+        <v>113</v>
+      </c>
+      <c r="E272" t="s">
         <v>454</v>
       </c>
-      <c r="E272" t="s">
+      <c r="G272" t="s">
         <v>455</v>
-      </c>
-      <c r="G272" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7800,13 +7800,13 @@
         <v>453</v>
       </c>
       <c r="D273" t="s">
+        <v>113</v>
+      </c>
+      <c r="E273" t="s">
         <v>454</v>
       </c>
-      <c r="E273" t="s">
+      <c r="G273" t="s">
         <v>455</v>
-      </c>
-      <c r="G273" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7820,13 +7820,13 @@
         <v>453</v>
       </c>
       <c r="D274" t="s">
+        <v>113</v>
+      </c>
+      <c r="E274" t="s">
         <v>454</v>
       </c>
-      <c r="E274" t="s">
+      <c r="G274" t="s">
         <v>455</v>
-      </c>
-      <c r="G274" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7840,13 +7840,13 @@
         <v>453</v>
       </c>
       <c r="D275" t="s">
+        <v>113</v>
+      </c>
+      <c r="E275" t="s">
         <v>454</v>
       </c>
-      <c r="E275" t="s">
+      <c r="G275" t="s">
         <v>455</v>
-      </c>
-      <c r="G275" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7860,13 +7860,13 @@
         <v>453</v>
       </c>
       <c r="D276" t="s">
+        <v>113</v>
+      </c>
+      <c r="E276" t="s">
         <v>454</v>
       </c>
-      <c r="E276" t="s">
+      <c r="G276" t="s">
         <v>455</v>
-      </c>
-      <c r="G276" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7880,13 +7880,13 @@
         <v>453</v>
       </c>
       <c r="D277" t="s">
+        <v>113</v>
+      </c>
+      <c r="E277" t="s">
         <v>454</v>
       </c>
-      <c r="E277" t="s">
+      <c r="G277" t="s">
         <v>455</v>
-      </c>
-      <c r="G277" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7900,13 +7900,13 @@
         <v>202</v>
       </c>
       <c r="D278" t="s">
+        <v>183</v>
+      </c>
+      <c r="E278" t="s">
+        <v>203</v>
+      </c>
+      <c r="G278" t="s">
         <v>463</v>
-      </c>
-      <c r="E278" t="s">
-        <v>204</v>
-      </c>
-      <c r="G278" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7920,13 +7920,13 @@
         <v>51</v>
       </c>
       <c r="D279" t="s">
+        <v>32</v>
+      </c>
+      <c r="E279" t="s">
+        <v>52</v>
+      </c>
+      <c r="G279" t="s">
         <v>463</v>
-      </c>
-      <c r="E279" t="s">
-        <v>53</v>
-      </c>
-      <c r="G279" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7940,13 +7940,13 @@
         <v>9</v>
       </c>
       <c r="D280" t="s">
-        <v>463</v>
+        <v>10</v>
       </c>
       <c r="E280" t="s">
         <v>11</v>
       </c>
       <c r="G280" t="s">
-        <v>13</v>
+        <v>463</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7960,13 +7960,13 @@
         <v>170</v>
       </c>
       <c r="D281" t="s">
-        <v>463</v>
+        <v>113</v>
       </c>
       <c r="E281" t="s">
         <v>171</v>
       </c>
       <c r="G281" t="s">
-        <v>116</v>
+        <v>463</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7980,13 +7980,13 @@
         <v>124</v>
       </c>
       <c r="D282" t="s">
+        <v>125</v>
+      </c>
+      <c r="E282" t="s">
+        <v>126</v>
+      </c>
+      <c r="G282" t="s">
         <v>463</v>
-      </c>
-      <c r="E282" t="s">
-        <v>125</v>
-      </c>
-      <c r="G282" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -8000,13 +8000,13 @@
         <v>398</v>
       </c>
       <c r="D283" t="s">
+        <v>164</v>
+      </c>
+      <c r="E283" t="s">
+        <v>364</v>
+      </c>
+      <c r="G283" t="s">
         <v>469</v>
-      </c>
-      <c r="E283" t="s">
-        <v>365</v>
-      </c>
-      <c r="G283" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8020,13 +8020,13 @@
         <v>124</v>
       </c>
       <c r="D284" t="s">
+        <v>125</v>
+      </c>
+      <c r="E284" t="s">
+        <v>126</v>
+      </c>
+      <c r="G284" t="s">
         <v>471</v>
-      </c>
-      <c r="E284" t="s">
-        <v>125</v>
-      </c>
-      <c r="G284" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8040,13 +8040,13 @@
         <v>170</v>
       </c>
       <c r="D285" t="s">
-        <v>473</v>
+        <v>113</v>
       </c>
       <c r="E285" t="s">
         <v>171</v>
       </c>
       <c r="G285" t="s">
-        <v>116</v>
+        <v>473</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8060,13 +8060,13 @@
         <v>438</v>
       </c>
       <c r="D286" t="s">
-        <v>475</v>
+        <v>183</v>
       </c>
       <c r="E286" t="s">
         <v>439</v>
       </c>
       <c r="G286" t="s">
-        <v>184</v>
+        <v>475</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8080,13 +8080,13 @@
         <v>438</v>
       </c>
       <c r="D287" t="s">
-        <v>475</v>
+        <v>183</v>
       </c>
       <c r="E287" t="s">
         <v>439</v>
       </c>
       <c r="G287" t="s">
-        <v>184</v>
+        <v>475</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8100,13 +8100,13 @@
         <v>41</v>
       </c>
       <c r="D288" t="s">
-        <v>475</v>
+        <v>10</v>
       </c>
       <c r="E288" t="s">
         <v>42</v>
       </c>
       <c r="G288" t="s">
-        <v>13</v>
+        <v>475</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8120,13 +8120,13 @@
         <v>31</v>
       </c>
       <c r="D289" t="s">
+        <v>32</v>
+      </c>
+      <c r="E289" t="s">
+        <v>33</v>
+      </c>
+      <c r="G289" t="s">
         <v>475</v>
-      </c>
-      <c r="E289" t="s">
-        <v>32</v>
-      </c>
-      <c r="G289" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8140,13 +8140,13 @@
         <v>31</v>
       </c>
       <c r="D290" t="s">
+        <v>32</v>
+      </c>
+      <c r="E290" t="s">
+        <v>33</v>
+      </c>
+      <c r="G290" t="s">
         <v>475</v>
-      </c>
-      <c r="E290" t="s">
-        <v>32</v>
-      </c>
-      <c r="G290" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8160,13 +8160,13 @@
         <v>170</v>
       </c>
       <c r="D291" t="s">
-        <v>475</v>
+        <v>113</v>
       </c>
       <c r="E291" t="s">
         <v>171</v>
       </c>
       <c r="G291" t="s">
-        <v>116</v>
+        <v>475</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8180,13 +8180,13 @@
         <v>170</v>
       </c>
       <c r="D292" t="s">
-        <v>475</v>
+        <v>113</v>
       </c>
       <c r="E292" t="s">
         <v>171</v>
       </c>
       <c r="G292" t="s">
-        <v>116</v>
+        <v>475</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8200,13 +8200,13 @@
         <v>170</v>
       </c>
       <c r="D293" t="s">
-        <v>475</v>
+        <v>113</v>
       </c>
       <c r="E293" t="s">
         <v>171</v>
       </c>
       <c r="G293" t="s">
-        <v>116</v>
+        <v>475</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8220,13 +8220,13 @@
         <v>170</v>
       </c>
       <c r="D294" t="s">
-        <v>475</v>
+        <v>113</v>
       </c>
       <c r="E294" t="s">
         <v>171</v>
       </c>
       <c r="G294" t="s">
-        <v>116</v>
+        <v>475</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8240,13 +8240,13 @@
         <v>170</v>
       </c>
       <c r="D295" t="s">
-        <v>485</v>
+        <v>113</v>
       </c>
       <c r="E295" t="s">
         <v>171</v>
       </c>
       <c r="G295" t="s">
-        <v>116</v>
+        <v>485</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8260,13 +8260,13 @@
         <v>170</v>
       </c>
       <c r="D296" t="s">
-        <v>485</v>
+        <v>113</v>
       </c>
       <c r="E296" t="s">
         <v>171</v>
       </c>
       <c r="G296" t="s">
-        <v>116</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,75 +22,75 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,99 +109,99 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>09.2.2 - Upper‐secondary education (IS)</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,42 +811,42 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>04.3.3 - Nuclear fuel (CS)</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>04.2.2 - Forestry (CS)</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>04.2.3 - Fishing and hunting (CS)</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,21 +1210,21 @@
     <t>32310</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>04.4.3 - Construction (CS)</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
   </si>
   <si>
     <t>60020</t>
@@ -1869,13 +1869,13 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1915,13 +1915,13 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1938,13 +1938,13 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1964,7 +1964,7 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -1984,13 +1984,13 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>23</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2007,13 +2007,13 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>23</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2024,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
       <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>23</v>
       </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2050,16 +2050,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2076,13 +2076,13 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
         <v>36</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2122,13 +2122,13 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" t="s">
         <v>42</v>
-      </c>
-      <c r="F14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2145,13 +2145,13 @@
         <v>10</v>
       </c>
       <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
         <v>45</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>46</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2168,13 +2168,13 @@
         <v>10</v>
       </c>
       <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" t="s">
         <v>49</v>
-      </c>
-      <c r="F16" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2188,10 +2188,10 @@
         <v>51</v>
       </c>
       <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
         <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>52</v>
       </c>
       <c r="F17" t="s">
         <v>53</v>
@@ -2211,10 +2211,10 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" t="s">
         <v>32</v>
-      </c>
-      <c r="E18" t="s">
-        <v>52</v>
       </c>
       <c r="F18" t="s">
         <v>53</v>
@@ -2234,16 +2234,16 @@
         <v>57</v>
       </c>
       <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" t="s">
         <v>32</v>
-      </c>
-      <c r="E19" t="s">
-        <v>58</v>
       </c>
       <c r="F19" t="s">
         <v>53</v>
       </c>
       <c r="G19" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2257,16 +2257,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" t="s">
         <v>32</v>
-      </c>
-      <c r="E20" t="s">
-        <v>61</v>
       </c>
       <c r="F20" t="s">
         <v>53</v>
       </c>
       <c r="G20" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2280,10 +2280,10 @@
         <v>51</v>
       </c>
       <c r="D21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" t="s">
         <v>32</v>
-      </c>
-      <c r="E21" t="s">
-        <v>52</v>
       </c>
       <c r="F21" t="s">
         <v>53</v>
@@ -2303,16 +2303,16 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" t="s">
         <v>32</v>
-      </c>
-      <c r="E22" t="s">
-        <v>33</v>
       </c>
       <c r="F22" t="s">
         <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2326,16 +2326,16 @@
         <v>66</v>
       </c>
       <c r="D23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" t="s">
         <v>32</v>
-      </c>
-      <c r="E23" t="s">
-        <v>67</v>
       </c>
       <c r="F23" t="s">
         <v>64</v>
       </c>
       <c r="G23" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2349,16 +2349,16 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
         <v>32</v>
-      </c>
-      <c r="E24" t="s">
-        <v>33</v>
       </c>
       <c r="F24" t="s">
         <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2372,16 +2372,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" t="s">
         <v>32</v>
-      </c>
-      <c r="E25" t="s">
-        <v>33</v>
       </c>
       <c r="F25" t="s">
         <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2395,16 +2395,16 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" t="s">
         <v>32</v>
-      </c>
-      <c r="E26" t="s">
-        <v>33</v>
       </c>
       <c r="F26" t="s">
         <v>64</v>
       </c>
       <c r="G26" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2418,16 +2418,16 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
         <v>32</v>
-      </c>
-      <c r="E27" t="s">
-        <v>33</v>
       </c>
       <c r="F27" t="s">
         <v>64</v>
       </c>
       <c r="G27" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2441,16 +2441,16 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
         <v>32</v>
-      </c>
-      <c r="E28" t="s">
-        <v>33</v>
       </c>
       <c r="F28" t="s">
         <v>64</v>
       </c>
       <c r="G28" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2464,16 +2464,16 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" t="s">
         <v>32</v>
-      </c>
-      <c r="E29" t="s">
-        <v>33</v>
       </c>
       <c r="F29" t="s">
         <v>64</v>
       </c>
       <c r="G29" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2487,10 +2487,10 @@
         <v>51</v>
       </c>
       <c r="D30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" t="s">
         <v>32</v>
-      </c>
-      <c r="E30" t="s">
-        <v>52</v>
       </c>
       <c r="F30" t="s">
         <v>64</v>
@@ -2510,16 +2510,16 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" t="s">
         <v>32</v>
-      </c>
-      <c r="E31" t="s">
-        <v>33</v>
       </c>
       <c r="F31" t="s">
         <v>76</v>
       </c>
       <c r="G31" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2533,16 +2533,16 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" t="s">
         <v>32</v>
-      </c>
-      <c r="E32" t="s">
-        <v>33</v>
       </c>
       <c r="F32" t="s">
         <v>76</v>
       </c>
       <c r="G32" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2556,16 +2556,16 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" t="s">
         <v>32</v>
-      </c>
-      <c r="E33" t="s">
-        <v>33</v>
       </c>
       <c r="F33" t="s">
         <v>76</v>
       </c>
       <c r="G33" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2579,16 +2579,16 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" t="s">
         <v>32</v>
-      </c>
-      <c r="E34" t="s">
-        <v>33</v>
       </c>
       <c r="F34" t="s">
         <v>76</v>
       </c>
       <c r="G34" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2602,16 +2602,16 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" t="s">
         <v>32</v>
-      </c>
-      <c r="E35" t="s">
-        <v>33</v>
       </c>
       <c r="F35" t="s">
         <v>76</v>
       </c>
       <c r="G35" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2625,16 +2625,16 @@
         <v>57</v>
       </c>
       <c r="D36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" t="s">
         <v>32</v>
-      </c>
-      <c r="E36" t="s">
-        <v>58</v>
       </c>
       <c r="F36" t="s">
         <v>76</v>
       </c>
       <c r="G36" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2648,13 +2648,13 @@
         <v>31</v>
       </c>
       <c r="D37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" t="s">
         <v>32</v>
       </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>33</v>
-      </c>
-      <c r="G37" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2668,13 +2668,13 @@
         <v>31</v>
       </c>
       <c r="D38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" t="s">
         <v>32</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>33</v>
-      </c>
-      <c r="G38" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2688,13 +2688,13 @@
         <v>31</v>
       </c>
       <c r="D39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" t="s">
         <v>32</v>
       </c>
-      <c r="E39" t="s">
+      <c r="G39" t="s">
         <v>33</v>
-      </c>
-      <c r="G39" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2708,13 +2708,13 @@
         <v>31</v>
       </c>
       <c r="D40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" t="s">
         <v>32</v>
       </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
         <v>33</v>
-      </c>
-      <c r="G40" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2728,13 +2728,13 @@
         <v>51</v>
       </c>
       <c r="D41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" t="s">
         <v>32</v>
       </c>
-      <c r="E41" t="s">
-        <v>52</v>
-      </c>
       <c r="G41" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2748,13 +2748,13 @@
         <v>57</v>
       </c>
       <c r="D42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" t="s">
         <v>32</v>
       </c>
-      <c r="E42" t="s">
+      <c r="G42" t="s">
         <v>58</v>
-      </c>
-      <c r="G42" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2788,13 +2788,13 @@
         <v>95</v>
       </c>
       <c r="D44" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" t="s">
         <v>96</v>
       </c>
-      <c r="E44" t="s">
+      <c r="G44" t="s">
         <v>97</v>
-      </c>
-      <c r="G44" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2848,13 +2848,13 @@
         <v>101</v>
       </c>
       <c r="D47" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" t="s">
         <v>96</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>102</v>
-      </c>
-      <c r="G47" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2908,13 +2908,13 @@
         <v>101</v>
       </c>
       <c r="D50" t="s">
+        <v>91</v>
+      </c>
+      <c r="E50" t="s">
         <v>96</v>
       </c>
-      <c r="E50" t="s">
+      <c r="G50" t="s">
         <v>102</v>
-      </c>
-      <c r="G50" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2948,13 +2948,13 @@
         <v>108</v>
       </c>
       <c r="D52" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" t="s">
         <v>96</v>
       </c>
-      <c r="E52" t="s">
+      <c r="G52" t="s">
         <v>109</v>
-      </c>
-      <c r="G52" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2968,13 +2968,13 @@
         <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3014,13 +3014,13 @@
         <v>113</v>
       </c>
       <c r="E55" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F55" t="s">
         <v>115</v>
       </c>
       <c r="G55" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3037,13 +3037,13 @@
         <v>113</v>
       </c>
       <c r="E56" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F56" t="s">
         <v>115</v>
       </c>
       <c r="G56" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3057,16 +3057,16 @@
         <v>124</v>
       </c>
       <c r="D57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" t="s">
         <v>125</v>
-      </c>
-      <c r="E57" t="s">
-        <v>126</v>
       </c>
       <c r="F57" t="s">
         <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3083,13 +3083,13 @@
         <v>113</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
         <v>115</v>
       </c>
       <c r="G58" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3106,13 +3106,13 @@
         <v>113</v>
       </c>
       <c r="E59" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
         <v>115</v>
       </c>
       <c r="G59" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3129,13 +3129,13 @@
         <v>113</v>
       </c>
       <c r="E60" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F60" t="s">
         <v>115</v>
       </c>
       <c r="G60" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3152,13 +3152,13 @@
         <v>113</v>
       </c>
       <c r="E61" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
       </c>
       <c r="G61" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3175,13 +3175,13 @@
         <v>113</v>
       </c>
       <c r="E62" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
       </c>
       <c r="G62" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3192,19 +3192,19 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
         <v>113</v>
       </c>
       <c r="E63" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
       </c>
       <c r="G63" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3215,19 +3215,19 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D64" t="s">
         <v>113</v>
       </c>
       <c r="E64" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
       </c>
       <c r="G64" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3244,13 +3244,13 @@
         <v>113</v>
       </c>
       <c r="E65" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F65" t="s">
         <v>115</v>
       </c>
       <c r="G65" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3290,13 +3290,13 @@
         <v>113</v>
       </c>
       <c r="E67" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
       </c>
       <c r="G67" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3307,7 +3307,7 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="D68" t="s">
         <v>113</v>
@@ -3319,7 +3319,7 @@
         <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3330,7 +3330,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D69" t="s">
         <v>113</v>
@@ -3342,7 +3342,7 @@
         <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3359,13 +3359,13 @@
         <v>113</v>
       </c>
       <c r="E70" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F70" t="s">
         <v>115</v>
       </c>
       <c r="G70" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3382,13 +3382,13 @@
         <v>113</v>
       </c>
       <c r="E71" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F71" t="s">
         <v>115</v>
       </c>
       <c r="G71" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3425,16 +3425,16 @@
         <v>148</v>
       </c>
       <c r="D73" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" t="s">
         <v>125</v>
-      </c>
-      <c r="E73" t="s">
-        <v>149</v>
       </c>
       <c r="F73" t="s">
         <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3448,16 +3448,16 @@
         <v>151</v>
       </c>
       <c r="D74" t="s">
+        <v>113</v>
+      </c>
+      <c r="E74" t="s">
         <v>125</v>
-      </c>
-      <c r="E74" t="s">
-        <v>152</v>
       </c>
       <c r="F74" t="s">
         <v>115</v>
       </c>
       <c r="G74" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3471,16 +3471,16 @@
         <v>154</v>
       </c>
       <c r="D75" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" t="s">
         <v>125</v>
-      </c>
-      <c r="E75" t="s">
-        <v>155</v>
       </c>
       <c r="F75" t="s">
         <v>115</v>
       </c>
       <c r="G75" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3494,16 +3494,16 @@
         <v>148</v>
       </c>
       <c r="D76" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76" t="s">
         <v>125</v>
-      </c>
-      <c r="E76" t="s">
-        <v>149</v>
       </c>
       <c r="F76" t="s">
         <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3517,16 +3517,16 @@
         <v>148</v>
       </c>
       <c r="D77" t="s">
+        <v>113</v>
+      </c>
+      <c r="E77" t="s">
         <v>125</v>
-      </c>
-      <c r="E77" t="s">
-        <v>149</v>
       </c>
       <c r="F77" t="s">
         <v>115</v>
       </c>
       <c r="G77" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3540,16 +3540,16 @@
         <v>151</v>
       </c>
       <c r="D78" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" t="s">
         <v>125</v>
-      </c>
-      <c r="E78" t="s">
-        <v>152</v>
       </c>
       <c r="F78" t="s">
         <v>115</v>
       </c>
       <c r="G78" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3563,16 +3563,16 @@
         <v>160</v>
       </c>
       <c r="D79" t="s">
+        <v>113</v>
+      </c>
+      <c r="E79" t="s">
         <v>125</v>
-      </c>
-      <c r="E79" t="s">
-        <v>161</v>
       </c>
       <c r="F79" t="s">
         <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3586,16 +3586,16 @@
         <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="E80" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F80" t="s">
         <v>115</v>
       </c>
       <c r="G80" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3609,16 +3609,16 @@
         <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="E81" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F81" t="s">
         <v>115</v>
       </c>
       <c r="G81" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3632,16 +3632,16 @@
         <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="E82" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F82" t="s">
         <v>115</v>
       </c>
       <c r="G82" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D83" t="s">
         <v>113</v>
@@ -3664,7 +3664,7 @@
         <v>115</v>
       </c>
       <c r="G83" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3681,13 +3681,13 @@
         <v>113</v>
       </c>
       <c r="E84" t="s">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="F84" t="s">
         <v>115</v>
       </c>
       <c r="G84" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3698,19 +3698,19 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="D85" t="s">
         <v>113</v>
       </c>
       <c r="E85" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F85" t="s">
         <v>115</v>
       </c>
       <c r="G85" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3724,16 +3724,16 @@
         <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="E86" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F86" t="s">
         <v>115</v>
       </c>
       <c r="G86" t="s">
-        <v>116</v>
+        <v>176</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,19 +3744,19 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="D87" t="s">
         <v>113</v>
       </c>
       <c r="E87" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F87" t="s">
         <v>115</v>
       </c>
       <c r="G87" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3773,13 +3773,13 @@
         <v>113</v>
       </c>
       <c r="E88" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F88" t="s">
         <v>115</v>
       </c>
       <c r="G88" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3796,13 +3796,13 @@
         <v>113</v>
       </c>
       <c r="E89" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F89" t="s">
         <v>115</v>
       </c>
       <c r="G89" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3816,16 +3816,16 @@
         <v>124</v>
       </c>
       <c r="D90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E90" t="s">
         <v>125</v>
-      </c>
-      <c r="E90" t="s">
-        <v>126</v>
       </c>
       <c r="F90" t="s">
         <v>115</v>
       </c>
       <c r="G90" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3839,16 +3839,16 @@
         <v>182</v>
       </c>
       <c r="D91" t="s">
+        <v>113</v>
+      </c>
+      <c r="E91" t="s">
         <v>183</v>
-      </c>
-      <c r="E91" t="s">
-        <v>184</v>
       </c>
       <c r="F91" t="s">
         <v>115</v>
       </c>
       <c r="G91" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3862,16 +3862,16 @@
         <v>124</v>
       </c>
       <c r="D92" t="s">
+        <v>113</v>
+      </c>
+      <c r="E92" t="s">
         <v>125</v>
-      </c>
-      <c r="E92" t="s">
-        <v>126</v>
       </c>
       <c r="F92" t="s">
         <v>115</v>
       </c>
       <c r="G92" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3888,13 +3888,13 @@
         <v>113</v>
       </c>
       <c r="E93" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F93" t="s">
         <v>115</v>
       </c>
       <c r="G93" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3908,16 +3908,16 @@
         <v>124</v>
       </c>
       <c r="D94" t="s">
+        <v>113</v>
+      </c>
+      <c r="E94" t="s">
         <v>125</v>
-      </c>
-      <c r="E94" t="s">
-        <v>126</v>
       </c>
       <c r="F94" t="s">
         <v>115</v>
       </c>
       <c r="G94" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3934,13 +3934,13 @@
         <v>113</v>
       </c>
       <c r="E95" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="F95" t="s">
         <v>115</v>
       </c>
       <c r="G95" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3954,16 +3954,16 @@
         <v>124</v>
       </c>
       <c r="D96" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" t="s">
         <v>125</v>
-      </c>
-      <c r="E96" t="s">
-        <v>126</v>
       </c>
       <c r="F96" t="s">
         <v>192</v>
       </c>
       <c r="G96" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3977,16 +3977,16 @@
         <v>124</v>
       </c>
       <c r="D97" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" t="s">
         <v>125</v>
-      </c>
-      <c r="E97" t="s">
-        <v>126</v>
       </c>
       <c r="F97" t="s">
         <v>192</v>
       </c>
       <c r="G97" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4000,16 +4000,16 @@
         <v>195</v>
       </c>
       <c r="D98" t="s">
+        <v>113</v>
+      </c>
+      <c r="E98" t="s">
         <v>196</v>
-      </c>
-      <c r="E98" t="s">
-        <v>197</v>
       </c>
       <c r="F98" t="s">
         <v>192</v>
       </c>
       <c r="G98" t="s">
-        <v>116</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4023,16 +4023,16 @@
         <v>124</v>
       </c>
       <c r="D99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99" t="s">
         <v>125</v>
-      </c>
-      <c r="E99" t="s">
-        <v>126</v>
       </c>
       <c r="F99" t="s">
         <v>192</v>
       </c>
       <c r="G99" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4046,16 +4046,16 @@
         <v>154</v>
       </c>
       <c r="D100" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" t="s">
         <v>125</v>
-      </c>
-      <c r="E100" t="s">
-        <v>155</v>
       </c>
       <c r="F100" t="s">
         <v>192</v>
       </c>
       <c r="G100" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4069,16 +4069,16 @@
         <v>124</v>
       </c>
       <c r="D101" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" t="s">
         <v>125</v>
-      </c>
-      <c r="E101" t="s">
-        <v>126</v>
       </c>
       <c r="F101" t="s">
         <v>192</v>
       </c>
       <c r="G101" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4092,10 +4092,10 @@
         <v>202</v>
       </c>
       <c r="D102" t="s">
+        <v>203</v>
+      </c>
+      <c r="E102" t="s">
         <v>183</v>
-      </c>
-      <c r="E102" t="s">
-        <v>203</v>
       </c>
       <c r="G102" t="s">
         <v>204</v>
@@ -4112,10 +4112,10 @@
         <v>202</v>
       </c>
       <c r="D103" t="s">
+        <v>203</v>
+      </c>
+      <c r="E103" t="s">
         <v>183</v>
-      </c>
-      <c r="E103" t="s">
-        <v>203</v>
       </c>
       <c r="G103" t="s">
         <v>204</v>
@@ -4132,10 +4132,10 @@
         <v>202</v>
       </c>
       <c r="D104" t="s">
+        <v>203</v>
+      </c>
+      <c r="E104" t="s">
         <v>183</v>
-      </c>
-      <c r="E104" t="s">
-        <v>203</v>
       </c>
       <c r="G104" t="s">
         <v>204</v>
@@ -4152,13 +4152,13 @@
         <v>208</v>
       </c>
       <c r="D105" t="s">
+        <v>203</v>
+      </c>
+      <c r="E105" t="s">
         <v>183</v>
       </c>
-      <c r="E105" t="s">
+      <c r="G105" t="s">
         <v>209</v>
-      </c>
-      <c r="G105" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4172,10 +4172,10 @@
         <v>202</v>
       </c>
       <c r="D106" t="s">
+        <v>203</v>
+      </c>
+      <c r="E106" t="s">
         <v>183</v>
-      </c>
-      <c r="E106" t="s">
-        <v>203</v>
       </c>
       <c r="G106" t="s">
         <v>204</v>
@@ -4192,13 +4192,13 @@
         <v>182</v>
       </c>
       <c r="D107" t="s">
+        <v>203</v>
+      </c>
+      <c r="E107" t="s">
         <v>183</v>
       </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>184</v>
-      </c>
-      <c r="G107" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4212,13 +4212,13 @@
         <v>213</v>
       </c>
       <c r="D108" t="s">
+        <v>203</v>
+      </c>
+      <c r="E108" t="s">
         <v>183</v>
       </c>
-      <c r="E108" t="s">
+      <c r="G108" t="s">
         <v>214</v>
-      </c>
-      <c r="G108" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4232,13 +4232,13 @@
         <v>216</v>
       </c>
       <c r="D109" t="s">
-        <v>91</v>
+        <v>203</v>
       </c>
       <c r="E109" t="s">
+        <v>92</v>
+      </c>
+      <c r="G109" t="s">
         <v>217</v>
-      </c>
-      <c r="G109" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4252,13 +4252,13 @@
         <v>219</v>
       </c>
       <c r="D110" t="s">
-        <v>91</v>
+        <v>203</v>
       </c>
       <c r="E110" t="s">
+        <v>92</v>
+      </c>
+      <c r="G110" t="s">
         <v>220</v>
-      </c>
-      <c r="G110" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4272,10 +4272,10 @@
         <v>202</v>
       </c>
       <c r="D111" t="s">
+        <v>203</v>
+      </c>
+      <c r="E111" t="s">
         <v>183</v>
-      </c>
-      <c r="E111" t="s">
-        <v>203</v>
       </c>
       <c r="G111" t="s">
         <v>204</v>
@@ -4292,13 +4292,13 @@
         <v>223</v>
       </c>
       <c r="D112" t="s">
+        <v>203</v>
+      </c>
+      <c r="E112" t="s">
         <v>224</v>
       </c>
-      <c r="E112" t="s">
+      <c r="G112" t="s">
         <v>225</v>
-      </c>
-      <c r="G112" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4309,16 +4309,16 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D113" t="s">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="E113" t="s">
         <v>114</v>
       </c>
       <c r="G113" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4332,13 +4332,13 @@
         <v>151</v>
       </c>
       <c r="D114" t="s">
+        <v>203</v>
+      </c>
+      <c r="E114" t="s">
         <v>125</v>
       </c>
-      <c r="E114" t="s">
+      <c r="G114" t="s">
         <v>152</v>
-      </c>
-      <c r="G114" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4352,13 +4352,13 @@
         <v>182</v>
       </c>
       <c r="D115" t="s">
+        <v>203</v>
+      </c>
+      <c r="E115" t="s">
         <v>183</v>
       </c>
-      <c r="E115" t="s">
+      <c r="G115" t="s">
         <v>184</v>
-      </c>
-      <c r="G115" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4372,13 +4372,13 @@
         <v>230</v>
       </c>
       <c r="D116" t="s">
+        <v>203</v>
+      </c>
+      <c r="E116" t="s">
         <v>224</v>
       </c>
-      <c r="E116" t="s">
+      <c r="G116" t="s">
         <v>231</v>
-      </c>
-      <c r="G116" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4392,13 +4392,13 @@
         <v>223</v>
       </c>
       <c r="D117" t="s">
+        <v>203</v>
+      </c>
+      <c r="E117" t="s">
         <v>224</v>
       </c>
-      <c r="E117" t="s">
+      <c r="G117" t="s">
         <v>225</v>
-      </c>
-      <c r="G117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4409,16 +4409,16 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
+        <v>163</v>
+      </c>
+      <c r="D118" t="s">
+        <v>203</v>
+      </c>
+      <c r="E118" t="s">
+        <v>164</v>
+      </c>
+      <c r="G118" t="s">
         <v>234</v>
-      </c>
-      <c r="D118" t="s">
-        <v>164</v>
-      </c>
-      <c r="E118" t="s">
-        <v>165</v>
-      </c>
-      <c r="G118" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4432,13 +4432,13 @@
         <v>182</v>
       </c>
       <c r="D119" t="s">
+        <v>203</v>
+      </c>
+      <c r="E119" t="s">
         <v>183</v>
       </c>
-      <c r="E119" t="s">
+      <c r="G119" t="s">
         <v>184</v>
-      </c>
-      <c r="G119" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4452,13 +4452,13 @@
         <v>170</v>
       </c>
       <c r="D120" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="E120" t="s">
+        <v>114</v>
+      </c>
+      <c r="G120" t="s">
         <v>171</v>
-      </c>
-      <c r="G120" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4469,16 +4469,16 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D121" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="E121" t="s">
         <v>114</v>
       </c>
       <c r="G121" t="s">
-        <v>237</v>
+        <v>143</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4492,13 +4492,13 @@
         <v>170</v>
       </c>
       <c r="D122" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="E122" t="s">
+        <v>114</v>
+      </c>
+      <c r="G122" t="s">
         <v>171</v>
-      </c>
-      <c r="G122" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4512,13 +4512,13 @@
         <v>170</v>
       </c>
       <c r="D123" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="E123" t="s">
+        <v>114</v>
+      </c>
+      <c r="G123" t="s">
         <v>171</v>
-      </c>
-      <c r="G123" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4532,13 +4532,13 @@
         <v>242</v>
       </c>
       <c r="D124" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="E124" t="s">
+        <v>164</v>
+      </c>
+      <c r="G124" t="s">
         <v>243</v>
-      </c>
-      <c r="G124" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4552,13 +4552,13 @@
         <v>242</v>
       </c>
       <c r="D125" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="E125" t="s">
+        <v>164</v>
+      </c>
+      <c r="G125" t="s">
         <v>243</v>
-      </c>
-      <c r="G125" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4572,13 +4572,13 @@
         <v>242</v>
       </c>
       <c r="D126" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="E126" t="s">
+        <v>164</v>
+      </c>
+      <c r="G126" t="s">
         <v>243</v>
-      </c>
-      <c r="G126" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4592,13 +4592,13 @@
         <v>242</v>
       </c>
       <c r="D127" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="E127" t="s">
+        <v>164</v>
+      </c>
+      <c r="G127" t="s">
         <v>243</v>
-      </c>
-      <c r="G127" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4612,13 +4612,13 @@
         <v>242</v>
       </c>
       <c r="D128" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="E128" t="s">
+        <v>164</v>
+      </c>
+      <c r="G128" t="s">
         <v>243</v>
-      </c>
-      <c r="G128" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>242</v>
+      </c>
+      <c r="D129" t="s">
+        <v>237</v>
+      </c>
+      <c r="E129" t="s">
+        <v>164</v>
+      </c>
+      <c r="G129" t="s">
         <v>249</v>
-      </c>
-      <c r="D129" t="s">
-        <v>164</v>
-      </c>
-      <c r="E129" t="s">
-        <v>243</v>
-      </c>
-      <c r="G129" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
+        <v>242</v>
+      </c>
+      <c r="D130" t="s">
+        <v>237</v>
+      </c>
+      <c r="E130" t="s">
+        <v>164</v>
+      </c>
+      <c r="G130" t="s">
         <v>251</v>
-      </c>
-      <c r="D130" t="s">
-        <v>164</v>
-      </c>
-      <c r="E130" t="s">
-        <v>243</v>
-      </c>
-      <c r="G130" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
+        <v>242</v>
+      </c>
+      <c r="D131" t="s">
+        <v>237</v>
+      </c>
+      <c r="E131" t="s">
+        <v>164</v>
+      </c>
+      <c r="G131" t="s">
         <v>253</v>
-      </c>
-      <c r="D131" t="s">
-        <v>164</v>
-      </c>
-      <c r="E131" t="s">
-        <v>243</v>
-      </c>
-      <c r="G131" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4692,13 +4692,13 @@
         <v>255</v>
       </c>
       <c r="D132" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="E132" t="s">
+        <v>164</v>
+      </c>
+      <c r="G132" t="s">
         <v>256</v>
-      </c>
-      <c r="G132" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4712,13 +4712,13 @@
         <v>189</v>
       </c>
       <c r="D133" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="E133" t="s">
+        <v>114</v>
+      </c>
+      <c r="G133" t="s">
         <v>190</v>
-      </c>
-      <c r="G133" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4732,13 +4732,13 @@
         <v>175</v>
       </c>
       <c r="D134" t="s">
-        <v>164</v>
+        <v>259</v>
       </c>
       <c r="E134" t="s">
+        <v>164</v>
+      </c>
+      <c r="G134" t="s">
         <v>176</v>
-      </c>
-      <c r="G134" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4752,13 +4752,13 @@
         <v>175</v>
       </c>
       <c r="D135" t="s">
-        <v>164</v>
+        <v>259</v>
       </c>
       <c r="E135" t="s">
+        <v>164</v>
+      </c>
+      <c r="G135" t="s">
         <v>176</v>
-      </c>
-      <c r="G135" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4772,13 +4772,13 @@
         <v>175</v>
       </c>
       <c r="D136" t="s">
-        <v>164</v>
+        <v>259</v>
       </c>
       <c r="E136" t="s">
+        <v>164</v>
+      </c>
+      <c r="G136" t="s">
         <v>176</v>
-      </c>
-      <c r="G136" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4792,13 +4792,13 @@
         <v>175</v>
       </c>
       <c r="D137" t="s">
-        <v>164</v>
+        <v>259</v>
       </c>
       <c r="E137" t="s">
+        <v>164</v>
+      </c>
+      <c r="G137" t="s">
         <v>176</v>
-      </c>
-      <c r="G137" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4812,13 +4812,13 @@
         <v>175</v>
       </c>
       <c r="D138" t="s">
-        <v>164</v>
+        <v>259</v>
       </c>
       <c r="E138" t="s">
+        <v>164</v>
+      </c>
+      <c r="G138" t="s">
         <v>176</v>
-      </c>
-      <c r="G138" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4832,13 +4832,13 @@
         <v>265</v>
       </c>
       <c r="D139" t="s">
+        <v>259</v>
+      </c>
+      <c r="E139" t="s">
         <v>224</v>
       </c>
-      <c r="E139" t="s">
+      <c r="G139" t="s">
         <v>266</v>
-      </c>
-      <c r="G139" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4852,13 +4852,13 @@
         <v>175</v>
       </c>
       <c r="D140" t="s">
-        <v>164</v>
+        <v>259</v>
       </c>
       <c r="E140" t="s">
+        <v>164</v>
+      </c>
+      <c r="G140" t="s">
         <v>176</v>
-      </c>
-      <c r="G140" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4872,10 +4872,10 @@
         <v>269</v>
       </c>
       <c r="D141" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F141" t="s">
         <v>271</v>
@@ -4895,10 +4895,10 @@
         <v>269</v>
       </c>
       <c r="D142" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F142" t="s">
         <v>271</v>
@@ -4918,16 +4918,16 @@
         <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E143" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="F143" t="s">
         <v>271</v>
       </c>
       <c r="G143" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4941,16 +4941,16 @@
         <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E144" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="F144" t="s">
         <v>271</v>
       </c>
       <c r="G144" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4964,16 +4964,16 @@
         <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E145" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="F145" t="s">
         <v>271</v>
       </c>
       <c r="G145" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4987,10 +4987,10 @@
         <v>269</v>
       </c>
       <c r="D146" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F146" t="s">
         <v>271</v>
@@ -5010,10 +5010,10 @@
         <v>269</v>
       </c>
       <c r="D147" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F147" t="s">
         <v>281</v>
@@ -5033,10 +5033,10 @@
         <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F148" t="s">
         <v>281</v>
@@ -5056,10 +5056,10 @@
         <v>269</v>
       </c>
       <c r="D149" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F149" t="s">
         <v>281</v>
@@ -5079,10 +5079,10 @@
         <v>269</v>
       </c>
       <c r="D150" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F150" t="s">
         <v>281</v>
@@ -5102,10 +5102,10 @@
         <v>269</v>
       </c>
       <c r="D151" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F151" t="s">
         <v>281</v>
@@ -5125,10 +5125,10 @@
         <v>269</v>
       </c>
       <c r="D152" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F152" t="s">
         <v>281</v>
@@ -5148,10 +5148,10 @@
         <v>269</v>
       </c>
       <c r="D153" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F153" t="s">
         <v>281</v>
@@ -5171,10 +5171,10 @@
         <v>269</v>
       </c>
       <c r="D154" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F154" t="s">
         <v>281</v>
@@ -5194,10 +5194,10 @@
         <v>269</v>
       </c>
       <c r="D155" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F155" t="s">
         <v>281</v>
@@ -5217,10 +5217,10 @@
         <v>269</v>
       </c>
       <c r="D156" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F156" t="s">
         <v>291</v>
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="D157" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E157" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F157" t="s">
         <v>291</v>
       </c>
       <c r="G157" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5263,10 +5263,10 @@
         <v>269</v>
       </c>
       <c r="D158" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F158" t="s">
         <v>291</v>
@@ -5286,10 +5286,10 @@
         <v>269</v>
       </c>
       <c r="D159" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F159" t="s">
         <v>291</v>
@@ -5309,10 +5309,10 @@
         <v>269</v>
       </c>
       <c r="D160" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F160" t="s">
         <v>291</v>
@@ -5332,10 +5332,10 @@
         <v>269</v>
       </c>
       <c r="D161" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F161" t="s">
         <v>291</v>
@@ -5355,10 +5355,10 @@
         <v>269</v>
       </c>
       <c r="D162" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F162" t="s">
         <v>299</v>
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
+        <v>269</v>
+      </c>
+      <c r="D163" t="s">
+        <v>270</v>
+      </c>
+      <c r="E163" t="s">
+        <v>164</v>
+      </c>
+      <c r="F163" t="s">
         <v>301</v>
       </c>
-      <c r="D163" t="s">
-        <v>164</v>
-      </c>
-      <c r="E163" t="s">
-        <v>270</v>
-      </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
         <v>302</v>
-      </c>
-      <c r="G163" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5401,10 +5401,10 @@
         <v>269</v>
       </c>
       <c r="D164" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F164" t="s">
         <v>304</v>
@@ -5424,10 +5424,10 @@
         <v>269</v>
       </c>
       <c r="D165" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F165" t="s">
         <v>304</v>
@@ -5447,10 +5447,10 @@
         <v>269</v>
       </c>
       <c r="D166" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F166" t="s">
         <v>304</v>
@@ -5470,10 +5470,10 @@
         <v>269</v>
       </c>
       <c r="D167" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F167" t="s">
         <v>304</v>
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="D168" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E168" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F168" t="s">
         <v>304</v>
       </c>
       <c r="G168" t="s">
-        <v>272</v>
+        <v>309</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="D169" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E169" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F169" t="s">
         <v>304</v>
       </c>
       <c r="G169" t="s">
-        <v>272</v>
+        <v>309</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5539,10 +5539,10 @@
         <v>269</v>
       </c>
       <c r="D170" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F170" t="s">
         <v>304</v>
@@ -5562,13 +5562,13 @@
         <v>163</v>
       </c>
       <c r="D171" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="E171" t="s">
+        <v>164</v>
+      </c>
+      <c r="G171" t="s">
         <v>165</v>
-      </c>
-      <c r="G171" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5582,13 +5582,13 @@
         <v>118</v>
       </c>
       <c r="D172" t="s">
-        <v>113</v>
+        <v>313</v>
       </c>
       <c r="E172" t="s">
+        <v>114</v>
+      </c>
+      <c r="G172" t="s">
         <v>119</v>
-      </c>
-      <c r="G172" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5602,13 +5602,13 @@
         <v>163</v>
       </c>
       <c r="D173" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="E173" t="s">
+        <v>164</v>
+      </c>
+      <c r="G173" t="s">
         <v>165</v>
-      </c>
-      <c r="G173" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5622,13 +5622,13 @@
         <v>163</v>
       </c>
       <c r="D174" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="E174" t="s">
+        <v>164</v>
+      </c>
+      <c r="G174" t="s">
         <v>165</v>
-      </c>
-      <c r="G174" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5642,13 +5642,13 @@
         <v>163</v>
       </c>
       <c r="D175" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="E175" t="s">
+        <v>164</v>
+      </c>
+      <c r="G175" t="s">
         <v>165</v>
-      </c>
-      <c r="G175" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5662,13 +5662,13 @@
         <v>163</v>
       </c>
       <c r="D176" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="E176" t="s">
+        <v>164</v>
+      </c>
+      <c r="G176" t="s">
         <v>165</v>
-      </c>
-      <c r="G176" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5682,13 +5682,13 @@
         <v>163</v>
       </c>
       <c r="D177" t="s">
-        <v>164</v>
+        <v>320</v>
       </c>
       <c r="E177" t="s">
+        <v>164</v>
+      </c>
+      <c r="G177" t="s">
         <v>165</v>
-      </c>
-      <c r="G177" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5702,13 +5702,13 @@
         <v>163</v>
       </c>
       <c r="D178" t="s">
-        <v>164</v>
+        <v>320</v>
       </c>
       <c r="E178" t="s">
+        <v>164</v>
+      </c>
+      <c r="G178" t="s">
         <v>165</v>
-      </c>
-      <c r="G178" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5722,13 +5722,13 @@
         <v>163</v>
       </c>
       <c r="D179" t="s">
-        <v>164</v>
+        <v>320</v>
       </c>
       <c r="E179" t="s">
+        <v>164</v>
+      </c>
+      <c r="G179" t="s">
         <v>165</v>
-      </c>
-      <c r="G179" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5742,13 +5742,13 @@
         <v>163</v>
       </c>
       <c r="D180" t="s">
-        <v>164</v>
+        <v>320</v>
       </c>
       <c r="E180" t="s">
+        <v>164</v>
+      </c>
+      <c r="G180" t="s">
         <v>165</v>
-      </c>
-      <c r="G180" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5762,10 +5762,10 @@
         <v>325</v>
       </c>
       <c r="D181" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F181" t="s">
         <v>327</v>
@@ -5785,10 +5785,10 @@
         <v>325</v>
       </c>
       <c r="D182" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F182" t="s">
         <v>327</v>
@@ -5808,10 +5808,10 @@
         <v>325</v>
       </c>
       <c r="D183" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F183" t="s">
         <v>327</v>
@@ -5831,10 +5831,10 @@
         <v>325</v>
       </c>
       <c r="D184" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F184" t="s">
         <v>327</v>
@@ -5854,10 +5854,10 @@
         <v>325</v>
       </c>
       <c r="D185" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F185" t="s">
         <v>327</v>
@@ -5877,10 +5877,10 @@
         <v>325</v>
       </c>
       <c r="D186" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F186" t="s">
         <v>327</v>
@@ -5900,10 +5900,10 @@
         <v>325</v>
       </c>
       <c r="D187" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F187" t="s">
         <v>327</v>
@@ -5923,10 +5923,10 @@
         <v>325</v>
       </c>
       <c r="D188" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F188" t="s">
         <v>327</v>
@@ -5946,10 +5946,10 @@
         <v>325</v>
       </c>
       <c r="D189" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F189" t="s">
         <v>327</v>
@@ -5969,10 +5969,10 @@
         <v>325</v>
       </c>
       <c r="D190" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F190" t="s">
         <v>327</v>
@@ -5992,10 +5992,10 @@
         <v>325</v>
       </c>
       <c r="D191" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F191" t="s">
         <v>327</v>
@@ -6015,10 +6015,10 @@
         <v>325</v>
       </c>
       <c r="D192" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F192" t="s">
         <v>327</v>
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>341</v>
+        <v>275</v>
       </c>
       <c r="D193" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E193" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="F193" t="s">
         <v>327</v>
       </c>
       <c r="G193" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6061,10 +6061,10 @@
         <v>325</v>
       </c>
       <c r="D194" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E194" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F194" t="s">
         <v>327</v>
@@ -6084,10 +6084,10 @@
         <v>325</v>
       </c>
       <c r="D195" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E195" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F195" t="s">
         <v>327</v>
@@ -6107,10 +6107,10 @@
         <v>325</v>
       </c>
       <c r="D196" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E196" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F196" t="s">
         <v>327</v>
@@ -6130,10 +6130,10 @@
         <v>325</v>
       </c>
       <c r="D197" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F197" t="s">
         <v>327</v>
@@ -6153,10 +6153,10 @@
         <v>325</v>
       </c>
       <c r="D198" t="s">
-        <v>164</v>
+        <v>326</v>
       </c>
       <c r="E198" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F198" t="s">
         <v>327</v>
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
+        <v>325</v>
+      </c>
+      <c r="D199" t="s">
+        <v>326</v>
+      </c>
+      <c r="E199" t="s">
+        <v>164</v>
+      </c>
+      <c r="F199" t="s">
         <v>348</v>
       </c>
-      <c r="D199" t="s">
-        <v>164</v>
-      </c>
-      <c r="E199" t="s">
-        <v>326</v>
-      </c>
-      <c r="F199" t="s">
+      <c r="G199" t="s">
         <v>349</v>
-      </c>
-      <c r="G199" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
+        <v>325</v>
+      </c>
+      <c r="D200" t="s">
+        <v>326</v>
+      </c>
+      <c r="E200" t="s">
+        <v>164</v>
+      </c>
+      <c r="F200" t="s">
         <v>348</v>
       </c>
-      <c r="D200" t="s">
-        <v>164</v>
-      </c>
-      <c r="E200" t="s">
-        <v>326</v>
-      </c>
-      <c r="F200" t="s">
+      <c r="G200" t="s">
         <v>349</v>
-      </c>
-      <c r="G200" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
+        <v>325</v>
+      </c>
+      <c r="D201" t="s">
+        <v>326</v>
+      </c>
+      <c r="E201" t="s">
+        <v>164</v>
+      </c>
+      <c r="F201" t="s">
         <v>348</v>
       </c>
-      <c r="D201" t="s">
-        <v>164</v>
-      </c>
-      <c r="E201" t="s">
-        <v>326</v>
-      </c>
-      <c r="F201" t="s">
+      <c r="G201" t="s">
         <v>349</v>
-      </c>
-      <c r="G201" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
+        <v>325</v>
+      </c>
+      <c r="D202" t="s">
+        <v>326</v>
+      </c>
+      <c r="E202" t="s">
+        <v>164</v>
+      </c>
+      <c r="F202" t="s">
         <v>348</v>
       </c>
-      <c r="D202" t="s">
-        <v>164</v>
-      </c>
-      <c r="E202" t="s">
-        <v>326</v>
-      </c>
-      <c r="F202" t="s">
+      <c r="G202" t="s">
         <v>349</v>
-      </c>
-      <c r="G202" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>275</v>
+      </c>
+      <c r="D203" t="s">
+        <v>326</v>
+      </c>
+      <c r="E203" t="s">
+        <v>164</v>
+      </c>
+      <c r="F203" t="s">
+        <v>348</v>
+      </c>
+      <c r="G203" t="s">
         <v>341</v>
-      </c>
-      <c r="D203" t="s">
-        <v>164</v>
-      </c>
-      <c r="E203" t="s">
-        <v>276</v>
-      </c>
-      <c r="F203" t="s">
-        <v>349</v>
-      </c>
-      <c r="G203" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
+        <v>325</v>
+      </c>
+      <c r="D204" t="s">
+        <v>326</v>
+      </c>
+      <c r="E204" t="s">
+        <v>164</v>
+      </c>
+      <c r="F204" t="s">
         <v>348</v>
       </c>
-      <c r="D204" t="s">
-        <v>164</v>
-      </c>
-      <c r="E204" t="s">
-        <v>326</v>
-      </c>
-      <c r="F204" t="s">
+      <c r="G204" t="s">
         <v>349</v>
-      </c>
-      <c r="G204" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
+        <v>325</v>
+      </c>
+      <c r="D205" t="s">
+        <v>326</v>
+      </c>
+      <c r="E205" t="s">
+        <v>164</v>
+      </c>
+      <c r="F205" t="s">
         <v>356</v>
       </c>
-      <c r="D205" t="s">
-        <v>164</v>
-      </c>
-      <c r="E205" t="s">
-        <v>326</v>
-      </c>
-      <c r="F205" t="s">
+      <c r="G205" t="s">
         <v>357</v>
-      </c>
-      <c r="G205" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
+        <v>325</v>
+      </c>
+      <c r="D206" t="s">
+        <v>326</v>
+      </c>
+      <c r="E206" t="s">
+        <v>164</v>
+      </c>
+      <c r="F206" t="s">
         <v>356</v>
       </c>
-      <c r="D206" t="s">
-        <v>164</v>
-      </c>
-      <c r="E206" t="s">
-        <v>326</v>
-      </c>
-      <c r="F206" t="s">
+      <c r="G206" t="s">
         <v>357</v>
-      </c>
-      <c r="G206" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
+        <v>325</v>
+      </c>
+      <c r="D207" t="s">
+        <v>326</v>
+      </c>
+      <c r="E207" t="s">
+        <v>164</v>
+      </c>
+      <c r="F207" t="s">
         <v>356</v>
       </c>
-      <c r="D207" t="s">
-        <v>164</v>
-      </c>
-      <c r="E207" t="s">
-        <v>326</v>
-      </c>
-      <c r="F207" t="s">
+      <c r="G207" t="s">
         <v>357</v>
-      </c>
-      <c r="G207" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>275</v>
+      </c>
+      <c r="D208" t="s">
+        <v>326</v>
+      </c>
+      <c r="E208" t="s">
+        <v>164</v>
+      </c>
+      <c r="F208" t="s">
+        <v>356</v>
+      </c>
+      <c r="G208" t="s">
         <v>341</v>
-      </c>
-      <c r="D208" t="s">
-        <v>164</v>
-      </c>
-      <c r="E208" t="s">
-        <v>276</v>
-      </c>
-      <c r="F208" t="s">
-        <v>357</v>
-      </c>
-      <c r="G208" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
+        <v>325</v>
+      </c>
+      <c r="D209" t="s">
+        <v>326</v>
+      </c>
+      <c r="E209" t="s">
+        <v>164</v>
+      </c>
+      <c r="F209" t="s">
         <v>356</v>
       </c>
-      <c r="D209" t="s">
-        <v>164</v>
-      </c>
-      <c r="E209" t="s">
-        <v>326</v>
-      </c>
-      <c r="F209" t="s">
+      <c r="G209" t="s">
         <v>357</v>
-      </c>
-      <c r="G209" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6429,10 +6429,10 @@
         <v>363</v>
       </c>
       <c r="D210" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E210" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F210" t="s">
         <v>365</v>
@@ -6452,10 +6452,10 @@
         <v>363</v>
       </c>
       <c r="D211" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E211" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F211" t="s">
         <v>365</v>
@@ -6475,10 +6475,10 @@
         <v>363</v>
       </c>
       <c r="D212" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E212" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F212" t="s">
         <v>365</v>
@@ -6498,10 +6498,10 @@
         <v>363</v>
       </c>
       <c r="D213" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E213" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F213" t="s">
         <v>365</v>
@@ -6521,10 +6521,10 @@
         <v>363</v>
       </c>
       <c r="D214" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E214" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F214" t="s">
         <v>365</v>
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D215" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E215" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="F215" t="s">
         <v>365</v>
       </c>
       <c r="G215" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6567,10 +6567,10 @@
         <v>363</v>
       </c>
       <c r="D216" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E216" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F216" t="s">
         <v>365</v>
@@ -6590,10 +6590,10 @@
         <v>363</v>
       </c>
       <c r="D217" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E217" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F217" t="s">
         <v>365</v>
@@ -6613,10 +6613,10 @@
         <v>363</v>
       </c>
       <c r="D218" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E218" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F218" t="s">
         <v>365</v>
@@ -6636,10 +6636,10 @@
         <v>363</v>
       </c>
       <c r="D219" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E219" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F219" t="s">
         <v>365</v>
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="D220" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E220" t="s">
-        <v>270</v>
+        <v>164</v>
       </c>
       <c r="F220" t="s">
         <v>365</v>
       </c>
       <c r="G220" t="s">
-        <v>366</v>
+        <v>309</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6682,10 +6682,10 @@
         <v>363</v>
       </c>
       <c r="D221" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E221" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F221" t="s">
         <v>365</v>
@@ -6705,10 +6705,10 @@
         <v>363</v>
       </c>
       <c r="D222" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E222" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F222" t="s">
         <v>365</v>
@@ -6728,10 +6728,10 @@
         <v>363</v>
       </c>
       <c r="D223" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E223" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F223" t="s">
         <v>365</v>
@@ -6751,10 +6751,10 @@
         <v>363</v>
       </c>
       <c r="D224" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E224" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F224" t="s">
         <v>365</v>
@@ -6774,10 +6774,10 @@
         <v>363</v>
       </c>
       <c r="D225" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E225" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F225" t="s">
         <v>365</v>
@@ -6797,16 +6797,16 @@
         <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E226" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="F226" t="s">
         <v>365</v>
       </c>
       <c r="G226" t="s">
-        <v>366</v>
+        <v>276</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6820,10 +6820,10 @@
         <v>363</v>
       </c>
       <c r="D227" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E227" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F227" t="s">
         <v>365</v>
@@ -6843,16 +6843,16 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="E228" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F228" t="s">
         <v>365</v>
       </c>
       <c r="G228" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
+        <v>363</v>
+      </c>
+      <c r="D229" t="s">
+        <v>364</v>
+      </c>
+      <c r="E229" t="s">
+        <v>164</v>
+      </c>
+      <c r="F229" t="s">
         <v>386</v>
       </c>
-      <c r="D229" t="s">
-        <v>164</v>
-      </c>
-      <c r="E229" t="s">
-        <v>364</v>
-      </c>
-      <c r="F229" t="s">
+      <c r="G229" t="s">
         <v>387</v>
-      </c>
-      <c r="G229" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
+        <v>363</v>
+      </c>
+      <c r="D230" t="s">
+        <v>364</v>
+      </c>
+      <c r="E230" t="s">
+        <v>164</v>
+      </c>
+      <c r="F230" t="s">
         <v>386</v>
       </c>
-      <c r="D230" t="s">
-        <v>164</v>
-      </c>
-      <c r="E230" t="s">
-        <v>364</v>
-      </c>
-      <c r="F230" t="s">
+      <c r="G230" t="s">
         <v>387</v>
-      </c>
-      <c r="G230" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
+        <v>269</v>
+      </c>
+      <c r="D231" t="s">
+        <v>364</v>
+      </c>
+      <c r="E231" t="s">
+        <v>164</v>
+      </c>
+      <c r="F231" t="s">
+        <v>386</v>
+      </c>
+      <c r="G231" t="s">
         <v>293</v>
-      </c>
-      <c r="D231" t="s">
-        <v>164</v>
-      </c>
-      <c r="E231" t="s">
-        <v>270</v>
-      </c>
-      <c r="F231" t="s">
-        <v>387</v>
-      </c>
-      <c r="G231" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
+        <v>269</v>
+      </c>
+      <c r="D232" t="s">
+        <v>364</v>
+      </c>
+      <c r="E232" t="s">
+        <v>164</v>
+      </c>
+      <c r="F232" t="s">
+        <v>386</v>
+      </c>
+      <c r="G232" t="s">
         <v>309</v>
-      </c>
-      <c r="D232" t="s">
-        <v>164</v>
-      </c>
-      <c r="E232" t="s">
-        <v>270</v>
-      </c>
-      <c r="F232" t="s">
-        <v>387</v>
-      </c>
-      <c r="G232" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
+        <v>363</v>
+      </c>
+      <c r="D233" t="s">
+        <v>364</v>
+      </c>
+      <c r="E233" t="s">
+        <v>164</v>
+      </c>
+      <c r="F233" t="s">
         <v>386</v>
       </c>
-      <c r="D233" t="s">
-        <v>164</v>
-      </c>
-      <c r="E233" t="s">
-        <v>364</v>
-      </c>
-      <c r="F233" t="s">
+      <c r="G233" t="s">
         <v>387</v>
-      </c>
-      <c r="G233" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
+        <v>363</v>
+      </c>
+      <c r="D234" t="s">
+        <v>364</v>
+      </c>
+      <c r="E234" t="s">
+        <v>164</v>
+      </c>
+      <c r="F234" t="s">
         <v>386</v>
       </c>
-      <c r="D234" t="s">
-        <v>164</v>
-      </c>
-      <c r="E234" t="s">
-        <v>364</v>
-      </c>
-      <c r="F234" t="s">
+      <c r="G234" t="s">
         <v>387</v>
-      </c>
-      <c r="G234" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
+        <v>363</v>
+      </c>
+      <c r="D235" t="s">
+        <v>364</v>
+      </c>
+      <c r="E235" t="s">
+        <v>164</v>
+      </c>
+      <c r="F235" t="s">
         <v>386</v>
       </c>
-      <c r="D235" t="s">
-        <v>164</v>
-      </c>
-      <c r="E235" t="s">
-        <v>364</v>
-      </c>
-      <c r="F235" t="s">
+      <c r="G235" t="s">
         <v>387</v>
-      </c>
-      <c r="G235" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
+        <v>363</v>
+      </c>
+      <c r="D236" t="s">
+        <v>364</v>
+      </c>
+      <c r="E236" t="s">
+        <v>164</v>
+      </c>
+      <c r="F236" t="s">
         <v>386</v>
       </c>
-      <c r="D236" t="s">
-        <v>164</v>
-      </c>
-      <c r="E236" t="s">
-        <v>364</v>
-      </c>
-      <c r="F236" t="s">
+      <c r="G236" t="s">
         <v>387</v>
-      </c>
-      <c r="G236" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
+        <v>363</v>
+      </c>
+      <c r="D237" t="s">
+        <v>364</v>
+      </c>
+      <c r="E237" t="s">
+        <v>164</v>
+      </c>
+      <c r="F237" t="s">
         <v>386</v>
       </c>
-      <c r="D237" t="s">
-        <v>164</v>
-      </c>
-      <c r="E237" t="s">
-        <v>364</v>
-      </c>
-      <c r="F237" t="s">
+      <c r="G237" t="s">
         <v>387</v>
-      </c>
-      <c r="G237" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
+        <v>363</v>
+      </c>
+      <c r="D238" t="s">
+        <v>364</v>
+      </c>
+      <c r="E238" t="s">
+        <v>164</v>
+      </c>
+      <c r="F238" t="s">
         <v>386</v>
       </c>
-      <c r="D238" t="s">
-        <v>164</v>
-      </c>
-      <c r="E238" t="s">
-        <v>364</v>
-      </c>
-      <c r="F238" t="s">
+      <c r="G238" t="s">
         <v>387</v>
-      </c>
-      <c r="G238" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
+        <v>363</v>
+      </c>
+      <c r="D239" t="s">
+        <v>364</v>
+      </c>
+      <c r="E239" t="s">
+        <v>164</v>
+      </c>
+      <c r="F239" t="s">
         <v>398</v>
       </c>
-      <c r="D239" t="s">
-        <v>164</v>
-      </c>
-      <c r="E239" t="s">
-        <v>364</v>
-      </c>
-      <c r="F239" t="s">
+      <c r="G239" t="s">
         <v>399</v>
-      </c>
-      <c r="G239" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7119,16 +7119,16 @@
         <v>163</v>
       </c>
       <c r="D240" t="s">
-        <v>164</v>
+        <v>401</v>
       </c>
       <c r="E240" t="s">
+        <v>164</v>
+      </c>
+      <c r="F240" t="s">
+        <v>402</v>
+      </c>
+      <c r="G240" t="s">
         <v>165</v>
-      </c>
-      <c r="F240" t="s">
-        <v>401</v>
-      </c>
-      <c r="G240" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7142,16 +7142,16 @@
         <v>163</v>
       </c>
       <c r="D241" t="s">
-        <v>164</v>
+        <v>401</v>
       </c>
       <c r="E241" t="s">
+        <v>164</v>
+      </c>
+      <c r="F241" t="s">
+        <v>402</v>
+      </c>
+      <c r="G241" t="s">
         <v>165</v>
-      </c>
-      <c r="F241" t="s">
-        <v>401</v>
-      </c>
-      <c r="G241" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7165,16 +7165,16 @@
         <v>163</v>
       </c>
       <c r="D242" t="s">
-        <v>164</v>
+        <v>401</v>
       </c>
       <c r="E242" t="s">
+        <v>164</v>
+      </c>
+      <c r="F242" t="s">
+        <v>402</v>
+      </c>
+      <c r="G242" t="s">
         <v>165</v>
-      </c>
-      <c r="F242" t="s">
-        <v>401</v>
-      </c>
-      <c r="G242" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7188,16 +7188,16 @@
         <v>163</v>
       </c>
       <c r="D243" t="s">
-        <v>164</v>
+        <v>401</v>
       </c>
       <c r="E243" t="s">
+        <v>164</v>
+      </c>
+      <c r="F243" t="s">
+        <v>402</v>
+      </c>
+      <c r="G243" t="s">
         <v>165</v>
-      </c>
-      <c r="F243" t="s">
-        <v>401</v>
-      </c>
-      <c r="G243" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7211,16 +7211,16 @@
         <v>163</v>
       </c>
       <c r="D244" t="s">
-        <v>164</v>
+        <v>401</v>
       </c>
       <c r="E244" t="s">
+        <v>164</v>
+      </c>
+      <c r="F244" t="s">
+        <v>402</v>
+      </c>
+      <c r="G244" t="s">
         <v>165</v>
-      </c>
-      <c r="F244" t="s">
-        <v>401</v>
-      </c>
-      <c r="G244" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7234,16 +7234,16 @@
         <v>163</v>
       </c>
       <c r="D245" t="s">
-        <v>164</v>
+        <v>401</v>
       </c>
       <c r="E245" t="s">
+        <v>164</v>
+      </c>
+      <c r="F245" t="s">
+        <v>402</v>
+      </c>
+      <c r="G245" t="s">
         <v>165</v>
-      </c>
-      <c r="F245" t="s">
-        <v>401</v>
-      </c>
-      <c r="G245" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>255</v>
+      </c>
+      <c r="D246" t="s">
+        <v>401</v>
+      </c>
+      <c r="E246" t="s">
+        <v>164</v>
+      </c>
+      <c r="F246" t="s">
         <v>409</v>
       </c>
-      <c r="D246" t="s">
-        <v>164</v>
-      </c>
-      <c r="E246" t="s">
-        <v>256</v>
-      </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
         <v>410</v>
-      </c>
-      <c r="G246" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7280,13 +7280,13 @@
         <v>95</v>
       </c>
       <c r="D247" t="s">
+        <v>412</v>
+      </c>
+      <c r="E247" t="s">
         <v>96</v>
       </c>
-      <c r="E247" t="s">
+      <c r="G247" t="s">
         <v>97</v>
-      </c>
-      <c r="G247" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7300,13 +7300,13 @@
         <v>95</v>
       </c>
       <c r="D248" t="s">
+        <v>412</v>
+      </c>
+      <c r="E248" t="s">
         <v>96</v>
       </c>
-      <c r="E248" t="s">
+      <c r="G248" t="s">
         <v>97</v>
-      </c>
-      <c r="G248" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7320,13 +7320,13 @@
         <v>415</v>
       </c>
       <c r="D249" t="s">
+        <v>412</v>
+      </c>
+      <c r="E249" t="s">
         <v>96</v>
       </c>
-      <c r="E249" t="s">
+      <c r="G249" t="s">
         <v>416</v>
-      </c>
-      <c r="G249" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7340,13 +7340,13 @@
         <v>95</v>
       </c>
       <c r="D250" t="s">
+        <v>412</v>
+      </c>
+      <c r="E250" t="s">
         <v>96</v>
       </c>
-      <c r="E250" t="s">
+      <c r="G250" t="s">
         <v>97</v>
-      </c>
-      <c r="G250" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7360,13 +7360,13 @@
         <v>95</v>
       </c>
       <c r="D251" t="s">
+        <v>412</v>
+      </c>
+      <c r="E251" t="s">
         <v>96</v>
       </c>
-      <c r="E251" t="s">
+      <c r="G251" t="s">
         <v>97</v>
-      </c>
-      <c r="G251" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7380,13 +7380,13 @@
         <v>95</v>
       </c>
       <c r="D252" t="s">
+        <v>412</v>
+      </c>
+      <c r="E252" t="s">
         <v>96</v>
       </c>
-      <c r="E252" t="s">
+      <c r="G252" t="s">
         <v>97</v>
-      </c>
-      <c r="G252" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7400,10 +7400,10 @@
         <v>421</v>
       </c>
       <c r="D253" t="s">
-        <v>164</v>
+        <v>422</v>
       </c>
       <c r="E253" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="G253" t="s">
         <v>423</v>
@@ -7420,13 +7420,13 @@
         <v>219</v>
       </c>
       <c r="D254" t="s">
-        <v>91</v>
+        <v>422</v>
       </c>
       <c r="E254" t="s">
+        <v>92</v>
+      </c>
+      <c r="G254" t="s">
         <v>220</v>
-      </c>
-      <c r="G254" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7440,13 +7440,13 @@
         <v>426</v>
       </c>
       <c r="D255" t="s">
-        <v>91</v>
+        <v>422</v>
       </c>
       <c r="E255" t="s">
+        <v>92</v>
+      </c>
+      <c r="G255" t="s">
         <v>427</v>
-      </c>
-      <c r="G255" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7460,13 +7460,13 @@
         <v>426</v>
       </c>
       <c r="D256" t="s">
-        <v>91</v>
+        <v>422</v>
       </c>
       <c r="E256" t="s">
+        <v>92</v>
+      </c>
+      <c r="G256" t="s">
         <v>427</v>
-      </c>
-      <c r="G256" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7480,13 +7480,13 @@
         <v>426</v>
       </c>
       <c r="D257" t="s">
-        <v>91</v>
+        <v>422</v>
       </c>
       <c r="E257" t="s">
+        <v>92</v>
+      </c>
+      <c r="G257" t="s">
         <v>427</v>
-      </c>
-      <c r="G257" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7500,13 +7500,13 @@
         <v>325</v>
       </c>
       <c r="D258" t="s">
-        <v>164</v>
+        <v>422</v>
       </c>
       <c r="E258" t="s">
-        <v>326</v>
+        <v>164</v>
       </c>
       <c r="G258" t="s">
-        <v>423</v>
+        <v>328</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7520,13 +7520,13 @@
         <v>426</v>
       </c>
       <c r="D259" t="s">
-        <v>91</v>
+        <v>422</v>
       </c>
       <c r="E259" t="s">
+        <v>92</v>
+      </c>
+      <c r="G259" t="s">
         <v>427</v>
-      </c>
-      <c r="G259" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7540,13 +7540,13 @@
         <v>163</v>
       </c>
       <c r="D260" t="s">
-        <v>164</v>
+        <v>422</v>
       </c>
       <c r="E260" t="s">
+        <v>164</v>
+      </c>
+      <c r="G260" t="s">
         <v>165</v>
-      </c>
-      <c r="G260" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7560,13 +7560,13 @@
         <v>434</v>
       </c>
       <c r="D261" t="s">
+        <v>422</v>
+      </c>
+      <c r="E261" t="s">
         <v>196</v>
       </c>
-      <c r="E261" t="s">
+      <c r="G261" t="s">
         <v>435</v>
-      </c>
-      <c r="G261" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7580,13 +7580,13 @@
         <v>163</v>
       </c>
       <c r="D262" t="s">
-        <v>164</v>
+        <v>422</v>
       </c>
       <c r="E262" t="s">
+        <v>164</v>
+      </c>
+      <c r="G262" t="s">
         <v>165</v>
-      </c>
-      <c r="G262" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7600,13 +7600,13 @@
         <v>438</v>
       </c>
       <c r="D263" t="s">
+        <v>422</v>
+      </c>
+      <c r="E263" t="s">
         <v>183</v>
       </c>
-      <c r="E263" t="s">
+      <c r="G263" t="s">
         <v>439</v>
-      </c>
-      <c r="G263" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7620,13 +7620,13 @@
         <v>31</v>
       </c>
       <c r="D264" t="s">
+        <v>422</v>
+      </c>
+      <c r="E264" t="s">
         <v>32</v>
       </c>
-      <c r="E264" t="s">
+      <c r="G264" t="s">
         <v>33</v>
-      </c>
-      <c r="G264" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7640,13 +7640,13 @@
         <v>9</v>
       </c>
       <c r="D265" t="s">
-        <v>10</v>
+        <v>422</v>
       </c>
       <c r="E265" t="s">
         <v>11</v>
       </c>
       <c r="G265" t="s">
-        <v>423</v>
+        <v>13</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7660,13 +7660,13 @@
         <v>443</v>
       </c>
       <c r="D266" t="s">
-        <v>113</v>
+        <v>422</v>
       </c>
       <c r="E266" t="s">
+        <v>114</v>
+      </c>
+      <c r="G266" t="s">
         <v>444</v>
-      </c>
-      <c r="G266" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7680,13 +7680,13 @@
         <v>118</v>
       </c>
       <c r="D267" t="s">
-        <v>113</v>
+        <v>446</v>
       </c>
       <c r="E267" t="s">
+        <v>114</v>
+      </c>
+      <c r="G267" t="s">
         <v>119</v>
-      </c>
-      <c r="G267" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7700,13 +7700,13 @@
         <v>202</v>
       </c>
       <c r="D268" t="s">
+        <v>448</v>
+      </c>
+      <c r="E268" t="s">
         <v>183</v>
       </c>
-      <c r="E268" t="s">
-        <v>203</v>
-      </c>
       <c r="G268" t="s">
-        <v>448</v>
+        <v>204</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7720,13 +7720,13 @@
         <v>118</v>
       </c>
       <c r="D269" t="s">
-        <v>113</v>
+        <v>450</v>
       </c>
       <c r="E269" t="s">
+        <v>114</v>
+      </c>
+      <c r="G269" t="s">
         <v>119</v>
-      </c>
-      <c r="G269" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7740,13 +7740,13 @@
         <v>118</v>
       </c>
       <c r="D270" t="s">
-        <v>113</v>
+        <v>450</v>
       </c>
       <c r="E270" t="s">
+        <v>114</v>
+      </c>
+      <c r="G270" t="s">
         <v>119</v>
-      </c>
-      <c r="G270" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7760,10 +7760,10 @@
         <v>453</v>
       </c>
       <c r="D271" t="s">
-        <v>113</v>
+        <v>454</v>
       </c>
       <c r="E271" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="G271" t="s">
         <v>455</v>
@@ -7780,10 +7780,10 @@
         <v>453</v>
       </c>
       <c r="D272" t="s">
-        <v>113</v>
+        <v>454</v>
       </c>
       <c r="E272" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="G272" t="s">
         <v>455</v>
@@ -7800,10 +7800,10 @@
         <v>453</v>
       </c>
       <c r="D273" t="s">
-        <v>113</v>
+        <v>454</v>
       </c>
       <c r="E273" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="G273" t="s">
         <v>455</v>
@@ -7820,10 +7820,10 @@
         <v>453</v>
       </c>
       <c r="D274" t="s">
-        <v>113</v>
+        <v>454</v>
       </c>
       <c r="E274" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="G274" t="s">
         <v>455</v>
@@ -7840,10 +7840,10 @@
         <v>453</v>
       </c>
       <c r="D275" t="s">
-        <v>113</v>
+        <v>454</v>
       </c>
       <c r="E275" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="G275" t="s">
         <v>455</v>
@@ -7860,10 +7860,10 @@
         <v>453</v>
       </c>
       <c r="D276" t="s">
-        <v>113</v>
+        <v>454</v>
       </c>
       <c r="E276" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="G276" t="s">
         <v>455</v>
@@ -7880,10 +7880,10 @@
         <v>453</v>
       </c>
       <c r="D277" t="s">
-        <v>113</v>
+        <v>454</v>
       </c>
       <c r="E277" t="s">
-        <v>454</v>
+        <v>114</v>
       </c>
       <c r="G277" t="s">
         <v>455</v>
@@ -7900,13 +7900,13 @@
         <v>202</v>
       </c>
       <c r="D278" t="s">
+        <v>463</v>
+      </c>
+      <c r="E278" t="s">
         <v>183</v>
       </c>
-      <c r="E278" t="s">
-        <v>203</v>
-      </c>
       <c r="G278" t="s">
-        <v>463</v>
+        <v>204</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7920,13 +7920,13 @@
         <v>51</v>
       </c>
       <c r="D279" t="s">
+        <v>463</v>
+      </c>
+      <c r="E279" t="s">
         <v>32</v>
       </c>
-      <c r="E279" t="s">
-        <v>52</v>
-      </c>
       <c r="G279" t="s">
-        <v>463</v>
+        <v>54</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7940,13 +7940,13 @@
         <v>9</v>
       </c>
       <c r="D280" t="s">
-        <v>10</v>
+        <v>463</v>
       </c>
       <c r="E280" t="s">
         <v>11</v>
       </c>
       <c r="G280" t="s">
-        <v>463</v>
+        <v>13</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7960,13 +7960,13 @@
         <v>170</v>
       </c>
       <c r="D281" t="s">
-        <v>113</v>
+        <v>463</v>
       </c>
       <c r="E281" t="s">
+        <v>114</v>
+      </c>
+      <c r="G281" t="s">
         <v>171</v>
-      </c>
-      <c r="G281" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7980,13 +7980,13 @@
         <v>124</v>
       </c>
       <c r="D282" t="s">
+        <v>463</v>
+      </c>
+      <c r="E282" t="s">
         <v>125</v>
       </c>
-      <c r="E282" t="s">
+      <c r="G282" t="s">
         <v>126</v>
-      </c>
-      <c r="G282" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7997,16 +7997,16 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="D283" t="s">
-        <v>164</v>
+        <v>469</v>
       </c>
       <c r="E283" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="G283" t="s">
-        <v>469</v>
+        <v>399</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8020,13 +8020,13 @@
         <v>124</v>
       </c>
       <c r="D284" t="s">
+        <v>471</v>
+      </c>
+      <c r="E284" t="s">
         <v>125</v>
       </c>
-      <c r="E284" t="s">
+      <c r="G284" t="s">
         <v>126</v>
-      </c>
-      <c r="G284" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8040,13 +8040,13 @@
         <v>170</v>
       </c>
       <c r="D285" t="s">
-        <v>113</v>
+        <v>473</v>
       </c>
       <c r="E285" t="s">
+        <v>114</v>
+      </c>
+      <c r="G285" t="s">
         <v>171</v>
-      </c>
-      <c r="G285" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8060,13 +8060,13 @@
         <v>438</v>
       </c>
       <c r="D286" t="s">
+        <v>475</v>
+      </c>
+      <c r="E286" t="s">
         <v>183</v>
       </c>
-      <c r="E286" t="s">
+      <c r="G286" t="s">
         <v>439</v>
-      </c>
-      <c r="G286" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8080,13 +8080,13 @@
         <v>438</v>
       </c>
       <c r="D287" t="s">
+        <v>475</v>
+      </c>
+      <c r="E287" t="s">
         <v>183</v>
       </c>
-      <c r="E287" t="s">
+      <c r="G287" t="s">
         <v>439</v>
-      </c>
-      <c r="G287" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8100,13 +8100,13 @@
         <v>41</v>
       </c>
       <c r="D288" t="s">
-        <v>10</v>
+        <v>475</v>
       </c>
       <c r="E288" t="s">
+        <v>11</v>
+      </c>
+      <c r="G288" t="s">
         <v>42</v>
-      </c>
-      <c r="G288" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8120,13 +8120,13 @@
         <v>31</v>
       </c>
       <c r="D289" t="s">
+        <v>475</v>
+      </c>
+      <c r="E289" t="s">
         <v>32</v>
       </c>
-      <c r="E289" t="s">
+      <c r="G289" t="s">
         <v>33</v>
-      </c>
-      <c r="G289" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8140,13 +8140,13 @@
         <v>31</v>
       </c>
       <c r="D290" t="s">
+        <v>475</v>
+      </c>
+      <c r="E290" t="s">
         <v>32</v>
       </c>
-      <c r="E290" t="s">
+      <c r="G290" t="s">
         <v>33</v>
-      </c>
-      <c r="G290" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8160,13 +8160,13 @@
         <v>170</v>
       </c>
       <c r="D291" t="s">
-        <v>113</v>
+        <v>475</v>
       </c>
       <c r="E291" t="s">
+        <v>114</v>
+      </c>
+      <c r="G291" t="s">
         <v>171</v>
-      </c>
-      <c r="G291" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8180,13 +8180,13 @@
         <v>170</v>
       </c>
       <c r="D292" t="s">
-        <v>113</v>
+        <v>475</v>
       </c>
       <c r="E292" t="s">
+        <v>114</v>
+      </c>
+      <c r="G292" t="s">
         <v>171</v>
-      </c>
-      <c r="G292" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8200,13 +8200,13 @@
         <v>170</v>
       </c>
       <c r="D293" t="s">
-        <v>113</v>
+        <v>475</v>
       </c>
       <c r="E293" t="s">
+        <v>114</v>
+      </c>
+      <c r="G293" t="s">
         <v>171</v>
-      </c>
-      <c r="G293" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8220,13 +8220,13 @@
         <v>170</v>
       </c>
       <c r="D294" t="s">
-        <v>113</v>
+        <v>475</v>
       </c>
       <c r="E294" t="s">
+        <v>114</v>
+      </c>
+      <c r="G294" t="s">
         <v>171</v>
-      </c>
-      <c r="G294" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8240,13 +8240,13 @@
         <v>170</v>
       </c>
       <c r="D295" t="s">
-        <v>113</v>
+        <v>485</v>
       </c>
       <c r="E295" t="s">
+        <v>114</v>
+      </c>
+      <c r="G295" t="s">
         <v>171</v>
-      </c>
-      <c r="G295" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8260,13 +8260,13 @@
         <v>170</v>
       </c>
       <c r="D296" t="s">
-        <v>113</v>
+        <v>485</v>
       </c>
       <c r="E296" t="s">
+        <v>114</v>
+      </c>
+      <c r="G296" t="s">
         <v>171</v>
-      </c>
-      <c r="G296" t="s">
-        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/1/xlsx/fr/SectorCOFOG.xlsx
@@ -22,18 +22,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
@@ -43,18 +43,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>11220</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>11420</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
@@ -169,15 +169,15 @@
     <t>12110</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
@@ -286,12 +286,12 @@
     <t>14010</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
@@ -352,18 +352,18 @@
     <t>15110</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
@@ -622,12 +622,12 @@
     <t>16010</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
@@ -823,15 +823,15 @@
     <t>23110</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
@@ -991,15 +991,15 @@
     <t>31110</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
@@ -1105,15 +1105,15 @@
     <t>32110</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
@@ -1219,12 +1219,12 @@
     <t>33110</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1279,12 +1279,12 @@
     <t>43010</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
@@ -1375,10 +1375,10 @@
     <t>60010</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
   </si>
   <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
@@ -1863,13 +1863,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1909,13 +1909,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -1938,10 +1938,10 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1955,7 +1955,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1964,7 +1964,7 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -1984,10 +1984,10 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -2007,10 +2007,10 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -2030,10 +2030,10 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
@@ -2047,16 +2047,16 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
       </c>
       <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
         <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>23</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2070,16 +2070,16 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>36</v>
@@ -2093,16 +2093,16 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2116,16 +2116,16 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
         <v>42</v>
@@ -2145,10 +2145,10 @@
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>46</v>
@@ -2162,16 +2162,16 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s">
         <v>49</v>
@@ -2191,10 +2191,10 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" t="s">
         <v>32</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2214,10 +2214,10 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" t="s">
         <v>32</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2231,16 +2231,16 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
         <v>52</v>
       </c>
       <c r="E19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" t="s">
         <v>32</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
       </c>
       <c r="G19" t="s">
         <v>58</v>
@@ -2254,16 +2254,16 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
         <v>52</v>
       </c>
       <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" t="s">
         <v>32</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
       </c>
       <c r="G20" t="s">
         <v>61</v>
@@ -2283,10 +2283,10 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" t="s">
         <v>32</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2300,16 +2300,16 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
         <v>52</v>
       </c>
       <c r="E22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" t="s">
         <v>32</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
       </c>
       <c r="G22" t="s">
         <v>33</v>
@@ -2323,16 +2323,16 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
         <v>52</v>
       </c>
       <c r="E23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" t="s">
         <v>32</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
       </c>
       <c r="G23" t="s">
         <v>67</v>
@@ -2346,16 +2346,16 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
         <v>52</v>
       </c>
       <c r="E24" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" t="s">
         <v>32</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
       </c>
       <c r="G24" t="s">
         <v>33</v>
@@ -2369,16 +2369,16 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
         <v>52</v>
       </c>
       <c r="E25" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" t="s">
         <v>32</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
       </c>
       <c r="G25" t="s">
         <v>33</v>
@@ -2392,16 +2392,16 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
         <v>52</v>
       </c>
       <c r="E26" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" t="s">
         <v>32</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
       </c>
       <c r="G26" t="s">
         <v>33</v>
@@ -2415,16 +2415,16 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
         <v>52</v>
       </c>
       <c r="E27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" t="s">
         <v>32</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
       </c>
       <c r="G27" t="s">
         <v>33</v>
@@ -2438,16 +2438,16 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
         <v>52</v>
       </c>
       <c r="E28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" t="s">
         <v>32</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
       </c>
       <c r="G28" t="s">
         <v>33</v>
@@ -2461,16 +2461,16 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
         <v>52</v>
       </c>
       <c r="E29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" t="s">
         <v>32</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
       </c>
       <c r="G29" t="s">
         <v>33</v>
@@ -2484,16 +2484,16 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
         <v>52</v>
       </c>
       <c r="E30" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" t="s">
         <v>32</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
       </c>
       <c r="G30" t="s">
         <v>54</v>
@@ -2507,16 +2507,16 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
         <v>52</v>
       </c>
       <c r="E31" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" t="s">
         <v>32</v>
-      </c>
-      <c r="F31" t="s">
-        <v>76</v>
       </c>
       <c r="G31" t="s">
         <v>33</v>
@@ -2530,16 +2530,16 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
         <v>52</v>
       </c>
       <c r="E32" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32" t="s">
         <v>32</v>
-      </c>
-      <c r="F32" t="s">
-        <v>76</v>
       </c>
       <c r="G32" t="s">
         <v>33</v>
@@ -2553,16 +2553,16 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
         <v>52</v>
       </c>
       <c r="E33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" t="s">
         <v>32</v>
-      </c>
-      <c r="F33" t="s">
-        <v>76</v>
       </c>
       <c r="G33" t="s">
         <v>33</v>
@@ -2576,16 +2576,16 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
         <v>52</v>
       </c>
       <c r="E34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" t="s">
         <v>32</v>
-      </c>
-      <c r="F34" t="s">
-        <v>76</v>
       </c>
       <c r="G34" t="s">
         <v>33</v>
@@ -2599,16 +2599,16 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
         <v>52</v>
       </c>
       <c r="E35" t="s">
+        <v>31</v>
+      </c>
+      <c r="F35" t="s">
         <v>32</v>
-      </c>
-      <c r="F35" t="s">
-        <v>76</v>
       </c>
       <c r="G35" t="s">
         <v>33</v>
@@ -2622,16 +2622,16 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
         <v>52</v>
       </c>
       <c r="E36" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36" t="s">
         <v>32</v>
-      </c>
-      <c r="F36" t="s">
-        <v>76</v>
       </c>
       <c r="G36" t="s">
         <v>58</v>
@@ -2644,13 +2644,13 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
-      <c r="C37" t="s">
-        <v>31</v>
-      </c>
       <c r="D37" t="s">
         <v>83</v>
       </c>
       <c r="E37" t="s">
+        <v>31</v>
+      </c>
+      <c r="F37" t="s">
         <v>32</v>
       </c>
       <c r="G37" t="s">
@@ -2664,13 +2664,13 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
-      <c r="C38" t="s">
-        <v>31</v>
-      </c>
       <c r="D38" t="s">
         <v>83</v>
       </c>
       <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" t="s">
         <v>32</v>
       </c>
       <c r="G38" t="s">
@@ -2684,13 +2684,13 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
-      <c r="C39" t="s">
-        <v>31</v>
-      </c>
       <c r="D39" t="s">
         <v>83</v>
       </c>
       <c r="E39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" t="s">
         <v>32</v>
       </c>
       <c r="G39" t="s">
@@ -2704,13 +2704,13 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
-      <c r="C40" t="s">
-        <v>31</v>
-      </c>
       <c r="D40" t="s">
         <v>83</v>
       </c>
       <c r="E40" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" t="s">
         <v>32</v>
       </c>
       <c r="G40" t="s">
@@ -2724,13 +2724,13 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="C41" t="s">
-        <v>51</v>
-      </c>
       <c r="D41" t="s">
         <v>83</v>
       </c>
       <c r="E41" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" t="s">
         <v>32</v>
       </c>
       <c r="G41" t="s">
@@ -2744,13 +2744,13 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
-      <c r="C42" t="s">
-        <v>57</v>
-      </c>
       <c r="D42" t="s">
         <v>83</v>
       </c>
       <c r="E42" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" t="s">
         <v>32</v>
       </c>
       <c r="G42" t="s">
@@ -2764,13 +2764,13 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>90</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>91</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>92</v>
       </c>
       <c r="G43" t="s">
@@ -2784,13 +2784,13 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" t="s">
         <v>95</v>
       </c>
-      <c r="D44" t="s">
-        <v>91</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>96</v>
       </c>
       <c r="G44" t="s">
@@ -2804,13 +2804,13 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>90</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>91</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>92</v>
       </c>
       <c r="G45" t="s">
@@ -2824,13 +2824,13 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>90</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>91</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>92</v>
       </c>
       <c r="G46" t="s">
@@ -2844,13 +2844,13 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" t="s">
         <v>101</v>
       </c>
-      <c r="D47" t="s">
-        <v>91</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>96</v>
       </c>
       <c r="G47" t="s">
@@ -2864,13 +2864,13 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>90</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>91</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>92</v>
       </c>
       <c r="G48" t="s">
@@ -2884,13 +2884,13 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>90</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>91</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>92</v>
       </c>
       <c r="G49" t="s">
@@ -2904,13 +2904,13 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" t="s">
         <v>101</v>
       </c>
-      <c r="D50" t="s">
-        <v>91</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>96</v>
       </c>
       <c r="G50" t="s">
@@ -2924,13 +2924,13 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>90</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>91</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>92</v>
       </c>
       <c r="G51" t="s">
@@ -2944,13 +2944,13 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" t="s">
         <v>108</v>
       </c>
-      <c r="D52" t="s">
-        <v>91</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>96</v>
       </c>
       <c r="G52" t="s">
@@ -2964,14 +2964,14 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C53" t="s">
-        <v>9</v>
-      </c>
       <c r="D53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
+      </c>
+      <c r="F53" t="s">
+        <v>12</v>
       </c>
       <c r="G53" t="s">
         <v>13</v>
@@ -3008,13 +3008,13 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D55" t="s">
         <v>113</v>
       </c>
       <c r="E55" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F55" t="s">
         <v>115</v>
@@ -3031,13 +3031,13 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D56" t="s">
         <v>113</v>
       </c>
       <c r="E56" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F56" t="s">
         <v>115</v>
@@ -3054,16 +3054,16 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D57" t="s">
         <v>113</v>
       </c>
       <c r="E57" t="s">
+        <v>124</v>
+      </c>
+      <c r="F57" t="s">
         <v>125</v>
-      </c>
-      <c r="F57" t="s">
-        <v>115</v>
       </c>
       <c r="G57" t="s">
         <v>126</v>
@@ -3077,13 +3077,13 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D58" t="s">
         <v>113</v>
       </c>
       <c r="E58" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F58" t="s">
         <v>115</v>
@@ -3100,13 +3100,13 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D59" t="s">
         <v>113</v>
       </c>
       <c r="E59" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F59" t="s">
         <v>115</v>
@@ -3123,13 +3123,13 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D60" t="s">
         <v>113</v>
       </c>
       <c r="E60" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F60" t="s">
         <v>115</v>
@@ -3146,13 +3146,13 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D61" t="s">
         <v>113</v>
       </c>
       <c r="E61" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
@@ -3169,13 +3169,13 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D62" t="s">
         <v>113</v>
       </c>
       <c r="E62" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
@@ -3192,13 +3192,13 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D63" t="s">
         <v>113</v>
       </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
@@ -3215,13 +3215,13 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D64" t="s">
         <v>113</v>
       </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
@@ -3238,13 +3238,13 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="D65" t="s">
         <v>113</v>
       </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="F65" t="s">
         <v>115</v>
@@ -3284,13 +3284,13 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D67" t="s">
         <v>113</v>
       </c>
       <c r="E67" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
@@ -3353,13 +3353,13 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D70" t="s">
         <v>113</v>
       </c>
       <c r="E70" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F70" t="s">
         <v>115</v>
@@ -3376,13 +3376,13 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D71" t="s">
         <v>113</v>
       </c>
       <c r="E71" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F71" t="s">
         <v>115</v>
@@ -3422,16 +3422,16 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="D73" t="s">
         <v>113</v>
       </c>
       <c r="E73" t="s">
+        <v>148</v>
+      </c>
+      <c r="F73" t="s">
         <v>125</v>
-      </c>
-      <c r="F73" t="s">
-        <v>115</v>
       </c>
       <c r="G73" t="s">
         <v>149</v>
@@ -3445,16 +3445,16 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="D74" t="s">
         <v>113</v>
       </c>
       <c r="E74" t="s">
+        <v>151</v>
+      </c>
+      <c r="F74" t="s">
         <v>125</v>
-      </c>
-      <c r="F74" t="s">
-        <v>115</v>
       </c>
       <c r="G74" t="s">
         <v>152</v>
@@ -3468,16 +3468,16 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="D75" t="s">
         <v>113</v>
       </c>
       <c r="E75" t="s">
+        <v>154</v>
+      </c>
+      <c r="F75" t="s">
         <v>125</v>
-      </c>
-      <c r="F75" t="s">
-        <v>115</v>
       </c>
       <c r="G75" t="s">
         <v>155</v>
@@ -3491,16 +3491,16 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="D76" t="s">
         <v>113</v>
       </c>
       <c r="E76" t="s">
+        <v>148</v>
+      </c>
+      <c r="F76" t="s">
         <v>125</v>
-      </c>
-      <c r="F76" t="s">
-        <v>115</v>
       </c>
       <c r="G76" t="s">
         <v>149</v>
@@ -3514,16 +3514,16 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
       </c>
       <c r="E77" t="s">
+        <v>148</v>
+      </c>
+      <c r="F77" t="s">
         <v>125</v>
-      </c>
-      <c r="F77" t="s">
-        <v>115</v>
       </c>
       <c r="G77" t="s">
         <v>149</v>
@@ -3537,16 +3537,16 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="D78" t="s">
         <v>113</v>
       </c>
       <c r="E78" t="s">
+        <v>151</v>
+      </c>
+      <c r="F78" t="s">
         <v>125</v>
-      </c>
-      <c r="F78" t="s">
-        <v>115</v>
       </c>
       <c r="G78" t="s">
         <v>152</v>
@@ -3560,16 +3560,16 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="D79" t="s">
         <v>113</v>
       </c>
       <c r="E79" t="s">
+        <v>160</v>
+      </c>
+      <c r="F79" t="s">
         <v>125</v>
-      </c>
-      <c r="F79" t="s">
-        <v>115</v>
       </c>
       <c r="G79" t="s">
         <v>161</v>
@@ -3583,16 +3583,16 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D80" t="s">
         <v>113</v>
       </c>
       <c r="E80" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F80" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="G80" t="s">
         <v>165</v>
@@ -3606,16 +3606,16 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D81" t="s">
         <v>113</v>
       </c>
       <c r="E81" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F81" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="G81" t="s">
         <v>165</v>
@@ -3629,16 +3629,16 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
         <v>113</v>
       </c>
       <c r="E82" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F82" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="G82" t="s">
         <v>165</v>
@@ -3675,13 +3675,13 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="D84" t="s">
         <v>113</v>
       </c>
       <c r="E84" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="F84" t="s">
         <v>115</v>
@@ -3698,13 +3698,13 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D85" t="s">
         <v>113</v>
       </c>
       <c r="E85" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F85" t="s">
         <v>115</v>
@@ -3721,16 +3721,16 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="D86" t="s">
         <v>113</v>
       </c>
       <c r="E86" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F86" t="s">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="G86" t="s">
         <v>176</v>
@@ -3744,13 +3744,13 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D87" t="s">
         <v>113</v>
       </c>
       <c r="E87" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F87" t="s">
         <v>115</v>
@@ -3767,13 +3767,13 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D88" t="s">
         <v>113</v>
       </c>
       <c r="E88" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F88" t="s">
         <v>115</v>
@@ -3790,13 +3790,13 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D89" t="s">
         <v>113</v>
       </c>
       <c r="E89" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F89" t="s">
         <v>115</v>
@@ -3813,16 +3813,16 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D90" t="s">
         <v>113</v>
       </c>
       <c r="E90" t="s">
+        <v>124</v>
+      </c>
+      <c r="F90" t="s">
         <v>125</v>
-      </c>
-      <c r="F90" t="s">
-        <v>115</v>
       </c>
       <c r="G90" t="s">
         <v>126</v>
@@ -3836,16 +3836,16 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>182</v>
+        <v>112</v>
       </c>
       <c r="D91" t="s">
         <v>113</v>
       </c>
       <c r="E91" t="s">
+        <v>182</v>
+      </c>
+      <c r="F91" t="s">
         <v>183</v>
-      </c>
-      <c r="F91" t="s">
-        <v>115</v>
       </c>
       <c r="G91" t="s">
         <v>184</v>
@@ -3859,16 +3859,16 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D92" t="s">
         <v>113</v>
       </c>
       <c r="E92" t="s">
+        <v>124</v>
+      </c>
+      <c r="F92" t="s">
         <v>125</v>
-      </c>
-      <c r="F92" t="s">
-        <v>115</v>
       </c>
       <c r="G92" t="s">
         <v>126</v>
@@ -3882,13 +3882,13 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D93" t="s">
         <v>113</v>
       </c>
       <c r="E93" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F93" t="s">
         <v>115</v>
@@ -3905,16 +3905,16 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D94" t="s">
         <v>113</v>
       </c>
       <c r="E94" t="s">
+        <v>124</v>
+      </c>
+      <c r="F94" t="s">
         <v>125</v>
-      </c>
-      <c r="F94" t="s">
-        <v>115</v>
       </c>
       <c r="G94" t="s">
         <v>126</v>
@@ -3928,13 +3928,13 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="D95" t="s">
         <v>113</v>
       </c>
       <c r="E95" t="s">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="F95" t="s">
         <v>115</v>
@@ -3951,16 +3951,16 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="D96" t="s">
         <v>113</v>
       </c>
       <c r="E96" t="s">
+        <v>124</v>
+      </c>
+      <c r="F96" t="s">
         <v>125</v>
-      </c>
-      <c r="F96" t="s">
-        <v>192</v>
       </c>
       <c r="G96" t="s">
         <v>126</v>
@@ -3974,16 +3974,16 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="D97" t="s">
         <v>113</v>
       </c>
       <c r="E97" t="s">
+        <v>124</v>
+      </c>
+      <c r="F97" t="s">
         <v>125</v>
-      </c>
-      <c r="F97" t="s">
-        <v>192</v>
       </c>
       <c r="G97" t="s">
         <v>126</v>
@@ -3997,16 +3997,16 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D98" t="s">
         <v>113</v>
       </c>
       <c r="E98" t="s">
+        <v>195</v>
+      </c>
+      <c r="F98" t="s">
         <v>196</v>
-      </c>
-      <c r="F98" t="s">
-        <v>192</v>
       </c>
       <c r="G98" t="s">
         <v>197</v>
@@ -4020,16 +4020,16 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="D99" t="s">
         <v>113</v>
       </c>
       <c r="E99" t="s">
+        <v>124</v>
+      </c>
+      <c r="F99" t="s">
         <v>125</v>
-      </c>
-      <c r="F99" t="s">
-        <v>192</v>
       </c>
       <c r="G99" t="s">
         <v>126</v>
@@ -4043,16 +4043,16 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="D100" t="s">
         <v>113</v>
       </c>
       <c r="E100" t="s">
+        <v>154</v>
+      </c>
+      <c r="F100" t="s">
         <v>125</v>
-      </c>
-      <c r="F100" t="s">
-        <v>192</v>
       </c>
       <c r="G100" t="s">
         <v>155</v>
@@ -4066,16 +4066,16 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="D101" t="s">
         <v>113</v>
       </c>
       <c r="E101" t="s">
+        <v>124</v>
+      </c>
+      <c r="F101" t="s">
         <v>125</v>
-      </c>
-      <c r="F101" t="s">
-        <v>192</v>
       </c>
       <c r="G101" t="s">
         <v>126</v>
@@ -4088,13 +4088,13 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>202</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>203</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>183</v>
       </c>
       <c r="G102" t="s">
@@ -4108,13 +4108,13 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>202</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>203</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>183</v>
       </c>
       <c r="G103" t="s">
@@ -4128,13 +4128,13 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>202</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>203</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>183</v>
       </c>
       <c r="G104" t="s">
@@ -4148,13 +4148,13 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
+        <v>202</v>
+      </c>
+      <c r="E105" t="s">
         <v>208</v>
       </c>
-      <c r="D105" t="s">
-        <v>203</v>
-      </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>183</v>
       </c>
       <c r="G105" t="s">
@@ -4168,13 +4168,13 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>202</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>203</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>183</v>
       </c>
       <c r="G106" t="s">
@@ -4188,13 +4188,13 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
+        <v>202</v>
+      </c>
+      <c r="E107" t="s">
         <v>182</v>
       </c>
-      <c r="D107" t="s">
-        <v>203</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>183</v>
       </c>
       <c r="G107" t="s">
@@ -4208,13 +4208,13 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
+        <v>202</v>
+      </c>
+      <c r="E108" t="s">
         <v>213</v>
       </c>
-      <c r="D108" t="s">
-        <v>203</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>183</v>
       </c>
       <c r="G108" t="s">
@@ -4228,13 +4228,13 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
+        <v>202</v>
+      </c>
+      <c r="E109" t="s">
         <v>216</v>
       </c>
-      <c r="D109" t="s">
-        <v>203</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>92</v>
       </c>
       <c r="G109" t="s">
@@ -4248,13 +4248,13 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
+        <v>202</v>
+      </c>
+      <c r="E110" t="s">
         <v>219</v>
       </c>
-      <c r="D110" t="s">
-        <v>203</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>92</v>
       </c>
       <c r="G110" t="s">
@@ -4268,13 +4268,13 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>202</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>203</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>183</v>
       </c>
       <c r="G111" t="s">
@@ -4288,13 +4288,13 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
+        <v>202</v>
+      </c>
+      <c r="E112" t="s">
         <v>223</v>
       </c>
-      <c r="D112" t="s">
-        <v>203</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>224</v>
       </c>
       <c r="G112" t="s">
@@ -4308,14 +4308,14 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="C113" t="s">
-        <v>112</v>
-      </c>
       <c r="D113" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E113" t="s">
         <v>114</v>
+      </c>
+      <c r="F113" t="s">
+        <v>115</v>
       </c>
       <c r="G113" t="s">
         <v>143</v>
@@ -4328,13 +4328,13 @@
       <c r="B114" t="s">
         <v>8</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
+        <v>202</v>
+      </c>
+      <c r="E114" t="s">
         <v>151</v>
       </c>
-      <c r="D114" t="s">
-        <v>203</v>
-      </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>125</v>
       </c>
       <c r="G114" t="s">
@@ -4348,13 +4348,13 @@
       <c r="B115" t="s">
         <v>8</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
+        <v>202</v>
+      </c>
+      <c r="E115" t="s">
         <v>182</v>
       </c>
-      <c r="D115" t="s">
-        <v>203</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>183</v>
       </c>
       <c r="G115" t="s">
@@ -4368,13 +4368,13 @@
       <c r="B116" t="s">
         <v>8</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
+        <v>202</v>
+      </c>
+      <c r="E116" t="s">
         <v>230</v>
       </c>
-      <c r="D116" t="s">
-        <v>203</v>
-      </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>224</v>
       </c>
       <c r="G116" t="s">
@@ -4388,13 +4388,13 @@
       <c r="B117" t="s">
         <v>8</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
+        <v>202</v>
+      </c>
+      <c r="E117" t="s">
         <v>223</v>
       </c>
-      <c r="D117" t="s">
-        <v>203</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>224</v>
       </c>
       <c r="G117" t="s">
@@ -4408,13 +4408,13 @@
       <c r="B118" t="s">
         <v>8</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
+        <v>202</v>
+      </c>
+      <c r="E118" t="s">
         <v>163</v>
       </c>
-      <c r="D118" t="s">
-        <v>203</v>
-      </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>164</v>
       </c>
       <c r="G118" t="s">
@@ -4428,13 +4428,13 @@
       <c r="B119" t="s">
         <v>8</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
+        <v>202</v>
+      </c>
+      <c r="E119" t="s">
         <v>182</v>
       </c>
-      <c r="D119" t="s">
-        <v>203</v>
-      </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>183</v>
       </c>
       <c r="G119" t="s">
@@ -4448,14 +4448,14 @@
       <c r="B120" t="s">
         <v>8</v>
       </c>
-      <c r="C120" t="s">
-        <v>170</v>
-      </c>
       <c r="D120" t="s">
         <v>237</v>
       </c>
       <c r="E120" t="s">
-        <v>114</v>
+        <v>170</v>
+      </c>
+      <c r="F120" t="s">
+        <v>115</v>
       </c>
       <c r="G120" t="s">
         <v>171</v>
@@ -4468,14 +4468,14 @@
       <c r="B121" t="s">
         <v>8</v>
       </c>
-      <c r="C121" t="s">
-        <v>112</v>
-      </c>
       <c r="D121" t="s">
         <v>237</v>
       </c>
       <c r="E121" t="s">
         <v>114</v>
+      </c>
+      <c r="F121" t="s">
+        <v>115</v>
       </c>
       <c r="G121" t="s">
         <v>143</v>
@@ -4488,14 +4488,14 @@
       <c r="B122" t="s">
         <v>8</v>
       </c>
-      <c r="C122" t="s">
-        <v>170</v>
-      </c>
       <c r="D122" t="s">
         <v>237</v>
       </c>
       <c r="E122" t="s">
-        <v>114</v>
+        <v>170</v>
+      </c>
+      <c r="F122" t="s">
+        <v>115</v>
       </c>
       <c r="G122" t="s">
         <v>171</v>
@@ -4508,14 +4508,14 @@
       <c r="B123" t="s">
         <v>8</v>
       </c>
-      <c r="C123" t="s">
-        <v>170</v>
-      </c>
       <c r="D123" t="s">
         <v>237</v>
       </c>
       <c r="E123" t="s">
-        <v>114</v>
+        <v>170</v>
+      </c>
+      <c r="F123" t="s">
+        <v>115</v>
       </c>
       <c r="G123" t="s">
         <v>171</v>
@@ -4528,13 +4528,13 @@
       <c r="B124" t="s">
         <v>8</v>
       </c>
-      <c r="C124" t="s">
-        <v>242</v>
-      </c>
       <c r="D124" t="s">
         <v>237</v>
       </c>
       <c r="E124" t="s">
+        <v>242</v>
+      </c>
+      <c r="F124" t="s">
         <v>164</v>
       </c>
       <c r="G124" t="s">
@@ -4548,13 +4548,13 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="C125" t="s">
-        <v>242</v>
-      </c>
       <c r="D125" t="s">
         <v>237</v>
       </c>
       <c r="E125" t="s">
+        <v>242</v>
+      </c>
+      <c r="F125" t="s">
         <v>164</v>
       </c>
       <c r="G125" t="s">
@@ -4568,13 +4568,13 @@
       <c r="B126" t="s">
         <v>8</v>
       </c>
-      <c r="C126" t="s">
-        <v>242</v>
-      </c>
       <c r="D126" t="s">
         <v>237</v>
       </c>
       <c r="E126" t="s">
+        <v>242</v>
+      </c>
+      <c r="F126" t="s">
         <v>164</v>
       </c>
       <c r="G126" t="s">
@@ -4588,13 +4588,13 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
-      <c r="C127" t="s">
-        <v>242</v>
-      </c>
       <c r="D127" t="s">
         <v>237</v>
       </c>
       <c r="E127" t="s">
+        <v>242</v>
+      </c>
+      <c r="F127" t="s">
         <v>164</v>
       </c>
       <c r="G127" t="s">
@@ -4608,13 +4608,13 @@
       <c r="B128" t="s">
         <v>8</v>
       </c>
-      <c r="C128" t="s">
-        <v>242</v>
-      </c>
       <c r="D128" t="s">
         <v>237</v>
       </c>
       <c r="E128" t="s">
+        <v>242</v>
+      </c>
+      <c r="F128" t="s">
         <v>164</v>
       </c>
       <c r="G128" t="s">
@@ -4628,13 +4628,13 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
-      <c r="C129" t="s">
-        <v>242</v>
-      </c>
       <c r="D129" t="s">
         <v>237</v>
       </c>
       <c r="E129" t="s">
+        <v>242</v>
+      </c>
+      <c r="F129" t="s">
         <v>164</v>
       </c>
       <c r="G129" t="s">
@@ -4648,13 +4648,13 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
-      <c r="C130" t="s">
-        <v>242</v>
-      </c>
       <c r="D130" t="s">
         <v>237</v>
       </c>
       <c r="E130" t="s">
+        <v>242</v>
+      </c>
+      <c r="F130" t="s">
         <v>164</v>
       </c>
       <c r="G130" t="s">
@@ -4668,13 +4668,13 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
-      <c r="C131" t="s">
-        <v>242</v>
-      </c>
       <c r="D131" t="s">
         <v>237</v>
       </c>
       <c r="E131" t="s">
+        <v>242</v>
+      </c>
+      <c r="F131" t="s">
         <v>164</v>
       </c>
       <c r="G131" t="s">
@@ -4688,13 +4688,13 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
-      <c r="C132" t="s">
-        <v>255</v>
-      </c>
       <c r="D132" t="s">
         <v>237</v>
       </c>
       <c r="E132" t="s">
+        <v>255</v>
+      </c>
+      <c r="F132" t="s">
         <v>164</v>
       </c>
       <c r="G132" t="s">
@@ -4708,14 +4708,14 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
-      <c r="C133" t="s">
-        <v>189</v>
-      </c>
       <c r="D133" t="s">
         <v>237</v>
       </c>
       <c r="E133" t="s">
-        <v>114</v>
+        <v>189</v>
+      </c>
+      <c r="F133" t="s">
+        <v>115</v>
       </c>
       <c r="G133" t="s">
         <v>190</v>
@@ -4728,13 +4728,13 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
-      <c r="C134" t="s">
-        <v>175</v>
-      </c>
       <c r="D134" t="s">
         <v>259</v>
       </c>
       <c r="E134" t="s">
+        <v>175</v>
+      </c>
+      <c r="F134" t="s">
         <v>164</v>
       </c>
       <c r="G134" t="s">
@@ -4748,13 +4748,13 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
-      <c r="C135" t="s">
-        <v>175</v>
-      </c>
       <c r="D135" t="s">
         <v>259</v>
       </c>
       <c r="E135" t="s">
+        <v>175</v>
+      </c>
+      <c r="F135" t="s">
         <v>164</v>
       </c>
       <c r="G135" t="s">
@@ -4768,13 +4768,13 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
-      <c r="C136" t="s">
-        <v>175</v>
-      </c>
       <c r="D136" t="s">
         <v>259</v>
       </c>
       <c r="E136" t="s">
+        <v>175</v>
+      </c>
+      <c r="F136" t="s">
         <v>164</v>
       </c>
       <c r="G136" t="s">
@@ -4788,13 +4788,13 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="C137" t="s">
-        <v>175</v>
-      </c>
       <c r="D137" t="s">
         <v>259</v>
       </c>
       <c r="E137" t="s">
+        <v>175</v>
+      </c>
+      <c r="F137" t="s">
         <v>164</v>
       </c>
       <c r="G137" t="s">
@@ -4808,13 +4808,13 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
-      <c r="C138" t="s">
-        <v>175</v>
-      </c>
       <c r="D138" t="s">
         <v>259</v>
       </c>
       <c r="E138" t="s">
+        <v>175</v>
+      </c>
+      <c r="F138" t="s">
         <v>164</v>
       </c>
       <c r="G138" t="s">
@@ -4828,13 +4828,13 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
-      <c r="C139" t="s">
-        <v>265</v>
-      </c>
       <c r="D139" t="s">
         <v>259</v>
       </c>
       <c r="E139" t="s">
+        <v>265</v>
+      </c>
+      <c r="F139" t="s">
         <v>224</v>
       </c>
       <c r="G139" t="s">
@@ -4848,13 +4848,13 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
-      <c r="C140" t="s">
-        <v>175</v>
-      </c>
       <c r="D140" t="s">
         <v>259</v>
       </c>
       <c r="E140" t="s">
+        <v>175</v>
+      </c>
+      <c r="F140" t="s">
         <v>164</v>
       </c>
       <c r="G140" t="s">
@@ -4875,10 +4875,10 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4898,10 +4898,10 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4915,16 +4915,16 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D143" t="s">
         <v>270</v>
       </c>
       <c r="E143" t="s">
-        <v>164</v>
+        <v>275</v>
       </c>
       <c r="F143" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G143" t="s">
         <v>276</v>
@@ -4938,16 +4938,16 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D144" t="s">
         <v>270</v>
       </c>
       <c r="E144" t="s">
-        <v>164</v>
+        <v>275</v>
       </c>
       <c r="F144" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G144" t="s">
         <v>276</v>
@@ -4961,16 +4961,16 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D145" t="s">
         <v>270</v>
       </c>
       <c r="E145" t="s">
-        <v>164</v>
+        <v>275</v>
       </c>
       <c r="F145" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G145" t="s">
         <v>276</v>
@@ -4990,10 +4990,10 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5007,16 +5007,16 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D147" t="s">
         <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="G147" t="s">
         <v>272</v>
@@ -5030,16 +5030,16 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D148" t="s">
         <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="G148" t="s">
         <v>272</v>
@@ -5053,16 +5053,16 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D149" t="s">
         <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="G149" t="s">
         <v>272</v>
@@ -5076,16 +5076,16 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D150" t="s">
         <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="G150" t="s">
         <v>272</v>
@@ -5099,16 +5099,16 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D151" t="s">
         <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="G151" t="s">
         <v>272</v>
@@ -5122,16 +5122,16 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D152" t="s">
         <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="G152" t="s">
         <v>272</v>
@@ -5145,16 +5145,16 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D153" t="s">
         <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="G153" t="s">
         <v>272</v>
@@ -5168,16 +5168,16 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D154" t="s">
         <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="G154" t="s">
         <v>272</v>
@@ -5191,16 +5191,16 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D155" t="s">
         <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="G155" t="s">
         <v>272</v>
@@ -5214,16 +5214,16 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D156" t="s">
         <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="G156" t="s">
         <v>272</v>
@@ -5237,16 +5237,16 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D157" t="s">
         <v>270</v>
       </c>
       <c r="E157" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F157" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="G157" t="s">
         <v>293</v>
@@ -5260,16 +5260,16 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D158" t="s">
         <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="G158" t="s">
         <v>272</v>
@@ -5283,16 +5283,16 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D159" t="s">
         <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="G159" t="s">
         <v>272</v>
@@ -5306,16 +5306,16 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D160" t="s">
         <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="G160" t="s">
         <v>272</v>
@@ -5329,16 +5329,16 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D161" t="s">
         <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="G161" t="s">
         <v>272</v>
@@ -5352,16 +5352,16 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="D162" t="s">
         <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>299</v>
+        <v>164</v>
       </c>
       <c r="G162" t="s">
         <v>272</v>
@@ -5375,16 +5375,16 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
         <v>270</v>
       </c>
       <c r="E163" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F163" t="s">
-        <v>301</v>
+        <v>164</v>
       </c>
       <c r="G163" t="s">
         <v>302</v>
@@ -5398,16 +5398,16 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D164" t="s">
         <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="G164" t="s">
         <v>272</v>
@@ -5421,16 +5421,16 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D165" t="s">
         <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="G165" t="s">
         <v>272</v>
@@ -5444,16 +5444,16 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D166" t="s">
         <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="G166" t="s">
         <v>272</v>
@@ -5467,16 +5467,16 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D167" t="s">
         <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="G167" t="s">
         <v>272</v>
@@ -5490,16 +5490,16 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D168" t="s">
         <v>270</v>
       </c>
       <c r="E168" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F168" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="G168" t="s">
         <v>309</v>
@@ -5513,16 +5513,16 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D169" t="s">
         <v>270</v>
       </c>
       <c r="E169" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F169" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="G169" t="s">
         <v>309</v>
@@ -5536,16 +5536,16 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D170" t="s">
         <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="G170" t="s">
         <v>272</v>
@@ -5558,13 +5558,13 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
-      <c r="C171" t="s">
-        <v>163</v>
-      </c>
       <c r="D171" t="s">
         <v>313</v>
       </c>
       <c r="E171" t="s">
+        <v>163</v>
+      </c>
+      <c r="F171" t="s">
         <v>164</v>
       </c>
       <c r="G171" t="s">
@@ -5578,14 +5578,14 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
-      <c r="C172" t="s">
-        <v>118</v>
-      </c>
       <c r="D172" t="s">
         <v>313</v>
       </c>
       <c r="E172" t="s">
-        <v>114</v>
+        <v>118</v>
+      </c>
+      <c r="F172" t="s">
+        <v>115</v>
       </c>
       <c r="G172" t="s">
         <v>119</v>
@@ -5598,13 +5598,13 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
-      <c r="C173" t="s">
-        <v>163</v>
-      </c>
       <c r="D173" t="s">
         <v>313</v>
       </c>
       <c r="E173" t="s">
+        <v>163</v>
+      </c>
+      <c r="F173" t="s">
         <v>164</v>
       </c>
       <c r="G173" t="s">
@@ -5618,13 +5618,13 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
-      <c r="C174" t="s">
-        <v>163</v>
-      </c>
       <c r="D174" t="s">
         <v>313</v>
       </c>
       <c r="E174" t="s">
+        <v>163</v>
+      </c>
+      <c r="F174" t="s">
         <v>164</v>
       </c>
       <c r="G174" t="s">
@@ -5638,13 +5638,13 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
-      <c r="C175" t="s">
-        <v>163</v>
-      </c>
       <c r="D175" t="s">
         <v>313</v>
       </c>
       <c r="E175" t="s">
+        <v>163</v>
+      </c>
+      <c r="F175" t="s">
         <v>164</v>
       </c>
       <c r="G175" t="s">
@@ -5658,13 +5658,13 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
-      <c r="C176" t="s">
-        <v>163</v>
-      </c>
       <c r="D176" t="s">
         <v>313</v>
       </c>
       <c r="E176" t="s">
+        <v>163</v>
+      </c>
+      <c r="F176" t="s">
         <v>164</v>
       </c>
       <c r="G176" t="s">
@@ -5678,13 +5678,13 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
-      <c r="C177" t="s">
-        <v>163</v>
-      </c>
       <c r="D177" t="s">
         <v>320</v>
       </c>
       <c r="E177" t="s">
+        <v>163</v>
+      </c>
+      <c r="F177" t="s">
         <v>164</v>
       </c>
       <c r="G177" t="s">
@@ -5698,13 +5698,13 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
-      <c r="C178" t="s">
-        <v>163</v>
-      </c>
       <c r="D178" t="s">
         <v>320</v>
       </c>
       <c r="E178" t="s">
+        <v>163</v>
+      </c>
+      <c r="F178" t="s">
         <v>164</v>
       </c>
       <c r="G178" t="s">
@@ -5718,13 +5718,13 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
-      <c r="C179" t="s">
-        <v>163</v>
-      </c>
       <c r="D179" t="s">
         <v>320</v>
       </c>
       <c r="E179" t="s">
+        <v>163</v>
+      </c>
+      <c r="F179" t="s">
         <v>164</v>
       </c>
       <c r="G179" t="s">
@@ -5738,13 +5738,13 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
-      <c r="C180" t="s">
-        <v>163</v>
-      </c>
       <c r="D180" t="s">
         <v>320</v>
       </c>
       <c r="E180" t="s">
+        <v>163</v>
+      </c>
+      <c r="F180" t="s">
         <v>164</v>
       </c>
       <c r="G180" t="s">
@@ -5765,10 +5765,10 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5788,10 +5788,10 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5811,10 +5811,10 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5834,10 +5834,10 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5857,10 +5857,10 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5880,10 +5880,10 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5903,10 +5903,10 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5926,10 +5926,10 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5949,10 +5949,10 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5972,10 +5972,10 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5995,10 +5995,10 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6018,10 +6018,10 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6035,16 +6035,16 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="D193" t="s">
         <v>326</v>
       </c>
       <c r="E193" t="s">
-        <v>164</v>
+        <v>275</v>
       </c>
       <c r="F193" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G193" t="s">
         <v>341</v>
@@ -6064,10 +6064,10 @@
         <v>326</v>
       </c>
       <c r="E194" t=